--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1625" uniqueCount="1625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="1626">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,103 +38,103 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58873558044434</t>
+    <t xml:space="preserve">2.58873581886292</t>
   </si>
   <si>
     <t xml:space="preserve">IG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5013575553894</t>
+    <t xml:space="preserve">2.50135779380798</t>
   </si>
   <si>
     <t xml:space="preserve">2.32790565490723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16488742828369</t>
+    <t xml:space="preserve">2.16488718986511</t>
   </si>
   <si>
     <t xml:space="preserve">2.17271208763123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09315896034241</t>
+    <t xml:space="preserve">2.09315872192383</t>
   </si>
   <si>
     <t xml:space="preserve">2.06185913085938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08663821220398</t>
+    <t xml:space="preserve">2.08663845062256</t>
   </si>
   <si>
     <t xml:space="preserve">2.04490542411804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06055545806885</t>
+    <t xml:space="preserve">2.06055521965027</t>
   </si>
   <si>
     <t xml:space="preserve">2.04360127449036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10489630699158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12967538833618</t>
+    <t xml:space="preserve">2.10489654541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1296751499176</t>
   </si>
   <si>
     <t xml:space="preserve">2.14532518386841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17923259735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2000994682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20140337944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17792892456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13228368759155</t>
+    <t xml:space="preserve">2.17923283576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20009922981262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20140314102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17792868614197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13228392601013</t>
   </si>
   <si>
     <t xml:space="preserve">2.09837555885315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22357392311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29138994216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33181858062744</t>
+    <t xml:space="preserve">2.22357416152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29138946533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33181810379028</t>
   </si>
   <si>
     <t xml:space="preserve">2.29791021347046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2379195690155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30051875114441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30443120002747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37094259262085</t>
+    <t xml:space="preserve">2.23791933059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30051851272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30443072319031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37094283103943</t>
   </si>
   <si>
     <t xml:space="preserve">2.3461639881134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3957211971283</t>
+    <t xml:space="preserve">2.39572167396545</t>
   </si>
   <si>
     <t xml:space="preserve">2.45571255683899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39702558517456</t>
+    <t xml:space="preserve">2.39702606201172</t>
   </si>
   <si>
     <t xml:space="preserve">2.38007187843323</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">2.39441752433777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42180442810059</t>
+    <t xml:space="preserve">2.42180418968201</t>
   </si>
   <si>
     <t xml:space="preserve">2.41006731987</t>
@@ -155,25 +155,25 @@
     <t xml:space="preserve">2.43745422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48701167106628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45049548149109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49092435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44527912139893</t>
+    <t xml:space="preserve">2.48701190948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45049571990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49092483520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4452793598175</t>
   </si>
   <si>
     <t xml:space="preserve">2.46614575386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43223834037781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44006252288818</t>
+    <t xml:space="preserve">2.43223738670349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44006276130676</t>
   </si>
   <si>
     <t xml:space="preserve">2.47788286209106</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">2.43615031242371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43354225158691</t>
+    <t xml:space="preserve">2.43354249000549</t>
   </si>
   <si>
     <t xml:space="preserve">2.4570164680481</t>
@@ -191,22 +191,22 @@
     <t xml:space="preserve">2.48831605911255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41789221763611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43484616279602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41267585754395</t>
+    <t xml:space="preserve">2.41789197921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43484592437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41267561912537</t>
   </si>
   <si>
     <t xml:space="preserve">2.35659694671631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27573990821838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29530191421509</t>
+    <t xml:space="preserve">2.27574014663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29530215263367</t>
   </si>
   <si>
     <t xml:space="preserve">2.31225609779358</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">2.38137602806091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40876293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39311337471008</t>
+    <t xml:space="preserve">2.40876317024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3931131362915</t>
   </si>
   <si>
     <t xml:space="preserve">2.44919180870056</t>
@@ -230,172 +230,172 @@
     <t xml:space="preserve">2.47397041320801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48440384864807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46353769302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47266626358032</t>
+    <t xml:space="preserve">2.48440361022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4635374546051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47266674041748</t>
   </si>
   <si>
     <t xml:space="preserve">2.47136235237122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4478874206543</t>
+    <t xml:space="preserve">2.44788718223572</t>
   </si>
   <si>
     <t xml:space="preserve">2.49614095687866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744534492493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51570320129395</t>
+    <t xml:space="preserve">2.49744510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51570343971252</t>
   </si>
   <si>
     <t xml:space="preserve">2.53135299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51439929008484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53656983375549</t>
+    <t xml:space="preserve">2.51439905166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53656959533691</t>
   </si>
   <si>
     <t xml:space="preserve">2.52744078636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5483067035675</t>
+    <t xml:space="preserve">2.54830718040466</t>
   </si>
   <si>
     <t xml:space="preserve">2.55091524124146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5378737449646</t>
+    <t xml:space="preserve">2.53787398338318</t>
   </si>
   <si>
     <t xml:space="preserve">2.58612728118896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57699847221375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59786462783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60438537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57308602333069</t>
+    <t xml:space="preserve">2.57699823379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59786486625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60438561439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57308578491211</t>
   </si>
   <si>
     <t xml:space="preserve">2.66959285736084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68393850326538</t>
+    <t xml:space="preserve">2.68393874168396</t>
   </si>
   <si>
     <t xml:space="preserve">2.69828414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64872646331787</t>
+    <t xml:space="preserve">2.64872622489929</t>
   </si>
   <si>
     <t xml:space="preserve">2.64742207527161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68133044242859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67480969429016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63438105583191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64350986480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69567561149597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69958806037903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67872166633606</t>
+    <t xml:space="preserve">2.68132996559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67480945587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63438081741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64350962638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69958853721619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67872190475464</t>
   </si>
   <si>
     <t xml:space="preserve">2.73480010032654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77262043952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75436210632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71262955665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70089268684387</t>
+    <t xml:space="preserve">2.772620677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7543625831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71262979507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70089244842529</t>
   </si>
   <si>
     <t xml:space="preserve">2.70219659805298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66176795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7830536365509</t>
+    <t xml:space="preserve">2.66176772117615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78305411338806</t>
   </si>
   <si>
     <t xml:space="preserve">2.7452335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6930673122406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71915078163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70610904693604</t>
+    <t xml:space="preserve">2.69306755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71915054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70610928535461</t>
   </si>
   <si>
     <t xml:space="preserve">2.74914598464966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77783727645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83522009849548</t>
+    <t xml:space="preserve">2.77783751487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8352198600769</t>
   </si>
   <si>
     <t xml:space="preserve">2.84043645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88738512992859</t>
+    <t xml:space="preserve">2.88738608360291</t>
   </si>
   <si>
     <t xml:space="preserve">2.89651489257812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85347771644592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91477274894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00867128372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02040934562683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96824264526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0073676109314</t>
+    <t xml:space="preserve">2.85347819328308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91477251052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00867104530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02040886878967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96824312210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00736784934998</t>
   </si>
   <si>
     <t xml:space="preserve">3.05822896957397</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">3.09885382652283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15591287612915</t>
+    <t xml:space="preserve">3.15591311454773</t>
   </si>
   <si>
     <t xml:space="preserve">3.09613728523254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13825178146362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0907027721405</t>
+    <t xml:space="preserve">3.13825154304504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09070253372192</t>
   </si>
   <si>
     <t xml:space="preserve">2.97658443450928</t>
@@ -425,142 +425,142 @@
     <t xml:space="preserve">3.20074486732483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24965310096741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28769254684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23063349723816</t>
+    <t xml:space="preserve">3.24965286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28769278526306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23063373565674</t>
   </si>
   <si>
     <t xml:space="preserve">3.24557733535767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22248244285583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25101161003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18715977668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09477877616882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11379814147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19938707351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10428833961487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12059092521667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15727186203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16270613670349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14504480361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03907775878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02820992469788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96707510948181</t>
+    <t xml:space="preserve">3.2224817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25101137161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18716025352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09477853775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11379790306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19938731193542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10428857803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12059116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15727138519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16270565986633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14504504203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03907752037048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02820944786072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96707439422607</t>
   </si>
   <si>
     <t xml:space="preserve">3.00375556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03636074066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02005839347839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.977942943573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9860942363739</t>
+    <t xml:space="preserve">3.03636050224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02005815505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97794318199158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98609447479248</t>
   </si>
   <si>
     <t xml:space="preserve">2.99560403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07575917243958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08390974998474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12466669082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10836410522461</t>
+    <t xml:space="preserve">3.07575869560242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0839102268219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12466621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10836434364319</t>
   </si>
   <si>
     <t xml:space="preserve">3.12874221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17900800704956</t>
+    <t xml:space="preserve">3.17900848388672</t>
   </si>
   <si>
     <t xml:space="preserve">3.17221593856812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12602519989014</t>
+    <t xml:space="preserve">3.12602496147156</t>
   </si>
   <si>
     <t xml:space="preserve">3.15863037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22519969940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26052141189575</t>
+    <t xml:space="preserve">3.22519946098328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26052165031433</t>
   </si>
   <si>
     <t xml:space="preserve">3.25237059593201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27682423591614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30671215057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30263662338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28090023994446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21025562286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28361701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29856085777283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2822585105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26323843002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25644612312317</t>
+    <t xml:space="preserve">3.27682447433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30671262741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30263686180115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2808997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21025466918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28361749649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29856109619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28225755691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26323866844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25644588470459</t>
   </si>
   <si>
     <t xml:space="preserve">3.27003169059753</t>
@@ -569,16 +569,16 @@
     <t xml:space="preserve">3.24693655967712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23335099220276</t>
+    <t xml:space="preserve">3.2333505153656</t>
   </si>
   <si>
     <t xml:space="preserve">3.21976494789124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2415018081665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26188039779663</t>
+    <t xml:space="preserve">3.24150156974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26188015937805</t>
   </si>
   <si>
     <t xml:space="preserve">3.23470902442932</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">3.19802832603455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23742604255676</t>
+    <t xml:space="preserve">3.23742628097534</t>
   </si>
   <si>
     <t xml:space="preserve">3.24829459190369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22791624069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1939525604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16542315483093</t>
+    <t xml:space="preserve">3.22791647911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19395232200623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16542291641235</t>
   </si>
   <si>
     <t xml:space="preserve">3.18444275856018</t>
@@ -608,94 +608,94 @@
     <t xml:space="preserve">3.18172550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20753812789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24014329910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26731467247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24286031723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.226557970047</t>
+    <t xml:space="preserve">3.20753836631775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2401430606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26731419563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24286079406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22655749320984</t>
   </si>
   <si>
     <t xml:space="preserve">3.2319917678833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20617938041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14640378952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16813993453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157132148743</t>
+    <t xml:space="preserve">3.20617961883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14640331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16814088821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157108306885</t>
   </si>
   <si>
     <t xml:space="preserve">3.16678166389465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21704816818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22927498817444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24421954154968</t>
+    <t xml:space="preserve">3.21704769134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22927474975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24421882629395</t>
   </si>
   <si>
     <t xml:space="preserve">3.21433091163635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25372838973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35154461860657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49147534370422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3936595916748</t>
+    <t xml:space="preserve">3.25372862815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35154414176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49147486686707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39365911483765</t>
   </si>
   <si>
     <t xml:space="preserve">3.46430420875549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50506067276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41675496101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40656566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44732213020325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4337363243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42694401741028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4710967540741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46770095825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48128581047058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50166392326355</t>
+    <t xml:space="preserve">3.50506091117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41675543785095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40656590461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44732260704041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43373656272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42694425582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47109699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46770071983337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.481285572052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50166487693787</t>
   </si>
   <si>
     <t xml:space="preserve">3.5424211025238</t>
@@ -707,37 +707,37 @@
     <t xml:space="preserve">3.54581713676453</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55940246582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6341233253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60015916824341</t>
+    <t xml:space="preserve">3.55940294265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412308692932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60015964508057</t>
   </si>
   <si>
     <t xml:space="preserve">3.53223133087158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48468255996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55261015892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61374497413635</t>
+    <t xml:space="preserve">3.4846818447113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55260992050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61374521255493</t>
   </si>
   <si>
     <t xml:space="preserve">3.52543902397156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58997011184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60355567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5933666229248</t>
+    <t xml:space="preserve">3.58996963500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60355544090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59336686134338</t>
   </si>
   <si>
     <t xml:space="preserve">3.62053751945496</t>
@@ -746,64 +746,64 @@
     <t xml:space="preserve">3.59676289558411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56619548797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45411515235901</t>
+    <t xml:space="preserve">3.5661952495575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53562808036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45411539077759</t>
   </si>
   <si>
     <t xml:space="preserve">3.45751166343689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39637684822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32301497459412</t>
+    <t xml:space="preserve">3.39637637138367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3230152130127</t>
   </si>
   <si>
     <t xml:space="preserve">3.38279128074646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40996193885803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38958358764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.328449010849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30807042121887</t>
+    <t xml:space="preserve">3.40996265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38958334922791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32844948768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30807065963745</t>
   </si>
   <si>
     <t xml:space="preserve">3.31078791618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35018539428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37599849700928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35426187515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37328124046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34339261054993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3664882183075</t>
+    <t xml:space="preserve">3.35018610954285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37599802017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35426211357117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37328171730042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34339308738708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36648869514465</t>
   </si>
   <si>
     <t xml:space="preserve">3.3787157535553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36105442047119</t>
+    <t xml:space="preserve">3.36105418205261</t>
   </si>
   <si>
     <t xml:space="preserve">3.12127017974854</t>
@@ -815,46 +815,46 @@
     <t xml:space="preserve">3.06624865531921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0458710193634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03228521347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00239682197571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02209568023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02549266815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04654979705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9942455291748</t>
+    <t xml:space="preserve">3.04587078094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03228545188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00239706039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02209615707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02549242973328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04655003547668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99424576759338</t>
   </si>
   <si>
     <t xml:space="preserve">2.96164059638977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9786229133606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092670440674</t>
+    <t xml:space="preserve">2.97862243652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092622756958</t>
   </si>
   <si>
     <t xml:space="preserve">3.11651515960693</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06828713417053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00035881996155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96639561653137</t>
+    <t xml:space="preserve">3.06828689575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00035929679871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96639537811279</t>
   </si>
   <si>
     <t xml:space="preserve">2.92903518676758</t>
@@ -863,82 +863,82 @@
     <t xml:space="preserve">2.924959897995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01326537132263</t>
+    <t xml:space="preserve">3.01326513290405</t>
   </si>
   <si>
     <t xml:space="preserve">3.0940990447998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1430070400238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2353880405426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22723698616028</t>
+    <t xml:space="preserve">3.14300656318665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23538875579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22723722457886</t>
   </si>
   <si>
     <t xml:space="preserve">3.21297216415405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19327282905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27342772483826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29448556900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20414161682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30739116668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28565454483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36377143859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39909386634827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47924828529358</t>
+    <t xml:space="preserve">3.19327354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27342748641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29448533058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20414209365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30739140510559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28565430641174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36377191543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39909410476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47924852371216</t>
   </si>
   <si>
     <t xml:space="preserve">3.475172996521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48196530342102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43713307380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44392585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49962663650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52815628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47788953781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51457023620605</t>
+    <t xml:space="preserve">3.4819655418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4371325969696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44392609596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49962639808655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52815556526184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4778892993927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51457071304321</t>
   </si>
   <si>
     <t xml:space="preserve">3.45886969566345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5267972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52000498771667</t>
+    <t xml:space="preserve">3.52679777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5200047492981</t>
   </si>
   <si>
     <t xml:space="preserve">3.57570552825928</t>
@@ -947,37 +947,37 @@
     <t xml:space="preserve">3.62733030319214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64499115943909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60423493385315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60287594795227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62597179412842</t>
+    <t xml:space="preserve">3.64499187469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60423469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60287642478943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62597155570984</t>
   </si>
   <si>
     <t xml:space="preserve">3.49419236183167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45615267753601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41539621353149</t>
+    <t xml:space="preserve">3.45615243911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41539597511292</t>
   </si>
   <si>
     <t xml:space="preserve">3.45479464530945</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44256734848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36309266090393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39298057556152</t>
+    <t xml:space="preserve">3.44256782531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36309242248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39298033714294</t>
   </si>
   <si>
     <t xml:space="preserve">3.39461994171143</t>
@@ -986,67 +986,67 @@
     <t xml:space="preserve">3.45400094985962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46107029914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36280822753906</t>
+    <t xml:space="preserve">3.46107006072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36280846595764</t>
   </si>
   <si>
     <t xml:space="preserve">3.28151273727417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23414897918701</t>
+    <t xml:space="preserve">3.23414921760559</t>
   </si>
   <si>
     <t xml:space="preserve">3.07367920875549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15285396575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18961358070374</t>
+    <t xml:space="preserve">3.16699194908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1528537273407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18961381912231</t>
   </si>
   <si>
     <t xml:space="preserve">3.27868509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25747752189636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23556303977966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23768401145935</t>
+    <t xml:space="preserve">3.2574770450592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23556327819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23768377304077</t>
   </si>
   <si>
     <t xml:space="preserve">3.20163106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34089422225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43774199485779</t>
+    <t xml:space="preserve">3.34089350700378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43774151802063</t>
   </si>
   <si>
     <t xml:space="preserve">3.39037775993347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41087865829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37624025344849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38967108726501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40946459770203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46319031715393</t>
+    <t xml:space="preserve">3.4108784198761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37624001502991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38967132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40946483612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46319103240967</t>
   </si>
   <si>
     <t xml:space="preserve">3.33735942840576</t>
@@ -1055,25 +1055,25 @@
     <t xml:space="preserve">3.3154444694519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29989242553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3444287776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35432505607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32958340644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3380663394928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29211640357971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3564465045929</t>
+    <t xml:space="preserve">3.29989266395569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34442830085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35432577133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32958364486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33806657791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29211664199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35644602775574</t>
   </si>
   <si>
     <t xml:space="preserve">3.3522047996521</t>
@@ -1082,49 +1082,49 @@
     <t xml:space="preserve">3.40098166465759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41865468025208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37765336036682</t>
+    <t xml:space="preserve">3.41865491867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3776535987854</t>
   </si>
   <si>
     <t xml:space="preserve">3.32534170150757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35573959350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34230804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40027523040771</t>
+    <t xml:space="preserve">3.3557391166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34230780601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40027499198914</t>
   </si>
   <si>
     <t xml:space="preserve">3.45258688926697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44834470748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4426896572113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45117259025574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41229271888733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40734457969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46036291122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43137955665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4787425994873</t>
+    <t xml:space="preserve">3.44834542274475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44269037246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4511730670929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41229319572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40734386444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46036267280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4313793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47874331474304</t>
   </si>
   <si>
     <t xml:space="preserve">3.42077589035034</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">3.42572450637817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51479601860046</t>
+    <t xml:space="preserve">3.51479578018188</t>
   </si>
   <si>
     <t xml:space="preserve">3.49429488182068</t>
@@ -1145,112 +1145,112 @@
     <t xml:space="preserve">3.41582727432251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42925906181335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4023962020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36139488220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38825750350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43279314041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33594560623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29706478118896</t>
+    <t xml:space="preserve">3.4292585849762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40239596366882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36139440536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3882577419281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43279337882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33594512939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29706525802612</t>
   </si>
   <si>
     <t xml:space="preserve">3.30413413047791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30837512016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2878749370575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31615138053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25182247161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28999614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33311820030212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3309965133667</t>
+    <t xml:space="preserve">3.3083758354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28787517547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3161518573761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25182223320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28999519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33311796188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33099699020386</t>
   </si>
   <si>
     <t xml:space="preserve">3.33382487297058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32675576210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34654879570007</t>
+    <t xml:space="preserve">3.32675552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34654951095581</t>
   </si>
   <si>
     <t xml:space="preserve">3.47450113296509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49924373626709</t>
+    <t xml:space="preserve">3.49924349784851</t>
   </si>
   <si>
     <t xml:space="preserve">3.49641609191895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46248364448547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45682811737061</t>
+    <t xml:space="preserve">3.46248340606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45682787895203</t>
   </si>
   <si>
     <t xml:space="preserve">3.45470786094666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38613629341125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45753479003906</t>
+    <t xml:space="preserve">3.38613653182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4575355052948</t>
   </si>
   <si>
     <t xml:space="preserve">3.45894908905029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37411856651306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39391279220581</t>
+    <t xml:space="preserve">3.37411880493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39391255378723</t>
   </si>
   <si>
     <t xml:space="preserve">3.42006874084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30978989601135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32816934585571</t>
+    <t xml:space="preserve">3.30978965759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32816958427429</t>
   </si>
   <si>
     <t xml:space="preserve">3.35715317726135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27797842025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24899482727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21011400222778</t>
+    <t xml:space="preserve">3.27797794342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24899458885193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21011424064636</t>
   </si>
   <si>
     <t xml:space="preserve">3.23485636711121</t>
@@ -1259,22 +1259,22 @@
     <t xml:space="preserve">3.20516586303711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15780234336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13093948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15356040000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24546027183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16911244392395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19809699058533</t>
+    <t xml:space="preserve">3.15780210494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13093900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15356063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24545979499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16911268234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19809651374817</t>
   </si>
   <si>
     <t xml:space="preserve">3.1889066696167</t>
@@ -1283,19 +1283,19 @@
     <t xml:space="preserve">3.23909783363342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23344230651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27727103233337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23202848434448</t>
+    <t xml:space="preserve">3.23344206809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27727127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23202872276306</t>
   </si>
   <si>
     <t xml:space="preserve">3.22920060157776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22495913505554</t>
+    <t xml:space="preserve">3.22495889663696</t>
   </si>
   <si>
     <t xml:space="preserve">3.2723228931427</t>
@@ -1307,103 +1307,103 @@
     <t xml:space="preserve">3.37341213226318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42501664161682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43491458892822</t>
+    <t xml:space="preserve">3.42501711845398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43491411209106</t>
   </si>
   <si>
     <t xml:space="preserve">3.48863959312439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44693183898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38755011558533</t>
+    <t xml:space="preserve">3.44693160057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38755083084106</t>
   </si>
   <si>
     <t xml:space="preserve">3.35927367210388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34160113334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30059957504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30484127998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27585768699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39603328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3493766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36068773269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3670494556427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39179229736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41653394699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45329427719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52327919006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59114265441895</t>
+    <t xml:space="preserve">3.34160137176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30060029029846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30484104156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27585744857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39603352546692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34937691688538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36068797111511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36705017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3917920589447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41653418540955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.453293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52327871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59114289283752</t>
   </si>
   <si>
     <t xml:space="preserve">3.61235022544861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63073039054871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61093664169312</t>
+    <t xml:space="preserve">3.63073015213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61093640327454</t>
   </si>
   <si>
     <t xml:space="preserve">3.62790250778198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60104012489319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59962558746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51055407524109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53176188468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57841801643372</t>
+    <t xml:space="preserve">3.60103964805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59962630271912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51055431365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53176116943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57841849327087</t>
   </si>
   <si>
     <t xml:space="preserve">3.61941933631897</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64911007881165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67880082130432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62083339691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68587040901184</t>
+    <t xml:space="preserve">3.64911031723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67880058288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62083387374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68587017059326</t>
   </si>
   <si>
     <t xml:space="preserve">3.70849084854126</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">3.68304204940796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68728375434875</t>
+    <t xml:space="preserve">3.68728399276733</t>
   </si>
   <si>
     <t xml:space="preserve">3.67738699913025</t>
@@ -1427,118 +1427,118 @@
     <t xml:space="preserve">3.71131896972656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70990538597107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72545719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7325267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73111248016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67173171043396</t>
+    <t xml:space="preserve">3.70990514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72545695304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73252630233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73111295700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6717312335968</t>
   </si>
   <si>
     <t xml:space="preserve">3.69293904304504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.719801902771</t>
+    <t xml:space="preserve">3.71980237960815</t>
   </si>
   <si>
     <t xml:space="preserve">3.63779950141907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61517739295959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68869733810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69576692581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6943531036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69718074798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68162798881531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75231981277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74383759498596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72262930870056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76504492759705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75938892364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71697425842285</t>
+    <t xml:space="preserve">3.61517834663391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68869709968567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69576668739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69435262680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69718027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68162894248962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75232028961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74383687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72262954711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76504445075989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7593891620636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71697354316711</t>
   </si>
   <si>
     <t xml:space="preserve">3.78342461585999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83997774124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86542725563049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83573698997498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8244252204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79756355285645</t>
+    <t xml:space="preserve">3.83997797966003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86542677879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83573651313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82442545890808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79756307601929</t>
   </si>
   <si>
     <t xml:space="preserve">3.81735682487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85977149009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86966848373413</t>
+    <t xml:space="preserve">3.8597719669342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86966824531555</t>
   </si>
   <si>
     <t xml:space="preserve">3.88380670547485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.875324010849</t>
+    <t xml:space="preserve">3.87532353401184</t>
   </si>
   <si>
     <t xml:space="preserve">3.89370369911194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88804864883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85270214080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87108182907104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89087605476379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84139251708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88239288330078</t>
+    <t xml:space="preserve">3.88804745674133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85270285606384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87108254432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89087629318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84139132499695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88239312171936</t>
   </si>
   <si>
     <t xml:space="preserve">3.92339444160461</t>
@@ -1547,112 +1547,112 @@
     <t xml:space="preserve">3.88946199417114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90360069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92056632041931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9191529750824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96439504623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95732641220093</t>
+    <t xml:space="preserve">3.90360045433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92056655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91915321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96439552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95732617378235</t>
   </si>
   <si>
     <t xml:space="preserve">3.91067004203796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9332914352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90642809867859</t>
+    <t xml:space="preserve">3.93329071998596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90642786026001</t>
   </si>
   <si>
     <t xml:space="preserve">3.90501427650452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92198061943054</t>
+    <t xml:space="preserve">3.92198014259338</t>
   </si>
   <si>
     <t xml:space="preserve">3.91208362579346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93046379089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87956547737122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89794492721558</t>
+    <t xml:space="preserve">3.9304633140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87956523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89794516563416</t>
   </si>
   <si>
     <t xml:space="preserve">3.88097929954529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94742965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89228940010071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87390995025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90925621986389</t>
+    <t xml:space="preserve">3.94743013381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89228987693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87390947341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90925645828247</t>
   </si>
   <si>
     <t xml:space="preserve">3.95025706291199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98136162757874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00963830947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08032941818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0789155960083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13016414642334</t>
+    <t xml:space="preserve">3.981360912323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00963878631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08033037185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07891654968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13016319274902</t>
   </si>
   <si>
     <t xml:space="preserve">4.16984796524048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21100282669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21394205093384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24921798706055</t>
+    <t xml:space="preserve">4.21100330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21394300460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24921846389771</t>
   </si>
   <si>
     <t xml:space="preserve">4.20512342453003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1948356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1228141784668</t>
+    <t xml:space="preserve">4.19483518600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12281465530396</t>
   </si>
   <si>
     <t xml:space="preserve">4.1081166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16543817520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21541261672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26979494094849</t>
+    <t xml:space="preserve">4.16543912887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21541213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26979541778564</t>
   </si>
   <si>
     <t xml:space="preserve">4.3050708770752</t>
@@ -1661,25 +1661,25 @@
     <t xml:space="preserve">4.32123899459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36827230453491</t>
+    <t xml:space="preserve">4.36827182769775</t>
   </si>
   <si>
     <t xml:space="preserve">4.33152723312378</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32564830780029</t>
+    <t xml:space="preserve">4.32564783096313</t>
   </si>
   <si>
     <t xml:space="preserve">4.288902759552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35651397705078</t>
+    <t xml:space="preserve">4.35651350021362</t>
   </si>
   <si>
     <t xml:space="preserve">4.34328556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49908542633057</t>
+    <t xml:space="preserve">4.49908590316772</t>
   </si>
   <si>
     <t xml:space="preserve">4.44764232635498</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">4.45352125167847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43735361099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35210418701172</t>
+    <t xml:space="preserve">4.43735313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35210466384888</t>
   </si>
   <si>
     <t xml:space="preserve">4.34181547164917</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">4.33446645736694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43147420883179</t>
+    <t xml:space="preserve">4.43147468566895</t>
   </si>
   <si>
     <t xml:space="preserve">4.47997808456421</t>
@@ -1718,13 +1718,13 @@
     <t xml:space="preserve">4.44911193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43882322311401</t>
+    <t xml:space="preserve">4.43882369995117</t>
   </si>
   <si>
     <t xml:space="preserve">4.49467658996582</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51966285705566</t>
+    <t xml:space="preserve">4.51966238021851</t>
   </si>
   <si>
     <t xml:space="preserve">4.50349473953247</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">4.57698535919189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52701139450073</t>
+    <t xml:space="preserve">4.52701187133789</t>
   </si>
   <si>
     <t xml:space="preserve">4.54170989990234</t>
@@ -1754,22 +1754,22 @@
     <t xml:space="preserve">4.43588352203369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4255952835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38884973526001</t>
+    <t xml:space="preserve">4.42559480667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38885021209717</t>
   </si>
   <si>
     <t xml:space="preserve">4.38150072097778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24480867385864</t>
+    <t xml:space="preserve">4.2448091506958</t>
   </si>
   <si>
     <t xml:space="preserve">4.20218420028687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29037189483643</t>
+    <t xml:space="preserve">4.29037237167358</t>
   </si>
   <si>
     <t xml:space="preserve">4.29331254959106</t>
@@ -1781,13 +1781,13 @@
     <t xml:space="preserve">4.26097631454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2844934463501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28743362426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11399555206299</t>
+    <t xml:space="preserve">4.28449296951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28743314743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11399507522583</t>
   </si>
   <si>
     <t xml:space="preserve">4.16102933883667</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">4.24186897277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15661954879761</t>
+    <t xml:space="preserve">4.15662002563477</t>
   </si>
   <si>
     <t xml:space="preserve">4.30360078811646</t>
@@ -1808,7 +1808,7 @@
     <t xml:space="preserve">4.20071411132812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1977744102478</t>
+    <t xml:space="preserve">4.19777488708496</t>
   </si>
   <si>
     <t xml:space="preserve">4.34034633636475</t>
@@ -1817,10 +1817,10 @@
     <t xml:space="preserve">4.33593702316284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34916543960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.313889503479</t>
+    <t xml:space="preserve">4.34916496276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31388998031616</t>
   </si>
   <si>
     <t xml:space="preserve">4.30213117599487</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">4.20806312561035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14192199707031</t>
+    <t xml:space="preserve">4.14192247390747</t>
   </si>
   <si>
     <t xml:space="preserve">4.1037073135376</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">4.14045190811157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12575387954712</t>
+    <t xml:space="preserve">4.12575435638428</t>
   </si>
   <si>
     <t xml:space="preserve">4.1933650970459</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">4.18160676956177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18454599380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25215721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29919147491455</t>
+    <t xml:space="preserve">4.18454647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25215768814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29919099807739</t>
   </si>
   <si>
     <t xml:space="preserve">4.39031934738159</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">4.30066108703613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21247243881226</t>
+    <t xml:space="preserve">4.2124719619751</t>
   </si>
   <si>
     <t xml:space="preserve">4.31241941452026</t>
@@ -1883,16 +1883,16 @@
     <t xml:space="preserve">4.18895530700684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011016845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18748617172241</t>
+    <t xml:space="preserve">4.23011064529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18748569488525</t>
   </si>
   <si>
     <t xml:space="preserve">4.17425727844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1727876663208</t>
+    <t xml:space="preserve">4.17278814315796</t>
   </si>
   <si>
     <t xml:space="preserve">4.14486122131348</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">4.16837882995605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18013715744019</t>
+    <t xml:space="preserve">4.18013668060303</t>
   </si>
   <si>
     <t xml:space="preserve">4.238929271698</t>
@@ -1910,43 +1910,43 @@
     <t xml:space="preserve">4.25362777709961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29478168487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33740615844727</t>
+    <t xml:space="preserve">4.29478216171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33740663528442</t>
   </si>
   <si>
     <t xml:space="preserve">4.35063457489014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28302335739136</t>
+    <t xml:space="preserve">4.28302383422852</t>
   </si>
   <si>
     <t xml:space="preserve">4.33299732208252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30654048919678</t>
+    <t xml:space="preserve">4.30654001235962</t>
   </si>
   <si>
     <t xml:space="preserve">4.37268161773682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39178943634033</t>
+    <t xml:space="preserve">4.39178895950317</t>
   </si>
   <si>
     <t xml:space="preserve">4.27861404418945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22423124313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23745918273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22570037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19189500808716</t>
+    <t xml:space="preserve">4.22423076629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23745965957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22570133209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19189596176147</t>
   </si>
   <si>
     <t xml:space="preserve">4.22129106521606</t>
@@ -1955,13 +1955,13 @@
     <t xml:space="preserve">4.23599004745483</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22717094421387</t>
+    <t xml:space="preserve">4.22717046737671</t>
   </si>
   <si>
     <t xml:space="preserve">4.00963926315308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07431125640869</t>
+    <t xml:space="preserve">4.07431077957153</t>
   </si>
   <si>
     <t xml:space="preserve">4.08900833129883</t>
@@ -1973,49 +1973,49 @@
     <t xml:space="preserve">4.01992702484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95378637313843</t>
+    <t xml:space="preserve">3.95378613471985</t>
   </si>
   <si>
     <t xml:space="preserve">3.99494099617004</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0419750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99053120613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0360951423645</t>
+    <t xml:space="preserve">4.04197406768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99053168296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03609561920166</t>
   </si>
   <si>
     <t xml:space="preserve">4.10664653778076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16396951675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12722396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13751220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00082063674927</t>
+    <t xml:space="preserve">4.16396903991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1272234916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13751268386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00081968307495</t>
   </si>
   <si>
     <t xml:space="preserve">4.09194803237915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08459901809692</t>
+    <t xml:space="preserve">4.08459949493408</t>
   </si>
   <si>
     <t xml:space="preserve">4.02727651596069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02286767959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10076713562012</t>
+    <t xml:space="preserve">4.02286720275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10076761245728</t>
   </si>
   <si>
     <t xml:space="preserve">4.20365381240845</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">4.13898229598999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25068807601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20659303665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.263916015625</t>
+    <t xml:space="preserve">4.25068759918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20659351348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26391649246216</t>
   </si>
   <si>
     <t xml:space="preserve">4.30801010131836</t>
@@ -2039,25 +2039,25 @@
     <t xml:space="preserve">4.48144769668579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5152530670166</t>
+    <t xml:space="preserve">4.51525354385376</t>
   </si>
   <si>
     <t xml:space="preserve">4.49761533737183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40648698806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41677665710449</t>
+    <t xml:space="preserve">4.40648746490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41677618026733</t>
   </si>
   <si>
     <t xml:space="preserve">4.46674966812134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49173641204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46087026596069</t>
+    <t xml:space="preserve">4.4917368888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46087074279785</t>
   </si>
   <si>
     <t xml:space="preserve">4.46234035491943</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">4.45205163955688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48585748672485</t>
+    <t xml:space="preserve">4.48585653305054</t>
   </si>
   <si>
     <t xml:space="preserve">4.62548923492432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26538610458374</t>
+    <t xml:space="preserve">4.26538515090942</t>
   </si>
   <si>
     <t xml:space="preserve">4.26244640350342</t>
@@ -2084,16 +2084,16 @@
     <t xml:space="preserve">4.06549215316772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08606958389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72890496253967</t>
+    <t xml:space="preserve">4.08606863021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72890543937683</t>
   </si>
   <si>
     <t xml:space="preserve">3.51798820495605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50182008743286</t>
+    <t xml:space="preserve">3.5018196105957</t>
   </si>
   <si>
     <t xml:space="preserve">3.02192735671997</t>
@@ -2102,76 +2102,76 @@
     <t xml:space="preserve">3.24754309654236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15127062797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27032470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29531240463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35189962387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21153259277344</t>
+    <t xml:space="preserve">3.15127086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27032494544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29531192779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35189938545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21153283119202</t>
   </si>
   <si>
     <t xml:space="preserve">3.12995839118958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35557436943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38937926292419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34381604194641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35924816131592</t>
+    <t xml:space="preserve">3.35557413101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38937950134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34381532669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3592483997345</t>
   </si>
   <si>
     <t xml:space="preserve">3.5709011554718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66643905639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44964146614075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55693793296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58780336380005</t>
+    <t xml:space="preserve">3.66643857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44964170455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55693817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58780384063721</t>
   </si>
   <si>
     <t xml:space="preserve">3.53636026382446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54958915710449</t>
+    <t xml:space="preserve">3.54958868026733</t>
   </si>
   <si>
     <t xml:space="preserve">3.4658100605011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54811882972717</t>
+    <t xml:space="preserve">3.54811859130859</t>
   </si>
   <si>
     <t xml:space="preserve">3.56428694725037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59368300437927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6260187625885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57163596153259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57310557365417</t>
+    <t xml:space="preserve">3.59368276596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62601900100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57163572311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57310605049133</t>
   </si>
   <si>
     <t xml:space="preserve">3.44082307815552</t>
@@ -2180,22 +2180,22 @@
     <t xml:space="preserve">3.61720013618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52754139900208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57457566261292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56722688674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5789852142334</t>
+    <t xml:space="preserve">3.52754187583923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57457542419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56722640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57898545265198</t>
   </si>
   <si>
     <t xml:space="preserve">3.75168776512146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68187141418457</t>
+    <t xml:space="preserve">3.68187189102173</t>
   </si>
   <si>
     <t xml:space="preserve">3.70391869544983</t>
@@ -2210,10 +2210,10 @@
     <t xml:space="preserve">3.66423416137695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63189768791199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62454867362976</t>
+    <t xml:space="preserve">3.63189816474915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6245493888855</t>
   </si>
   <si>
     <t xml:space="preserve">3.63777732849121</t>
@@ -2228,28 +2228,28 @@
     <t xml:space="preserve">3.73626279830933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60662722587585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66372919082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63440656661987</t>
+    <t xml:space="preserve">3.60662746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66372871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63440632820129</t>
   </si>
   <si>
     <t xml:space="preserve">3.68533492088318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75015234947205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73008918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70231080055237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80725336074829</t>
+    <t xml:space="preserve">3.75015211105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73008966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70231056213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80725288391113</t>
   </si>
   <si>
     <t xml:space="preserve">3.77021479606628</t>
@@ -2258,34 +2258,34 @@
     <t xml:space="preserve">3.81959939002991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90447950363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99707508087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05108976364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02408361434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92762899398804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8813304901123</t>
+    <t xml:space="preserve">3.90447926521301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99707531929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05109024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02408266067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92762875556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88133025169373</t>
   </si>
   <si>
     <t xml:space="preserve">3.81651282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9199116230011</t>
+    <t xml:space="preserve">3.91991209983826</t>
   </si>
   <si>
     <t xml:space="preserve">4.08581352233887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05880689620972</t>
+    <t xml:space="preserve">4.0588059425354</t>
   </si>
   <si>
     <t xml:space="preserve">4.10896253585815</t>
@@ -2309,22 +2309,22 @@
     <t xml:space="preserve">4.08967208862305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03179931640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07038164138794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11282110214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0549488067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95463538169861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96235227584839</t>
+    <t xml:space="preserve">4.03179883956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07038116455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11282062530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05494832992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95463585853577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96235203742981</t>
   </si>
   <si>
     <t xml:space="preserve">3.93534445762634</t>
@@ -2333,19 +2333,19 @@
     <t xml:space="preserve">3.97006821632385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07423973083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12439489364624</t>
+    <t xml:space="preserve">3.97392630577087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0742392539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1243953704834</t>
   </si>
   <si>
     <t xml:space="preserve">4.10510492324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09353017807007</t>
+    <t xml:space="preserve">4.09352970123291</t>
   </si>
   <si>
     <t xml:space="preserve">4.04723167419434</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">4.12825345993042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2594313621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26714849472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21313333511353</t>
+    <t xml:space="preserve">4.25943183898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26714897155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21313381195068</t>
   </si>
   <si>
     <t xml:space="preserve">4.19770097732544</t>
@@ -2381,13 +2381,13 @@
     <t xml:space="preserve">4.36746120452881</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42147541046143</t>
+    <t xml:space="preserve">4.42147588729858</t>
   </si>
   <si>
     <t xml:space="preserve">4.3906102180481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37517738342285</t>
+    <t xml:space="preserve">4.37517786026001</t>
   </si>
   <si>
     <t xml:space="preserve">4.36360311508179</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">4.30572986602783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26329040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24399900436401</t>
+    <t xml:space="preserve">4.26328992843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24399948120117</t>
   </si>
   <si>
     <t xml:space="preserve">4.31344652175903</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">4.30187129974365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13597059249878</t>
+    <t xml:space="preserve">4.13597011566162</t>
   </si>
   <si>
     <t xml:space="preserve">4.22856616973877</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">4.18612670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17455196380615</t>
+    <t xml:space="preserve">4.17455148696899</t>
   </si>
   <si>
     <t xml:space="preserve">4.18998432159424</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">4.17841005325317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15526151657104</t>
+    <t xml:space="preserve">4.15526103973389</t>
   </si>
   <si>
     <t xml:space="preserve">4.15140295028687</t>
@@ -2438,52 +2438,52 @@
     <t xml:space="preserve">4.15911960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19384288787842</t>
+    <t xml:space="preserve">4.19384241104126</t>
   </si>
   <si>
     <t xml:space="preserve">4.07809782028198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89290475845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97778487205505</t>
+    <t xml:space="preserve">3.89290452003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9777843952179</t>
   </si>
   <si>
     <t xml:space="preserve">4.06266450881958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94691967964172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98550128936768</t>
+    <t xml:space="preserve">3.94691920280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9855010509491</t>
   </si>
   <si>
     <t xml:space="preserve">3.98164296150208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88904643058777</t>
+    <t xml:space="preserve">3.88904595375061</t>
   </si>
   <si>
     <t xml:space="preserve">3.71157050132751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72700309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82885885238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83194541931152</t>
+    <t xml:space="preserve">3.72700262069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8288586139679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8319456577301</t>
   </si>
   <si>
     <t xml:space="preserve">3.86589789390564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00479221343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95077705383301</t>
+    <t xml:space="preserve">4.00479125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95077776908875</t>
   </si>
   <si>
     <t xml:space="preserve">4.08195543289185</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">4.03951549530029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1398286819458</t>
+    <t xml:space="preserve">4.13982772827148</t>
   </si>
   <si>
     <t xml:space="preserve">4.17069387435913</t>
@@ -2501,22 +2501,22 @@
     <t xml:space="preserve">4.14368629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13211154937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93920278549194</t>
+    <t xml:space="preserve">4.1321120262146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93920302391052</t>
   </si>
   <si>
     <t xml:space="preserve">3.90062117576599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80879640579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9932177066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01250839233398</t>
+    <t xml:space="preserve">3.80879664421082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99321818351746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01250791549683</t>
   </si>
   <si>
     <t xml:space="preserve">3.95849394798279</t>
@@ -2528,19 +2528,19 @@
     <t xml:space="preserve">3.93148589134216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92377066612244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86203980445862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81805634498596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80570983886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85818099975586</t>
+    <t xml:space="preserve">3.92377018928528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86203932762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81805610656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80571031570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85818123817444</t>
   </si>
   <si>
     <t xml:space="preserve">3.89676308631897</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">3.85663795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82114291191101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83811807632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9430615901947</t>
+    <t xml:space="preserve">3.82114267349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83811902999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94306111335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.90833783149719</t>
@@ -2564,22 +2564,22 @@
     <t xml:space="preserve">3.88518834114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83503150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7671275138855</t>
+    <t xml:space="preserve">3.83503174781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76712822914124</t>
   </si>
   <si>
     <t xml:space="preserve">3.76249814033508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8226854801178</t>
+    <t xml:space="preserve">3.82268571853638</t>
   </si>
   <si>
     <t xml:space="preserve">3.79799342155457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87361335754395</t>
+    <t xml:space="preserve">3.87361407279968</t>
   </si>
   <si>
     <t xml:space="preserve">4.02794075012207</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">4.25171566009521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25557327270508</t>
+    <t xml:space="preserve">4.25557374954224</t>
   </si>
   <si>
     <t xml:space="preserve">4.3173041343689</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">4.14985942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12979745864868</t>
+    <t xml:space="preserve">4.12979698181152</t>
   </si>
   <si>
     <t xml:space="preserve">4.14059972763062</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">4.16837930679321</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17146587371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19924449920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23628282546997</t>
+    <t xml:space="preserve">4.1714653968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19924402236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23628234863281</t>
   </si>
   <si>
     <t xml:space="preserve">4.18844127655029</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">4.1776385307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17918109893799</t>
+    <t xml:space="preserve">4.17918157577515</t>
   </si>
   <si>
     <t xml:space="preserve">4.1838116645813</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">4.20387411117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18535470962524</t>
+    <t xml:space="preserve">4.18535423278809</t>
   </si>
   <si>
     <t xml:space="preserve">4.21622037887573</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">4.29338407516479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23165369033813</t>
+    <t xml:space="preserve">4.23165321350098</t>
   </si>
   <si>
     <t xml:space="preserve">4.25017213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23782587051392</t>
+    <t xml:space="preserve">4.23782634735107</t>
   </si>
   <si>
     <t xml:space="preserve">4.35048532485962</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">4.34122562408447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39369678497314</t>
+    <t xml:space="preserve">4.39369630813599</t>
   </si>
   <si>
     <t xml:space="preserve">4.47086048126221</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">4.46610307693481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44025039672852</t>
+    <t xml:space="preserve">4.44024991989136</t>
   </si>
   <si>
     <t xml:space="preserve">4.3885440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35622835159302</t>
+    <t xml:space="preserve">4.35622787475586</t>
   </si>
   <si>
     <t xml:space="preserve">4.38531255722046</t>
@@ -2702,19 +2702,19 @@
     <t xml:space="preserve">4.37400197982788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39016008377075</t>
+    <t xml:space="preserve">4.39015960693359</t>
   </si>
   <si>
     <t xml:space="preserve">4.37723398208618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40147113800049</t>
+    <t xml:space="preserve">4.40147066116333</t>
   </si>
   <si>
     <t xml:space="preserve">4.45156097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47418260574341</t>
+    <t xml:space="preserve">4.47418212890625</t>
   </si>
   <si>
     <t xml:space="preserve">4.49357175827026</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">4.52911996841431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55174112319946</t>
+    <t xml:space="preserve">4.55174160003662</t>
   </si>
   <si>
     <t xml:space="preserve">4.55012512207031</t>
@@ -2735,16 +2735,16 @@
     <t xml:space="preserve">4.62122058868408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58405685424805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56628370285034</t>
+    <t xml:space="preserve">4.58405733108521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56628322601318</t>
   </si>
   <si>
     <t xml:space="preserve">4.54527807235718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52750444412231</t>
+    <t xml:space="preserve">4.52750396728516</t>
   </si>
   <si>
     <t xml:space="preserve">4.45640802383423</t>
@@ -2756,19 +2756,19 @@
     <t xml:space="preserve">4.48226118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48710870742798</t>
+    <t xml:space="preserve">4.48710918426514</t>
   </si>
   <si>
     <t xml:space="preserve">4.45317697525024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46771907806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49841928482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50649833679199</t>
+    <t xml:space="preserve">4.46771955490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49841976165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50649881362915</t>
   </si>
   <si>
     <t xml:space="preserve">4.55335712432861</t>
@@ -2777,10 +2777,10 @@
     <t xml:space="preserve">4.4790301322937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52265739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54204702377319</t>
+    <t xml:space="preserve">4.52265644073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54204654693604</t>
   </si>
   <si>
     <t xml:space="preserve">4.54689359664917</t>
@@ -2792,10 +2792,10 @@
     <t xml:space="preserve">4.37884902954102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35461235046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37238645553589</t>
+    <t xml:space="preserve">4.35461282730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37238597869873</t>
   </si>
   <si>
     <t xml:space="preserve">4.53719902038574</t>
@@ -2810,19 +2810,19 @@
     <t xml:space="preserve">4.6147575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61637401580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62768411636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59375286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60829448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63091611862183</t>
+    <t xml:space="preserve">4.61637353897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62768459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59375190734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60829496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63091564178467</t>
   </si>
   <si>
     <t xml:space="preserve">4.65676927566528</t>
@@ -2837,34 +2837,34 @@
     <t xml:space="preserve">4.73271179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76502799987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80219221115112</t>
+    <t xml:space="preserve">4.76502847671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80219173431396</t>
   </si>
   <si>
     <t xml:space="preserve">4.79896068572998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76987504959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82804441452026</t>
+    <t xml:space="preserve">4.76987600326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.82481384277344</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84420299530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80703973770142</t>
+    <t xml:space="preserve">4.84420347213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80703926086426</t>
   </si>
   <si>
     <t xml:space="preserve">4.69554853439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57436275482178</t>
+    <t xml:space="preserve">4.57436323165894</t>
   </si>
   <si>
     <t xml:space="preserve">4.53558301925659</t>
@@ -2873,10 +2873,10 @@
     <t xml:space="preserve">4.59213638305664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54366159439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49034023284912</t>
+    <t xml:space="preserve">4.54366207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49034070968628</t>
   </si>
   <si>
     <t xml:space="preserve">4.49195623397827</t>
@@ -2885,13 +2885,13 @@
     <t xml:space="preserve">4.48549270629883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45964002609253</t>
+    <t xml:space="preserve">4.45964050292969</t>
   </si>
   <si>
     <t xml:space="preserve">4.51134586334229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52427196502686</t>
+    <t xml:space="preserve">4.52427244186401</t>
   </si>
   <si>
     <t xml:space="preserve">4.46125555038452</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">4.58567380905151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63576316833496</t>
+    <t xml:space="preserve">4.63576364517212</t>
   </si>
   <si>
     <t xml:space="preserve">4.58890438079834</t>
@@ -2909,31 +2909,31 @@
     <t xml:space="preserve">4.65353727340698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57113075256348</t>
+    <t xml:space="preserve">4.57113122940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.4757981300354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42247581481934</t>
+    <t xml:space="preserve">4.42247629165649</t>
   </si>
   <si>
     <t xml:space="preserve">4.46933507919312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43217134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47095060348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48387765884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39985513687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37076997756958</t>
+    <t xml:space="preserve">4.43217182159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47095108032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48387718200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39985466003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37077045440674</t>
   </si>
   <si>
     <t xml:space="preserve">4.39662313461304</t>
@@ -2942,16 +2942,16 @@
     <t xml:space="preserve">4.41116571426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51457738876343</t>
+    <t xml:space="preserve">4.51457786560059</t>
   </si>
   <si>
     <t xml:space="preserve">4.46287155151367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43540287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50003480911255</t>
+    <t xml:space="preserve">4.43540239334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50003528594971</t>
   </si>
   <si>
     <t xml:space="preserve">4.53881454467773</t>
@@ -2960,10 +2960,10 @@
     <t xml:space="preserve">4.61314249038696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63253211975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60021591186523</t>
+    <t xml:space="preserve">4.63253164291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60021543502808</t>
   </si>
   <si>
     <t xml:space="preserve">4.55658864974976</t>
@@ -2975,13 +2975,13 @@
     <t xml:space="preserve">4.52588844299316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48064517974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53235197067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44832944869995</t>
+    <t xml:space="preserve">4.48064565658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53235149383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44832992553711</t>
   </si>
   <si>
     <t xml:space="preserve">4.5048828125</t>
@@ -2996,37 +2996,37 @@
     <t xml:space="preserve">4.65838479995728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68262195587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65515279769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64384269714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7020115852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68585348129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70362758636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6680793762207</t>
+    <t xml:space="preserve">4.68262147903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65515327453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6438422203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70201206207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68585395812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7036280632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66807985305786</t>
   </si>
   <si>
     <t xml:space="preserve">4.64545822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72624826431274</t>
+    <t xml:space="preserve">4.7262487411499</t>
   </si>
   <si>
     <t xml:space="preserve">4.76179695129395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75048589706421</t>
+    <t xml:space="preserve">4.75048637390137</t>
   </si>
   <si>
     <t xml:space="preserve">4.84905052185059</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">4.87490367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88944625854492</t>
+    <t xml:space="preserve">4.88944530487061</t>
   </si>
   <si>
     <t xml:space="preserve">4.91853046417236</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">4.66161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64061069488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7294807434082</t>
+    <t xml:space="preserve">4.64061117172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72948026657104</t>
   </si>
   <si>
     <t xml:space="preserve">4.74402284622192</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">4.74079132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79734468460083</t>
+    <t xml:space="preserve">4.79734516143799</t>
   </si>
   <si>
     <t xml:space="preserve">4.71655368804932</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">4.83450841903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74563837051392</t>
+    <t xml:space="preserve">4.74563884735107</t>
   </si>
   <si>
     <t xml:space="preserve">4.50972986221313</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">4.62930059432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55982065200806</t>
+    <t xml:space="preserve">4.5598201751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.54850959777832</t>
@@ -3107,31 +3107,31 @@
     <t xml:space="preserve">4.35299634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32068014144897</t>
+    <t xml:space="preserve">4.32068061828613</t>
   </si>
   <si>
     <t xml:space="preserve">4.55820465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51780891418457</t>
+    <t xml:space="preserve">4.51780939102173</t>
   </si>
   <si>
     <t xml:space="preserve">4.49518775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4176287651062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48872518539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43378734588623</t>
+    <t xml:space="preserve">4.41762828826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48872470855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43378686904907</t>
   </si>
   <si>
     <t xml:space="preserve">4.70524311065674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7302885055542</t>
+    <t xml:space="preserve">4.73028898239136</t>
   </si>
   <si>
     <t xml:space="preserve">4.68181419372559</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">4.77472305297852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89590930938721</t>
+    <t xml:space="preserve">4.89590883255005</t>
   </si>
   <si>
     <t xml:space="preserve">4.94034385681152</t>
@@ -3152,40 +3152,40 @@
     <t xml:space="preserve">4.91206693649292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00497627258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04537105560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15039968490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08980655670166</t>
+    <t xml:space="preserve">5.00497674942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04537153244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15039920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08980703353882</t>
   </si>
   <si>
     <t xml:space="preserve">5.0655689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98073959350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96054172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99285793304443</t>
+    <t xml:space="preserve">4.9807391166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96054124832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99285745620728</t>
   </si>
   <si>
     <t xml:space="preserve">5.01709508895874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00093650817871</t>
+    <t xml:space="preserve">5.00093698501587</t>
   </si>
   <si>
     <t xml:space="preserve">5.01305532455444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97266006469727</t>
+    <t xml:space="preserve">4.97266054153442</t>
   </si>
   <si>
     <t xml:space="preserve">4.8999490737915</t>
@@ -3197,25 +3197,25 @@
     <t xml:space="preserve">4.92014646530151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10596466064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05345106124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16251802444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20222187042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11777067184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15577411651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18533182144165</t>
+    <t xml:space="preserve">5.10596513748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05345058441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16251850128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20222234725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11777019500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15577363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18533134460449</t>
   </si>
   <si>
     <t xml:space="preserve">5.10088014602661</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">5.06287670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07554531097412</t>
+    <t xml:space="preserve">5.07554483413696</t>
   </si>
   <si>
     <t xml:space="preserve">5.02909660339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04598665237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02487373352051</t>
+    <t xml:space="preserve">5.04598617553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02487325668335</t>
   </si>
   <si>
     <t xml:space="preserve">4.87286043167114</t>
@@ -3248,13 +3248,13 @@
     <t xml:space="preserve">4.54772233963013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60261583328247</t>
+    <t xml:space="preserve">4.60261535644531</t>
   </si>
   <si>
     <t xml:space="preserve">4.53505373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71662473678589</t>
+    <t xml:space="preserve">4.71662521362305</t>
   </si>
   <si>
     <t xml:space="preserve">4.64906406402588</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">4.73773813247681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69128942489624</t>
+    <t xml:space="preserve">4.6912899017334</t>
   </si>
   <si>
     <t xml:space="preserve">4.72929286956787</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">4.61950540542603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61106014251709</t>
+    <t xml:space="preserve">4.61106061935425</t>
   </si>
   <si>
     <t xml:space="preserve">4.6068377494812</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">4.51816368103027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45482540130615</t>
+    <t xml:space="preserve">4.45482492446899</t>
   </si>
   <si>
     <t xml:space="preserve">4.38726377487183</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">4.46327018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59417057037354</t>
+    <t xml:space="preserve">4.59417009353638</t>
   </si>
   <si>
     <t xml:space="preserve">4.67017698287964</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">4.61528301239014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62795114517212</t>
+    <t xml:space="preserve">4.62795066833496</t>
   </si>
   <si>
     <t xml:space="preserve">4.6575083732605</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">4.6363959312439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77996397018433</t>
+    <t xml:space="preserve">4.77996349334717</t>
   </si>
   <si>
     <t xml:space="preserve">4.80107641220093</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">4.72506999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77151870727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70817995071411</t>
+    <t xml:space="preserve">4.77151918411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70817947387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.66173124313354</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">4.53927659988403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47593784332275</t>
+    <t xml:space="preserve">4.47593832015991</t>
   </si>
   <si>
     <t xml:space="preserve">4.33659267425537</t>
@@ -3374,13 +3374,13 @@
     <t xml:space="preserve">4.31125688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42104387283325</t>
+    <t xml:space="preserve">4.42104434967041</t>
   </si>
   <si>
     <t xml:space="preserve">4.29436683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33237028121948</t>
+    <t xml:space="preserve">4.33236980438232</t>
   </si>
   <si>
     <t xml:space="preserve">4.25636339187622</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">4.39148569107056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41259956359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4041543006897</t>
+    <t xml:space="preserve">4.41259908676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40415382385254</t>
   </si>
   <si>
     <t xml:space="preserve">4.32392454147339</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">4.3197021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36192846298218</t>
+    <t xml:space="preserve">4.36192798614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.27747631072998</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">4.34503793716431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27325391769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14319801330566</t>
+    <t xml:space="preserve">4.27325439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14319849014282</t>
   </si>
   <si>
     <t xml:space="preserve">4.07225894927979</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">4.02665519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03341102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12630844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22680616378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10097217559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.036789894104</t>
+    <t xml:space="preserve">4.03341150283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12630796432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22680568695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1009726524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03678941726685</t>
   </si>
   <si>
     <t xml:space="preserve">4.02834415435791</t>
@@ -3452,10 +3452,10 @@
     <t xml:space="preserve">3.88984346389771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84761762619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97091674804688</t>
+    <t xml:space="preserve">3.84761786460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97091698646545</t>
   </si>
   <si>
     <t xml:space="preserve">4.06719160079956</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">4.04016733169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09421634674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01483201980591</t>
+    <t xml:space="preserve">4.09421682357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01483249664307</t>
   </si>
   <si>
     <t xml:space="preserve">4.15333271026611</t>
@@ -3485,13 +3485,13 @@
     <t xml:space="preserve">4.43371200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56461238861084</t>
+    <t xml:space="preserve">4.56461191177368</t>
   </si>
   <si>
     <t xml:space="preserve">4.68706703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80952215194702</t>
+    <t xml:space="preserve">4.80952167510986</t>
   </si>
   <si>
     <t xml:space="preserve">4.75462818145752</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">4.73351573944092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75040578842163</t>
+    <t xml:space="preserve">4.75040531158447</t>
   </si>
   <si>
     <t xml:space="preserve">4.76307344436646</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">4.51394081115723</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56883430480957</t>
+    <t xml:space="preserve">4.56883478164673</t>
   </si>
   <si>
     <t xml:space="preserve">4.78418684005737</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">4.58994770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52238655090332</t>
+    <t xml:space="preserve">4.52238607406616</t>
   </si>
   <si>
     <t xml:space="preserve">4.62372827529907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48438310623169</t>
+    <t xml:space="preserve">4.48438262939453</t>
   </si>
   <si>
     <t xml:space="preserve">4.44215726852417</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">4.35348320007324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42526626586914</t>
+    <t xml:space="preserve">4.4252667427063</t>
   </si>
   <si>
     <t xml:space="preserve">4.47171497344971</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">4.90241813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97842502593994</t>
+    <t xml:space="preserve">4.9784255027771</t>
   </si>
   <si>
     <t xml:space="preserve">5.04176378250122</t>
@@ -3593,10 +3593,10 @@
     <t xml:space="preserve">5.09243488311768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01220560073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98687028884888</t>
+    <t xml:space="preserve">5.01220607757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98687076568604</t>
   </si>
   <si>
     <t xml:space="preserve">4.91930913925171</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">5.00798320770264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86019325256348</t>
+    <t xml:space="preserve">4.86019277572632</t>
   </si>
   <si>
     <t xml:space="preserve">4.94042158126831</t>
@@ -3626,25 +3626,25 @@
     <t xml:space="preserve">5.00376081466675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96998071670532</t>
+    <t xml:space="preserve">4.96998023986816</t>
   </si>
   <si>
     <t xml:space="preserve">4.83908033370972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88975143432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82535934448242</t>
+    <t xml:space="preserve">4.88975095748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82535886764526</t>
   </si>
   <si>
     <t xml:space="preserve">4.82981061935425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75858783721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66955900192261</t>
+    <t xml:space="preserve">4.75858736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66955852508545</t>
   </si>
   <si>
     <t xml:space="preserve">4.71852493286133</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">4.78529596328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90993642807007</t>
+    <t xml:space="preserve">4.90993595123291</t>
   </si>
   <si>
     <t xml:space="preserve">4.95890283584595</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">4.93219375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96780490875244</t>
+    <t xml:space="preserve">4.9678053855896</t>
   </si>
   <si>
     <t xml:space="preserve">4.9989652633667</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">4.99006223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86987352371216</t>
+    <t xml:space="preserve">4.869873046875</t>
   </si>
   <si>
     <t xml:space="preserve">4.95445108413696</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">4.88322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87432479858398</t>
+    <t xml:space="preserve">4.87432527542114</t>
   </si>
   <si>
     <t xml:space="preserve">4.80755376815796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75413656234741</t>
+    <t xml:space="preserve">4.75413608551025</t>
   </si>
   <si>
     <t xml:space="preserve">4.85206747055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63839864730835</t>
+    <t xml:space="preserve">4.63839912414551</t>
   </si>
   <si>
     <t xml:space="preserve">4.60278749465942</t>
@@ -3716,19 +3716,19 @@
     <t xml:space="preserve">4.70517015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69626712799072</t>
+    <t xml:space="preserve">4.69626760482788</t>
   </si>
   <si>
     <t xml:space="preserve">4.68291330337524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7452335357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76303863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77194166183472</t>
+    <t xml:space="preserve">4.74523305892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76303911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77194213867188</t>
   </si>
   <si>
     <t xml:space="preserve">4.71407318115234</t>
@@ -3746,25 +3746,25 @@
     <t xml:space="preserve">4.57607841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5538215637207</t>
+    <t xml:space="preserve">4.55382108688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.53156423568726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59388446807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.647301197052</t>
+    <t xml:space="preserve">4.59388399124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64730167388916</t>
   </si>
   <si>
     <t xml:space="preserve">4.66510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61614179611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54937028884888</t>
+    <t xml:space="preserve">4.6161413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54936981201172</t>
   </si>
   <si>
     <t xml:space="preserve">4.50485563278198</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">4.500403881073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49595260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48704957962036</t>
+    <t xml:space="preserve">4.49595308303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48705005645752</t>
   </si>
   <si>
     <t xml:space="preserve">4.70071887969971</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">4.73187923431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.722975730896</t>
+    <t xml:space="preserve">4.72297620773315</t>
   </si>
   <si>
     <t xml:space="preserve">4.44609642028809</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">4.24489164352417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28228330612183</t>
+    <t xml:space="preserve">4.28228378295898</t>
   </si>
   <si>
     <t xml:space="preserve">4.31789493560791</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">4.34282302856445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41226577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43541288375854</t>
+    <t xml:space="preserve">4.41226530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4354133605957</t>
   </si>
   <si>
     <t xml:space="preserve">4.42829084396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39267921447754</t>
+    <t xml:space="preserve">4.3926796913147</t>
   </si>
   <si>
     <t xml:space="preserve">4.45588970184326</t>
@@ -3857,22 +3857,22 @@
     <t xml:space="preserve">4.30186986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25201416015625</t>
+    <t xml:space="preserve">4.25201368331909</t>
   </si>
   <si>
     <t xml:space="preserve">4.26625823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27694225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20928049087524</t>
+    <t xml:space="preserve">4.27694177627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20928001403809</t>
   </si>
   <si>
     <t xml:space="preserve">4.19147443771362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21996307373047</t>
+    <t xml:space="preserve">4.21996355056763</t>
   </si>
   <si>
     <t xml:space="preserve">4.27160024642944</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">4.30899238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30543088912964</t>
+    <t xml:space="preserve">4.3054313659668</t>
   </si>
   <si>
     <t xml:space="preserve">4.39445972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40336322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47369575500488</t>
+    <t xml:space="preserve">4.40336275100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47369527816772</t>
   </si>
   <si>
     <t xml:space="preserve">4.49150133132935</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">4.46034145355225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43185186386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52266120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47814750671387</t>
+    <t xml:space="preserve">4.43185234069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5226616859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47814702987671</t>
   </si>
   <si>
     <t xml:space="preserve">4.56717586517334</t>
@@ -3944,22 +3944,22 @@
     <t xml:space="preserve">4.61169004440308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59833574295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55827236175537</t>
+    <t xml:space="preserve">4.5983362197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55827283859253</t>
   </si>
   <si>
     <t xml:space="preserve">4.58053016662598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56272411346436</t>
+    <t xml:space="preserve">4.56272459030151</t>
   </si>
   <si>
     <t xml:space="preserve">4.5849814414978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54046726226807</t>
+    <t xml:space="preserve">4.54046678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.51375865936279</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">4.6918158531189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74968481063843</t>
+    <t xml:space="preserve">4.74968433380127</t>
   </si>
   <si>
     <t xml:space="preserve">4.4692440032959</t>
@@ -3998,16 +3998,16 @@
     <t xml:space="preserve">4.44787693023682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57162714004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79419946670532</t>
+    <t xml:space="preserve">4.57162761688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79419898986816</t>
   </si>
   <si>
     <t xml:space="preserve">4.80310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8209080696106</t>
+    <t xml:space="preserve">4.82090759277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
@@ -4887,6 +4887,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.39500045776367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4350004196167</t>
   </si>
 </sst>
 </file>
@@ -64323,7 +64326,7 @@
     </row>
     <row r="2274">
       <c r="A2274" s="1" t="n">
-        <v>45946.6493287037</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2274" t="n">
         <v>3121268</v>
@@ -64344,6 +64347,32 @@
         <v>1624</v>
       </c>
       <c r="H2274" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" s="1" t="n">
+        <v>45947.6500462963</v>
+      </c>
+      <c r="B2275" t="n">
+        <v>2359124</v>
+      </c>
+      <c r="C2275" t="n">
+        <v>8.50500011444092</v>
+      </c>
+      <c r="D2275" t="n">
+        <v>8.34000015258789</v>
+      </c>
+      <c r="E2275" t="n">
+        <v>8.43000030517578</v>
+      </c>
+      <c r="F2275" t="n">
+        <v>8.4350004196167</v>
+      </c>
+      <c r="G2275" t="s">
+        <v>1625</v>
+      </c>
+      <c r="H2275" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="1626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="1627">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58873581886292</t>
+    <t xml:space="preserve">2.58873558044434</t>
   </si>
   <si>
     <t xml:space="preserve">IG.MI</t>
@@ -56,16 +56,16 @@
     <t xml:space="preserve">2.17271208763123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09315872192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06185913085938</t>
+    <t xml:space="preserve">2.09315896034241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06185936927795</t>
   </si>
   <si>
     <t xml:space="preserve">2.08663845062256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04490542411804</t>
+    <t xml:space="preserve">2.0449059009552</t>
   </si>
   <si>
     <t xml:space="preserve">2.06055521965027</t>
@@ -74,55 +74,55 @@
     <t xml:space="preserve">2.04360127449036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10489654541016</t>
+    <t xml:space="preserve">2.10489630699158</t>
   </si>
   <si>
     <t xml:space="preserve">2.1296751499176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14532518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17923283576965</t>
+    <t xml:space="preserve">2.14532494544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1792323589325</t>
   </si>
   <si>
     <t xml:space="preserve">2.20009922981262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20140314102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17792868614197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13228392601013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09837555885315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22357416152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29138946533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33181810379028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29791021347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23791933059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30051851272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30443072319031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37094283103943</t>
+    <t xml:space="preserve">2.20140337944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17792844772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13228368759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09837579727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22357392311096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29138970375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33181834220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29791045188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2379195690155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30051898956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30443120002747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37094259262085</t>
   </si>
   <si>
     <t xml:space="preserve">2.3461639881134</t>
@@ -131,43 +131,43 @@
     <t xml:space="preserve">2.39572167396545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45571255683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39702606201172</t>
+    <t xml:space="preserve">2.45571231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39702582359314</t>
   </si>
   <si>
     <t xml:space="preserve">2.38007187843323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39441752433777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42180418968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41006731987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43093347549438</t>
+    <t xml:space="preserve">2.39441728591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42180466651917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41006708145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43093371391296</t>
   </si>
   <si>
     <t xml:space="preserve">2.43745422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48701190948486</t>
+    <t xml:space="preserve">2.48701167106628</t>
   </si>
   <si>
     <t xml:space="preserve">2.45049571990967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49092483520508</t>
+    <t xml:space="preserve">2.4909245967865</t>
   </si>
   <si>
     <t xml:space="preserve">2.4452793598175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46614575386047</t>
+    <t xml:space="preserve">2.46614551544189</t>
   </si>
   <si>
     <t xml:space="preserve">2.43223738670349</t>
@@ -176,40 +176,40 @@
     <t xml:space="preserve">2.44006276130676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47788286209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43615031242371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43354249000549</t>
+    <t xml:space="preserve">2.47788333892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43615007400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43354177474976</t>
   </si>
   <si>
     <t xml:space="preserve">2.4570164680481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48831605911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41789197921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43484592437744</t>
+    <t xml:space="preserve">2.48831653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41789221763611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43484616279602</t>
   </si>
   <si>
     <t xml:space="preserve">2.41267561912537</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35659694671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27574014663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29530215263367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31225609779358</t>
+    <t xml:space="preserve">2.35659718513489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27573990821838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29530191421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.312255859375</t>
   </si>
   <si>
     <t xml:space="preserve">2.38137602806091</t>
@@ -218,31 +218,31 @@
     <t xml:space="preserve">2.40876317024231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3931131362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44919180870056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46744966506958</t>
+    <t xml:space="preserve">2.39311361312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44919204711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46744990348816</t>
   </si>
   <si>
     <t xml:space="preserve">2.47397041320801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48440361022949</t>
+    <t xml:space="preserve">2.48440384864807</t>
   </si>
   <si>
     <t xml:space="preserve">2.4635374546051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47266674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47136235237122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44788718223572</t>
+    <t xml:space="preserve">2.47266626358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47136211395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44788765907288</t>
   </si>
   <si>
     <t xml:space="preserve">2.49614095687866</t>
@@ -257,76 +257,76 @@
     <t xml:space="preserve">2.53135299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51439905166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53656959533691</t>
+    <t xml:space="preserve">2.51439929008484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53656983375549</t>
   </si>
   <si>
     <t xml:space="preserve">2.52744078636169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54830718040466</t>
+    <t xml:space="preserve">2.54830694198608</t>
   </si>
   <si>
     <t xml:space="preserve">2.55091524124146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53787398338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58612728118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57699823379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59786486625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60438561439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57308578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66959285736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68393874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69828414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64872622489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64742207527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68132996559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67480945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63438081741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64350962638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69567584991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69958853721619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67872190475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73480010032654</t>
+    <t xml:space="preserve">2.5378737449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58612751960754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57699847221375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59786462783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60438537597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57308602333069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66959261894226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68393850326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69828391075134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64872646331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64742231369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68133044242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67480969429016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63438057899475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64351010322571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69567561149597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69958829879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67872214317322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73480033874512</t>
   </si>
   <si>
     <t xml:space="preserve">2.772620677948</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">2.7543625831604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71262979507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70089244842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70219659805298</t>
+    <t xml:space="preserve">2.71262955665588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70089268684387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7021963596344</t>
   </si>
   <si>
     <t xml:space="preserve">2.66176772117615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78305411338806</t>
+    <t xml:space="preserve">2.7830536365509</t>
   </si>
   <si>
     <t xml:space="preserve">2.7452335357666</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">2.69306755065918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71915054321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70610928535461</t>
+    <t xml:space="preserve">2.71915030479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70610904693604</t>
   </si>
   <si>
     <t xml:space="preserve">2.74914598464966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77783751487732</t>
+    <t xml:space="preserve">2.77783799171448</t>
   </si>
   <si>
     <t xml:space="preserve">2.8352198600769</t>
@@ -374,31 +374,31 @@
     <t xml:space="preserve">2.84043645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88738608360291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89651489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85347819328308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91477251052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00867104530334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02040886878967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96824312210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00736784934998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05822896957397</t>
+    <t xml:space="preserve">2.88738536834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89651465415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8534779548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91477227210999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0086715221405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02040910720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96824288368225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00736737251282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05822944641113</t>
   </si>
   <si>
     <t xml:space="preserve">3.09885382652283</t>
@@ -407,55 +407,55 @@
     <t xml:space="preserve">3.15591311454773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09613728523254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13825154304504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09070253372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97658443450928</t>
+    <t xml:space="preserve">3.09613704681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1382520198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09070324897766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97658467292786</t>
   </si>
   <si>
     <t xml:space="preserve">3.13417601585388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20074486732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24965286254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28769278526306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23063373565674</t>
+    <t xml:space="preserve">3.20074510574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24965333938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28769254684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23063349723816</t>
   </si>
   <si>
     <t xml:space="preserve">3.24557733535767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2224817276001</t>
+    <t xml:space="preserve">3.22248196601868</t>
   </si>
   <si>
     <t xml:space="preserve">3.25101137161255</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18716025352478</t>
+    <t xml:space="preserve">3.1871600151062</t>
   </si>
   <si>
     <t xml:space="preserve">3.09477853775024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11379790306091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19938731193542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10428857803345</t>
+    <t xml:space="preserve">3.11379861831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19938683509827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10428833961487</t>
   </si>
   <si>
     <t xml:space="preserve">3.12059116363525</t>
@@ -464,145 +464,145 @@
     <t xml:space="preserve">3.15727138519287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16270565986633</t>
+    <t xml:space="preserve">3.16270613670349</t>
   </si>
   <si>
     <t xml:space="preserve">3.14504504203796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03907752037048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02820944786072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96707439422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00375556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03636050224304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02005815505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97794318199158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98609447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99560403823853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07575869560242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0839102268219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12466621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10836434364319</t>
+    <t xml:space="preserve">3.03907799720764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0282096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96707487106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00375533103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03636002540588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02005839347839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97794270515442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98609399795532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9956042766571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.075758934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.124666929245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10836410522461</t>
   </si>
   <si>
     <t xml:space="preserve">3.12874221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17900848388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17221593856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12602496147156</t>
+    <t xml:space="preserve">3.17900800704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17221617698669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12602519989014</t>
   </si>
   <si>
     <t xml:space="preserve">3.15863037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22519946098328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26052165031433</t>
+    <t xml:space="preserve">3.22519969940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26052117347717</t>
   </si>
   <si>
     <t xml:space="preserve">3.25237059593201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27682447433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30671262741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30263686180115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2808997631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21025466918945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28361749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29856109619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28225755691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26323866844177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25644588470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27003169059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24693655967712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2333505153656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21976494789124</t>
+    <t xml:space="preserve">3.27682423591614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30671238899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30263638496399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28090023994446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21025490760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2836172580719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29856085777283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28225803375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26323914527893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25644612312317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27003192901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24693632125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23335075378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21976470947266</t>
   </si>
   <si>
     <t xml:space="preserve">3.24150156974792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26188015937805</t>
+    <t xml:space="preserve">3.26188063621521</t>
   </si>
   <si>
     <t xml:space="preserve">3.23470902442932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19802832603455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23742628097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24829459190369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22791647911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19395232200623</t>
+    <t xml:space="preserve">3.19802856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23742580413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24829483032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22791600227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19395279884338</t>
   </si>
   <si>
     <t xml:space="preserve">3.16542291641235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18444275856018</t>
+    <t xml:space="preserve">3.1844425201416</t>
   </si>
   <si>
     <t xml:space="preserve">3.18172550201416</t>
@@ -611,79 +611,79 @@
     <t xml:space="preserve">3.20753836631775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2401430606842</t>
+    <t xml:space="preserve">3.24014353752136</t>
   </si>
   <si>
     <t xml:space="preserve">3.26731419563293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24286079406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22655749320984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2319917678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20617961883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14640331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16814088821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157108306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678166389465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21704769134521</t>
+    <t xml:space="preserve">3.2428605556488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22655773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23199200630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20617914199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14640355110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16814017295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157155990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678190231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21704816818237</t>
   </si>
   <si>
     <t xml:space="preserve">3.22927474975586</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24421882629395</t>
+    <t xml:space="preserve">3.24421906471252</t>
   </si>
   <si>
     <t xml:space="preserve">3.21433091163635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25372862815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35154414176941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49147486686707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39365911483765</t>
+    <t xml:space="preserve">3.25372838973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35154485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49147510528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39366006851196</t>
   </si>
   <si>
     <t xml:space="preserve">3.46430420875549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50506091117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41675543785095</t>
+    <t xml:space="preserve">3.50506067276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41675448417664</t>
   </si>
   <si>
     <t xml:space="preserve">3.40656590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44732260704041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43373656272888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42694425582886</t>
+    <t xml:space="preserve">3.44732213020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43373680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42694449424744</t>
   </si>
   <si>
     <t xml:space="preserve">3.47109699249268</t>
@@ -692,142 +692,142 @@
     <t xml:space="preserve">3.46770071983337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.481285572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50166487693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5424211025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51185369491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54581713676453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55940294265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412308692932</t>
+    <t xml:space="preserve">3.48128628730774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50166463851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54242086410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51185393333435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54581737518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55940270423889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412261009216</t>
   </si>
   <si>
     <t xml:space="preserve">3.60015964508057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53223133087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4846818447113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55260992050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61374521255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52543902397156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58996963500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60355544090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59336686134338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62053751945496</t>
+    <t xml:space="preserve">3.53223180770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48468232154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55261039733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61374449729919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5254385471344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58997011184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60355567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5933666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62053728103638</t>
   </si>
   <si>
     <t xml:space="preserve">3.59676289558411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5661952495575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562808036804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45411539077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45751166343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39637637138367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3230152130127</t>
+    <t xml:space="preserve">3.56619548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53562784194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45411491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45751142501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39637684822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32301473617554</t>
   </si>
   <si>
     <t xml:space="preserve">3.38279128074646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40996265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38958334922791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32844948768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30807065963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31078791618347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35018610954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37599802017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35426211357117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37328171730042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34339308738708</t>
+    <t xml:space="preserve">3.40996217727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38958358764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.328449010849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30807113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31078815460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35018587112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37599778175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35426115989685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37328124046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34339284896851</t>
   </si>
   <si>
     <t xml:space="preserve">3.36648869514465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3787157535553</t>
+    <t xml:space="preserve">3.37871527671814</t>
   </si>
   <si>
     <t xml:space="preserve">3.36105418205261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12127017974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16406440734863</t>
+    <t xml:space="preserve">3.12126970291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16406416893005</t>
   </si>
   <si>
     <t xml:space="preserve">3.06624865531921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04587078094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03228545188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00239706039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02209615707397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02549242973328</t>
+    <t xml:space="preserve">3.0458710193634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03228569030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00239682197571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02209568023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02549266815186</t>
   </si>
   <si>
     <t xml:space="preserve">3.04655003547668</t>
@@ -836,28 +836,28 @@
     <t xml:space="preserve">2.99424576759338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96164059638977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97862243652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092622756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11651515960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06828689575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00035929679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96639537811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92903518676758</t>
+    <t xml:space="preserve">2.96164035797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97862267494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11651492118835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06828713417053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00035881996155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96639513969421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.929034948349</t>
   </si>
   <si>
     <t xml:space="preserve">2.924959897995</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">3.01326513290405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0940990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14300656318665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23538875579834</t>
+    <t xml:space="preserve">3.09409880638123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14300680160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2353880405426</t>
   </si>
   <si>
     <t xml:space="preserve">3.22723722457886</t>
@@ -881,97 +881,97 @@
     <t xml:space="preserve">3.21297216415405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19327354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27342748641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29448533058167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20414209365845</t>
+    <t xml:space="preserve">3.19327306747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27342772483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29448556900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20414161682129</t>
   </si>
   <si>
     <t xml:space="preserve">3.30739140510559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28565430641174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36377191543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39909410476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47924852371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.475172996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4819655418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4371325969696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44392609596252</t>
+    <t xml:space="preserve">3.2856547832489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36377120018005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39909338951111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47924828529358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47517251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48196530342102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43713355064392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44392585754395</t>
   </si>
   <si>
     <t xml:space="preserve">3.49962639808655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52815556526184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4778892993927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51457071304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45886969566345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52679777145386</t>
+    <t xml:space="preserve">3.52815628051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47788953781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51457047462463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45887017250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5267972946167</t>
   </si>
   <si>
     <t xml:space="preserve">3.5200047492981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57570552825928</t>
+    <t xml:space="preserve">3.5757052898407</t>
   </si>
   <si>
     <t xml:space="preserve">3.62733030319214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64499187469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60423469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60287642478943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62597155570984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49419236183167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45615243911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41539597511292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45479464530945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44256782531738</t>
+    <t xml:space="preserve">3.64499139785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60423517227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60287618637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62597107887268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49419260025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45615339279175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41539692878723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45479393005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4425675868988</t>
   </si>
   <si>
     <t xml:space="preserve">3.36309242248535</t>
@@ -983,22 +983,22 @@
     <t xml:space="preserve">3.39461994171143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45400094985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46107006072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36280846595764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28151273727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23414921760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07367920875549</t>
+    <t xml:space="preserve">3.45400047302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46107029914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36280798912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28151297569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23414874076843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07367897033691</t>
   </si>
   <si>
     <t xml:space="preserve">3.16699194908142</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">3.1528537273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18961381912231</t>
+    <t xml:space="preserve">3.18961334228516</t>
   </si>
   <si>
     <t xml:space="preserve">3.27868509292603</t>
@@ -1016,64 +1016,64 @@
     <t xml:space="preserve">3.2574770450592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23556327819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23768377304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34089350700378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43774151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39037775993347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4108784198761</t>
+    <t xml:space="preserve">3.23556351661682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23768401145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20163083076477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34089374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43774175643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39037823677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41087865829468</t>
   </si>
   <si>
     <t xml:space="preserve">3.37624001502991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38967132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40946483612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46319103240967</t>
+    <t xml:space="preserve">3.38967084884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40946459770203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46319055557251</t>
   </si>
   <si>
     <t xml:space="preserve">3.33735942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3154444694519</t>
+    <t xml:space="preserve">3.31544470787048</t>
   </si>
   <si>
     <t xml:space="preserve">3.29989266395569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34442830085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35432577133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32958364486694</t>
+    <t xml:space="preserve">3.3444287776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35432529449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32958340644836</t>
   </si>
   <si>
     <t xml:space="preserve">3.33806657791138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29211664199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35644602775574</t>
+    <t xml:space="preserve">3.29211640357971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35644626617432</t>
   </si>
   <si>
     <t xml:space="preserve">3.3522047996521</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">3.41865491867065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3776535987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32534170150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3557391166687</t>
+    <t xml:space="preserve">3.37765336036682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32534146308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35573959350586</t>
   </si>
   <si>
     <t xml:space="preserve">3.34230780601501</t>
@@ -1103,49 +1103,49 @@
     <t xml:space="preserve">3.45258688926697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44834542274475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44269037246704</t>
+    <t xml:space="preserve">3.44834494590759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44269013404846</t>
   </si>
   <si>
     <t xml:space="preserve">3.4511730670929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41229319572449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40734386444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46036267280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4313793182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47874331474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42077589035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42572450637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51479578018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49429488182068</t>
+    <t xml:space="preserve">3.41229295730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40734434127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46036291122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43137979507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47874283790588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42077541351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42572402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51479601860046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49429512023926</t>
   </si>
   <si>
     <t xml:space="preserve">3.39532661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41582727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4292585849762</t>
+    <t xml:space="preserve">3.41582703590393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42925882339478</t>
   </si>
   <si>
     <t xml:space="preserve">3.40239596366882</t>
@@ -1157,31 +1157,31 @@
     <t xml:space="preserve">3.3882577419281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43279337882996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33594512939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29706525802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30413413047791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3083758354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28787517547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3161518573761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25182223320007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28999519348145</t>
+    <t xml:space="preserve">3.4327929019928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33594536781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29706478118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30413389205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30837559700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2878749370575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31615138053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25182247161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2899956703186</t>
   </si>
   <si>
     <t xml:space="preserve">3.33311796188354</t>
@@ -1190,19 +1190,19 @@
     <t xml:space="preserve">3.33099699020386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33382487297058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32675552368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34654951095581</t>
+    <t xml:space="preserve">3.33382511138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32675528526306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34654903411865</t>
   </si>
   <si>
     <t xml:space="preserve">3.47450113296509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49924349784851</t>
+    <t xml:space="preserve">3.49924325942993</t>
   </si>
   <si>
     <t xml:space="preserve">3.49641609191895</t>
@@ -1211,19 +1211,19 @@
     <t xml:space="preserve">3.46248340606689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45682787895203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45470786094666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38613653182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4575355052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45894908905029</t>
+    <t xml:space="preserve">3.45682883262634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45470762252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38613629341125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45753526687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45894956588745</t>
   </si>
   <si>
     <t xml:space="preserve">3.37411880493164</t>
@@ -1232,25 +1232,25 @@
     <t xml:space="preserve">3.39391255378723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42006874084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30978965759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32816958427429</t>
+    <t xml:space="preserve">3.42006850242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30978989601135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32816934585571</t>
   </si>
   <si>
     <t xml:space="preserve">3.35715317726135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27797794342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24899458885193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21011424064636</t>
+    <t xml:space="preserve">3.27797842025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24899482727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21011400222778</t>
   </si>
   <si>
     <t xml:space="preserve">3.23485636711121</t>
@@ -1259,103 +1259,103 @@
     <t xml:space="preserve">3.20516586303711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15780210494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13093900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15356063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24545979499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16911268234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19809651374817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1889066696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23909783363342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23344206809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27727127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23202872276306</t>
+    <t xml:space="preserve">3.15780258178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13093948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15356040000916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24546003341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16911220550537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19809675216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18890714645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23909735679626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23344230651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27727150917053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23202848434448</t>
   </si>
   <si>
     <t xml:space="preserve">3.22920060157776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22495889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2723228931427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31473803520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37341213226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42501711845398</t>
+    <t xml:space="preserve">3.22495913505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27232313156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31473827362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3734118938446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4250168800354</t>
   </si>
   <si>
     <t xml:space="preserve">3.43491411209106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48863959312439</t>
+    <t xml:space="preserve">3.48863935470581</t>
   </si>
   <si>
     <t xml:space="preserve">3.44693160057068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38755083084106</t>
+    <t xml:space="preserve">3.38755011558533</t>
   </si>
   <si>
     <t xml:space="preserve">3.35927367210388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34160137176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30060029029846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30484104156494</t>
+    <t xml:space="preserve">3.34160113334656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3005998134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3048415184021</t>
   </si>
   <si>
     <t xml:space="preserve">3.27585744857788</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39603352546692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34937691688538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36068797111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36705017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3917920589447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41653418540955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.453293800354</t>
+    <t xml:space="preserve">3.3960337638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34937739372253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36068773269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36704969406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39179182052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41653394699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45329427719116</t>
   </si>
   <si>
     <t xml:space="preserve">3.52327871322632</t>
@@ -1364,220 +1364,220 @@
     <t xml:space="preserve">3.59114289283752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61235022544861</t>
+    <t xml:space="preserve">3.61235046386719</t>
   </si>
   <si>
     <t xml:space="preserve">3.63073015213013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61093640327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62790250778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60103964805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59962630271912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51055431365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53176116943359</t>
+    <t xml:space="preserve">3.61093664169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62790298461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60104036331177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59962582588196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51055407524109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53176212310791</t>
   </si>
   <si>
     <t xml:space="preserve">3.57841849327087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61941933631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64911031723022</t>
+    <t xml:space="preserve">3.61941909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64910984039307</t>
   </si>
   <si>
     <t xml:space="preserve">3.67880058288574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62083387374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68587017059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70849084854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65335178375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68304204940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68728399276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67738699913025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71414685249329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71131896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70990514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72545695304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73252630233765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73111295700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6717312335968</t>
+    <t xml:space="preserve">3.6208336353302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68586993217468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70849132537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65335154533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68304252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68728351593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67738676071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71414637565613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71131873130798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70990490913391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72545719146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73252701759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.731112241745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67173147201538</t>
   </si>
   <si>
     <t xml:space="preserve">3.69293904304504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71980237960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779950141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61517834663391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68869709968567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69576668739319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69435262680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69718027114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68162894248962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75232028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74383687973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72262954711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76504445075989</t>
+    <t xml:space="preserve">3.71980166435242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779926300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61517810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68869733810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69576644897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69435286521912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69718074798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68162798881531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75232005119324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7438371181488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72262978553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76504516601562</t>
   </si>
   <si>
     <t xml:space="preserve">3.7593891620636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71697354316711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78342461585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83997797966003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86542677879333</t>
+    <t xml:space="preserve">3.71697425842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78342485427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83997774124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86542725563049</t>
   </si>
   <si>
     <t xml:space="preserve">3.83573651313782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82442545890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79756307601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81735682487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8597719669342</t>
+    <t xml:space="preserve">3.8244252204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79756283760071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81735587120056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85977125167847</t>
   </si>
   <si>
     <t xml:space="preserve">3.86966824531555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88380670547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87532353401184</t>
+    <t xml:space="preserve">3.88380718231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87532377243042</t>
   </si>
   <si>
     <t xml:space="preserve">3.89370369911194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88804745674133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85270285606384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87108254432678</t>
+    <t xml:space="preserve">3.88804864883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85270261764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87108206748962</t>
   </si>
   <si>
     <t xml:space="preserve">3.89087629318237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84139132499695</t>
+    <t xml:space="preserve">3.84139204025269</t>
   </si>
   <si>
     <t xml:space="preserve">3.88239312171936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92339444160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88946199417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90360045433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92056655883789</t>
+    <t xml:space="preserve">3.92339468002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88946175575256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90360069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92056584358215</t>
   </si>
   <si>
     <t xml:space="preserve">3.91915321350098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96439552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95732617378235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91067004203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93329071998596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90642786026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90501427650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92198014259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91208362579346</t>
+    <t xml:space="preserve">3.96439528465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95732641220093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91066932678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93329119682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90642738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90501475334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92198038101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91208386421204</t>
   </si>
   <si>
     <t xml:space="preserve">3.9304633140564</t>
@@ -1592,1054 +1592,1054 @@
     <t xml:space="preserve">3.88097929954529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94743013381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89228987693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87390947341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90925645828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95025706291199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.981360912323</t>
+    <t xml:space="preserve">3.947429895401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89228963851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87390971183777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90925621986389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95025730133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98136186599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00963830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08032989501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07891607284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13016366958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16984748840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21100330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.213942527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24921846389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20512390136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1948356628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12281465530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1081166267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16543865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21541213989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26979494094849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30507040023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32123899459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36827230453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33152723312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32564783096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.288902759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35651397705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34328508377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49908590316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44764232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44617223739624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48291778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48732662200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45352172851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43735408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35210466384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34181642532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33446645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43147420883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47997808456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44911193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43882322311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49467611312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51966285705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50349473953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54317951202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56228685379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57698535919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52701187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54170989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54905891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40207767486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43588304519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42559480667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38885021209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38150072097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24480867385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20218372344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29037237167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29331254959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27420473098755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26097631454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28449296951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28743314743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11399555206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16102933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24186849594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15662002563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30360078811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2183518409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20071458816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1977744102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34034633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33593702316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34916496276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.313889503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30213117599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20806360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14192199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1037073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18307638168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14045143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12575387954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19336462020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18160676956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18454599380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25215721130371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29919099807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39031982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32711744308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30066156387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21247243881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31241989135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36974239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24774837493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18895578384399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23011016845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18748617172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17425680160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1727876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14486122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1683783531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18013715744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.238929271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25362730026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29478120803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33740663528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35063505172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28302383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33299732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30654096603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268161773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39178895950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27861404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2242317199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23745918273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22570037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19189500808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22129154205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23598957061768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22717094421387</t>
   </si>
   <si>
     <t xml:space="preserve">4.00963878631592</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08033037185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07891654968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13016319274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16984796524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21100330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21394300460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24921846389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20512342453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19483518600464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12281465530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1081166267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16543912887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21541213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26979541778564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3050708770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32123899459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36827182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33152723312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32564783096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.288902759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35651350021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34328556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49908590316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44764232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4461727142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48291778564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48732662200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45352125167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43735313415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35210466384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34181547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33446645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43147468566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47997808456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44911193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43882369995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49467658996582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51966238021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50349473953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54317998886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56228733062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57698535919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52701187133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54170989990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54905891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40207767486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43588352203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42559480667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38885021209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38150072097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2448091506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20218420028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29037237167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29331254959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27420425415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26097631454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28449296951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28743314743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11399507522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16102933883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24186897277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15662002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30360078811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21835136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20071411132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19777488708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34034633636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33593702316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34916496276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31388998031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30213117599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20806312561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14192247390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1037073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18307638168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14045190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12575435638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1933650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18160676956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18454647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25215768814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29919099807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39031934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32711791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30066108703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2124719619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31241941452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36974239349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24774837493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18895530700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23011064529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18748569488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17425727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17278814315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14486122131348</t>
+    <t xml:space="preserve">4.07431125640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08900880813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04932403564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01992702484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95378661155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99494099617004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04197549819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99053120613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03609561920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10664653778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16396856307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12722396850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13751220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00082063674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09194803237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08459949493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02727651596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02286720275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10076713562012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20365381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13898277282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25068759918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20659255981445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26391649246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30801010131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48144817352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51525354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49761533737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40648746490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41677665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4667501449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49173641204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46086978912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46234083175659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5123143196106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45205163955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48585796356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62548875808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26538562774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26244592666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06549167633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08606910705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72890543937683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51798820495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50182008743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02192711830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24754309654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15127062797546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27032446861267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29531240463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35189938545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21153259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.129958152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35557436943054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38937950134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34381604194641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35924863815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5709011554718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66643881797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44964170455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55693793296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58780384063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53636002540588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54958915710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4658100605011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54811882972717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56428694725037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368348121643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62601923942566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57163619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57310557365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4408233165741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61719965934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52754139900208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57457542419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56722688674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5789852142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75168776512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68187141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70391869544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60691142082214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61279058456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66423416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63189792633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62454891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63777709007263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62307906150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71126770973206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73626255989075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60662770271301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66372871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63440680503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68533444404602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75015187263489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73008918762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70231056213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80725312232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77021503448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81959915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90447926521301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99707531929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05108976364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02408313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92762875556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88133025169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81651282310486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91991186141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08581352233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05880641937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10896253585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14754486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02022504806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96620988845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9893593788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03565740585327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08967208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03179979324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07038164138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11282110214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0549488067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95463562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96235203742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93534517288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97006845474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97392630577087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0742392539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1243953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10510492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09352970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04723167419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12825345993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25943183898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26714897155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21313333511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19770097732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16297721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16683578491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470855712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28643894195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36746072769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42147588729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3906102180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37517738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36360311508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30572986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26328992843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24399948120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31344652175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30187225341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13597011566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22856664657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18612623214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17455148696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1899847984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11667919158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17841005325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15526151657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15140295028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15911912918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19384288787842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07809734344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89290499687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97778511047363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06266450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94691896438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98550152778625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9816427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88904619216919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71157026290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72700309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82885885238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83194518089294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86589765548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00479173660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95077729225159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08195543289185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03951501846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13982820510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17069387435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14368629455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13211250305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93920254707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90062141418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80879640579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99321746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01250791549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95849370956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87747192382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9314866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9237699508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86203980445862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8180558681488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80571007728577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85818147659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89676308631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85663795471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82114219665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83811855316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94306135177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90833735466003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88518834114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83503198623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76712822914124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76249814033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82268595695496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79799294471741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87361359596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02794122695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04337310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2092752456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25171566009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25557327270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31730461120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27100658416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26251888275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2872109413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25634527206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24554252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14985942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12979745864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14060020446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12362337112427</t>
   </si>
   <si>
     <t xml:space="preserve">4.16837882995605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18013668060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.238929271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25362777709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29478216171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33740663528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35063457489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28302383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33299732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30654001235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268161773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39178895950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27861404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22423076629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23745965957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22570133209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19189596176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22129106521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23599004745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22717046737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00963926315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07431077957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08900833129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04932403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01992702484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95378613471985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99494099617004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04197406768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99053168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03609561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10664653778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16396903991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1272234916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13751268386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00081968307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09194803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08459949493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02727651596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02286720275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10076761245728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20365381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13898229598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25068759918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20659351348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26391649246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30801010131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48144769668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51525354385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49761533737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40648746490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41677618026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46674966812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4917368888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46087074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46234035491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51231384277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45205163955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48585653305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62548923492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26538515090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26244640350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06549215316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08606863021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72890543937683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51798820495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5018196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02192735671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24754309654236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15127086639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27032494544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29531192779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35189938545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21153283119202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12995839118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35557413101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38937950134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34381532669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3592483997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5709011554718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66643857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44964170455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55693817138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58780384063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53636026382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54958868026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4658100605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54811859130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56428694725037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368276596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62601900100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57163572311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57310605049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44082307815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61720013618469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52754187583923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57457542419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56722640991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57898545265198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75168776512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68187189102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70391869544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60691165924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61279082298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66423416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63189816474915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6245493888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63777732849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62307953834534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71126818656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73626279830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60662746429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66372871398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63440632820129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68533492088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75015211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73008966445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70231056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80725288391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77021479606628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81959939002991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90447926521301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99707531929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05109024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02408266067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92762875556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88133025169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81651282310486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91991209983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08581352233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0588059425354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10896253585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14754438400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02022457122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96621012687683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98935961723328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03565788269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08967208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03179883956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07038116455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11282062530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05494832992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95463585853577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96235203742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93534445762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97006821632385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97392630577087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0742392539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1243953704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10510492324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09352970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04723167419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12825345993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25943183898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26714897155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21313381195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19770097732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16297769546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16683530807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470808029175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28643941879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36746120452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42147588729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3906102180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37517786026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36360311508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30572986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26328992843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24399948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31344652175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30187129974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13597011566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22856616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18612670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17455148696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18998432159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11667966842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17841005325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15526103973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15140295028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15911960601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19384241104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07809782028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89290452003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9777843952179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06266450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94691920280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9855010509491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98164296150208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88904595375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71157050132751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72700262069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8288586139679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8319456577301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86589789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00479125976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95077776908875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08195543289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03951549530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13982772827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17069387435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14368629455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1321120262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93920302391052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90062117576599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80879664421082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99321818351746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01250791549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95849394798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8774721622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93148589134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92377018928528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86203932762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81805610656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80571031570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85818123817444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89676308631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85663795471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82114267349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83811902999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94306111335754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90833783149719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88518834114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83503174781799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76712822914124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76249814033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82268571853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79799342155457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87361407279968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02794075012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04337358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2092752456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25171566009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25557374954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3173041343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27100658416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26251840591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2872109413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25634527206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24554252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14985942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12979698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14059972763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12362384796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16837930679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1714653968811</t>
+    <t xml:space="preserve">4.17146587371826</t>
   </si>
   <si>
     <t xml:space="preserve">4.19924402236938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23628234863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18844127655029</t>
+    <t xml:space="preserve">4.23628282546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18844175338745</t>
   </si>
   <si>
     <t xml:space="preserve">4.1776385307312</t>
@@ -2651,64 +2651,64 @@
     <t xml:space="preserve">4.1838116645813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20387411117554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18535423278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21622037887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29338407516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23165321350098</t>
+    <t xml:space="preserve">4.20387363433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1853551864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21621990203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23165369033813</t>
   </si>
   <si>
     <t xml:space="preserve">4.25017213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23782634735107</t>
+    <t xml:space="preserve">4.23782587051392</t>
   </si>
   <si>
     <t xml:space="preserve">4.35048532485962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34122562408447</t>
+    <t xml:space="preserve">4.34122610092163</t>
   </si>
   <si>
     <t xml:space="preserve">4.39369630813599</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47086048126221</t>
+    <t xml:space="preserve">4.47086000442505</t>
   </si>
   <si>
     <t xml:space="preserve">4.46610307693481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44024991989136</t>
+    <t xml:space="preserve">4.44025039672852</t>
   </si>
   <si>
     <t xml:space="preserve">4.3885440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35622787475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38531255722046</t>
+    <t xml:space="preserve">4.35622835159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38531303405762</t>
   </si>
   <si>
     <t xml:space="preserve">4.37400197982788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39015960693359</t>
+    <t xml:space="preserve">4.39016008377075</t>
   </si>
   <si>
     <t xml:space="preserve">4.37723398208618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40147066116333</t>
+    <t xml:space="preserve">4.40147018432617</t>
   </si>
   <si>
     <t xml:space="preserve">4.45156097412109</t>
@@ -2723,16 +2723,16 @@
     <t xml:space="preserve">4.50165128707886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52911996841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55174160003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55012512207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62122058868408</t>
+    <t xml:space="preserve">4.52911949157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55174112319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55012559890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62122106552124</t>
   </si>
   <si>
     <t xml:space="preserve">4.58405733108521</t>
@@ -2741,10 +2741,10 @@
     <t xml:space="preserve">4.56628322601318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54527807235718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52750396728516</t>
+    <t xml:space="preserve">4.54527854919434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52750444412231</t>
   </si>
   <si>
     <t xml:space="preserve">4.45640802383423</t>
@@ -2765,10 +2765,10 @@
     <t xml:space="preserve">4.46771955490112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49841976165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50649881362915</t>
+    <t xml:space="preserve">4.49841928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50649833679199</t>
   </si>
   <si>
     <t xml:space="preserve">4.55335712432861</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">4.4790301322937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52265644073486</t>
+    <t xml:space="preserve">4.52265739440918</t>
   </si>
   <si>
     <t xml:space="preserve">4.54204654693604</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">4.37884902954102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35461282730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37238597869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53719902038574</t>
+    <t xml:space="preserve">4.35461235046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37238645553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5371994972229</t>
   </si>
   <si>
     <t xml:space="preserve">4.56789922714233</t>
@@ -2813,10 +2813,10 @@
     <t xml:space="preserve">4.61637353897095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62768459320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59375190734863</t>
+    <t xml:space="preserve">4.62768411636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59375238418579</t>
   </si>
   <si>
     <t xml:space="preserve">4.60829496383667</t>
@@ -2825,10 +2825,10 @@
     <t xml:space="preserve">4.63091564178467</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65676927566528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66484832763672</t>
+    <t xml:space="preserve">4.65676879882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66484880447388</t>
   </si>
   <si>
     <t xml:space="preserve">4.69070148468018</t>
@@ -2837,43 +2837,43 @@
     <t xml:space="preserve">4.73271179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76502847671509</t>
+    <t xml:space="preserve">4.76502799987793</t>
   </si>
   <si>
     <t xml:space="preserve">4.80219173431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79896068572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76987600326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82804489135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82481384277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84420347213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80703926086426</t>
+    <t xml:space="preserve">4.79896020889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76987552642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82804441452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82481336593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84420299530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80703973770142</t>
   </si>
   <si>
     <t xml:space="preserve">4.69554853439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57436323165894</t>
+    <t xml:space="preserve">4.57436275482178</t>
   </si>
   <si>
     <t xml:space="preserve">4.53558301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59213638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54366207122803</t>
+    <t xml:space="preserve">4.5921368598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54366159439087</t>
   </si>
   <si>
     <t xml:space="preserve">4.49034070968628</t>
@@ -2885,10 +2885,10 @@
     <t xml:space="preserve">4.48549270629883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45964050292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51134586334229</t>
+    <t xml:space="preserve">4.45963954925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51134634017944</t>
   </si>
   <si>
     <t xml:space="preserve">4.52427244186401</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">4.58890438079834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65353727340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57113122940063</t>
+    <t xml:space="preserve">4.65353775024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57113075256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.4757981300354</t>
@@ -2921,34 +2921,34 @@
     <t xml:space="preserve">4.46933507919312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43217182159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47095108032227</t>
+    <t xml:space="preserve">4.43217134475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47095012664795</t>
   </si>
   <si>
     <t xml:space="preserve">4.48387718200684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39985466003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37077045440674</t>
+    <t xml:space="preserve">4.39985513687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37076997756958</t>
   </si>
   <si>
     <t xml:space="preserve">4.39662313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41116571426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51457786560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46287155151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43540239334106</t>
+    <t xml:space="preserve">4.41116523742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51457738876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46287202835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43540287017822</t>
   </si>
   <si>
     <t xml:space="preserve">4.50003528594971</t>
@@ -2957,10 +2957,10 @@
     <t xml:space="preserve">4.53881454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61314249038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63253164291382</t>
+    <t xml:space="preserve">4.6131420135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63253211975098</t>
   </si>
   <si>
     <t xml:space="preserve">4.60021543502808</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">4.55658864974976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57921028137207</t>
+    <t xml:space="preserve">4.57920980453491</t>
   </si>
   <si>
     <t xml:space="preserve">4.52588844299316</t>
@@ -2981,37 +2981,37 @@
     <t xml:space="preserve">4.53235149383545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44832992553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5048828125</t>
+    <t xml:space="preserve">4.44832897186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50488328933716</t>
   </si>
   <si>
     <t xml:space="preserve">4.71978569030762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72301769256592</t>
+    <t xml:space="preserve">4.72301816940308</t>
   </si>
   <si>
     <t xml:space="preserve">4.65838479995728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68262147903442</t>
+    <t xml:space="preserve">4.68262195587158</t>
   </si>
   <si>
     <t xml:space="preserve">4.65515327453613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6438422203064</t>
+    <t xml:space="preserve">4.64384269714355</t>
   </si>
   <si>
     <t xml:space="preserve">4.70201206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585395812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7036280632019</t>
+    <t xml:space="preserve">4.68585348129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70362710952759</t>
   </si>
   <si>
     <t xml:space="preserve">4.66807985305786</t>
@@ -3023,28 +3023,28 @@
     <t xml:space="preserve">4.7262487411499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76179695129395</t>
+    <t xml:space="preserve">4.76179647445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.75048637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84905052185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87490367889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88944530487061</t>
+    <t xml:space="preserve">4.84905004501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87490320205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88944578170776</t>
   </si>
   <si>
     <t xml:space="preserve">4.91853046417236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85874557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83127689361572</t>
+    <t xml:space="preserve">4.85874509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83127641677856</t>
   </si>
   <si>
     <t xml:space="preserve">4.66161632537842</t>
@@ -3056,22 +3056,22 @@
     <t xml:space="preserve">4.72948026657104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74402284622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76018095016479</t>
+    <t xml:space="preserve">4.74402236938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76018142700195</t>
   </si>
   <si>
     <t xml:space="preserve">4.74079132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79734516143799</t>
+    <t xml:space="preserve">4.79734468460083</t>
   </si>
   <si>
     <t xml:space="preserve">4.71655368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79572868347168</t>
+    <t xml:space="preserve">4.79572916030884</t>
   </si>
   <si>
     <t xml:space="preserve">4.83450841903687</t>
@@ -3080,19 +3080,19 @@
     <t xml:space="preserve">4.74563884735107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50972986221313</t>
+    <t xml:space="preserve">4.50973033905029</t>
   </si>
   <si>
     <t xml:space="preserve">4.46448755264282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57759380340576</t>
+    <t xml:space="preserve">4.57759428024292</t>
   </si>
   <si>
     <t xml:space="preserve">4.62930059432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5598201751709</t>
+    <t xml:space="preserve">4.55982065200806</t>
   </si>
   <si>
     <t xml:space="preserve">4.54850959777832</t>
@@ -3107,19 +3107,19 @@
     <t xml:space="preserve">4.35299634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32068061828613</t>
+    <t xml:space="preserve">4.32068014144897</t>
   </si>
   <si>
     <t xml:space="preserve">4.55820465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51780939102173</t>
+    <t xml:space="preserve">4.51780891418457</t>
   </si>
   <si>
     <t xml:space="preserve">4.49518775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41762828826904</t>
+    <t xml:space="preserve">4.41762924194336</t>
   </si>
   <si>
     <t xml:space="preserve">4.48872470855713</t>
@@ -3128,10 +3128,10 @@
     <t xml:space="preserve">4.43378686904907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70524311065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73028898239136</t>
+    <t xml:space="preserve">4.7052435874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7302885055542</t>
   </si>
   <si>
     <t xml:space="preserve">4.68181419372559</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">4.77472305297852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89590883255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94034385681152</t>
+    <t xml:space="preserve">4.89590930938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94034337997437</t>
   </si>
   <si>
     <t xml:space="preserve">4.91610670089722</t>
@@ -3155,28 +3155,28 @@
     <t xml:space="preserve">5.00497674942017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04537153244019</t>
+    <t xml:space="preserve">5.04537105560303</t>
   </si>
   <si>
     <t xml:space="preserve">5.15039920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08980703353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0655689239502</t>
+    <t xml:space="preserve">5.08980655670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06556987762451</t>
   </si>
   <si>
     <t xml:space="preserve">4.9807391166687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96054124832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99285745620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01709508895874</t>
+    <t xml:space="preserve">4.96054172515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99285793304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01709461212158</t>
   </si>
   <si>
     <t xml:space="preserve">5.00093698501587</t>
@@ -3185,10 +3185,10 @@
     <t xml:space="preserve">5.01305532455444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97266054153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8999490737915</t>
+    <t xml:space="preserve">4.97266006469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89994859695435</t>
   </si>
   <si>
     <t xml:space="preserve">4.94842290878296</t>
@@ -3203,19 +3203,19 @@
     <t xml:space="preserve">5.05345058441162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16251850128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20222234725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11777019500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15577363967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18533134460449</t>
+    <t xml:space="preserve">5.16251802444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20222187042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11777067184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15577411651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18533182144165</t>
   </si>
   <si>
     <t xml:space="preserve">5.10088014602661</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">5.06287670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07554483413696</t>
+    <t xml:space="preserve">5.07554531097412</t>
   </si>
   <si>
     <t xml:space="preserve">5.02909660339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04598617553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02487325668335</t>
+    <t xml:space="preserve">5.04598665237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02487373352051</t>
   </si>
   <si>
     <t xml:space="preserve">4.87286043167114</t>
@@ -3248,13 +3248,13 @@
     <t xml:space="preserve">4.54772233963013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60261535644531</t>
+    <t xml:space="preserve">4.60261583328247</t>
   </si>
   <si>
     <t xml:space="preserve">4.53505373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71662521362305</t>
+    <t xml:space="preserve">4.71662473678589</t>
   </si>
   <si>
     <t xml:space="preserve">4.64906406402588</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">4.73773813247681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6912899017334</t>
+    <t xml:space="preserve">4.69128942489624</t>
   </si>
   <si>
     <t xml:space="preserve">4.72929286956787</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">4.61950540542603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61106061935425</t>
+    <t xml:space="preserve">4.61106014251709</t>
   </si>
   <si>
     <t xml:space="preserve">4.6068377494812</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">4.51816368103027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45482492446899</t>
+    <t xml:space="preserve">4.45482540130615</t>
   </si>
   <si>
     <t xml:space="preserve">4.38726377487183</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">4.46327018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59417009353638</t>
+    <t xml:space="preserve">4.59417057037354</t>
   </si>
   <si>
     <t xml:space="preserve">4.67017698287964</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">4.61528301239014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62795066833496</t>
+    <t xml:space="preserve">4.62795114517212</t>
   </si>
   <si>
     <t xml:space="preserve">4.6575083732605</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">4.6363959312439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77996349334717</t>
+    <t xml:space="preserve">4.77996397018433</t>
   </si>
   <si>
     <t xml:space="preserve">4.80107641220093</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">4.72506999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77151918411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70817947387695</t>
+    <t xml:space="preserve">4.77151870727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70817995071411</t>
   </si>
   <si>
     <t xml:space="preserve">4.66173124313354</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">4.53927659988403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47593832015991</t>
+    <t xml:space="preserve">4.47593784332275</t>
   </si>
   <si>
     <t xml:space="preserve">4.33659267425537</t>
@@ -3374,13 +3374,13 @@
     <t xml:space="preserve">4.31125688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42104434967041</t>
+    <t xml:space="preserve">4.42104387283325</t>
   </si>
   <si>
     <t xml:space="preserve">4.29436683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33236980438232</t>
+    <t xml:space="preserve">4.33237028121948</t>
   </si>
   <si>
     <t xml:space="preserve">4.25636339187622</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">4.39148569107056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41259908676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40415382385254</t>
+    <t xml:space="preserve">4.41259956359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4041543006897</t>
   </si>
   <si>
     <t xml:space="preserve">4.32392454147339</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">4.3197021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36192798614502</t>
+    <t xml:space="preserve">4.36192846298218</t>
   </si>
   <si>
     <t xml:space="preserve">4.27747631072998</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">4.34503793716431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27325439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14319849014282</t>
+    <t xml:space="preserve">4.27325391769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14319801330566</t>
   </si>
   <si>
     <t xml:space="preserve">4.07225894927979</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">4.02665519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03341150283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12630796432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22680568695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1009726524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03678941726685</t>
+    <t xml:space="preserve">4.03341102600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12630844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22680616378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10097217559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.036789894104</t>
   </si>
   <si>
     <t xml:space="preserve">4.02834415435791</t>
@@ -3452,10 +3452,10 @@
     <t xml:space="preserve">3.88984346389771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84761786460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97091698646545</t>
+    <t xml:space="preserve">3.84761762619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97091674804688</t>
   </si>
   <si>
     <t xml:space="preserve">4.06719160079956</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">4.04016733169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09421682357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01483249664307</t>
+    <t xml:space="preserve">4.09421634674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01483201980591</t>
   </si>
   <si>
     <t xml:space="preserve">4.15333271026611</t>
@@ -3485,13 +3485,13 @@
     <t xml:space="preserve">4.43371200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56461191177368</t>
+    <t xml:space="preserve">4.56461238861084</t>
   </si>
   <si>
     <t xml:space="preserve">4.68706703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80952167510986</t>
+    <t xml:space="preserve">4.80952215194702</t>
   </si>
   <si>
     <t xml:space="preserve">4.75462818145752</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">4.73351573944092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75040531158447</t>
+    <t xml:space="preserve">4.75040578842163</t>
   </si>
   <si>
     <t xml:space="preserve">4.76307344436646</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">4.51394081115723</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56883478164673</t>
+    <t xml:space="preserve">4.56883430480957</t>
   </si>
   <si>
     <t xml:space="preserve">4.78418684005737</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">4.58994770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52238607406616</t>
+    <t xml:space="preserve">4.52238655090332</t>
   </si>
   <si>
     <t xml:space="preserve">4.62372827529907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48438262939453</t>
+    <t xml:space="preserve">4.48438310623169</t>
   </si>
   <si>
     <t xml:space="preserve">4.44215726852417</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">4.35348320007324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4252667427063</t>
+    <t xml:space="preserve">4.42526626586914</t>
   </si>
   <si>
     <t xml:space="preserve">4.47171497344971</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">4.90241813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9784255027771</t>
+    <t xml:space="preserve">4.97842502593994</t>
   </si>
   <si>
     <t xml:space="preserve">5.04176378250122</t>
@@ -3593,10 +3593,10 @@
     <t xml:space="preserve">5.09243488311768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01220607757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98687076568604</t>
+    <t xml:space="preserve">5.01220560073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98687028884888</t>
   </si>
   <si>
     <t xml:space="preserve">4.91930913925171</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">5.00798320770264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86019277572632</t>
+    <t xml:space="preserve">4.86019325256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.94042158126831</t>
@@ -3626,25 +3626,25 @@
     <t xml:space="preserve">5.00376081466675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96998023986816</t>
+    <t xml:space="preserve">4.96998071670532</t>
   </si>
   <si>
     <t xml:space="preserve">4.83908033370972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88975095748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82535886764526</t>
+    <t xml:space="preserve">4.88975143432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82535934448242</t>
   </si>
   <si>
     <t xml:space="preserve">4.82981061935425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66955852508545</t>
+    <t xml:space="preserve">4.75858783721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66955900192261</t>
   </si>
   <si>
     <t xml:space="preserve">4.71852493286133</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">4.78529596328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90993595123291</t>
+    <t xml:space="preserve">4.90993642807007</t>
   </si>
   <si>
     <t xml:space="preserve">4.95890283584595</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">4.93219375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9678053855896</t>
+    <t xml:space="preserve">4.96780490875244</t>
   </si>
   <si>
     <t xml:space="preserve">4.9989652633667</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">4.99006223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.869873046875</t>
+    <t xml:space="preserve">4.86987352371216</t>
   </si>
   <si>
     <t xml:space="preserve">4.95445108413696</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">4.88322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87432527542114</t>
+    <t xml:space="preserve">4.87432479858398</t>
   </si>
   <si>
     <t xml:space="preserve">4.80755376815796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75413608551025</t>
+    <t xml:space="preserve">4.75413656234741</t>
   </si>
   <si>
     <t xml:space="preserve">4.85206747055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63839912414551</t>
+    <t xml:space="preserve">4.63839864730835</t>
   </si>
   <si>
     <t xml:space="preserve">4.60278749465942</t>
@@ -3716,19 +3716,19 @@
     <t xml:space="preserve">4.70517015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69626760482788</t>
+    <t xml:space="preserve">4.69626712799072</t>
   </si>
   <si>
     <t xml:space="preserve">4.68291330337524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74523305892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76303911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77194213867188</t>
+    <t xml:space="preserve">4.7452335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76303863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77194166183472</t>
   </si>
   <si>
     <t xml:space="preserve">4.71407318115234</t>
@@ -3746,25 +3746,25 @@
     <t xml:space="preserve">4.57607841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55382108688354</t>
+    <t xml:space="preserve">4.5538215637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.53156423568726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59388399124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64730167388916</t>
+    <t xml:space="preserve">4.59388446807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.647301197052</t>
   </si>
   <si>
     <t xml:space="preserve">4.66510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6161413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54936981201172</t>
+    <t xml:space="preserve">4.61614179611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54937028884888</t>
   </si>
   <si>
     <t xml:space="preserve">4.50485563278198</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">4.500403881073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49595308303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48705005645752</t>
+    <t xml:space="preserve">4.49595260620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48704957962036</t>
   </si>
   <si>
     <t xml:space="preserve">4.70071887969971</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">4.73187923431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72297620773315</t>
+    <t xml:space="preserve">4.722975730896</t>
   </si>
   <si>
     <t xml:space="preserve">4.44609642028809</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">4.24489164352417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28228378295898</t>
+    <t xml:space="preserve">4.28228330612183</t>
   </si>
   <si>
     <t xml:space="preserve">4.31789493560791</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">4.34282302856445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41226530075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4354133605957</t>
+    <t xml:space="preserve">4.41226577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43541288375854</t>
   </si>
   <si>
     <t xml:space="preserve">4.42829084396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3926796913147</t>
+    <t xml:space="preserve">4.39267921447754</t>
   </si>
   <si>
     <t xml:space="preserve">4.45588970184326</t>
@@ -3857,22 +3857,22 @@
     <t xml:space="preserve">4.30186986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25201368331909</t>
+    <t xml:space="preserve">4.25201416015625</t>
   </si>
   <si>
     <t xml:space="preserve">4.26625823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27694177627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20928001403809</t>
+    <t xml:space="preserve">4.27694225311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20928049087524</t>
   </si>
   <si>
     <t xml:space="preserve">4.19147443771362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21996355056763</t>
+    <t xml:space="preserve">4.21996307373047</t>
   </si>
   <si>
     <t xml:space="preserve">4.27160024642944</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">4.30899238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3054313659668</t>
+    <t xml:space="preserve">4.30543088912964</t>
   </si>
   <si>
     <t xml:space="preserve">4.39445972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40336275100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47369527816772</t>
+    <t xml:space="preserve">4.40336322784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47369575500488</t>
   </si>
   <si>
     <t xml:space="preserve">4.49150133132935</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">4.46034145355225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43185234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5226616859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47814702987671</t>
+    <t xml:space="preserve">4.43185186386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52266120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47814750671387</t>
   </si>
   <si>
     <t xml:space="preserve">4.56717586517334</t>
@@ -3944,22 +3944,22 @@
     <t xml:space="preserve">4.61169004440308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5983362197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55827283859253</t>
+    <t xml:space="preserve">4.59833574295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55827236175537</t>
   </si>
   <si>
     <t xml:space="preserve">4.58053016662598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56272459030151</t>
+    <t xml:space="preserve">4.56272411346436</t>
   </si>
   <si>
     <t xml:space="preserve">4.5849814414978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54046678543091</t>
+    <t xml:space="preserve">4.54046726226807</t>
   </si>
   <si>
     <t xml:space="preserve">4.51375865936279</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">4.6918158531189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74968433380127</t>
+    <t xml:space="preserve">4.74968481063843</t>
   </si>
   <si>
     <t xml:space="preserve">4.4692440032959</t>
@@ -3998,16 +3998,16 @@
     <t xml:space="preserve">4.44787693023682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57162761688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79419898986816</t>
+    <t xml:space="preserve">4.57162714004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79419946670532</t>
   </si>
   <si>
     <t xml:space="preserve">4.80310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82090759277344</t>
+    <t xml:space="preserve">4.8209080696106</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
@@ -4890,6 +4890,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.4350004196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45499992370605</t>
   </si>
 </sst>
 </file>
@@ -64352,7 +64355,7 @@
     </row>
     <row r="2275">
       <c r="A2275" s="1" t="n">
-        <v>45947.6500462963</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2275" t="n">
         <v>2359124</v>
@@ -64373,6 +64376,32 @@
         <v>1625</v>
       </c>
       <c r="H2275" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" s="1" t="n">
+        <v>45950.6496296296</v>
+      </c>
+      <c r="B2276" t="n">
+        <v>3098911</v>
+      </c>
+      <c r="C2276" t="n">
+        <v>8.56999969482422</v>
+      </c>
+      <c r="D2276" t="n">
+        <v>8.43000030517578</v>
+      </c>
+      <c r="E2276" t="n">
+        <v>8.4350004196167</v>
+      </c>
+      <c r="F2276" t="n">
+        <v>8.45499992370605</v>
+      </c>
+      <c r="G2276" t="s">
+        <v>1626</v>
+      </c>
+      <c r="H2276" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="1627">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="1628">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,34 +44,34 @@
     <t xml:space="preserve">IG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50135779380798</t>
+    <t xml:space="preserve">2.5013575553894</t>
   </si>
   <si>
     <t xml:space="preserve">2.32790565490723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16488718986511</t>
+    <t xml:space="preserve">2.16488695144653</t>
   </si>
   <si>
     <t xml:space="preserve">2.17271208763123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09315896034241</t>
+    <t xml:space="preserve">2.09315919876099</t>
   </si>
   <si>
     <t xml:space="preserve">2.06185936927795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08663845062256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0449059009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06055521965027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04360127449036</t>
+    <t xml:space="preserve">2.08663821220398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04490542411804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06055545806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04360151290894</t>
   </si>
   <si>
     <t xml:space="preserve">2.10489630699158</t>
@@ -83,52 +83,52 @@
     <t xml:space="preserve">2.14532494544983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1792323589325</t>
+    <t xml:space="preserve">2.17923307418823</t>
   </si>
   <si>
     <t xml:space="preserve">2.20009922981262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20140337944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17792844772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13228368759155</t>
+    <t xml:space="preserve">2.20140361785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17792892456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13228344917297</t>
   </si>
   <si>
     <t xml:space="preserve">2.09837579727173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22357392311096</t>
+    <t xml:space="preserve">2.22357416152954</t>
   </si>
   <si>
     <t xml:space="preserve">2.29138970375061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33181834220886</t>
+    <t xml:space="preserve">2.3318178653717</t>
   </si>
   <si>
     <t xml:space="preserve">2.29791045188904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2379195690155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30051898956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30443120002747</t>
+    <t xml:space="preserve">2.23791933059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30051875114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30443096160889</t>
   </si>
   <si>
     <t xml:space="preserve">2.37094259262085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3461639881134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39572167396545</t>
+    <t xml:space="preserve">2.34616374969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39572191238403</t>
   </si>
   <si>
     <t xml:space="preserve">2.45571231842041</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">2.42180466651917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41006708145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43093371391296</t>
+    <t xml:space="preserve">2.41006731987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43093347549438</t>
   </si>
   <si>
     <t xml:space="preserve">2.43745422363281</t>
@@ -167,82 +167,82 @@
     <t xml:space="preserve">2.4452793598175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46614551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43223738670349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44006276130676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47788333892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43615007400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43354177474976</t>
+    <t xml:space="preserve">2.46614599227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43223786354065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44006252288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47788310050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43615031242371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43354201316833</t>
   </si>
   <si>
     <t xml:space="preserve">2.4570164680481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48831653594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41789221763611</t>
+    <t xml:space="preserve">2.48831605911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41789197921753</t>
   </si>
   <si>
     <t xml:space="preserve">2.43484616279602</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41267561912537</t>
+    <t xml:space="preserve">2.41267585754395</t>
   </si>
   <si>
     <t xml:space="preserve">2.35659718513489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27573990821838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29530191421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.312255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38137602806091</t>
+    <t xml:space="preserve">2.2757396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29530215263367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31225609779358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38137555122375</t>
   </si>
   <si>
     <t xml:space="preserve">2.40876317024231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39311361312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44919204711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46744990348816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47397041320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48440384864807</t>
+    <t xml:space="preserve">2.39311337471008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44919180870056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46744918823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47397065162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48440337181091</t>
   </si>
   <si>
     <t xml:space="preserve">2.4635374546051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47266626358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47136211395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44788765907288</t>
+    <t xml:space="preserve">2.47266602516174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47136259078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4478874206543</t>
   </si>
   <si>
     <t xml:space="preserve">2.49614095687866</t>
@@ -254,28 +254,28 @@
     <t xml:space="preserve">2.51570343971252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53135299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51439929008484</t>
+    <t xml:space="preserve">2.53135323524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51439905166626</t>
   </si>
   <si>
     <t xml:space="preserve">2.53656983375549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52744078636169</t>
+    <t xml:space="preserve">2.52744054794312</t>
   </si>
   <si>
     <t xml:space="preserve">2.54830694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55091524124146</t>
+    <t xml:space="preserve">2.55091547966003</t>
   </si>
   <si>
     <t xml:space="preserve">2.5378737449646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58612751960754</t>
+    <t xml:space="preserve">2.58612728118896</t>
   </si>
   <si>
     <t xml:space="preserve">2.57699847221375</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">2.60438537597656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57308602333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66959261894226</t>
+    <t xml:space="preserve">2.57308578491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66959285736084</t>
   </si>
   <si>
     <t xml:space="preserve">2.68393850326538</t>
@@ -299,22 +299,22 @@
     <t xml:space="preserve">2.69828391075134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64872646331787</t>
+    <t xml:space="preserve">2.64872622489929</t>
   </si>
   <si>
     <t xml:space="preserve">2.64742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68133044242859</t>
+    <t xml:space="preserve">2.68133020401001</t>
   </si>
   <si>
     <t xml:space="preserve">2.67480969429016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63438057899475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64351010322571</t>
+    <t xml:space="preserve">2.63438105583191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64350962638855</t>
   </si>
   <si>
     <t xml:space="preserve">2.69567561149597</t>
@@ -323,58 +323,58 @@
     <t xml:space="preserve">2.69958829879761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67872214317322</t>
+    <t xml:space="preserve">2.67872166633606</t>
   </si>
   <si>
     <t xml:space="preserve">2.73480033874512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.772620677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7543625831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71262955665588</t>
+    <t xml:space="preserve">2.77262020111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75436210632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71262979507446</t>
   </si>
   <si>
     <t xml:space="preserve">2.70089268684387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7021963596344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66176772117615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7830536365509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7452335357666</t>
+    <t xml:space="preserve">2.70219659805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66176819801331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78305387496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74523305892944</t>
   </si>
   <si>
     <t xml:space="preserve">2.69306755065918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71915030479431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70610904693604</t>
+    <t xml:space="preserve">2.71915054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70610928535461</t>
   </si>
   <si>
     <t xml:space="preserve">2.74914598464966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77783799171448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8352198600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84043645858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88738536834717</t>
+    <t xml:space="preserve">2.77783751487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83522009849548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84043622016907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88738560676575</t>
   </si>
   <si>
     <t xml:space="preserve">2.89651465415955</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">2.8534779548645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91477227210999</t>
+    <t xml:space="preserve">2.91477274894714</t>
   </si>
   <si>
     <t xml:space="preserve">3.0086715221405</t>
@@ -392,40 +392,40 @@
     <t xml:space="preserve">3.02040910720825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96824288368225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00736737251282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05822944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09885382652283</t>
+    <t xml:space="preserve">2.96824312210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00736713409424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05822896957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09885406494141</t>
   </si>
   <si>
     <t xml:space="preserve">3.15591311454773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09613704681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1382520198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09070324897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97658467292786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13417601585388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20074510574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24965333938599</t>
+    <t xml:space="preserve">3.09613680839539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13825154304504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09070301055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9765841960907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13417625427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20074534416199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24965310096741</t>
   </si>
   <si>
     <t xml:space="preserve">3.28769254684448</t>
@@ -434,79 +434,79 @@
     <t xml:space="preserve">3.23063349723816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24557733535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22248196601868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25101137161255</t>
+    <t xml:space="preserve">3.24557709693909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22248220443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25101184844971</t>
   </si>
   <si>
     <t xml:space="preserve">3.1871600151062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09477853775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11379861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19938683509827</t>
+    <t xml:space="preserve">3.09477877616882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11379837989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19938707351685</t>
   </si>
   <si>
     <t xml:space="preserve">3.10428833961487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12059116363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15727138519287</t>
+    <t xml:space="preserve">3.12059092521667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15727186203003</t>
   </si>
   <si>
     <t xml:space="preserve">3.16270613670349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14504504203796</t>
+    <t xml:space="preserve">3.14504480361938</t>
   </si>
   <si>
     <t xml:space="preserve">3.03907799720764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0282096862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96707487106323</t>
+    <t xml:space="preserve">3.02820992469788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96707463264465</t>
   </si>
   <si>
     <t xml:space="preserve">3.00375533103943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03636002540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02005839347839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97794270515442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98609399795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9956042766571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.075758934021</t>
+    <t xml:space="preserve">3.03636050224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02005815505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97794246673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98609447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99560403823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07575845718384</t>
   </si>
   <si>
     <t xml:space="preserve">3.08390998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.124666929245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10836410522461</t>
+    <t xml:space="preserve">3.12466645240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10836386680603</t>
   </si>
   <si>
     <t xml:space="preserve">3.12874221801758</t>
@@ -518,67 +518,67 @@
     <t xml:space="preserve">3.17221617698669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12602519989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15863037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22519969940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26052117347717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25237059593201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27682423591614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30671238899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30263638496399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28090023994446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21025490760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2836172580719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29856085777283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28225803375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26323914527893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25644612312317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27003192901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24693632125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23335075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21976470947266</t>
+    <t xml:space="preserve">3.12602496147156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15863060951233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2251992225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26052165031433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25237035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27682447433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30671262741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30263662338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2808997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21025514602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28361654281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29856061935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2822585105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26323843002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25644588470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27003169059753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24693655967712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23335099220276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21976494789124</t>
   </si>
   <si>
     <t xml:space="preserve">3.24150156974792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26188063621521</t>
+    <t xml:space="preserve">3.26188039779663</t>
   </si>
   <si>
     <t xml:space="preserve">3.23470902442932</t>
@@ -590,10 +590,10 @@
     <t xml:space="preserve">3.23742580413818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24829483032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22791600227356</t>
+    <t xml:space="preserve">3.24829459190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22791624069214</t>
   </si>
   <si>
     <t xml:space="preserve">3.19395279884338</t>
@@ -602,193 +602,193 @@
     <t xml:space="preserve">3.16542291641235</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1844425201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18172550201416</t>
+    <t xml:space="preserve">3.18444299697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18172597885132</t>
   </si>
   <si>
     <t xml:space="preserve">3.20753836631775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24014353752136</t>
+    <t xml:space="preserve">3.24014377593994</t>
   </si>
   <si>
     <t xml:space="preserve">3.26731419563293</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2428605556488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22655773162842</t>
+    <t xml:space="preserve">3.24286007881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.226557970047</t>
   </si>
   <si>
     <t xml:space="preserve">3.23199200630188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20617914199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14640355110168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16814017295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157155990601</t>
+    <t xml:space="preserve">3.20617938041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14640331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16813993453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157132148743</t>
   </si>
   <si>
     <t xml:space="preserve">3.16678190231323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21704816818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22927474975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24421906471252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21433091163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25372838973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35154485702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49147510528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39366006851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46430420875549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50506067276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41675448417664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40656590461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44732213020325</t>
+    <t xml:space="preserve">3.21704792976379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22927522659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2442193031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21433067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25372886657715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35154438018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49147534370422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3936595916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46430444717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50506091117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41675496101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40656542778015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44732236862183</t>
   </si>
   <si>
     <t xml:space="preserve">3.43373680114746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42694449424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47109699249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46770071983337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48128628730774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50166463851929</t>
+    <t xml:space="preserve">3.42694425582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47109723091125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46770048141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.481285572052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50166440010071</t>
   </si>
   <si>
     <t xml:space="preserve">3.54242086410522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51185393333435</t>
+    <t xml:space="preserve">3.51185369491577</t>
   </si>
   <si>
     <t xml:space="preserve">3.54581737518311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55940270423889</t>
+    <t xml:space="preserve">3.55940246582031</t>
   </si>
   <si>
     <t xml:space="preserve">3.63412261009216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60015964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53223180770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48468232154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55261039733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61374449729919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5254385471344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58997011184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60355567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5933666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62053728103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59676289558411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56619548797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562784194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45411491394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45751142501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39637684822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32301473617554</t>
+    <t xml:space="preserve">3.60015988349915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53223133087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48468279838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55260992050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61374473571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52543878555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5899703502655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60355544090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59336614608765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62053775787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59676241874695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5661952495575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53562808036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45411539077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45751166343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39637660980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3230152130127</t>
   </si>
   <si>
     <t xml:space="preserve">3.38279128074646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40996217727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38958358764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.328449010849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30807113647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31078815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35018587112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37599778175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35426115989685</t>
+    <t xml:space="preserve">3.40996241569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38958382606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32844924926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30807065963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31078863143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35018610954285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37599802017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35426139831543</t>
   </si>
   <si>
     <t xml:space="preserve">3.37328124046326</t>
@@ -797,232 +797,232 @@
     <t xml:space="preserve">3.34339284896851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36648869514465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37871527671814</t>
+    <t xml:space="preserve">3.3664882183075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37871551513672</t>
   </si>
   <si>
     <t xml:space="preserve">3.36105418205261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12126970291138</t>
+    <t xml:space="preserve">3.12127041816711</t>
   </si>
   <si>
     <t xml:space="preserve">3.16406416893005</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06624865531921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0458710193634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03228569030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00239682197571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02209568023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02549266815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04655003547668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99424576759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96164035797119</t>
+    <t xml:space="preserve">3.06624889373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04587078094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03228545188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00239706039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0220959186554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0254921913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04654979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9942455291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96164059638977</t>
   </si>
   <si>
     <t xml:space="preserve">2.97862267494202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11651492118835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06828713417053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00035881996155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96639513969421</t>
+    <t xml:space="preserve">3.03092622756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11651539802551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06828737258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00035858154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96639537811279</t>
   </si>
   <si>
     <t xml:space="preserve">2.929034948349</t>
   </si>
   <si>
-    <t xml:space="preserve">2.924959897995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01326513290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09409880638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14300680160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2353880405426</t>
+    <t xml:space="preserve">2.92495965957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01326537132263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0940990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14300727844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23538780212402</t>
   </si>
   <si>
     <t xml:space="preserve">3.22723722457886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21297216415405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19327306747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27342772483826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29448556900024</t>
+    <t xml:space="preserve">3.21297264099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19327354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27342796325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29448509216309</t>
   </si>
   <si>
     <t xml:space="preserve">3.20414161682129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30739140510559</t>
+    <t xml:space="preserve">3.30739116668701</t>
   </si>
   <si>
     <t xml:space="preserve">3.2856547832489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36377120018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39909338951111</t>
+    <t xml:space="preserve">3.36377167701721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39909410476685</t>
   </si>
   <si>
     <t xml:space="preserve">3.47924828529358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47517251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48196530342102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43713355064392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44392585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49962639808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52815628051758</t>
+    <t xml:space="preserve">3.47517275810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4819655418396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43713307380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44392561912537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49962615966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52815580368042</t>
   </si>
   <si>
     <t xml:space="preserve">3.47788953781128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51457047462463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45887017250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5267972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5200047492981</t>
+    <t xml:space="preserve">3.51456999778748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45886969566345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52679753303528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52000498771667</t>
   </si>
   <si>
     <t xml:space="preserve">3.5757052898407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62733030319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64499139785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60423517227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60287618637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62597107887268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49419260025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45615339279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41539692878723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45479393005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4425675868988</t>
+    <t xml:space="preserve">3.62733054161072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64499163627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60423493385315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60287594795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62597179412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49419236183167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45615315437317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41539621353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45479416847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44256711006165</t>
   </si>
   <si>
     <t xml:space="preserve">3.36309242248535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39298033714294</t>
+    <t xml:space="preserve">3.39298009872437</t>
   </si>
   <si>
     <t xml:space="preserve">3.39461994171143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45400047302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46107029914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36280798912048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28151297569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23414874076843</t>
+    <t xml:space="preserve">3.45400094985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46107006072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36280846595764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28151273727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23414921760559</t>
   </si>
   <si>
     <t xml:space="preserve">3.07367897033691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16699194908142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1528537273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18961334228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27868509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2574770450592</t>
+    <t xml:space="preserve">3.1669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15285348892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18961358070374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2786853313446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25747728347778</t>
   </si>
   <si>
     <t xml:space="preserve">3.23556351661682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23768401145935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20163083076477</t>
+    <t xml:space="preserve">3.23768377304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20163106918335</t>
   </si>
   <si>
     <t xml:space="preserve">3.34089374542236</t>
@@ -1031,46 +1031,46 @@
     <t xml:space="preserve">3.43774175643921</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39037823677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41087865829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37624001502991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38967084884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40946459770203</t>
+    <t xml:space="preserve">3.39037775993347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41087889671326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37624025344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38967132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40946435928345</t>
   </si>
   <si>
     <t xml:space="preserve">3.46319055557251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33735942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31544470787048</t>
+    <t xml:space="preserve">3.33735966682434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3154444694519</t>
   </si>
   <si>
     <t xml:space="preserve">3.29989266395569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3444287776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35432529449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32958340644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33806657791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29211640357971</t>
+    <t xml:space="preserve">3.34442853927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35432505607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32958316802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3380663394928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29211664199829</t>
   </si>
   <si>
     <t xml:space="preserve">3.35644626617432</t>
@@ -1082,64 +1082,64 @@
     <t xml:space="preserve">3.40098166465759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41865491867065</t>
+    <t xml:space="preserve">3.41865515708923</t>
   </si>
   <si>
     <t xml:space="preserve">3.37765336036682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32534146308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35573959350586</t>
+    <t xml:space="preserve">3.32534170150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35573935508728</t>
   </si>
   <si>
     <t xml:space="preserve">3.34230780601501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40027499198914</t>
+    <t xml:space="preserve">3.40027475357056</t>
   </si>
   <si>
     <t xml:space="preserve">3.45258688926697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44834494590759</t>
+    <t xml:space="preserve">3.44834518432617</t>
   </si>
   <si>
     <t xml:space="preserve">3.44269013404846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4511730670929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41229295730591</t>
+    <t xml:space="preserve">3.45117330551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41229248046875</t>
   </si>
   <si>
     <t xml:space="preserve">3.40734434127808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46036291122437</t>
+    <t xml:space="preserve">3.46036314964294</t>
   </si>
   <si>
     <t xml:space="preserve">3.43137979507446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47874283790588</t>
+    <t xml:space="preserve">3.4787425994873</t>
   </si>
   <si>
     <t xml:space="preserve">3.42077541351318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42572402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51479601860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49429512023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39532661437988</t>
+    <t xml:space="preserve">3.42572426795959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51479554176331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4942946434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39532685279846</t>
   </si>
   <si>
     <t xml:space="preserve">3.41582703590393</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">3.42925882339478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40239596366882</t>
+    <t xml:space="preserve">3.4023962020874</t>
   </si>
   <si>
     <t xml:space="preserve">3.36139440536499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3882577419281</t>
+    <t xml:space="preserve">3.38825750350952</t>
   </si>
   <si>
     <t xml:space="preserve">3.4327929019928</t>
@@ -1166,22 +1166,22 @@
     <t xml:space="preserve">3.29706478118896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30413389205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30837559700012</t>
+    <t xml:space="preserve">3.30413365364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30837535858154</t>
   </si>
   <si>
     <t xml:space="preserve">3.2878749370575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31615138053894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25182247161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2899956703186</t>
+    <t xml:space="preserve">3.31615161895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25182223320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28999590873718</t>
   </si>
   <si>
     <t xml:space="preserve">3.33311796188354</t>
@@ -1190,22 +1190,22 @@
     <t xml:space="preserve">3.33099699020386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33382511138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32675528526306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34654903411865</t>
+    <t xml:space="preserve">3.33382487297058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32675504684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34654927253723</t>
   </si>
   <si>
     <t xml:space="preserve">3.47450113296509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49924325942993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49641609191895</t>
+    <t xml:space="preserve">3.49924373626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49641561508179</t>
   </si>
   <si>
     <t xml:space="preserve">3.46248340606689</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">3.45682883262634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45470762252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38613629341125</t>
+    <t xml:space="preserve">3.45470809936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38613677024841</t>
   </si>
   <si>
     <t xml:space="preserve">3.45753526687622</t>
@@ -1229,13 +1229,13 @@
     <t xml:space="preserve">3.37411880493164</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39391255378723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42006850242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30978989601135</t>
+    <t xml:space="preserve">3.39391231536865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42006874084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30978965759277</t>
   </si>
   <si>
     <t xml:space="preserve">3.32816934585571</t>
@@ -1244,19 +1244,19 @@
     <t xml:space="preserve">3.35715317726135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27797842025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24899482727051</t>
+    <t xml:space="preserve">3.27797865867615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24899458885193</t>
   </si>
   <si>
     <t xml:space="preserve">3.21011400222778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23485636711121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20516586303711</t>
+    <t xml:space="preserve">3.23485612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20516562461853</t>
   </si>
   <si>
     <t xml:space="preserve">3.15780258178711</t>
@@ -1268,34 +1268,34 @@
     <t xml:space="preserve">3.15356040000916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24546003341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16911220550537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19809675216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18890714645386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23909735679626</t>
+    <t xml:space="preserve">3.24546027183533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16911244392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19809651374817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1889066696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23909759521484</t>
   </si>
   <si>
     <t xml:space="preserve">3.23344230651855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27727150917053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23202848434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22920060157776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22495913505554</t>
+    <t xml:space="preserve">3.27727127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23202896118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22920107841492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22495937347412</t>
   </si>
   <si>
     <t xml:space="preserve">3.27232313156128</t>
@@ -1310,40 +1310,40 @@
     <t xml:space="preserve">3.4250168800354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43491411209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48863935470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44693160057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38755011558533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35927367210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34160113334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3005998134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3048415184021</t>
+    <t xml:space="preserve">3.43491387367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48863983154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4469313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38755083084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3592734336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34160137176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30059957504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30484127998352</t>
   </si>
   <si>
     <t xml:space="preserve">3.27585744857788</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3960337638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34937739372253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36068773269653</t>
+    <t xml:space="preserve">3.39603328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34937715530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36068797111511</t>
   </si>
   <si>
     <t xml:space="preserve">3.36704969406128</t>
@@ -1352,31 +1352,31 @@
     <t xml:space="preserve">3.39179182052612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41653394699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45329427719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52327871322632</t>
+    <t xml:space="preserve">3.41653418540955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.453293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5232789516449</t>
   </si>
   <si>
     <t xml:space="preserve">3.59114289283752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61235046386719</t>
+    <t xml:space="preserve">3.61235070228577</t>
   </si>
   <si>
     <t xml:space="preserve">3.63073015213013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61093664169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62790298461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60104036331177</t>
+    <t xml:space="preserve">3.61093616485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62790274620056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60103988647461</t>
   </si>
   <si>
     <t xml:space="preserve">3.59962582588196</t>
@@ -1385,52 +1385,52 @@
     <t xml:space="preserve">3.51055407524109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53176212310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57841849327087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61941909790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64910984039307</t>
+    <t xml:space="preserve">3.53176164627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57841801643372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61941933631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64911031723022</t>
   </si>
   <si>
     <t xml:space="preserve">3.67880058288574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6208336353302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68586993217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70849132537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65335154533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68304252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68728351593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67738676071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71414637565613</t>
+    <t xml:space="preserve">3.62083315849304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68587017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70849061012268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65335130691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68304228782654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68728375434875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67738699913025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71414685249329</t>
   </si>
   <si>
     <t xml:space="preserve">3.71131873130798</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70990490913391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72545719146729</t>
+    <t xml:space="preserve">3.70990538597107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72545742988586</t>
   </si>
   <si>
     <t xml:space="preserve">3.73252701759338</t>
@@ -1439,106 +1439,106 @@
     <t xml:space="preserve">3.731112241745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67173147201538</t>
+    <t xml:space="preserve">3.6717312335968</t>
   </si>
   <si>
     <t xml:space="preserve">3.69293904304504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71980166435242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779926300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61517810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68869733810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69576644897461</t>
+    <t xml:space="preserve">3.71980214118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779902458191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61517786979675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68869709968567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69576668739319</t>
   </si>
   <si>
     <t xml:space="preserve">3.69435286521912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69718074798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68162798881531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75232005119324</t>
+    <t xml:space="preserve">3.69718050956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68162894248962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7523205280304</t>
   </si>
   <si>
     <t xml:space="preserve">3.7438371181488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72262978553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76504516601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7593891620636</t>
+    <t xml:space="preserve">3.72262954711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76504492759705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75938892364502</t>
   </si>
   <si>
     <t xml:space="preserve">3.71697425842285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78342485427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83997774124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86542725563049</t>
+    <t xml:space="preserve">3.78342461585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83997821807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86542701721191</t>
   </si>
   <si>
     <t xml:space="preserve">3.83573651313782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8244252204895</t>
+    <t xml:space="preserve">3.82442545890808</t>
   </si>
   <si>
     <t xml:space="preserve">3.79756283760071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81735587120056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85977125167847</t>
+    <t xml:space="preserve">3.81735682487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8597719669342</t>
   </si>
   <si>
     <t xml:space="preserve">3.86966824531555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88380718231201</t>
+    <t xml:space="preserve">3.88380670547485</t>
   </si>
   <si>
     <t xml:space="preserve">3.87532377243042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89370369911194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88804864883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85270261764526</t>
+    <t xml:space="preserve">3.89370346069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88804841041565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85270237922668</t>
   </si>
   <si>
     <t xml:space="preserve">3.87108206748962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89087629318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84139204025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88239312171936</t>
+    <t xml:space="preserve">3.89087581634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84139180183411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88239336013794</t>
   </si>
   <si>
     <t xml:space="preserve">3.92339468002319</t>
@@ -1547,37 +1547,37 @@
     <t xml:space="preserve">3.88946175575256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90360069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92056584358215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91915321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96439528465271</t>
+    <t xml:space="preserve">3.90360045433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92056655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9191529750824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96439504623413</t>
   </si>
   <si>
     <t xml:space="preserve">3.95732641220093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91066932678223</t>
+    <t xml:space="preserve">3.91067004203796</t>
   </si>
   <si>
     <t xml:space="preserve">3.93329119682312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90642738342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90501475334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92198038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91208386421204</t>
+    <t xml:space="preserve">3.90642786026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90501403808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92197966575623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9120831489563</t>
   </si>
   <si>
     <t xml:space="preserve">3.9304633140564</t>
@@ -1586,34 +1586,34 @@
     <t xml:space="preserve">3.87956523895264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89794516563416</t>
+    <t xml:space="preserve">3.89794540405273</t>
   </si>
   <si>
     <t xml:space="preserve">3.88097929954529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.947429895401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89228963851929</t>
+    <t xml:space="preserve">3.94742941856384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89228987693787</t>
   </si>
   <si>
     <t xml:space="preserve">3.87390971183777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90925621986389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95025730133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98136186599731</t>
+    <t xml:space="preserve">3.90925598144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95025777816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98136162757874</t>
   </si>
   <si>
     <t xml:space="preserve">4.00963830947876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08032989501953</t>
+    <t xml:space="preserve">4.08032941818237</t>
   </si>
   <si>
     <t xml:space="preserve">4.07891607284546</t>
@@ -1628,16 +1628,16 @@
     <t xml:space="preserve">4.21100330352783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.213942527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24921846389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20512390136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1948356628418</t>
+    <t xml:space="preserve">4.21394300460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24921798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20512342453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19483518600464</t>
   </si>
   <si>
     <t xml:space="preserve">4.12281465530396</t>
@@ -1646,16 +1646,16 @@
     <t xml:space="preserve">4.1081166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16543865203857</t>
+    <t xml:space="preserve">4.16543912887573</t>
   </si>
   <si>
     <t xml:space="preserve">4.21541213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26979494094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30507040023804</t>
+    <t xml:space="preserve">4.26979541778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3050708770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.32123899459839</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">4.36827230453491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33152723312378</t>
+    <t xml:space="preserve">4.33152770996094</t>
   </si>
   <si>
     <t xml:space="preserve">4.32564783096313</t>
@@ -1673,22 +1673,22 @@
     <t xml:space="preserve">4.288902759552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35651397705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34328508377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49908590316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44764232635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44617223739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48291778564453</t>
+    <t xml:space="preserve">4.35651350021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34328556060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49908542633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44764184951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4461727142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48291730880737</t>
   </si>
   <si>
     <t xml:space="preserve">4.48732662200928</t>
@@ -1697,19 +1697,19 @@
     <t xml:space="preserve">4.45352172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43735408782959</t>
+    <t xml:space="preserve">4.43735361099243</t>
   </si>
   <si>
     <t xml:space="preserve">4.35210466384888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34181642532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33446645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43147420883179</t>
+    <t xml:space="preserve">4.34181594848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33446598052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43147468566895</t>
   </si>
   <si>
     <t xml:space="preserve">4.47997808456421</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">4.44911193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43882322311401</t>
+    <t xml:space="preserve">4.43882369995117</t>
   </si>
   <si>
     <t xml:space="preserve">4.49467611312866</t>
@@ -1727,13 +1727,13 @@
     <t xml:space="preserve">4.51966285705566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50349473953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54317951202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56228685379028</t>
+    <t xml:space="preserve">4.50349521636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54317998886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56228733062744</t>
   </si>
   <si>
     <t xml:space="preserve">4.57698535919189</t>
@@ -1745,13 +1745,13 @@
     <t xml:space="preserve">4.54170989990234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54905891418457</t>
+    <t xml:space="preserve">4.54905939102173</t>
   </si>
   <si>
     <t xml:space="preserve">4.40207767486572</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43588304519653</t>
+    <t xml:space="preserve">4.43588352203369</t>
   </si>
   <si>
     <t xml:space="preserve">4.42559480667114</t>
@@ -1760,13 +1760,13 @@
     <t xml:space="preserve">4.38885021209717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38150072097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24480867385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20218372344971</t>
+    <t xml:space="preserve">4.38150119781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24480819702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20218420028687</t>
   </si>
   <si>
     <t xml:space="preserve">4.29037237167358</t>
@@ -1775,10 +1775,10 @@
     <t xml:space="preserve">4.29331254959106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27420473098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26097631454468</t>
+    <t xml:space="preserve">4.27420520782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26097583770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.28449296951294</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">4.2183518409729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20071458816528</t>
+    <t xml:space="preserve">4.20071411132812</t>
   </si>
   <si>
     <t xml:space="preserve">4.1977744102478</t>
@@ -1826,43 +1826,43 @@
     <t xml:space="preserve">4.30213117599487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20806360244751</t>
+    <t xml:space="preserve">4.20806264877319</t>
   </si>
   <si>
     <t xml:space="preserve">4.14192199707031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1037073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18307638168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14045143127441</t>
+    <t xml:space="preserve">4.10370683670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18307685852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14045190811157</t>
   </si>
   <si>
     <t xml:space="preserve">4.12575387954712</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19336462020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18160676956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18454599380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25215721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29919099807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39031982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32711744308472</t>
+    <t xml:space="preserve">4.1933650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18160629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18454647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25215768814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29919052124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39031934738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32711791992188</t>
   </si>
   <si>
     <t xml:space="preserve">4.30066156387329</t>
@@ -1877,19 +1877,19 @@
     <t xml:space="preserve">4.36974239349365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24774837493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18895578384399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23011016845703</t>
+    <t xml:space="preserve">4.24774885177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18895483016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23011064529419</t>
   </si>
   <si>
     <t xml:space="preserve">4.18748617172241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17425680160522</t>
+    <t xml:space="preserve">4.17425727844238</t>
   </si>
   <si>
     <t xml:space="preserve">4.1727876663208</t>
@@ -1901,31 +1901,31 @@
     <t xml:space="preserve">4.1683783531189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18013715744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.238929271698</t>
+    <t xml:space="preserve">4.18013763427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23892879486084</t>
   </si>
   <si>
     <t xml:space="preserve">4.25362730026245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29478120803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33740663528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35063505172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28302383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33299732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30654096603394</t>
+    <t xml:space="preserve">4.29478216171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33740615844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35063457489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28302335739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33299684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30654001235962</t>
   </si>
   <si>
     <t xml:space="preserve">4.37268161773682</t>
@@ -1934,34 +1934,34 @@
     <t xml:space="preserve">4.39178895950317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27861404418945</t>
+    <t xml:space="preserve">4.27861356735229</t>
   </si>
   <si>
     <t xml:space="preserve">4.2242317199707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23745918273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22570037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19189500808716</t>
+    <t xml:space="preserve">4.23745965957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22570085525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19189548492432</t>
   </si>
   <si>
     <t xml:space="preserve">4.22129154205322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23598957061768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22717094421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00963878631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07431125640869</t>
+    <t xml:space="preserve">4.23599004745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22717046737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00963926315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07431077957153</t>
   </si>
   <si>
     <t xml:space="preserve">4.08900880813599</t>
@@ -1973,25 +1973,25 @@
     <t xml:space="preserve">4.01992702484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95378661155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99494099617004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04197549819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99053120613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03609561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10664653778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16396856307983</t>
+    <t xml:space="preserve">3.95378637313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9949414730072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0419750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99053168296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03609609603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10664701461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16396903991699</t>
   </si>
   <si>
     <t xml:space="preserve">4.12722396850586</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">4.13751220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00082063674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09194803237915</t>
+    <t xml:space="preserve">4.00082015991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09194850921631</t>
   </si>
   <si>
     <t xml:space="preserve">4.08459949493408</t>
@@ -2021,67 +2021,67 @@
     <t xml:space="preserve">4.20365381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13898277282715</t>
+    <t xml:space="preserve">4.13898229598999</t>
   </si>
   <si>
     <t xml:space="preserve">4.25068759918213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20659255981445</t>
+    <t xml:space="preserve">4.20659303665161</t>
   </si>
   <si>
     <t xml:space="preserve">4.26391649246216</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30801010131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48144817352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51525354385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49761533737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40648746490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41677665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4667501449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49173641204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46086978912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46234083175659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5123143196106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45205163955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48585796356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62548875808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26538562774658</t>
+    <t xml:space="preserve">4.30801105499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48144769668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51525402069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49761581420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40648698806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41677618026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46674966812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4917368888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46087074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46234035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51231336593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45205116271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4858570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62548923492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26538515090942</t>
   </si>
   <si>
     <t xml:space="preserve">4.26244592666626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06549167633057</t>
+    <t xml:space="preserve">4.06549215316772</t>
   </si>
   <si>
     <t xml:space="preserve">4.08606910705566</t>
@@ -2096,91 +2096,91 @@
     <t xml:space="preserve">3.50182008743286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02192711830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24754309654236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15127062797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27032446861267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29531240463257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35189938545227</t>
+    <t xml:space="preserve">3.02192759513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24754333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15127086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27032470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29531216621399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35189962387085</t>
   </si>
   <si>
     <t xml:space="preserve">3.21153259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.129958152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35557436943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38937950134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34381604194641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35924863815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5709011554718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66643881797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44964170455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55693793296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58780384063721</t>
+    <t xml:space="preserve">3.12995839118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35557413101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38937926292419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34381556510925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35924816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57090091705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66643834114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44964194297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55693769454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58780407905579</t>
   </si>
   <si>
     <t xml:space="preserve">3.53636002540588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54958915710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4658100605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54811882972717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56428694725037</t>
+    <t xml:space="preserve">3.54958891868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46580982208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54811930656433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56428647041321</t>
   </si>
   <si>
     <t xml:space="preserve">3.59368348121643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62601923942566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57163619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57310557365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4408233165741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61719965934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52754139900208</t>
+    <t xml:space="preserve">3.6260187625885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57163596153259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5731053352356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44082307815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61719989776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52754163742065</t>
   </si>
   <si>
     <t xml:space="preserve">3.57457542419434</t>
@@ -2189,13 +2189,13 @@
     <t xml:space="preserve">3.56722688674927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5789852142334</t>
+    <t xml:space="preserve">3.57898497581482</t>
   </si>
   <si>
     <t xml:space="preserve">3.75168776512146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68187141418457</t>
+    <t xml:space="preserve">3.68187165260315</t>
   </si>
   <si>
     <t xml:space="preserve">3.70391869544983</t>
@@ -2204,31 +2204,31 @@
     <t xml:space="preserve">3.60691142082214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61279058456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66423416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63189792633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62454891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63777709007263</t>
+    <t xml:space="preserve">3.61279034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66423368453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6318986415863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6245493888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63777756690979</t>
   </si>
   <si>
     <t xml:space="preserve">3.62307906150818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71126770973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73626255989075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60662770271301</t>
+    <t xml:space="preserve">3.71126794815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73626279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60662698745728</t>
   </si>
   <si>
     <t xml:space="preserve">3.66372871398926</t>
@@ -2237,10 +2237,10 @@
     <t xml:space="preserve">3.63440680503845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68533444404602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75015187263489</t>
+    <t xml:space="preserve">3.68533492088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75015211105347</t>
   </si>
   <si>
     <t xml:space="preserve">3.73008918762207</t>
@@ -2249,19 +2249,19 @@
     <t xml:space="preserve">3.70231056213379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80725312232971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77021503448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81959915161133</t>
+    <t xml:space="preserve">3.80725288391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77021479606628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81959939002991</t>
   </si>
   <si>
     <t xml:space="preserve">3.90447926521301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99707531929016</t>
+    <t xml:space="preserve">3.99707579612732</t>
   </si>
   <si>
     <t xml:space="preserve">4.05108976364136</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">4.02408313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92762875556946</t>
+    <t xml:space="preserve">3.9276282787323</t>
   </si>
   <si>
     <t xml:space="preserve">3.88133025169373</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">3.81651282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91991186141968</t>
+    <t xml:space="preserve">3.91991209983826</t>
   </si>
   <si>
     <t xml:space="preserve">4.08581352233887</t>
@@ -2291,16 +2291,16 @@
     <t xml:space="preserve">4.10896253585815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14754486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02022504806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96620988845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9893593788147</t>
+    <t xml:space="preserve">4.14754438400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02022457122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96621012687683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98935961723328</t>
   </si>
   <si>
     <t xml:space="preserve">4.03565740585327</t>
@@ -2309,46 +2309,46 @@
     <t xml:space="preserve">4.08967208862305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03179979324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07038164138794</t>
+    <t xml:space="preserve">4.03179931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07038116455078</t>
   </si>
   <si>
     <t xml:space="preserve">4.11282110214233</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0549488067627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95463562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96235203742981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93534517288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97006845474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97392630577087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0742392539978</t>
+    <t xml:space="preserve">4.05494785308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95463538169861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96235156059265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93534445762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97006821632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97392678260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07423973083496</t>
   </si>
   <si>
     <t xml:space="preserve">4.1243953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10510492324829</t>
+    <t xml:space="preserve">4.10510444641113</t>
   </si>
   <si>
     <t xml:space="preserve">4.09352970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04723167419434</t>
+    <t xml:space="preserve">4.04723119735718</t>
   </si>
   <si>
     <t xml:space="preserve">4.12825345993042</t>
@@ -2357,37 +2357,37 @@
     <t xml:space="preserve">4.25943183898926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26714897155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21313333511353</t>
+    <t xml:space="preserve">4.26714849472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21313381195068</t>
   </si>
   <si>
     <t xml:space="preserve">4.19770097732544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16297721862793</t>
+    <t xml:space="preserve">4.16297769546509</t>
   </si>
   <si>
     <t xml:space="preserve">4.16683578491211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22470855712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28643894195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36746072769165</t>
+    <t xml:space="preserve">4.22470808029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28643941879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36746120452881</t>
   </si>
   <si>
     <t xml:space="preserve">4.42147588729858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3906102180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37517738342285</t>
+    <t xml:space="preserve">4.39060974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37517786026001</t>
   </si>
   <si>
     <t xml:space="preserve">4.36360311508179</t>
@@ -2405,16 +2405,16 @@
     <t xml:space="preserve">4.31344652175903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30187225341797</t>
+    <t xml:space="preserve">4.30187129974365</t>
   </si>
   <si>
     <t xml:space="preserve">4.13597011566162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22856664657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18612623214722</t>
+    <t xml:space="preserve">4.22856616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18612670898438</t>
   </si>
   <si>
     <t xml:space="preserve">4.17455148696899</t>
@@ -2423,13 +2423,13 @@
     <t xml:space="preserve">4.1899847984314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11667919158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17841005325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15526151657104</t>
+    <t xml:space="preserve">4.11667966842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17840957641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15526103973389</t>
   </si>
   <si>
     <t xml:space="preserve">4.15140295028687</t>
@@ -2447,25 +2447,25 @@
     <t xml:space="preserve">3.89290499687195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97778511047363</t>
+    <t xml:space="preserve">3.97778487205505</t>
   </si>
   <si>
     <t xml:space="preserve">4.06266450881958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94691896438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98550152778625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9816427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88904619216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71157026290894</t>
+    <t xml:space="preserve">3.94691920280457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9855010509491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98164296150208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88904643058777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71157002449036</t>
   </si>
   <si>
     <t xml:space="preserve">3.72700309753418</t>
@@ -2477,10 +2477,10 @@
     <t xml:space="preserve">3.83194518089294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86589765548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00479173660278</t>
+    <t xml:space="preserve">3.86589741706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00479125976562</t>
   </si>
   <si>
     <t xml:space="preserve">3.95077729225159</t>
@@ -2489,7 +2489,7 @@
     <t xml:space="preserve">4.08195543289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03951501846313</t>
+    <t xml:space="preserve">4.03951597213745</t>
   </si>
   <si>
     <t xml:space="preserve">4.13982820510864</t>
@@ -2501,46 +2501,46 @@
     <t xml:space="preserve">4.14368629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13211250305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93920254707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90062141418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80879640579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99321746826172</t>
+    <t xml:space="preserve">4.13211154937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93920302391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90062117576599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80879664421082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9932177066803</t>
   </si>
   <si>
     <t xml:space="preserve">4.01250791549683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95849370956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87747192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9314866065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9237699508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86203980445862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8180558681488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80571007728577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85818147659302</t>
+    <t xml:space="preserve">3.95849394798279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8774721622467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93148636817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92377018928528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86203932762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81805562973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80570983886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85818123817444</t>
   </si>
   <si>
     <t xml:space="preserve">3.89676308631897</t>
@@ -2549,22 +2549,22 @@
     <t xml:space="preserve">3.85663795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82114219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83811855316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94306135177612</t>
+    <t xml:space="preserve">3.82114267349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83811902999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9430615901947</t>
   </si>
   <si>
     <t xml:space="preserve">3.90833735466003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88518834114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83503198623657</t>
+    <t xml:space="preserve">3.88518786430359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83503174781799</t>
   </si>
   <si>
     <t xml:space="preserve">3.76712822914124</t>
@@ -2573,22 +2573,22 @@
     <t xml:space="preserve">3.76249814033508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82268595695496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79799294471741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87361359596252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02794122695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04337310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2092752456665</t>
+    <t xml:space="preserve">3.82268571853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79799342155457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87361407279968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02794075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04337358474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20927619934082</t>
   </si>
   <si>
     <t xml:space="preserve">4.25171566009521</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">4.31730461120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27100658416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26251888275146</t>
+    <t xml:space="preserve">4.27100610733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26251840591431</t>
   </si>
   <si>
     <t xml:space="preserve">4.2872109413147</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">4.25634527206421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24554252624512</t>
+    <t xml:space="preserve">4.24554204940796</t>
   </si>
   <si>
     <t xml:space="preserve">4.14985942840576</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">4.12979745864868</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14060020446777</t>
+    <t xml:space="preserve">4.14059972763062</t>
   </si>
   <si>
     <t xml:space="preserve">4.12362337112427</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">4.23628282546997</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18844175338745</t>
+    <t xml:space="preserve">4.18844127655029</t>
   </si>
   <si>
     <t xml:space="preserve">4.1776385307312</t>
@@ -2651,52 +2651,52 @@
     <t xml:space="preserve">4.1838116645813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20387363433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1853551864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21621990203857</t>
+    <t xml:space="preserve">4.20387411117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18535423278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21622037887573</t>
   </si>
   <si>
     <t xml:space="preserve">4.29338359832764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23165369033813</t>
+    <t xml:space="preserve">4.23165321350098</t>
   </si>
   <si>
     <t xml:space="preserve">4.25017213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23782587051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35048532485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34122610092163</t>
+    <t xml:space="preserve">4.23782634735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35048484802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34122562408447</t>
   </si>
   <si>
     <t xml:space="preserve">4.39369630813599</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47086000442505</t>
+    <t xml:space="preserve">4.47086048126221</t>
   </si>
   <si>
     <t xml:space="preserve">4.46610307693481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44025039672852</t>
+    <t xml:space="preserve">4.44024991989136</t>
   </si>
   <si>
     <t xml:space="preserve">4.3885440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35622835159302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38531303405762</t>
+    <t xml:space="preserve">4.35622787475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38531255722046</t>
   </si>
   <si>
     <t xml:space="preserve">4.37400197982788</t>
@@ -2708,13 +2708,13 @@
     <t xml:space="preserve">4.37723398208618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40147018432617</t>
+    <t xml:space="preserve">4.40147066116333</t>
   </si>
   <si>
     <t xml:space="preserve">4.45156097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47418212890625</t>
+    <t xml:space="preserve">4.47418260574341</t>
   </si>
   <si>
     <t xml:space="preserve">4.49357175827026</t>
@@ -2723,28 +2723,28 @@
     <t xml:space="preserve">4.50165128707886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52911949157715</t>
+    <t xml:space="preserve">4.52911996841431</t>
   </si>
   <si>
     <t xml:space="preserve">4.55174112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55012559890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62122106552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58405733108521</t>
+    <t xml:space="preserve">4.55012512207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62122058868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58405685424805</t>
   </si>
   <si>
     <t xml:space="preserve">4.56628322601318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54527854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52750444412231</t>
+    <t xml:space="preserve">4.54527807235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52750396728516</t>
   </si>
   <si>
     <t xml:space="preserve">4.45640802383423</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">4.45317697525024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46771955490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49841928482056</t>
+    <t xml:space="preserve">4.46771907806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49841976165771</t>
   </si>
   <si>
     <t xml:space="preserve">4.50649833679199</t>
@@ -2777,10 +2777,10 @@
     <t xml:space="preserve">4.4790301322937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52265739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54204654693604</t>
+    <t xml:space="preserve">4.52265691757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54204702377319</t>
   </si>
   <si>
     <t xml:space="preserve">4.54689359664917</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">4.37884902954102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35461235046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37238645553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5371994972229</t>
+    <t xml:space="preserve">4.35461282730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37238597869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53719902038574</t>
   </si>
   <si>
     <t xml:space="preserve">4.56789922714233</t>
@@ -2810,7 +2810,7 @@
     <t xml:space="preserve">4.6147575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61637353897095</t>
+    <t xml:space="preserve">4.61637401580811</t>
   </si>
   <si>
     <t xml:space="preserve">4.62768411636353</t>
@@ -2822,13 +2822,13 @@
     <t xml:space="preserve">4.60829496383667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63091564178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65676879882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66484880447388</t>
+    <t xml:space="preserve">4.63091611862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65676927566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66484832763672</t>
   </si>
   <si>
     <t xml:space="preserve">4.69070148468018</t>
@@ -2837,28 +2837,28 @@
     <t xml:space="preserve">4.73271179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76502799987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80219173431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79896020889282</t>
+    <t xml:space="preserve">4.76502847671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80219221115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79896068572998</t>
   </si>
   <si>
     <t xml:space="preserve">4.76987552642822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82804441452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82481336593628</t>
+    <t xml:space="preserve">4.82804489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82481384277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.84420299530029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80703973770142</t>
+    <t xml:space="preserve">4.80703926086426</t>
   </si>
   <si>
     <t xml:space="preserve">4.69554853439331</t>
@@ -2870,25 +2870,25 @@
     <t xml:space="preserve">4.53558301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5921368598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54366159439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49034070968628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49195623397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48549270629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45963954925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51134634017944</t>
+    <t xml:space="preserve">4.59213638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54366207122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49034023284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49195671081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48549318313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45964002609253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51134586334229</t>
   </si>
   <si>
     <t xml:space="preserve">4.52427244186401</t>
@@ -2912,28 +2912,28 @@
     <t xml:space="preserve">4.57113075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4757981300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42247629165649</t>
+    <t xml:space="preserve">4.47579860687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42247581481934</t>
   </si>
   <si>
     <t xml:space="preserve">4.46933507919312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43217134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47095012664795</t>
+    <t xml:space="preserve">4.43217182159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47095108032227</t>
   </si>
   <si>
     <t xml:space="preserve">4.48387718200684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39985513687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37076997756958</t>
+    <t xml:space="preserve">4.39985466003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37077045440674</t>
   </si>
   <si>
     <t xml:space="preserve">4.39662313461304</t>
@@ -2942,25 +2942,25 @@
     <t xml:space="preserve">4.41116523742676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51457738876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46287202835083</t>
+    <t xml:space="preserve">4.51457786560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46287155151367</t>
   </si>
   <si>
     <t xml:space="preserve">4.43540287017822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50003528594971</t>
+    <t xml:space="preserve">4.50003480911255</t>
   </si>
   <si>
     <t xml:space="preserve">4.53881454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6131420135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63253211975098</t>
+    <t xml:space="preserve">4.61314249038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63253164291382</t>
   </si>
   <si>
     <t xml:space="preserve">4.60021543502808</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">4.55658864974976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57920980453491</t>
+    <t xml:space="preserve">4.57921028137207</t>
   </si>
   <si>
     <t xml:space="preserve">4.52588844299316</t>
@@ -2981,40 +2981,40 @@
     <t xml:space="preserve">4.53235149383545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44832897186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50488328933716</t>
+    <t xml:space="preserve">4.44832992553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5048828125</t>
   </si>
   <si>
     <t xml:space="preserve">4.71978569030762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72301816940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65838479995728</t>
+    <t xml:space="preserve">4.72301769256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65838432312012</t>
   </si>
   <si>
     <t xml:space="preserve">4.68262195587158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65515327453613</t>
+    <t xml:space="preserve">4.65515279769897</t>
   </si>
   <si>
     <t xml:space="preserve">4.64384269714355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70201206207275</t>
+    <t xml:space="preserve">4.7020115852356</t>
   </si>
   <si>
     <t xml:space="preserve">4.68585348129272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70362710952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66807985305786</t>
+    <t xml:space="preserve">4.70362758636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6680793762207</t>
   </si>
   <si>
     <t xml:space="preserve">4.64545822143555</t>
@@ -3023,16 +3023,16 @@
     <t xml:space="preserve">4.7262487411499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76179647445679</t>
+    <t xml:space="preserve">4.76179695129395</t>
   </si>
   <si>
     <t xml:space="preserve">4.75048637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84905004501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87490320205688</t>
+    <t xml:space="preserve">4.84905052185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87490367889404</t>
   </si>
   <si>
     <t xml:space="preserve">4.88944578170776</t>
@@ -3041,10 +3041,10 @@
     <t xml:space="preserve">4.91853046417236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85874509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83127641677856</t>
+    <t xml:space="preserve">4.85874557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83127689361572</t>
   </si>
   <si>
     <t xml:space="preserve">4.66161632537842</t>
@@ -3056,10 +3056,10 @@
     <t xml:space="preserve">4.72948026657104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74402236938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76018142700195</t>
+    <t xml:space="preserve">4.74402284622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76018095016479</t>
   </si>
   <si>
     <t xml:space="preserve">4.74079132080078</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">4.71655368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79572916030884</t>
+    <t xml:space="preserve">4.79572868347168</t>
   </si>
   <si>
     <t xml:space="preserve">4.83450841903687</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">4.74563884735107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50973033905029</t>
+    <t xml:space="preserve">4.50972986221313</t>
   </si>
   <si>
     <t xml:space="preserve">4.46448755264282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57759428024292</t>
+    <t xml:space="preserve">4.57759380340576</t>
   </si>
   <si>
     <t xml:space="preserve">4.62930059432983</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">4.35299634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32068014144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55820465087891</t>
+    <t xml:space="preserve">4.32068061828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55820512771606</t>
   </si>
   <si>
     <t xml:space="preserve">4.51780891418457</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">4.49518775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41762924194336</t>
+    <t xml:space="preserve">4.4176287651062</t>
   </si>
   <si>
     <t xml:space="preserve">4.48872470855713</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">4.43378686904907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7052435874939</t>
+    <t xml:space="preserve">4.70524311065674</t>
   </si>
   <si>
     <t xml:space="preserve">4.7302885055542</t>
@@ -3143,7 +3143,7 @@
     <t xml:space="preserve">4.89590930938721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94034337997437</t>
+    <t xml:space="preserve">4.94034433364868</t>
   </si>
   <si>
     <t xml:space="preserve">4.91610670089722</t>
@@ -3152,10 +3152,10 @@
     <t xml:space="preserve">4.91206693649292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00497674942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04537105560303</t>
+    <t xml:space="preserve">5.00497627258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04537153244019</t>
   </si>
   <si>
     <t xml:space="preserve">5.15039920806885</t>
@@ -3164,19 +3164,19 @@
     <t xml:space="preserve">5.08980655670166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06556987762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9807391166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96054172515869</t>
+    <t xml:space="preserve">5.0655689239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98073959350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96054124832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.99285793304443</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01709461212158</t>
+    <t xml:space="preserve">5.01709508895874</t>
   </si>
   <si>
     <t xml:space="preserve">5.00093698501587</t>
@@ -3185,10 +3185,10 @@
     <t xml:space="preserve">5.01305532455444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97266006469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89994859695435</t>
+    <t xml:space="preserve">4.97266054153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8999490737915</t>
   </si>
   <si>
     <t xml:space="preserve">4.94842290878296</t>
@@ -3197,25 +3197,25 @@
     <t xml:space="preserve">4.92014646530151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10596513748169</t>
+    <t xml:space="preserve">5.10596466064453</t>
   </si>
   <si>
     <t xml:space="preserve">5.05345058441162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16251802444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20222187042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11777067184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15577411651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18533182144165</t>
+    <t xml:space="preserve">5.16251850128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20222234725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11777019500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15577363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18533134460449</t>
   </si>
   <si>
     <t xml:space="preserve">5.10088014602661</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">5.06287670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07554531097412</t>
+    <t xml:space="preserve">5.07554483413696</t>
   </si>
   <si>
     <t xml:space="preserve">5.02909660339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04598665237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02487373352051</t>
+    <t xml:space="preserve">5.04598617553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02487325668335</t>
   </si>
   <si>
     <t xml:space="preserve">4.87286043167114</t>
@@ -3248,13 +3248,13 @@
     <t xml:space="preserve">4.54772233963013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60261583328247</t>
+    <t xml:space="preserve">4.60261535644531</t>
   </si>
   <si>
     <t xml:space="preserve">4.53505373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71662473678589</t>
+    <t xml:space="preserve">4.71662521362305</t>
   </si>
   <si>
     <t xml:space="preserve">4.64906406402588</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">4.73773813247681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69128942489624</t>
+    <t xml:space="preserve">4.6912899017334</t>
   </si>
   <si>
     <t xml:space="preserve">4.72929286956787</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">4.61950540542603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61106014251709</t>
+    <t xml:space="preserve">4.61106061935425</t>
   </si>
   <si>
     <t xml:space="preserve">4.6068377494812</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">4.51816368103027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45482540130615</t>
+    <t xml:space="preserve">4.45482492446899</t>
   </si>
   <si>
     <t xml:space="preserve">4.38726377487183</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">4.46327018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59417057037354</t>
+    <t xml:space="preserve">4.59417009353638</t>
   </si>
   <si>
     <t xml:space="preserve">4.67017698287964</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">4.61528301239014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62795114517212</t>
+    <t xml:space="preserve">4.62795066833496</t>
   </si>
   <si>
     <t xml:space="preserve">4.6575083732605</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">4.6363959312439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77996397018433</t>
+    <t xml:space="preserve">4.77996349334717</t>
   </si>
   <si>
     <t xml:space="preserve">4.80107641220093</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">4.72506999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77151870727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70817995071411</t>
+    <t xml:space="preserve">4.77151918411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70817947387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.66173124313354</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">4.53927659988403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47593784332275</t>
+    <t xml:space="preserve">4.47593832015991</t>
   </si>
   <si>
     <t xml:space="preserve">4.33659267425537</t>
@@ -3374,13 +3374,13 @@
     <t xml:space="preserve">4.31125688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42104387283325</t>
+    <t xml:space="preserve">4.42104434967041</t>
   </si>
   <si>
     <t xml:space="preserve">4.29436683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33237028121948</t>
+    <t xml:space="preserve">4.33236980438232</t>
   </si>
   <si>
     <t xml:space="preserve">4.25636339187622</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">4.39148569107056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41259956359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4041543006897</t>
+    <t xml:space="preserve">4.41259908676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40415382385254</t>
   </si>
   <si>
     <t xml:space="preserve">4.32392454147339</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">4.3197021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36192846298218</t>
+    <t xml:space="preserve">4.36192798614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.27747631072998</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">4.34503793716431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27325391769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14319801330566</t>
+    <t xml:space="preserve">4.27325439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14319849014282</t>
   </si>
   <si>
     <t xml:space="preserve">4.07225894927979</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">4.02665519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03341102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12630844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22680616378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10097217559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.036789894104</t>
+    <t xml:space="preserve">4.03341150283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12630796432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22680568695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1009726524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03678941726685</t>
   </si>
   <si>
     <t xml:space="preserve">4.02834415435791</t>
@@ -3452,10 +3452,10 @@
     <t xml:space="preserve">3.88984346389771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84761762619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97091674804688</t>
+    <t xml:space="preserve">3.84761786460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97091698646545</t>
   </si>
   <si>
     <t xml:space="preserve">4.06719160079956</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">4.04016733169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09421634674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01483201980591</t>
+    <t xml:space="preserve">4.09421682357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01483249664307</t>
   </si>
   <si>
     <t xml:space="preserve">4.15333271026611</t>
@@ -3485,13 +3485,13 @@
     <t xml:space="preserve">4.43371200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56461238861084</t>
+    <t xml:space="preserve">4.56461191177368</t>
   </si>
   <si>
     <t xml:space="preserve">4.68706703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80952215194702</t>
+    <t xml:space="preserve">4.80952167510986</t>
   </si>
   <si>
     <t xml:space="preserve">4.75462818145752</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">4.73351573944092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75040578842163</t>
+    <t xml:space="preserve">4.75040531158447</t>
   </si>
   <si>
     <t xml:space="preserve">4.76307344436646</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">4.51394081115723</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56883430480957</t>
+    <t xml:space="preserve">4.56883478164673</t>
   </si>
   <si>
     <t xml:space="preserve">4.78418684005737</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">4.58994770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52238655090332</t>
+    <t xml:space="preserve">4.52238607406616</t>
   </si>
   <si>
     <t xml:space="preserve">4.62372827529907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48438310623169</t>
+    <t xml:space="preserve">4.48438262939453</t>
   </si>
   <si>
     <t xml:space="preserve">4.44215726852417</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">4.35348320007324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42526626586914</t>
+    <t xml:space="preserve">4.4252667427063</t>
   </si>
   <si>
     <t xml:space="preserve">4.47171497344971</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">4.90241813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97842502593994</t>
+    <t xml:space="preserve">4.9784255027771</t>
   </si>
   <si>
     <t xml:space="preserve">5.04176378250122</t>
@@ -3593,10 +3593,10 @@
     <t xml:space="preserve">5.09243488311768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01220560073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98687028884888</t>
+    <t xml:space="preserve">5.01220607757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98687076568604</t>
   </si>
   <si>
     <t xml:space="preserve">4.91930913925171</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">5.00798320770264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86019325256348</t>
+    <t xml:space="preserve">4.86019277572632</t>
   </si>
   <si>
     <t xml:space="preserve">4.94042158126831</t>
@@ -3626,25 +3626,25 @@
     <t xml:space="preserve">5.00376081466675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96998071670532</t>
+    <t xml:space="preserve">4.96998023986816</t>
   </si>
   <si>
     <t xml:space="preserve">4.83908033370972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88975143432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82535934448242</t>
+    <t xml:space="preserve">4.88975095748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82535886764526</t>
   </si>
   <si>
     <t xml:space="preserve">4.82981061935425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75858783721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66955900192261</t>
+    <t xml:space="preserve">4.75858736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66955852508545</t>
   </si>
   <si>
     <t xml:space="preserve">4.71852493286133</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">4.78529596328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90993642807007</t>
+    <t xml:space="preserve">4.90993595123291</t>
   </si>
   <si>
     <t xml:space="preserve">4.95890283584595</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">4.93219375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96780490875244</t>
+    <t xml:space="preserve">4.9678053855896</t>
   </si>
   <si>
     <t xml:space="preserve">4.9989652633667</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">4.99006223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86987352371216</t>
+    <t xml:space="preserve">4.869873046875</t>
   </si>
   <si>
     <t xml:space="preserve">4.95445108413696</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">4.88322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87432479858398</t>
+    <t xml:space="preserve">4.87432527542114</t>
   </si>
   <si>
     <t xml:space="preserve">4.80755376815796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75413656234741</t>
+    <t xml:space="preserve">4.75413608551025</t>
   </si>
   <si>
     <t xml:space="preserve">4.85206747055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63839864730835</t>
+    <t xml:space="preserve">4.63839912414551</t>
   </si>
   <si>
     <t xml:space="preserve">4.60278749465942</t>
@@ -3716,19 +3716,19 @@
     <t xml:space="preserve">4.70517015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69626712799072</t>
+    <t xml:space="preserve">4.69626760482788</t>
   </si>
   <si>
     <t xml:space="preserve">4.68291330337524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7452335357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76303863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77194166183472</t>
+    <t xml:space="preserve">4.74523305892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76303911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77194213867188</t>
   </si>
   <si>
     <t xml:space="preserve">4.71407318115234</t>
@@ -3746,25 +3746,25 @@
     <t xml:space="preserve">4.57607841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5538215637207</t>
+    <t xml:space="preserve">4.55382108688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.53156423568726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59388446807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.647301197052</t>
+    <t xml:space="preserve">4.59388399124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64730167388916</t>
   </si>
   <si>
     <t xml:space="preserve">4.66510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61614179611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54937028884888</t>
+    <t xml:space="preserve">4.6161413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54936981201172</t>
   </si>
   <si>
     <t xml:space="preserve">4.50485563278198</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">4.500403881073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49595260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48704957962036</t>
+    <t xml:space="preserve">4.49595308303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48705005645752</t>
   </si>
   <si>
     <t xml:space="preserve">4.70071887969971</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">4.73187923431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.722975730896</t>
+    <t xml:space="preserve">4.72297620773315</t>
   </si>
   <si>
     <t xml:space="preserve">4.44609642028809</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">4.24489164352417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28228330612183</t>
+    <t xml:space="preserve">4.28228378295898</t>
   </si>
   <si>
     <t xml:space="preserve">4.31789493560791</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">4.34282302856445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41226577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43541288375854</t>
+    <t xml:space="preserve">4.41226530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4354133605957</t>
   </si>
   <si>
     <t xml:space="preserve">4.42829084396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39267921447754</t>
+    <t xml:space="preserve">4.3926796913147</t>
   </si>
   <si>
     <t xml:space="preserve">4.45588970184326</t>
@@ -3857,22 +3857,22 @@
     <t xml:space="preserve">4.30186986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25201416015625</t>
+    <t xml:space="preserve">4.25201368331909</t>
   </si>
   <si>
     <t xml:space="preserve">4.26625823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27694225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20928049087524</t>
+    <t xml:space="preserve">4.27694177627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20928001403809</t>
   </si>
   <si>
     <t xml:space="preserve">4.19147443771362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21996307373047</t>
+    <t xml:space="preserve">4.21996355056763</t>
   </si>
   <si>
     <t xml:space="preserve">4.27160024642944</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">4.30899238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30543088912964</t>
+    <t xml:space="preserve">4.3054313659668</t>
   </si>
   <si>
     <t xml:space="preserve">4.39445972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40336322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47369575500488</t>
+    <t xml:space="preserve">4.40336275100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47369527816772</t>
   </si>
   <si>
     <t xml:space="preserve">4.49150133132935</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">4.46034145355225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43185186386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52266120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47814750671387</t>
+    <t xml:space="preserve">4.43185234069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5226616859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47814702987671</t>
   </si>
   <si>
     <t xml:space="preserve">4.56717586517334</t>
@@ -3944,22 +3944,22 @@
     <t xml:space="preserve">4.61169004440308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59833574295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55827236175537</t>
+    <t xml:space="preserve">4.5983362197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55827283859253</t>
   </si>
   <si>
     <t xml:space="preserve">4.58053016662598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56272411346436</t>
+    <t xml:space="preserve">4.56272459030151</t>
   </si>
   <si>
     <t xml:space="preserve">4.5849814414978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54046726226807</t>
+    <t xml:space="preserve">4.54046678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.51375865936279</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">4.6918158531189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74968481063843</t>
+    <t xml:space="preserve">4.74968433380127</t>
   </si>
   <si>
     <t xml:space="preserve">4.4692440032959</t>
@@ -3998,16 +3998,16 @@
     <t xml:space="preserve">4.44787693023682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57162714004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79419946670532</t>
+    <t xml:space="preserve">4.57162761688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79419898986816</t>
   </si>
   <si>
     <t xml:space="preserve">4.80310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8209080696106</t>
+    <t xml:space="preserve">4.82090759277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
@@ -4893,6 +4893,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.45499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59000015258789</t>
   </si>
 </sst>
 </file>
@@ -64381,7 +64384,7 @@
     </row>
     <row r="2276">
       <c r="A2276" s="1" t="n">
-        <v>45950.6496296296</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2276" t="n">
         <v>3098911</v>
@@ -64402,6 +64405,32 @@
         <v>1626</v>
       </c>
       <c r="H2276" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" s="1" t="n">
+        <v>45951.6493402778</v>
+      </c>
+      <c r="B2277" t="n">
+        <v>3058850</v>
+      </c>
+      <c r="C2277" t="n">
+        <v>8.60000038146973</v>
+      </c>
+      <c r="D2277" t="n">
+        <v>8.49499988555908</v>
+      </c>
+      <c r="E2277" t="n">
+        <v>8.52000045776367</v>
+      </c>
+      <c r="F2277" t="n">
+        <v>8.59000015258789</v>
+      </c>
+      <c r="G2277" t="s">
+        <v>1627</v>
+      </c>
+      <c r="H2277" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1628" uniqueCount="1628">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="1629">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">IG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5013575553894</t>
+    <t xml:space="preserve">2.50135779380798</t>
   </si>
   <si>
     <t xml:space="preserve">2.32790565490723</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16488695144653</t>
+    <t xml:space="preserve">2.16488718986511</t>
   </si>
   <si>
     <t xml:space="preserve">2.17271208763123</t>
@@ -62,40 +62,40 @@
     <t xml:space="preserve">2.06185936927795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08663821220398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04490542411804</t>
+    <t xml:space="preserve">2.08663845062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04490566253662</t>
   </si>
   <si>
     <t xml:space="preserve">2.06055545806885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04360151290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10489630699158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1296751499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14532494544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17923307418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20009922981262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20140361785889</t>
+    <t xml:space="preserve">2.04360103607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10489678382874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12967538833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14532518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17923283576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2000994682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20140314102173</t>
   </si>
   <si>
     <t xml:space="preserve">2.17792892456055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13228344917297</t>
+    <t xml:space="preserve">2.13228368759155</t>
   </si>
   <si>
     <t xml:space="preserve">2.09837579727173</t>
@@ -104,16 +104,16 @@
     <t xml:space="preserve">2.22357416152954</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29138970375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3318178653717</t>
+    <t xml:space="preserve">2.29138946533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33181810379028</t>
   </si>
   <si>
     <t xml:space="preserve">2.29791045188904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23791933059692</t>
+    <t xml:space="preserve">2.23791980743408</t>
   </si>
   <si>
     <t xml:space="preserve">2.30051875114441</t>
@@ -122,22 +122,22 @@
     <t xml:space="preserve">2.30443096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37094259262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34616374969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39572191238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45571231842041</t>
+    <t xml:space="preserve">2.37094283103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3461639881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39572167396545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45571255683899</t>
   </si>
   <si>
     <t xml:space="preserve">2.39702582359314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38007187843323</t>
+    <t xml:space="preserve">2.38007164001465</t>
   </si>
   <si>
     <t xml:space="preserve">2.39441728591919</t>
@@ -146,28 +146,28 @@
     <t xml:space="preserve">2.42180466651917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41006731987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43093347549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43745422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701167106628</t>
+    <t xml:space="preserve">2.41006708145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43093371391296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43745446205139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701214790344</t>
   </si>
   <si>
     <t xml:space="preserve">2.45049571990967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4909245967865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4452793598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46614599227905</t>
+    <t xml:space="preserve">2.49092435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44527912139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46614575386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.43223786354065</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">2.44006252288818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47788310050964</t>
+    <t xml:space="preserve">2.47788286209106</t>
   </si>
   <si>
     <t xml:space="preserve">2.43615031242371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43354201316833</t>
+    <t xml:space="preserve">2.43354177474976</t>
   </si>
   <si>
     <t xml:space="preserve">2.4570164680481</t>
@@ -200,52 +200,52 @@
     <t xml:space="preserve">2.41267585754395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35659718513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2757396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29530215263367</t>
+    <t xml:space="preserve">2.35659694671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27573990821838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29530191421509</t>
   </si>
   <si>
     <t xml:space="preserve">2.31225609779358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38137555122375</t>
+    <t xml:space="preserve">2.38137602806091</t>
   </si>
   <si>
     <t xml:space="preserve">2.40876317024231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39311337471008</t>
+    <t xml:space="preserve">2.3931131362915</t>
   </si>
   <si>
     <t xml:space="preserve">2.44919180870056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46744918823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47397065162659</t>
+    <t xml:space="preserve">2.46744990348816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47397041320801</t>
   </si>
   <si>
     <t xml:space="preserve">2.48440337181091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4635374546051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47266602516174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47136259078979</t>
+    <t xml:space="preserve">2.46353769302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4726665019989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47136187553406</t>
   </si>
   <si>
     <t xml:space="preserve">2.4478874206543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49614095687866</t>
+    <t xml:space="preserve">2.49614071846008</t>
   </si>
   <si>
     <t xml:space="preserve">2.49744510650635</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">2.53135323524475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51439905166626</t>
+    <t xml:space="preserve">2.51439929008484</t>
   </si>
   <si>
     <t xml:space="preserve">2.53656983375549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52744054794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54830694198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55091547966003</t>
+    <t xml:space="preserve">2.52744078636169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54830718040466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55091524124146</t>
   </si>
   <si>
     <t xml:space="preserve">2.5378737449646</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">2.58612728118896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57699847221375</t>
+    <t xml:space="preserve">2.57699823379517</t>
   </si>
   <si>
     <t xml:space="preserve">2.59786462783813</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">2.60438537597656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57308578491211</t>
+    <t xml:space="preserve">2.57308602333069</t>
   </si>
   <si>
     <t xml:space="preserve">2.66959285736084</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">2.68393850326538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69828391075134</t>
+    <t xml:space="preserve">2.6982843875885</t>
   </si>
   <si>
     <t xml:space="preserve">2.64872622489929</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">2.64742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68133020401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67480969429016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63438105583191</t>
+    <t xml:space="preserve">2.68132996559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.674809217453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63438129425049</t>
   </si>
   <si>
     <t xml:space="preserve">2.64350962638855</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">2.69958829879761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67872166633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73480033874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77262020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75436210632324</t>
+    <t xml:space="preserve">2.67872190475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73480010032654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.772620677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7543625831604</t>
   </si>
   <si>
     <t xml:space="preserve">2.71262979507446</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">2.70089268684387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70219659805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66176819801331</t>
+    <t xml:space="preserve">2.7021963596344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66176772117615</t>
   </si>
   <si>
     <t xml:space="preserve">2.78305387496948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74523305892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69306755065918</t>
+    <t xml:space="preserve">2.74523329734802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69306778907776</t>
   </si>
   <si>
     <t xml:space="preserve">2.71915054321289</t>
@@ -365,19 +365,19 @@
     <t xml:space="preserve">2.74914598464966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77783751487732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83522009849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84043622016907</t>
+    <t xml:space="preserve">2.77783727645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8352198600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84043645858765</t>
   </si>
   <si>
     <t xml:space="preserve">2.88738560676575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89651465415955</t>
+    <t xml:space="preserve">2.89651489257812</t>
   </si>
   <si>
     <t xml:space="preserve">2.8534779548645</t>
@@ -389,64 +389,64 @@
     <t xml:space="preserve">3.0086715221405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02040910720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96824312210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00736713409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05822896957397</t>
+    <t xml:space="preserve">3.02040886878967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96824336051941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0073676109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05822944641113</t>
   </si>
   <si>
     <t xml:space="preserve">3.09885406494141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15591311454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09613680839539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13825154304504</t>
+    <t xml:space="preserve">3.15591287612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09613704681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1382520198822</t>
   </si>
   <si>
     <t xml:space="preserve">3.09070301055908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9765841960907</t>
+    <t xml:space="preserve">2.97658467292786</t>
   </si>
   <si>
     <t xml:space="preserve">3.13417625427246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20074534416199</t>
+    <t xml:space="preserve">3.20074510574341</t>
   </si>
   <si>
     <t xml:space="preserve">3.24965310096741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28769254684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23063349723816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24557709693909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22248220443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25101184844971</t>
+    <t xml:space="preserve">3.28769326210022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.230633020401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24557733535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22248196601868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25101161003113</t>
   </si>
   <si>
     <t xml:space="preserve">3.1871600151062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09477877616882</t>
+    <t xml:space="preserve">3.09477829933167</t>
   </si>
   <si>
     <t xml:space="preserve">3.11379837989807</t>
@@ -455,82 +455,82 @@
     <t xml:space="preserve">3.19938707351685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10428833961487</t>
+    <t xml:space="preserve">3.10428857803345</t>
   </si>
   <si>
     <t xml:space="preserve">3.12059092521667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15727186203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16270613670349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14504480361938</t>
+    <t xml:space="preserve">3.15727162361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16270542144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14504504203796</t>
   </si>
   <si>
     <t xml:space="preserve">3.03907799720764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02820992469788</t>
+    <t xml:space="preserve">3.0282096862793</t>
   </si>
   <si>
     <t xml:space="preserve">2.96707463264465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00375533103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03636050224304</t>
+    <t xml:space="preserve">3.00375580787659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03636074066162</t>
   </si>
   <si>
     <t xml:space="preserve">3.02005815505981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97794246673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98609447479248</t>
+    <t xml:space="preserve">2.97794318199158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98609399795532</t>
   </si>
   <si>
     <t xml:space="preserve">2.99560403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07575845718384</t>
+    <t xml:space="preserve">3.075758934021</t>
   </si>
   <si>
     <t xml:space="preserve">3.08390998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12466645240784</t>
+    <t xml:space="preserve">3.12466669082642</t>
   </si>
   <si>
     <t xml:space="preserve">3.10836386680603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12874221801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17900800704956</t>
+    <t xml:space="preserve">3.128741979599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1790087223053</t>
   </si>
   <si>
     <t xml:space="preserve">3.17221617698669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12602496147156</t>
+    <t xml:space="preserve">3.12602519989014</t>
   </si>
   <si>
     <t xml:space="preserve">3.15863060951233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2251992225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26052165031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25237035751343</t>
+    <t xml:space="preserve">3.22519946098328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26052212715149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25237059593201</t>
   </si>
   <si>
     <t xml:space="preserve">3.27682447433472</t>
@@ -539,85 +539,85 @@
     <t xml:space="preserve">3.30671262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30263662338257</t>
+    <t xml:space="preserve">3.30263686180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.2808997631073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21025514602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28361654281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29856061935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2822585105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26323843002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25644588470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27003169059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24693655967712</t>
+    <t xml:space="preserve">3.21025490760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2836172580719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29856085777283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28225779533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26323890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25644612312317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27003145217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2469367980957</t>
   </si>
   <si>
     <t xml:space="preserve">3.23335099220276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21976494789124</t>
+    <t xml:space="preserve">3.21976542472839</t>
   </si>
   <si>
     <t xml:space="preserve">3.24150156974792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26188039779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23470902442932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19802856445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23742580413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24829459190369</t>
+    <t xml:space="preserve">3.26187968254089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2347092628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19802832603455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23742604255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24829435348511</t>
   </si>
   <si>
     <t xml:space="preserve">3.22791624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19395279884338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16542291641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18444299697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18172597885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20753836631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24014377593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26731419563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24286007881165</t>
+    <t xml:space="preserve">3.19395232200623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16542315483093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18444323539734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18172550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20753812789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24014353752136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26731467247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24286079406738</t>
   </si>
   <si>
     <t xml:space="preserve">3.226557970047</t>
@@ -626,31 +626,31 @@
     <t xml:space="preserve">3.23199200630188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20617938041687</t>
+    <t xml:space="preserve">3.20617961883545</t>
   </si>
   <si>
     <t xml:space="preserve">3.14640331268311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16813993453979</t>
+    <t xml:space="preserve">3.16814017295837</t>
   </si>
   <si>
     <t xml:space="preserve">3.10157132148743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16678190231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21704792976379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22927522659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2442193031311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21433067321777</t>
+    <t xml:space="preserve">3.16678166389465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21704769134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22927474975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24421882629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21433043479919</t>
   </si>
   <si>
     <t xml:space="preserve">3.25372886657715</t>
@@ -659,25 +659,25 @@
     <t xml:space="preserve">3.35154438018799</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49147534370422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3936595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46430444717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50506091117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41675496101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40656542778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44732236862183</t>
+    <t xml:space="preserve">3.49147462844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39365911483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46430373191833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50506067276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41675472259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40656614303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44732213020325</t>
   </si>
   <si>
     <t xml:space="preserve">3.43373680114746</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">3.42694425582886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47109723091125</t>
+    <t xml:space="preserve">3.47109651565552</t>
   </si>
   <si>
     <t xml:space="preserve">3.46770048141479</t>
@@ -701,49 +701,49 @@
     <t xml:space="preserve">3.54242086410522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51185369491577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54581737518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55940246582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412261009216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60015988349915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53223133087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48468279838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55260992050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61374473571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52543878555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5899703502655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60355544090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59336614608765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62053775787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59676241874695</t>
+    <t xml:space="preserve">3.51185345649719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54581713676453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55940222740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412308692932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60015964508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53223156929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48468208312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55260944366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61374497413635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52543902397156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58997011184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60355567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5933666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62053680419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59676289558411</t>
   </si>
   <si>
     <t xml:space="preserve">3.5661952495575</t>
@@ -752,10 +752,10 @@
     <t xml:space="preserve">3.53562808036804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45411539077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45751166343689</t>
+    <t xml:space="preserve">3.45411515235901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45751118659973</t>
   </si>
   <si>
     <t xml:space="preserve">3.39637660980225</t>
@@ -764,61 +764,61 @@
     <t xml:space="preserve">3.3230152130127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38279128074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40996241569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38958382606506</t>
+    <t xml:space="preserve">3.3827908039093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40996217727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38958334922791</t>
   </si>
   <si>
     <t xml:space="preserve">3.32844924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30807065963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31078863143921</t>
+    <t xml:space="preserve">3.30807089805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31078839302063</t>
   </si>
   <si>
     <t xml:space="preserve">3.35018610954285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37599802017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35426139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37328124046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34339284896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3664882183075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37871551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36105418205261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12127041816711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16406416893005</t>
+    <t xml:space="preserve">3.3759982585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35426211357117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37328147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34339308738708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36648869514465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37871599197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36105442047119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12127017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16406464576721</t>
   </si>
   <si>
     <t xml:space="preserve">3.06624889373779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04587078094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03228545188904</t>
+    <t xml:space="preserve">3.0458710193634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03228569030762</t>
   </si>
   <si>
     <t xml:space="preserve">3.00239706039429</t>
@@ -827,52 +827,52 @@
     <t xml:space="preserve">3.0220959186554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0254921913147</t>
+    <t xml:space="preserve">3.02549266815186</t>
   </si>
   <si>
     <t xml:space="preserve">3.04654979705811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9942455291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96164059638977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97862267494202</t>
+    <t xml:space="preserve">2.99424529075623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96164035797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9786229133606</t>
   </si>
   <si>
     <t xml:space="preserve">3.03092622756958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11651539802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06828737258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00035858154297</t>
+    <t xml:space="preserve">3.11651515960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06828713417053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00035905838013</t>
   </si>
   <si>
     <t xml:space="preserve">2.96639537811279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.929034948349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92495965957642</t>
+    <t xml:space="preserve">2.92903542518616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.924959897995</t>
   </si>
   <si>
     <t xml:space="preserve">3.01326537132263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0940990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14300727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23538780212402</t>
+    <t xml:space="preserve">3.09409880638123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14300632476807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23538827896118</t>
   </si>
   <si>
     <t xml:space="preserve">3.22723722457886</t>
@@ -884,43 +884,43 @@
     <t xml:space="preserve">3.19327354431152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27342796325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29448509216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20414161682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30739116668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2856547832489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36377167701721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39909410476685</t>
+    <t xml:space="preserve">3.27342772483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29448556900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20414185523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30739212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28565454483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36377143859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39909434318542</t>
   </si>
   <si>
     <t xml:space="preserve">3.47924828529358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47517275810242</t>
+    <t xml:space="preserve">3.475172996521</t>
   </si>
   <si>
     <t xml:space="preserve">3.4819655418396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43713307380676</t>
+    <t xml:space="preserve">3.43713283538818</t>
   </si>
   <si>
     <t xml:space="preserve">3.44392561912537</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49962615966797</t>
+    <t xml:space="preserve">3.49962663650513</t>
   </si>
   <si>
     <t xml:space="preserve">3.52815580368042</t>
@@ -929,19 +929,19 @@
     <t xml:space="preserve">3.47788953781128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51456999778748</t>
+    <t xml:space="preserve">3.51457095146179</t>
   </si>
   <si>
     <t xml:space="preserve">3.45886969566345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52679753303528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52000498771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5757052898407</t>
+    <t xml:space="preserve">3.52679777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5200047492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57570576667786</t>
   </si>
   <si>
     <t xml:space="preserve">3.62733054161072</t>
@@ -950,25 +950,25 @@
     <t xml:space="preserve">3.64499163627625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60423493385315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60287594795227</t>
+    <t xml:space="preserve">3.60423445701599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60287690162659</t>
   </si>
   <si>
     <t xml:space="preserve">3.62597179412842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49419236183167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45615315437317</t>
+    <t xml:space="preserve">3.49419283866882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45615267753601</t>
   </si>
   <si>
     <t xml:space="preserve">3.41539621353149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45479416847229</t>
+    <t xml:space="preserve">3.45479440689087</t>
   </si>
   <si>
     <t xml:space="preserve">3.44256711006165</t>
@@ -977,7 +977,7 @@
     <t xml:space="preserve">3.36309242248535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39298009872437</t>
+    <t xml:space="preserve">3.39297986030579</t>
   </si>
   <si>
     <t xml:space="preserve">3.39461994171143</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">3.45400094985962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46107006072998</t>
+    <t xml:space="preserve">3.46107029914856</t>
   </si>
   <si>
     <t xml:space="preserve">3.36280846595764</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">3.28151273727417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23414921760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07367897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15285348892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18961358070374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2786853313446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25747728347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23556351661682</t>
+    <t xml:space="preserve">3.23414945602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07367920875549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16699194908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1528537273407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18961381912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27868509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2574770450592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23556327819824</t>
   </si>
   <si>
     <t xml:space="preserve">3.23768377304077</t>
@@ -1025,52 +1025,52 @@
     <t xml:space="preserve">3.20163106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34089374542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43774175643921</t>
+    <t xml:space="preserve">3.34089326858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43774151802063</t>
   </si>
   <si>
     <t xml:space="preserve">3.39037775993347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41087889671326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37624025344849</t>
+    <t xml:space="preserve">3.41087818145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37624001502991</t>
   </si>
   <si>
     <t xml:space="preserve">3.38967132568359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40946435928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46319055557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33735966682434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3154444694519</t>
+    <t xml:space="preserve">3.40946507453918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46319079399109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33735942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31544470787048</t>
   </si>
   <si>
     <t xml:space="preserve">3.29989266395569</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34442853927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35432505607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32958316802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3380663394928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29211664199829</t>
+    <t xml:space="preserve">3.34442806243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35432529449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32958340644836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33806657791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29211688041687</t>
   </si>
   <si>
     <t xml:space="preserve">3.35644626617432</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">3.3522047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40098166465759</t>
+    <t xml:space="preserve">3.40098142623901</t>
   </si>
   <si>
     <t xml:space="preserve">3.41865515708923</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37765336036682</t>
+    <t xml:space="preserve">3.3776535987854</t>
   </si>
   <si>
     <t xml:space="preserve">3.32534170150757</t>
@@ -1094,97 +1094,97 @@
     <t xml:space="preserve">3.35573935508728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34230780601501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40027475357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45258688926697</t>
+    <t xml:space="preserve">3.34230804443359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40027546882629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45258665084839</t>
   </si>
   <si>
     <t xml:space="preserve">3.44834518432617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44269013404846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45117330551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41229248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40734434127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46036314964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43137979507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4787425994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42077541351318</t>
+    <t xml:space="preserve">3.44269061088562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4511730670929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41229295730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4073441028595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46036291122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4313793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47874307632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42077612876892</t>
   </si>
   <si>
     <t xml:space="preserve">3.42572426795959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51479554176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4942946434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39532685279846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41582703590393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42925882339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4023962020874</t>
+    <t xml:space="preserve">3.51479578018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49429488182068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3953263759613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41582679748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4292585849762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40239596366882</t>
   </si>
   <si>
     <t xml:space="preserve">3.36139440536499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38825750350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4327929019928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33594536781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29706478118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30413365364075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30837535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2878749370575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31615161895752</t>
+    <t xml:space="preserve">3.3882577419281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43279337882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33594512939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29706525802612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30413389205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30837559700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28787517547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3161518573761</t>
   </si>
   <si>
     <t xml:space="preserve">3.25182223320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28999590873718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33311796188354</t>
+    <t xml:space="preserve">3.28999543190002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33311772346497</t>
   </si>
   <si>
     <t xml:space="preserve">3.33099699020386</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">3.33382487297058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32675504684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34654927253723</t>
+    <t xml:space="preserve">3.32675552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34654951095581</t>
   </si>
   <si>
     <t xml:space="preserve">3.47450113296509</t>
@@ -1205,46 +1205,46 @@
     <t xml:space="preserve">3.49924373626709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49641561508179</t>
+    <t xml:space="preserve">3.49641609191895</t>
   </si>
   <si>
     <t xml:space="preserve">3.46248340606689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45682883262634</t>
+    <t xml:space="preserve">3.45682835578918</t>
   </si>
   <si>
     <t xml:space="preserve">3.45470809936523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38613677024841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45753526687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45894956588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37411880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39391231536865</t>
+    <t xml:space="preserve">3.38613653182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45753574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45894932746887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37411856651306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39391279220581</t>
   </si>
   <si>
     <t xml:space="preserve">3.42006874084473</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30978965759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32816934585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35715317726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27797865867615</t>
+    <t xml:space="preserve">3.30978989601135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32816982269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35715293884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27797794342041</t>
   </si>
   <si>
     <t xml:space="preserve">3.24899458885193</t>
@@ -1253,28 +1253,28 @@
     <t xml:space="preserve">3.21011400222778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23485612869263</t>
+    <t xml:space="preserve">3.23485660552979</t>
   </si>
   <si>
     <t xml:space="preserve">3.20516562461853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15780258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13093948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15356040000916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24546027183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16911244392395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19809651374817</t>
+    <t xml:space="preserve">3.15780210494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.130939245224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15356087684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24545979499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16911268234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19809675216675</t>
   </si>
   <si>
     <t xml:space="preserve">3.1889066696167</t>
@@ -1283,25 +1283,25 @@
     <t xml:space="preserve">3.23909759521484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23344230651855</t>
+    <t xml:space="preserve">3.23344206809998</t>
   </si>
   <si>
     <t xml:space="preserve">3.27727127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23202896118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22920107841492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22495937347412</t>
+    <t xml:space="preserve">3.23202872276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22920060157776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22495913505554</t>
   </si>
   <si>
     <t xml:space="preserve">3.27232313156128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31473827362061</t>
+    <t xml:space="preserve">3.31473803520203</t>
   </si>
   <si>
     <t xml:space="preserve">3.3734118938446</t>
@@ -1310,13 +1310,13 @@
     <t xml:space="preserve">3.4250168800354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43491387367249</t>
+    <t xml:space="preserve">3.43491411209106</t>
   </si>
   <si>
     <t xml:space="preserve">3.48863983154297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4469313621521</t>
+    <t xml:space="preserve">3.44693112373352</t>
   </si>
   <si>
     <t xml:space="preserve">3.38755083084106</t>
@@ -1325,52 +1325,52 @@
     <t xml:space="preserve">3.3592734336853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34160137176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30059957504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30484127998352</t>
+    <t xml:space="preserve">3.34160161018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30060005187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3048415184021</t>
   </si>
   <si>
     <t xml:space="preserve">3.27585744857788</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39603328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34937715530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36068797111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36704969406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39179182052612</t>
+    <t xml:space="preserve">3.3960337638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34937691688538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36068773269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36705040931702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39179158210754</t>
   </si>
   <si>
     <t xml:space="preserve">3.41653418540955</t>
   </si>
   <si>
-    <t xml:space="preserve">3.453293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5232789516449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59114289283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61235070228577</t>
+    <t xml:space="preserve">3.45329403877258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52327871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59114265441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61235046386719</t>
   </si>
   <si>
     <t xml:space="preserve">3.63073015213013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61093616485596</t>
+    <t xml:space="preserve">3.61093640327454</t>
   </si>
   <si>
     <t xml:space="preserve">3.62790274620056</t>
@@ -1379,13 +1379,13 @@
     <t xml:space="preserve">3.60103988647461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59962582588196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51055407524109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53176164627075</t>
+    <t xml:space="preserve">3.59962630271912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51055431365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53176140785217</t>
   </si>
   <si>
     <t xml:space="preserve">3.57841801643372</t>
@@ -1397,10 +1397,10 @@
     <t xml:space="preserve">3.64911031723022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67880058288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62083315849304</t>
+    <t xml:space="preserve">3.67880082130432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6208336353302</t>
   </si>
   <si>
     <t xml:space="preserve">3.68587017059326</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">3.70849061012268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65335130691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68304228782654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68728375434875</t>
+    <t xml:space="preserve">3.65335154533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68304181098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68728423118591</t>
   </si>
   <si>
     <t xml:space="preserve">3.67738699913025</t>
@@ -1424,19 +1424,19 @@
     <t xml:space="preserve">3.71414685249329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71131873130798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70990538597107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72545742988586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73252701759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.731112241745</t>
+    <t xml:space="preserve">3.71131920814514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70990467071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72545695304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73252654075623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73111271858215</t>
   </si>
   <si>
     <t xml:space="preserve">3.6717312335968</t>
@@ -1448,37 +1448,37 @@
     <t xml:space="preserve">3.71980214118958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63779902458191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61517786979675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68869709968567</t>
+    <t xml:space="preserve">3.63779950141907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61517834663391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68869757652283</t>
   </si>
   <si>
     <t xml:space="preserve">3.69576668739319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69435286521912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69718050956726</t>
+    <t xml:space="preserve">3.69435238838196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69718027114868</t>
   </si>
   <si>
     <t xml:space="preserve">3.68162894248962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7523205280304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7438371181488</t>
+    <t xml:space="preserve">3.75232005119324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74383759498596</t>
   </si>
   <si>
     <t xml:space="preserve">3.72262954711914</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76504492759705</t>
+    <t xml:space="preserve">3.76504445075989</t>
   </si>
   <si>
     <t xml:space="preserve">3.75938892364502</t>
@@ -1487,16 +1487,16 @@
     <t xml:space="preserve">3.71697425842285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78342461585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83997821807861</t>
+    <t xml:space="preserve">3.78342413902283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83997774124146</t>
   </si>
   <si>
     <t xml:space="preserve">3.86542701721191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83573651313782</t>
+    <t xml:space="preserve">3.83573698997498</t>
   </si>
   <si>
     <t xml:space="preserve">3.82442545890808</t>
@@ -1508,7 +1508,7 @@
     <t xml:space="preserve">3.81735682487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8597719669342</t>
+    <t xml:space="preserve">3.85977244377136</t>
   </si>
   <si>
     <t xml:space="preserve">3.86966824531555</t>
@@ -1523,13 +1523,13 @@
     <t xml:space="preserve">3.89370346069336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88804841041565</t>
+    <t xml:space="preserve">3.88804817199707</t>
   </si>
   <si>
     <t xml:space="preserve">3.85270237922668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87108206748962</t>
+    <t xml:space="preserve">3.87108254432678</t>
   </si>
   <si>
     <t xml:space="preserve">3.89087581634521</t>
@@ -1538,16 +1538,16 @@
     <t xml:space="preserve">3.84139180183411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88239336013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92339468002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88946175575256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90360045433044</t>
+    <t xml:space="preserve">3.88239312171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92339420318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88946270942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9036009311676</t>
   </si>
   <si>
     <t xml:space="preserve">3.92056655883789</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">3.9191529750824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96439504623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95732641220093</t>
+    <t xml:space="preserve">3.96439552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95732593536377</t>
   </si>
   <si>
     <t xml:space="preserve">3.91067004203796</t>
@@ -1568,13 +1568,13 @@
     <t xml:space="preserve">3.93329119682312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90642786026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90501403808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92197966575623</t>
+    <t xml:space="preserve">3.90642809867859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9050145149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92198061943054</t>
   </si>
   <si>
     <t xml:space="preserve">3.9120831489563</t>
@@ -1586,55 +1586,55 @@
     <t xml:space="preserve">3.87956523895264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89794540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88097929954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94742941856384</t>
+    <t xml:space="preserve">3.89794492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88097882270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.947429895401</t>
   </si>
   <si>
     <t xml:space="preserve">3.89228987693787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87390971183777</t>
+    <t xml:space="preserve">3.87391018867493</t>
   </si>
   <si>
     <t xml:space="preserve">3.90925598144531</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95025777816772</t>
+    <t xml:space="preserve">3.95025730133057</t>
   </si>
   <si>
     <t xml:space="preserve">3.98136162757874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00963830947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08032941818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07891607284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13016366958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16984748840332</t>
+    <t xml:space="preserve">4.00963878631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08032989501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07891654968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13016319274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16984796524048</t>
   </si>
   <si>
     <t xml:space="preserve">4.21100330352783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21394300460815</t>
+    <t xml:space="preserve">4.213942527771</t>
   </si>
   <si>
     <t xml:space="preserve">4.24921798706055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20512342453003</t>
+    <t xml:space="preserve">4.20512294769287</t>
   </si>
   <si>
     <t xml:space="preserve">4.19483518600464</t>
@@ -1658,16 +1658,16 @@
     <t xml:space="preserve">4.3050708770752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32123899459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36827230453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33152770996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32564783096313</t>
+    <t xml:space="preserve">4.32123851776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36827182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33152723312378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32564735412598</t>
   </si>
   <si>
     <t xml:space="preserve">4.288902759552</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">4.34328556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49908542633057</t>
+    <t xml:space="preserve">4.49908638000488</t>
   </si>
   <si>
     <t xml:space="preserve">4.44764184951782</t>
@@ -1688,55 +1688,55 @@
     <t xml:space="preserve">4.4461727142334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48291730880737</t>
+    <t xml:space="preserve">4.48291778564453</t>
   </si>
   <si>
     <t xml:space="preserve">4.48732662200928</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45352172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43735361099243</t>
+    <t xml:space="preserve">4.45352125167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43735313415527</t>
   </si>
   <si>
     <t xml:space="preserve">4.35210466384888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34181594848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33446598052979</t>
+    <t xml:space="preserve">4.34181547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33446645736694</t>
   </si>
   <si>
     <t xml:space="preserve">4.43147468566895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47997808456421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44911193847656</t>
+    <t xml:space="preserve">4.47997856140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44911241531372</t>
   </si>
   <si>
     <t xml:space="preserve">4.43882369995117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49467611312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51966285705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50349521636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54317998886108</t>
+    <t xml:space="preserve">4.49467658996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51966238021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50349473953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54318046569824</t>
   </si>
   <si>
     <t xml:space="preserve">4.56228733062744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57698535919189</t>
+    <t xml:space="preserve">4.57698583602905</t>
   </si>
   <si>
     <t xml:space="preserve">4.52701187133789</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">4.54170989990234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54905939102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40207767486572</t>
+    <t xml:space="preserve">4.54905891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40207815170288</t>
   </si>
   <si>
     <t xml:space="preserve">4.43588352203369</t>
@@ -1760,10 +1760,10 @@
     <t xml:space="preserve">4.38885021209717</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38150119781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24480819702148</t>
+    <t xml:space="preserve">4.38150072097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2448091506958</t>
   </si>
   <si>
     <t xml:space="preserve">4.20218420028687</t>
@@ -1772,28 +1772,28 @@
     <t xml:space="preserve">4.29037237167358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29331254959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27420520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26097583770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28449296951294</t>
+    <t xml:space="preserve">4.29331207275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27420425415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26097631454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2844934463501</t>
   </si>
   <si>
     <t xml:space="preserve">4.28743314743042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11399555206299</t>
+    <t xml:space="preserve">4.11399507522583</t>
   </si>
   <si>
     <t xml:space="preserve">4.16102933883667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24186849594116</t>
+    <t xml:space="preserve">4.24186897277832</t>
   </si>
   <si>
     <t xml:space="preserve">4.15662002563477</t>
@@ -1808,10 +1808,10 @@
     <t xml:space="preserve">4.20071411132812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1977744102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34034633636475</t>
+    <t xml:space="preserve">4.19777488708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34034585952759</t>
   </si>
   <si>
     <t xml:space="preserve">4.33593702316284</t>
@@ -1820,34 +1820,34 @@
     <t xml:space="preserve">4.34916496276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.313889503479</t>
+    <t xml:space="preserve">4.31388998031616</t>
   </si>
   <si>
     <t xml:space="preserve">4.30213117599487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20806264877319</t>
+    <t xml:space="preserve">4.20806312561035</t>
   </si>
   <si>
     <t xml:space="preserve">4.14192199707031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10370683670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18307685852051</t>
+    <t xml:space="preserve">4.1037073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18307638168335</t>
   </si>
   <si>
     <t xml:space="preserve">4.14045190811157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12575387954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1933650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18160629272461</t>
+    <t xml:space="preserve">4.12575435638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19336557388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18160676956177</t>
   </si>
   <si>
     <t xml:space="preserve">4.18454647064209</t>
@@ -1856,7 +1856,7 @@
     <t xml:space="preserve">4.25215768814087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29919052124023</t>
+    <t xml:space="preserve">4.29919099807739</t>
   </si>
   <si>
     <t xml:space="preserve">4.39031934738159</t>
@@ -1877,37 +1877,37 @@
     <t xml:space="preserve">4.36974239349365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24774885177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18895483016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23011064529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18748617172241</t>
+    <t xml:space="preserve">4.24774789810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18895530700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23011016845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18748569488525</t>
   </si>
   <si>
     <t xml:space="preserve">4.17425727844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1727876663208</t>
+    <t xml:space="preserve">4.17278814315796</t>
   </si>
   <si>
     <t xml:space="preserve">4.14486122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1683783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18013763427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23892879486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25362730026245</t>
+    <t xml:space="preserve">4.16837882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18013668060303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.238929271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25362777709961</t>
   </si>
   <si>
     <t xml:space="preserve">4.29478216171265</t>
@@ -1919,40 +1919,40 @@
     <t xml:space="preserve">4.35063457489014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28302335739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33299684524536</t>
+    <t xml:space="preserve">4.28302383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33299732208252</t>
   </si>
   <si>
     <t xml:space="preserve">4.30654001235962</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37268161773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39178895950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27861356735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2242317199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23745965957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22570085525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19189548492432</t>
+    <t xml:space="preserve">4.37268209457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39178943634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27861404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22423124313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23746013641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22570133209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19189596176147</t>
   </si>
   <si>
     <t xml:space="preserve">4.22129154205322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23599004745483</t>
+    <t xml:space="preserve">4.23598957061768</t>
   </si>
   <si>
     <t xml:space="preserve">4.22717046737671</t>
@@ -1976,46 +1976,46 @@
     <t xml:space="preserve">3.95378637313843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9949414730072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0419750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99053168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03609609603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10664701461792</t>
+    <t xml:space="preserve">3.99494099617004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04197454452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99053120613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03609561920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10664653778076</t>
   </si>
   <si>
     <t xml:space="preserve">4.16396903991699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12722396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13751220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00082015991211</t>
+    <t xml:space="preserve">4.1272234916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13751268386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00081968307495</t>
   </si>
   <si>
     <t xml:space="preserve">4.09194850921631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08459949493408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02727651596069</t>
+    <t xml:space="preserve">4.08459901809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02727699279785</t>
   </si>
   <si>
     <t xml:space="preserve">4.02286720275879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10076713562012</t>
+    <t xml:space="preserve">4.10076761245728</t>
   </si>
   <si>
     <t xml:space="preserve">4.20365381240845</t>
@@ -2027,25 +2027,25 @@
     <t xml:space="preserve">4.25068759918213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20659303665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26391649246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30801105499268</t>
+    <t xml:space="preserve">4.20659351348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.263916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30801010131836</t>
   </si>
   <si>
     <t xml:space="preserve">4.48144769668579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51525402069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49761581420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40648698806763</t>
+    <t xml:space="preserve">4.51525354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49761533737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40648746490479</t>
   </si>
   <si>
     <t xml:space="preserve">4.41677618026733</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">4.46674966812134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4917368888855</t>
+    <t xml:space="preserve">4.49173641204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.46087074279785</t>
@@ -2063,13 +2063,13 @@
     <t xml:space="preserve">4.46234035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51231336593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45205116271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4858570098877</t>
+    <t xml:space="preserve">4.51231384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45205163955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48585653305054</t>
   </si>
   <si>
     <t xml:space="preserve">4.62548923492432</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">4.26538515090942</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26244592666626</t>
+    <t xml:space="preserve">4.26244640350342</t>
   </si>
   <si>
     <t xml:space="preserve">4.06549215316772</t>
@@ -2087,34 +2087,34 @@
     <t xml:space="preserve">4.08606910705566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72890543937683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51798820495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50182008743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02192759513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24754333496094</t>
+    <t xml:space="preserve">3.72890567779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51798796653748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5018196105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02192735671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24754309654236</t>
   </si>
   <si>
     <t xml:space="preserve">3.15127086639404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27032470703125</t>
+    <t xml:space="preserve">3.27032494544983</t>
   </si>
   <si>
     <t xml:space="preserve">3.29531216621399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35189962387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21153259277344</t>
+    <t xml:space="preserve">3.35189914703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21153283119202</t>
   </si>
   <si>
     <t xml:space="preserve">3.12995839118958</t>
@@ -2123,94 +2123,94 @@
     <t xml:space="preserve">3.35557413101196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38937926292419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34381556510925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35924816131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57090091705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66643834114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44964194297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55693769454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58780407905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53636002540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54958891868591</t>
+    <t xml:space="preserve">3.38937950134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34381532669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3592483997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5709011554718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66643881797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44964170455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55693817138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58780384063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53636026382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54958868026733</t>
   </si>
   <si>
     <t xml:space="preserve">3.46580982208252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54811930656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56428647041321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368348121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6260187625885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57163596153259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5731053352356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44082307815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61719989776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52754163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57457542419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56722688674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57898497581482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75168776512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68187165260315</t>
+    <t xml:space="preserve">3.54811882972717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56428718566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368300437927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62601900100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57163619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57310605049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4408233165741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61719965934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52754211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57457518577576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56722640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57898545265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75168752670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68187212944031</t>
   </si>
   <si>
     <t xml:space="preserve">3.70391869544983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60691142082214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61279034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66423368453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6318986415863</t>
+    <t xml:space="preserve">3.60691165924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61279082298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66423392295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63189816474915</t>
   </si>
   <si>
     <t xml:space="preserve">3.6245493888855</t>
@@ -2219,34 +2219,34 @@
     <t xml:space="preserve">3.63777756690979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62307906150818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71126794815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73626279830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60662698745728</t>
+    <t xml:space="preserve">3.62307929992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71126842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73626255989075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60662770271301</t>
   </si>
   <si>
     <t xml:space="preserve">3.66372871398926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63440680503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68533492088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75015211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73008918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70231056213379</t>
+    <t xml:space="preserve">3.63440656661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6853346824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75015234947205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73008966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70231080055237</t>
   </si>
   <si>
     <t xml:space="preserve">3.80725288391113</t>
@@ -2255,31 +2255,31 @@
     <t xml:space="preserve">3.77021479606628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81959939002991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90447926521301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99707579612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05108976364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02408313751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9276282787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88133025169373</t>
+    <t xml:space="preserve">3.81959891319275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90447878837585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99707531929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05109024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02408266067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92762875556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88133072853088</t>
   </si>
   <si>
     <t xml:space="preserve">3.81651282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91991209983826</t>
+    <t xml:space="preserve">3.9199116230011</t>
   </si>
   <si>
     <t xml:space="preserve">4.08581352233887</t>
@@ -2306,25 +2306,25 @@
     <t xml:space="preserve">4.03565740585327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08967208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03179931640625</t>
+    <t xml:space="preserve">4.08967256546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03179836273193</t>
   </si>
   <si>
     <t xml:space="preserve">4.07038116455078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11282110214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05494785308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95463538169861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96235156059265</t>
+    <t xml:space="preserve">4.11282062530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05494832992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95463585853577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96235251426697</t>
   </si>
   <si>
     <t xml:space="preserve">3.93534445762634</t>
@@ -2336,28 +2336,28 @@
     <t xml:space="preserve">3.97392678260803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07423973083496</t>
+    <t xml:space="preserve">4.0742392539978</t>
   </si>
   <si>
     <t xml:space="preserve">4.1243953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10510444641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09352970123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04723119735718</t>
+    <t xml:space="preserve">4.10510492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09353017807007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04723167419434</t>
   </si>
   <si>
     <t xml:space="preserve">4.12825345993042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25943183898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26714849472046</t>
+    <t xml:space="preserve">4.25943231582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26714897155762</t>
   </si>
   <si>
     <t xml:space="preserve">4.21313381195068</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">4.19770097732544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16297769546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16683578491211</t>
+    <t xml:space="preserve">4.16297721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16683530807495</t>
   </si>
   <si>
     <t xml:space="preserve">4.22470808029175</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">4.42147588729858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39060974121094</t>
+    <t xml:space="preserve">4.39061069488525</t>
   </si>
   <si>
     <t xml:space="preserve">4.37517786026001</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">4.26328992843628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24399948120117</t>
+    <t xml:space="preserve">4.24399900436401</t>
   </si>
   <si>
     <t xml:space="preserve">4.31344652175903</t>
@@ -2414,19 +2414,19 @@
     <t xml:space="preserve">4.22856616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18612670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17455148696899</t>
+    <t xml:space="preserve">4.18612718582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17455196380615</t>
   </si>
   <si>
     <t xml:space="preserve">4.1899847984314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11667966842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17840957641602</t>
+    <t xml:space="preserve">4.11667919158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17841005325317</t>
   </si>
   <si>
     <t xml:space="preserve">4.15526103973389</t>
@@ -2435,22 +2435,22 @@
     <t xml:space="preserve">4.15140295028687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15911912918091</t>
+    <t xml:space="preserve">4.15911960601807</t>
   </si>
   <si>
     <t xml:space="preserve">4.19384288787842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07809734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89290499687195</t>
+    <t xml:space="preserve">4.07809782028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89290452003479</t>
   </si>
   <si>
     <t xml:space="preserve">3.97778487205505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06266450881958</t>
+    <t xml:space="preserve">4.06266498565674</t>
   </si>
   <si>
     <t xml:space="preserve">3.94691920280457</t>
@@ -2465,19 +2465,19 @@
     <t xml:space="preserve">3.88904643058777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71157002449036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72700309753418</t>
+    <t xml:space="preserve">3.71157050132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72700262069702</t>
   </si>
   <si>
     <t xml:space="preserve">3.82885885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83194518089294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86589741706848</t>
+    <t xml:space="preserve">3.8319456577301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86589789390564</t>
   </si>
   <si>
     <t xml:space="preserve">4.00479125976562</t>
@@ -2489,28 +2489,28 @@
     <t xml:space="preserve">4.08195543289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03951597213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13982820510864</t>
+    <t xml:space="preserve">4.03951549530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13982772827148</t>
   </si>
   <si>
     <t xml:space="preserve">4.17069387435913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14368629455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13211154937744</t>
+    <t xml:space="preserve">4.14368677139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1321120262146</t>
   </si>
   <si>
     <t xml:space="preserve">3.93920302391052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90062117576599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80879664421082</t>
+    <t xml:space="preserve">3.90062069892883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80879616737366</t>
   </si>
   <si>
     <t xml:space="preserve">3.9932177066803</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">3.86203932762146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81805562973022</t>
+    <t xml:space="preserve">3.81805610656738</t>
   </si>
   <si>
     <t xml:space="preserve">3.80570983886719</t>
@@ -2555,16 +2555,16 @@
     <t xml:space="preserve">3.83811902999878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9430615901947</t>
+    <t xml:space="preserve">3.94306111335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.90833735466003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88518786430359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83503174781799</t>
+    <t xml:space="preserve">3.88518834114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83503127098083</t>
   </si>
   <si>
     <t xml:space="preserve">3.76712822914124</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">3.82268571853638</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79799342155457</t>
+    <t xml:space="preserve">3.79799294471741</t>
   </si>
   <si>
     <t xml:space="preserve">3.87361407279968</t>
@@ -2588,37 +2588,37 @@
     <t xml:space="preserve">4.04337358474731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20927619934082</t>
+    <t xml:space="preserve">4.2092752456665</t>
   </si>
   <si>
     <t xml:space="preserve">4.25171566009521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25557327270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31730461120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27100610733032</t>
+    <t xml:space="preserve">4.25557374954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3173041343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27100658416748</t>
   </si>
   <si>
     <t xml:space="preserve">4.26251840591431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2872109413147</t>
+    <t xml:space="preserve">4.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">4.25634527206421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24554204940796</t>
+    <t xml:space="preserve">4.24554252624512</t>
   </si>
   <si>
     <t xml:space="preserve">4.14985942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12979745864868</t>
+    <t xml:space="preserve">4.12979698181152</t>
   </si>
   <si>
     <t xml:space="preserve">4.14059972763062</t>
@@ -2627,16 +2627,16 @@
     <t xml:space="preserve">4.12362337112427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16837882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17146587371826</t>
+    <t xml:space="preserve">4.16837930679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1714653968811</t>
   </si>
   <si>
     <t xml:space="preserve">4.19924402236938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23628282546997</t>
+    <t xml:space="preserve">4.23628234863281</t>
   </si>
   <si>
     <t xml:space="preserve">4.18844127655029</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">4.1776385307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17918157577515</t>
+    <t xml:space="preserve">4.1791820526123</t>
   </si>
   <si>
     <t xml:space="preserve">4.1838116645813</t>
@@ -2654,13 +2654,13 @@
     <t xml:space="preserve">4.20387411117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18535423278809</t>
+    <t xml:space="preserve">4.18535470962524</t>
   </si>
   <si>
     <t xml:space="preserve">4.21622037887573</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29338359832764</t>
+    <t xml:space="preserve">4.29338407516479</t>
   </si>
   <si>
     <t xml:space="preserve">4.23165321350098</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">4.34122562408447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39369630813599</t>
+    <t xml:space="preserve">4.39369678497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.47086048126221</t>
@@ -2702,7 +2702,7 @@
     <t xml:space="preserve">4.37400197982788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39016008377075</t>
+    <t xml:space="preserve">4.39015960693359</t>
   </si>
   <si>
     <t xml:space="preserve">4.37723398208618</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">4.45156097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47418260574341</t>
+    <t xml:space="preserve">4.47418212890625</t>
   </si>
   <si>
     <t xml:space="preserve">4.49357175827026</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">4.52911996841431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55174112319946</t>
+    <t xml:space="preserve">4.55174160003662</t>
   </si>
   <si>
     <t xml:space="preserve">4.55012512207031</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">4.62122058868408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58405685424805</t>
+    <t xml:space="preserve">4.58405733108521</t>
   </si>
   <si>
     <t xml:space="preserve">4.56628322601318</t>
@@ -2762,13 +2762,13 @@
     <t xml:space="preserve">4.45317697525024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46771907806396</t>
+    <t xml:space="preserve">4.46771955490112</t>
   </si>
   <si>
     <t xml:space="preserve">4.49841976165771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50649833679199</t>
+    <t xml:space="preserve">4.50649881362915</t>
   </si>
   <si>
     <t xml:space="preserve">4.55335712432861</t>
@@ -2777,10 +2777,10 @@
     <t xml:space="preserve">4.4790301322937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52265691757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54204702377319</t>
+    <t xml:space="preserve">4.52265644073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54204654693604</t>
   </si>
   <si>
     <t xml:space="preserve">4.54689359664917</t>
@@ -2810,19 +2810,19 @@
     <t xml:space="preserve">4.6147575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61637401580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62768411636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59375238418579</t>
+    <t xml:space="preserve">4.61637353897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62768459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59375190734863</t>
   </si>
   <si>
     <t xml:space="preserve">4.60829496383667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63091611862183</t>
+    <t xml:space="preserve">4.63091564178467</t>
   </si>
   <si>
     <t xml:space="preserve">4.65676927566528</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">4.76502847671509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80219221115112</t>
+    <t xml:space="preserve">4.80219173431396</t>
   </si>
   <si>
     <t xml:space="preserve">4.79896068572998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76987552642822</t>
+    <t xml:space="preserve">4.76987600326538</t>
   </si>
   <si>
     <t xml:space="preserve">4.82804489135742</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">4.82481384277344</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84420299530029</t>
+    <t xml:space="preserve">4.84420347213745</t>
   </si>
   <si>
     <t xml:space="preserve">4.80703926086426</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">4.69554853439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57436275482178</t>
+    <t xml:space="preserve">4.57436323165894</t>
   </si>
   <si>
     <t xml:space="preserve">4.53558301925659</t>
@@ -2876,16 +2876,16 @@
     <t xml:space="preserve">4.54366207122803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49034023284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49195671081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48549318313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45964002609253</t>
+    <t xml:space="preserve">4.49034070968628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49195623397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48549270629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45964050292969</t>
   </si>
   <si>
     <t xml:space="preserve">4.51134586334229</t>
@@ -2906,16 +2906,16 @@
     <t xml:space="preserve">4.58890438079834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65353775024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57113075256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47579860687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42247581481934</t>
+    <t xml:space="preserve">4.65353727340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57113122940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4757981300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42247629165649</t>
   </si>
   <si>
     <t xml:space="preserve">4.46933507919312</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">4.39662313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41116523742676</t>
+    <t xml:space="preserve">4.41116571426392</t>
   </si>
   <si>
     <t xml:space="preserve">4.51457786560059</t>
@@ -2948,10 +2948,10 @@
     <t xml:space="preserve">4.46287155151367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43540287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50003480911255</t>
+    <t xml:space="preserve">4.43540239334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50003528594971</t>
   </si>
   <si>
     <t xml:space="preserve">4.53881454467773</t>
@@ -2993,28 +2993,28 @@
     <t xml:space="preserve">4.72301769256592</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65838432312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68262195587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65515279769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64384269714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7020115852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68585348129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70362758636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6680793762207</t>
+    <t xml:space="preserve">4.65838479995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68262147903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65515327453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6438422203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70201206207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68585395812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7036280632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66807985305786</t>
   </si>
   <si>
     <t xml:space="preserve">4.64545822143555</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">4.87490367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88944578170776</t>
+    <t xml:space="preserve">4.88944530487061</t>
   </si>
   <si>
     <t xml:space="preserve">4.91853046417236</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">4.74079132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79734468460083</t>
+    <t xml:space="preserve">4.79734516143799</t>
   </si>
   <si>
     <t xml:space="preserve">4.71655368804932</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">4.62930059432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55982065200806</t>
+    <t xml:space="preserve">4.5598201751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.54850959777832</t>
@@ -3110,16 +3110,16 @@
     <t xml:space="preserve">4.32068061828613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55820512771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51780891418457</t>
+    <t xml:space="preserve">4.55820465087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51780939102173</t>
   </si>
   <si>
     <t xml:space="preserve">4.49518775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4176287651062</t>
+    <t xml:space="preserve">4.41762828826904</t>
   </si>
   <si>
     <t xml:space="preserve">4.48872470855713</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">4.70524311065674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7302885055542</t>
+    <t xml:space="preserve">4.73028898239136</t>
   </si>
   <si>
     <t xml:space="preserve">4.68181419372559</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">4.77472305297852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89590930938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94034433364868</t>
+    <t xml:space="preserve">4.89590883255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94034385681152</t>
   </si>
   <si>
     <t xml:space="preserve">4.91610670089722</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">4.91206693649292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00497627258301</t>
+    <t xml:space="preserve">5.00497674942017</t>
   </si>
   <si>
     <t xml:space="preserve">5.04537153244019</t>
@@ -3161,19 +3161,19 @@
     <t xml:space="preserve">5.15039920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08980655670166</t>
+    <t xml:space="preserve">5.08980703353882</t>
   </si>
   <si>
     <t xml:space="preserve">5.0655689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98073959350586</t>
+    <t xml:space="preserve">4.9807391166687</t>
   </si>
   <si>
     <t xml:space="preserve">4.96054124832153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99285793304443</t>
+    <t xml:space="preserve">4.99285745620728</t>
   </si>
   <si>
     <t xml:space="preserve">5.01709508895874</t>
@@ -3197,7 +3197,7 @@
     <t xml:space="preserve">4.92014646530151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10596466064453</t>
+    <t xml:space="preserve">5.10596513748169</t>
   </si>
   <si>
     <t xml:space="preserve">5.05345058441162</t>
@@ -4896,6 +4896,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.59000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64999961853027</t>
   </si>
 </sst>
 </file>
@@ -64410,13 +64413,13 @@
     </row>
     <row r="2277">
       <c r="A2277" s="1" t="n">
-        <v>45951.6493402778</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2277" t="n">
         <v>3058850</v>
       </c>
       <c r="C2277" t="n">
-        <v>8.60000038146973</v>
+        <v>8.60499954223633</v>
       </c>
       <c r="D2277" t="n">
         <v>8.49499988555908</v>
@@ -64431,6 +64434,32 @@
         <v>1627</v>
       </c>
       <c r="H2277" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" s="1" t="n">
+        <v>45952.6495717593</v>
+      </c>
+      <c r="B2278" t="n">
+        <v>3140616</v>
+      </c>
+      <c r="C2278" t="n">
+        <v>8.6899995803833</v>
+      </c>
+      <c r="D2278" t="n">
+        <v>8.57999992370605</v>
+      </c>
+      <c r="E2278" t="n">
+        <v>8.58500003814697</v>
+      </c>
+      <c r="F2278" t="n">
+        <v>8.64999961853027</v>
+      </c>
+      <c r="G2278" t="s">
+        <v>1628</v>
+      </c>
+      <c r="H2278" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58873581886292</t>
+    <t xml:space="preserve">2.58873558044434</t>
   </si>
   <si>
     <t xml:space="preserve">IG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50135779380798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32790589332581</t>
+    <t xml:space="preserve">2.5013575553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32790613174438</t>
   </si>
   <si>
     <t xml:space="preserve">2.16488718986511</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">2.17271208763123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09315919876099</t>
+    <t xml:space="preserve">2.09315896034241</t>
   </si>
   <si>
     <t xml:space="preserve">2.06185936927795</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">2.08663821220398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04490566253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06055545806885</t>
+    <t xml:space="preserve">2.04490518569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06055521965027</t>
   </si>
   <si>
     <t xml:space="preserve">2.04360127449036</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">2.10489630699158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12967491149902</t>
+    <t xml:space="preserve">2.12967538833618</t>
   </si>
   <si>
     <t xml:space="preserve">2.14532518386841</t>
@@ -86,10 +86,10 @@
     <t xml:space="preserve">2.17923283576965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2000994682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20140385627747</t>
+    <t xml:space="preserve">2.20009875297546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20140314102173</t>
   </si>
   <si>
     <t xml:space="preserve">2.17792868614197</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">2.13228344917297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09837579727173</t>
+    <t xml:space="preserve">2.09837532043457</t>
   </si>
   <si>
     <t xml:space="preserve">2.22357392311096</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">2.29138946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33181834220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29791069030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23791933059692</t>
+    <t xml:space="preserve">2.3318178653717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29791045188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2379195690155</t>
   </si>
   <si>
     <t xml:space="preserve">2.30051851272583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30443143844604</t>
+    <t xml:space="preserve">2.30443120002747</t>
   </si>
   <si>
     <t xml:space="preserve">2.37094259262085</t>
@@ -131,52 +131,52 @@
     <t xml:space="preserve">2.39572167396545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45571208000183</t>
+    <t xml:space="preserve">2.45571255683899</t>
   </si>
   <si>
     <t xml:space="preserve">2.39702558517456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38007187843323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39441704750061</t>
+    <t xml:space="preserve">2.38007164001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39441728591919</t>
   </si>
   <si>
     <t xml:space="preserve">2.42180466651917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41006708145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43093371391296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43745446205139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701214790344</t>
+    <t xml:space="preserve">2.41006731987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43093347549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43745422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701190948486</t>
   </si>
   <si>
     <t xml:space="preserve">2.45049595832825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49092411994934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44527959823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46614575386047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43223762512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44006276130676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47788310050964</t>
+    <t xml:space="preserve">2.4909245967865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44527912139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46614551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43223786354065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44006252288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47788286209106</t>
   </si>
   <si>
     <t xml:space="preserve">2.43615031242371</t>
@@ -185,43 +185,43 @@
     <t xml:space="preserve">2.43354201316833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45701670646667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48831605911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41789197921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43484592437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41267561912537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35659718513489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27573990821838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29530262947083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.312255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38137578964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40876269340515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39311337471008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44919204711914</t>
+    <t xml:space="preserve">2.4570164680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48831582069397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41789221763611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4348464012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41267585754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35659694671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2757396697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29530191421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31225609779358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38137602806091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40876293182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3931131362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44919180870056</t>
   </si>
   <si>
     <t xml:space="preserve">2.46744966506958</t>
@@ -233,103 +233,103 @@
     <t xml:space="preserve">2.48440361022949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4635374546051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4726665019989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47136211395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44788765907288</t>
+    <t xml:space="preserve">2.46353721618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47266626358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47136187553406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4478874206543</t>
   </si>
   <si>
     <t xml:space="preserve">2.49614119529724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744534492493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51570296287537</t>
+    <t xml:space="preserve">2.49744510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51570343971252</t>
   </si>
   <si>
     <t xml:space="preserve">2.53135323524475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51439905166626</t>
+    <t xml:space="preserve">2.51439881324768</t>
   </si>
   <si>
     <t xml:space="preserve">2.53656959533691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52744054794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54830718040466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55091547966003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53787350654602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58612751960754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57699823379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59786486625671</t>
+    <t xml:space="preserve">2.52744030952454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54830694198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55091524124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53787398338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58612728118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57699799537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59786462783813</t>
   </si>
   <si>
     <t xml:space="preserve">2.60438537597656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57308602333069</t>
+    <t xml:space="preserve">2.57308578491211</t>
   </si>
   <si>
     <t xml:space="preserve">2.66959285736084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68393850326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6982843875885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64872670173645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64742207527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68133020401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67480945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63438105583191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64350962638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69567584991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69958829879761</t>
+    <t xml:space="preserve">2.68393874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69828414916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64872622489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64742231369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68132996559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67480969429016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63438057899475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64350986480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69567561149597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69958806037903</t>
   </si>
   <si>
     <t xml:space="preserve">2.67872190475464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73480033874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77262043952942</t>
+    <t xml:space="preserve">2.7348005771637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77262020111084</t>
   </si>
   <si>
     <t xml:space="preserve">2.75436234474182</t>
@@ -344,16 +344,16 @@
     <t xml:space="preserve">2.70219659805298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66176772117615</t>
+    <t xml:space="preserve">2.66176795959473</t>
   </si>
   <si>
     <t xml:space="preserve">2.78305387496948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7452335357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6930673122406</t>
+    <t xml:space="preserve">2.74523377418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69306755065918</t>
   </si>
   <si>
     <t xml:space="preserve">2.71915054321289</t>
@@ -362,19 +362,19 @@
     <t xml:space="preserve">2.70610904693604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74914574623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77783703804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8352198600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84043645858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88738608360291</t>
+    <t xml:space="preserve">2.74914622306824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77783751487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83521962165833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84043669700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88738584518433</t>
   </si>
   <si>
     <t xml:space="preserve">2.89651465415955</t>
@@ -386,61 +386,61 @@
     <t xml:space="preserve">2.91477274894714</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00867176055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02040934562683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96824312210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00736713409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05822944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09885382652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15591287612915</t>
+    <t xml:space="preserve">3.0086715221405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02040886878967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96824288368225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00736737251282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05822968482971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09885406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15591359138489</t>
   </si>
   <si>
     <t xml:space="preserve">3.09613704681396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13825154304504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09070301055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9765841960907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13417649269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20074510574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24965357780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28769254684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23063349723816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24557709693909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22248220443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25101137161255</t>
+    <t xml:space="preserve">3.1382520198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09070324897766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97658443450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13417625427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20074558258057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24965286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28769302368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23063397407532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24557757377625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22248196601868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25101161003113</t>
   </si>
   <si>
     <t xml:space="preserve">3.18715977668762</t>
@@ -449,85 +449,85 @@
     <t xml:space="preserve">3.09477853775024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11379837989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19938707351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10428857803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12059092521667</t>
+    <t xml:space="preserve">3.11379790306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19938683509827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10428810119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1205906867981</t>
   </si>
   <si>
     <t xml:space="preserve">3.15727186203003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16270565986633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14504480361938</t>
+    <t xml:space="preserve">3.16270613670349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14504456520081</t>
   </si>
   <si>
     <t xml:space="preserve">3.03907775878906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0282096862793</t>
+    <t xml:space="preserve">3.02820944786072</t>
   </si>
   <si>
     <t xml:space="preserve">2.96707463264465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00375533103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03636050224304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02005839347839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97794270515442</t>
+    <t xml:space="preserve">3.00375556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03636074066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02005791664124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97794318199158</t>
   </si>
   <si>
     <t xml:space="preserve">2.9860942363739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99560451507568</t>
+    <t xml:space="preserve">2.9956042766571</t>
   </si>
   <si>
     <t xml:space="preserve">3.07575845718384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08390998840332</t>
+    <t xml:space="preserve">3.08390974998474</t>
   </si>
   <si>
     <t xml:space="preserve">3.12466621398926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10836434364319</t>
+    <t xml:space="preserve">3.10836410522461</t>
   </si>
   <si>
     <t xml:space="preserve">3.128741979599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17900848388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17221617698669</t>
+    <t xml:space="preserve">3.17900824546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17221593856812</t>
   </si>
   <si>
     <t xml:space="preserve">3.12602543830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15863060951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22519946098328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26052141189575</t>
+    <t xml:space="preserve">3.15863037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2251992225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26052165031433</t>
   </si>
   <si>
     <t xml:space="preserve">3.25237059593201</t>
@@ -539,82 +539,82 @@
     <t xml:space="preserve">3.30671262741089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30263686180115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2808997631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21025490760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28361678123474</t>
+    <t xml:space="preserve">3.30263710021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28090000152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21025514602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28361701965332</t>
   </si>
   <si>
     <t xml:space="preserve">3.29856085777283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2822585105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26323819160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25644612312317</t>
+    <t xml:space="preserve">3.28225803375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26323890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25644659996033</t>
   </si>
   <si>
     <t xml:space="preserve">3.27003145217896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24693655967712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23335075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21976518630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24150204658508</t>
+    <t xml:space="preserve">3.24693608283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23335027694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21976447105408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24150156974792</t>
   </si>
   <si>
     <t xml:space="preserve">3.26188039779663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23470902442932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19802832603455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23742580413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24829459190369</t>
+    <t xml:space="preserve">3.23470878601074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19802856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23742604255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24829483032227</t>
   </si>
   <si>
     <t xml:space="preserve">3.22791624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19395303726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1654224395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18444299697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18172550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20753812789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24014329910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26731443405151</t>
+    <t xml:space="preserve">3.19395279884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16542291641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18444275856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18172597885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20753836631775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2401430606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26731395721436</t>
   </si>
   <si>
     <t xml:space="preserve">3.24286079406738</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">3.23199200630188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20617961883545</t>
+    <t xml:space="preserve">3.20617938041687</t>
   </si>
   <si>
     <t xml:space="preserve">3.14640355110168</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">3.16813993453979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10157108306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678190231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21704792976379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22927498817444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2442193031311</t>
+    <t xml:space="preserve">3.10157155990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678166389465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21704816818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22927522659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24421906471252</t>
   </si>
   <si>
     <t xml:space="preserve">3.21433067321777</t>
@@ -656,28 +656,28 @@
     <t xml:space="preserve">3.25372886657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35154414176941</t>
+    <t xml:space="preserve">3.35154509544373</t>
   </si>
   <si>
     <t xml:space="preserve">3.49147510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39365935325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46430397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50506067276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41675472259521</t>
+    <t xml:space="preserve">3.39365911483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46430373191833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50506019592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41675519943237</t>
   </si>
   <si>
     <t xml:space="preserve">3.40656590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44732213020325</t>
+    <t xml:space="preserve">3.44732189178467</t>
   </si>
   <si>
     <t xml:space="preserve">3.43373680114746</t>
@@ -686,109 +686,109 @@
     <t xml:space="preserve">3.42694401741028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47109699249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46770095825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48128652572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50166463851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54242062568665</t>
+    <t xml:space="preserve">3.47109723091125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46770048141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48128604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50166487693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54242134094238</t>
   </si>
   <si>
     <t xml:space="preserve">3.51185369491577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54581737518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55940294265747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412308692932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60015940666199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5322322845459</t>
+    <t xml:space="preserve">3.54581689834595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55940246582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412261009216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60015964508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53223133087158</t>
   </si>
   <si>
     <t xml:space="preserve">3.48468255996704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55261063575745</t>
+    <t xml:space="preserve">3.55260992050171</t>
   </si>
   <si>
     <t xml:space="preserve">3.61374497413635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52543878555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58997011184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60355520248413</t>
+    <t xml:space="preserve">3.52543926239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58996987342834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60355544090271</t>
   </si>
   <si>
     <t xml:space="preserve">3.5933666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62053728103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59676313400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5661952495575</t>
+    <t xml:space="preserve">3.62053751945496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59676337242126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56619548797607</t>
   </si>
   <si>
     <t xml:space="preserve">3.53562784194946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45411539077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45751142501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39637637138367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32301497459412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38279128074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40996241569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38958382606506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32844948768616</t>
+    <t xml:space="preserve">3.45411515235901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45751190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39637660980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32301545143127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38279104232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40996217727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38958358764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32844924926758</t>
   </si>
   <si>
     <t xml:space="preserve">3.30807065963745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31078743934631</t>
+    <t xml:space="preserve">3.31078815460205</t>
   </si>
   <si>
     <t xml:space="preserve">3.35018610954285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37599802017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35426211357117</t>
+    <t xml:space="preserve">3.3759982585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35426163673401</t>
   </si>
   <si>
     <t xml:space="preserve">3.37328147888184</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">3.34339308738708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36648797988892</t>
+    <t xml:space="preserve">3.36648845672607</t>
   </si>
   <si>
     <t xml:space="preserve">3.37871551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36105394363403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12126994132996</t>
+    <t xml:space="preserve">3.36105465888977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12127017974854</t>
   </si>
   <si>
     <t xml:space="preserve">3.16406440734863</t>
@@ -815,43 +815,43 @@
     <t xml:space="preserve">3.06624889373779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04587078094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03228497505188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00239682197571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0220959186554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0254921913147</t>
+    <t xml:space="preserve">3.0458710193634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03228521347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00239706039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02209568023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02549266815186</t>
   </si>
   <si>
     <t xml:space="preserve">3.04655003547668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9942455291748</t>
+    <t xml:space="preserve">2.99424576759338</t>
   </si>
   <si>
     <t xml:space="preserve">2.96164035797119</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97862267494202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11651515960693</t>
+    <t xml:space="preserve">2.97862243652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092646598816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11651539802551</t>
   </si>
   <si>
     <t xml:space="preserve">3.06828689575195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00035905838013</t>
+    <t xml:space="preserve">3.00035929679871</t>
   </si>
   <si>
     <t xml:space="preserve">2.96639537811279</t>
@@ -860,97 +860,97 @@
     <t xml:space="preserve">2.92903518676758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92495965957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01326537132263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0940990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14300656318665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2353880405426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22723698616028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21297240257263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19327354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27342772483826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29448533058167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20414185523987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30739092826843</t>
+    <t xml:space="preserve">2.924959897995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01326489448547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09409928321838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1430070400238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23538827896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2272367477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21297264099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19327330589294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27342748641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29448509216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20414233207703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30739164352417</t>
   </si>
   <si>
     <t xml:space="preserve">3.2856547832489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36377120018005</t>
+    <t xml:space="preserve">3.36377191543579</t>
   </si>
   <si>
     <t xml:space="preserve">3.39909386634827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47924828529358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.475172996521</t>
+    <t xml:space="preserve">3.47924852371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47517251968384</t>
   </si>
   <si>
     <t xml:space="preserve">3.48196530342102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43713331222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44392561912537</t>
+    <t xml:space="preserve">3.43713307380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4439263343811</t>
   </si>
   <si>
     <t xml:space="preserve">3.49962639808655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52815580368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47788953781128</t>
+    <t xml:space="preserve">3.528156042099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4778892993927</t>
   </si>
   <si>
     <t xml:space="preserve">3.51457023620605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45886969566345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52679753303528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5200047492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5757052898407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62733006477356</t>
+    <t xml:space="preserve">3.45887041091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52679800987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52000498771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57570505142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62733054161072</t>
   </si>
   <si>
     <t xml:space="preserve">3.64499163627625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60423541069031</t>
+    <t xml:space="preserve">3.60423493385315</t>
   </si>
   <si>
     <t xml:space="preserve">3.60287618637085</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">3.62597131729126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49419188499451</t>
+    <t xml:space="preserve">3.49419236183167</t>
   </si>
   <si>
     <t xml:space="preserve">3.45615291595459</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">3.41539621353149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45479440689087</t>
+    <t xml:space="preserve">3.45479393005371</t>
   </si>
   <si>
     <t xml:space="preserve">3.44256734848022</t>
@@ -977,16 +977,16 @@
     <t xml:space="preserve">3.36309266090393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39298033714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39462018013</t>
+    <t xml:space="preserve">3.39298009872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39461994171143</t>
   </si>
   <si>
     <t xml:space="preserve">3.45400071144104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46106958389282</t>
+    <t xml:space="preserve">3.46106934547424</t>
   </si>
   <si>
     <t xml:space="preserve">3.36280822753906</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">3.1669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15285348892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18961381912231</t>
+    <t xml:space="preserve">3.1528537273407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18961310386658</t>
   </si>
   <si>
     <t xml:space="preserve">3.2786853313446</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">3.23556327819824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23768424987793</t>
+    <t xml:space="preserve">3.23768377304077</t>
   </si>
   <si>
     <t xml:space="preserve">3.20163106918335</t>
@@ -1028,16 +1028,16 @@
     <t xml:space="preserve">3.34089350700378</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43774151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39037799835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4108784198761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37624001502991</t>
+    <t xml:space="preserve">3.43774175643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39037847518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41087818145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37623977661133</t>
   </si>
   <si>
     <t xml:space="preserve">3.38967132568359</t>
@@ -1049,91 +1049,91 @@
     <t xml:space="preserve">3.46319055557251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33735942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31544494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29989266395569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34442853927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35432529449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32958340644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3380663394928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29211664199829</t>
+    <t xml:space="preserve">3.33735918998718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31544518470764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29989290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3444287776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35432505607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32958316802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33806681632996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29211688041687</t>
   </si>
   <si>
     <t xml:space="preserve">3.35644626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35220432281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40098190307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41865539550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3776535987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32534170150757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35573959350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34230780601501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40027499198914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45258665084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44834518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44268989562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45117259025574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41229271888733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40734434127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46036291122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43137955665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47874307632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42077589035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42572474479675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51479578018188</t>
+    <t xml:space="preserve">3.3522047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40098118782043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41865468025208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37765336036682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32534146308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35573935508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34230828285217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40027475357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45258688926697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44834542274475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44269013404846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45117330551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41229295730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4073441028595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46036267280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43137979507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47874283790588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42077565193176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42572450637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51479601860046</t>
   </si>
   <si>
     <t xml:space="preserve">3.4942946434021</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">3.39532661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41582703590393</t>
+    <t xml:space="preserve">3.41582679748535</t>
   </si>
   <si>
     <t xml:space="preserve">3.42925834655762</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">3.40239596366882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36139464378357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3882577419281</t>
+    <t xml:space="preserve">3.36139488220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38825750350952</t>
   </si>
   <si>
     <t xml:space="preserve">3.43279314041138</t>
@@ -1163,16 +1163,16 @@
     <t xml:space="preserve">3.33594536781311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29706454277039</t>
+    <t xml:space="preserve">3.29706501960754</t>
   </si>
   <si>
     <t xml:space="preserve">3.30413389205933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30837559700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28787469863892</t>
+    <t xml:space="preserve">3.30837535858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28787541389465</t>
   </si>
   <si>
     <t xml:space="preserve">3.31615161895752</t>
@@ -1181,22 +1181,22 @@
     <t xml:space="preserve">3.25182199478149</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28999590873718</t>
+    <t xml:space="preserve">3.28999614715576</t>
   </si>
   <si>
     <t xml:space="preserve">3.33311796188354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33099675178528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33382439613342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3267560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34654951095581</t>
+    <t xml:space="preserve">3.33099722862244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33382511138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32675576210022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34654903411865</t>
   </si>
   <si>
     <t xml:space="preserve">3.47450137138367</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">3.49924349784851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49641609191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46248364448547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45682883262634</t>
+    <t xml:space="preserve">3.49641633033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46248316764832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45682835578918</t>
   </si>
   <si>
     <t xml:space="preserve">3.45470762252808</t>
@@ -1223,124 +1223,124 @@
     <t xml:space="preserve">3.45753502845764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45894980430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37411832809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39391255378723</t>
+    <t xml:space="preserve">3.45894956588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37411856651306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39391303062439</t>
   </si>
   <si>
     <t xml:space="preserve">3.42006850242615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30978918075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32816910743713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35715317726135</t>
+    <t xml:space="preserve">3.30978941917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32816958427429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35715293884277</t>
   </si>
   <si>
     <t xml:space="preserve">3.27797842025757</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24899458885193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21011424064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23485660552979</t>
+    <t xml:space="preserve">3.24899482727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21011400222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23485612869263</t>
   </si>
   <si>
     <t xml:space="preserve">3.20516562461853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15780186653137</t>
+    <t xml:space="preserve">3.15780234336853</t>
   </si>
   <si>
     <t xml:space="preserve">3.13093876838684</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15356111526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24546027183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16911268234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19809651374817</t>
+    <t xml:space="preserve">3.15356087684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24545979499817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16911292076111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19809627532959</t>
   </si>
   <si>
     <t xml:space="preserve">3.18890643119812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23909759521484</t>
+    <t xml:space="preserve">3.23909735679626</t>
   </si>
   <si>
     <t xml:space="preserve">3.23344254493713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27727150917053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2320282459259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22920060157776</t>
+    <t xml:space="preserve">3.27727127075195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23202896118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22920083999634</t>
   </si>
   <si>
     <t xml:space="preserve">3.22495937347412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2723228931427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31473803520203</t>
+    <t xml:space="preserve">3.27232313156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31473779678345</t>
   </si>
   <si>
     <t xml:space="preserve">3.37341213226318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42501640319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43491458892822</t>
+    <t xml:space="preserve">3.4250168800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43491435050964</t>
   </si>
   <si>
     <t xml:space="preserve">3.48863959312439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4469313621521</t>
+    <t xml:space="preserve">3.44693160057068</t>
   </si>
   <si>
     <t xml:space="preserve">3.38755011558533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35927367210388</t>
+    <t xml:space="preserve">3.3592734336853</t>
   </si>
   <si>
     <t xml:space="preserve">3.34160113334656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3005998134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3048415184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27585697174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39603281021118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3493766784668</t>
+    <t xml:space="preserve">3.30059933662415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30484127998352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27585744857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3960337638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34937691688538</t>
   </si>
   <si>
     <t xml:space="preserve">3.36068773269653</t>
@@ -1349,124 +1349,124 @@
     <t xml:space="preserve">3.36704993247986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39179182052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4165346622467</t>
+    <t xml:space="preserve">3.3917920589447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41653418540955</t>
   </si>
   <si>
     <t xml:space="preserve">3.45329403877258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5232789516449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59114289283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61235022544861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073062896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61093688011169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62790274620056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60103940963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59962582588196</t>
+    <t xml:space="preserve">3.52327871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59114241600037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61235070228577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073015213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61093616485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6279022693634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60103964805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59962606430054</t>
   </si>
   <si>
     <t xml:space="preserve">3.51055407524109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53176164627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57841801643372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61941981315613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64911031723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67880082130432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62083315849304</t>
+    <t xml:space="preserve">3.53176116943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57841777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61941909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6491105556488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67880058288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62083339691162</t>
   </si>
   <si>
     <t xml:space="preserve">3.68587017059326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70849061012268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65335130691528</t>
+    <t xml:space="preserve">3.70849084854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65335178375244</t>
   </si>
   <si>
     <t xml:space="preserve">3.68304228782654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68728375434875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67738652229309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71414685249329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71131920814514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70990538597107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72545742988586</t>
+    <t xml:space="preserve">3.68728351593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67738699913025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71414732933044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71131873130798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70990514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72545695304871</t>
   </si>
   <si>
     <t xml:space="preserve">3.73252654075623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73111271858215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6717312335968</t>
+    <t xml:space="preserve">3.73111176490784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67173171043396</t>
   </si>
   <si>
     <t xml:space="preserve">3.69293904304504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71980166435242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779950141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61517786979675</t>
+    <t xml:space="preserve">3.71980214118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779902458191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61517810821533</t>
   </si>
   <si>
     <t xml:space="preserve">3.68869709968567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69576716423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69435238838196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69718050956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68162846565247</t>
+    <t xml:space="preserve">3.69576668739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69435214996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69718074798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68162870407104</t>
   </si>
   <si>
     <t xml:space="preserve">3.75232005119324</t>
@@ -1475,25 +1475,25 @@
     <t xml:space="preserve">3.7438371181488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72262907028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76504492759705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7593891620636</t>
+    <t xml:space="preserve">3.72262930870056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7650454044342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75938868522644</t>
   </si>
   <si>
     <t xml:space="preserve">3.71697402000427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78342413902283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83997774124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86542701721191</t>
+    <t xml:space="preserve">3.78342485427856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83997797966003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86542677879333</t>
   </si>
   <si>
     <t xml:space="preserve">3.83573651313782</t>
@@ -1505,55 +1505,55 @@
     <t xml:space="preserve">3.79756307601929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81735730171204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85977149009705</t>
+    <t xml:space="preserve">3.8173565864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85977125167847</t>
   </si>
   <si>
     <t xml:space="preserve">3.86966872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8838062286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87532377243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89370346069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88804841041565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85270237922668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87108206748962</t>
+    <t xml:space="preserve">3.88380670547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87532329559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89370322227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88804817199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85270214080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8710823059082</t>
   </si>
   <si>
     <t xml:space="preserve">3.89087581634521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84139227867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88239336013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92339420318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88946223258972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90360045433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92056655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9191529750824</t>
+    <t xml:space="preserve">3.84139156341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88239312171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92339491844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88946175575256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90359973907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92056679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91915249824524</t>
   </si>
   <si>
     <t xml:space="preserve">3.96439552307129</t>
@@ -1562,49 +1562,49 @@
     <t xml:space="preserve">3.95732641220093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91066956520081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93329119682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90642809867859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9050145149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92198061943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9120831489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93046283721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87956476211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89794492721558</t>
+    <t xml:space="preserve">3.91066980361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9332914352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90642833709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90501475334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92198038101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91208338737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9304633140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87956571578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89794516563416</t>
   </si>
   <si>
     <t xml:space="preserve">3.88097929954529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.947429895401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89228987693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87391018867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90925598144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95025682449341</t>
+    <t xml:space="preserve">3.94742941856384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89228940010071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87390971183777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90925621986389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95025706291199</t>
   </si>
   <si>
     <t xml:space="preserve">3.98136162757874</t>
@@ -1613,46 +1613,46 @@
     <t xml:space="preserve">4.00963830947876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08032941818237</t>
+    <t xml:space="preserve">4.08033037185669</t>
   </si>
   <si>
     <t xml:space="preserve">4.07891607284546</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13016319274902</t>
+    <t xml:space="preserve">4.13016366958618</t>
   </si>
   <si>
     <t xml:space="preserve">4.16984796524048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21100330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21394300460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24921798706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20512342453003</t>
+    <t xml:space="preserve">4.21100282669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.213942527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24921846389771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20512390136719</t>
   </si>
   <si>
     <t xml:space="preserve">4.19483518600464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12281465530396</t>
+    <t xml:space="preserve">4.1228141784668</t>
   </si>
   <si>
     <t xml:space="preserve">4.1081166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16543912887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21541213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26979541778564</t>
+    <t xml:space="preserve">4.16543865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21541166305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26979494094849</t>
   </si>
   <si>
     <t xml:space="preserve">4.30507040023804</t>
@@ -1661,40 +1661,40 @@
     <t xml:space="preserve">4.32123899459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36827278137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33152723312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32564783096313</t>
+    <t xml:space="preserve">4.36827230453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33152770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32564830780029</t>
   </si>
   <si>
     <t xml:space="preserve">4.288902759552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35651445388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34328603744507</t>
+    <t xml:space="preserve">4.35651397705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34328556060791</t>
   </si>
   <si>
     <t xml:space="preserve">4.49908590316772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44764184951782</t>
+    <t xml:space="preserve">4.44764232635498</t>
   </si>
   <si>
     <t xml:space="preserve">4.4461727142334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48291683197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48732709884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45352125167847</t>
+    <t xml:space="preserve">4.48291778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48732662200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45352077484131</t>
   </si>
   <si>
     <t xml:space="preserve">4.43735361099243</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">4.35210466384888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34181547164917</t>
+    <t xml:space="preserve">4.34181594848633</t>
   </si>
   <si>
     <t xml:space="preserve">4.33446645736694</t>
@@ -1715,34 +1715,34 @@
     <t xml:space="preserve">4.47997808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44911193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43882369995117</t>
+    <t xml:space="preserve">4.4491114616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43882322311401</t>
   </si>
   <si>
     <t xml:space="preserve">4.49467611312866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51966285705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50349521636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54317951202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5622878074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57698488235474</t>
+    <t xml:space="preserve">4.51966238021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50349426269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54317998886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56228733062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57698583602905</t>
   </si>
   <si>
     <t xml:space="preserve">4.52701187133789</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5417103767395</t>
+    <t xml:space="preserve">4.54170989990234</t>
   </si>
   <si>
     <t xml:space="preserve">4.54905939102173</t>
@@ -1751,19 +1751,19 @@
     <t xml:space="preserve">4.40207815170288</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43588352203369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42559480667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38885021209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38150119781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2448091506958</t>
+    <t xml:space="preserve">4.43588399887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4255952835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38884973526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38150072097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24480867385864</t>
   </si>
   <si>
     <t xml:space="preserve">4.20218420028687</t>
@@ -1775,13 +1775,13 @@
     <t xml:space="preserve">4.29331254959106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27420473098755</t>
+    <t xml:space="preserve">4.27420425415039</t>
   </si>
   <si>
     <t xml:space="preserve">4.26097631454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28449296951294</t>
+    <t xml:space="preserve">4.2844934463501</t>
   </si>
   <si>
     <t xml:space="preserve">4.28743314743042</t>
@@ -1790,40 +1790,40 @@
     <t xml:space="preserve">4.11399555206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16102981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24186849594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15662002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3036003112793</t>
+    <t xml:space="preserve">4.16102933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24186897277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15661954879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30360078811646</t>
   </si>
   <si>
     <t xml:space="preserve">4.2183518409729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20071363449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19777393341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34034633636475</t>
+    <t xml:space="preserve">4.20071458816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1977744102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34034585952759</t>
   </si>
   <si>
     <t xml:space="preserve">4.33593702316284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34916496276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31388998031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30213165283203</t>
+    <t xml:space="preserve">4.34916543960571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31388902664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30213117599487</t>
   </si>
   <si>
     <t xml:space="preserve">4.20806312561035</t>
@@ -1832,49 +1832,49 @@
     <t xml:space="preserve">4.14192247390747</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1037073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18307685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14045143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12575435638428</t>
+    <t xml:space="preserve">4.10370683670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18307638168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14045190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12575387954712</t>
   </si>
   <si>
     <t xml:space="preserve">4.1933650970459</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18160629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18454599380493</t>
+    <t xml:space="preserve">4.18160676956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18454647064209</t>
   </si>
   <si>
     <t xml:space="preserve">4.25215721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29919099807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39031934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32711791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30066108703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21247243881226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31241941452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36974239349365</t>
+    <t xml:space="preserve">4.29919147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39031982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32711744308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30066156387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21247291564941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31241989135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36974287033081</t>
   </si>
   <si>
     <t xml:space="preserve">4.24774837493896</t>
@@ -1883,19 +1883,19 @@
     <t xml:space="preserve">4.18895530700684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011016845703</t>
+    <t xml:space="preserve">4.23011064529419</t>
   </si>
   <si>
     <t xml:space="preserve">4.18748569488525</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17425775527954</t>
+    <t xml:space="preserve">4.17425727844238</t>
   </si>
   <si>
     <t xml:space="preserve">4.1727876663208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14486169815063</t>
+    <t xml:space="preserve">4.14486122131348</t>
   </si>
   <si>
     <t xml:space="preserve">4.1683783531189</t>
@@ -1907,28 +1907,28 @@
     <t xml:space="preserve">4.238929271698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25362777709961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29478216171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33740615844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35063505172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28302335739136</t>
+    <t xml:space="preserve">4.25362730026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29478168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33740663528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35063457489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28302383422852</t>
   </si>
   <si>
     <t xml:space="preserve">4.33299684524536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30654048919678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268161773682</t>
+    <t xml:space="preserve">4.30654096603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268209457397</t>
   </si>
   <si>
     <t xml:space="preserve">4.39178895950317</t>
@@ -1940,70 +1940,70 @@
     <t xml:space="preserve">4.22423124313354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23745965957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22570133209229</t>
+    <t xml:space="preserve">4.23745918273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22570085525513</t>
   </si>
   <si>
     <t xml:space="preserve">4.19189548492432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22129154205322</t>
+    <t xml:space="preserve">4.22129106521606</t>
   </si>
   <si>
     <t xml:space="preserve">4.23598957061768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22717046737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00963926315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07431077957153</t>
+    <t xml:space="preserve">4.22716999053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00963878631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07431030273438</t>
   </si>
   <si>
     <t xml:space="preserve">4.08900880813599</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04932355880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01992750167847</t>
+    <t xml:space="preserve">4.04932403564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01992797851562</t>
   </si>
   <si>
     <t xml:space="preserve">3.95378637313843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99494004249573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0419750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99053168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03609609603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1066460609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16396903991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12722396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13751220703125</t>
+    <t xml:space="preserve">3.99494075775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04197454452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99053120613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03609561920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10664653778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16396856307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1272234916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13751268386841</t>
   </si>
   <si>
     <t xml:space="preserve">4.00082015991211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09194803237915</t>
+    <t xml:space="preserve">4.09194850921631</t>
   </si>
   <si>
     <t xml:space="preserve">4.08459949493408</t>
@@ -2012,40 +2012,40 @@
     <t xml:space="preserve">4.02727699279785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02286767959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10076713562012</t>
+    <t xml:space="preserve">4.02286720275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10076665878296</t>
   </si>
   <si>
     <t xml:space="preserve">4.20365381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13898229598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25068807601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20659351348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26391649246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30801010131836</t>
+    <t xml:space="preserve">4.13898181915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25068759918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20659399032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.263916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30801057815552</t>
   </si>
   <si>
     <t xml:space="preserve">4.48144769668579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5152530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49761533737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40648698806763</t>
+    <t xml:space="preserve">4.51525354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49761486053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40648746490479</t>
   </si>
   <si>
     <t xml:space="preserve">4.41677618026733</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">4.46674966812134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4917368888855</t>
+    <t xml:space="preserve">4.49173641204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.46087074279785</t>
@@ -2063,79 +2063,79 @@
     <t xml:space="preserve">4.46234035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51231336593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45205116271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4858570098877</t>
+    <t xml:space="preserve">4.51231384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45205163955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48585748672485</t>
   </si>
   <si>
     <t xml:space="preserve">4.62548923492432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26538562774658</t>
+    <t xml:space="preserve">4.26538610458374</t>
   </si>
   <si>
     <t xml:space="preserve">4.26244640350342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06549167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08606863021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72890543937683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51798796653748</t>
+    <t xml:space="preserve">4.06549215316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08606910705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72890520095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51798844337463</t>
   </si>
   <si>
     <t xml:space="preserve">3.50181984901428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02192759513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24754309654236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15127086639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27032470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29531216621399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35189938545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21153283119202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.129958152771</t>
+    <t xml:space="preserve">3.02192735671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24754333496094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15127038955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27032518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29531240463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35189986228943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21153259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12995791435242</t>
   </si>
   <si>
     <t xml:space="preserve">3.35557413101196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38937950134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34381556510925</t>
+    <t xml:space="preserve">3.38937973976135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34381580352783</t>
   </si>
   <si>
     <t xml:space="preserve">3.35924887657166</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57090163230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66643881797791</t>
+    <t xml:space="preserve">3.5709011554718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66643857955933</t>
   </si>
   <si>
     <t xml:space="preserve">3.44964146614075</t>
@@ -2144,73 +2144,73 @@
     <t xml:space="preserve">3.55693817138672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58780336380005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53636026382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54958868026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46580934524536</t>
+    <t xml:space="preserve">3.58780431747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53636002540588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54958891868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4658100605011</t>
   </si>
   <si>
     <t xml:space="preserve">3.54811906814575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56428694725037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368348121643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62601900100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57163572311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57310557365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44082260131836</t>
+    <t xml:space="preserve">3.56428670883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368276596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62601923942566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57163619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57310605049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44082283973694</t>
   </si>
   <si>
     <t xml:space="preserve">3.61719989776611</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52754163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57457566261292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56722664833069</t>
+    <t xml:space="preserve">3.52754211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57457542419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56722688674927</t>
   </si>
   <si>
     <t xml:space="preserve">3.57898473739624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75168752670288</t>
+    <t xml:space="preserve">3.75168776512146</t>
   </si>
   <si>
     <t xml:space="preserve">3.68187165260315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70391845703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60691118240356</t>
+    <t xml:space="preserve">3.70391869544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60691142082214</t>
   </si>
   <si>
     <t xml:space="preserve">3.61279034614563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66423416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6318986415863</t>
+    <t xml:space="preserve">3.66423392295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63189816474915</t>
   </si>
   <si>
     <t xml:space="preserve">3.62454915046692</t>
@@ -2219,76 +2219,76 @@
     <t xml:space="preserve">3.63777732849121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62307906150818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71126818656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73626279830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60662746429443</t>
+    <t xml:space="preserve">3.6230788230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71126747131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73626255989075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60662722587585</t>
   </si>
   <si>
     <t xml:space="preserve">3.66372871398926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63440680503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68533444404602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75015187263489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73008942604065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70231056213379</t>
+    <t xml:space="preserve">3.63440656661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6853346824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75015234947205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73008966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70231032371521</t>
   </si>
   <si>
     <t xml:space="preserve">3.80725336074829</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77021431922913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81959891319275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90447974205017</t>
+    <t xml:space="preserve">3.77021455764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81959915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90447902679443</t>
   </si>
   <si>
     <t xml:space="preserve">3.99707531929016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05109024047852</t>
+    <t xml:space="preserve">4.05108976364136</t>
   </si>
   <si>
     <t xml:space="preserve">4.02408266067505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9276282787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88133025169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81651282310486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91991209983826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08581399917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05880641937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10896301269531</t>
+    <t xml:space="preserve">3.92762851715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8813304901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81651306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91991186141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08581352233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05880689620972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10896253585815</t>
   </si>
   <si>
     <t xml:space="preserve">4.14754438400269</t>
@@ -2297,10 +2297,10 @@
     <t xml:space="preserve">4.02022457122803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96620965003967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98935914039612</t>
+    <t xml:space="preserve">3.96620988845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9893593788147</t>
   </si>
   <si>
     <t xml:space="preserve">4.03565740585327</t>
@@ -2318,37 +2318,37 @@
     <t xml:space="preserve">4.11282062530518</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05494832992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95463585853577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96235251426697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93534398078918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97006869316101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97392630577087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07423877716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12439489364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10510444641113</t>
+    <t xml:space="preserve">4.0549488067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95463562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96235203742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93534445762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97006845474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97392678260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07423973083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1243953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10510540008545</t>
   </si>
   <si>
     <t xml:space="preserve">4.09352970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04723167419434</t>
+    <t xml:space="preserve">4.04723215103149</t>
   </si>
   <si>
     <t xml:space="preserve">4.12825345993042</t>
@@ -2357,22 +2357,22 @@
     <t xml:space="preserve">4.25943183898926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26714897155762</t>
+    <t xml:space="preserve">4.26714849472046</t>
   </si>
   <si>
     <t xml:space="preserve">4.21313381195068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1977014541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16297721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16683578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470855712891</t>
+    <t xml:space="preserve">4.19770097732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16297769546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16683626174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470808029175</t>
   </si>
   <si>
     <t xml:space="preserve">4.28643894195557</t>
@@ -2381,28 +2381,28 @@
     <t xml:space="preserve">4.36746072769165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42147588729858</t>
+    <t xml:space="preserve">4.42147541046143</t>
   </si>
   <si>
     <t xml:space="preserve">4.3906102180481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37517786026001</t>
+    <t xml:space="preserve">4.37517738342285</t>
   </si>
   <si>
     <t xml:space="preserve">4.36360311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30573034286499</t>
+    <t xml:space="preserve">4.30572986602783</t>
   </si>
   <si>
     <t xml:space="preserve">4.26328992843628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24399948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31344652175903</t>
+    <t xml:space="preserve">4.24399900436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31344699859619</t>
   </si>
   <si>
     <t xml:space="preserve">4.30187177658081</t>
@@ -2417,10 +2417,10 @@
     <t xml:space="preserve">4.18612670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17455196380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1899847984314</t>
+    <t xml:space="preserve">4.17455148696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18998432159424</t>
   </si>
   <si>
     <t xml:space="preserve">4.11667919158936</t>
@@ -2429,13 +2429,13 @@
     <t xml:space="preserve">4.17841005325317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15526103973389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15140247344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15911912918091</t>
+    <t xml:space="preserve">4.15526151657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15140295028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15911865234375</t>
   </si>
   <si>
     <t xml:space="preserve">4.19384288787842</t>
@@ -2444,10 +2444,10 @@
     <t xml:space="preserve">4.07809734344482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89290499687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97778534889221</t>
+    <t xml:space="preserve">3.89290475845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97778511047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.06266450881958</t>
@@ -2456,31 +2456,31 @@
     <t xml:space="preserve">3.94691920280457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98550152778625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98164296150208</t>
+    <t xml:space="preserve">3.9855010509491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9816427230835</t>
   </si>
   <si>
     <t xml:space="preserve">3.88904643058777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71157026290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72700309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82885885238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83194518089294</t>
+    <t xml:space="preserve">3.71157002449036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7270028591156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82885909080505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83194541931152</t>
   </si>
   <si>
     <t xml:space="preserve">3.86589741706848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00479173660278</t>
+    <t xml:space="preserve">4.00479221343994</t>
   </si>
   <si>
     <t xml:space="preserve">3.95077729225159</t>
@@ -2501,37 +2501,37 @@
     <t xml:space="preserve">4.14368629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13211154937744</t>
+    <t xml:space="preserve">4.1321120262146</t>
   </si>
   <si>
     <t xml:space="preserve">3.93920302391052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90062117576599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80879616737366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9932177066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01250839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95849394798279</t>
+    <t xml:space="preserve">3.90062069892883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80879640579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99321794509888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01250791549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95849370956421</t>
   </si>
   <si>
     <t xml:space="preserve">3.8774721622467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93148684501648</t>
+    <t xml:space="preserve">3.93148612976074</t>
   </si>
   <si>
     <t xml:space="preserve">3.92377066612244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86203932762146</t>
+    <t xml:space="preserve">3.86203980445862</t>
   </si>
   <si>
     <t xml:space="preserve">3.81805610656738</t>
@@ -2540,85 +2540,85 @@
     <t xml:space="preserve">3.80570983886719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85818076133728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89676308631897</t>
+    <t xml:space="preserve">3.85818147659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89676284790039</t>
   </si>
   <si>
     <t xml:space="preserve">3.85663795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82114267349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83811855316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94306111335754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90833735466003</t>
+    <t xml:space="preserve">3.82114315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83811831474304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94306135177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90833759307861</t>
   </si>
   <si>
     <t xml:space="preserve">3.88518834114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83503174781799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76712775230408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76249814033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82268619537354</t>
+    <t xml:space="preserve">3.83503198623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76712846755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76249837875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82268571853638</t>
   </si>
   <si>
     <t xml:space="preserve">3.79799342155457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87361407279968</t>
+    <t xml:space="preserve">3.87361359596252</t>
   </si>
   <si>
     <t xml:space="preserve">4.02794075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04337310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20927572250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25171566009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25557327270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31730461120605</t>
+    <t xml:space="preserve">4.04337406158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2092752456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25171613693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25557374954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31730508804321</t>
   </si>
   <si>
     <t xml:space="preserve">4.27100610733032</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26251840591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2872109413147</t>
+    <t xml:space="preserve">4.26251888275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">4.25634527206421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24554252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14985990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12979698181152</t>
+    <t xml:space="preserve">4.24554204940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14985942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12979745864868</t>
   </si>
   <si>
     <t xml:space="preserve">4.14060020446777</t>
@@ -2630,10 +2630,10 @@
     <t xml:space="preserve">4.16837882995605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1714653968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19924402236938</t>
+    <t xml:space="preserve">4.17146587371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19924354553223</t>
   </si>
   <si>
     <t xml:space="preserve">4.23628282546997</t>
@@ -2642,10 +2642,10 @@
     <t xml:space="preserve">4.18844127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17763805389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17918157577515</t>
+    <t xml:space="preserve">4.17763900756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1791820526123</t>
   </si>
   <si>
     <t xml:space="preserve">4.1838116645813</t>
@@ -2654,31 +2654,31 @@
     <t xml:space="preserve">4.20387411117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18535470962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21621990203857</t>
+    <t xml:space="preserve">4.1853551864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21622037887573</t>
   </si>
   <si>
     <t xml:space="preserve">4.29338407516479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23165273666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25017213821411</t>
+    <t xml:space="preserve">4.23165321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25017166137695</t>
   </si>
   <si>
     <t xml:space="preserve">4.23782634735107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35048484802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34122562408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39369583129883</t>
+    <t xml:space="preserve">4.35048532485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34122514724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39369678497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.47086048126221</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">4.44025039672852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3885440826416</t>
+    <t xml:space="preserve">4.38854455947876</t>
   </si>
   <si>
     <t xml:space="preserve">4.35622835159302</t>
@@ -2699,19 +2699,19 @@
     <t xml:space="preserve">4.38531255722046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37400197982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39016008377075</t>
+    <t xml:space="preserve">4.37400245666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39015960693359</t>
   </si>
   <si>
     <t xml:space="preserve">4.37723398208618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40147113800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45156097412109</t>
+    <t xml:space="preserve">4.40147066116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45156145095825</t>
   </si>
   <si>
     <t xml:space="preserve">4.47418212890625</t>
@@ -2720,19 +2720,19 @@
     <t xml:space="preserve">4.49357223510742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5016508102417</t>
+    <t xml:space="preserve">4.50165128707886</t>
   </si>
   <si>
     <t xml:space="preserve">4.52911996841431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5517406463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55012559890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62122058868408</t>
+    <t xml:space="preserve">4.55174112319946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55012512207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62122106552124</t>
   </si>
   <si>
     <t xml:space="preserve">4.58405733108521</t>
@@ -2741,19 +2741,19 @@
     <t xml:space="preserve">4.56628370285034</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54527807235718</t>
+    <t xml:space="preserve">4.54527759552002</t>
   </si>
   <si>
     <t xml:space="preserve">4.52750396728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45640802383423</t>
+    <t xml:space="preserve">4.45640850067139</t>
   </si>
   <si>
     <t xml:space="preserve">4.49680376052856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48226165771484</t>
+    <t xml:space="preserve">4.48226118087769</t>
   </si>
   <si>
     <t xml:space="preserve">4.48710870742798</t>
@@ -2768,43 +2768,43 @@
     <t xml:space="preserve">4.49841928482056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50649881362915</t>
+    <t xml:space="preserve">4.50649833679199</t>
   </si>
   <si>
     <t xml:space="preserve">4.55335760116577</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4790301322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52265644073486</t>
+    <t xml:space="preserve">4.47902965545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52265691757202</t>
   </si>
   <si>
     <t xml:space="preserve">4.54204702377319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54689359664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50811433792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37884902954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35461235046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37238597869873</t>
+    <t xml:space="preserve">4.54689407348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50811386108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37884950637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35461187362671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37238645553589</t>
   </si>
   <si>
     <t xml:space="preserve">4.53719902038574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56789922714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61152601242065</t>
+    <t xml:space="preserve">4.56789970397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61152648925781</t>
   </si>
   <si>
     <t xml:space="preserve">4.6147575378418</t>
@@ -2816,10 +2816,10 @@
     <t xml:space="preserve">4.62768459320068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59375190734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60829496383667</t>
+    <t xml:space="preserve">4.59375238418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60829448699951</t>
   </si>
   <si>
     <t xml:space="preserve">4.63091611862183</t>
@@ -2828,73 +2828,73 @@
     <t xml:space="preserve">4.65676879882812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66484880447388</t>
+    <t xml:space="preserve">4.66484832763672</t>
   </si>
   <si>
     <t xml:space="preserve">4.69070148468018</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73271179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76502847671509</t>
+    <t xml:space="preserve">4.73271226882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76502799987793</t>
   </si>
   <si>
     <t xml:space="preserve">4.80219221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79896020889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76987600326538</t>
+    <t xml:space="preserve">4.79896068572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76987552642822</t>
   </si>
   <si>
     <t xml:space="preserve">4.82804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82481384277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84420299530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80703926086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69554805755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57436323165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53558349609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5921368598938</t>
+    <t xml:space="preserve">4.82481336593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84420347213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80703973770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69554853439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57436275482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53558301925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59213638305664</t>
   </si>
   <si>
     <t xml:space="preserve">4.54366207122803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49034023284912</t>
+    <t xml:space="preserve">4.49034070968628</t>
   </si>
   <si>
     <t xml:space="preserve">4.49195623397827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48549318313599</t>
+    <t xml:space="preserve">4.48549270629883</t>
   </si>
   <si>
     <t xml:space="preserve">4.45964002609253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51134634017944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52427244186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46125555038452</t>
+    <t xml:space="preserve">4.51134586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52427196502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46125507354736</t>
   </si>
   <si>
     <t xml:space="preserve">4.58567333221436</t>
@@ -2903,22 +2903,22 @@
     <t xml:space="preserve">4.63576316833496</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5889048576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65353727340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57113122940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47579860687256</t>
+    <t xml:space="preserve">4.58890438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65353775024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57113075256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4757981300354</t>
   </si>
   <si>
     <t xml:space="preserve">4.42247629165649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46933460235596</t>
+    <t xml:space="preserve">4.46933507919312</t>
   </si>
   <si>
     <t xml:space="preserve">4.43217134475708</t>
@@ -2927,49 +2927,49 @@
     <t xml:space="preserve">4.47095060348511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48387718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39985466003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37077045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39662313461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41116523742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51457786560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46287155151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43540239334106</t>
+    <t xml:space="preserve">4.48387765884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39985513687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37076997756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39662265777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41116571426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51457738876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46287202835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43540287017822</t>
   </si>
   <si>
     <t xml:space="preserve">4.50003576278687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53881502151489</t>
+    <t xml:space="preserve">4.53881454467773</t>
   </si>
   <si>
     <t xml:space="preserve">4.61314249038696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63253164291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60021495819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55658864974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57920980453491</t>
+    <t xml:space="preserve">4.63253211975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60021591186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5565881729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57921028137207</t>
   </si>
   <si>
     <t xml:space="preserve">4.52588844299316</t>
@@ -2981,16 +2981,16 @@
     <t xml:space="preserve">4.53235149383545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44832944869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50488233566284</t>
+    <t xml:space="preserve">4.44832897186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5048828125</t>
   </si>
   <si>
     <t xml:space="preserve">4.71978569030762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72301721572876</t>
+    <t xml:space="preserve">4.72301769256592</t>
   </si>
   <si>
     <t xml:space="preserve">4.65838479995728</t>
@@ -3005,16 +3005,16 @@
     <t xml:space="preserve">4.64384269714355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7020115852356</t>
+    <t xml:space="preserve">4.70201206207275</t>
   </si>
   <si>
     <t xml:space="preserve">4.68585395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7036280632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66807985305786</t>
+    <t xml:space="preserve">4.70362758636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6680793762207</t>
   </si>
   <si>
     <t xml:space="preserve">4.64545822143555</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">4.7262487411499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76179647445679</t>
+    <t xml:space="preserve">4.76179695129395</t>
   </si>
   <si>
     <t xml:space="preserve">4.75048637390137</t>
@@ -3044,34 +3044,34 @@
     <t xml:space="preserve">4.85874557495117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83127689361572</t>
+    <t xml:space="preserve">4.83127641677856</t>
   </si>
   <si>
     <t xml:space="preserve">4.66161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64061117172241</t>
+    <t xml:space="preserve">4.6406102180481</t>
   </si>
   <si>
     <t xml:space="preserve">4.7294807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74402284622192</t>
+    <t xml:space="preserve">4.74402332305908</t>
   </si>
   <si>
     <t xml:space="preserve">4.76018095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74079084396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79734468460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71655321121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79572868347168</t>
+    <t xml:space="preserve">4.74079132080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79734516143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71655416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79572820663452</t>
   </si>
   <si>
     <t xml:space="preserve">4.83450841903687</t>
@@ -3083,13 +3083,13 @@
     <t xml:space="preserve">4.50972986221313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46448802947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57759428024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62930059432983</t>
+    <t xml:space="preserve">4.46448755264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57759380340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62930011749268</t>
   </si>
   <si>
     <t xml:space="preserve">4.55982065200806</t>
@@ -3098,49 +3098,49 @@
     <t xml:space="preserve">4.54851007461548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50326728820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41278171539307</t>
+    <t xml:space="preserve">4.50326681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41278123855591</t>
   </si>
   <si>
     <t xml:space="preserve">4.35299634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32068061828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55820465087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51780939102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49518775939941</t>
+    <t xml:space="preserve">4.32068014144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55820512771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51780891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49518823623657</t>
   </si>
   <si>
     <t xml:space="preserve">4.4176287651062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48872423171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43378686904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70524311065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73028802871704</t>
+    <t xml:space="preserve">4.48872518539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43378734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70524263381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7302885055542</t>
   </si>
   <si>
     <t xml:space="preserve">4.68181419372559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77472352981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89590930938721</t>
+    <t xml:space="preserve">4.77472305297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89590883255005</t>
   </si>
   <si>
     <t xml:space="preserve">4.94034385681152</t>
@@ -3149,10 +3149,10 @@
     <t xml:space="preserve">4.91610670089722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91206741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00497674942017</t>
+    <t xml:space="preserve">4.91206693649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00497627258301</t>
   </si>
   <si>
     <t xml:space="preserve">5.04537153244019</t>
@@ -3161,19 +3161,19 @@
     <t xml:space="preserve">5.15039920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08980655670166</t>
+    <t xml:space="preserve">5.08980703353882</t>
   </si>
   <si>
     <t xml:space="preserve">5.0655689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98073959350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96054124832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99285745620728</t>
+    <t xml:space="preserve">4.9807391166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96054172515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99285793304443</t>
   </si>
   <si>
     <t xml:space="preserve">5.01709508895874</t>
@@ -3182,7 +3182,7 @@
     <t xml:space="preserve">5.00093698501587</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01305532455444</t>
+    <t xml:space="preserve">5.01305484771729</t>
   </si>
   <si>
     <t xml:space="preserve">4.97266054153442</t>
@@ -3194,31 +3194,31 @@
     <t xml:space="preserve">4.94842290878296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92014598846436</t>
+    <t xml:space="preserve">4.92014646530151</t>
   </si>
   <si>
     <t xml:space="preserve">5.10596466064453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05345058441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16251850128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20222234725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11777019500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15577363967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18533134460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10088014602661</t>
+    <t xml:space="preserve">5.05345106124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16251802444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20222187042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11777067184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15577411651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18533182144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10087966918945</t>
   </si>
   <si>
     <t xml:space="preserve">5.06287670135498</t>
@@ -3227,13 +3227,13 @@
     <t xml:space="preserve">5.07554483413696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02909660339355</t>
+    <t xml:space="preserve">5.0290961265564</t>
   </si>
   <si>
     <t xml:space="preserve">5.04598665237427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02487325668335</t>
+    <t xml:space="preserve">5.02487373352051</t>
   </si>
   <si>
     <t xml:space="preserve">4.87286043167114</t>
@@ -3248,19 +3248,19 @@
     <t xml:space="preserve">4.54772186279297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60261487960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53505420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71662521362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64906406402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50971841812134</t>
+    <t xml:space="preserve">4.60261535644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53505373001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71662473678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64906358718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5097188949585</t>
   </si>
   <si>
     <t xml:space="preserve">4.34081506729126</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">4.69551229476929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63217353820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74196004867554</t>
+    <t xml:space="preserve">4.63217401504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7419605255127</t>
   </si>
   <si>
     <t xml:space="preserve">4.73773813247681</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">4.69128942489624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72929286956787</t>
+    <t xml:space="preserve">4.72929239273071</t>
   </si>
   <si>
     <t xml:space="preserve">4.64061880111694</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">4.6068377494812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64484119415283</t>
+    <t xml:space="preserve">4.64484071731567</t>
   </si>
   <si>
     <t xml:space="preserve">4.45060253143311</t>
@@ -3311,10 +3311,10 @@
     <t xml:space="preserve">4.45482492446899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38726377487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46327018737793</t>
+    <t xml:space="preserve">4.38726329803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46326971054077</t>
   </si>
   <si>
     <t xml:space="preserve">4.59417009353638</t>
@@ -3326,13 +3326,13 @@
     <t xml:space="preserve">4.71240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61528348922729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62795066833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6575083732605</t>
+    <t xml:space="preserve">4.61528301239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62795114517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65750885009766</t>
   </si>
   <si>
     <t xml:space="preserve">4.65328645706177</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">4.72506999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77151870727539</t>
+    <t xml:space="preserve">4.77151918411255</t>
   </si>
   <si>
     <t xml:space="preserve">4.70817995071411</t>
@@ -3362,19 +3362,19 @@
     <t xml:space="preserve">4.66173124313354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53927612304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47593832015991</t>
+    <t xml:space="preserve">4.53927659988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47593784332275</t>
   </si>
   <si>
     <t xml:space="preserve">4.33659267425537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31125688552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42104482650757</t>
+    <t xml:space="preserve">4.31125736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42104434967041</t>
   </si>
   <si>
     <t xml:space="preserve">4.29436683654785</t>
@@ -3386,13 +3386,13 @@
     <t xml:space="preserve">4.25636339187622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39148616790771</t>
+    <t xml:space="preserve">4.39148569107056</t>
   </si>
   <si>
     <t xml:space="preserve">4.41259908676147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40415382385254</t>
+    <t xml:space="preserve">4.4041543006897</t>
   </si>
   <si>
     <t xml:space="preserve">4.32392454147339</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">4.3197021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36192846298218</t>
+    <t xml:space="preserve">4.36192798614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.27747631072998</t>
@@ -3416,34 +3416,34 @@
     <t xml:space="preserve">4.34503793716431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27325439453125</t>
+    <t xml:space="preserve">4.27325344085693</t>
   </si>
   <si>
     <t xml:space="preserve">4.14319849014282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07225894927979</t>
+    <t xml:space="preserve">4.07225847244263</t>
   </si>
   <si>
     <t xml:space="preserve">4.02665519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03341150283813</t>
+    <t xml:space="preserve">4.03341102600098</t>
   </si>
   <si>
     <t xml:space="preserve">4.12630796432495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22680521011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1009726524353</t>
+    <t xml:space="preserve">4.22680568695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10097217559814</t>
   </si>
   <si>
     <t xml:space="preserve">4.03678941726685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02834367752075</t>
+    <t xml:space="preserve">4.02834415435791</t>
   </si>
   <si>
     <t xml:space="preserve">4.01314258575439</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">3.84761762619019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97091698646545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06719207763672</t>
+    <t xml:space="preserve">3.97091722488403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06719160079956</t>
   </si>
   <si>
     <t xml:space="preserve">4.04016733169556</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">4.09421634674072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01483249664307</t>
+    <t xml:space="preserve">4.01483201980591</t>
   </si>
   <si>
     <t xml:space="preserve">4.15333271026611</t>
@@ -3479,28 +3479,28 @@
     <t xml:space="preserve">4.49282836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38304138183594</t>
+    <t xml:space="preserve">4.38304090499878</t>
   </si>
   <si>
     <t xml:space="preserve">4.43371200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56461238861084</t>
+    <t xml:space="preserve">4.564612865448</t>
   </si>
   <si>
     <t xml:space="preserve">4.68706703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80952167510986</t>
+    <t xml:space="preserve">4.80952215194702</t>
   </si>
   <si>
     <t xml:space="preserve">4.75462818145752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73351573944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75040578842163</t>
+    <t xml:space="preserve">4.73351526260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75040626525879</t>
   </si>
   <si>
     <t xml:space="preserve">4.76307344436646</t>
@@ -3509,10 +3509,10 @@
     <t xml:space="preserve">4.7672963142395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75885152816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74618291854858</t>
+    <t xml:space="preserve">4.75885105133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74618339538574</t>
   </si>
   <si>
     <t xml:space="preserve">4.55194425582886</t>
@@ -3530,19 +3530,19 @@
     <t xml:space="preserve">4.52660894393921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44637966156006</t>
+    <t xml:space="preserve">4.44638013839722</t>
   </si>
   <si>
     <t xml:space="preserve">4.5561671257019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51394081115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56883478164673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78418684005737</t>
+    <t xml:space="preserve">4.51394128799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56883430480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78418636322021</t>
   </si>
   <si>
     <t xml:space="preserve">4.58994770050049</t>
@@ -3551,13 +3551,13 @@
     <t xml:space="preserve">4.52238607406616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62372875213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48438262939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44215726852417</t>
+    <t xml:space="preserve">4.62372827529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48438310623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44215774536133</t>
   </si>
   <si>
     <t xml:space="preserve">4.35348320007324</t>
@@ -3587,34 +3587,34 @@
     <t xml:space="preserve">5.05020904541016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99109315872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09243488311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01220607757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98687076568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91930913925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95731210708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00798273086548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86019277572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94042205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93619918823242</t>
+    <t xml:space="preserve">4.99109268188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09243535995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01220560073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98687028884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91930866241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95731258392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00798320770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86019325256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94042158126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93619966506958</t>
   </si>
   <si>
     <t xml:space="preserve">4.96575784683228</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">4.96153497695923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00376081466675</t>
+    <t xml:space="preserve">5.00376129150391</t>
   </si>
   <si>
     <t xml:space="preserve">4.96998023986816</t>
@@ -3632,19 +3632,19 @@
     <t xml:space="preserve">4.83908033370972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88975048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82535886764526</t>
+    <t xml:space="preserve">4.88975143432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82535934448242</t>
   </si>
   <si>
     <t xml:space="preserve">4.82981061935425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66955852508545</t>
+    <t xml:space="preserve">4.75858783721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66955900192261</t>
   </si>
   <si>
     <t xml:space="preserve">4.71852493286133</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">4.78529596328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90993595123291</t>
+    <t xml:space="preserve">4.90993642807007</t>
   </si>
   <si>
     <t xml:space="preserve">4.95890283584595</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">4.93219375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9678053855896</t>
+    <t xml:space="preserve">4.96780490875244</t>
   </si>
   <si>
     <t xml:space="preserve">4.9989652633667</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">4.99006223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.869873046875</t>
+    <t xml:space="preserve">4.86987352371216</t>
   </si>
   <si>
     <t xml:space="preserve">4.95445108413696</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">4.88322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87432527542114</t>
+    <t xml:space="preserve">4.87432479858398</t>
   </si>
   <si>
     <t xml:space="preserve">4.80755376815796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75413608551025</t>
+    <t xml:space="preserve">4.75413656234741</t>
   </si>
   <si>
     <t xml:space="preserve">4.85206747055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63839912414551</t>
+    <t xml:space="preserve">4.63839864730835</t>
   </si>
   <si>
     <t xml:space="preserve">4.60278749465942</t>
@@ -3716,19 +3716,19 @@
     <t xml:space="preserve">4.70517015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69626760482788</t>
+    <t xml:space="preserve">4.69626712799072</t>
   </si>
   <si>
     <t xml:space="preserve">4.68291330337524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74523305892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76303911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77194213867188</t>
+    <t xml:space="preserve">4.7452335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76303863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77194166183472</t>
   </si>
   <si>
     <t xml:space="preserve">4.71407318115234</t>
@@ -3746,25 +3746,25 @@
     <t xml:space="preserve">4.57607841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55382108688354</t>
+    <t xml:space="preserve">4.5538215637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.53156423568726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59388399124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64730167388916</t>
+    <t xml:space="preserve">4.59388446807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.647301197052</t>
   </si>
   <si>
     <t xml:space="preserve">4.66510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6161413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54936981201172</t>
+    <t xml:space="preserve">4.61614179611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54937028884888</t>
   </si>
   <si>
     <t xml:space="preserve">4.50485563278198</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">4.500403881073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49595308303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48705005645752</t>
+    <t xml:space="preserve">4.49595260620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48704957962036</t>
   </si>
   <si>
     <t xml:space="preserve">4.70071887969971</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">4.73187923431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72297620773315</t>
+    <t xml:space="preserve">4.722975730896</t>
   </si>
   <si>
     <t xml:space="preserve">4.44609642028809</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">4.24489164352417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28228378295898</t>
+    <t xml:space="preserve">4.28228330612183</t>
   </si>
   <si>
     <t xml:space="preserve">4.31789493560791</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">4.34282302856445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41226530075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4354133605957</t>
+    <t xml:space="preserve">4.41226577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43541288375854</t>
   </si>
   <si>
     <t xml:space="preserve">4.42829084396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3926796913147</t>
+    <t xml:space="preserve">4.39267921447754</t>
   </si>
   <si>
     <t xml:space="preserve">4.45588970184326</t>
@@ -3857,22 +3857,22 @@
     <t xml:space="preserve">4.30186986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25201368331909</t>
+    <t xml:space="preserve">4.25201416015625</t>
   </si>
   <si>
     <t xml:space="preserve">4.26625823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27694177627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20928001403809</t>
+    <t xml:space="preserve">4.27694225311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20928049087524</t>
   </si>
   <si>
     <t xml:space="preserve">4.19147443771362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21996355056763</t>
+    <t xml:space="preserve">4.21996307373047</t>
   </si>
   <si>
     <t xml:space="preserve">4.27160024642944</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">4.30899238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3054313659668</t>
+    <t xml:space="preserve">4.30543088912964</t>
   </si>
   <si>
     <t xml:space="preserve">4.39445972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40336275100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47369527816772</t>
+    <t xml:space="preserve">4.40336322784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47369575500488</t>
   </si>
   <si>
     <t xml:space="preserve">4.49150133132935</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">4.46034145355225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43185234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5226616859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47814702987671</t>
+    <t xml:space="preserve">4.43185186386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52266120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47814750671387</t>
   </si>
   <si>
     <t xml:space="preserve">4.56717586517334</t>
@@ -3944,22 +3944,22 @@
     <t xml:space="preserve">4.61169004440308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5983362197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55827283859253</t>
+    <t xml:space="preserve">4.59833574295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55827236175537</t>
   </si>
   <si>
     <t xml:space="preserve">4.58053016662598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56272459030151</t>
+    <t xml:space="preserve">4.56272411346436</t>
   </si>
   <si>
     <t xml:space="preserve">4.5849814414978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54046678543091</t>
+    <t xml:space="preserve">4.54046726226807</t>
   </si>
   <si>
     <t xml:space="preserve">4.51375865936279</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">4.6918158531189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74968433380127</t>
+    <t xml:space="preserve">4.74968481063843</t>
   </si>
   <si>
     <t xml:space="preserve">4.4692440032959</t>
@@ -3998,16 +3998,16 @@
     <t xml:space="preserve">4.44787693023682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57162761688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79419898986816</t>
+    <t xml:space="preserve">4.57162714004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79419946670532</t>
   </si>
   <si>
     <t xml:space="preserve">4.80310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82090759277344</t>
+    <t xml:space="preserve">4.8209080696106</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
@@ -4130,9 +4130,6 @@
     <t xml:space="preserve">4.52464294433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54170989990234</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.53602123260498</t>
   </si>
   <si>
@@ -4905,6 +4902,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.72500038146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76000022888184</t>
   </si>
 </sst>
 </file>
@@ -56117,7 +56117,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>1372</v>
+        <v>576</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -56143,7 +56143,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1958" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -56195,7 +56195,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G1960" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -56247,7 +56247,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G1962" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -56273,7 +56273,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1963" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -56299,7 +56299,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G1964" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -56325,7 +56325,7 @@
         <v>4.92799997329712</v>
       </c>
       <c r="G1965" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -56351,7 +56351,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1966" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -56377,7 +56377,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1967" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -56403,7 +56403,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G1968" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -56429,7 +56429,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1969" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -56455,7 +56455,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G1970" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -56481,7 +56481,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G1971" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56507,7 +56507,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G1972" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -56533,7 +56533,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G1973" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -56559,7 +56559,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G1974" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -56585,7 +56585,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1975" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -56611,7 +56611,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G1976" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -56637,7 +56637,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1977" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -56663,7 +56663,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1978" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -56741,7 +56741,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G1981" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -56767,7 +56767,7 @@
         <v>4.98199987411499</v>
       </c>
       <c r="G1982" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -56793,7 +56793,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1983" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -56819,7 +56819,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1984" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56845,7 +56845,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G1985" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56871,7 +56871,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1986" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56897,7 +56897,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1987" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56949,7 +56949,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1989" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56975,7 +56975,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G1990" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -57001,7 +57001,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1991" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -57027,7 +57027,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -57053,7 +57053,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1993" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -57079,7 +57079,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1994" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -57105,7 +57105,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1995" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -57131,7 +57131,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1996" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -57157,7 +57157,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G1997" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -57183,7 +57183,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G1998" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -57209,7 +57209,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G1999" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57235,7 +57235,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G2000" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57261,7 +57261,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -57287,7 +57287,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G2002" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -57313,7 +57313,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -57339,7 +57339,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2004" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -57365,7 +57365,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G2005" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -57391,7 +57391,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G2006" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -57417,7 +57417,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G2007" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -57443,7 +57443,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2008" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -57469,7 +57469,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G2009" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -57495,7 +57495,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2010" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -57521,7 +57521,7 @@
         <v>5.5</v>
       </c>
       <c r="G2011" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -57547,7 +57547,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2012" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -57573,7 +57573,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G2013" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -57599,7 +57599,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2014" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -57625,7 +57625,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2015" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -57651,7 +57651,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2016" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -57677,7 +57677,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G2017" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -57703,7 +57703,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G2018" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -57729,7 +57729,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2019" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57755,7 +57755,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G2020" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -57781,7 +57781,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2021" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -57807,7 +57807,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G2022" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -57833,7 +57833,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2023" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57859,7 +57859,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G2024" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57885,7 +57885,7 @@
         <v>5.875</v>
       </c>
       <c r="G2025" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57911,7 +57911,7 @@
         <v>5.79500007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57937,7 +57937,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G2027" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57963,7 +57963,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2028" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -57989,7 +57989,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G2029" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -58015,7 +58015,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G2030" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -58041,7 +58041,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2031" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -58067,7 +58067,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2032" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -58093,7 +58093,7 @@
         <v>5.625</v>
       </c>
       <c r="G2033" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -58119,7 +58119,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G2034" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -58145,7 +58145,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2035" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58171,7 +58171,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2036" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58197,7 +58197,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2037" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58223,7 +58223,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G2038" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58249,7 +58249,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G2039" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58275,7 +58275,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G2040" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -58301,7 +58301,7 @@
         <v>5.5</v>
       </c>
       <c r="G2041" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -58327,7 +58327,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G2042" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -58353,7 +58353,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2043" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -58379,7 +58379,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G2044" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58405,7 +58405,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G2045" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -58431,7 +58431,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G2046" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -58457,7 +58457,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G2047" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58483,7 +58483,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2048" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -58509,7 +58509,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G2049" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -58535,7 +58535,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G2050" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -58561,7 +58561,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2051" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -58587,7 +58587,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -58613,7 +58613,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2053" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -58639,7 +58639,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2054" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -58665,7 +58665,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G2055" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -58691,7 +58691,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G2056" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -58717,7 +58717,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G2057" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -58743,7 +58743,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G2058" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -58769,7 +58769,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G2059" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -58795,7 +58795,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G2060" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -58821,7 +58821,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G2061" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58847,7 +58847,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G2062" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58873,7 +58873,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G2063" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58899,7 +58899,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2064" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58925,7 +58925,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2065" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58951,7 +58951,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2066" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58977,7 +58977,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2067" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -59003,7 +59003,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G2068" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -59029,7 +59029,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2069" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -59055,7 +59055,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2070" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -59081,7 +59081,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2071" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -59107,7 +59107,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2072" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -59133,7 +59133,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G2073" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -59159,7 +59159,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2074" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -59185,7 +59185,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G2075" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -59211,7 +59211,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2076" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59237,7 +59237,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2077" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59263,7 +59263,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G2078" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -59289,7 +59289,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G2079" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -59315,7 +59315,7 @@
         <v>5.375</v>
       </c>
       <c r="G2080" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -59341,7 +59341,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2081" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -59367,7 +59367,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G2082" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59393,7 +59393,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G2083" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -59419,7 +59419,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2084" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -59445,7 +59445,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G2085" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59471,7 +59471,7 @@
         <v>5.625</v>
       </c>
       <c r="G2086" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -59497,7 +59497,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G2087" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -59523,7 +59523,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2088" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -59549,7 +59549,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G2089" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -59575,7 +59575,7 @@
         <v>5.63500022888184</v>
       </c>
       <c r="G2090" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -59601,7 +59601,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G2091" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -59627,7 +59627,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G2092" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -59653,7 +59653,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G2093" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -59679,7 +59679,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2094" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -59705,7 +59705,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G2095" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -59731,7 +59731,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G2096" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -59757,7 +59757,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G2097" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -59783,7 +59783,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2098" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -59809,7 +59809,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2099" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59835,7 +59835,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G2100" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59861,7 +59861,7 @@
         <v>5.875</v>
       </c>
       <c r="G2101" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59887,7 +59887,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G2102" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59913,7 +59913,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G2103" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59939,7 +59939,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G2104" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59965,7 +59965,7 @@
         <v>5.90500020980835</v>
       </c>
       <c r="G2105" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59991,7 +59991,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G2106" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -60017,7 +60017,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G2107" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -60043,7 +60043,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2108" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -60069,7 +60069,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G2109" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -60095,7 +60095,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G2110" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60121,7 +60121,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G2111" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -60147,7 +60147,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G2112" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -60173,7 +60173,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G2113" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -60199,7 +60199,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G2114" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60225,7 +60225,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G2115" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60251,7 +60251,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G2116" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -60277,7 +60277,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G2117" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -60303,7 +60303,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G2118" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -60329,7 +60329,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -60355,7 +60355,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G2120" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -60381,7 +60381,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G2121" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60407,7 +60407,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G2122" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60433,7 +60433,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G2123" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60459,7 +60459,7 @@
         <v>6.125</v>
       </c>
       <c r="G2124" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -60485,7 +60485,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G2125" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -60511,7 +60511,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G2126" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -60537,7 +60537,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G2127" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -60563,7 +60563,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G2128" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -60589,7 +60589,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G2129" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -60615,7 +60615,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G2130" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -60641,7 +60641,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G2131" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -60667,7 +60667,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G2132" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -60693,7 +60693,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G2133" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -60719,7 +60719,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G2134" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -60745,7 +60745,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G2135" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -60771,7 +60771,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G2136" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -60797,7 +60797,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G2137" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -60823,7 +60823,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G2138" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60849,7 +60849,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G2139" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60875,7 +60875,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2140" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60901,7 +60901,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G2141" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60927,7 +60927,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G2142" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60953,7 +60953,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2143" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60979,7 +60979,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G2144" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -61005,7 +61005,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G2145" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -61031,7 +61031,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G2146" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -61057,7 +61057,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G2147" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -61083,7 +61083,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2148" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61109,7 +61109,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G2149" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -61135,7 +61135,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G2150" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -61161,7 +61161,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G2151" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -61187,7 +61187,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G2152" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -61213,7 +61213,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G2153" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61239,7 +61239,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G2154" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61265,7 +61265,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2155" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -61291,7 +61291,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2156" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -61317,7 +61317,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -61343,7 +61343,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G2158" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -61369,7 +61369,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G2159" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61395,7 +61395,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G2160" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61421,7 +61421,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2161" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61447,7 +61447,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G2162" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61473,7 +61473,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2163" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -61499,7 +61499,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2164" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -61525,7 +61525,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G2165" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -61551,7 +61551,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G2166" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -61577,7 +61577,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2167" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -61603,7 +61603,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G2168" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -61629,7 +61629,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G2169" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -61655,7 +61655,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G2170" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -61681,7 +61681,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G2171" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -61707,7 +61707,7 @@
         <v>6.72816181182861</v>
       </c>
       <c r="G2172" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -61733,7 +61733,7 @@
         <v>6.69060087203979</v>
       </c>
       <c r="G2173" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -61759,7 +61759,7 @@
         <v>6.66712522506714</v>
       </c>
       <c r="G2174" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61785,7 +61785,7 @@
         <v>6.61547899246216</v>
       </c>
       <c r="G2175" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -61811,7 +61811,7 @@
         <v>6.78919982910156</v>
       </c>
       <c r="G2176" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61837,7 +61837,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G2177" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61863,7 +61863,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G2178" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61889,7 +61889,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2179" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61915,7 +61915,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61941,7 +61941,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G2181" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61967,7 +61967,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G2182" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61993,7 +61993,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2183" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62019,7 +62019,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G2184" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62045,7 +62045,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2185" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62071,7 +62071,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G2186" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62097,7 +62097,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2187" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62123,7 +62123,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G2188" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62149,7 +62149,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2189" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62175,7 +62175,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G2190" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62201,7 +62201,7 @@
         <v>7</v>
       </c>
       <c r="G2191" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62227,7 +62227,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2192" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62253,7 +62253,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2193" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62279,7 +62279,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G2194" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62305,7 +62305,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G2195" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62331,7 +62331,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2196" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62357,7 +62357,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2197" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62383,7 +62383,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2198" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62409,7 +62409,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G2199" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62435,7 +62435,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2200" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62461,7 +62461,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2201" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62487,7 +62487,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G2202" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62513,7 +62513,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G2203" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -62539,7 +62539,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -62565,7 +62565,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2205" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -62591,7 +62591,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2206" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -62617,7 +62617,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2207" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -62643,7 +62643,7 @@
         <v>6.88500022888184</v>
       </c>
       <c r="G2208" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -62669,7 +62669,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G2209" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62695,7 +62695,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G2210" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62721,7 +62721,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2211" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -62747,7 +62747,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G2212" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62773,7 +62773,7 @@
         <v>7.25</v>
       </c>
       <c r="G2213" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -62799,7 +62799,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2214" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -62825,7 +62825,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G2215" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62851,7 +62851,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G2216" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62877,7 +62877,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2217" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62903,7 +62903,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G2218" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62929,7 +62929,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G2219" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62955,7 +62955,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G2220" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62981,7 +62981,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2221" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63007,7 +63007,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2222" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63033,7 +63033,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2223" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63059,7 +63059,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2224" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63085,7 +63085,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2225" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63111,7 +63111,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G2226" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63137,7 +63137,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G2227" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63163,7 +63163,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G2228" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63189,7 +63189,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G2229" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63215,7 +63215,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2230" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63241,7 +63241,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G2231" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63267,7 +63267,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2232" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63293,7 +63293,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2233" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63319,7 +63319,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G2234" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63345,7 +63345,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2235" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63371,7 +63371,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G2236" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63397,7 +63397,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2237" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63423,7 +63423,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63449,7 +63449,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G2239" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63475,7 +63475,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G2240" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63501,7 +63501,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G2241" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63527,7 +63527,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G2242" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -63553,7 +63553,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2243" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -63579,7 +63579,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G2244" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -63605,7 +63605,7 @@
         <v>7.625</v>
       </c>
       <c r="G2245" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -63631,7 +63631,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G2246" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -63657,7 +63657,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G2247" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -63683,7 +63683,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2248" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63709,7 +63709,7 @@
         <v>7.625</v>
       </c>
       <c r="G2249" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63735,7 +63735,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G2250" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63761,7 +63761,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2251" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63787,7 +63787,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2252" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63813,7 +63813,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2253" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63839,7 +63839,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G2254" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63865,7 +63865,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2255" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63891,7 +63891,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63917,7 +63917,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G2257" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63943,7 +63943,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G2258" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63969,7 +63969,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G2259" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63995,7 +63995,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G2260" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64021,7 +64021,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G2261" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64047,7 +64047,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G2262" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64073,7 +64073,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G2263" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64099,7 +64099,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G2264" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64125,7 +64125,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G2265" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64151,7 +64151,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2266" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64177,7 +64177,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2267" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64203,7 +64203,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G2268" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64229,7 +64229,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G2269" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64255,7 +64255,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G2270" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64281,7 +64281,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2271" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64307,7 +64307,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G2272" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64333,7 +64333,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2273" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64359,7 +64359,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G2274" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64385,7 +64385,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G2275" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64411,7 +64411,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G2276" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64437,7 +64437,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2277" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64463,7 +64463,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2278" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64471,7 +64471,7 @@
     </row>
     <row r="2279">
       <c r="A2279" s="1" t="n">
-        <v>45953.649375</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2279" t="n">
         <v>2299421</v>
@@ -64489,9 +64489,35 @@
         <v>8.72500038146973</v>
       </c>
       <c r="G2279" t="s">
+        <v>1629</v>
+      </c>
+      <c r="H2279" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="1" t="n">
+        <v>45954.6494212963</v>
+      </c>
+      <c r="B2280" t="n">
+        <v>2381116</v>
+      </c>
+      <c r="C2280" t="n">
+        <v>8.78999996185303</v>
+      </c>
+      <c r="D2280" t="n">
+        <v>8.66499996185303</v>
+      </c>
+      <c r="E2280" t="n">
+        <v>8.76000022888184</v>
+      </c>
+      <c r="F2280" t="n">
+        <v>8.76000022888184</v>
+      </c>
+      <c r="G2280" t="s">
         <v>1630</v>
       </c>
-      <c r="H2279" t="s">
+      <c r="H2280" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="1631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="1632">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58873558044434</t>
+    <t xml:space="preserve">2.58873581886292</t>
   </si>
   <si>
     <t xml:space="preserve">IG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5013575553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32790613174438</t>
+    <t xml:space="preserve">2.50135779380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32790589332581</t>
   </si>
   <si>
     <t xml:space="preserve">2.16488718986511</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">2.06185936927795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08663821220398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04490518569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06055521965027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04360127449036</t>
+    <t xml:space="preserve">2.0866379737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04490542411804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06055545806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04360151290894</t>
   </si>
   <si>
     <t xml:space="preserve">2.10489630699158</t>
@@ -80,46 +80,46 @@
     <t xml:space="preserve">2.12967538833618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14532518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17923283576965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20009875297546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20140314102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17792868614197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13228344917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09837532043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22357392311096</t>
+    <t xml:space="preserve">2.14532494544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17923259735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2000994682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20140337944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17792844772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13228321075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09837555885315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22357416152954</t>
   </si>
   <si>
     <t xml:space="preserve">2.29138946533203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3318178653717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29791045188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2379195690155</t>
+    <t xml:space="preserve">2.33181810379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29790997505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23791980743408</t>
   </si>
   <si>
     <t xml:space="preserve">2.30051851272583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30443120002747</t>
+    <t xml:space="preserve">2.30443072319031</t>
   </si>
   <si>
     <t xml:space="preserve">2.37094259262085</t>
@@ -134,25 +134,25 @@
     <t xml:space="preserve">2.45571255683899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39702558517456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38007164001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39441728591919</t>
+    <t xml:space="preserve">2.39702606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38007187843323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39441776275635</t>
   </si>
   <si>
     <t xml:space="preserve">2.42180466651917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41006731987</t>
+    <t xml:space="preserve">2.41006755828857</t>
   </si>
   <si>
     <t xml:space="preserve">2.43093347549438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43745422363281</t>
+    <t xml:space="preserve">2.43745446205139</t>
   </si>
   <si>
     <t xml:space="preserve">2.48701190948486</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">2.45049595832825</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4909245967865</t>
+    <t xml:space="preserve">2.49092435836792</t>
   </si>
   <si>
     <t xml:space="preserve">2.44527912139893</t>
@@ -173,10 +173,10 @@
     <t xml:space="preserve">2.43223786354065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44006252288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47788286209106</t>
+    <t xml:space="preserve">2.44006299972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47788310050964</t>
   </si>
   <si>
     <t xml:space="preserve">2.43615031242371</t>
@@ -188,25 +188,25 @@
     <t xml:space="preserve">2.4570164680481</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48831582069397</t>
+    <t xml:space="preserve">2.48831605911255</t>
   </si>
   <si>
     <t xml:space="preserve">2.41789221763611</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4348464012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41267585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35659694671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2757396697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29530191421509</t>
+    <t xml:space="preserve">2.43484592437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41267538070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35659742355347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27573990821838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29530215263367</t>
   </si>
   <si>
     <t xml:space="preserve">2.31225609779358</t>
@@ -215,10 +215,10 @@
     <t xml:space="preserve">2.38137602806091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40876293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3931131362915</t>
+    <t xml:space="preserve">2.40876269340515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39311337471008</t>
   </si>
   <si>
     <t xml:space="preserve">2.44919180870056</t>
@@ -227,28 +227,28 @@
     <t xml:space="preserve">2.46744966506958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47397041320801</t>
+    <t xml:space="preserve">2.47397065162659</t>
   </si>
   <si>
     <t xml:space="preserve">2.48440361022949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46353721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47266626358032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47136187553406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4478874206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49614119529724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49744510650635</t>
+    <t xml:space="preserve">2.46353769302368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4726665019989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47136211395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44788789749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49614095687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49744534492493</t>
   </si>
   <si>
     <t xml:space="preserve">2.51570343971252</t>
@@ -257,10 +257,10 @@
     <t xml:space="preserve">2.53135323524475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51439881324768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53656959533691</t>
+    <t xml:space="preserve">2.51439905166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53656935691833</t>
   </si>
   <si>
     <t xml:space="preserve">2.52744030952454</t>
@@ -269,25 +269,25 @@
     <t xml:space="preserve">2.54830694198608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55091524124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53787398338318</t>
+    <t xml:space="preserve">2.55091547966003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5378737449646</t>
   </si>
   <si>
     <t xml:space="preserve">2.58612728118896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57699799537659</t>
+    <t xml:space="preserve">2.57699823379517</t>
   </si>
   <si>
     <t xml:space="preserve">2.59786462783813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57308578491211</t>
+    <t xml:space="preserve">2.60438561439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57308602333069</t>
   </si>
   <si>
     <t xml:space="preserve">2.66959285736084</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">2.68393874168396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69828414916992</t>
+    <t xml:space="preserve">2.69828391075134</t>
   </si>
   <si>
     <t xml:space="preserve">2.64872622489929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64742231369019</t>
+    <t xml:space="preserve">2.64742207527161</t>
   </si>
   <si>
     <t xml:space="preserve">2.68132996559143</t>
@@ -311,184 +311,184 @@
     <t xml:space="preserve">2.67480969429016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63438057899475</t>
+    <t xml:space="preserve">2.63438081741333</t>
   </si>
   <si>
     <t xml:space="preserve">2.64350986480713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69567561149597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69958806037903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67872190475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7348005771637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77262020111084</t>
+    <t xml:space="preserve">2.69567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69958829879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67872166633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73480033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.772620677948</t>
   </si>
   <si>
     <t xml:space="preserve">2.75436234474182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71262955665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70089268684387</t>
+    <t xml:space="preserve">2.71262979507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70089221000671</t>
   </si>
   <si>
     <t xml:space="preserve">2.70219659805298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66176795959473</t>
+    <t xml:space="preserve">2.66176772117615</t>
   </si>
   <si>
     <t xml:space="preserve">2.78305387496948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74523377418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69306755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71915054321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70610904693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74914622306824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77783751487732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83521962165833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84043669700623</t>
+    <t xml:space="preserve">2.7452335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6930673122406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71915078163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70610928535461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74914598464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77783727645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8352198600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8404369354248</t>
   </si>
   <si>
     <t xml:space="preserve">2.88738584518433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89651465415955</t>
+    <t xml:space="preserve">2.89651489257812</t>
   </si>
   <si>
     <t xml:space="preserve">2.8534779548645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91477274894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0086715221405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02040886878967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96824288368225</t>
+    <t xml:space="preserve">2.91477251052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00867128372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02040863037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96824264526367</t>
   </si>
   <si>
     <t xml:space="preserve">3.00736737251282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05822968482971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09885406494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15591359138489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09613704681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1382520198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09070324897766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97658443450928</t>
+    <t xml:space="preserve">3.05822896957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09885382652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15591311454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09613680839539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13825178146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0907027721405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9765841960907</t>
   </si>
   <si>
     <t xml:space="preserve">3.13417625427246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20074558258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24965286254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28769302368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23063397407532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24557757377625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22248196601868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25101161003113</t>
+    <t xml:space="preserve">3.20074510574341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24965310096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28769254684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23063373565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24557733535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22248220443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25101137161255</t>
   </si>
   <si>
     <t xml:space="preserve">3.18715977668762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09477853775024</t>
+    <t xml:space="preserve">3.09477829933167</t>
   </si>
   <si>
     <t xml:space="preserve">3.11379790306091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19938683509827</t>
+    <t xml:space="preserve">3.19938659667969</t>
   </si>
   <si>
     <t xml:space="preserve">3.10428810119629</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1205906867981</t>
+    <t xml:space="preserve">3.12059044837952</t>
   </si>
   <si>
     <t xml:space="preserve">3.15727186203003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16270613670349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14504456520081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03907775878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02820944786072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96707463264465</t>
+    <t xml:space="preserve">3.16270589828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14504480361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03907799720764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0282096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96707487106323</t>
   </si>
   <si>
     <t xml:space="preserve">3.00375556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03636074066162</t>
+    <t xml:space="preserve">3.03636026382446</t>
   </si>
   <si>
     <t xml:space="preserve">3.02005791664124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97794318199158</t>
+    <t xml:space="preserve">2.977942943573</t>
   </si>
   <si>
     <t xml:space="preserve">2.9860942363739</t>
@@ -497,28 +497,28 @@
     <t xml:space="preserve">2.9956042766571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07575845718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08390974998474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12466621398926</t>
+    <t xml:space="preserve">3.07575869560242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12466645240784</t>
   </si>
   <si>
     <t xml:space="preserve">3.10836410522461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.128741979599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17900824546814</t>
+    <t xml:space="preserve">3.12874221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17900800704956</t>
   </si>
   <si>
     <t xml:space="preserve">3.17221593856812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12602543830872</t>
+    <t xml:space="preserve">3.12602519989014</t>
   </si>
   <si>
     <t xml:space="preserve">3.15863037109375</t>
@@ -533,118 +533,118 @@
     <t xml:space="preserve">3.25237059593201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27682399749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30671262741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30263710021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28090000152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21025514602661</t>
+    <t xml:space="preserve">3.27682423591614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30671238899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30263686180115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2808997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21025490760803</t>
   </si>
   <si>
     <t xml:space="preserve">3.28361701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29856085777283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28225803375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26323890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25644659996033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27003145217896</t>
+    <t xml:space="preserve">3.29856109619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28225827217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26323819160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25644564628601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27003121376038</t>
   </si>
   <si>
     <t xml:space="preserve">3.24693608283997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23335027694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21976447105408</t>
+    <t xml:space="preserve">3.23335099220276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21976494789124</t>
   </si>
   <si>
     <t xml:space="preserve">3.24150156974792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26188039779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23470878601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19802856445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23742604255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24829483032227</t>
+    <t xml:space="preserve">3.26188063621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23470902442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19802832603455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23742628097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24829459190369</t>
   </si>
   <si>
     <t xml:space="preserve">3.22791624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19395279884338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16542291641235</t>
+    <t xml:space="preserve">3.1939525604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16542267799377</t>
   </si>
   <si>
     <t xml:space="preserve">3.18444275856018</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18172597885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20753836631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2401430606842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26731395721436</t>
+    <t xml:space="preserve">3.18172574043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20753788948059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24014329910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26731443405151</t>
   </si>
   <si>
     <t xml:space="preserve">3.24286079406738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22655773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23199200630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20617938041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14640355110168</t>
+    <t xml:space="preserve">3.22655749320984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2319917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20617961883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14640307426453</t>
   </si>
   <si>
     <t xml:space="preserve">3.16813993453979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10157155990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678166389465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21704816818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22927522659302</t>
+    <t xml:space="preserve">3.10157108306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678190231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21704792976379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22927498817444</t>
   </si>
   <si>
     <t xml:space="preserve">3.24421906471252</t>
@@ -653,52 +653,52 @@
     <t xml:space="preserve">3.21433067321777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25372886657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35154509544373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49147510528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39365911483765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46430373191833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50506019592285</t>
+    <t xml:space="preserve">3.25372862815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35154461860657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4914755821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39365983009338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46430444717407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50506091117859</t>
   </si>
   <si>
     <t xml:space="preserve">3.41675519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40656590461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44732189178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43373680114746</t>
+    <t xml:space="preserve">3.40656518936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44732213020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43373656272888</t>
   </si>
   <si>
     <t xml:space="preserve">3.42694401741028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47109723091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46770048141479</t>
+    <t xml:space="preserve">3.47109746932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46770071983337</t>
   </si>
   <si>
     <t xml:space="preserve">3.48128604888916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50166487693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54242134094238</t>
+    <t xml:space="preserve">3.50166463851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5424211025238</t>
   </si>
   <si>
     <t xml:space="preserve">3.51185369491577</t>
@@ -707,19 +707,19 @@
     <t xml:space="preserve">3.54581689834595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55940246582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412261009216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60015964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53223133087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48468255996704</t>
+    <t xml:space="preserve">3.55940222740173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412284851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60015916824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53223156929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4846830368042</t>
   </si>
   <si>
     <t xml:space="preserve">3.55260992050171</t>
@@ -728,37 +728,37 @@
     <t xml:space="preserve">3.61374497413635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52543926239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58996987342834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60355544090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5933666229248</t>
+    <t xml:space="preserve">3.5254385471344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5899703502655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60355567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59336590766907</t>
   </si>
   <si>
     <t xml:space="preserve">3.62053751945496</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59676337242126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56619548797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562784194946</t>
+    <t xml:space="preserve">3.59676313400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56619596481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53562831878662</t>
   </si>
   <si>
     <t xml:space="preserve">3.45411515235901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45751190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39637660980225</t>
+    <t xml:space="preserve">3.45751118659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39637637138367</t>
   </si>
   <si>
     <t xml:space="preserve">3.32301545143127</t>
@@ -770,37 +770,37 @@
     <t xml:space="preserve">3.40996217727661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38958358764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32844924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30807065963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31078815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35018610954285</t>
+    <t xml:space="preserve">3.38958382606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32844877243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30807113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31078791618347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35018587112427</t>
   </si>
   <si>
     <t xml:space="preserve">3.3759982585907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35426163673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37328147888184</t>
+    <t xml:space="preserve">3.35426187515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37328124046326</t>
   </si>
   <si>
     <t xml:space="preserve">3.34339308738708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36648845672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37871551513672</t>
+    <t xml:space="preserve">3.3664882183075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37871599197388</t>
   </si>
   <si>
     <t xml:space="preserve">3.36105465888977</t>
@@ -809,10 +809,10 @@
     <t xml:space="preserve">3.12127017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16406440734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06624889373779</t>
+    <t xml:space="preserve">3.16406464576721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06624865531921</t>
   </si>
   <si>
     <t xml:space="preserve">3.0458710193634</t>
@@ -821,16 +821,16 @@
     <t xml:space="preserve">3.03228521347046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00239706039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02209568023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02549266815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04655003547668</t>
+    <t xml:space="preserve">3.00239729881287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02209615707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02549242973328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04655027389526</t>
   </si>
   <si>
     <t xml:space="preserve">2.99424576759338</t>
@@ -842,19 +842,19 @@
     <t xml:space="preserve">2.97862243652344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092646598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11651539802551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06828689575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00035929679871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96639537811279</t>
+    <t xml:space="preserve">3.03092694282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11651492118835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06828665733337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00035881996155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96639561653137</t>
   </si>
   <si>
     <t xml:space="preserve">2.92903518676758</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">2.924959897995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01326489448547</t>
+    <t xml:space="preserve">3.01326560974121</t>
   </si>
   <si>
     <t xml:space="preserve">3.09409928321838</t>
@@ -872,28 +872,28 @@
     <t xml:space="preserve">3.1430070400238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23538827896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2272367477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21297264099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19327330589294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27342748641968</t>
+    <t xml:space="preserve">3.23538851737976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22723722457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21297240257263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19327354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27342772483826</t>
   </si>
   <si>
     <t xml:space="preserve">3.29448509216309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20414233207703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30739164352417</t>
+    <t xml:space="preserve">3.20414185523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30739140510559</t>
   </si>
   <si>
     <t xml:space="preserve">3.2856547832489</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">3.39909386634827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47924852371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47517251968384</t>
+    <t xml:space="preserve">3.47924828529358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47517275810242</t>
   </si>
   <si>
     <t xml:space="preserve">3.48196530342102</t>
@@ -917,103 +917,103 @@
     <t xml:space="preserve">3.43713307380676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4439263343811</t>
+    <t xml:space="preserve">3.44392585754395</t>
   </si>
   <si>
     <t xml:space="preserve">3.49962639808655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.528156042099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4778892993927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51457023620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45887041091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52679800987244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52000498771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57570505142212</t>
+    <t xml:space="preserve">3.52815532684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47789001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51456999778748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45887017250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52679777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52000522613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57570552825928</t>
   </si>
   <si>
     <t xml:space="preserve">3.62733054161072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64499163627625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60423493385315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60287618637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62597131729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49419236183167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45615291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41539621353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45479393005371</t>
+    <t xml:space="preserve">3.64499139785767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60423517227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60287642478943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62597155570984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49419212341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45615315437317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41539645195007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45479416847229</t>
   </si>
   <si>
     <t xml:space="preserve">3.44256734848022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36309266090393</t>
+    <t xml:space="preserve">3.36309218406677</t>
   </si>
   <si>
     <t xml:space="preserve">3.39298009872437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39461994171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45400071144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46106934547424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36280822753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28151297569275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23414921760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07367873191833</t>
+    <t xml:space="preserve">3.39461970329285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45400047302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46107006072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36280846595764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28151249885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23414897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07367897033691</t>
   </si>
   <si>
     <t xml:space="preserve">3.1669921875</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1528537273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18961310386658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2786853313446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25747752189636</t>
+    <t xml:space="preserve">3.15285420417786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18961381912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27868509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2574770450592</t>
   </si>
   <si>
     <t xml:space="preserve">3.23556327819824</t>
@@ -1022,64 +1022,64 @@
     <t xml:space="preserve">3.23768377304077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34089350700378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43774175643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39037847518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41087818145752</t>
+    <t xml:space="preserve">3.20163130760193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34089374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43774151802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39037775993347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41087889671326</t>
   </si>
   <si>
     <t xml:space="preserve">3.37623977661133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38967132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40946483612061</t>
+    <t xml:space="preserve">3.38967108726501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40946507453918</t>
   </si>
   <si>
     <t xml:space="preserve">3.46319055557251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33735918998718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31544518470764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29989290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3444287776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35432505607605</t>
+    <t xml:space="preserve">3.33735966682434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3154444694519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29989266395569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34442853927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35432553291321</t>
   </si>
   <si>
     <t xml:space="preserve">3.32958316802979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33806681632996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29211688041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35644626617432</t>
+    <t xml:space="preserve">3.33806610107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29211640357971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35644602775574</t>
   </si>
   <si>
     <t xml:space="preserve">3.3522047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40098118782043</t>
+    <t xml:space="preserve">3.40098237991333</t>
   </si>
   <si>
     <t xml:space="preserve">3.41865468025208</t>
@@ -1088,49 +1088,49 @@
     <t xml:space="preserve">3.37765336036682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32534146308899</t>
+    <t xml:space="preserve">3.32534193992615</t>
   </si>
   <si>
     <t xml:space="preserve">3.35573935508728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34230828285217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40027475357056</t>
+    <t xml:space="preserve">3.34230756759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40027499198914</t>
   </si>
   <si>
     <t xml:space="preserve">3.45258688926697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44834542274475</t>
+    <t xml:space="preserve">3.44834566116333</t>
   </si>
   <si>
     <t xml:space="preserve">3.44269013404846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45117330551147</t>
+    <t xml:space="preserve">3.4511730670929</t>
   </si>
   <si>
     <t xml:space="preserve">3.41229295730591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4073441028595</t>
+    <t xml:space="preserve">3.40734457969666</t>
   </si>
   <si>
     <t xml:space="preserve">3.46036267280579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43137979507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47874283790588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42077565193176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42572450637817</t>
+    <t xml:space="preserve">3.43137907981873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4787425994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42077589035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42572402954102</t>
   </si>
   <si>
     <t xml:space="preserve">3.51479601860046</t>
@@ -1139,25 +1139,25 @@
     <t xml:space="preserve">3.4942946434021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39532661437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41582679748535</t>
+    <t xml:space="preserve">3.39532685279846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41582703590393</t>
   </si>
   <si>
     <t xml:space="preserve">3.42925834655762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40239596366882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36139488220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38825750350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43279314041138</t>
+    <t xml:space="preserve">3.4023962020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36139464378357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3882577419281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43279337882996</t>
   </si>
   <si>
     <t xml:space="preserve">3.33594536781311</t>
@@ -1166,37 +1166,37 @@
     <t xml:space="preserve">3.29706501960754</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30413389205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30837535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28787541389465</t>
+    <t xml:space="preserve">3.30413413047791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30837512016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2878749370575</t>
   </si>
   <si>
     <t xml:space="preserve">3.31615161895752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25182199478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28999614715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33311796188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33099722862244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33382511138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32675576210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34654903411865</t>
+    <t xml:space="preserve">3.25182223320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28999519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33311820030212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33099699020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33382487297058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32675552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34654951095581</t>
   </si>
   <si>
     <t xml:space="preserve">3.47450137138367</t>
@@ -1205,28 +1205,28 @@
     <t xml:space="preserve">3.49924349784851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49641633033752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46248316764832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45682835578918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45470762252808</t>
+    <t xml:space="preserve">3.49641585350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46248340606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45682859420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45470786094666</t>
   </si>
   <si>
     <t xml:space="preserve">3.38613653182983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45753502845764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45894956588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37411856651306</t>
+    <t xml:space="preserve">3.45753479003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45894932746887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37411880493164</t>
   </si>
   <si>
     <t xml:space="preserve">3.39391303062439</t>
@@ -1235,100 +1235,100 @@
     <t xml:space="preserve">3.42006850242615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30978941917419</t>
+    <t xml:space="preserve">3.30978965759277</t>
   </si>
   <si>
     <t xml:space="preserve">3.32816958427429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35715293884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27797842025757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24899482727051</t>
+    <t xml:space="preserve">3.35715317726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27797818183899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24899458885193</t>
   </si>
   <si>
     <t xml:space="preserve">3.21011400222778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23485612869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20516562461853</t>
+    <t xml:space="preserve">3.23485636711121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20516586303711</t>
   </si>
   <si>
     <t xml:space="preserve">3.15780234336853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13093876838684</t>
+    <t xml:space="preserve">3.130939245224</t>
   </si>
   <si>
     <t xml:space="preserve">3.15356087684631</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24545979499817</t>
+    <t xml:space="preserve">3.24546027183533</t>
   </si>
   <si>
     <t xml:space="preserve">3.16911292076111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19809627532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18890643119812</t>
+    <t xml:space="preserve">3.19809675216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1889066696167</t>
   </si>
   <si>
     <t xml:space="preserve">3.23909735679626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23344254493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27727127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23202896118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22920083999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22495937347412</t>
+    <t xml:space="preserve">3.23344206809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27727150917053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2320282459259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22920060157776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22495889663696</t>
   </si>
   <si>
     <t xml:space="preserve">3.27232313156128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31473779678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37341213226318</t>
+    <t xml:space="preserve">3.31473827362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3734118938446</t>
   </si>
   <si>
     <t xml:space="preserve">3.4250168800354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43491435050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48863959312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44693160057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38755011558533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3592734336853</t>
+    <t xml:space="preserve">3.43491387367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48863935470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4469313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38755059242249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35927367210388</t>
   </si>
   <si>
     <t xml:space="preserve">3.34160113334656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30059933662415</t>
+    <t xml:space="preserve">3.3005998134613</t>
   </si>
   <si>
     <t xml:space="preserve">3.30484127998352</t>
@@ -1337,43 +1337,43 @@
     <t xml:space="preserve">3.27585744857788</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3960337638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34937691688538</t>
+    <t xml:space="preserve">3.39603304862976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3493766784668</t>
   </si>
   <si>
     <t xml:space="preserve">3.36068773269653</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36704993247986</t>
+    <t xml:space="preserve">3.36705017089844</t>
   </si>
   <si>
     <t xml:space="preserve">3.3917920589447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41653418540955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45329403877258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52327871322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59114241600037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61235070228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073015213013</t>
+    <t xml:space="preserve">3.41653442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.453293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52327942848206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59114265441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61235094070435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63072991371155</t>
   </si>
   <si>
     <t xml:space="preserve">3.61093616485596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6279022693634</t>
+    <t xml:space="preserve">3.62790250778198</t>
   </si>
   <si>
     <t xml:space="preserve">3.60103964805603</t>
@@ -1382,28 +1382,28 @@
     <t xml:space="preserve">3.59962606430054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51055407524109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53176116943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57841777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61941909790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6491105556488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67880058288574</t>
+    <t xml:space="preserve">3.51055431365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53176212310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57841825485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61941981315613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64911031723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67880010604858</t>
   </si>
   <si>
     <t xml:space="preserve">3.62083339691162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68587017059326</t>
+    <t xml:space="preserve">3.6858696937561</t>
   </si>
   <si>
     <t xml:space="preserve">3.70849084854126</t>
@@ -1412,82 +1412,82 @@
     <t xml:space="preserve">3.65335178375244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68304228782654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68728351593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67738699913025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71414732933044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71131873130798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70990514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72545695304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73252654075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73111176490784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67173171043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69293904304504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71980214118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779902458191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61517810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68869709968567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69576668739319</t>
+    <t xml:space="preserve">3.68304204940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68728375434875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67738652229309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71414709091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71131896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70990490913391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72545671463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73252630233765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.731112241745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67173099517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69293880462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71980166435242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779926300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61517834663391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68869757652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69576692581177</t>
   </si>
   <si>
     <t xml:space="preserve">3.69435214996338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69718074798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68162870407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75232005119324</t>
+    <t xml:space="preserve">3.69718027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68162822723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7523193359375</t>
   </si>
   <si>
     <t xml:space="preserve">3.7438371181488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72262930870056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7650454044342</t>
+    <t xml:space="preserve">3.72262954711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76504492759705</t>
   </si>
   <si>
     <t xml:space="preserve">3.75938868522644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71697402000427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78342485427856</t>
+    <t xml:space="preserve">3.71697354316711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78342461585999</t>
   </si>
   <si>
     <t xml:space="preserve">3.83997797966003</t>
@@ -1505,10 +1505,10 @@
     <t xml:space="preserve">3.79756307601929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8173565864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85977125167847</t>
+    <t xml:space="preserve">3.81735682487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8597719669342</t>
   </si>
   <si>
     <t xml:space="preserve">3.86966872215271</t>
@@ -1517,73 +1517,73 @@
     <t xml:space="preserve">3.88380670547485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87532329559326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89370322227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88804817199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85270214080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8710823059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89087581634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84139156341553</t>
+    <t xml:space="preserve">3.87532353401184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89370369911194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88804841041565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85270285606384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87108254432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89087629318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84139132499695</t>
   </si>
   <si>
     <t xml:space="preserve">3.88239312171936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92339491844177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88946175575256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90359973907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92056679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91915249824524</t>
+    <t xml:space="preserve">3.92339420318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88946199417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9036009311676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92056655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91915321350098</t>
   </si>
   <si>
     <t xml:space="preserve">3.96439552307129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95732641220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91066980361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9332914352417</t>
+    <t xml:space="preserve">3.95732617378235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91067051887512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93329119682312</t>
   </si>
   <si>
     <t xml:space="preserve">3.90642833709717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90501475334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92198038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91208338737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9304633140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87956571578979</t>
+    <t xml:space="preserve">3.90501427650452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92197966575623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91208362579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93046379089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87956523895264</t>
   </si>
   <si>
     <t xml:space="preserve">3.89794516563416</t>
@@ -1592,13 +1592,13 @@
     <t xml:space="preserve">3.88097929954529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94742941856384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89228940010071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87390971183777</t>
+    <t xml:space="preserve">3.94742965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89228987693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87390947341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.90925621986389</t>
@@ -1607,49 +1607,49 @@
     <t xml:space="preserve">3.95025706291199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98136162757874</t>
+    <t xml:space="preserve">3.98136138916016</t>
   </si>
   <si>
     <t xml:space="preserve">4.00963830947876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08033037185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07891607284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13016366958618</t>
+    <t xml:space="preserve">4.08032989501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0789155960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13016319274902</t>
   </si>
   <si>
     <t xml:space="preserve">4.16984796524048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21100282669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.213942527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24921846389771</t>
+    <t xml:space="preserve">4.21100378036499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21394205093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24921798706055</t>
   </si>
   <si>
     <t xml:space="preserve">4.20512390136719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19483518600464</t>
+    <t xml:space="preserve">4.1948356628418</t>
   </si>
   <si>
     <t xml:space="preserve">4.1228141784668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1081166267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16543865203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21541166305542</t>
+    <t xml:space="preserve">4.10811710357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16543912887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21541213989258</t>
   </si>
   <si>
     <t xml:space="preserve">4.26979494094849</t>
@@ -1667,22 +1667,22 @@
     <t xml:space="preserve">4.33152770996094</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32564830780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.288902759552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35651397705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34328556060791</t>
+    <t xml:space="preserve">4.32564735412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28890228271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35651350021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34328508377075</t>
   </si>
   <si>
     <t xml:space="preserve">4.49908590316772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44764232635498</t>
+    <t xml:space="preserve">4.44764184951782</t>
   </si>
   <si>
     <t xml:space="preserve">4.4461727142334</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">4.48291778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48732662200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45352077484131</t>
+    <t xml:space="preserve">4.48732709884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45352125167847</t>
   </si>
   <si>
     <t xml:space="preserve">4.43735361099243</t>
@@ -1703,19 +1703,19 @@
     <t xml:space="preserve">4.35210466384888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34181594848633</t>
+    <t xml:space="preserve">4.34181547164917</t>
   </si>
   <si>
     <t xml:space="preserve">4.33446645736694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43147420883179</t>
+    <t xml:space="preserve">4.43147468566895</t>
   </si>
   <si>
     <t xml:space="preserve">4.47997808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4491114616394</t>
+    <t xml:space="preserve">4.44911193847656</t>
   </si>
   <si>
     <t xml:space="preserve">4.43882322311401</t>
@@ -1724,10 +1724,10 @@
     <t xml:space="preserve">4.49467611312866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51966238021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50349426269531</t>
+    <t xml:space="preserve">4.51966285705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50349473953247</t>
   </si>
   <si>
     <t xml:space="preserve">4.54317998886108</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">4.56228733062744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57698583602905</t>
+    <t xml:space="preserve">4.57698535919189</t>
   </si>
   <si>
     <t xml:space="preserve">4.52701187133789</t>
@@ -1745,19 +1745,19 @@
     <t xml:space="preserve">4.54170989990234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54905939102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40207815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43588399887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4255952835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38884973526001</t>
+    <t xml:space="preserve">4.54905891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40207719802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43588352203369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42559480667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38885021209717</t>
   </si>
   <si>
     <t xml:space="preserve">4.38150072097778</t>
@@ -1766,43 +1766,43 @@
     <t xml:space="preserve">4.24480867385864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20218420028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29037237167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29331254959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27420425415039</t>
+    <t xml:space="preserve">4.20218467712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29037189483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29331207275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27420473098755</t>
   </si>
   <si>
     <t xml:space="preserve">4.26097631454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2844934463501</t>
+    <t xml:space="preserve">4.28449296951294</t>
   </si>
   <si>
     <t xml:space="preserve">4.28743314743042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11399555206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16102933883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24186897277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15661954879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30360078811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2183518409729</t>
+    <t xml:space="preserve">4.11399507522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16102981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24186849594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15662002563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3036003112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21835231781006</t>
   </si>
   <si>
     <t xml:space="preserve">4.20071458816528</t>
@@ -1811,16 +1811,16 @@
     <t xml:space="preserve">4.1977744102478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34034585952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33593702316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34916543960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31388902664185</t>
+    <t xml:space="preserve">4.34034633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33593654632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34916496276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.313889503479</t>
   </si>
   <si>
     <t xml:space="preserve">4.30213117599487</t>
@@ -1835,13 +1835,13 @@
     <t xml:space="preserve">4.10370683670044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18307638168335</t>
+    <t xml:space="preserve">4.18307685852051</t>
   </si>
   <si>
     <t xml:space="preserve">4.14045190811157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12575387954712</t>
+    <t xml:space="preserve">4.12575435638428</t>
   </si>
   <si>
     <t xml:space="preserve">4.1933650970459</t>
@@ -1856,25 +1856,25 @@
     <t xml:space="preserve">4.25215721130371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29919147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39031982421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32711744308472</t>
+    <t xml:space="preserve">4.29919099807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39031934738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32711696624756</t>
   </si>
   <si>
     <t xml:space="preserve">4.30066156387329</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21247291564941</t>
+    <t xml:space="preserve">4.21247243881226</t>
   </si>
   <si>
     <t xml:space="preserve">4.31241989135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36974287033081</t>
+    <t xml:space="preserve">4.36974239349365</t>
   </si>
   <si>
     <t xml:space="preserve">4.24774837493896</t>
@@ -1883,22 +1883,22 @@
     <t xml:space="preserve">4.18895530700684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011064529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18748569488525</t>
+    <t xml:space="preserve">4.23011016845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18748617172241</t>
   </si>
   <si>
     <t xml:space="preserve">4.17425727844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1727876663208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14486122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1683783531189</t>
+    <t xml:space="preserve">4.17278814315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14486169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16837882995605</t>
   </si>
   <si>
     <t xml:space="preserve">4.18013715744019</t>
@@ -1907,52 +1907,52 @@
     <t xml:space="preserve">4.238929271698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25362730026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29478168487549</t>
+    <t xml:space="preserve">4.25362682342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2947826385498</t>
   </si>
   <si>
     <t xml:space="preserve">4.33740663528442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35063457489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28302383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33299684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30654096603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268209457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39178895950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27861404418945</t>
+    <t xml:space="preserve">4.35063505172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28302335739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33299732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30654001235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268161773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39178943634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27861452102661</t>
   </si>
   <si>
     <t xml:space="preserve">4.22423124313354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23745918273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22570085525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19189548492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22129106521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23598957061768</t>
+    <t xml:space="preserve">4.23745965957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22570133209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19189596176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22129201889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23598909378052</t>
   </si>
   <si>
     <t xml:space="preserve">4.22716999053955</t>
@@ -1961,46 +1961,46 @@
     <t xml:space="preserve">4.00963878631592</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07431030273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08900880813599</t>
+    <t xml:space="preserve">4.07431077957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08900928497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.04932403564453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01992797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95378637313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99494075775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04197454452515</t>
+    <t xml:space="preserve">4.01992750167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95378613471985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99494099617004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0419750213623</t>
   </si>
   <si>
     <t xml:space="preserve">3.99053120613098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03609561920166</t>
+    <t xml:space="preserve">4.03609609603882</t>
   </si>
   <si>
     <t xml:space="preserve">4.10664653778076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16396856307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1272234916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13751268386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00082015991211</t>
+    <t xml:space="preserve">4.16396903991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12722444534302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13751220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00081968307495</t>
   </si>
   <si>
     <t xml:space="preserve">4.09194850921631</t>
@@ -2009,31 +2009,31 @@
     <t xml:space="preserve">4.08459949493408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02727699279785</t>
+    <t xml:space="preserve">4.02727651596069</t>
   </si>
   <si>
     <t xml:space="preserve">4.02286720275879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10076665878296</t>
+    <t xml:space="preserve">4.10076713562012</t>
   </si>
   <si>
     <t xml:space="preserve">4.20365381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13898181915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25068759918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20659399032593</t>
+    <t xml:space="preserve">4.13898229598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25068712234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20659351348877</t>
   </si>
   <si>
     <t xml:space="preserve">4.263916015625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30801057815552</t>
+    <t xml:space="preserve">4.30801010131836</t>
   </si>
   <si>
     <t xml:space="preserve">4.48144769668579</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">4.51525354385376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49761486053467</t>
+    <t xml:space="preserve">4.49761581420898</t>
   </si>
   <si>
     <t xml:space="preserve">4.40648746490479</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">4.46674966812134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49173641204834</t>
+    <t xml:space="preserve">4.4917368888855</t>
   </si>
   <si>
     <t xml:space="preserve">4.46087074279785</t>
@@ -2063,19 +2063,19 @@
     <t xml:space="preserve">4.46234035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51231384277344</t>
+    <t xml:space="preserve">4.51231336593628</t>
   </si>
   <si>
     <t xml:space="preserve">4.45205163955688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48585748672485</t>
+    <t xml:space="preserve">4.4858570098877</t>
   </si>
   <si>
     <t xml:space="preserve">4.62548923492432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26538610458374</t>
+    <t xml:space="preserve">4.26538515090942</t>
   </si>
   <si>
     <t xml:space="preserve">4.26244640350342</t>
@@ -2084,25 +2084,25 @@
     <t xml:space="preserve">4.06549215316772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08606910705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72890520095825</t>
+    <t xml:space="preserve">4.08606863021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72890543937683</t>
   </si>
   <si>
     <t xml:space="preserve">3.51798844337463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50181984901428</t>
+    <t xml:space="preserve">3.50182032585144</t>
   </si>
   <si>
     <t xml:space="preserve">3.02192735671997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24754333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15127038955688</t>
+    <t xml:space="preserve">3.24754309654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15127086639404</t>
   </si>
   <si>
     <t xml:space="preserve">3.27032518386841</t>
@@ -2111,61 +2111,61 @@
     <t xml:space="preserve">3.29531240463257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35189986228943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21153259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12995791435242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35557413101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38937973976135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34381580352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35924887657166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5709011554718</t>
+    <t xml:space="preserve">3.35189914703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21153283119202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.129958152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3555736541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38937950134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34381532669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35924863815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57090091705322</t>
   </si>
   <si>
     <t xml:space="preserve">3.66643857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44964146614075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55693817138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58780431747437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53636002540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54958891868591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4658100605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54811906814575</t>
+    <t xml:space="preserve">3.44964170455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55693769454956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58780384063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53636050224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54958844184875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46580982208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54811930656433</t>
   </si>
   <si>
     <t xml:space="preserve">3.56428670883179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59368276596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62601923942566</t>
+    <t xml:space="preserve">3.59368324279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62601900100708</t>
   </si>
   <si>
     <t xml:space="preserve">3.57163619995117</t>
@@ -2174,43 +2174,43 @@
     <t xml:space="preserve">3.57310605049133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44082283973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61719989776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52754211425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57457542419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56722688674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57898473739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75168776512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68187165260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70391869544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60691142082214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61279034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66423392295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63189816474915</t>
+    <t xml:space="preserve">3.44082307815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61720013618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52754187583923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57457494735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56722617149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5789852142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75168800354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68187189102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70391845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60691118240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61279058456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66423416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63189840316772</t>
   </si>
   <si>
     <t xml:space="preserve">3.62454915046692</t>
@@ -2219,145 +2219,145 @@
     <t xml:space="preserve">3.63777732849121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6230788230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71126747131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73626255989075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60662722587585</t>
+    <t xml:space="preserve">3.62307906150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71126770973206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73626232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60662746429443</t>
   </si>
   <si>
     <t xml:space="preserve">3.66372871398926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63440656661987</t>
+    <t xml:space="preserve">3.63440680503845</t>
   </si>
   <si>
     <t xml:space="preserve">3.6853346824646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75015234947205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73008966445923</t>
+    <t xml:space="preserve">3.75015211105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73009014129639</t>
   </si>
   <si>
     <t xml:space="preserve">3.70231032371521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80725336074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77021455764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81959915161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90447902679443</t>
+    <t xml:space="preserve">3.80725288391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77021479606628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81959939002991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90447926521301</t>
   </si>
   <si>
     <t xml:space="preserve">3.99707531929016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05108976364136</t>
+    <t xml:space="preserve">4.05109024047852</t>
   </si>
   <si>
     <t xml:space="preserve">4.02408266067505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92762851715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8813304901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81651306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91991186141968</t>
+    <t xml:space="preserve">3.92762875556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88133025169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8165123462677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91991209983826</t>
   </si>
   <si>
     <t xml:space="preserve">4.08581352233887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05880689620972</t>
+    <t xml:space="preserve">4.05880641937256</t>
   </si>
   <si>
     <t xml:space="preserve">4.10896253585815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14754438400269</t>
+    <t xml:space="preserve">4.14754486083984</t>
   </si>
   <si>
     <t xml:space="preserve">4.02022457122803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96620988845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9893593788147</t>
+    <t xml:space="preserve">3.96620965003967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98935914039612</t>
   </si>
   <si>
     <t xml:space="preserve">4.03565740585327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08967208862305</t>
+    <t xml:space="preserve">4.08967161178589</t>
   </si>
   <si>
     <t xml:space="preserve">4.03179931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07038116455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11282062530518</t>
+    <t xml:space="preserve">4.07038068771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11282110214233</t>
   </si>
   <si>
     <t xml:space="preserve">4.0549488067627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95463562011719</t>
+    <t xml:space="preserve">3.95463585853577</t>
   </si>
   <si>
     <t xml:space="preserve">3.96235203742981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93534445762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97006845474243</t>
+    <t xml:space="preserve">3.9353449344635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97006821632385</t>
   </si>
   <si>
     <t xml:space="preserve">3.97392678260803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07423973083496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1243953704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10510540008545</t>
+    <t xml:space="preserve">4.0742392539978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12439584732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10510492324829</t>
   </si>
   <si>
     <t xml:space="preserve">4.09352970123291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04723215103149</t>
+    <t xml:space="preserve">4.04723167419434</t>
   </si>
   <si>
     <t xml:space="preserve">4.12825345993042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25943183898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26714849472046</t>
+    <t xml:space="preserve">4.25943231582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26714897155762</t>
   </si>
   <si>
     <t xml:space="preserve">4.21313381195068</t>
@@ -2366,28 +2366,28 @@
     <t xml:space="preserve">4.19770097732544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16297769546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16683626174927</t>
+    <t xml:space="preserve">4.16297721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16683578491211</t>
   </si>
   <si>
     <t xml:space="preserve">4.22470808029175</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28643894195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36746072769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42147541046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3906102180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37517738342285</t>
+    <t xml:space="preserve">4.28643941879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36746120452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42147588729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39061069488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37517786026001</t>
   </si>
   <si>
     <t xml:space="preserve">4.36360311508179</t>
@@ -2396,19 +2396,19 @@
     <t xml:space="preserve">4.30572986602783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26328992843628</t>
+    <t xml:space="preserve">4.26329040527344</t>
   </si>
   <si>
     <t xml:space="preserve">4.24399900436401</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31344699859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30187177658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13597011566162</t>
+    <t xml:space="preserve">4.31344652175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30187129974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13597059249878</t>
   </si>
   <si>
     <t xml:space="preserve">4.22856664657593</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">4.18612670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17455148696899</t>
+    <t xml:space="preserve">4.17455196380615</t>
   </si>
   <si>
     <t xml:space="preserve">4.18998432159424</t>
@@ -2435,22 +2435,22 @@
     <t xml:space="preserve">4.15140295028687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15911865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19384288787842</t>
+    <t xml:space="preserve">4.15911960601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19384241104126</t>
   </si>
   <si>
     <t xml:space="preserve">4.07809734344482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89290475845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97778511047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06266450881958</t>
+    <t xml:space="preserve">3.89290499687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9777843952179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06266498565674</t>
   </si>
   <si>
     <t xml:space="preserve">3.94691920280457</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">3.9855010509491</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9816427230835</t>
+    <t xml:space="preserve">3.98164296150208</t>
   </si>
   <si>
     <t xml:space="preserve">3.88904643058777</t>
@@ -2471,67 +2471,67 @@
     <t xml:space="preserve">3.7270028591156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82885909080505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83194541931152</t>
+    <t xml:space="preserve">3.82885885238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8319456577301</t>
   </si>
   <si>
     <t xml:space="preserve">3.86589741706848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00479221343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95077729225159</t>
+    <t xml:space="preserve">4.00479173660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95077776908875</t>
   </si>
   <si>
     <t xml:space="preserve">4.08195543289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03951597213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13982820510864</t>
+    <t xml:space="preserve">4.03951549530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13982772827148</t>
   </si>
   <si>
     <t xml:space="preserve">4.17069387435913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14368629455566</t>
+    <t xml:space="preserve">4.14368677139282</t>
   </si>
   <si>
     <t xml:space="preserve">4.1321120262146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93920302391052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90062069892883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80879640579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99321794509888</t>
+    <t xml:space="preserve">3.93920350074768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90062117576599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80879616737366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9932177066803</t>
   </si>
   <si>
     <t xml:space="preserve">4.01250791549683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95849370956421</t>
+    <t xml:space="preserve">3.95849347114563</t>
   </si>
   <si>
     <t xml:space="preserve">3.8774721622467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93148612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92377066612244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86203980445862</t>
+    <t xml:space="preserve">3.93148636817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92377018928528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8620388507843</t>
   </si>
   <si>
     <t xml:space="preserve">3.81805610656738</t>
@@ -2540,40 +2540,40 @@
     <t xml:space="preserve">3.80570983886719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85818147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89676284790039</t>
+    <t xml:space="preserve">3.85818123817444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89676260948181</t>
   </si>
   <si>
     <t xml:space="preserve">3.85663795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82114315032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83811831474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94306135177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90833759307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88518834114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83503198623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76712846755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76249837875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82268571853638</t>
+    <t xml:space="preserve">3.82114267349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83811855316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94306111335754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90833783149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88518786430359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83503174781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76712775230408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76249814033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82268619537354</t>
   </si>
   <si>
     <t xml:space="preserve">3.79799342155457</t>
@@ -2591,49 +2591,49 @@
     <t xml:space="preserve">4.2092752456665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25171613693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25557374954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31730508804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27100610733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26251888275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28721141815186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25634527206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24554204940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14985942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12979745864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14060020446777</t>
+    <t xml:space="preserve">4.25171566009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25557327270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3173041343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27100658416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26251840591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2872109413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25634479522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24554252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14985990524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12979698181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14059972763062</t>
   </si>
   <si>
     <t xml:space="preserve">4.12362384796143</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16837882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17146587371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19924354553223</t>
+    <t xml:space="preserve">4.16837930679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1714653968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19924449920654</t>
   </si>
   <si>
     <t xml:space="preserve">4.23628282546997</t>
@@ -2642,7 +2642,7 @@
     <t xml:space="preserve">4.18844127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17763900756836</t>
+    <t xml:space="preserve">4.1776385307312</t>
   </si>
   <si>
     <t xml:space="preserve">4.1791820526123</t>
@@ -2654,31 +2654,31 @@
     <t xml:space="preserve">4.20387411117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1853551864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21622037887573</t>
+    <t xml:space="preserve">4.18535423278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21622085571289</t>
   </si>
   <si>
     <t xml:space="preserve">4.29338407516479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23165321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25017166137695</t>
+    <t xml:space="preserve">4.23165273666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25017261505127</t>
   </si>
   <si>
     <t xml:space="preserve">4.23782634735107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35048532485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34122514724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39369678497314</t>
+    <t xml:space="preserve">4.35048484802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34122562408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39369630813599</t>
   </si>
   <si>
     <t xml:space="preserve">4.47086048126221</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">4.44025039672852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38854455947876</t>
+    <t xml:space="preserve">4.3885440826416</t>
   </si>
   <si>
     <t xml:space="preserve">4.35622835159302</t>
@@ -2699,55 +2699,55 @@
     <t xml:space="preserve">4.38531255722046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37400245666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39015960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37723398208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40147066116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45156145095825</t>
+    <t xml:space="preserve">4.37400197982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39016008377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37723350524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40147113800049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45156097412109</t>
   </si>
   <si>
     <t xml:space="preserve">4.47418212890625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49357223510742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50165128707886</t>
+    <t xml:space="preserve">4.49357175827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5016508102417</t>
   </si>
   <si>
     <t xml:space="preserve">4.52911996841431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55174112319946</t>
+    <t xml:space="preserve">4.55174160003662</t>
   </si>
   <si>
     <t xml:space="preserve">4.55012512207031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62122106552124</t>
+    <t xml:space="preserve">4.62122058868408</t>
   </si>
   <si>
     <t xml:space="preserve">4.58405733108521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56628370285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54527759552002</t>
+    <t xml:space="preserve">4.56628322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54527807235718</t>
   </si>
   <si>
     <t xml:space="preserve">4.52750396728516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45640850067139</t>
+    <t xml:space="preserve">4.45640802383423</t>
   </si>
   <si>
     <t xml:space="preserve">4.49680376052856</t>
@@ -2777,31 +2777,31 @@
     <t xml:space="preserve">4.47902965545654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52265691757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54204702377319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54689407348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50811386108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37884950637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35461187362671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37238645553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53719902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56789970397949</t>
+    <t xml:space="preserve">4.52265644073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54204654693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54689359664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50811433792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37884902954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35461235046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37238597869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5371994972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56789922714233</t>
   </si>
   <si>
     <t xml:space="preserve">4.61152648925781</t>
@@ -2810,52 +2810,52 @@
     <t xml:space="preserve">4.6147575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61637401580811</t>
+    <t xml:space="preserve">4.61637353897095</t>
   </si>
   <si>
     <t xml:space="preserve">4.62768459320068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59375238418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60829448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63091611862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65676879882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66484832763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69070148468018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73271226882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76502799987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80219221115112</t>
+    <t xml:space="preserve">4.59375190734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60829496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63091564178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65676927566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66484880447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69070100784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73271179199219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76502847671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80219173431396</t>
   </si>
   <si>
     <t xml:space="preserve">4.79896068572998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76987552642822</t>
+    <t xml:space="preserve">4.76987600326538</t>
   </si>
   <si>
     <t xml:space="preserve">4.82804489135742</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82481336593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84420347213745</t>
+    <t xml:space="preserve">4.82481384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84420299530029</t>
   </si>
   <si>
     <t xml:space="preserve">4.80703973770142</t>
@@ -2867,16 +2867,16 @@
     <t xml:space="preserve">4.57436275482178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53558301925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59213638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54366207122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49034070968628</t>
+    <t xml:space="preserve">4.53558349609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5921368598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54366254806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49034023284912</t>
   </si>
   <si>
     <t xml:space="preserve">4.49195623397827</t>
@@ -2888,19 +2888,19 @@
     <t xml:space="preserve">4.45964002609253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51134586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52427196502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46125507354736</t>
+    <t xml:space="preserve">4.51134538650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52427291870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46125555038452</t>
   </si>
   <si>
     <t xml:space="preserve">4.58567333221436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63576316833496</t>
+    <t xml:space="preserve">4.63576364517212</t>
   </si>
   <si>
     <t xml:space="preserve">4.58890438079834</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">4.65353775024414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57113075256348</t>
+    <t xml:space="preserve">4.57113122940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.4757981300354</t>
@@ -2921,58 +2921,58 @@
     <t xml:space="preserve">4.46933507919312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43217134475708</t>
+    <t xml:space="preserve">4.43217182159424</t>
   </si>
   <si>
     <t xml:space="preserve">4.47095060348511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48387765884399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39985513687134</t>
+    <t xml:space="preserve">4.48387718200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39985466003418</t>
   </si>
   <si>
     <t xml:space="preserve">4.37076997756958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39662265777588</t>
+    <t xml:space="preserve">4.3966236114502</t>
   </si>
   <si>
     <t xml:space="preserve">4.41116571426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51457738876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46287202835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43540287017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50003576278687</t>
+    <t xml:space="preserve">4.51457786560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46287155151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43540239334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50003528594971</t>
   </si>
   <si>
     <t xml:space="preserve">4.53881454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61314249038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63253211975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60021591186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5565881729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57921028137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52588844299316</t>
+    <t xml:space="preserve">4.6131420135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63253164291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60021543502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55658864974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57920980453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52588891983032</t>
   </si>
   <si>
     <t xml:space="preserve">4.48064565658569</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">4.53235149383545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44832897186279</t>
+    <t xml:space="preserve">4.44832992553711</t>
   </si>
   <si>
     <t xml:space="preserve">4.5048828125</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">4.65838479995728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68262195587158</t>
+    <t xml:space="preserve">4.68262147903442</t>
   </si>
   <si>
     <t xml:space="preserve">4.65515327453613</t>
@@ -3011,10 +3011,10 @@
     <t xml:space="preserve">4.68585395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70362758636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6680793762207</t>
+    <t xml:space="preserve">4.7036280632019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66807985305786</t>
   </si>
   <si>
     <t xml:space="preserve">4.64545822143555</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">4.7262487411499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76179695129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75048637390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84905052185059</t>
+    <t xml:space="preserve">4.76179647445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75048589706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84905004501343</t>
   </si>
   <si>
     <t xml:space="preserve">4.87490367889404</t>
@@ -3038,25 +3038,25 @@
     <t xml:space="preserve">4.88944578170776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91853046417236</t>
+    <t xml:space="preserve">4.91853094100952</t>
   </si>
   <si>
     <t xml:space="preserve">4.85874557495117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83127641677856</t>
+    <t xml:space="preserve">4.83127689361572</t>
   </si>
   <si>
     <t xml:space="preserve">4.66161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6406102180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7294807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74402332305908</t>
+    <t xml:space="preserve">4.64061117172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72948026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74402284622192</t>
   </si>
   <si>
     <t xml:space="preserve">4.76018095016479</t>
@@ -3068,16 +3068,16 @@
     <t xml:space="preserve">4.79734516143799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71655416488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79572820663452</t>
+    <t xml:space="preserve">4.71655368804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79572916030884</t>
   </si>
   <si>
     <t xml:space="preserve">4.83450841903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74563884735107</t>
+    <t xml:space="preserve">4.74563837051392</t>
   </si>
   <si>
     <t xml:space="preserve">4.50972986221313</t>
@@ -3098,37 +3098,37 @@
     <t xml:space="preserve">4.54851007461548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50326681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41278123855591</t>
+    <t xml:space="preserve">4.50326633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41278171539307</t>
   </si>
   <si>
     <t xml:space="preserve">4.35299634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32068014144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55820512771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51780891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49518823623657</t>
+    <t xml:space="preserve">4.32068061828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55820465087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51780939102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49518728256226</t>
   </si>
   <si>
     <t xml:space="preserve">4.4176287651062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48872518539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43378734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70524263381958</t>
+    <t xml:space="preserve">4.48872470855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43378686904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70524311065674</t>
   </si>
   <si>
     <t xml:space="preserve">4.7302885055542</t>
@@ -3137,10 +3137,10 @@
     <t xml:space="preserve">4.68181419372559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77472305297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89590883255005</t>
+    <t xml:space="preserve">4.77472352981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89590930938721</t>
   </si>
   <si>
     <t xml:space="preserve">4.94034385681152</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">4.91610670089722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91206693649292</t>
+    <t xml:space="preserve">4.91206741333008</t>
   </si>
   <si>
     <t xml:space="preserve">5.00497627258301</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">5.04537153244019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15039920806885</t>
+    <t xml:space="preserve">5.15039968490601</t>
   </si>
   <si>
     <t xml:space="preserve">5.08980703353882</t>
@@ -3170,25 +3170,25 @@
     <t xml:space="preserve">4.9807391166687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96054172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99285793304443</t>
+    <t xml:space="preserve">4.96054124832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99285697937012</t>
   </si>
   <si>
     <t xml:space="preserve">5.01709508895874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00093698501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01305484771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97266054153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89994859695435</t>
+    <t xml:space="preserve">5.00093650817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0130558013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97266006469727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8999490737915</t>
   </si>
   <si>
     <t xml:space="preserve">4.94842290878296</t>
@@ -3197,28 +3197,28 @@
     <t xml:space="preserve">4.92014646530151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10596466064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05345106124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16251802444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20222187042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11777067184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15577411651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18533182144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10087966918945</t>
+    <t xml:space="preserve">5.10596513748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05345058441162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16251850128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20222234725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11777019500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15577363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18533134460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10088014602661</t>
   </si>
   <si>
     <t xml:space="preserve">5.06287670135498</t>
@@ -3227,13 +3227,13 @@
     <t xml:space="preserve">5.07554483413696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0290961265564</t>
+    <t xml:space="preserve">5.02909660339355</t>
   </si>
   <si>
     <t xml:space="preserve">5.04598665237427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02487373352051</t>
+    <t xml:space="preserve">5.02487325668335</t>
   </si>
   <si>
     <t xml:space="preserve">4.87286043167114</t>
@@ -3248,19 +3248,19 @@
     <t xml:space="preserve">4.54772186279297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60261535644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53505373001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71662473678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64906358718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5097188949585</t>
+    <t xml:space="preserve">4.60261487960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53505420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71662521362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64906406402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50971841812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.34081506729126</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">4.69551229476929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63217401504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7419605255127</t>
+    <t xml:space="preserve">4.63217353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74196004867554</t>
   </si>
   <si>
     <t xml:space="preserve">4.73773813247681</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">4.69128942489624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72929239273071</t>
+    <t xml:space="preserve">4.72929286956787</t>
   </si>
   <si>
     <t xml:space="preserve">4.64061880111694</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">4.6068377494812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64484071731567</t>
+    <t xml:space="preserve">4.64484119415283</t>
   </si>
   <si>
     <t xml:space="preserve">4.45060253143311</t>
@@ -3311,10 +3311,10 @@
     <t xml:space="preserve">4.45482492446899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38726329803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46326971054077</t>
+    <t xml:space="preserve">4.38726377487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46327018737793</t>
   </si>
   <si>
     <t xml:space="preserve">4.59417009353638</t>
@@ -3326,13 +3326,13 @@
     <t xml:space="preserve">4.71240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61528301239014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62795114517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65750885009766</t>
+    <t xml:space="preserve">4.61528348922729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62795066833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6575083732605</t>
   </si>
   <si>
     <t xml:space="preserve">4.65328645706177</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">4.72506999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77151918411255</t>
+    <t xml:space="preserve">4.77151870727539</t>
   </si>
   <si>
     <t xml:space="preserve">4.70817995071411</t>
@@ -3362,19 +3362,19 @@
     <t xml:space="preserve">4.66173124313354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53927659988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47593784332275</t>
+    <t xml:space="preserve">4.53927612304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47593832015991</t>
   </si>
   <si>
     <t xml:space="preserve">4.33659267425537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31125736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42104434967041</t>
+    <t xml:space="preserve">4.31125688552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42104482650757</t>
   </si>
   <si>
     <t xml:space="preserve">4.29436683654785</t>
@@ -3386,13 +3386,13 @@
     <t xml:space="preserve">4.25636339187622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39148569107056</t>
+    <t xml:space="preserve">4.39148616790771</t>
   </si>
   <si>
     <t xml:space="preserve">4.41259908676147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4041543006897</t>
+    <t xml:space="preserve">4.40415382385254</t>
   </si>
   <si>
     <t xml:space="preserve">4.32392454147339</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">4.3197021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36192798614502</t>
+    <t xml:space="preserve">4.36192846298218</t>
   </si>
   <si>
     <t xml:space="preserve">4.27747631072998</t>
@@ -3416,34 +3416,34 @@
     <t xml:space="preserve">4.34503793716431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27325344085693</t>
+    <t xml:space="preserve">4.27325439453125</t>
   </si>
   <si>
     <t xml:space="preserve">4.14319849014282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07225847244263</t>
+    <t xml:space="preserve">4.07225894927979</t>
   </si>
   <si>
     <t xml:space="preserve">4.02665519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03341102600098</t>
+    <t xml:space="preserve">4.03341150283813</t>
   </si>
   <si>
     <t xml:space="preserve">4.12630796432495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22680568695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10097217559814</t>
+    <t xml:space="preserve">4.22680521011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1009726524353</t>
   </si>
   <si>
     <t xml:space="preserve">4.03678941726685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02834415435791</t>
+    <t xml:space="preserve">4.02834367752075</t>
   </si>
   <si>
     <t xml:space="preserve">4.01314258575439</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">3.84761762619019</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97091722488403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06719160079956</t>
+    <t xml:space="preserve">3.97091698646545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06719207763672</t>
   </si>
   <si>
     <t xml:space="preserve">4.04016733169556</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">4.09421634674072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01483201980591</t>
+    <t xml:space="preserve">4.01483249664307</t>
   </si>
   <si>
     <t xml:space="preserve">4.15333271026611</t>
@@ -3479,28 +3479,28 @@
     <t xml:space="preserve">4.49282836914062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38304090499878</t>
+    <t xml:space="preserve">4.38304138183594</t>
   </si>
   <si>
     <t xml:space="preserve">4.43371200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.564612865448</t>
+    <t xml:space="preserve">4.56461238861084</t>
   </si>
   <si>
     <t xml:space="preserve">4.68706703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80952215194702</t>
+    <t xml:space="preserve">4.80952167510986</t>
   </si>
   <si>
     <t xml:space="preserve">4.75462818145752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73351526260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75040626525879</t>
+    <t xml:space="preserve">4.73351573944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75040578842163</t>
   </si>
   <si>
     <t xml:space="preserve">4.76307344436646</t>
@@ -3509,10 +3509,10 @@
     <t xml:space="preserve">4.7672963142395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75885105133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74618339538574</t>
+    <t xml:space="preserve">4.75885152816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74618291854858</t>
   </si>
   <si>
     <t xml:space="preserve">4.55194425582886</t>
@@ -3530,19 +3530,19 @@
     <t xml:space="preserve">4.52660894393921</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44638013839722</t>
+    <t xml:space="preserve">4.44637966156006</t>
   </si>
   <si>
     <t xml:space="preserve">4.5561671257019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51394128799438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56883430480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78418636322021</t>
+    <t xml:space="preserve">4.51394081115723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56883478164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78418684005737</t>
   </si>
   <si>
     <t xml:space="preserve">4.58994770050049</t>
@@ -3551,13 +3551,13 @@
     <t xml:space="preserve">4.52238607406616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62372827529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48438310623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44215774536133</t>
+    <t xml:space="preserve">4.62372875213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48438262939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44215726852417</t>
   </si>
   <si>
     <t xml:space="preserve">4.35348320007324</t>
@@ -3587,34 +3587,34 @@
     <t xml:space="preserve">5.05020904541016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99109268188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09243535995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01220560073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98687028884888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91930866241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95731258392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00798320770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86019325256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94042158126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93619966506958</t>
+    <t xml:space="preserve">4.99109315872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09243488311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01220607757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98687076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91930913925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95731210708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00798273086548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86019277572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94042205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93619918823242</t>
   </si>
   <si>
     <t xml:space="preserve">4.96575784683228</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">4.96153497695923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00376129150391</t>
+    <t xml:space="preserve">5.00376081466675</t>
   </si>
   <si>
     <t xml:space="preserve">4.96998023986816</t>
@@ -3632,19 +3632,19 @@
     <t xml:space="preserve">4.83908033370972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88975143432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82535934448242</t>
+    <t xml:space="preserve">4.88975048065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82535886764526</t>
   </si>
   <si>
     <t xml:space="preserve">4.82981061935425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75858783721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66955900192261</t>
+    <t xml:space="preserve">4.75858736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66955852508545</t>
   </si>
   <si>
     <t xml:space="preserve">4.71852493286133</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">4.78529596328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90993642807007</t>
+    <t xml:space="preserve">4.90993595123291</t>
   </si>
   <si>
     <t xml:space="preserve">4.95890283584595</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">4.93219375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96780490875244</t>
+    <t xml:space="preserve">4.9678053855896</t>
   </si>
   <si>
     <t xml:space="preserve">4.9989652633667</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">4.99006223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86987352371216</t>
+    <t xml:space="preserve">4.869873046875</t>
   </si>
   <si>
     <t xml:space="preserve">4.95445108413696</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">4.88322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87432479858398</t>
+    <t xml:space="preserve">4.87432527542114</t>
   </si>
   <si>
     <t xml:space="preserve">4.80755376815796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75413656234741</t>
+    <t xml:space="preserve">4.75413608551025</t>
   </si>
   <si>
     <t xml:space="preserve">4.85206747055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63839864730835</t>
+    <t xml:space="preserve">4.63839912414551</t>
   </si>
   <si>
     <t xml:space="preserve">4.60278749465942</t>
@@ -3716,19 +3716,19 @@
     <t xml:space="preserve">4.70517015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69626712799072</t>
+    <t xml:space="preserve">4.69626760482788</t>
   </si>
   <si>
     <t xml:space="preserve">4.68291330337524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7452335357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76303863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77194166183472</t>
+    <t xml:space="preserve">4.74523305892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76303911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77194213867188</t>
   </si>
   <si>
     <t xml:space="preserve">4.71407318115234</t>
@@ -3746,25 +3746,25 @@
     <t xml:space="preserve">4.57607841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5538215637207</t>
+    <t xml:space="preserve">4.55382108688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.53156423568726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59388446807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.647301197052</t>
+    <t xml:space="preserve">4.59388399124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64730167388916</t>
   </si>
   <si>
     <t xml:space="preserve">4.66510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61614179611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54937028884888</t>
+    <t xml:space="preserve">4.6161413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54936981201172</t>
   </si>
   <si>
     <t xml:space="preserve">4.50485563278198</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">4.500403881073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49595260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48704957962036</t>
+    <t xml:space="preserve">4.49595308303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48705005645752</t>
   </si>
   <si>
     <t xml:space="preserve">4.70071887969971</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">4.73187923431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.722975730896</t>
+    <t xml:space="preserve">4.72297620773315</t>
   </si>
   <si>
     <t xml:space="preserve">4.44609642028809</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">4.24489164352417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28228330612183</t>
+    <t xml:space="preserve">4.28228378295898</t>
   </si>
   <si>
     <t xml:space="preserve">4.31789493560791</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">4.34282302856445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41226577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43541288375854</t>
+    <t xml:space="preserve">4.41226530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4354133605957</t>
   </si>
   <si>
     <t xml:space="preserve">4.42829084396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39267921447754</t>
+    <t xml:space="preserve">4.3926796913147</t>
   </si>
   <si>
     <t xml:space="preserve">4.45588970184326</t>
@@ -3857,22 +3857,22 @@
     <t xml:space="preserve">4.30186986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25201416015625</t>
+    <t xml:space="preserve">4.25201368331909</t>
   </si>
   <si>
     <t xml:space="preserve">4.26625823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27694225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20928049087524</t>
+    <t xml:space="preserve">4.27694177627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20928001403809</t>
   </si>
   <si>
     <t xml:space="preserve">4.19147443771362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21996307373047</t>
+    <t xml:space="preserve">4.21996355056763</t>
   </si>
   <si>
     <t xml:space="preserve">4.27160024642944</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">4.30899238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30543088912964</t>
+    <t xml:space="preserve">4.3054313659668</t>
   </si>
   <si>
     <t xml:space="preserve">4.39445972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40336322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47369575500488</t>
+    <t xml:space="preserve">4.40336275100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47369527816772</t>
   </si>
   <si>
     <t xml:space="preserve">4.49150133132935</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">4.46034145355225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43185186386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52266120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47814750671387</t>
+    <t xml:space="preserve">4.43185234069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5226616859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47814702987671</t>
   </si>
   <si>
     <t xml:space="preserve">4.56717586517334</t>
@@ -3944,22 +3944,22 @@
     <t xml:space="preserve">4.61169004440308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59833574295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55827236175537</t>
+    <t xml:space="preserve">4.5983362197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55827283859253</t>
   </si>
   <si>
     <t xml:space="preserve">4.58053016662598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56272411346436</t>
+    <t xml:space="preserve">4.56272459030151</t>
   </si>
   <si>
     <t xml:space="preserve">4.5849814414978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54046726226807</t>
+    <t xml:space="preserve">4.54046678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.51375865936279</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">4.6918158531189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74968481063843</t>
+    <t xml:space="preserve">4.74968433380127</t>
   </si>
   <si>
     <t xml:space="preserve">4.4692440032959</t>
@@ -3998,16 +3998,16 @@
     <t xml:space="preserve">4.44787693023682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57162714004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79419946670532</t>
+    <t xml:space="preserve">4.57162761688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79419898986816</t>
   </si>
   <si>
     <t xml:space="preserve">4.80310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8209080696106</t>
+    <t xml:space="preserve">4.82090759277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
@@ -4905,6 +4905,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.76000022888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76500034332275</t>
   </si>
 </sst>
 </file>
@@ -64497,7 +64500,7 @@
     </row>
     <row r="2280">
       <c r="A2280" s="1" t="n">
-        <v>45954.6494212963</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2280" t="n">
         <v>2381116</v>
@@ -64518,6 +64521,32 @@
         <v>1630</v>
       </c>
       <c r="H2280" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" s="1" t="n">
+        <v>45957.6909953704</v>
+      </c>
+      <c r="B2281" t="n">
+        <v>2631922</v>
+      </c>
+      <c r="C2281" t="n">
+        <v>8.83500003814697</v>
+      </c>
+      <c r="D2281" t="n">
+        <v>8.72999954223633</v>
+      </c>
+      <c r="E2281" t="n">
+        <v>8.72999954223633</v>
+      </c>
+      <c r="F2281" t="n">
+        <v>8.76500034332275</v>
+      </c>
+      <c r="G2281" t="s">
+        <v>1631</v>
+      </c>
+      <c r="H2281" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58873558044434</t>
+    <t xml:space="preserve">2.58873581886292</t>
   </si>
   <si>
     <t xml:space="preserve">IG.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">2.50135779380798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32790589332581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16488742828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17271184921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09315896034241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06185913085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08663821220398</t>
+    <t xml:space="preserve">2.32790565490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16488718986511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17271208763123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09315872192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06185936927795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0866379737854</t>
   </si>
   <si>
     <t xml:space="preserve">2.04490542411804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06055521965027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04360127449036</t>
+    <t xml:space="preserve">2.06055545806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04360151290894</t>
   </si>
   <si>
     <t xml:space="preserve">2.10489630699158</t>
@@ -80,49 +80,49 @@
     <t xml:space="preserve">2.12967538833618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14532518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17923259735107</t>
+    <t xml:space="preserve">2.14532494544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17923283576965</t>
   </si>
   <si>
     <t xml:space="preserve">2.2000994682312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20140337944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17792868614197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13228321075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09837532043457</t>
+    <t xml:space="preserve">2.20140314102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17792844772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13228344917297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09837579727173</t>
   </si>
   <si>
     <t xml:space="preserve">2.22357392311096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29138946533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33181834220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29791069030762</t>
+    <t xml:space="preserve">2.29138970375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33181810379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29791045188904</t>
   </si>
   <si>
     <t xml:space="preserve">2.23791933059692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30051898956299</t>
+    <t xml:space="preserve">2.30051851272583</t>
   </si>
   <si>
     <t xml:space="preserve">2.30443120002747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37094283103943</t>
+    <t xml:space="preserve">2.37094259262085</t>
   </si>
   <si>
     <t xml:space="preserve">2.3461639881134</t>
@@ -137,16 +137,16 @@
     <t xml:space="preserve">2.39702582359314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38007187843323</t>
+    <t xml:space="preserve">2.38007164001465</t>
   </si>
   <si>
     <t xml:space="preserve">2.39441728591919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42180442810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41006755828857</t>
+    <t xml:space="preserve">2.42180466651917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41006731987</t>
   </si>
   <si>
     <t xml:space="preserve">2.43093347549438</t>
@@ -158,40 +158,40 @@
     <t xml:space="preserve">2.48701190948486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45049548149109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4909245967865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4452793598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46614575386047</t>
+    <t xml:space="preserve">2.45049571990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49092435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44527912139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46614599227905</t>
   </si>
   <si>
     <t xml:space="preserve">2.43223786354065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44006276130676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47788286209106</t>
+    <t xml:space="preserve">2.44006252288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47788310050964</t>
   </si>
   <si>
     <t xml:space="preserve">2.43615031242371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43354201316833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45701670646667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48831605911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41789197921753</t>
+    <t xml:space="preserve">2.43354177474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4570164680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48831629753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41789221763611</t>
   </si>
   <si>
     <t xml:space="preserve">2.43484616279602</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">2.41267538070679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35659694671631</t>
+    <t xml:space="preserve">2.35659718513489</t>
   </si>
   <si>
     <t xml:space="preserve">2.27573990821838</t>
@@ -209,19 +209,19 @@
     <t xml:space="preserve">2.29530167579651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31225609779358</t>
+    <t xml:space="preserve">2.312255859375</t>
   </si>
   <si>
     <t xml:space="preserve">2.38137578964233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40876317024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39311337471008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44919180870056</t>
+    <t xml:space="preserve">2.40876340866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3931131362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44919157028198</t>
   </si>
   <si>
     <t xml:space="preserve">2.46744966506958</t>
@@ -233,46 +233,46 @@
     <t xml:space="preserve">2.48440384864807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46353721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47266697883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47136187553406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44788765907288</t>
+    <t xml:space="preserve">2.46353697776794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47266626358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47136235237122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44788789749146</t>
   </si>
   <si>
     <t xml:space="preserve">2.49614095687866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744534492493</t>
+    <t xml:space="preserve">2.49744510650635</t>
   </si>
   <si>
     <t xml:space="preserve">2.51570343971252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53135299682617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51439929008484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53657007217407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52744078636169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54830694198608</t>
+    <t xml:space="preserve">2.53135323524475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51439881324768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53656983375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52744054794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54830718040466</t>
   </si>
   <si>
     <t xml:space="preserve">2.55091500282288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5378737449646</t>
+    <t xml:space="preserve">2.53787350654602</t>
   </si>
   <si>
     <t xml:space="preserve">2.58612751960754</t>
@@ -281,40 +281,40 @@
     <t xml:space="preserve">2.57699823379517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59786510467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60438537597656</t>
+    <t xml:space="preserve">2.59786438941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60438561439514</t>
   </si>
   <si>
     <t xml:space="preserve">2.57308602333069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66959261894226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68393850326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6982843875885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64872646331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64742207527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68133044242859</t>
+    <t xml:space="preserve">2.66959285736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68393874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69828414916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64872622489929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64742231369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68132996559143</t>
   </si>
   <si>
     <t xml:space="preserve">2.67480969429016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63438081741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64350986480713</t>
+    <t xml:space="preserve">2.63438105583191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64351010322571</t>
   </si>
   <si>
     <t xml:space="preserve">2.69567561149597</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">2.69958829879761</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67872166633606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73479986190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.772620677948</t>
+    <t xml:space="preserve">2.67872190475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73480033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77262043952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.75436282157898</t>
@@ -341,22 +341,22 @@
     <t xml:space="preserve">2.70089244842529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7021963596344</t>
+    <t xml:space="preserve">2.70219683647156</t>
   </si>
   <si>
     <t xml:space="preserve">2.66176795959473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7830536365509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74523329734802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6930673122406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71915078163147</t>
+    <t xml:space="preserve">2.78305387496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74523377418518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69306778907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71915054321289</t>
   </si>
   <si>
     <t xml:space="preserve">2.70610904693604</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">2.77783751487732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83522009849548</t>
+    <t xml:space="preserve">2.83521962165833</t>
   </si>
   <si>
     <t xml:space="preserve">2.84043645858765</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88738584518433</t>
+    <t xml:space="preserve">2.88738536834717</t>
   </si>
   <si>
     <t xml:space="preserve">2.89651465415955</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">2.8534779548645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91477298736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00867176055908</t>
+    <t xml:space="preserve">2.91477251052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00867128372192</t>
   </si>
   <si>
     <t xml:space="preserve">3.02040886878967</t>
@@ -395,61 +395,61 @@
     <t xml:space="preserve">2.96824288368225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00736713409424</t>
+    <t xml:space="preserve">3.00736737251282</t>
   </si>
   <si>
     <t xml:space="preserve">3.05822944641113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09885382652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15591335296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09613704681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1382520198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0907027721405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9765841960907</t>
+    <t xml:space="preserve">3.09885358810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15591311454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09613680839539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13825178146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09070301055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97658467292786</t>
   </si>
   <si>
     <t xml:space="preserve">3.13417625427246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20074534416199</t>
+    <t xml:space="preserve">3.20074510574341</t>
   </si>
   <si>
     <t xml:space="preserve">3.24965310096741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28769254684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.230633020401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24557757377625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2224817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25101137161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18715977668762</t>
+    <t xml:space="preserve">3.28769302368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23063349723816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24557781219482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22248220443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25101161003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18715953826904</t>
   </si>
   <si>
     <t xml:space="preserve">3.09477853775024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11379814147949</t>
+    <t xml:space="preserve">3.11379837989807</t>
   </si>
   <si>
     <t xml:space="preserve">3.19938707351685</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">3.10428833961487</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12059044837952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15727162361145</t>
+    <t xml:space="preserve">3.12059092521667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15727186203003</t>
   </si>
   <si>
     <t xml:space="preserve">3.16270589828491</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">3.0282096862793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96707487106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00375580787659</t>
+    <t xml:space="preserve">2.96707439422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00375533103943</t>
   </si>
   <si>
     <t xml:space="preserve">3.03636050224304</t>
@@ -497,13 +497,13 @@
     <t xml:space="preserve">2.99560403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07575869560242</t>
+    <t xml:space="preserve">3.07575845718384</t>
   </si>
   <si>
     <t xml:space="preserve">3.08390998840332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12466645240784</t>
+    <t xml:space="preserve">3.12466621398926</t>
   </si>
   <si>
     <t xml:space="preserve">3.10836410522461</t>
@@ -512,37 +512,37 @@
     <t xml:space="preserve">3.128741979599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17900848388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17221617698669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12602496147156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15862989425659</t>
+    <t xml:space="preserve">3.1790087223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17221570014954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12602519989014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15863037109375</t>
   </si>
   <si>
     <t xml:space="preserve">3.22519946098328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26052188873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25237011909485</t>
+    <t xml:space="preserve">3.26052165031433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25237059593201</t>
   </si>
   <si>
     <t xml:space="preserve">3.27682399749756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30671262741089</t>
+    <t xml:space="preserve">3.30671215057373</t>
   </si>
   <si>
     <t xml:space="preserve">3.30263686180115</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28090000152588</t>
+    <t xml:space="preserve">3.2808997631073</t>
   </si>
   <si>
     <t xml:space="preserve">3.21025490760803</t>
@@ -551,145 +551,145 @@
     <t xml:space="preserve">3.2836172580719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29856133460999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28225827217102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26323843002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25644612312317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27003145217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24693655967712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23335099220276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21976518630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24150156974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26188015937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2347092628479</t>
+    <t xml:space="preserve">3.29856085777283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28225898742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26323866844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25644588470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27003121376038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24693608283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23335075378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21976494789124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24150204658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26188039779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23470878601074</t>
   </si>
   <si>
     <t xml:space="preserve">3.19802832603455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23742604255676</t>
+    <t xml:space="preserve">3.23742580413818</t>
   </si>
   <si>
     <t xml:space="preserve">3.24829459190369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22791624069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1939525604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16542291641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18444299697876</t>
+    <t xml:space="preserve">3.22791647911072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19395279884338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16542267799377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18444323539734</t>
   </si>
   <si>
     <t xml:space="preserve">3.18172550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20753812789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24014329910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26731419563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2428605556488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22655749320984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23199200630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20617914199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14640331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16814041137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157108306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678166389465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21704816818237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22927522659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24421906471252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21433019638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25372886657715</t>
+    <t xml:space="preserve">3.20753788948059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2401430606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26731443405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24286079406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22655773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23199224472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20617961883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14640307426453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16813993453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157084465027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678190231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21704769134521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22927498817444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24421882629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21433067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25372862815857</t>
   </si>
   <si>
     <t xml:space="preserve">3.35154461860657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49147510528564</t>
+    <t xml:space="preserve">3.49147534370422</t>
   </si>
   <si>
     <t xml:space="preserve">3.39365911483765</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46430397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50506019592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41675496101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40656590461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44732189178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43373680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42694449424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47109699249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46770095825195</t>
+    <t xml:space="preserve">3.46430420875549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50506091117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41675519943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40656542778015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44732236862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43373656272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4269437789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4710967540741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46770071983337</t>
   </si>
   <si>
     <t xml:space="preserve">3.481285572052</t>
@@ -698,118 +698,118 @@
     <t xml:space="preserve">3.50166463851929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5424211025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51185321807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54581737518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55940270423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412308692932</t>
+    <t xml:space="preserve">3.54242062568665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51185369491577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54581761360168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55940246582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6341233253479</t>
   </si>
   <si>
     <t xml:space="preserve">3.60015940666199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53223156929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48468232154846</t>
+    <t xml:space="preserve">3.53223133087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48468255996704</t>
   </si>
   <si>
     <t xml:space="preserve">3.55260968208313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61374521255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52543902397156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58997011184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60355567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5933666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62053728103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59676265716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56619548797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562831878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45411562919617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45751094818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39637684822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3230152130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38279151916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40996265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38958311080933</t>
+    <t xml:space="preserve">3.61374473571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52543926239014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58996987342834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60355544090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59336638450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62053751945496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59676289558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56619596481323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53562808036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45411491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45751166343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3963770866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32301545143127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3827908039093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40996193885803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38958334922791</t>
   </si>
   <si>
     <t xml:space="preserve">3.32844924926758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30807065963745</t>
+    <t xml:space="preserve">3.30807089805603</t>
   </si>
   <si>
     <t xml:space="preserve">3.31078791618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35018634796143</t>
+    <t xml:space="preserve">3.35018610954285</t>
   </si>
   <si>
     <t xml:space="preserve">3.37599849700928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35426211357117</t>
+    <t xml:space="preserve">3.35426187515259</t>
   </si>
   <si>
     <t xml:space="preserve">3.37328124046326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34339332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36648845672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37871551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36105442047119</t>
+    <t xml:space="preserve">3.34339284896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36648869514465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37871527671814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36105465888977</t>
   </si>
   <si>
     <t xml:space="preserve">3.12127017974854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16406488418579</t>
+    <t xml:space="preserve">3.16406464576721</t>
   </si>
   <si>
     <t xml:space="preserve">3.06624889373779</t>
@@ -818,16 +818,16 @@
     <t xml:space="preserve">3.04587078094482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03228545188904</t>
+    <t xml:space="preserve">3.03228521347046</t>
   </si>
   <si>
     <t xml:space="preserve">3.00239682197571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02209568023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02549266815186</t>
+    <t xml:space="preserve">3.02209615707397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02549195289612</t>
   </si>
   <si>
     <t xml:space="preserve">3.04655003547668</t>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">2.9942455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96164035797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97862219810486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092622756958</t>
+    <t xml:space="preserve">2.96164083480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97862243652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">3.11651515960693</t>
@@ -851,10 +851,10 @@
     <t xml:space="preserve">3.06828713417053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00035905838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96639561653137</t>
+    <t xml:space="preserve">3.00035929679871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96639537811279</t>
   </si>
   <si>
     <t xml:space="preserve">2.92903518676758</t>
@@ -863,154 +863,154 @@
     <t xml:space="preserve">2.924959897995</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01326560974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09409856796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14300656318665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23538851737976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22723722457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21297240257263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19327354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27342748641968</t>
+    <t xml:space="preserve">3.01326513290405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09409880638123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14300680160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23538875579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22723698616028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21297216415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19327306747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27342772483826</t>
   </si>
   <si>
     <t xml:space="preserve">3.29448556900024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20414161682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30739164352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28565406799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36377191543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39909410476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47924828529358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47517228126526</t>
+    <t xml:space="preserve">3.20414185523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30739188194275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2856547832489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36377143859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39909362792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47924852371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47517251968384</t>
   </si>
   <si>
     <t xml:space="preserve">3.48196530342102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4371325969696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4439263343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49962663650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52815580368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47789001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51457071304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45887017250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52679753303528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52000451087952</t>
+    <t xml:space="preserve">3.43713355064392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44392609596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49962687492371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.528156042099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47788953781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51457023620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45886993408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5267972946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5200047492981</t>
   </si>
   <si>
     <t xml:space="preserve">3.57570576667786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62733030319214</t>
+    <t xml:space="preserve">3.6273307800293</t>
   </si>
   <si>
     <t xml:space="preserve">3.64499163627625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60423517227173</t>
+    <t xml:space="preserve">3.60423445701599</t>
   </si>
   <si>
     <t xml:space="preserve">3.60287618637085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62597155570984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49419260025024</t>
+    <t xml:space="preserve">3.62597107887268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49419236183167</t>
   </si>
   <si>
     <t xml:space="preserve">3.45615243911743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41539621353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45479440689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44256734848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36309242248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39298009872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39461970329285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45400142669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4610698223114</t>
+    <t xml:space="preserve">3.41539597511292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45479416847229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4425675868988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36309218406677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39298057556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39461994171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45400094985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46106958389282</t>
   </si>
   <si>
     <t xml:space="preserve">3.36280846595764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28151273727417</t>
+    <t xml:space="preserve">3.28151321411133</t>
   </si>
   <si>
     <t xml:space="preserve">3.23414921760559</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07367920875549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16699171066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15285396575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18961381912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27868485450745</t>
+    <t xml:space="preserve">3.07367873191833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16699194908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1528537273407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18961358070374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2786853313446</t>
   </si>
   <si>
     <t xml:space="preserve">3.25747752189636</t>
@@ -1025,16 +1025,16 @@
     <t xml:space="preserve">3.20163106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34089350700378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43774151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39037799835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4108784198761</t>
+    <t xml:space="preserve">3.34089374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43774199485779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39037823677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41087889671326</t>
   </si>
   <si>
     <t xml:space="preserve">3.37623977661133</t>
@@ -1043,22 +1043,22 @@
     <t xml:space="preserve">3.38967132568359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40946483612061</t>
+    <t xml:space="preserve">3.40946507453918</t>
   </si>
   <si>
     <t xml:space="preserve">3.46319079399109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33735990524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3154444694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29989266395569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34442830085754</t>
+    <t xml:space="preserve">3.33735942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31544494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29989242553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34442853927612</t>
   </si>
   <si>
     <t xml:space="preserve">3.35432553291321</t>
@@ -1067,25 +1067,25 @@
     <t xml:space="preserve">3.32958340644836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3380663394928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29211664199829</t>
+    <t xml:space="preserve">3.33806610107422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29211640357971</t>
   </si>
   <si>
     <t xml:space="preserve">3.35644626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35220432281494</t>
+    <t xml:space="preserve">3.3522047996521</t>
   </si>
   <si>
     <t xml:space="preserve">3.40098190307617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41865468025208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3776535987854</t>
+    <t xml:space="preserve">3.41865491867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37765407562256</t>
   </si>
   <si>
     <t xml:space="preserve">3.32534170150757</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">3.3557391166687</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34230804443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40027475357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45258665084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44834518432617</t>
+    <t xml:space="preserve">3.34230780601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40027499198914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45258712768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44834542274475</t>
   </si>
   <si>
     <t xml:space="preserve">3.44268989562988</t>
@@ -1115,34 +1115,34 @@
     <t xml:space="preserve">3.41229271888733</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40734457969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46036314964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4313793182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47874283790588</t>
+    <t xml:space="preserve">3.4073441028595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46036267280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43137955665588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4787425994873</t>
   </si>
   <si>
     <t xml:space="preserve">3.42077565193176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42572426795959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51479578018188</t>
+    <t xml:space="preserve">3.42572402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51479554176331</t>
   </si>
   <si>
     <t xml:space="preserve">3.4942946434021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39532685279846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41582703590393</t>
+    <t xml:space="preserve">3.3953263759613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41582751274109</t>
   </si>
   <si>
     <t xml:space="preserve">3.42925834655762</t>
@@ -1157,94 +1157,94 @@
     <t xml:space="preserve">3.3882577419281</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43279361724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33594536781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29706525802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30413460731506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30837559700012</t>
+    <t xml:space="preserve">3.43279337882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33594512939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29706501960754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30413413047791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3083758354187</t>
   </si>
   <si>
     <t xml:space="preserve">3.2878749370575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31615138053894</t>
+    <t xml:space="preserve">3.3161518573761</t>
   </si>
   <si>
     <t xml:space="preserve">3.25182223320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28999543190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33311820030212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33099699020386</t>
+    <t xml:space="preserve">3.28999519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33311772346497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33099675178528</t>
   </si>
   <si>
     <t xml:space="preserve">3.333824634552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32675552368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34654951095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47450137138367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49924373626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49641633033752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46248388290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45682811737061</t>
+    <t xml:space="preserve">3.32675576210022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34654998779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47450160980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49924325942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49641585350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46248364448547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45682835578918</t>
   </si>
   <si>
     <t xml:space="preserve">3.45470809936523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38613677024841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45753526687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45894932746887</t>
+    <t xml:space="preserve">3.38613653182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45753502845764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45894980430603</t>
   </si>
   <si>
     <t xml:space="preserve">3.37411856651306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39391255378723</t>
+    <t xml:space="preserve">3.39391303062439</t>
   </si>
   <si>
     <t xml:space="preserve">3.42006850242615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30978965759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32816934585571</t>
+    <t xml:space="preserve">3.30978918075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32816910743713</t>
   </si>
   <si>
     <t xml:space="preserve">3.35715317726135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27797794342041</t>
+    <t xml:space="preserve">3.27797842025757</t>
   </si>
   <si>
     <t xml:space="preserve">3.24899458885193</t>
@@ -1253,46 +1253,46 @@
     <t xml:space="preserve">3.21011400222778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23485636711121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20516562461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15780210494995</t>
+    <t xml:space="preserve">3.23485612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20516538619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15780234336853</t>
   </si>
   <si>
     <t xml:space="preserve">3.13093900680542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15356063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24545979499817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16911244392395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19809675216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18890690803528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23909759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23344206809998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27727150917053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23202848434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22920060157776</t>
+    <t xml:space="preserve">3.15356087684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24546003341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16911268234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19809651374817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1889066696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23909783363342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23344230651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27727103233337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23202872276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22920083999634</t>
   </si>
   <si>
     <t xml:space="preserve">3.22495913505554</t>
@@ -1301,151 +1301,151 @@
     <t xml:space="preserve">3.27232313156128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31473827362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3734118938446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42501735687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43491435050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48863959312439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44693112373352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38755059242249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35927367210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34160161018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30059957504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3048415184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27585768699646</t>
+    <t xml:space="preserve">3.31473851203918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37341213226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42501640319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43491387367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48863983154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44693160057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38755035400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35927391052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34160137176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3005998134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30484104156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27585744857788</t>
   </si>
   <si>
     <t xml:space="preserve">3.39603328704834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34937644004822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36068797111511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36704993247986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39179158210754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4165346622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45329403877258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52327847480774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59114265441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61235046386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073015213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61093688011169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62790250778198</t>
+    <t xml:space="preserve">3.3493766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36068773269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36705017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39179182052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41653442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.453293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52327919006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59114289283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61234998703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073039054871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61093664169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6279022693634</t>
   </si>
   <si>
     <t xml:space="preserve">3.60103964805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59962606430054</t>
+    <t xml:space="preserve">3.59962582588196</t>
   </si>
   <si>
     <t xml:space="preserve">3.51055407524109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53176116943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57841777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61941981315613</t>
+    <t xml:space="preserve">3.53176164627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57841825485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61941957473755</t>
   </si>
   <si>
     <t xml:space="preserve">3.6491105556488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6788010597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62083339691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68586993217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70849084854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6533522605896</t>
+    <t xml:space="preserve">3.67880082130432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62083387374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68587017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70849108695984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65335178375244</t>
   </si>
   <si>
     <t xml:space="preserve">3.68304204940796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68728399276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67738699913025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71414637565613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71131896972656</t>
+    <t xml:space="preserve">3.6872832775116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67738676071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71414709091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71131920814514</t>
   </si>
   <si>
     <t xml:space="preserve">3.70990490913391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72545766830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73252654075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73111248016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6717312335968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69293880462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71980166435242</t>
+    <t xml:space="preserve">3.72545695304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7325267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.731112241745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67173147201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69293928146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71980142593384</t>
   </si>
   <si>
     <t xml:space="preserve">3.63779926300049</t>
@@ -1454,109 +1454,109 @@
     <t xml:space="preserve">3.61517786979675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68869757652283</t>
+    <t xml:space="preserve">3.68869709968567</t>
   </si>
   <si>
     <t xml:space="preserve">3.69576692581177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6943531036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69718027114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68162822723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75232028961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7438371181488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72262954711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76504468917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7593891620636</t>
+    <t xml:space="preserve">3.69435238838196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69718050956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68162846565247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75232005119324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74383735656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72262907028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76504516601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75938940048218</t>
   </si>
   <si>
     <t xml:space="preserve">3.71697425842285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78342461585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83997774124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86542725563049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83573698997498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8244252204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79756355285645</t>
+    <t xml:space="preserve">3.78342437744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83997845649719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86542701721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8357367515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82442593574524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79756307601929</t>
   </si>
   <si>
     <t xml:space="preserve">3.81735634803772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85977125167847</t>
+    <t xml:space="preserve">3.8597719669342</t>
   </si>
   <si>
     <t xml:space="preserve">3.86966848373413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88380718231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87532353401184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89370369911194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88804817199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85270214080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8710823059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89087605476379</t>
+    <t xml:space="preserve">3.88380670547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.875324010849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89370346069336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88804841041565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85270190238953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87108182907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89087629318237</t>
   </si>
   <si>
     <t xml:space="preserve">3.84139204025269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88239288330078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92339396476746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88946199417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90360069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92056679725647</t>
+    <t xml:space="preserve">3.88239312171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92339444160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88946223258972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90359997749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92056703567505</t>
   </si>
   <si>
     <t xml:space="preserve">3.9191529750824</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96439576148987</t>
+    <t xml:space="preserve">3.96439552307129</t>
   </si>
   <si>
     <t xml:space="preserve">3.95732593536377</t>
@@ -1565,49 +1565,49 @@
     <t xml:space="preserve">3.91066956520081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9332914352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90642809867859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90501427650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92198061943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91208410263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93046379089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87956547737122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89794540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88097929954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94743013381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89228987693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87390995025635</t>
+    <t xml:space="preserve">3.93329167366028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90642881393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9050145149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92198038101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91208338737488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93046355247498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87956571578979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89794516563416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88097882270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94742941856384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89228963851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87390971183777</t>
   </si>
   <si>
     <t xml:space="preserve">3.90925574302673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95025706291199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98136115074158</t>
+    <t xml:space="preserve">3.95025682449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98136162757874</t>
   </si>
   <si>
     <t xml:space="preserve">4.00963830947876</t>
@@ -1616,25 +1616,25 @@
     <t xml:space="preserve">4.08032989501953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07891654968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13016366958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16984796524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21100234985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.213942527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24921846389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20512342453003</t>
+    <t xml:space="preserve">4.07891607284546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13016319274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16984844207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21100330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21394300460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24921798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20512390136719</t>
   </si>
   <si>
     <t xml:space="preserve">4.19483518600464</t>
@@ -1643,52 +1643,52 @@
     <t xml:space="preserve">4.12281465530396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1081166267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16543865203857</t>
+    <t xml:space="preserve">4.10811614990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16543912887573</t>
   </si>
   <si>
     <t xml:space="preserve">4.21541261672974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26979541778564</t>
+    <t xml:space="preserve">4.26979494094849</t>
   </si>
   <si>
     <t xml:space="preserve">4.3050708770752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32123899459839</t>
+    <t xml:space="preserve">4.32123851776123</t>
   </si>
   <si>
     <t xml:space="preserve">4.36827230453491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33152723312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32564830780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28890323638916</t>
+    <t xml:space="preserve">4.33152770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32564783096313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28890228271484</t>
   </si>
   <si>
     <t xml:space="preserve">4.35651397705078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34328508377075</t>
+    <t xml:space="preserve">4.34328556060791</t>
   </si>
   <si>
     <t xml:space="preserve">4.49908542633057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44764232635498</t>
+    <t xml:space="preserve">4.44764184951782</t>
   </si>
   <si>
     <t xml:space="preserve">4.4461727142334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48291826248169</t>
+    <t xml:space="preserve">4.48291730880737</t>
   </si>
   <si>
     <t xml:space="preserve">4.48732709884644</t>
@@ -1697,22 +1697,22 @@
     <t xml:space="preserve">4.45352125167847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43735408782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35210371017456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34181594848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33446645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43147468566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47997760772705</t>
+    <t xml:space="preserve">4.43735361099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35210466384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34181547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3344669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43147373199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47997856140137</t>
   </si>
   <si>
     <t xml:space="preserve">4.44911193847656</t>
@@ -1721,52 +1721,52 @@
     <t xml:space="preserve">4.43882322311401</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49467658996582</t>
+    <t xml:space="preserve">4.49467611312866</t>
   </si>
   <si>
     <t xml:space="preserve">4.51966285705566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50349521636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54318046569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56228733062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57698535919189</t>
+    <t xml:space="preserve">4.50349473953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54317951202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5622878074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57698583602905</t>
   </si>
   <si>
     <t xml:space="preserve">4.52701139450073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54170942306519</t>
+    <t xml:space="preserve">4.54170989990234</t>
   </si>
   <si>
     <t xml:space="preserve">4.54905891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40207767486572</t>
+    <t xml:space="preserve">4.40207815170288</t>
   </si>
   <si>
     <t xml:space="preserve">4.43588352203369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4255952835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38884973526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38150072097778</t>
+    <t xml:space="preserve">4.42559480667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38885021209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38150024414062</t>
   </si>
   <si>
     <t xml:space="preserve">4.24480867385864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20218420028687</t>
+    <t xml:space="preserve">4.20218372344971</t>
   </si>
   <si>
     <t xml:space="preserve">4.29037237167358</t>
@@ -1781,49 +1781,49 @@
     <t xml:space="preserve">4.26097631454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28449392318726</t>
+    <t xml:space="preserve">4.2844934463501</t>
   </si>
   <si>
     <t xml:space="preserve">4.28743314743042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11399507522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16102981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24186897277832</t>
+    <t xml:space="preserve">4.11399555206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16102933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24186849594116</t>
   </si>
   <si>
     <t xml:space="preserve">4.15661954879761</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3036003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2183518409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20071458816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1977744102478</t>
+    <t xml:space="preserve">4.30360078811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21835231781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20071411132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19777393341064</t>
   </si>
   <si>
     <t xml:space="preserve">4.34034585952759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33593654632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34916543960571</t>
+    <t xml:space="preserve">4.33593702316284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34916496276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.313889503479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30213165283203</t>
+    <t xml:space="preserve">4.30213117599487</t>
   </si>
   <si>
     <t xml:space="preserve">4.20806312561035</t>
@@ -1835,7 +1835,7 @@
     <t xml:space="preserve">4.1037073135376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18307685852051</t>
+    <t xml:space="preserve">4.18307638168335</t>
   </si>
   <si>
     <t xml:space="preserve">4.14045190811157</t>
@@ -1847,13 +1847,13 @@
     <t xml:space="preserve">4.19336557388306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18160724639893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18454647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25215768814087</t>
+    <t xml:space="preserve">4.18160629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18454599380493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25215721130371</t>
   </si>
   <si>
     <t xml:space="preserve">4.29919099807739</t>
@@ -1868,19 +1868,19 @@
     <t xml:space="preserve">4.30066108703613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21247291564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31241941452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36974191665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24774885177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18895530700684</t>
+    <t xml:space="preserve">4.21247243881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31241989135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36974239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24774789810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18895578384399</t>
   </si>
   <si>
     <t xml:space="preserve">4.23011064529419</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">4.1683783531189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18013668060303</t>
+    <t xml:space="preserve">4.18013715744019</t>
   </si>
   <si>
     <t xml:space="preserve">4.238929271698</t>
@@ -1910,13 +1910,13 @@
     <t xml:space="preserve">4.25362777709961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29478120803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33740615844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35063457489014</t>
+    <t xml:space="preserve">4.29478168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33740663528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35063505172729</t>
   </si>
   <si>
     <t xml:space="preserve">4.28302335739136</t>
@@ -1928,10 +1928,10 @@
     <t xml:space="preserve">4.30654096603394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37268161773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39178943634033</t>
+    <t xml:space="preserve">4.37268209457397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39178895950317</t>
   </si>
   <si>
     <t xml:space="preserve">4.27861404418945</t>
@@ -1940,19 +1940,19 @@
     <t xml:space="preserve">4.22423124313354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23745918273926</t>
+    <t xml:space="preserve">4.23745965957642</t>
   </si>
   <si>
     <t xml:space="preserve">4.22570037841797</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19189548492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22129154205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23598957061768</t>
+    <t xml:space="preserve">4.19189596176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22129106521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23599004745483</t>
   </si>
   <si>
     <t xml:space="preserve">4.22717046737671</t>
@@ -1967,31 +1967,31 @@
     <t xml:space="preserve">4.08900880813599</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04932403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01992750167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95378589630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99494099617004</t>
+    <t xml:space="preserve">4.04932451248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01992702484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95378637313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99494051933289</t>
   </si>
   <si>
     <t xml:space="preserve">4.04197454452515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99053144454956</t>
+    <t xml:space="preserve">3.99053120613098</t>
   </si>
   <si>
     <t xml:space="preserve">4.03609561920166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10664653778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16396951675415</t>
+    <t xml:space="preserve">4.1066460609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16396903991699</t>
   </si>
   <si>
     <t xml:space="preserve">4.12722396850586</t>
@@ -2009,37 +2009,37 @@
     <t xml:space="preserve">4.08459901809692</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02727651596069</t>
+    <t xml:space="preserve">4.02727699279785</t>
   </si>
   <si>
     <t xml:space="preserve">4.02286720275879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10076665878296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20365381240845</t>
+    <t xml:space="preserve">4.10076761245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20365333557129</t>
   </si>
   <si>
     <t xml:space="preserve">4.13898229598999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25068807601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20659303665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26391553878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30801057815552</t>
+    <t xml:space="preserve">4.25068759918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20659351348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.263916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30801010131836</t>
   </si>
   <si>
     <t xml:space="preserve">4.48144769668579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5152530670166</t>
+    <t xml:space="preserve">4.51525354385376</t>
   </si>
   <si>
     <t xml:space="preserve">4.49761533737183</t>
@@ -2048,19 +2048,19 @@
     <t xml:space="preserve">4.40648698806763</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41677665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46674966812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4917368888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46087026596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46233987808228</t>
+    <t xml:space="preserve">4.41677618026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4667501449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49173641204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46087074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46234035491943</t>
   </si>
   <si>
     <t xml:space="preserve">4.51231384277344</t>
@@ -2069,52 +2069,52 @@
     <t xml:space="preserve">4.45205163955688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48585748672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62548875808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26538610458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26244640350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06549167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08606958389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72890543937683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51798844337463</t>
+    <t xml:space="preserve">4.4858570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62548923492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26538562774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26244688034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06549215316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08606910705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72890496253967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51798796653748</t>
   </si>
   <si>
     <t xml:space="preserve">3.50181984901428</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02192711830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24754333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15127062797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27032470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29531216621399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35189914703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21153259277344</t>
+    <t xml:space="preserve">3.02192735671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24754309654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15127086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27032494544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29531192779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35189938545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21153283119202</t>
   </si>
   <si>
     <t xml:space="preserve">3.129958152771</t>
@@ -2129,136 +2129,136 @@
     <t xml:space="preserve">3.34381580352783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35924863815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57090163230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66643834114075</t>
+    <t xml:space="preserve">3.35924887657166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57090139389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66643857955933</t>
   </si>
   <si>
     <t xml:space="preserve">3.44964170455933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55693769454956</t>
+    <t xml:space="preserve">3.55693793296814</t>
   </si>
   <si>
     <t xml:space="preserve">3.58780360221863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53636026382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54958891868591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46580958366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54811906814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56428694725037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368276596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62601900100708</t>
+    <t xml:space="preserve">3.53636050224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54958844184875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46580934524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54811859130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56428670883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368300437927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62601947784424</t>
   </si>
   <si>
     <t xml:space="preserve">3.57163596153259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57310581207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44082307815552</t>
+    <t xml:space="preserve">3.57310557365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44082260131836</t>
   </si>
   <si>
     <t xml:space="preserve">3.61720013618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52754187583923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57457518577576</t>
+    <t xml:space="preserve">3.52754163742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57457542419434</t>
   </si>
   <si>
     <t xml:space="preserve">3.56722640991211</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57898473739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75168800354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68187165260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70391845703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60691118240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61279082298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66423392295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63189744949341</t>
+    <t xml:space="preserve">3.57898497581482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75168752670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68187212944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70391917228699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60691142082214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61279058456421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66423416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63189816474915</t>
   </si>
   <si>
     <t xml:space="preserve">3.6245493888855</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63777756690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6230788230896</t>
+    <t xml:space="preserve">3.63777732849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62307858467102</t>
   </si>
   <si>
     <t xml:space="preserve">3.71126794815063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73626303672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60662770271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66372895240784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63440656661987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68533492088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75015187263489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73008942604065</t>
+    <t xml:space="preserve">3.73626279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60662746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66372919082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63440680503845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68533444404602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75015211105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73008966445923</t>
   </si>
   <si>
     <t xml:space="preserve">3.70231056213379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80725336074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77021503448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81959939002991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90447902679443</t>
+    <t xml:space="preserve">3.80725359916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77021455764771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81959915161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90447926521301</t>
   </si>
   <si>
     <t xml:space="preserve">3.99707555770874</t>
@@ -2270,13 +2270,13 @@
     <t xml:space="preserve">4.02408313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92762851715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8813304901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81651282310486</t>
+    <t xml:space="preserve">3.9276282787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88133025169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81651306152344</t>
   </si>
   <si>
     <t xml:space="preserve">3.91991209983826</t>
@@ -2285,46 +2285,46 @@
     <t xml:space="preserve">4.08581399917603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05880689620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10896253585815</t>
+    <t xml:space="preserve">4.05880641937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10896301269531</t>
   </si>
   <si>
     <t xml:space="preserve">4.14754486083984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02022457122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96621012687683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98935914039612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03565740585327</t>
+    <t xml:space="preserve">4.02022504806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96621036529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98935985565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03565788269043</t>
   </si>
   <si>
     <t xml:space="preserve">4.08967208862305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03179931640625</t>
+    <t xml:space="preserve">4.03179883956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.07038164138794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11282157897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0549488067627</t>
+    <t xml:space="preserve">4.11282110214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05494832992554</t>
   </si>
   <si>
     <t xml:space="preserve">3.95463585853577</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96235227584839</t>
+    <t xml:space="preserve">3.96235203742981</t>
   </si>
   <si>
     <t xml:space="preserve">3.93534445762634</t>
@@ -2336,25 +2336,25 @@
     <t xml:space="preserve">3.97392654418945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0742392539978</t>
+    <t xml:space="preserve">4.07423877716064</t>
   </si>
   <si>
     <t xml:space="preserve">4.1243953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10510492324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09353017807007</t>
+    <t xml:space="preserve">4.10510444641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09353065490723</t>
   </si>
   <si>
     <t xml:space="preserve">4.04723215103149</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12825393676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25943183898926</t>
+    <t xml:space="preserve">4.12825345993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25943231582642</t>
   </si>
   <si>
     <t xml:space="preserve">4.26714849472046</t>
@@ -2366,34 +2366,34 @@
     <t xml:space="preserve">4.19770097732544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16297769546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16683530807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470855712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28643941879272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36746120452881</t>
+    <t xml:space="preserve">4.16297721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16683578491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470808029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28643894195557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36746025085449</t>
   </si>
   <si>
     <t xml:space="preserve">4.42147588729858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39061069488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36360311508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30572986602783</t>
+    <t xml:space="preserve">4.39060974121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37517738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36360359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30573034286499</t>
   </si>
   <si>
     <t xml:space="preserve">4.26329040527344</t>
@@ -2405,28 +2405,28 @@
     <t xml:space="preserve">4.31344652175903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30187177658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13597011566162</t>
+    <t xml:space="preserve">4.30187129974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13597059249878</t>
   </si>
   <si>
     <t xml:space="preserve">4.22856664657593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18612670898438</t>
+    <t xml:space="preserve">4.18612623214722</t>
   </si>
   <si>
     <t xml:space="preserve">4.17455196380615</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1899847984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11667966842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17840957641602</t>
+    <t xml:space="preserve">4.18998432159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11667919158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17841005325317</t>
   </si>
   <si>
     <t xml:space="preserve">4.15526103973389</t>
@@ -2441,52 +2441,52 @@
     <t xml:space="preserve">4.19384288787842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07809734344482</t>
+    <t xml:space="preserve">4.07809782028198</t>
   </si>
   <si>
     <t xml:space="preserve">3.89290475845337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97778487205505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06266403198242</t>
+    <t xml:space="preserve">3.97778534889221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06266450881958</t>
   </si>
   <si>
     <t xml:space="preserve">3.94691872596741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98550081253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98164296150208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88904643058777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71157026290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72700309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82885885238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83194494247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86589741706848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00479173660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95077753067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.081955909729</t>
+    <t xml:space="preserve">3.9855010509491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9816427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88904690742493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71157002449036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72700262069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8288586139679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83194541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86589789390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00479221343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95077705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08195543289185</t>
   </si>
   <si>
     <t xml:space="preserve">4.03951549530029</t>
@@ -2501,34 +2501,34 @@
     <t xml:space="preserve">4.14368629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1321120262146</t>
+    <t xml:space="preserve">4.13211154937744</t>
   </si>
   <si>
     <t xml:space="preserve">3.93920278549194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90062069892883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80879640579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9932177066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01250839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95849394798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87747263908386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93148589134216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92377066612244</t>
+    <t xml:space="preserve">3.90062093734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80879592895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99321722984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01250886917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95849370956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87747240066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9314866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9237699508667</t>
   </si>
   <si>
     <t xml:space="preserve">3.86203932762146</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">3.8180558681488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80571031570435</t>
+    <t xml:space="preserve">3.80571007728577</t>
   </si>
   <si>
     <t xml:space="preserve">3.85818099975586</t>
@@ -2555,34 +2555,34 @@
     <t xml:space="preserve">3.83811855316162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94306111335754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90833735466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88518834114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83503198623657</t>
+    <t xml:space="preserve">3.94306135177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90833711624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88518810272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83503150939941</t>
   </si>
   <si>
     <t xml:space="preserve">3.76712775230408</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76249837875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8226854801178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79799342155457</t>
+    <t xml:space="preserve">3.76249814033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82268571853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79799365997314</t>
   </si>
   <si>
     <t xml:space="preserve">3.87361359596252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02794075012207</t>
+    <t xml:space="preserve">4.02794122695923</t>
   </si>
   <si>
     <t xml:space="preserve">4.04337406158447</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">4.31730461120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27100610733032</t>
+    <t xml:space="preserve">4.27100658416748</t>
   </si>
   <si>
     <t xml:space="preserve">4.26251840591431</t>
@@ -2612,19 +2612,19 @@
     <t xml:space="preserve">4.25634527206421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24554252624512</t>
+    <t xml:space="preserve">4.24554300308228</t>
   </si>
   <si>
     <t xml:space="preserve">4.14985942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12979745864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14059972763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12362337112427</t>
+    <t xml:space="preserve">4.12979698181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14060068130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12362384796143</t>
   </si>
   <si>
     <t xml:space="preserve">4.16837882995605</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">4.17146492004395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19924449920654</t>
+    <t xml:space="preserve">4.19924402236938</t>
   </si>
   <si>
     <t xml:space="preserve">4.23628282546997</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">4.17918157577515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1838116645813</t>
+    <t xml:space="preserve">4.18381118774414</t>
   </si>
   <si>
     <t xml:space="preserve">4.20387411117554</t>
@@ -2657,31 +2657,31 @@
     <t xml:space="preserve">4.18535470962524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21622085571289</t>
+    <t xml:space="preserve">4.21622037887573</t>
   </si>
   <si>
     <t xml:space="preserve">4.29338407516479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23165369033813</t>
+    <t xml:space="preserve">4.23165273666382</t>
   </si>
   <si>
     <t xml:space="preserve">4.25017261505127</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23782587051392</t>
+    <t xml:space="preserve">4.23782634735107</t>
   </si>
   <si>
     <t xml:space="preserve">4.35048484802246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34122562408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39369678497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47086048126221</t>
+    <t xml:space="preserve">4.34122514724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39369630813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47086000442505</t>
   </si>
   <si>
     <t xml:space="preserve">4.46610307693481</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">4.35622835159302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38531303405762</t>
+    <t xml:space="preserve">4.38531255722046</t>
   </si>
   <si>
     <t xml:space="preserve">4.37400197982788</t>
@@ -2705,22 +2705,22 @@
     <t xml:space="preserve">4.39016008377075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37723350524902</t>
+    <t xml:space="preserve">4.37723398208618</t>
   </si>
   <si>
     <t xml:space="preserve">4.40147066116333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45156145095825</t>
+    <t xml:space="preserve">4.45156097412109</t>
   </si>
   <si>
     <t xml:space="preserve">4.47418212890625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49357175827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50165128707886</t>
+    <t xml:space="preserve">4.49357128143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5016508102417</t>
   </si>
   <si>
     <t xml:space="preserve">4.52911996841431</t>
@@ -2732,13 +2732,13 @@
     <t xml:space="preserve">4.55012512207031</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62122106552124</t>
+    <t xml:space="preserve">4.6212215423584</t>
   </si>
   <si>
     <t xml:space="preserve">4.58405733108521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56628322601318</t>
+    <t xml:space="preserve">4.56628370285034</t>
   </si>
   <si>
     <t xml:space="preserve">4.54527807235718</t>
@@ -2747,7 +2747,7 @@
     <t xml:space="preserve">4.52750444412231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45640850067139</t>
+    <t xml:space="preserve">4.45640802383423</t>
   </si>
   <si>
     <t xml:space="preserve">4.49680376052856</t>
@@ -2756,40 +2756,40 @@
     <t xml:space="preserve">4.48226118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48710918426514</t>
+    <t xml:space="preserve">4.48710870742798</t>
   </si>
   <si>
     <t xml:space="preserve">4.45317697525024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46771907806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49841928482056</t>
+    <t xml:space="preserve">4.46771955490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4984188079834</t>
   </si>
   <si>
     <t xml:space="preserve">4.50649833679199</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55335712432861</t>
+    <t xml:space="preserve">4.55335760116577</t>
   </si>
   <si>
     <t xml:space="preserve">4.47902965545654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52265739440918</t>
+    <t xml:space="preserve">4.52265691757202</t>
   </si>
   <si>
     <t xml:space="preserve">4.54204654693604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54689359664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50811386108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37884902954102</t>
+    <t xml:space="preserve">4.54689407348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50811433792114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37884950637817</t>
   </si>
   <si>
     <t xml:space="preserve">4.35461235046387</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">4.37238645553589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53719902038574</t>
+    <t xml:space="preserve">4.5371994972229</t>
   </si>
   <si>
     <t xml:space="preserve">4.56789922714233</t>
@@ -2807,19 +2807,19 @@
     <t xml:space="preserve">4.61152648925781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61475706100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61637353897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62768411636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59375286102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60829448699951</t>
+    <t xml:space="preserve">4.6147575378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61637449264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62768459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59375238418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60829496383667</t>
   </si>
   <si>
     <t xml:space="preserve">4.63091611862183</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">4.66484880447388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69070148468018</t>
+    <t xml:space="preserve">4.69070100784302</t>
   </si>
   <si>
     <t xml:space="preserve">4.73271179199219</t>
@@ -2843,13 +2843,13 @@
     <t xml:space="preserve">4.80219173431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79896068572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76987552642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82804441452026</t>
+    <t xml:space="preserve">4.79896020889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76987600326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.82481384277344</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">4.84420299530029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80703973770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69554853439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57436275482178</t>
+    <t xml:space="preserve">4.8070387840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69554805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57436323165894</t>
   </si>
   <si>
     <t xml:space="preserve">4.53558301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5921368598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54366159439087</t>
+    <t xml:space="preserve">4.59213638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54366207122803</t>
   </si>
   <si>
     <t xml:space="preserve">4.49034070968628</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">4.45964002609253</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51134586334229</t>
+    <t xml:space="preserve">4.51134634017944</t>
   </si>
   <si>
     <t xml:space="preserve">4.52427244186401</t>
@@ -2897,28 +2897,28 @@
     <t xml:space="preserve">4.46125555038452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58567380905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63576316833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58890438079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65353775024414</t>
+    <t xml:space="preserve">4.58567333221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63576364517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5889048576355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65353727340698</t>
   </si>
   <si>
     <t xml:space="preserve">4.57113075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4757981300354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42247629165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46933507919312</t>
+    <t xml:space="preserve">4.47579860687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42247581481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46933460235596</t>
   </si>
   <si>
     <t xml:space="preserve">4.43217134475708</t>
@@ -2933,13 +2933,13 @@
     <t xml:space="preserve">4.39985513687134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37076997756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39662313461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41116523742676</t>
+    <t xml:space="preserve">4.37077045440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3966236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41116571426392</t>
   </si>
   <si>
     <t xml:space="preserve">4.51457738876343</t>
@@ -2951,13 +2951,13 @@
     <t xml:space="preserve">4.43540239334106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50003528594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53881454467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6131420135498</t>
+    <t xml:space="preserve">4.50003576278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53881502151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61314249038696</t>
   </si>
   <si>
     <t xml:space="preserve">4.63253211975098</t>
@@ -2969,28 +2969,28 @@
     <t xml:space="preserve">4.55658864974976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57920980453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52588844299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48064517974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53235149383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44832897186279</t>
+    <t xml:space="preserve">4.57921028137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52588796615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48064613342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53235197067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44832992553711</t>
   </si>
   <si>
     <t xml:space="preserve">4.5048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71978569030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72301816940308</t>
+    <t xml:space="preserve">4.71978616714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72301721572876</t>
   </si>
   <si>
     <t xml:space="preserve">4.65838479995728</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">4.64384269714355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70201206207275</t>
+    <t xml:space="preserve">4.7020115852356</t>
   </si>
   <si>
     <t xml:space="preserve">4.68585348129272</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">4.70362758636475</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6680793762207</t>
+    <t xml:space="preserve">4.66807985305786</t>
   </si>
   <si>
     <t xml:space="preserve">4.64545822143555</t>
@@ -3023,64 +3023,64 @@
     <t xml:space="preserve">4.7262487411499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76179695129395</t>
+    <t xml:space="preserve">4.7617974281311</t>
   </si>
   <si>
     <t xml:space="preserve">4.75048589706421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84905004501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87490320205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88944625854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91853046417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85874557495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83127689361572</t>
+    <t xml:space="preserve">4.84905052185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87490367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88944578170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91852998733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85874509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83127641677856</t>
   </si>
   <si>
     <t xml:space="preserve">4.66161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64061069488525</t>
+    <t xml:space="preserve">4.64061117172241</t>
   </si>
   <si>
     <t xml:space="preserve">4.7294807434082</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74402236938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76018142700195</t>
+    <t xml:space="preserve">4.74402284622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76018095016479</t>
   </si>
   <si>
     <t xml:space="preserve">4.74079132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79734468460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71655416488647</t>
+    <t xml:space="preserve">4.79734516143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71655368804932</t>
   </si>
   <si>
     <t xml:space="preserve">4.79572868347168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83450841903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74563837051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50973033905029</t>
+    <t xml:space="preserve">4.83450794219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74563884735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50972986221313</t>
   </si>
   <si>
     <t xml:space="preserve">4.46448755264282</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">4.62930059432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55982065200806</t>
+    <t xml:space="preserve">4.5598201751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.54850959777832</t>
@@ -3101,37 +3101,37 @@
     <t xml:space="preserve">4.50326681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41278123855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35299634933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32068061828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55820512771606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51780891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49518775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41762924194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48872518539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43378734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70524311065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7302885055542</t>
+    <t xml:space="preserve">4.41278171539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35299587249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32068014144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55820465087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51780939102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49518823623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4176287651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48872470855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43378686904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7052435874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73028802871704</t>
   </si>
   <si>
     <t xml:space="preserve">4.68181419372559</t>
@@ -3143,34 +3143,34 @@
     <t xml:space="preserve">4.89590930938721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94034337997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91610622406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91206693649292</t>
+    <t xml:space="preserve">4.94034385681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91610670089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91206741333008</t>
   </si>
   <si>
     <t xml:space="preserve">5.00497627258301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04537105560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15039968490601</t>
+    <t xml:space="preserve">5.04537153244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15039920806885</t>
   </si>
   <si>
     <t xml:space="preserve">5.08980703353882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06556940078735</t>
+    <t xml:space="preserve">5.0655689239502</t>
   </si>
   <si>
     <t xml:space="preserve">4.9807391166687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96054172515869</t>
+    <t xml:space="preserve">4.96054124832153</t>
   </si>
   <si>
     <t xml:space="preserve">4.99285793304443</t>
@@ -3179,22 +3179,22 @@
     <t xml:space="preserve">5.01709508895874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00093650817871</t>
+    <t xml:space="preserve">5.00093746185303</t>
   </si>
   <si>
     <t xml:space="preserve">5.01305532455444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97266006469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8999490737915</t>
+    <t xml:space="preserve">4.97266054153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89994859695435</t>
   </si>
   <si>
     <t xml:space="preserve">4.94842290878296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92014646530151</t>
+    <t xml:space="preserve">4.92014598846436</t>
   </si>
   <si>
     <t xml:space="preserve">5.10596466064453</t>
@@ -3227,52 +3227,52 @@
     <t xml:space="preserve">5.07554531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02909660339355</t>
+    <t xml:space="preserve">5.0290961265564</t>
   </si>
   <si>
     <t xml:space="preserve">5.04598665237427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02487373352051</t>
+    <t xml:space="preserve">5.02487325668335</t>
   </si>
   <si>
     <t xml:space="preserve">4.87286043167114</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70395755767822</t>
+    <t xml:space="preserve">4.70395803451538</t>
   </si>
   <si>
     <t xml:space="preserve">4.58572483062744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54772233963013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60261583328247</t>
+    <t xml:space="preserve">4.54772186279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60261487960815</t>
   </si>
   <si>
     <t xml:space="preserve">4.53505373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71662473678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64906406402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5097188949585</t>
+    <t xml:space="preserve">4.71662521362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64906358718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50971841812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.34081506729126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45904779434204</t>
+    <t xml:space="preserve">4.45904731750488</t>
   </si>
   <si>
     <t xml:space="preserve">4.69551229476929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63217353820801</t>
+    <t xml:space="preserve">4.63217401504517</t>
   </si>
   <si>
     <t xml:space="preserve">4.7419605255127</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">4.69128942489624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72929286956787</t>
+    <t xml:space="preserve">4.72929239273071</t>
   </si>
   <si>
     <t xml:space="preserve">4.64061880111694</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">4.64484119415283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45060253143311</t>
+    <t xml:space="preserve">4.45060205459595</t>
   </si>
   <si>
     <t xml:space="preserve">4.51816368103027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45482540130615</t>
+    <t xml:space="preserve">4.45482492446899</t>
   </si>
   <si>
     <t xml:space="preserve">4.38726377487183</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">4.46327018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59417057037354</t>
+    <t xml:space="preserve">4.59417009353638</t>
   </si>
   <si>
     <t xml:space="preserve">4.67017698287964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61528301239014</t>
+    <t xml:space="preserve">4.71240282058716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61528348922729</t>
   </si>
   <si>
     <t xml:space="preserve">4.62795114517212</t>
@@ -3359,22 +3359,22 @@
     <t xml:space="preserve">4.70817995071411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66173124313354</t>
+    <t xml:space="preserve">4.6617317199707</t>
   </si>
   <si>
     <t xml:space="preserve">4.53927659988403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47593784332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33659267425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31125688552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42104387283325</t>
+    <t xml:space="preserve">4.47593832015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33659315109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31125736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42104434967041</t>
   </si>
   <si>
     <t xml:space="preserve">4.29436683654785</t>
@@ -3383,22 +3383,22 @@
     <t xml:space="preserve">4.33237028121948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25636339187622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39148569107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41259956359863</t>
+    <t xml:space="preserve">4.25636386871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39148616790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41259908676147</t>
   </si>
   <si>
     <t xml:space="preserve">4.4041543006897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32392454147339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35770559310913</t>
+    <t xml:space="preserve">4.32392501831055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35770511627197</t>
   </si>
   <si>
     <t xml:space="preserve">4.3197021484375</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">4.03341102600098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12630844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22680616378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10097217559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.036789894104</t>
+    <t xml:space="preserve">4.12630796432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22680521011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1009726524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03678941726685</t>
   </si>
   <si>
     <t xml:space="preserve">4.02834415435791</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">3.88984346389771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84761762619019</t>
+    <t xml:space="preserve">3.84761738777161</t>
   </si>
   <si>
     <t xml:space="preserve">3.97091674804688</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">4.09421634674072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01483201980591</t>
+    <t xml:space="preserve">4.01483249664307</t>
   </si>
   <si>
     <t xml:space="preserve">4.15333271026611</t>
@@ -3491,13 +3491,13 @@
     <t xml:space="preserve">4.68706703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80952215194702</t>
+    <t xml:space="preserve">4.80952167510986</t>
   </si>
   <si>
     <t xml:space="preserve">4.75462818145752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73351573944092</t>
+    <t xml:space="preserve">4.73351526260376</t>
   </si>
   <si>
     <t xml:space="preserve">4.75040578842163</t>
@@ -3506,22 +3506,22 @@
     <t xml:space="preserve">4.76307344436646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76729583740234</t>
+    <t xml:space="preserve">4.7672963142395</t>
   </si>
   <si>
     <t xml:space="preserve">4.75885105133057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74618339538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55194425582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5308313369751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48016023635864</t>
+    <t xml:space="preserve">4.74618291854858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55194473266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53083086013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4801607131958</t>
   </si>
   <si>
     <t xml:space="preserve">4.42948913574219</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">4.51394081115723</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56883430480957</t>
+    <t xml:space="preserve">4.56883478164673</t>
   </si>
   <si>
     <t xml:space="preserve">4.78418684005737</t>
@@ -3548,10 +3548,10 @@
     <t xml:space="preserve">4.58994770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52238655090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62372827529907</t>
+    <t xml:space="preserve">4.52238607406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62372875213623</t>
   </si>
   <si>
     <t xml:space="preserve">4.48438310623169</t>
@@ -3563,16 +3563,16 @@
     <t xml:space="preserve">4.35348320007324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42526626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47171497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56038951873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90241813659668</t>
+    <t xml:space="preserve">4.4252667427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47171545028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56038999557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90241861343384</t>
   </si>
   <si>
     <t xml:space="preserve">4.97842502593994</t>
@@ -3590,10 +3590,10 @@
     <t xml:space="preserve">4.99109268188477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09243488311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01220560073853</t>
+    <t xml:space="preserve">5.09243535995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01220607757568</t>
   </si>
   <si>
     <t xml:space="preserve">4.98687028884888</t>
@@ -3611,10 +3611,10 @@
     <t xml:space="preserve">4.86019325256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94042158126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93619966506958</t>
+    <t xml:space="preserve">4.94042205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93619918823242</t>
   </si>
   <si>
     <t xml:space="preserve">4.96575784683228</t>
@@ -3623,28 +3623,28 @@
     <t xml:space="preserve">4.96153497695923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00376081466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96998071670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83908033370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88975143432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82535934448242</t>
+    <t xml:space="preserve">5.00376129150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96998023986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83907985687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88975095748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82535886764526</t>
   </si>
   <si>
     <t xml:space="preserve">4.82981061935425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75858783721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66955900192261</t>
+    <t xml:space="preserve">4.75858736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66955852508545</t>
   </si>
   <si>
     <t xml:space="preserve">4.71852493286133</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">4.78529596328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90993642807007</t>
+    <t xml:space="preserve">4.90993595123291</t>
   </si>
   <si>
     <t xml:space="preserve">4.95890283584595</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">4.93219375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96780490875244</t>
+    <t xml:space="preserve">4.9678053855896</t>
   </si>
   <si>
     <t xml:space="preserve">4.9989652633667</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">4.99006223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86987352371216</t>
+    <t xml:space="preserve">4.869873046875</t>
   </si>
   <si>
     <t xml:space="preserve">4.95445108413696</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">4.88322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87432479858398</t>
+    <t xml:space="preserve">4.87432527542114</t>
   </si>
   <si>
     <t xml:space="preserve">4.80755376815796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75413656234741</t>
+    <t xml:space="preserve">4.75413608551025</t>
   </si>
   <si>
     <t xml:space="preserve">4.85206747055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63839864730835</t>
+    <t xml:space="preserve">4.63839912414551</t>
   </si>
   <si>
     <t xml:space="preserve">4.60278749465942</t>
@@ -3716,19 +3716,19 @@
     <t xml:space="preserve">4.70517015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69626712799072</t>
+    <t xml:space="preserve">4.69626760482788</t>
   </si>
   <si>
     <t xml:space="preserve">4.68291330337524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7452335357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76303863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77194166183472</t>
+    <t xml:space="preserve">4.74523305892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76303911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77194213867188</t>
   </si>
   <si>
     <t xml:space="preserve">4.71407318115234</t>
@@ -3746,25 +3746,25 @@
     <t xml:space="preserve">4.57607841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5538215637207</t>
+    <t xml:space="preserve">4.55382108688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.53156423568726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59388446807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.647301197052</t>
+    <t xml:space="preserve">4.59388399124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64730167388916</t>
   </si>
   <si>
     <t xml:space="preserve">4.66510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61614179611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54937028884888</t>
+    <t xml:space="preserve">4.6161413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54936981201172</t>
   </si>
   <si>
     <t xml:space="preserve">4.50485563278198</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">4.500403881073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49595260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48704957962036</t>
+    <t xml:space="preserve">4.49595308303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48705005645752</t>
   </si>
   <si>
     <t xml:space="preserve">4.70071887969971</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">4.73187923431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.722975730896</t>
+    <t xml:space="preserve">4.72297620773315</t>
   </si>
   <si>
     <t xml:space="preserve">4.44609642028809</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">4.24489164352417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28228330612183</t>
+    <t xml:space="preserve">4.28228378295898</t>
   </si>
   <si>
     <t xml:space="preserve">4.31789493560791</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">4.34282302856445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41226577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43541288375854</t>
+    <t xml:space="preserve">4.41226530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4354133605957</t>
   </si>
   <si>
     <t xml:space="preserve">4.42829084396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39267921447754</t>
+    <t xml:space="preserve">4.3926796913147</t>
   </si>
   <si>
     <t xml:space="preserve">4.45588970184326</t>
@@ -3857,22 +3857,22 @@
     <t xml:space="preserve">4.30186986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25201416015625</t>
+    <t xml:space="preserve">4.25201368331909</t>
   </si>
   <si>
     <t xml:space="preserve">4.26625823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27694225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20928049087524</t>
+    <t xml:space="preserve">4.27694177627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20928001403809</t>
   </si>
   <si>
     <t xml:space="preserve">4.19147443771362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21996307373047</t>
+    <t xml:space="preserve">4.21996355056763</t>
   </si>
   <si>
     <t xml:space="preserve">4.27160024642944</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">4.30899238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30543088912964</t>
+    <t xml:space="preserve">4.3054313659668</t>
   </si>
   <si>
     <t xml:space="preserve">4.39445972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40336322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47369575500488</t>
+    <t xml:space="preserve">4.40336275100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47369527816772</t>
   </si>
   <si>
     <t xml:space="preserve">4.49150133132935</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">4.46034145355225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43185186386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52266120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47814750671387</t>
+    <t xml:space="preserve">4.43185234069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5226616859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47814702987671</t>
   </si>
   <si>
     <t xml:space="preserve">4.56717586517334</t>
@@ -3944,22 +3944,22 @@
     <t xml:space="preserve">4.61169004440308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59833574295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55827236175537</t>
+    <t xml:space="preserve">4.5983362197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55827283859253</t>
   </si>
   <si>
     <t xml:space="preserve">4.58053016662598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56272411346436</t>
+    <t xml:space="preserve">4.56272459030151</t>
   </si>
   <si>
     <t xml:space="preserve">4.5849814414978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54046726226807</t>
+    <t xml:space="preserve">4.54046678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.51375865936279</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">4.6918158531189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74968481063843</t>
+    <t xml:space="preserve">4.74968433380127</t>
   </si>
   <si>
     <t xml:space="preserve">4.4692440032959</t>
@@ -3998,16 +3998,16 @@
     <t xml:space="preserve">4.44787693023682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57162714004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79419946670532</t>
+    <t xml:space="preserve">4.57162761688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79419898986816</t>
   </si>
   <si>
     <t xml:space="preserve">4.80310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8209080696106</t>
+    <t xml:space="preserve">4.82090759277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
@@ -4130,9 +4130,6 @@
     <t xml:space="preserve">4.52464294433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54170989990234</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.53602123260498</t>
   </si>
   <si>
@@ -4914,6 +4911,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86999988555908</t>
   </si>
 </sst>
 </file>
@@ -56126,7 +56126,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>1372</v>
+        <v>576</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -56152,7 +56152,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1958" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -56204,7 +56204,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G1960" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -56256,7 +56256,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G1962" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -56282,7 +56282,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1963" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -56308,7 +56308,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G1964" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -56334,7 +56334,7 @@
         <v>4.92799997329712</v>
       </c>
       <c r="G1965" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -56360,7 +56360,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1966" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -56386,7 +56386,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1967" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -56412,7 +56412,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G1968" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -56438,7 +56438,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1969" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -56464,7 +56464,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G1970" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -56490,7 +56490,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G1971" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56516,7 +56516,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G1972" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -56542,7 +56542,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G1973" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -56568,7 +56568,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G1974" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -56594,7 +56594,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1975" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -56620,7 +56620,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G1976" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -56646,7 +56646,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1977" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -56672,7 +56672,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1978" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -56750,7 +56750,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G1981" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -56776,7 +56776,7 @@
         <v>4.98199987411499</v>
       </c>
       <c r="G1982" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -56802,7 +56802,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1983" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -56828,7 +56828,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1984" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56854,7 +56854,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G1985" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56880,7 +56880,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1986" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56906,7 +56906,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1987" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56958,7 +56958,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1989" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56984,7 +56984,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G1990" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -57010,7 +57010,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1991" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -57036,7 +57036,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -57062,7 +57062,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1993" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -57088,7 +57088,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1994" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -57114,7 +57114,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1995" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -57140,7 +57140,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1996" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -57166,7 +57166,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G1997" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -57192,7 +57192,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G1998" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -57218,7 +57218,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G1999" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57244,7 +57244,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G2000" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57270,7 +57270,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -57296,7 +57296,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G2002" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -57322,7 +57322,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -57348,7 +57348,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2004" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -57374,7 +57374,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G2005" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -57400,7 +57400,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G2006" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -57426,7 +57426,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G2007" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -57452,7 +57452,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2008" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -57478,7 +57478,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G2009" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -57504,7 +57504,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2010" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -57530,7 +57530,7 @@
         <v>5.5</v>
       </c>
       <c r="G2011" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -57556,7 +57556,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2012" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -57582,7 +57582,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G2013" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -57608,7 +57608,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2014" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -57634,7 +57634,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2015" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -57660,7 +57660,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2016" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -57686,7 +57686,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G2017" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -57712,7 +57712,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G2018" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -57738,7 +57738,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2019" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57764,7 +57764,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G2020" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -57790,7 +57790,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2021" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -57816,7 +57816,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G2022" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -57842,7 +57842,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2023" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57868,7 +57868,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G2024" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57894,7 +57894,7 @@
         <v>5.875</v>
       </c>
       <c r="G2025" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57920,7 +57920,7 @@
         <v>5.79500007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57946,7 +57946,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G2027" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57972,7 +57972,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2028" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -57998,7 +57998,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G2029" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -58024,7 +58024,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G2030" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -58050,7 +58050,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2031" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -58076,7 +58076,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2032" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -58102,7 +58102,7 @@
         <v>5.625</v>
       </c>
       <c r="G2033" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -58128,7 +58128,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G2034" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -58154,7 +58154,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2035" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58180,7 +58180,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2036" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58206,7 +58206,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2037" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58232,7 +58232,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G2038" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58258,7 +58258,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G2039" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58284,7 +58284,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G2040" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -58310,7 +58310,7 @@
         <v>5.5</v>
       </c>
       <c r="G2041" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -58336,7 +58336,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G2042" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -58362,7 +58362,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2043" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -58388,7 +58388,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G2044" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58414,7 +58414,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G2045" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -58440,7 +58440,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G2046" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -58466,7 +58466,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G2047" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58492,7 +58492,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2048" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -58518,7 +58518,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G2049" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -58544,7 +58544,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G2050" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -58570,7 +58570,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2051" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -58596,7 +58596,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -58622,7 +58622,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2053" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -58648,7 +58648,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2054" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -58674,7 +58674,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G2055" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -58700,7 +58700,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G2056" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -58726,7 +58726,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G2057" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -58752,7 +58752,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G2058" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -58778,7 +58778,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G2059" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -58804,7 +58804,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G2060" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -58830,7 +58830,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G2061" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58856,7 +58856,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G2062" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58882,7 +58882,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G2063" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58908,7 +58908,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2064" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58934,7 +58934,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2065" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58960,7 +58960,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2066" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58986,7 +58986,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2067" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -59012,7 +59012,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G2068" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -59038,7 +59038,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2069" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -59064,7 +59064,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2070" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -59090,7 +59090,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2071" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -59116,7 +59116,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2072" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -59142,7 +59142,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G2073" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -59168,7 +59168,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2074" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -59194,7 +59194,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G2075" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -59220,7 +59220,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2076" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59246,7 +59246,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2077" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59272,7 +59272,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G2078" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -59298,7 +59298,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G2079" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -59324,7 +59324,7 @@
         <v>5.375</v>
       </c>
       <c r="G2080" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -59350,7 +59350,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2081" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -59376,7 +59376,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G2082" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59402,7 +59402,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G2083" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -59428,7 +59428,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2084" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -59454,7 +59454,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G2085" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59480,7 +59480,7 @@
         <v>5.625</v>
       </c>
       <c r="G2086" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -59506,7 +59506,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G2087" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -59532,7 +59532,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2088" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -59558,7 +59558,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G2089" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -59584,7 +59584,7 @@
         <v>5.63500022888184</v>
       </c>
       <c r="G2090" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -59610,7 +59610,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G2091" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -59636,7 +59636,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G2092" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -59662,7 +59662,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G2093" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -59688,7 +59688,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2094" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -59714,7 +59714,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G2095" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -59740,7 +59740,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G2096" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -59766,7 +59766,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G2097" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -59792,7 +59792,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2098" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -59818,7 +59818,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2099" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59844,7 +59844,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G2100" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59870,7 +59870,7 @@
         <v>5.875</v>
       </c>
       <c r="G2101" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59896,7 +59896,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G2102" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59922,7 +59922,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G2103" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59948,7 +59948,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G2104" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59974,7 +59974,7 @@
         <v>5.90500020980835</v>
       </c>
       <c r="G2105" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -60000,7 +60000,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G2106" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -60026,7 +60026,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G2107" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -60052,7 +60052,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2108" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -60078,7 +60078,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G2109" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -60104,7 +60104,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G2110" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60130,7 +60130,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G2111" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -60156,7 +60156,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G2112" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -60182,7 +60182,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G2113" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -60208,7 +60208,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G2114" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60234,7 +60234,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G2115" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60260,7 +60260,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G2116" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -60286,7 +60286,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G2117" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -60312,7 +60312,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G2118" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -60338,7 +60338,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -60364,7 +60364,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G2120" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -60390,7 +60390,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G2121" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60416,7 +60416,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G2122" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60442,7 +60442,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G2123" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60468,7 +60468,7 @@
         <v>6.125</v>
       </c>
       <c r="G2124" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -60494,7 +60494,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G2125" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -60520,7 +60520,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G2126" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -60546,7 +60546,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G2127" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -60572,7 +60572,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G2128" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -60598,7 +60598,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G2129" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -60624,7 +60624,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G2130" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -60650,7 +60650,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G2131" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -60676,7 +60676,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G2132" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -60702,7 +60702,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G2133" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -60728,7 +60728,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G2134" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -60754,7 +60754,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G2135" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -60780,7 +60780,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G2136" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -60806,7 +60806,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G2137" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -60832,7 +60832,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G2138" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60858,7 +60858,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G2139" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60884,7 +60884,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2140" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60910,7 +60910,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G2141" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60936,7 +60936,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G2142" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60962,7 +60962,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2143" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60988,7 +60988,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G2144" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -61014,7 +61014,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G2145" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -61040,7 +61040,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G2146" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -61066,7 +61066,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G2147" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -61092,7 +61092,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2148" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61118,7 +61118,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G2149" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -61144,7 +61144,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G2150" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -61170,7 +61170,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G2151" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -61196,7 +61196,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G2152" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -61222,7 +61222,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G2153" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61248,7 +61248,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G2154" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61274,7 +61274,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2155" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -61300,7 +61300,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2156" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -61326,7 +61326,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -61352,7 +61352,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G2158" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -61378,7 +61378,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G2159" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61404,7 +61404,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G2160" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61430,7 +61430,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2161" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61456,7 +61456,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G2162" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61482,7 +61482,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2163" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -61508,7 +61508,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2164" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -61534,7 +61534,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G2165" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -61560,7 +61560,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G2166" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -61586,7 +61586,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2167" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -61612,7 +61612,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G2168" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -61638,7 +61638,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G2169" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -61664,7 +61664,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G2170" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -61690,7 +61690,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G2171" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -61716,7 +61716,7 @@
         <v>6.72816181182861</v>
       </c>
       <c r="G2172" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -61742,7 +61742,7 @@
         <v>6.69060087203979</v>
       </c>
       <c r="G2173" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -61768,7 +61768,7 @@
         <v>6.66712522506714</v>
       </c>
       <c r="G2174" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61794,7 +61794,7 @@
         <v>6.61547899246216</v>
       </c>
       <c r="G2175" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -61820,7 +61820,7 @@
         <v>6.78919982910156</v>
       </c>
       <c r="G2176" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61846,7 +61846,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G2177" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61872,7 +61872,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G2178" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61898,7 +61898,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2179" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61924,7 +61924,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61950,7 +61950,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G2181" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61976,7 +61976,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G2182" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62002,7 +62002,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2183" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62028,7 +62028,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G2184" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62054,7 +62054,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2185" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62080,7 +62080,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G2186" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62106,7 +62106,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2187" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62132,7 +62132,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G2188" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62158,7 +62158,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2189" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62184,7 +62184,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G2190" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62210,7 +62210,7 @@
         <v>7</v>
       </c>
       <c r="G2191" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62236,7 +62236,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2192" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62262,7 +62262,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2193" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62288,7 +62288,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G2194" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62314,7 +62314,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G2195" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62340,7 +62340,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2196" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62366,7 +62366,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2197" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62392,7 +62392,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2198" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62418,7 +62418,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G2199" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62444,7 +62444,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2200" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62470,7 +62470,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2201" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62496,7 +62496,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G2202" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62522,7 +62522,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G2203" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -62548,7 +62548,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -62574,7 +62574,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2205" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -62600,7 +62600,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2206" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -62626,7 +62626,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2207" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -62652,7 +62652,7 @@
         <v>6.88500022888184</v>
       </c>
       <c r="G2208" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -62678,7 +62678,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G2209" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62704,7 +62704,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G2210" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62730,7 +62730,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2211" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -62756,7 +62756,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G2212" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62782,7 +62782,7 @@
         <v>7.25</v>
       </c>
       <c r="G2213" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -62808,7 +62808,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2214" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -62834,7 +62834,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G2215" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62860,7 +62860,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G2216" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62886,7 +62886,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2217" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62912,7 +62912,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G2218" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62938,7 +62938,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G2219" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62964,7 +62964,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G2220" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62990,7 +62990,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2221" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63016,7 +63016,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2222" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63042,7 +63042,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2223" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63068,7 +63068,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2224" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63094,7 +63094,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2225" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63120,7 +63120,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G2226" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63146,7 +63146,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G2227" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63172,7 +63172,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G2228" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63198,7 +63198,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G2229" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63224,7 +63224,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2230" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63250,7 +63250,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G2231" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63276,7 +63276,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2232" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63302,7 +63302,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2233" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63328,7 +63328,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G2234" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63354,7 +63354,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2235" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63380,7 +63380,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G2236" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63406,7 +63406,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2237" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63432,7 +63432,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63458,7 +63458,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G2239" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63484,7 +63484,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G2240" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63510,7 +63510,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G2241" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63536,7 +63536,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G2242" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -63562,7 +63562,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2243" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -63588,7 +63588,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G2244" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -63614,7 +63614,7 @@
         <v>7.625</v>
       </c>
       <c r="G2245" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -63640,7 +63640,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G2246" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -63666,7 +63666,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G2247" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -63692,7 +63692,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2248" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63718,7 +63718,7 @@
         <v>7.625</v>
       </c>
       <c r="G2249" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63744,7 +63744,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G2250" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63770,7 +63770,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2251" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63796,7 +63796,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2252" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63822,7 +63822,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2253" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63848,7 +63848,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G2254" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63874,7 +63874,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2255" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63900,7 +63900,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63926,7 +63926,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G2257" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63952,7 +63952,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G2258" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63978,7 +63978,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G2259" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64004,7 +64004,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G2260" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64030,7 +64030,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G2261" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64056,7 +64056,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G2262" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64082,7 +64082,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G2263" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64108,7 +64108,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G2264" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64134,7 +64134,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G2265" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64160,7 +64160,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2266" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64186,7 +64186,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2267" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64212,7 +64212,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G2268" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64238,7 +64238,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G2269" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64264,7 +64264,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G2270" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64290,7 +64290,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2271" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64316,7 +64316,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G2272" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64342,7 +64342,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2273" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64368,7 +64368,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G2274" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64394,7 +64394,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G2275" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64420,7 +64420,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G2276" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64446,7 +64446,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2277" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64472,7 +64472,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2278" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64498,7 +64498,7 @@
         <v>8.72500038146973</v>
       </c>
       <c r="G2279" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -64524,7 +64524,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2280" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64550,7 +64550,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G2281" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64558,7 +64558,7 @@
     </row>
     <row r="2282">
       <c r="A2282" s="1" t="n">
-        <v>45958.6916319444</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2282" t="n">
         <v>2618099</v>
@@ -64576,9 +64576,35 @@
         <v>8.875</v>
       </c>
       <c r="G2282" t="s">
+        <v>1632</v>
+      </c>
+      <c r="H2282" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" s="1" t="n">
+        <v>45959.6912615741</v>
+      </c>
+      <c r="B2283" t="n">
+        <v>3409744</v>
+      </c>
+      <c r="C2283" t="n">
+        <v>8.90499973297119</v>
+      </c>
+      <c r="D2283" t="n">
+        <v>8.76000022888184</v>
+      </c>
+      <c r="E2283" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="F2283" t="n">
+        <v>8.86999988555908</v>
+      </c>
+      <c r="G2283" t="s">
         <v>1633</v>
       </c>
-      <c r="H2282" t="s">
+      <c r="H2283" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58873581886292</t>
+    <t xml:space="preserve">2.58873558044434</t>
   </si>
   <si>
     <t xml:space="preserve">IG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50135779380798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32790565490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16488718986511</t>
+    <t xml:space="preserve">2.50135731697083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32790589332581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16488742828369</t>
   </si>
   <si>
     <t xml:space="preserve">2.1727123260498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09315896034241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06185960769653</t>
+    <t xml:space="preserve">2.09315872192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06185936927795</t>
   </si>
   <si>
     <t xml:space="preserve">2.08663845062256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04490542411804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06055569648743</t>
+    <t xml:space="preserve">2.04490518569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06055545806885</t>
   </si>
   <si>
     <t xml:space="preserve">2.04360127449036</t>
   </si>
   <si>
-    <t xml:space="preserve">2.104896068573</t>
+    <t xml:space="preserve">2.10489630699158</t>
   </si>
   <si>
     <t xml:space="preserve">2.1296751499176</t>
@@ -83,34 +83,34 @@
     <t xml:space="preserve">2.14532494544983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17923259735107</t>
+    <t xml:space="preserve">2.17923283576965</t>
   </si>
   <si>
     <t xml:space="preserve">2.2000994682312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20140314102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17792892456055</t>
+    <t xml:space="preserve">2.20140337944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17792868614197</t>
   </si>
   <si>
     <t xml:space="preserve">2.13228321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09837579727173</t>
+    <t xml:space="preserve">2.09837555885315</t>
   </si>
   <si>
     <t xml:space="preserve">2.22357392311096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29138946533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33181858062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29791021347046</t>
+    <t xml:space="preserve">2.29138970375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33181834220886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29791069030762</t>
   </si>
   <si>
     <t xml:space="preserve">2.23791933059692</t>
@@ -119,43 +119,43 @@
     <t xml:space="preserve">2.30051875114441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30443120002747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37094259262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34616446495056</t>
+    <t xml:space="preserve">2.30443096160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37094283103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3461639881134</t>
   </si>
   <si>
     <t xml:space="preserve">2.39572143554688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45571231842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3970263004303</t>
+    <t xml:space="preserve">2.45571255683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39702558517456</t>
   </si>
   <si>
     <t xml:space="preserve">2.38007164001465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39441752433777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42180442810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41006708145142</t>
+    <t xml:space="preserve">2.39441728591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42180490493774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41006755828857</t>
   </si>
   <si>
     <t xml:space="preserve">2.43093347549438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43745446205139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701167106628</t>
+    <t xml:space="preserve">2.43745422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701190948486</t>
   </si>
   <si>
     <t xml:space="preserve">2.45049571990967</t>
@@ -179,25 +179,25 @@
     <t xml:space="preserve">2.47788286209106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43615055084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43354177474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4570164680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48831629753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41789174079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43484616279602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41267585754395</t>
+    <t xml:space="preserve">2.43615031242371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43354201316833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45701622962952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48831605911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41789197921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43484592437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41267538070679</t>
   </si>
   <si>
     <t xml:space="preserve">2.35659718513489</t>
@@ -215,67 +215,67 @@
     <t xml:space="preserve">2.38137602806091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40876317024231</t>
+    <t xml:space="preserve">2.40876293182373</t>
   </si>
   <si>
     <t xml:space="preserve">2.39311337471008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44919180870056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46744966506958</t>
+    <t xml:space="preserve">2.44919157028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46744990348816</t>
   </si>
   <si>
     <t xml:space="preserve">2.47397041320801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48440361022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46353721618652</t>
+    <t xml:space="preserve">2.48440384864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4635374546051</t>
   </si>
   <si>
     <t xml:space="preserve">2.47266626358032</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47136211395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44788765907288</t>
+    <t xml:space="preserve">2.47136235237122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44788718223572</t>
   </si>
   <si>
     <t xml:space="preserve">2.49614095687866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744486808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51570320129395</t>
+    <t xml:space="preserve">2.49744534492493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51570343971252</t>
   </si>
   <si>
     <t xml:space="preserve">2.53135299682617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51439929008484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53656983375549</t>
+    <t xml:space="preserve">2.51439905166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53656959533691</t>
   </si>
   <si>
     <t xml:space="preserve">2.52744054794312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5483067035675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55091524124146</t>
+    <t xml:space="preserve">2.54830694198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55091571807861</t>
   </si>
   <si>
     <t xml:space="preserve">2.5378737449646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58612751960754</t>
+    <t xml:space="preserve">2.58612728118896</t>
   </si>
   <si>
     <t xml:space="preserve">2.57699823379517</t>
@@ -284,16 +284,16 @@
     <t xml:space="preserve">2.59786462783813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438537597656</t>
+    <t xml:space="preserve">2.60438561439514</t>
   </si>
   <si>
     <t xml:space="preserve">2.57308578491211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66959285736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68393850326538</t>
+    <t xml:space="preserve">2.66959261894226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68393874168396</t>
   </si>
   <si>
     <t xml:space="preserve">2.69828414916992</t>
@@ -302,199 +302,199 @@
     <t xml:space="preserve">2.64872646331787</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64742255210876</t>
+    <t xml:space="preserve">2.64742231369019</t>
   </si>
   <si>
     <t xml:space="preserve">2.68133020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67480945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63438057899475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64350962638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69567561149597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69958829879761</t>
+    <t xml:space="preserve">2.67480969429016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63438105583191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64350986480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69958806037903</t>
   </si>
   <si>
     <t xml:space="preserve">2.67872190475464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73480010032654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77262020111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75436282157898</t>
+    <t xml:space="preserve">2.73480033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77262043952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7543625831604</t>
   </si>
   <si>
     <t xml:space="preserve">2.71262979507446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70089268684387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70219683647156</t>
+    <t xml:space="preserve">2.70089292526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70219659805298</t>
   </si>
   <si>
     <t xml:space="preserve">2.66176772117615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7830536365509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74523377418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69306778907776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71915054321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70610928535461</t>
+    <t xml:space="preserve">2.78305387496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7452335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6930673122406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71915030479431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70610904693604</t>
   </si>
   <si>
     <t xml:space="preserve">2.74914598464966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77783751487732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83522009849548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84043669700623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88738584518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8965151309967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85347747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91477251052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0086715221405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02040958404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96824288368225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00736713409424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05822944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09885382652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15591335296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09613680839539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1382520198822</t>
+    <t xml:space="preserve">2.77783727645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83521962165833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84043645858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88738560676575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89651441574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8534779548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91477274894714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00867128372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02040910720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96824312210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00736737251282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05822920799255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09885406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15591287612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09613728523254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13825154304504</t>
   </si>
   <si>
     <t xml:space="preserve">3.0907027721405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97658443450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13417625427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20074558258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24965262413025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28769254684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23063349723816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24557757377625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2224817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25101137161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1871600151062</t>
+    <t xml:space="preserve">2.97658467292786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13417601585388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20074582099915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24965333938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28769302368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23063325881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24557709693909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22248220443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25101161003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18716025352478</t>
   </si>
   <si>
     <t xml:space="preserve">3.09477853775024</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11379861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19938683509827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10428810119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12059092521667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15727162361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16270613670349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14504504203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03907799720764</t>
+    <t xml:space="preserve">3.11379814147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19938731193542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10428857803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12059044837952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15727138519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16270637512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14504480361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03907775878906</t>
   </si>
   <si>
     <t xml:space="preserve">3.02820944786072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96707463264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00375556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03636074066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02005815505981</t>
+    <t xml:space="preserve">2.96707439422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00375533103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03636050224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02005791664124</t>
   </si>
   <si>
     <t xml:space="preserve">2.977942943573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98609399795532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99560403823853</t>
+    <t xml:space="preserve">2.9860942363739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9956042766571</t>
   </si>
   <si>
     <t xml:space="preserve">3.07575869560242</t>
@@ -503,46 +503,46 @@
     <t xml:space="preserve">3.08390974998474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12466669082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10836410522461</t>
+    <t xml:space="preserve">3.12466621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10836386680603</t>
   </si>
   <si>
     <t xml:space="preserve">3.12874221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17900824546814</t>
+    <t xml:space="preserve">3.17900848388672</t>
   </si>
   <si>
     <t xml:space="preserve">3.17221593856812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12602567672729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15863037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22519946098328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26052165031433</t>
+    <t xml:space="preserve">3.12602496147156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15863013267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2251992225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26052188873291</t>
   </si>
   <si>
     <t xml:space="preserve">3.25237011909485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27682399749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30671215057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30263662338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2808997631073</t>
+    <t xml:space="preserve">3.27682423591614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30671191215515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30263638496399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28090000152588</t>
   </si>
   <si>
     <t xml:space="preserve">3.21025538444519</t>
@@ -551,16 +551,16 @@
     <t xml:space="preserve">3.28361701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29856133460999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28225874900818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26323843002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25644636154175</t>
+    <t xml:space="preserve">3.29856085777283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28225827217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26323866844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25644588470459</t>
   </si>
   <si>
     <t xml:space="preserve">3.27003145217896</t>
@@ -572,28 +572,28 @@
     <t xml:space="preserve">3.2333505153656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21976518630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24150133132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26188063621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2347092628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1980288028717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23742580413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24829435348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22791647911072</t>
+    <t xml:space="preserve">3.21976494789124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24150156974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26188015937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23470902442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19802832603455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23742604255676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24829483032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22791600227356</t>
   </si>
   <si>
     <t xml:space="preserve">3.19395303726196</t>
@@ -605,16 +605,16 @@
     <t xml:space="preserve">3.18444299697876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18172574043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20753836631775</t>
+    <t xml:space="preserve">3.18172597885132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20753812789917</t>
   </si>
   <si>
     <t xml:space="preserve">3.24014329910278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26731419563293</t>
+    <t xml:space="preserve">3.26731443405151</t>
   </si>
   <si>
     <t xml:space="preserve">3.24286031723022</t>
@@ -623,16 +623,16 @@
     <t xml:space="preserve">3.22655773162842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23199200630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20617961883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14640331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16814017295837</t>
+    <t xml:space="preserve">3.2319917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20617914199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14640355110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16814041137695</t>
   </si>
   <si>
     <t xml:space="preserve">3.10157108306885</t>
@@ -641,13 +641,13 @@
     <t xml:space="preserve">3.16678166389465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21704769134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22927474975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24421906471252</t>
+    <t xml:space="preserve">3.21704792976379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22927451133728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24421882629395</t>
   </si>
   <si>
     <t xml:space="preserve">3.21433091163635</t>
@@ -659,22 +659,22 @@
     <t xml:space="preserve">3.35154461860657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4914755821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39365935325623</t>
+    <t xml:space="preserve">3.49147534370422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39365911483765</t>
   </si>
   <si>
     <t xml:space="preserve">3.46430420875549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50506067276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41675472259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40656542778015</t>
+    <t xml:space="preserve">3.50506114959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41675448417664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40656566619873</t>
   </si>
   <si>
     <t xml:space="preserve">3.44732236862183</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">3.43373656272888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42694449424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47109699249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46770071983337</t>
+    <t xml:space="preserve">3.42694401741028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47109746932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46770119667053</t>
   </si>
   <si>
     <t xml:space="preserve">3.48128604888916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50166440010071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54242086410522</t>
+    <t xml:space="preserve">3.50166368484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5424211025238</t>
   </si>
   <si>
     <t xml:space="preserve">3.51185321807861</t>
@@ -710,43 +710,43 @@
     <t xml:space="preserve">3.55940270423889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6341233253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60015916824341</t>
+    <t xml:space="preserve">3.63412284851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60015964508057</t>
   </si>
   <si>
     <t xml:space="preserve">3.53223133087158</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48468279838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55260992050171</t>
+    <t xml:space="preserve">3.48468208312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55261039733887</t>
   </si>
   <si>
     <t xml:space="preserve">3.61374497413635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52543902397156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58996987342834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60355544090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5933666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62053775787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59676313400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56619572639465</t>
+    <t xml:space="preserve">3.52543878555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58997011184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60355567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59336638450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62053728103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59676289558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56619596481323</t>
   </si>
   <si>
     <t xml:space="preserve">3.53562760353088</t>
@@ -755,22 +755,22 @@
     <t xml:space="preserve">3.45411539077759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45751166343689</t>
+    <t xml:space="preserve">3.45751190185547</t>
   </si>
   <si>
     <t xml:space="preserve">3.39637660980225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32301473617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38279104232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40996217727661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38958382606506</t>
+    <t xml:space="preserve">3.32301545143127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38279128074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40996193885803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38958358764648</t>
   </si>
   <si>
     <t xml:space="preserve">3.32844924926758</t>
@@ -779,46 +779,46 @@
     <t xml:space="preserve">3.30807113647461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31078815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35018634796143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37599802017212</t>
+    <t xml:space="preserve">3.31078791618347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35018610954285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3759982585907</t>
   </si>
   <si>
     <t xml:space="preserve">3.35426187515259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37328100204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34339284896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36648845672607</t>
+    <t xml:space="preserve">3.37328124046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34339332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3664882183075</t>
   </si>
   <si>
     <t xml:space="preserve">3.37871551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36105442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12127017974854</t>
+    <t xml:space="preserve">3.36105489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12126970291138</t>
   </si>
   <si>
     <t xml:space="preserve">3.16406488418579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06624865531921</t>
+    <t xml:space="preserve">3.06624889373779</t>
   </si>
   <si>
     <t xml:space="preserve">3.0458710193634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03228497505188</t>
+    <t xml:space="preserve">3.03228521347046</t>
   </si>
   <si>
     <t xml:space="preserve">3.00239682197571</t>
@@ -830,211 +830,211 @@
     <t xml:space="preserve">3.02549242973328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04654979705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9942455291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96164011955261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97862267494202</t>
+    <t xml:space="preserve">3.04655003547668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99424576759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96164059638977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97862243652344</t>
   </si>
   <si>
     <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11651515960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06828665733337</t>
+    <t xml:space="preserve">3.11651492118835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06828713417053</t>
   </si>
   <si>
     <t xml:space="preserve">3.00035905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96639513969421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.929034948349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92495965957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01326513290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09409880638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14300727844238</t>
+    <t xml:space="preserve">2.96639561653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92903518676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.924959897995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01326560974121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0940990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14300680160522</t>
   </si>
   <si>
     <t xml:space="preserve">3.23538851737976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22723722457886</t>
+    <t xml:space="preserve">3.22723698616028</t>
   </si>
   <si>
     <t xml:space="preserve">3.21297240257263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19327354431152</t>
+    <t xml:space="preserve">3.1932737827301</t>
   </si>
   <si>
     <t xml:space="preserve">3.27342772483826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29448509216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20414161682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30739164352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28565454483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36377191543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39909386634827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47924828529358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47517275810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48196578025818</t>
+    <t xml:space="preserve">3.29448533058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20414185523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30739140510559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28565502166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36377143859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39909362792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47924852371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.475172996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48196530342102</t>
   </si>
   <si>
     <t xml:space="preserve">3.43713307380676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44392609596252</t>
+    <t xml:space="preserve">3.4439263343811</t>
   </si>
   <si>
     <t xml:space="preserve">3.49962639808655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52815628051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47788977622986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51456999778748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45887017250061</t>
+    <t xml:space="preserve">3.528156042099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47788953781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5145697593689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45887041091919</t>
   </si>
   <si>
     <t xml:space="preserve">3.5267972946167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52000498771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57570576667786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62733030319214</t>
+    <t xml:space="preserve">3.52000451087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57570481300354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62733054161072</t>
   </si>
   <si>
     <t xml:space="preserve">3.64499115943909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60423517227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60287666320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62597179412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49419283866882</t>
+    <t xml:space="preserve">3.60423493385315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60287594795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62597131729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49419236183167</t>
   </si>
   <si>
     <t xml:space="preserve">3.45615291595459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41539645195007</t>
+    <t xml:space="preserve">3.41539597511292</t>
   </si>
   <si>
     <t xml:space="preserve">3.45479464530945</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44256711006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36309266090393</t>
+    <t xml:space="preserve">3.44256734848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36309242248535</t>
   </si>
   <si>
     <t xml:space="preserve">3.39298009872437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39461970329285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4540011882782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4610698223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36280870437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28151273727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23414945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07367920875549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16699194908142</t>
+    <t xml:space="preserve">3.39461946487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45400094985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46106958389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36280822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28151321411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23414921760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07367873191833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16699242591858</t>
   </si>
   <si>
     <t xml:space="preserve">3.1528537273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18961381912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27868485450745</t>
+    <t xml:space="preserve">3.18961358070374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27868509292603</t>
   </si>
   <si>
     <t xml:space="preserve">3.25747728347778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23556351661682</t>
+    <t xml:space="preserve">3.23556327819824</t>
   </si>
   <si>
     <t xml:space="preserve">3.23768401145935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34089326858521</t>
+    <t xml:space="preserve">3.20163083076477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34089422225952</t>
   </si>
   <si>
     <t xml:space="preserve">3.43774151802063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39037823677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41087818145752</t>
+    <t xml:space="preserve">3.39037847518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4108784198761</t>
   </si>
   <si>
     <t xml:space="preserve">3.37623977661133</t>
@@ -1043,136 +1043,136 @@
     <t xml:space="preserve">3.38967132568359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40946483612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46319079399109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33735966682434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31544423103333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29989242553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34442806243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35432553291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32958340644836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33806657791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29211688041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35644626617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35220432281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40098166465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4186544418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3776535987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32534146308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35573935508728</t>
+    <t xml:space="preserve">3.40946435928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46319103240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33735942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31544470787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29989290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34442853927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35432505607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32958316802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3380663394928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29211640357971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35644602775574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3522047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40098190307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41865468025208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37765336036682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32534217834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35573959350586</t>
   </si>
   <si>
     <t xml:space="preserve">3.34230804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40027475357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45258665084839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44834518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44268989562988</t>
+    <t xml:space="preserve">3.40027451515198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45258688926697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44834566116333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44269013404846</t>
   </si>
   <si>
     <t xml:space="preserve">3.4511730670929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41229271888733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40734457969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46036314964294</t>
+    <t xml:space="preserve">3.41229224205017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4073441028595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46036291122437</t>
   </si>
   <si>
     <t xml:space="preserve">3.43137955665588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47874283790588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42077589035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42572450637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51479554176331</t>
+    <t xml:space="preserve">3.47874307632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42077612876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42572426795959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51479578018188</t>
   </si>
   <si>
     <t xml:space="preserve">3.49429488182068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39532661437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41582727432251</t>
+    <t xml:space="preserve">3.39532685279846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41582703590393</t>
   </si>
   <si>
     <t xml:space="preserve">3.42925834655762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40239572525024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36139464378357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38825798034668</t>
+    <t xml:space="preserve">3.4023962020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36139440536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38825750350952</t>
   </si>
   <si>
     <t xml:space="preserve">3.43279361724854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33594536781311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29706525802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30413436889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30837559700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28787469863892</t>
+    <t xml:space="preserve">3.33594584465027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29706501960754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30413389205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30837512016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28787541389465</t>
   </si>
   <si>
     <t xml:space="preserve">3.31615161895752</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">3.25182223320007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28999519348145</t>
+    <t xml:space="preserve">3.28999590873718</t>
   </si>
   <si>
     <t xml:space="preserve">3.33311796188354</t>
@@ -1193,130 +1193,130 @@
     <t xml:space="preserve">3.33382487297058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32675552368164</t>
+    <t xml:space="preserve">3.32675576210022</t>
   </si>
   <si>
     <t xml:space="preserve">3.34654951095581</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47450137138367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49924373626709</t>
+    <t xml:space="preserve">3.47450113296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49924325942993</t>
   </si>
   <si>
     <t xml:space="preserve">3.49641609191895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46248412132263</t>
+    <t xml:space="preserve">3.46248340606689</t>
   </si>
   <si>
     <t xml:space="preserve">3.45682811737061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45470786094666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38613653182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45753502845764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45894956588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37411856651306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39391255378723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42006874084473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30978989601135</t>
+    <t xml:space="preserve">3.4547073841095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38613677024841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45753526687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45894908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37411904335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39391303062439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42006850242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30978965759277</t>
   </si>
   <si>
     <t xml:space="preserve">3.32816934585571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35715293884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27797818183899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24899482727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21011424064636</t>
+    <t xml:space="preserve">3.35715317726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27797865867615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24899458885193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21011400222778</t>
   </si>
   <si>
     <t xml:space="preserve">3.23485612869263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20516586303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15780210494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.130939245224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15356087684631</t>
+    <t xml:space="preserve">3.20516562461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15780234336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13093900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15356063842773</t>
   </si>
   <si>
     <t xml:space="preserve">3.24545979499817</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16911244392395</t>
+    <t xml:space="preserve">3.16911268234253</t>
   </si>
   <si>
     <t xml:space="preserve">3.19809675216675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18890714645386</t>
+    <t xml:space="preserve">3.1889066696167</t>
   </si>
   <si>
     <t xml:space="preserve">3.23909759521484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23344206809998</t>
+    <t xml:space="preserve">3.23344230651855</t>
   </si>
   <si>
     <t xml:space="preserve">3.27727150917053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23202872276306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22920060157776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22495937347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2723228931427</t>
+    <t xml:space="preserve">3.23202896118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22920083999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22495913505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27232313156128</t>
   </si>
   <si>
     <t xml:space="preserve">3.31473827362061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3734118938446</t>
+    <t xml:space="preserve">3.37341213226318</t>
   </si>
   <si>
     <t xml:space="preserve">3.42501711845398</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43491458892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48863935470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44693112373352</t>
+    <t xml:space="preserve">3.43491435050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48863983154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44693183898926</t>
   </si>
   <si>
     <t xml:space="preserve">3.38755035400391</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">3.35927391052246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34160161018372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30059957504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3048415184021</t>
+    <t xml:space="preserve">3.34160137176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3005998134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30484080314636</t>
   </si>
   <si>
     <t xml:space="preserve">3.27585744857788</t>
@@ -1340,37 +1340,37 @@
     <t xml:space="preserve">3.39603352546692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3493766784668</t>
+    <t xml:space="preserve">3.34937691688538</t>
   </si>
   <si>
     <t xml:space="preserve">3.36068797111511</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36705017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39179182052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41653442382812</t>
+    <t xml:space="preserve">3.36704969406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3917920589447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41653418540955</t>
   </si>
   <si>
     <t xml:space="preserve">3.453293800354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52327847480774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59114289283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61235022544861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073015213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61093664169312</t>
+    <t xml:space="preserve">3.52327871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59114265441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61235070228577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073039054871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61093688011169</t>
   </si>
   <si>
     <t xml:space="preserve">3.62790274620056</t>
@@ -1379,28 +1379,28 @@
     <t xml:space="preserve">3.60103964805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59962606430054</t>
+    <t xml:space="preserve">3.59962582588196</t>
   </si>
   <si>
     <t xml:space="preserve">3.51055407524109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53176116943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57841777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61941981315613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64911031723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67880082130432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6208336353302</t>
+    <t xml:space="preserve">3.53176140785217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57841801643372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61941909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6491105556488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67880058288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62083292007446</t>
   </si>
   <si>
     <t xml:space="preserve">3.68586993217468</t>
@@ -1409,61 +1409,61 @@
     <t xml:space="preserve">3.70849132537842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6533522605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68304204940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68728446960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67738747596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71414637565613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71131896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70990467071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72545766830444</t>
+    <t xml:space="preserve">3.65335202217102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68304181098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68728351593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67738676071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71414709091187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71131944656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70990538597107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72545695304871</t>
   </si>
   <si>
     <t xml:space="preserve">3.7325267791748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73111248016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67173099517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69293856620789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71980166435242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779926300049</t>
+    <t xml:space="preserve">3.73111271858215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67173171043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69293928146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71980237960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779878616333</t>
   </si>
   <si>
     <t xml:space="preserve">3.61517810821533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68869733810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69576668739319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69435286521912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69718050956726</t>
+    <t xml:space="preserve">3.68869757652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69576740264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69435262680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69718074798584</t>
   </si>
   <si>
     <t xml:space="preserve">3.68162822723389</t>
@@ -1472,94 +1472,94 @@
     <t xml:space="preserve">3.75232005119324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74383735656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72262954711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76504445075989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75938940048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71697402000427</t>
+    <t xml:space="preserve">3.7438371181488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72262930870056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76504492759705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75938892364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71697473526001</t>
   </si>
   <si>
     <t xml:space="preserve">3.78342437744141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83997774124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86542725563049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8357367515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82442545890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79756355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8173565864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85977172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86966872215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88380718231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87532377243042</t>
+    <t xml:space="preserve">3.83997821807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86542677879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83573627471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82442593574524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79756283760071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81735706329346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85977125167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86966848373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88380670547485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87532448768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.89370369911194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88804817199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85270261764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87108206748962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89087581634521</t>
+    <t xml:space="preserve">3.88804769515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85270237922668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87108254432678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89087557792664</t>
   </si>
   <si>
     <t xml:space="preserve">3.84139156341553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88239359855652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92339420318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88946175575256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90360069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92056679725647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91915273666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96439576148987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95732593536377</t>
+    <t xml:space="preserve">3.88239336013794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92339396476746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88946223258972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90360045433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92056608200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91915345191956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96439528465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95732641220093</t>
   </si>
   <si>
     <t xml:space="preserve">3.91066980361938</t>
@@ -1568,49 +1568,49 @@
     <t xml:space="preserve">3.93329119682312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90642786026001</t>
+    <t xml:space="preserve">3.90642833709717</t>
   </si>
   <si>
     <t xml:space="preserve">3.90501427650452</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92198038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91208338737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93046426773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87956571578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89794516563416</t>
+    <t xml:space="preserve">3.92198014259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91208362579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9304633140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87956523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89794540405273</t>
   </si>
   <si>
     <t xml:space="preserve">3.88097882270813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94742941856384</t>
+    <t xml:space="preserve">3.94742894172668</t>
   </si>
   <si>
     <t xml:space="preserve">3.89229011535645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87390971183777</t>
+    <t xml:space="preserve">3.87391042709351</t>
   </si>
   <si>
     <t xml:space="preserve">3.90925574302673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95025730133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98136138916016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00963830947876</t>
+    <t xml:space="preserve">3.95025658607483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98136186599731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00963735580444</t>
   </si>
   <si>
     <t xml:space="preserve">4.08032989501953</t>
@@ -1619,31 +1619,31 @@
     <t xml:space="preserve">4.07891654968262</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13016366958618</t>
+    <t xml:space="preserve">4.13016319274902</t>
   </si>
   <si>
     <t xml:space="preserve">4.16984796524048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21100282669067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.213942527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24921846389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20512342453003</t>
+    <t xml:space="preserve">4.21100330352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21394205093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24921798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20512390136719</t>
   </si>
   <si>
     <t xml:space="preserve">4.19483518600464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12281465530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1081166267395</t>
+    <t xml:space="preserve">4.1228141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10811614990234</t>
   </si>
   <si>
     <t xml:space="preserve">4.16543865203857</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">4.21541213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26979541778564</t>
+    <t xml:space="preserve">4.26979494094849</t>
   </si>
   <si>
     <t xml:space="preserve">4.3050708770752</t>
@@ -1664,49 +1664,49 @@
     <t xml:space="preserve">4.36827230453491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33152723312378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32564783096313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28890323638916</t>
+    <t xml:space="preserve">4.33152675628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32564830780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28890228271484</t>
   </si>
   <si>
     <t xml:space="preserve">4.35651397705078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34328508377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49908590316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44764280319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4461727142334</t>
+    <t xml:space="preserve">4.34328556060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49908542633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44764232635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44617223739624</t>
   </si>
   <si>
     <t xml:space="preserve">4.48291778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48732709884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45352125167847</t>
+    <t xml:space="preserve">4.48732662200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45352172851562</t>
   </si>
   <si>
     <t xml:space="preserve">4.43735361099243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35210418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34181594848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33446598052979</t>
+    <t xml:space="preserve">4.35210466384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34181547164917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3344669342041</t>
   </si>
   <si>
     <t xml:space="preserve">4.43147420883179</t>
@@ -1715,13 +1715,13 @@
     <t xml:space="preserve">4.47997808456421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44911193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43882369995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49467658996582</t>
+    <t xml:space="preserve">4.4491114616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43882322311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4946756362915</t>
   </si>
   <si>
     <t xml:space="preserve">4.51966285705566</t>
@@ -1730,22 +1730,22 @@
     <t xml:space="preserve">4.50349521636963</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54317998886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56228733062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57698583602905</t>
+    <t xml:space="preserve">4.54318046569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56228685379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57698535919189</t>
   </si>
   <si>
     <t xml:space="preserve">4.52701187133789</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54170942306519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54905891418457</t>
+    <t xml:space="preserve">4.54170989990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54905986785889</t>
   </si>
   <si>
     <t xml:space="preserve">4.40207767486572</t>
@@ -1757,10 +1757,10 @@
     <t xml:space="preserve">4.4255952835083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38885021209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38150024414062</t>
+    <t xml:space="preserve">4.38884973526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38150072097778</t>
   </si>
   <si>
     <t xml:space="preserve">4.24480867385864</t>
@@ -1775,7 +1775,7 @@
     <t xml:space="preserve">4.29331207275391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27420425415039</t>
+    <t xml:space="preserve">4.27420473098755</t>
   </si>
   <si>
     <t xml:space="preserve">4.26097631454468</t>
@@ -1784,25 +1784,25 @@
     <t xml:space="preserve">4.2844934463501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28743314743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11399507522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16102981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24186897277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15662002563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3036003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2183518409729</t>
+    <t xml:space="preserve">4.28743267059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11399602890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16102933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24186849594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15662050247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30360078811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21835136413574</t>
   </si>
   <si>
     <t xml:space="preserve">4.20071458816528</t>
@@ -1817,22 +1817,22 @@
     <t xml:space="preserve">4.33593654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34916543960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.313889503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30213117599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20806312561035</t>
+    <t xml:space="preserve">4.34916496276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31388902664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30213165283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20806360244751</t>
   </si>
   <si>
     <t xml:space="preserve">4.14192247390747</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10370683670044</t>
+    <t xml:space="preserve">4.10370635986328</t>
   </si>
   <si>
     <t xml:space="preserve">4.18307638168335</t>
@@ -1841,22 +1841,22 @@
     <t xml:space="preserve">4.14045190811157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12575435638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1933650970459</t>
+    <t xml:space="preserve">4.12575387954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19336462020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.18160724639893</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18454647064209</t>
+    <t xml:space="preserve">4.18454694747925</t>
   </si>
   <si>
     <t xml:space="preserve">4.25215768814087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29919099807739</t>
+    <t xml:space="preserve">4.29919147491455</t>
   </si>
   <si>
     <t xml:space="preserve">4.39031934738159</t>
@@ -1871,10 +1871,10 @@
     <t xml:space="preserve">4.21247291564941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31241893768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36974239349365</t>
+    <t xml:space="preserve">4.31241989135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36974287033081</t>
   </si>
   <si>
     <t xml:space="preserve">4.24774837493896</t>
@@ -1886,49 +1886,49 @@
     <t xml:space="preserve">4.23011064529419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18748569488525</t>
+    <t xml:space="preserve">4.18748617172241</t>
   </si>
   <si>
     <t xml:space="preserve">4.17425727844238</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17278814315796</t>
+    <t xml:space="preserve">4.1727876663208</t>
   </si>
   <si>
     <t xml:space="preserve">4.14486122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1683783531189</t>
+    <t xml:space="preserve">4.16837739944458</t>
   </si>
   <si>
     <t xml:space="preserve">4.18013715744019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.238929271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25362730026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29478120803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33740663528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35063505172729</t>
+    <t xml:space="preserve">4.23892879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25362777709961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29478168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33740615844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35063457489014</t>
   </si>
   <si>
     <t xml:space="preserve">4.28302335739136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33299684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30654096603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268114089966</t>
+    <t xml:space="preserve">4.33299732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30654048919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268209457397</t>
   </si>
   <si>
     <t xml:space="preserve">4.39178895950317</t>
@@ -1937,19 +1937,19 @@
     <t xml:space="preserve">4.27861404418945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22423076629639</t>
+    <t xml:space="preserve">4.22423124313354</t>
   </si>
   <si>
     <t xml:space="preserve">4.23745918273926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22570037841797</t>
+    <t xml:space="preserve">4.22570085525513</t>
   </si>
   <si>
     <t xml:space="preserve">4.19189548492432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22129154205322</t>
+    <t xml:space="preserve">4.22129106521606</t>
   </si>
   <si>
     <t xml:space="preserve">4.23598957061768</t>
@@ -1958,163 +1958,163 @@
     <t xml:space="preserve">4.22717046737671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00963926315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07431077957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08900880813599</t>
+    <t xml:space="preserve">4.00963878631592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07431125640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0890097618103</t>
   </si>
   <si>
     <t xml:space="preserve">4.04932403564453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01992750167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95378613471985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99494099617004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0419750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99053168296814</t>
+    <t xml:space="preserve">4.01992702484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95378684997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99494051933289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04197454452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99053120613098</t>
   </si>
   <si>
     <t xml:space="preserve">4.03609561920166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10664653778076</t>
+    <t xml:space="preserve">4.1066460609436</t>
   </si>
   <si>
     <t xml:space="preserve">4.16396903991699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1272234916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13751220703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00082015991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09194803237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08459901809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02727651596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02286767959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10076665878296</t>
+    <t xml:space="preserve">4.12722396850586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13751268386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00081968307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09194850921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08459949493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02727699279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02286720275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1007661819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.20365381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13898229598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25068807601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20659303665161</t>
+    <t xml:space="preserve">4.13898277282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25068759918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20659399032593</t>
   </si>
   <si>
     <t xml:space="preserve">4.26391553878784</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30801010131836</t>
+    <t xml:space="preserve">4.30801057815552</t>
   </si>
   <si>
     <t xml:space="preserve">4.48144769668579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5152530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49761486053467</t>
+    <t xml:space="preserve">4.51525354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49761581420898</t>
   </si>
   <si>
     <t xml:space="preserve">4.40648746490479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41677665710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4667501449585</t>
+    <t xml:space="preserve">4.41677618026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46674966812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.49173641204834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46087026596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46233987808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51231384277344</t>
+    <t xml:space="preserve">4.46087074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46234035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51231336593628</t>
   </si>
   <si>
     <t xml:space="preserve">4.45205163955688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48585748672485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62548875808716</t>
+    <t xml:space="preserve">4.4858570098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62548923492432</t>
   </si>
   <si>
     <t xml:space="preserve">4.26538562774658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26244592666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06549167633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08606958389282</t>
+    <t xml:space="preserve">4.26244640350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06549215316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08606910705566</t>
   </si>
   <si>
     <t xml:space="preserve">3.72890543937683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51798820495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5018196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02192711830139</t>
+    <t xml:space="preserve">3.5179877281189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50181984901428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02192735671997</t>
   </si>
   <si>
     <t xml:space="preserve">3.24754309654236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15127062797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27032470703125</t>
+    <t xml:space="preserve">3.15127038955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27032494544983</t>
   </si>
   <si>
     <t xml:space="preserve">3.29531216621399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35189914703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21153283119202</t>
+    <t xml:space="preserve">3.35189938545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21153259277344</t>
   </si>
   <si>
     <t xml:space="preserve">3.129958152771</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">3.38937973976135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34381580352783</t>
+    <t xml:space="preserve">3.34381604194641</t>
   </si>
   <si>
     <t xml:space="preserve">3.35924863815308</t>
@@ -2135,13 +2135,13 @@
     <t xml:space="preserve">3.57090139389038</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66643857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44964194297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55693769454956</t>
+    <t xml:space="preserve">3.66643810272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44964170455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55693793296814</t>
   </si>
   <si>
     <t xml:space="preserve">3.58780384063721</t>
@@ -2156,22 +2156,22 @@
     <t xml:space="preserve">3.46580982208252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54811882972717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56428694725037</t>
+    <t xml:space="preserve">3.54811930656433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56428670883179</t>
   </si>
   <si>
     <t xml:space="preserve">3.59368276596069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62601900100708</t>
+    <t xml:space="preserve">3.6260187625885</t>
   </si>
   <si>
     <t xml:space="preserve">3.57163619995117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57310581207275</t>
+    <t xml:space="preserve">3.57310557365417</t>
   </si>
   <si>
     <t xml:space="preserve">3.44082307815552</t>
@@ -2180,67 +2180,67 @@
     <t xml:space="preserve">3.61720013618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52754163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57457542419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56722664833069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57898497581482</t>
+    <t xml:space="preserve">3.52754139900208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57457566261292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56722688674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57898473739624</t>
   </si>
   <si>
     <t xml:space="preserve">3.75168776512146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68187165260315</t>
+    <t xml:space="preserve">3.68187212944031</t>
   </si>
   <si>
     <t xml:space="preserve">3.70391869544983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60691118240356</t>
+    <t xml:space="preserve">3.60691142082214</t>
   </si>
   <si>
     <t xml:space="preserve">3.61279058456421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66423416137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63189744949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62454915046692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63777756690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6230788230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71126794815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73626279830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60662770271301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66372895240784</t>
+    <t xml:space="preserve">3.66423368453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63189840316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62454891204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63777709007263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62307929992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71126747131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73626232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60662746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66372871398926</t>
   </si>
   <si>
     <t xml:space="preserve">3.63440656661987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68533492088318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75015187263489</t>
+    <t xml:space="preserve">3.6853346824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75015234947205</t>
   </si>
   <si>
     <t xml:space="preserve">3.73008966445923</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">3.80725312232971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77021479606628</t>
+    <t xml:space="preserve">3.77021455764771</t>
   </si>
   <si>
     <t xml:space="preserve">3.81959915161133</t>
@@ -2261,37 +2261,37 @@
     <t xml:space="preserve">3.90447926521301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99707579612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05108976364136</t>
+    <t xml:space="preserve">3.99707555770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05109024047852</t>
   </si>
   <si>
     <t xml:space="preserve">4.02408313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9276282787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88133072853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81651258468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91991209983826</t>
+    <t xml:space="preserve">3.92762875556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88133025169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81651306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9199116230011</t>
   </si>
   <si>
     <t xml:space="preserve">4.08581399917603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05880641937256</t>
+    <t xml:space="preserve">4.05880689620972</t>
   </si>
   <si>
     <t xml:space="preserve">4.10896301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14754486083984</t>
+    <t xml:space="preserve">4.14754438400269</t>
   </si>
   <si>
     <t xml:space="preserve">4.02022457122803</t>
@@ -2300,40 +2300,40 @@
     <t xml:space="preserve">3.96621036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98935890197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03565740585327</t>
+    <t xml:space="preserve">3.98935985565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03565788269043</t>
   </si>
   <si>
     <t xml:space="preserve">4.08967208862305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03179931640625</t>
+    <t xml:space="preserve">4.03179883956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.07038116455078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11282157897949</t>
+    <t xml:space="preserve">4.11282110214233</t>
   </si>
   <si>
     <t xml:space="preserve">4.0549488067627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95463609695435</t>
+    <t xml:space="preserve">3.95463585853577</t>
   </si>
   <si>
     <t xml:space="preserve">3.96235203742981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93534469604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97006797790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97392678260803</t>
+    <t xml:space="preserve">3.9353449344635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97006821632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97392654418945</t>
   </si>
   <si>
     <t xml:space="preserve">4.0742392539978</t>
@@ -2342,10 +2342,10 @@
     <t xml:space="preserve">4.1243953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10510444641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09352970123291</t>
+    <t xml:space="preserve">4.10510492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09353017807007</t>
   </si>
   <si>
     <t xml:space="preserve">4.04723215103149</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">4.12825393676758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25943183898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26714897155762</t>
+    <t xml:space="preserve">4.2594313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26714849472046</t>
   </si>
   <si>
     <t xml:space="preserve">4.21313333511353</t>
@@ -2366,13 +2366,13 @@
     <t xml:space="preserve">4.19770097732544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16297721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16683578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470855712891</t>
+    <t xml:space="preserve">4.16297769546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16683626174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470808029175</t>
   </si>
   <si>
     <t xml:space="preserve">4.28643894195557</t>
@@ -2393,19 +2393,19 @@
     <t xml:space="preserve">4.36360263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30572986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26328992843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24399900436401</t>
+    <t xml:space="preserve">4.30572938919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26329040527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24399852752686</t>
   </si>
   <si>
     <t xml:space="preserve">4.31344652175903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30187225341797</t>
+    <t xml:space="preserve">4.30187177658081</t>
   </si>
   <si>
     <t xml:space="preserve">4.13597011566162</t>
@@ -2417,43 +2417,43 @@
     <t xml:space="preserve">4.18612670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17455148696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18998527526855</t>
+    <t xml:space="preserve">4.17455244064331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1899847984314</t>
   </si>
   <si>
     <t xml:space="preserve">4.11667966842651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17841005325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15526151657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15140295028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15911960601807</t>
+    <t xml:space="preserve">4.17841053009033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15526103973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15140342712402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15911912918091</t>
   </si>
   <si>
     <t xml:space="preserve">4.19384288787842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07809782028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89290499687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97778463363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06266403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94691896438599</t>
+    <t xml:space="preserve">4.07809734344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89290475845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97778534889221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06266498565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94691920280457</t>
   </si>
   <si>
     <t xml:space="preserve">3.9855010509491</t>
@@ -2462,58 +2462,58 @@
     <t xml:space="preserve">3.9816427230835</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88904619216919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71157050132751</t>
+    <t xml:space="preserve">3.88904643058777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71156978607178</t>
   </si>
   <si>
     <t xml:space="preserve">3.7270028591156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82885837554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83194518089294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86589765548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00479173660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95077729225159</t>
+    <t xml:space="preserve">3.8288586139679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83194541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86589789390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0047926902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95077705383301</t>
   </si>
   <si>
     <t xml:space="preserve">4.08195543289185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03951549530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13982772827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17069339752197</t>
+    <t xml:space="preserve">4.03951597213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13982820510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17069387435913</t>
   </si>
   <si>
     <t xml:space="preserve">4.14368629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1321120262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93920254707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90062046051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80879664421082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99321746826172</t>
+    <t xml:space="preserve">4.13211154937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93920302391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90062093734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80879640579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9932177066803</t>
   </si>
   <si>
     <t xml:space="preserve">4.01250839233398</t>
@@ -2534,13 +2534,13 @@
     <t xml:space="preserve">3.86203932762146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8180558681488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80571007728577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85818076133728</t>
+    <t xml:space="preserve">3.81805634498596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80570983886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85818099975586</t>
   </si>
   <si>
     <t xml:space="preserve">3.89676260948181</t>
@@ -2549,22 +2549,22 @@
     <t xml:space="preserve">3.85663795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82114219665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83811902999878</t>
+    <t xml:space="preserve">3.82114291191101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83811807632446</t>
   </si>
   <si>
     <t xml:space="preserve">3.94306135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90833735466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88518834114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83503198623657</t>
+    <t xml:space="preserve">3.90833711624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88518810272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83503150939941</t>
   </si>
   <si>
     <t xml:space="preserve">3.76712799072266</t>
@@ -2573,16 +2573,16 @@
     <t xml:space="preserve">3.76249837875366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8226854801178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79799342155457</t>
+    <t xml:space="preserve">3.82268571853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79799365997314</t>
   </si>
   <si>
     <t xml:space="preserve">3.87361359596252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02794075012207</t>
+    <t xml:space="preserve">4.02794122695923</t>
   </si>
   <si>
     <t xml:space="preserve">4.04337406158447</t>
@@ -2594,28 +2594,28 @@
     <t xml:space="preserve">4.25171566009521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25557374954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31730461120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27100658416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26251888275146</t>
+    <t xml:space="preserve">4.25557327270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3173041343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27100610733032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26251840591431</t>
   </si>
   <si>
     <t xml:space="preserve">4.28721141815186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25634527206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24554204940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14985942840576</t>
+    <t xml:space="preserve">4.25634479522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24554252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1498589515686</t>
   </si>
   <si>
     <t xml:space="preserve">4.12979745864868</t>
@@ -2636,19 +2636,19 @@
     <t xml:space="preserve">4.19924449920654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23628282546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18844127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17763805389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17918109893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18381118774414</t>
+    <t xml:space="preserve">4.23628234863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18844079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17763900756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17918157577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1838116645813</t>
   </si>
   <si>
     <t xml:space="preserve">4.20387411117554</t>
@@ -2657,31 +2657,31 @@
     <t xml:space="preserve">4.18535470962524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21622037887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29338407516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23165369033813</t>
+    <t xml:space="preserve">4.21622085571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29338455200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23165321350098</t>
   </si>
   <si>
     <t xml:space="preserve">4.25017213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23782587051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35048532485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34122562408447</t>
+    <t xml:space="preserve">4.23782634735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35048484802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34122514724731</t>
   </si>
   <si>
     <t xml:space="preserve">4.39369678497314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47086048126221</t>
+    <t xml:space="preserve">4.47086000442505</t>
   </si>
   <si>
     <t xml:space="preserve">4.46610307693481</t>
@@ -2696,19 +2696,19 @@
     <t xml:space="preserve">4.35622835159302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38531303405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37400197982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39016008377075</t>
+    <t xml:space="preserve">4.38531255722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37400245666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39015960693359</t>
   </si>
   <si>
     <t xml:space="preserve">4.37723398208618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40147018432617</t>
+    <t xml:space="preserve">4.40147066116333</t>
   </si>
   <si>
     <t xml:space="preserve">4.45156097412109</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">4.50165128707886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52911949157715</t>
+    <t xml:space="preserve">4.52911996841431</t>
   </si>
   <si>
     <t xml:space="preserve">4.55174112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55012559890747</t>
+    <t xml:space="preserve">4.55012512207031</t>
   </si>
   <si>
     <t xml:space="preserve">4.62122106552124</t>
@@ -2738,13 +2738,13 @@
     <t xml:space="preserve">4.58405733108521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56628322601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54527854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52750444412231</t>
+    <t xml:space="preserve">4.56628370285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54527759552002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52750396728516</t>
   </si>
   <si>
     <t xml:space="preserve">4.45640802383423</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">4.45317697525024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46771955490112</t>
+    <t xml:space="preserve">4.46771907806396</t>
   </si>
   <si>
     <t xml:space="preserve">4.49841928482056</t>
@@ -2771,34 +2771,34 @@
     <t xml:space="preserve">4.50649833679199</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55335712432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4790301322937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52265739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54204654693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54689359664917</t>
+    <t xml:space="preserve">4.55335760116577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47902965545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52265691757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54204702377319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54689407348633</t>
   </si>
   <si>
     <t xml:space="preserve">4.50811433792114</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37884902954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35461235046387</t>
+    <t xml:space="preserve">4.37884950637817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35461187362671</t>
   </si>
   <si>
     <t xml:space="preserve">4.37238645553589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5371994972229</t>
+    <t xml:space="preserve">4.53719902038574</t>
   </si>
   <si>
     <t xml:space="preserve">4.56789922714233</t>
@@ -2807,13 +2807,13 @@
     <t xml:space="preserve">4.61152648925781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6147575378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61637353897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62768411636353</t>
+    <t xml:space="preserve">4.61475801467896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61637401580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62768459320068</t>
   </si>
   <si>
     <t xml:space="preserve">4.59375238418579</t>
@@ -2822,16 +2822,16 @@
     <t xml:space="preserve">4.60829496383667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63091564178467</t>
+    <t xml:space="preserve">4.63091659545898</t>
   </si>
   <si>
     <t xml:space="preserve">4.65676879882812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66484880447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69070148468018</t>
+    <t xml:space="preserve">4.66484832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69070100784302</t>
   </si>
   <si>
     <t xml:space="preserve">4.73271179199219</t>
@@ -2840,16 +2840,16 @@
     <t xml:space="preserve">4.76502799987793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80219173431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79896020889282</t>
+    <t xml:space="preserve">4.80219221115112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79896068572998</t>
   </si>
   <si>
     <t xml:space="preserve">4.76987552642822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82804441452026</t>
+    <t xml:space="preserve">4.82804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.82481336593628</t>
@@ -2858,10 +2858,10 @@
     <t xml:space="preserve">4.84420299530029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80703973770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69554853439331</t>
+    <t xml:space="preserve">4.80703926086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69554805755615</t>
   </si>
   <si>
     <t xml:space="preserve">4.57436275482178</t>
@@ -2870,10 +2870,10 @@
     <t xml:space="preserve">4.53558301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5921368598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54366159439087</t>
+    <t xml:space="preserve">4.59213638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54366207122803</t>
   </si>
   <si>
     <t xml:space="preserve">4.49034070968628</t>
@@ -2882,13 +2882,13 @@
     <t xml:space="preserve">4.49195623397827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48549270629883</t>
+    <t xml:space="preserve">4.48549318313599</t>
   </si>
   <si>
     <t xml:space="preserve">4.45963954925537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51134634017944</t>
+    <t xml:space="preserve">4.51134586334229</t>
   </si>
   <si>
     <t xml:space="preserve">4.52427244186401</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">4.46125555038452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58567380905151</t>
+    <t xml:space="preserve">4.58567333221436</t>
   </si>
   <si>
     <t xml:space="preserve">4.63576364517212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58890438079834</t>
+    <t xml:space="preserve">4.5889048576355</t>
   </si>
   <si>
     <t xml:space="preserve">4.65353775024414</t>
@@ -2912,7 +2912,7 @@
     <t xml:space="preserve">4.57113075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4757981300354</t>
+    <t xml:space="preserve">4.47579860687256</t>
   </si>
   <si>
     <t xml:space="preserve">4.42247629165649</t>
@@ -2921,16 +2921,16 @@
     <t xml:space="preserve">4.46933507919312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43217134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47095012664795</t>
+    <t xml:space="preserve">4.43217086791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47095060348511</t>
   </si>
   <si>
     <t xml:space="preserve">4.48387718200684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39985513687134</t>
+    <t xml:space="preserve">4.39985466003418</t>
   </si>
   <si>
     <t xml:space="preserve">4.37076997756958</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">4.39662313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41116523742676</t>
+    <t xml:space="preserve">4.41116571426392</t>
   </si>
   <si>
     <t xml:space="preserve">4.51457738876343</t>
@@ -2951,16 +2951,16 @@
     <t xml:space="preserve">4.43540287017822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50003528594971</t>
+    <t xml:space="preserve">4.50003576278687</t>
   </si>
   <si>
     <t xml:space="preserve">4.53881454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6131420135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63253211975098</t>
+    <t xml:space="preserve">4.61314249038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63253164291382</t>
   </si>
   <si>
     <t xml:space="preserve">4.60021543502808</t>
@@ -2969,28 +2969,28 @@
     <t xml:space="preserve">4.55658864974976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57920980453491</t>
+    <t xml:space="preserve">4.57921028137207</t>
   </si>
   <si>
     <t xml:space="preserve">4.52588844299316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48064565658569</t>
+    <t xml:space="preserve">4.48064613342285</t>
   </si>
   <si>
     <t xml:space="preserve">4.53235149383545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44832897186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50488328933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71978569030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72301816940308</t>
+    <t xml:space="preserve">4.44832944869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71978616714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72301721572876</t>
   </si>
   <si>
     <t xml:space="preserve">4.65838479995728</t>
@@ -3002,16 +3002,16 @@
     <t xml:space="preserve">4.65515327453613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64384269714355</t>
+    <t xml:space="preserve">4.6438422203064</t>
   </si>
   <si>
     <t xml:space="preserve">4.70201206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585348129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70362710952759</t>
+    <t xml:space="preserve">4.68585395812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70362758636475</t>
   </si>
   <si>
     <t xml:space="preserve">4.66807985305786</t>
@@ -3023,7 +3023,7 @@
     <t xml:space="preserve">4.7262487411499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76179647445679</t>
+    <t xml:space="preserve">4.76179695129395</t>
   </si>
   <si>
     <t xml:space="preserve">4.75048637390137</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">4.84905004501343</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87490320205688</t>
+    <t xml:space="preserve">4.8749041557312</t>
   </si>
   <si>
     <t xml:space="preserve">4.88944578170776</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">4.91853046417236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85874509811401</t>
+    <t xml:space="preserve">4.85874557495117</t>
   </si>
   <si>
     <t xml:space="preserve">4.83127641677856</t>
@@ -3050,28 +3050,28 @@
     <t xml:space="preserve">4.66161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64061117172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72948026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74402236938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76018142700195</t>
+    <t xml:space="preserve">4.64061069488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7294807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74402332305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76018047332764</t>
   </si>
   <si>
     <t xml:space="preserve">4.74079132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79734468460083</t>
+    <t xml:space="preserve">4.79734516143799</t>
   </si>
   <si>
     <t xml:space="preserve">4.71655368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79572916030884</t>
+    <t xml:space="preserve">4.79572868347168</t>
   </si>
   <si>
     <t xml:space="preserve">4.83450841903687</t>
@@ -3080,19 +3080,19 @@
     <t xml:space="preserve">4.74563884735107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50973033905029</t>
+    <t xml:space="preserve">4.50972986221313</t>
   </si>
   <si>
     <t xml:space="preserve">4.46448755264282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57759428024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62930059432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55982065200806</t>
+    <t xml:space="preserve">4.57759380340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62930011749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5598201751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.54850959777832</t>
@@ -3110,25 +3110,25 @@
     <t xml:space="preserve">4.32068014144897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55820465087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51780891418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49518775939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41762924194336</t>
+    <t xml:space="preserve">4.55820512771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51780939102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49518823623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4176287651062</t>
   </si>
   <si>
     <t xml:space="preserve">4.48872470855713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43378686904907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7052435874939</t>
+    <t xml:space="preserve">4.43378734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70524311065674</t>
   </si>
   <si>
     <t xml:space="preserve">4.7302885055542</t>
@@ -3140,52 +3140,52 @@
     <t xml:space="preserve">4.77472305297852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89590930938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94034337997437</t>
+    <t xml:space="preserve">4.89590883255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94034385681152</t>
   </si>
   <si>
     <t xml:space="preserve">4.91610670089722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91206693649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00497674942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04537105560303</t>
+    <t xml:space="preserve">4.91206741333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00497627258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04537153244019</t>
   </si>
   <si>
     <t xml:space="preserve">5.15039920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08980655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06556987762451</t>
+    <t xml:space="preserve">5.08980703353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0655689239502</t>
   </si>
   <si>
     <t xml:space="preserve">4.9807391166687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96054172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99285793304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01709461212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00093698501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01305532455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97266006469727</t>
+    <t xml:space="preserve">4.96054124832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99285745620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01709508895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00093746185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01305484771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97266054153442</t>
   </si>
   <si>
     <t xml:space="preserve">4.89994859695435</t>
@@ -3194,13 +3194,13 @@
     <t xml:space="preserve">4.94842290878296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92014646530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10596513748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05345058441162</t>
+    <t xml:space="preserve">4.92014598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10596466064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05345106124878</t>
   </si>
   <si>
     <t xml:space="preserve">5.16251802444458</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">5.20222187042236</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11777067184448</t>
+    <t xml:space="preserve">5.11777019500732</t>
   </si>
   <si>
     <t xml:space="preserve">5.15577411651611</t>
@@ -3230,16 +3230,16 @@
     <t xml:space="preserve">5.02909660339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04598665237427</t>
+    <t xml:space="preserve">5.04598617553711</t>
   </si>
   <si>
     <t xml:space="preserve">5.02487373352051</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87286043167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70395755767822</t>
+    <t xml:space="preserve">4.8728609085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70395803451538</t>
   </si>
   <si>
     <t xml:space="preserve">4.58572483062744</t>
@@ -3248,16 +3248,16 @@
     <t xml:space="preserve">4.54772233963013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60261583328247</t>
+    <t xml:space="preserve">4.60261487960815</t>
   </si>
   <si>
     <t xml:space="preserve">4.53505373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71662473678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64906406402588</t>
+    <t xml:space="preserve">4.71662521362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64906358718872</t>
   </si>
   <si>
     <t xml:space="preserve">4.5097188949585</t>
@@ -3266,13 +3266,13 @@
     <t xml:space="preserve">4.34081506729126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45904779434204</t>
+    <t xml:space="preserve">4.45904731750488</t>
   </si>
   <si>
     <t xml:space="preserve">4.69551229476929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63217353820801</t>
+    <t xml:space="preserve">4.63217401504517</t>
   </si>
   <si>
     <t xml:space="preserve">4.7419605255127</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">4.73773813247681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69128942489624</t>
+    <t xml:space="preserve">4.6912899017334</t>
   </si>
   <si>
     <t xml:space="preserve">4.72929286956787</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">4.64061880111694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61950540542603</t>
+    <t xml:space="preserve">4.61950588226318</t>
   </si>
   <si>
     <t xml:space="preserve">4.61106014251709</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">4.64484119415283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45060253143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51816368103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45482540130615</t>
+    <t xml:space="preserve">4.45060205459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51816320419312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45482444763184</t>
   </si>
   <si>
     <t xml:space="preserve">4.38726377487183</t>
@@ -3317,22 +3317,22 @@
     <t xml:space="preserve">4.46327018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59417057037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67017698287964</t>
+    <t xml:space="preserve">4.59417009353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67017650604248</t>
   </si>
   <si>
     <t xml:space="preserve">4.71240234375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61528301239014</t>
+    <t xml:space="preserve">4.61528348922729</t>
   </si>
   <si>
     <t xml:space="preserve">4.62795114517212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6575083732605</t>
+    <t xml:space="preserve">4.65750885009766</t>
   </si>
   <si>
     <t xml:space="preserve">4.65328645706177</t>
@@ -3344,16 +3344,16 @@
     <t xml:space="preserve">4.6363959312439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77996397018433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80107641220093</t>
+    <t xml:space="preserve">4.77996349334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80107688903809</t>
   </si>
   <si>
     <t xml:space="preserve">4.72506999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77151870727539</t>
+    <t xml:space="preserve">4.77151918411255</t>
   </si>
   <si>
     <t xml:space="preserve">4.70817995071411</t>
@@ -3365,16 +3365,16 @@
     <t xml:space="preserve">4.53927659988403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47593784332275</t>
+    <t xml:space="preserve">4.47593832015991</t>
   </si>
   <si>
     <t xml:space="preserve">4.33659267425537</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31125688552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42104387283325</t>
+    <t xml:space="preserve">4.31125736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42104434967041</t>
   </si>
   <si>
     <t xml:space="preserve">4.29436683654785</t>
@@ -3386,10 +3386,10 @@
     <t xml:space="preserve">4.25636339187622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39148569107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41259956359863</t>
+    <t xml:space="preserve">4.39148616790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41259908676147</t>
   </si>
   <si>
     <t xml:space="preserve">4.4041543006897</t>
@@ -3401,10 +3401,10 @@
     <t xml:space="preserve">4.35770559310913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3197021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36192846298218</t>
+    <t xml:space="preserve">4.31970262527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36192798614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.27747631072998</t>
@@ -3422,25 +3422,25 @@
     <t xml:space="preserve">4.14319801330566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07225894927979</t>
+    <t xml:space="preserve">4.07225847244263</t>
   </si>
   <si>
     <t xml:space="preserve">4.02665519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03341102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12630844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22680616378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10097217559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.036789894104</t>
+    <t xml:space="preserve">4.03341150283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12630796432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22680521011353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1009726524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03678941726685</t>
   </si>
   <si>
     <t xml:space="preserve">4.02834415435791</t>
@@ -3452,10 +3452,10 @@
     <t xml:space="preserve">3.88984346389771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84761762619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97091674804688</t>
+    <t xml:space="preserve">3.84761786460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97091722488403</t>
   </si>
   <si>
     <t xml:space="preserve">4.06719160079956</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">4.04016733169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09421634674072</t>
+    <t xml:space="preserve">4.09421682357788</t>
   </si>
   <si>
     <t xml:space="preserve">4.01483201980591</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">4.15333271026611</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26480913162231</t>
+    <t xml:space="preserve">4.26480865478516</t>
   </si>
   <si>
     <t xml:space="preserve">4.49282836914062</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">4.75462818145752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73351573944092</t>
+    <t xml:space="preserve">4.73351526260376</t>
   </si>
   <si>
     <t xml:space="preserve">4.75040578842163</t>
@@ -3506,28 +3506,28 @@
     <t xml:space="preserve">4.76307344436646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76729583740234</t>
+    <t xml:space="preserve">4.7672963142395</t>
   </si>
   <si>
     <t xml:space="preserve">4.75885105133057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74618339538574</t>
+    <t xml:space="preserve">4.74618291854858</t>
   </si>
   <si>
     <t xml:space="preserve">4.55194425582886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5308313369751</t>
+    <t xml:space="preserve">4.53083086013794</t>
   </si>
   <si>
     <t xml:space="preserve">4.48016023635864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42948913574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52660894393921</t>
+    <t xml:space="preserve">4.42948961257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52660846710205</t>
   </si>
   <si>
     <t xml:space="preserve">4.44637966156006</t>
@@ -3536,19 +3536,19 @@
     <t xml:space="preserve">4.5561671257019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51394081115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56883430480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78418684005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58994770050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52238655090332</t>
+    <t xml:space="preserve">4.51394128799438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56883478164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78418636322021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58994722366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52238607406616</t>
   </si>
   <si>
     <t xml:space="preserve">4.62372827529907</t>
@@ -3563,16 +3563,16 @@
     <t xml:space="preserve">4.35348320007324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42526626586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47171497344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56038951873779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90241813659668</t>
+    <t xml:space="preserve">4.4252667427063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47171545028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56038999557495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90241861343384</t>
   </si>
   <si>
     <t xml:space="preserve">4.97842502593994</t>
@@ -3590,10 +3590,10 @@
     <t xml:space="preserve">4.99109268188477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09243488311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01220560073853</t>
+    <t xml:space="preserve">5.09243535995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01220607757568</t>
   </si>
   <si>
     <t xml:space="preserve">4.98687028884888</t>
@@ -3602,7 +3602,7 @@
     <t xml:space="preserve">4.91930913925171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95731210708618</t>
+    <t xml:space="preserve">4.95731258392334</t>
   </si>
   <si>
     <t xml:space="preserve">5.00798320770264</t>
@@ -3611,10 +3611,10 @@
     <t xml:space="preserve">4.86019325256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94042158126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93619966506958</t>
+    <t xml:space="preserve">4.94042205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93619918823242</t>
   </si>
   <si>
     <t xml:space="preserve">4.96575784683228</t>
@@ -3623,16 +3623,16 @@
     <t xml:space="preserve">4.96153497695923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00376081466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96998071670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83908033370972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88975143432617</t>
+    <t xml:space="preserve">5.00376129150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96997976303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83907985687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88975095748901</t>
   </si>
   <si>
     <t xml:space="preserve">4.82535934448242</t>
@@ -4130,9 +4130,6 @@
     <t xml:space="preserve">4.52464294433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54170989990234</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.53602123260498</t>
   </si>
   <si>
@@ -4920,6 +4917,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.23999977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09000015258789</t>
   </si>
 </sst>
 </file>
@@ -56132,7 +56132,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>1372</v>
+        <v>576</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -56158,7 +56158,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1958" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -56210,7 +56210,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G1960" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -56262,7 +56262,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G1962" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -56288,7 +56288,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1963" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -56314,7 +56314,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G1964" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -56340,7 +56340,7 @@
         <v>4.92799997329712</v>
       </c>
       <c r="G1965" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -56366,7 +56366,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1966" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -56392,7 +56392,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1967" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -56418,7 +56418,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G1968" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -56444,7 +56444,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1969" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -56470,7 +56470,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G1970" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -56496,7 +56496,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G1971" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56522,7 +56522,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G1972" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -56548,7 +56548,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G1973" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -56574,7 +56574,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G1974" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -56600,7 +56600,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1975" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -56626,7 +56626,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G1976" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -56652,7 +56652,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1977" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -56678,7 +56678,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1978" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -56756,7 +56756,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G1981" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -56782,7 +56782,7 @@
         <v>4.98199987411499</v>
       </c>
       <c r="G1982" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -56808,7 +56808,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1983" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -56834,7 +56834,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1984" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56860,7 +56860,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G1985" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56886,7 +56886,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1986" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56912,7 +56912,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1987" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56964,7 +56964,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1989" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56990,7 +56990,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G1990" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -57016,7 +57016,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1991" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -57042,7 +57042,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -57068,7 +57068,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1993" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -57094,7 +57094,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1994" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -57120,7 +57120,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1995" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -57146,7 +57146,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1996" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -57172,7 +57172,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G1997" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -57198,7 +57198,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G1998" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -57224,7 +57224,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G1999" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57250,7 +57250,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G2000" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57276,7 +57276,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -57302,7 +57302,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G2002" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -57328,7 +57328,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -57354,7 +57354,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2004" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -57380,7 +57380,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G2005" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -57406,7 +57406,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G2006" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -57432,7 +57432,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G2007" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -57458,7 +57458,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2008" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -57484,7 +57484,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G2009" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -57510,7 +57510,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2010" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -57536,7 +57536,7 @@
         <v>5.5</v>
       </c>
       <c r="G2011" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -57562,7 +57562,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2012" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -57588,7 +57588,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G2013" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -57614,7 +57614,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2014" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -57640,7 +57640,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2015" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -57666,7 +57666,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2016" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -57692,7 +57692,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G2017" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -57718,7 +57718,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G2018" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -57744,7 +57744,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2019" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57770,7 +57770,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G2020" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -57796,7 +57796,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2021" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -57822,7 +57822,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G2022" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -57848,7 +57848,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2023" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57874,7 +57874,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G2024" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57900,7 +57900,7 @@
         <v>5.875</v>
       </c>
       <c r="G2025" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57926,7 +57926,7 @@
         <v>5.79500007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57952,7 +57952,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G2027" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57978,7 +57978,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2028" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -58004,7 +58004,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G2029" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -58030,7 +58030,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G2030" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -58056,7 +58056,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2031" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -58082,7 +58082,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2032" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -58108,7 +58108,7 @@
         <v>5.625</v>
       </c>
       <c r="G2033" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -58134,7 +58134,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G2034" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -58160,7 +58160,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2035" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58186,7 +58186,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2036" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58212,7 +58212,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2037" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58238,7 +58238,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G2038" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58264,7 +58264,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G2039" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58290,7 +58290,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G2040" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -58316,7 +58316,7 @@
         <v>5.5</v>
       </c>
       <c r="G2041" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -58342,7 +58342,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G2042" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -58368,7 +58368,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2043" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -58394,7 +58394,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G2044" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58420,7 +58420,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G2045" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -58446,7 +58446,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G2046" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -58472,7 +58472,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G2047" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58498,7 +58498,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2048" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -58524,7 +58524,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G2049" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -58550,7 +58550,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G2050" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -58576,7 +58576,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2051" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -58602,7 +58602,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -58628,7 +58628,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2053" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -58654,7 +58654,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2054" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -58680,7 +58680,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G2055" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -58706,7 +58706,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G2056" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -58732,7 +58732,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G2057" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -58758,7 +58758,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G2058" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -58784,7 +58784,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G2059" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -58810,7 +58810,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G2060" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -58836,7 +58836,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G2061" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58862,7 +58862,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G2062" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58888,7 +58888,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G2063" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58914,7 +58914,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2064" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58940,7 +58940,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2065" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58966,7 +58966,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2066" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58992,7 +58992,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2067" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -59018,7 +59018,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G2068" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -59044,7 +59044,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2069" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -59070,7 +59070,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2070" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -59096,7 +59096,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2071" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -59122,7 +59122,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2072" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -59148,7 +59148,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G2073" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -59174,7 +59174,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2074" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -59200,7 +59200,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G2075" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -59226,7 +59226,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2076" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59252,7 +59252,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2077" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59278,7 +59278,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G2078" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -59304,7 +59304,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G2079" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -59330,7 +59330,7 @@
         <v>5.375</v>
       </c>
       <c r="G2080" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -59356,7 +59356,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2081" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -59382,7 +59382,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G2082" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59408,7 +59408,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G2083" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -59434,7 +59434,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2084" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -59460,7 +59460,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G2085" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59486,7 +59486,7 @@
         <v>5.625</v>
       </c>
       <c r="G2086" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -59512,7 +59512,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G2087" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -59538,7 +59538,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2088" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -59564,7 +59564,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G2089" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -59590,7 +59590,7 @@
         <v>5.63500022888184</v>
       </c>
       <c r="G2090" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -59616,7 +59616,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G2091" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -59642,7 +59642,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G2092" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -59668,7 +59668,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G2093" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -59694,7 +59694,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2094" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -59720,7 +59720,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G2095" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -59746,7 +59746,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G2096" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -59772,7 +59772,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G2097" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -59798,7 +59798,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2098" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -59824,7 +59824,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2099" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59850,7 +59850,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G2100" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59876,7 +59876,7 @@
         <v>5.875</v>
       </c>
       <c r="G2101" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59902,7 +59902,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G2102" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59928,7 +59928,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G2103" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59954,7 +59954,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G2104" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59980,7 +59980,7 @@
         <v>5.90500020980835</v>
       </c>
       <c r="G2105" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -60006,7 +60006,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G2106" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -60032,7 +60032,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G2107" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -60058,7 +60058,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2108" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -60084,7 +60084,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G2109" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -60110,7 +60110,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G2110" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60136,7 +60136,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G2111" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -60162,7 +60162,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G2112" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -60188,7 +60188,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G2113" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -60214,7 +60214,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G2114" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60240,7 +60240,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G2115" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60266,7 +60266,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G2116" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -60292,7 +60292,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G2117" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -60318,7 +60318,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G2118" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -60344,7 +60344,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -60370,7 +60370,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G2120" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -60396,7 +60396,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G2121" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60422,7 +60422,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G2122" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60448,7 +60448,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G2123" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60474,7 +60474,7 @@
         <v>6.125</v>
       </c>
       <c r="G2124" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -60500,7 +60500,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G2125" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -60526,7 +60526,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G2126" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -60552,7 +60552,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G2127" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -60578,7 +60578,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G2128" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -60604,7 +60604,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G2129" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -60630,7 +60630,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G2130" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -60656,7 +60656,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G2131" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -60682,7 +60682,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G2132" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -60708,7 +60708,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G2133" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -60734,7 +60734,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G2134" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -60760,7 +60760,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G2135" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -60786,7 +60786,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G2136" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -60812,7 +60812,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G2137" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -60838,7 +60838,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G2138" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60864,7 +60864,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G2139" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60890,7 +60890,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2140" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60916,7 +60916,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G2141" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60942,7 +60942,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G2142" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60968,7 +60968,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2143" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60994,7 +60994,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G2144" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -61020,7 +61020,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G2145" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -61046,7 +61046,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G2146" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -61072,7 +61072,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G2147" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -61098,7 +61098,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2148" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61124,7 +61124,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G2149" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -61150,7 +61150,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G2150" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -61176,7 +61176,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G2151" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -61202,7 +61202,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G2152" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -61228,7 +61228,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G2153" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61254,7 +61254,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G2154" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61280,7 +61280,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2155" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -61306,7 +61306,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2156" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -61332,7 +61332,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -61358,7 +61358,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G2158" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -61384,7 +61384,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G2159" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61410,7 +61410,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G2160" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61436,7 +61436,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2161" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61462,7 +61462,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G2162" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61488,7 +61488,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2163" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -61514,7 +61514,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2164" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -61540,7 +61540,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G2165" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -61566,7 +61566,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G2166" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -61592,7 +61592,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2167" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -61618,7 +61618,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G2168" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -61644,7 +61644,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G2169" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -61670,7 +61670,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G2170" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -61696,7 +61696,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G2171" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -61722,7 +61722,7 @@
         <v>6.72816181182861</v>
       </c>
       <c r="G2172" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -61748,7 +61748,7 @@
         <v>6.69060087203979</v>
       </c>
       <c r="G2173" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -61774,7 +61774,7 @@
         <v>6.66712522506714</v>
       </c>
       <c r="G2174" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61800,7 +61800,7 @@
         <v>6.61547899246216</v>
       </c>
       <c r="G2175" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -61826,7 +61826,7 @@
         <v>6.78919982910156</v>
       </c>
       <c r="G2176" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61852,7 +61852,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G2177" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61878,7 +61878,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G2178" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61904,7 +61904,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2179" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61930,7 +61930,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61956,7 +61956,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G2181" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61982,7 +61982,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G2182" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62008,7 +62008,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2183" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62034,7 +62034,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G2184" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62060,7 +62060,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2185" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62086,7 +62086,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G2186" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62112,7 +62112,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2187" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62138,7 +62138,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G2188" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62164,7 +62164,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2189" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62190,7 +62190,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G2190" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62216,7 +62216,7 @@
         <v>7</v>
       </c>
       <c r="G2191" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62242,7 +62242,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2192" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62268,7 +62268,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2193" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62294,7 +62294,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G2194" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62320,7 +62320,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G2195" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62346,7 +62346,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2196" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62372,7 +62372,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2197" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62398,7 +62398,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2198" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62424,7 +62424,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G2199" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62450,7 +62450,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2200" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62476,7 +62476,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2201" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62502,7 +62502,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G2202" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62528,7 +62528,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G2203" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -62554,7 +62554,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -62580,7 +62580,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2205" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -62606,7 +62606,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2206" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -62632,7 +62632,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2207" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -62658,7 +62658,7 @@
         <v>6.88500022888184</v>
       </c>
       <c r="G2208" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -62684,7 +62684,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G2209" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62710,7 +62710,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G2210" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62736,7 +62736,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2211" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -62762,7 +62762,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G2212" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62788,7 +62788,7 @@
         <v>7.25</v>
       </c>
       <c r="G2213" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -62814,7 +62814,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2214" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -62840,7 +62840,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G2215" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62866,7 +62866,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G2216" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62892,7 +62892,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2217" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62918,7 +62918,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G2218" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62944,7 +62944,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G2219" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62970,7 +62970,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G2220" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -62996,7 +62996,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2221" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63022,7 +63022,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2222" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63048,7 +63048,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2223" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63074,7 +63074,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2224" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63100,7 +63100,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2225" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63126,7 +63126,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G2226" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63152,7 +63152,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G2227" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63178,7 +63178,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G2228" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63204,7 +63204,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G2229" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63230,7 +63230,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2230" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63256,7 +63256,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G2231" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63282,7 +63282,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2232" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63308,7 +63308,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2233" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63334,7 +63334,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G2234" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63360,7 +63360,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2235" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63386,7 +63386,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G2236" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63412,7 +63412,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2237" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63438,7 +63438,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63464,7 +63464,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G2239" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63490,7 +63490,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G2240" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63516,7 +63516,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G2241" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63542,7 +63542,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G2242" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -63568,7 +63568,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2243" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -63594,7 +63594,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G2244" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -63620,7 +63620,7 @@
         <v>7.625</v>
       </c>
       <c r="G2245" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -63646,7 +63646,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G2246" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -63672,7 +63672,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G2247" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -63698,7 +63698,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2248" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63724,7 +63724,7 @@
         <v>7.625</v>
       </c>
       <c r="G2249" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63750,7 +63750,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G2250" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63776,7 +63776,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2251" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63802,7 +63802,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2252" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63828,7 +63828,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2253" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63854,7 +63854,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G2254" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63880,7 +63880,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2255" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63906,7 +63906,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63932,7 +63932,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G2257" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63958,7 +63958,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G2258" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63984,7 +63984,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G2259" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64010,7 +64010,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G2260" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64036,7 +64036,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G2261" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64062,7 +64062,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G2262" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64088,7 +64088,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G2263" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64114,7 +64114,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G2264" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64140,7 +64140,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G2265" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64166,7 +64166,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2266" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64192,7 +64192,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2267" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64218,7 +64218,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G2268" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64244,7 +64244,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G2269" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64270,7 +64270,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G2270" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64296,7 +64296,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2271" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64322,7 +64322,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G2272" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64348,7 +64348,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2273" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64374,7 +64374,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G2274" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64400,7 +64400,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G2275" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64426,7 +64426,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G2276" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64452,7 +64452,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2277" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64478,7 +64478,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2278" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64504,7 +64504,7 @@
         <v>8.72500038146973</v>
       </c>
       <c r="G2279" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -64530,7 +64530,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2280" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64556,7 +64556,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G2281" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64582,7 +64582,7 @@
         <v>8.875</v>
       </c>
       <c r="G2282" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64608,7 +64608,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G2283" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64616,7 +64616,7 @@
     </row>
     <row r="2284">
       <c r="A2284" s="1" t="n">
-        <v>45960.6911342593</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2284" t="n">
         <v>5929188</v>
@@ -64634,9 +64634,35 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G2284" t="s">
+        <v>1634</v>
+      </c>
+      <c r="H2284" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" s="1" t="n">
+        <v>45961.6941087963</v>
+      </c>
+      <c r="B2285" t="n">
+        <v>4894459</v>
+      </c>
+      <c r="C2285" t="n">
+        <v>9.34000015258789</v>
+      </c>
+      <c r="D2285" t="n">
+        <v>9.04500007629395</v>
+      </c>
+      <c r="E2285" t="n">
+        <v>9.32999992370605</v>
+      </c>
+      <c r="F2285" t="n">
+        <v>9.09000015258789</v>
+      </c>
+      <c r="G2285" t="s">
         <v>1635</v>
       </c>
-      <c r="H2284" t="s">
+      <c r="H2285" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58873605728149</t>
+    <t xml:space="preserve">2.58873581886292</t>
   </si>
   <si>
     <t xml:space="preserve">IG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5013575553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32790613174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16488695144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17271184921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09315896034241</t>
+    <t xml:space="preserve">2.50135779380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32790589332581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16488718986511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17271208763123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09315919876099</t>
   </si>
   <si>
     <t xml:space="preserve">2.06185936927795</t>
@@ -71,28 +71,28 @@
     <t xml:space="preserve">2.06055521965027</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04360151290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.104896068573</t>
+    <t xml:space="preserve">2.04360127449036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10489630699158</t>
   </si>
   <si>
     <t xml:space="preserve">2.1296751499176</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14532518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17923283576965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2000994682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20140337944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17792868614197</t>
+    <t xml:space="preserve">2.14532494544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17923307418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20009922981262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20140361785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17792844772339</t>
   </si>
   <si>
     <t xml:space="preserve">2.13228344917297</t>
@@ -101,79 +101,79 @@
     <t xml:space="preserve">2.09837555885315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22357416152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29138994216919</t>
+    <t xml:space="preserve">2.22357392311096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29138970375061</t>
   </si>
   <si>
     <t xml:space="preserve">2.33181834220886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29791045188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2379195690155</t>
+    <t xml:space="preserve">2.29791021347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23791933059692</t>
   </si>
   <si>
     <t xml:space="preserve">2.30051875114441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30443096160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37094235420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34616422653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39572167396545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45571208000183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39702582359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38007187843323</t>
+    <t xml:space="preserve">2.30443072319031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37094283103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3461639881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39572143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45571255683899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39702606201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38007211685181</t>
   </si>
   <si>
     <t xml:space="preserve">2.39441752433777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42180466651917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41006708145142</t>
+    <t xml:space="preserve">2.42180442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41006731987</t>
   </si>
   <si>
     <t xml:space="preserve">2.43093371391296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43745446205139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701214790344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45049571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49092435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4452793598175</t>
+    <t xml:space="preserve">2.43745422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701167106628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45049548149109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4909245967865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44527959823608</t>
   </si>
   <si>
     <t xml:space="preserve">2.46614575386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43223786354065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4400622844696</t>
+    <t xml:space="preserve">2.43223762512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44006252288818</t>
   </si>
   <si>
     <t xml:space="preserve">2.47788286209106</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">2.48831629753113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41789197921753</t>
+    <t xml:space="preserve">2.41789221763611</t>
   </si>
   <si>
     <t xml:space="preserve">2.43484616279602</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">2.27573990821838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29530239105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.312255859375</t>
+    <t xml:space="preserve">2.29530215263367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31225609779358</t>
   </si>
   <si>
     <t xml:space="preserve">2.38137602806091</t>
@@ -224,19 +224,19 @@
     <t xml:space="preserve">2.44919180870056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46744966506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47397017478943</t>
+    <t xml:space="preserve">2.467449426651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47397065162659</t>
   </si>
   <si>
     <t xml:space="preserve">2.48440361022949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46353721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47266626358032</t>
+    <t xml:space="preserve">2.4635374546051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4726665019989</t>
   </si>
   <si>
     <t xml:space="preserve">2.47136211395264</t>
@@ -245,52 +245,52 @@
     <t xml:space="preserve">2.44788718223572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49614119529724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49744534492493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51570320129395</t>
+    <t xml:space="preserve">2.49614143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49744510650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51570343971252</t>
   </si>
   <si>
     <t xml:space="preserve">2.53135323524475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51439881324768</t>
+    <t xml:space="preserve">2.51439905166626</t>
   </si>
   <si>
     <t xml:space="preserve">2.53656983375549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52744078636169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54830718040466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55091524124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53787398338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58612728118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57699823379517</t>
+    <t xml:space="preserve">2.52744054794312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54830694198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55091500282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5378737449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58612751960754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57699847221375</t>
   </si>
   <si>
     <t xml:space="preserve">2.59786486625671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438537597656</t>
+    <t xml:space="preserve">2.60438561439514</t>
   </si>
   <si>
     <t xml:space="preserve">2.57308578491211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66959309577942</t>
+    <t xml:space="preserve">2.66959285736084</t>
   </si>
   <si>
     <t xml:space="preserve">2.68393874168396</t>
@@ -305,13 +305,13 @@
     <t xml:space="preserve">2.64742207527161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68132996559143</t>
+    <t xml:space="preserve">2.68133020401001</t>
   </si>
   <si>
     <t xml:space="preserve">2.67480969429016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63438105583191</t>
+    <t xml:space="preserve">2.63438129425049</t>
   </si>
   <si>
     <t xml:space="preserve">2.64350986480713</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">2.69567584991455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69958853721619</t>
+    <t xml:space="preserve">2.69958829879761</t>
   </si>
   <si>
     <t xml:space="preserve">2.67872190475464</t>
@@ -329,64 +329,64 @@
     <t xml:space="preserve">2.73480010032654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.772620677948</t>
+    <t xml:space="preserve">2.77262043952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.75436234474182</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7126293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70089244842529</t>
+    <t xml:space="preserve">2.71262955665588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70089268684387</t>
   </si>
   <si>
     <t xml:space="preserve">2.70219659805298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66176772117615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78305411338806</t>
+    <t xml:space="preserve">2.66176795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78305387496948</t>
   </si>
   <si>
     <t xml:space="preserve">2.7452335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69306755065918</t>
+    <t xml:space="preserve">2.6930673122406</t>
   </si>
   <si>
     <t xml:space="preserve">2.71915054321289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70610904693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74914622306824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77783727645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8352198600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84043645858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88738560676575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89651465415955</t>
+    <t xml:space="preserve">2.70610928535461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74914598464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77783751487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83521962165833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84043669700623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88738584518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89651489257812</t>
   </si>
   <si>
     <t xml:space="preserve">2.85347747802734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91477274894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00867176055908</t>
+    <t xml:space="preserve">2.91477251052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00867128372192</t>
   </si>
   <si>
     <t xml:space="preserve">3.02040886878967</t>
@@ -395,19 +395,19 @@
     <t xml:space="preserve">2.96824288368225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00736737251282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05822920799255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09885358810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15591287612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09613704681396</t>
+    <t xml:space="preserve">3.0073676109314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05822944641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09885406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15591311454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09613680839539</t>
   </si>
   <si>
     <t xml:space="preserve">3.13825154304504</t>
@@ -416,16 +416,16 @@
     <t xml:space="preserve">3.0907027721405</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9765841960907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13417673110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20074558258057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24965333938599</t>
+    <t xml:space="preserve">2.97658443450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13417625427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20074534416199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24965310096741</t>
   </si>
   <si>
     <t xml:space="preserve">3.28769278526306</t>
@@ -434,34 +434,34 @@
     <t xml:space="preserve">3.23063373565674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24557757377625</t>
+    <t xml:space="preserve">3.24557781219482</t>
   </si>
   <si>
     <t xml:space="preserve">3.22248196601868</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25101137161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1871600151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09477877616882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11379766464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19938683509827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10428810119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12059092521667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15727162361145</t>
+    <t xml:space="preserve">3.25101161003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18715977668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09477829933167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11379814147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19938635826111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10428857803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12059116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15727114677429</t>
   </si>
   <si>
     <t xml:space="preserve">3.16270589828491</t>
@@ -470,19 +470,19 @@
     <t xml:space="preserve">3.14504504203796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03907799720764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02820992469788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96707487106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00375556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0363609790802</t>
+    <t xml:space="preserve">3.03907823562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0282096862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96707463264465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00375533103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03636050224304</t>
   </si>
   <si>
     <t xml:space="preserve">3.02005815505981</t>
@@ -491,79 +491,79 @@
     <t xml:space="preserve">2.977942943573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98609447479248</t>
+    <t xml:space="preserve">2.9860942363739</t>
   </si>
   <si>
     <t xml:space="preserve">2.99560403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07575869560242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08390974998474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12466621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10836362838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12874174118042</t>
+    <t xml:space="preserve">3.07575845718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0839102268219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12466645240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10836410522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12874245643616</t>
   </si>
   <si>
     <t xml:space="preserve">3.17900848388672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17221546173096</t>
+    <t xml:space="preserve">3.17221570014954</t>
   </si>
   <si>
     <t xml:space="preserve">3.12602543830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15863060951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2251992225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26052212715149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25237059593201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27682447433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30671238899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30263686180115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28089952468872</t>
+    <t xml:space="preserve">3.15863037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22519946098328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26052165031433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25237035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27682423591614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30671215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30263638496399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2808997631073</t>
   </si>
   <si>
     <t xml:space="preserve">3.21025514602661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2836172580719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29856109619141</t>
+    <t xml:space="preserve">3.28361678123474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29856133460999</t>
   </si>
   <si>
     <t xml:space="preserve">3.28225803375244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26323866844177</t>
+    <t xml:space="preserve">3.26323890686035</t>
   </si>
   <si>
     <t xml:space="preserve">3.25644588470459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27003145217896</t>
+    <t xml:space="preserve">3.27003169059753</t>
   </si>
   <si>
     <t xml:space="preserve">3.24693608283997</t>
@@ -575,28 +575,28 @@
     <t xml:space="preserve">3.21976470947266</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24150156974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26188015937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23470878601074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1980288028717</t>
+    <t xml:space="preserve">3.24150133132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26187992095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23470950126648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19802784919739</t>
   </si>
   <si>
     <t xml:space="preserve">3.23742604255676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24829459190369</t>
+    <t xml:space="preserve">3.24829483032227</t>
   </si>
   <si>
     <t xml:space="preserve">3.22791624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19395279884338</t>
+    <t xml:space="preserve">3.19395327568054</t>
   </si>
   <si>
     <t xml:space="preserve">3.16542315483093</t>
@@ -605,10 +605,10 @@
     <t xml:space="preserve">3.18444299697876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18172574043274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20753836631775</t>
+    <t xml:space="preserve">3.18172550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20753812789917</t>
   </si>
   <si>
     <t xml:space="preserve">3.24014353752136</t>
@@ -626,25 +626,25 @@
     <t xml:space="preserve">3.2319917678833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20617985725403</t>
+    <t xml:space="preserve">3.20617961883545</t>
   </si>
   <si>
     <t xml:space="preserve">3.14640331268311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16814041137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157132148743</t>
+    <t xml:space="preserve">3.16814017295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157155990601</t>
   </si>
   <si>
     <t xml:space="preserve">3.16678166389465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21704769134521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22927498817444</t>
+    <t xml:space="preserve">3.21704816818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22927522659302</t>
   </si>
   <si>
     <t xml:space="preserve">3.24421906471252</t>
@@ -653,37 +653,37 @@
     <t xml:space="preserve">3.21433067321777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25372862815857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35154461860657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4914755821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39365935325623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46430373191833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50506138801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41675472259521</t>
+    <t xml:space="preserve">3.25372910499573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35154414176941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49147510528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39365911483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46430420875549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50506043434143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41675496101379</t>
   </si>
   <si>
     <t xml:space="preserve">3.40656590461731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44732213020325</t>
+    <t xml:space="preserve">3.44732260704041</t>
   </si>
   <si>
     <t xml:space="preserve">3.4337363243103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42694449424744</t>
+    <t xml:space="preserve">3.42694401741028</t>
   </si>
   <si>
     <t xml:space="preserve">3.47109723091125</t>
@@ -692,10 +692,10 @@
     <t xml:space="preserve">3.46770048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48128652572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50166416168213</t>
+    <t xml:space="preserve">3.48128604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50166463851929</t>
   </si>
   <si>
     <t xml:space="preserve">3.5424211025238</t>
@@ -710,16 +710,16 @@
     <t xml:space="preserve">3.55940222740173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63412284851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60015940666199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53223133087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48468232154846</t>
+    <t xml:space="preserve">3.6341233253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60015892982483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53223204612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48468255996704</t>
   </si>
   <si>
     <t xml:space="preserve">3.55261015892029</t>
@@ -731,25 +731,25 @@
     <t xml:space="preserve">3.52543878555298</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5899703502655</t>
+    <t xml:space="preserve">3.58996987342834</t>
   </si>
   <si>
     <t xml:space="preserve">3.60355567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5933666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62053775787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59676313400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56619572639465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562808036804</t>
+    <t xml:space="preserve">3.59336638450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62053728103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59676337242126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56619548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53562784194946</t>
   </si>
   <si>
     <t xml:space="preserve">3.45411515235901</t>
@@ -764,106 +764,106 @@
     <t xml:space="preserve">3.32301497459412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38279104232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40996265411377</t>
+    <t xml:space="preserve">3.38279151916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40996193885803</t>
   </si>
   <si>
     <t xml:space="preserve">3.38958358764648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32844924926758</t>
+    <t xml:space="preserve">3.328449010849</t>
   </si>
   <si>
     <t xml:space="preserve">3.30807089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31078791618347</t>
+    <t xml:space="preserve">3.31078767776489</t>
   </si>
   <si>
     <t xml:space="preserve">3.35018610954285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37599802017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35426163673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37328124046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34339332580566</t>
+    <t xml:space="preserve">3.3759982585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35426187515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37328147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34339380264282</t>
   </si>
   <si>
     <t xml:space="preserve">3.36648845672607</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37871527671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36105442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12127017974854</t>
+    <t xml:space="preserve">3.3787157535553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36105418205261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12126994132996</t>
   </si>
   <si>
     <t xml:space="preserve">3.16406440734863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06624865531921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0458710193634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03228521347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00239706039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0220959186554</t>
+    <t xml:space="preserve">3.06624841690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04587078094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03228497505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00239658355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02209615707397</t>
   </si>
   <si>
     <t xml:space="preserve">3.02549242973328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04655003547668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99424600601196</t>
+    <t xml:space="preserve">3.04654979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99424576759338</t>
   </si>
   <si>
     <t xml:space="preserve">2.96164059638977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97862267494202</t>
+    <t xml:space="preserve">2.97862243652344</t>
   </si>
   <si>
     <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11651468276978</t>
+    <t xml:space="preserve">3.11651492118835</t>
   </si>
   <si>
     <t xml:space="preserve">3.06828689575195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00035881996155</t>
+    <t xml:space="preserve">3.00035929679871</t>
   </si>
   <si>
     <t xml:space="preserve">2.96639537811279</t>
   </si>
   <si>
-    <t xml:space="preserve">2.929034948349</t>
+    <t xml:space="preserve">2.92903518676758</t>
   </si>
   <si>
     <t xml:space="preserve">2.92495965957642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01326513290405</t>
+    <t xml:space="preserve">3.01326489448547</t>
   </si>
   <si>
     <t xml:space="preserve">3.09409880638123</t>
@@ -872,34 +872,34 @@
     <t xml:space="preserve">3.14300680160522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23538827896118</t>
+    <t xml:space="preserve">3.23538899421692</t>
   </si>
   <si>
     <t xml:space="preserve">3.2272367477417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21297264099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1932737827301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27342796325684</t>
+    <t xml:space="preserve">3.21297216415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19327306747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27342772483826</t>
   </si>
   <si>
     <t xml:space="preserve">3.29448533058167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20414209365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30739164352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2856547832489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36377143859863</t>
+    <t xml:space="preserve">3.20414161682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30739116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28565502166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36377191543579</t>
   </si>
   <si>
     <t xml:space="preserve">3.39909386634827</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">3.47924828529358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.475172996521</t>
+    <t xml:space="preserve">3.47517275810242</t>
   </si>
   <si>
     <t xml:space="preserve">3.48196530342102</t>
@@ -923,64 +923,64 @@
     <t xml:space="preserve">3.49962687492371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.528156042099</t>
+    <t xml:space="preserve">3.52815628051758</t>
   </si>
   <si>
     <t xml:space="preserve">3.47788953781128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51457071304321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45886993408203</t>
+    <t xml:space="preserve">3.51456999778748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45887017250061</t>
   </si>
   <si>
     <t xml:space="preserve">3.5267972946167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5200047492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5757052898407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62733101844788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64499139785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60423493385315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60287666320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.625972032547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49419212341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45615267753601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41539621353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45479393005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4425675868988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36309218406677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39298009872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39461970329285</t>
+    <t xml:space="preserve">3.52000451087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57570552825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62733054161072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64499115943909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60423541069031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60287642478943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62597131729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49419260025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45615243911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41539597511292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45479464530945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44256806373596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36309266090393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39298033714294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39461922645569</t>
   </si>
   <si>
     <t xml:space="preserve">3.45400071144104</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">3.28151297569275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23414921760559</t>
+    <t xml:space="preserve">3.23414897918701</t>
   </si>
   <si>
     <t xml:space="preserve">3.07367920875549</t>
@@ -1010,13 +1010,13 @@
     <t xml:space="preserve">3.18961334228516</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2786853313446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25747752189636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23556327819824</t>
+    <t xml:space="preserve">3.27868485450745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25747728347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23556351661682</t>
   </si>
   <si>
     <t xml:space="preserve">3.23768401145935</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">3.34089374542236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43774127960205</t>
+    <t xml:space="preserve">3.43774223327637</t>
   </si>
   <si>
     <t xml:space="preserve">3.39037799835205</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">3.38967132568359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40946507453918</t>
+    <t xml:space="preserve">3.40946459770203</t>
   </si>
   <si>
     <t xml:space="preserve">3.46319055557251</t>
@@ -1052,16 +1052,16 @@
     <t xml:space="preserve">3.33735918998718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31544494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29989290237427</t>
+    <t xml:space="preserve">3.31544470787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29989266395569</t>
   </si>
   <si>
     <t xml:space="preserve">3.34442830085754</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35432577133179</t>
+    <t xml:space="preserve">3.35432553291321</t>
   </si>
   <si>
     <t xml:space="preserve">3.32958340644836</t>
@@ -1070,43 +1070,43 @@
     <t xml:space="preserve">3.3380663394928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29211664199829</t>
+    <t xml:space="preserve">3.29211688041687</t>
   </si>
   <si>
     <t xml:space="preserve">3.35644626617432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35220456123352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40098166465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41865515708923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3776535987854</t>
+    <t xml:space="preserve">3.35220408439636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40098237991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41865491867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37765336036682</t>
   </si>
   <si>
     <t xml:space="preserve">3.32534193992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35573935508728</t>
+    <t xml:space="preserve">3.35573959350586</t>
   </si>
   <si>
     <t xml:space="preserve">3.34230780601501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40027475357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45258688926697</t>
+    <t xml:space="preserve">3.40027499198914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45258665084839</t>
   </si>
   <si>
     <t xml:space="preserve">3.44834518432617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4426896572113</t>
+    <t xml:space="preserve">3.44269013404846</t>
   </si>
   <si>
     <t xml:space="preserve">3.45117282867432</t>
@@ -1118,61 +1118,61 @@
     <t xml:space="preserve">3.40734434127808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46036291122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43137955665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4787425994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42077589035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42572402954102</t>
+    <t xml:space="preserve">3.46036314964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4313793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47874307632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42077541351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42572426795959</t>
   </si>
   <si>
     <t xml:space="preserve">3.51479578018188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4942946434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39532661437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41582751274109</t>
+    <t xml:space="preserve">3.49429512023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39532685279846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41582727432251</t>
   </si>
   <si>
     <t xml:space="preserve">3.42925834655762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40239596366882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36139464378357</t>
+    <t xml:space="preserve">3.4023962020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36139488220215</t>
   </si>
   <si>
     <t xml:space="preserve">3.38825750350952</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43279337882996</t>
+    <t xml:space="preserve">3.43279361724854</t>
   </si>
   <si>
     <t xml:space="preserve">3.33594536781311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29706501960754</t>
+    <t xml:space="preserve">3.29706525802612</t>
   </si>
   <si>
     <t xml:space="preserve">3.30413413047791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30837535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28787469863892</t>
+    <t xml:space="preserve">3.3083758354187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28787541389465</t>
   </si>
   <si>
     <t xml:space="preserve">3.31615161895752</t>
@@ -1184,28 +1184,28 @@
     <t xml:space="preserve">3.28999543190002</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33311796188354</t>
+    <t xml:space="preserve">3.33311820030212</t>
   </si>
   <si>
     <t xml:space="preserve">3.33099699020386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33382487297058</t>
+    <t xml:space="preserve">3.33382511138916</t>
   </si>
   <si>
     <t xml:space="preserve">3.32675552368164</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34654951095581</t>
+    <t xml:space="preserve">3.34654927253723</t>
   </si>
   <si>
     <t xml:space="preserve">3.47450113296509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49924373626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49641609191895</t>
+    <t xml:space="preserve">3.49924325942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49641561508179</t>
   </si>
   <si>
     <t xml:space="preserve">3.46248340606689</t>
@@ -1217,37 +1217,37 @@
     <t xml:space="preserve">3.45470809936523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38613700866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4575355052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45894932746887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37411856651306</t>
+    <t xml:space="preserve">3.38613677024841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45753526687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45894956588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37411904335022</t>
   </si>
   <si>
     <t xml:space="preserve">3.39391303062439</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42006826400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30978989601135</t>
+    <t xml:space="preserve">3.42006850242615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30978965759277</t>
   </si>
   <si>
     <t xml:space="preserve">3.32816958427429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35715317726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27797818183899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24899435043335</t>
+    <t xml:space="preserve">3.35715293884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27797842025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24899482727051</t>
   </si>
   <si>
     <t xml:space="preserve">3.2101137638092</t>
@@ -1256,19 +1256,19 @@
     <t xml:space="preserve">3.23485636711121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20516562461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15780186653137</t>
+    <t xml:space="preserve">3.20516538619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15780234336853</t>
   </si>
   <si>
     <t xml:space="preserve">3.130939245224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15356087684631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24546003341675</t>
+    <t xml:space="preserve">3.15356063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24546051025391</t>
   </si>
   <si>
     <t xml:space="preserve">3.16911292076111</t>
@@ -1289,16 +1289,16 @@
     <t xml:space="preserve">3.27727127075195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23202848434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22920083999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22495889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27232265472412</t>
+    <t xml:space="preserve">3.2320282459259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22920060157776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22495913505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27232336997986</t>
   </si>
   <si>
     <t xml:space="preserve">3.31473779678345</t>
@@ -1307,28 +1307,28 @@
     <t xml:space="preserve">3.3734118938446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42501711845398</t>
+    <t xml:space="preserve">3.42501664161682</t>
   </si>
   <si>
     <t xml:space="preserve">3.43491411209106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48863959312439</t>
+    <t xml:space="preserve">3.48863911628723</t>
   </si>
   <si>
     <t xml:space="preserve">3.44693112373352</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38755083084106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35927367210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34160137176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30059957504272</t>
+    <t xml:space="preserve">3.38755035400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3592734336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3416006565094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30059933662415</t>
   </si>
   <si>
     <t xml:space="preserve">3.3048415184021</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">3.39603328704834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34937644004822</t>
+    <t xml:space="preserve">3.34937715530396</t>
   </si>
   <si>
     <t xml:space="preserve">3.36068773269653</t>
@@ -1349,25 +1349,25 @@
     <t xml:space="preserve">3.36704969406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3917920589447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41653418540955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.453293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5232789516449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59114265441895</t>
+    <t xml:space="preserve">3.39179182052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41653394699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45329475402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52327871322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59114289283752</t>
   </si>
   <si>
     <t xml:space="preserve">3.61235022544861</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63073015213013</t>
+    <t xml:space="preserve">3.63073039054871</t>
   </si>
   <si>
     <t xml:space="preserve">3.61093616485596</t>
@@ -1379,43 +1379,43 @@
     <t xml:space="preserve">3.60103940963745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59962582588196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51055431365967</t>
+    <t xml:space="preserve">3.59962630271912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51055455207825</t>
   </si>
   <si>
     <t xml:space="preserve">3.53176188468933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57841777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61941981315613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64911007881165</t>
+    <t xml:space="preserve">3.57841849327087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61941933631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6491105556488</t>
   </si>
   <si>
     <t xml:space="preserve">3.67880082130432</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62083315849304</t>
+    <t xml:space="preserve">3.6208336353302</t>
   </si>
   <si>
     <t xml:space="preserve">3.68586993217468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70849084854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65335154533386</t>
+    <t xml:space="preserve">3.70849132537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65335202217102</t>
   </si>
   <si>
     <t xml:space="preserve">3.68304228782654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68728375434875</t>
+    <t xml:space="preserve">3.68728351593018</t>
   </si>
   <si>
     <t xml:space="preserve">3.67738723754883</t>
@@ -1424,22 +1424,22 @@
     <t xml:space="preserve">3.71414637565613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71131920814514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70990490913391</t>
+    <t xml:space="preserve">3.71131873130798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70990514755249</t>
   </si>
   <si>
     <t xml:space="preserve">3.72545719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7325267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73111295700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67173171043396</t>
+    <t xml:space="preserve">3.73252606391907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73111248016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6717312335968</t>
   </si>
   <si>
     <t xml:space="preserve">3.69293904304504</t>
@@ -1448,10 +1448,10 @@
     <t xml:space="preserve">3.71980214118958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63779973983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61517810821533</t>
+    <t xml:space="preserve">3.63779926300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61517763137817</t>
   </si>
   <si>
     <t xml:space="preserve">3.68869733810425</t>
@@ -1460,31 +1460,31 @@
     <t xml:space="preserve">3.69576692581177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69435214996338</t>
+    <t xml:space="preserve">3.6943531036377</t>
   </si>
   <si>
     <t xml:space="preserve">3.69718050956726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6816291809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75231981277466</t>
+    <t xml:space="preserve">3.68162870407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75232028961182</t>
   </si>
   <si>
     <t xml:space="preserve">3.7438371181488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72262930870056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76504468917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7593891620636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71697425842285</t>
+    <t xml:space="preserve">3.72262978553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76504516601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75938940048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71697378158569</t>
   </si>
   <si>
     <t xml:space="preserve">3.78342461585999</t>
@@ -1496,19 +1496,19 @@
     <t xml:space="preserve">3.86542677879333</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83573698997498</t>
+    <t xml:space="preserve">3.83573651313782</t>
   </si>
   <si>
     <t xml:space="preserve">3.82442569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79756355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81735634803772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85977149009705</t>
+    <t xml:space="preserve">3.79756307601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81735682487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85977125167847</t>
   </si>
   <si>
     <t xml:space="preserve">3.86966848373413</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">3.87532353401184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89370369911194</t>
+    <t xml:space="preserve">3.89370322227478</t>
   </si>
   <si>
     <t xml:space="preserve">3.88804817199707</t>
@@ -1547,25 +1547,25 @@
     <t xml:space="preserve">3.88946199417114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90360069274902</t>
+    <t xml:space="preserve">3.90360021591187</t>
   </si>
   <si>
     <t xml:space="preserve">3.92056679725647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9191529750824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96439528465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95732593536377</t>
+    <t xml:space="preserve">3.91915249824524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96439504623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95732641220093</t>
   </si>
   <si>
     <t xml:space="preserve">3.91067004203796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9332914352417</t>
+    <t xml:space="preserve">3.93329095840454</t>
   </si>
   <si>
     <t xml:space="preserve">3.90642762184143</t>
@@ -1580,31 +1580,31 @@
     <t xml:space="preserve">3.91208362579346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9304633140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87956500053406</t>
+    <t xml:space="preserve">3.93046379089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87956547737122</t>
   </si>
   <si>
     <t xml:space="preserve">3.89794492721558</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88097834587097</t>
+    <t xml:space="preserve">3.88097929954529</t>
   </si>
   <si>
     <t xml:space="preserve">3.94742918014526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89228987693787</t>
+    <t xml:space="preserve">3.89228940010071</t>
   </si>
   <si>
     <t xml:space="preserve">3.87391018867493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90925621986389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95025706291199</t>
+    <t xml:space="preserve">3.90925574302673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95025658607483</t>
   </si>
   <si>
     <t xml:space="preserve">3.98136162757874</t>
@@ -1628,28 +1628,28 @@
     <t xml:space="preserve">4.21100282669067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.213942527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24921751022339</t>
+    <t xml:space="preserve">4.21394205093384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24921798706055</t>
   </si>
   <si>
     <t xml:space="preserve">4.20512342453003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19483518600464</t>
+    <t xml:space="preserve">4.1948356628418</t>
   </si>
   <si>
     <t xml:space="preserve">4.1228141784668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10811614990234</t>
+    <t xml:space="preserve">4.1081166267395</t>
   </si>
   <si>
     <t xml:space="preserve">4.16543865203857</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21541213989258</t>
+    <t xml:space="preserve">4.21541261672974</t>
   </si>
   <si>
     <t xml:space="preserve">4.26979541778564</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">4.32123899459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36827278137207</t>
+    <t xml:space="preserve">4.36827230453491</t>
   </si>
   <si>
     <t xml:space="preserve">4.33152723312378</t>
@@ -1676,10 +1676,10 @@
     <t xml:space="preserve">4.35651397705078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34328556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49908590316772</t>
+    <t xml:space="preserve">4.34328508377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49908542633057</t>
   </si>
   <si>
     <t xml:space="preserve">4.44764184951782</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">4.48291778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48732662200928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45352172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43735361099243</t>
+    <t xml:space="preserve">4.48732709884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45352125167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43735408782959</t>
   </si>
   <si>
     <t xml:space="preserve">4.35210418701172</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">4.43147468566895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47997760772705</t>
+    <t xml:space="preserve">4.47997808456421</t>
   </si>
   <si>
     <t xml:space="preserve">4.44911193847656</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">4.43882322311401</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49467611312866</t>
+    <t xml:space="preserve">4.49467658996582</t>
   </si>
   <si>
     <t xml:space="preserve">4.51966285705566</t>
@@ -1730,13 +1730,13 @@
     <t xml:space="preserve">4.50349473953247</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54318046569824</t>
+    <t xml:space="preserve">4.54317998886108</t>
   </si>
   <si>
     <t xml:space="preserve">4.56228733062744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57698583602905</t>
+    <t xml:space="preserve">4.57698535919189</t>
   </si>
   <si>
     <t xml:space="preserve">4.52701139450073</t>
@@ -1748,10 +1748,10 @@
     <t xml:space="preserve">4.54905891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40207815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43588304519653</t>
+    <t xml:space="preserve">4.40207767486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43588352203369</t>
   </si>
   <si>
     <t xml:space="preserve">4.42559480667114</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">4.20218420028687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29037237167358</t>
+    <t xml:space="preserve">4.29037189483643</t>
   </si>
   <si>
     <t xml:space="preserve">4.29331207275391</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">4.26097631454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28449296951294</t>
+    <t xml:space="preserve">4.2844934463501</t>
   </si>
   <si>
     <t xml:space="preserve">4.28743314743042</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">4.11399507522583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16102933883667</t>
+    <t xml:space="preserve">4.16102981567383</t>
   </si>
   <si>
     <t xml:space="preserve">4.24186849594116</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">4.15662002563477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30360078811646</t>
+    <t xml:space="preserve">4.3036003112793</t>
   </si>
   <si>
     <t xml:space="preserve">4.21835231781006</t>
@@ -1817,31 +1817,31 @@
     <t xml:space="preserve">4.33593654632568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3491644859314</t>
+    <t xml:space="preserve">4.34916496276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.313889503479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30213165283203</t>
+    <t xml:space="preserve">4.30213117599487</t>
   </si>
   <si>
     <t xml:space="preserve">4.20806312561035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14192199707031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1037073135376</t>
+    <t xml:space="preserve">4.14192247390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10370683670044</t>
   </si>
   <si>
     <t xml:space="preserve">4.18307638168335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14045190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12575435638428</t>
+    <t xml:space="preserve">4.14045238494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12575387954712</t>
   </si>
   <si>
     <t xml:space="preserve">4.19336557388306</t>
@@ -1850,16 +1850,16 @@
     <t xml:space="preserve">4.18160676956177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18454599380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25215768814087</t>
+    <t xml:space="preserve">4.18454694747925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25215721130371</t>
   </si>
   <si>
     <t xml:space="preserve">4.29919147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39031982421875</t>
+    <t xml:space="preserve">4.39031934738159</t>
   </si>
   <si>
     <t xml:space="preserve">4.32711744308472</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">4.21247291564941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31241989135742</t>
+    <t xml:space="preserve">4.31241941452026</t>
   </si>
   <si>
     <t xml:space="preserve">4.36974191665649</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">4.18748617172241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17425680160522</t>
+    <t xml:space="preserve">4.17425727844238</t>
   </si>
   <si>
     <t xml:space="preserve">4.17278814315796</t>
@@ -1907,19 +1907,19 @@
     <t xml:space="preserve">4.238929271698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25362777709961</t>
+    <t xml:space="preserve">4.25362730026245</t>
   </si>
   <si>
     <t xml:space="preserve">4.29478168487549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33740615844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35063457489014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28302335739136</t>
+    <t xml:space="preserve">4.33740663528442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35063505172729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2830228805542</t>
   </si>
   <si>
     <t xml:space="preserve">4.33299684524536</t>
@@ -1949,10 +1949,10 @@
     <t xml:space="preserve">4.19189596176147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22129154205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23599004745483</t>
+    <t xml:space="preserve">4.22129201889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23598957061768</t>
   </si>
   <si>
     <t xml:space="preserve">4.22717046737671</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">4.08900880813599</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04932403564453</t>
+    <t xml:space="preserve">4.04932451248169</t>
   </si>
   <si>
     <t xml:space="preserve">4.01992750167847</t>
@@ -1991,25 +1991,25 @@
     <t xml:space="preserve">4.10664653778076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16396856307983</t>
+    <t xml:space="preserve">4.16396903991699</t>
   </si>
   <si>
     <t xml:space="preserve">4.12722444534302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13751268386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00082015991211</t>
+    <t xml:space="preserve">4.13751220703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00081968307495</t>
   </si>
   <si>
     <t xml:space="preserve">4.09194850921631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08459901809692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02727699279785</t>
+    <t xml:space="preserve">4.08459949493408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02727651596069</t>
   </si>
   <si>
     <t xml:space="preserve">4.02286720275879</t>
@@ -2021,13 +2021,13 @@
     <t xml:space="preserve">4.20365381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13898181915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25068712234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20659303665161</t>
+    <t xml:space="preserve">4.13898229598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25068759918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20659351348877</t>
   </si>
   <si>
     <t xml:space="preserve">4.263916015625</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">4.30801057815552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48144721984863</t>
+    <t xml:space="preserve">4.48144769668579</t>
   </si>
   <si>
     <t xml:space="preserve">4.5152530670166</t>
@@ -2057,7 +2057,7 @@
     <t xml:space="preserve">4.4917368888855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46087026596069</t>
+    <t xml:space="preserve">4.46087074279785</t>
   </si>
   <si>
     <t xml:space="preserve">4.46233987808228</t>
@@ -2069,10 +2069,10 @@
     <t xml:space="preserve">4.45205163955688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4858570098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62548875808716</t>
+    <t xml:space="preserve">4.48585748672485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62548923492432</t>
   </si>
   <si>
     <t xml:space="preserve">4.26538562774658</t>
@@ -2093,19 +2093,19 @@
     <t xml:space="preserve">3.51798820495605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50181984901428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02192735671997</t>
+    <t xml:space="preserve">3.50182032585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02192711830139</t>
   </si>
   <si>
     <t xml:space="preserve">3.24754309654236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15127062797546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27032494544983</t>
+    <t xml:space="preserve">3.15127086639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27032518386841</t>
   </si>
   <si>
     <t xml:space="preserve">3.29531240463257</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">3.35189914703369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21153259277344</t>
+    <t xml:space="preserve">3.21153283119202</t>
   </si>
   <si>
     <t xml:space="preserve">3.129958152771</t>
@@ -2123,16 +2123,16 @@
     <t xml:space="preserve">3.35557389259338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38937926292419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34381556510925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3592483997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57090163230896</t>
+    <t xml:space="preserve">3.38937950134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34381532669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35924863815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5709011554718</t>
   </si>
   <si>
     <t xml:space="preserve">3.66643834114075</t>
@@ -2144,13 +2144,13 @@
     <t xml:space="preserve">3.55693769454956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58780384063721</t>
+    <t xml:space="preserve">3.58780360221863</t>
   </si>
   <si>
     <t xml:space="preserve">3.53636050224304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54958891868591</t>
+    <t xml:space="preserve">3.54958868026733</t>
   </si>
   <si>
     <t xml:space="preserve">3.46580982208252</t>
@@ -2159,10 +2159,10 @@
     <t xml:space="preserve">3.54811930656433</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56428670883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368348121643</t>
+    <t xml:space="preserve">3.56428647041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368324279785</t>
   </si>
   <si>
     <t xml:space="preserve">3.6260187625885</t>
@@ -2171,22 +2171,22 @@
     <t xml:space="preserve">3.57163619995117</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57310581207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44082355499268</t>
+    <t xml:space="preserve">3.57310557365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44082307815552</t>
   </si>
   <si>
     <t xml:space="preserve">3.61719989776611</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52754211425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57457566261292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56722664833069</t>
+    <t xml:space="preserve">3.52754187583923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57457518577576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56722640991211</t>
   </si>
   <si>
     <t xml:space="preserve">3.57898497581482</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">3.75168776512146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68187165260315</t>
+    <t xml:space="preserve">3.68187212944031</t>
   </si>
   <si>
     <t xml:space="preserve">3.70391869544983</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">3.66423392295837</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63189792633057</t>
+    <t xml:space="preserve">3.63189840316772</t>
   </si>
   <si>
     <t xml:space="preserve">3.62454891204834</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">3.63777732849121</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6230788230896</t>
+    <t xml:space="preserve">3.62307929992676</t>
   </si>
   <si>
     <t xml:space="preserve">3.71126794815063</t>
@@ -4931,7 +4931,7 @@
     <t xml:space="preserve">9.33500003814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27999973297119</t>
+    <t xml:space="preserve">9.27499961853027</t>
   </si>
 </sst>
 </file>
@@ -64732,22 +64732,22 @@
     </row>
     <row r="2288">
       <c r="A2288" s="1" t="n">
-        <v>45967.6943865741</v>
+        <v>45968.6911458333</v>
       </c>
       <c r="B2288" t="n">
-        <v>3287827</v>
+        <v>3129271</v>
       </c>
       <c r="C2288" t="n">
-        <v>9.39500045776367</v>
+        <v>9.38000011444092</v>
       </c>
       <c r="D2288" t="n">
-        <v>9.25500011444092</v>
+        <v>9.22999954223633</v>
       </c>
       <c r="E2288" t="n">
-        <v>9.35499954223633</v>
+        <v>9.3100004196167</v>
       </c>
       <c r="F2288" t="n">
-        <v>9.27999973297119</v>
+        <v>9.27499961853027</v>
       </c>
       <c r="G2288" t="s">
         <v>1639</v>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">IG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50135731697083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32790613174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16488742828369</t>
+    <t xml:space="preserve">2.5013575553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32790589332581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16488695144653</t>
   </si>
   <si>
     <t xml:space="preserve">2.17271208763123</t>
@@ -62,58 +62,58 @@
     <t xml:space="preserve">2.06185936927795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08663868904114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04490518569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06055498123169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04360127449036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10489654541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12967491149902</t>
+    <t xml:space="preserve">2.0866379737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04490542411804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06055569648743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04360151290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10489630699158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1296751499176</t>
   </si>
   <si>
     <t xml:space="preserve">2.14532518386841</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17923259735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20009922981262</t>
+    <t xml:space="preserve">2.17923283576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2000994682312</t>
   </si>
   <si>
     <t xml:space="preserve">2.20140337944031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17792844772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13228344917297</t>
+    <t xml:space="preserve">2.17792868614197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13228368759155</t>
   </si>
   <si>
     <t xml:space="preserve">2.09837579727173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22357416152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29138946533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33181834220886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29791045188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23791933059692</t>
+    <t xml:space="preserve">2.2235746383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29138970375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33181810379028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29791021347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2379195690155</t>
   </si>
   <si>
     <t xml:space="preserve">2.30051875114441</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">2.39702606201172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38007164001465</t>
+    <t xml:space="preserve">2.38007187843323</t>
   </si>
   <si>
     <t xml:space="preserve">2.39441752433777</t>
@@ -146,25 +146,25 @@
     <t xml:space="preserve">2.42180466651917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41006755828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43093371391296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43745398521423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701167106628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45049571990967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49092435836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44527912139893</t>
+    <t xml:space="preserve">2.41006708145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43093347549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43745446205139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701190948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45049595832825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49092411994934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44527888298035</t>
   </si>
   <si>
     <t xml:space="preserve">2.46614551544189</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">2.43223786354065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44006252288818</t>
+    <t xml:space="preserve">2.44006276130676</t>
   </si>
   <si>
     <t xml:space="preserve">2.47788286209106</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">2.43615031242371</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43354225158691</t>
+    <t xml:space="preserve">2.43354201316833</t>
   </si>
   <si>
     <t xml:space="preserve">2.4570164680481</t>
@@ -191,25 +191,25 @@
     <t xml:space="preserve">2.48831605911255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41789197921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43484616279602</t>
+    <t xml:space="preserve">2.41789221763611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43484592437744</t>
   </si>
   <si>
     <t xml:space="preserve">2.41267538070679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35659718513489</t>
+    <t xml:space="preserve">2.35659694671631</t>
   </si>
   <si>
     <t xml:space="preserve">2.27573990821838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29530215263367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.312255859375</t>
+    <t xml:space="preserve">2.29530191421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31225609779358</t>
   </si>
   <si>
     <t xml:space="preserve">2.38137602806091</t>
@@ -221,16 +221,16 @@
     <t xml:space="preserve">2.39311337471008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44919180870056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.467449426651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47397065162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48440384864807</t>
+    <t xml:space="preserve">2.44919157028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46744966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47397017478943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48440337181091</t>
   </si>
   <si>
     <t xml:space="preserve">2.4635374546051</t>
@@ -239,52 +239,52 @@
     <t xml:space="preserve">2.4726665019989</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47136211395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44788718223572</t>
+    <t xml:space="preserve">2.47136235237122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4478874206543</t>
   </si>
   <si>
     <t xml:space="preserve">2.49614119529724</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744486808777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51570343971252</t>
+    <t xml:space="preserve">2.49744534492493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51570320129395</t>
   </si>
   <si>
     <t xml:space="preserve">2.53135323524475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51439929008484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53656959533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52744054794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54830718040466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55091524124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53787398338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58612728118896</t>
+    <t xml:space="preserve">2.51439905166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53656983375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52744030952454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54830694198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55091547966003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5378737449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58612751960754</t>
   </si>
   <si>
     <t xml:space="preserve">2.57699823379517</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59786462783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60438513755798</t>
+    <t xml:space="preserve">2.59786438941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60438537597656</t>
   </si>
   <si>
     <t xml:space="preserve">2.57308578491211</t>
@@ -299,13 +299,13 @@
     <t xml:space="preserve">2.69828414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64872646331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64742231369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68133020401001</t>
+    <t xml:space="preserve">2.64872598648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64742207527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68132996559143</t>
   </si>
   <si>
     <t xml:space="preserve">2.67480945587158</t>
@@ -317,31 +317,31 @@
     <t xml:space="preserve">2.64350962638855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69567608833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69958829879761</t>
+    <t xml:space="preserve">2.69567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69958806037903</t>
   </si>
   <si>
     <t xml:space="preserve">2.67872190475464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73480010032654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.772620677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75436234474182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71262955665588</t>
+    <t xml:space="preserve">2.7348005771637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77262043952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7543625831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71262979507446</t>
   </si>
   <si>
     <t xml:space="preserve">2.70089244842529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70219707489014</t>
+    <t xml:space="preserve">2.70219659805298</t>
   </si>
   <si>
     <t xml:space="preserve">2.66176772117615</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">2.70610928535461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74914598464966</t>
+    <t xml:space="preserve">2.74914646148682</t>
   </si>
   <si>
     <t xml:space="preserve">2.77783727645874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83521938323975</t>
+    <t xml:space="preserve">2.83521962165833</t>
   </si>
   <si>
     <t xml:space="preserve">2.84043645858765</t>
@@ -377,70 +377,70 @@
     <t xml:space="preserve">2.88738584518433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89651441574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8534779548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91477274894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00867128372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02040886878967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96824312210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0073676109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05822920799255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09885358810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15591335296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09613680839539</t>
+    <t xml:space="preserve">2.89651465415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85347771644592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91477251052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00867176055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02040934562683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96824288368225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00736784934998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05822896957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09885382652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15591311454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09613728523254</t>
   </si>
   <si>
     <t xml:space="preserve">3.13825178146362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0907027721405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9765841960907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13417625427246</t>
+    <t xml:space="preserve">3.09070301055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97658443450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13417649269104</t>
   </si>
   <si>
     <t xml:space="preserve">3.20074534416199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24965333938599</t>
+    <t xml:space="preserve">3.24965310096741</t>
   </si>
   <si>
     <t xml:space="preserve">3.28769254684448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23063325881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24557733535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2224817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25101137161255</t>
+    <t xml:space="preserve">3.23063349723816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24557757377625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22248196601868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25101208686829</t>
   </si>
   <si>
     <t xml:space="preserve">3.18716025352478</t>
@@ -452,40 +452,40 @@
     <t xml:space="preserve">3.11379790306091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19938683509827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10428810119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1205906867981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15727138519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16270613670349</t>
+    <t xml:space="preserve">3.19938707351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10428833961487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12059092521667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15727186203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16270589828491</t>
   </si>
   <si>
     <t xml:space="preserve">3.14504480361938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03907799720764</t>
+    <t xml:space="preserve">3.03907775878906</t>
   </si>
   <si>
     <t xml:space="preserve">3.0282096862793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96707439422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00375556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03636074066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02005815505981</t>
+    <t xml:space="preserve">2.96707463264465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00375533103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03636050224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02005791664124</t>
   </si>
   <si>
     <t xml:space="preserve">2.977942943573</t>
@@ -494,34 +494,34 @@
     <t xml:space="preserve">2.98609399795532</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9956042766571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.075758934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08390974998474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12466621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10836410522461</t>
+    <t xml:space="preserve">2.99560403823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07575845718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08390998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12466645240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10836434364319</t>
   </si>
   <si>
     <t xml:space="preserve">3.12874221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17900824546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17221617698669</t>
+    <t xml:space="preserve">3.17900776863098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17221593856812</t>
   </si>
   <si>
     <t xml:space="preserve">3.12602519989014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15863037109375</t>
+    <t xml:space="preserve">3.15863060951233</t>
   </si>
   <si>
     <t xml:space="preserve">3.2251992225647</t>
@@ -533,28 +533,28 @@
     <t xml:space="preserve">3.25237059593201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27682447433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30671238899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30263686180115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28090000152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21025562286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28361701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29856085777283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2822585105896</t>
+    <t xml:space="preserve">3.27682399749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30671215057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30263662338257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2808997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21025490760803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2836172580719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29856133460999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28225827217102</t>
   </si>
   <si>
     <t xml:space="preserve">3.26323843002319</t>
@@ -563,67 +563,67 @@
     <t xml:space="preserve">3.25644612312317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27003169059753</t>
+    <t xml:space="preserve">3.27003145217896</t>
   </si>
   <si>
     <t xml:space="preserve">3.24693584442139</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23335075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21976494789124</t>
+    <t xml:space="preserve">3.23335027694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21976518630981</t>
   </si>
   <si>
     <t xml:space="preserve">3.24150156974792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26188015937805</t>
+    <t xml:space="preserve">3.26188039779663</t>
   </si>
   <si>
     <t xml:space="preserve">3.2347092628479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19802808761597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23742604255676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24829483032227</t>
+    <t xml:space="preserve">3.19802856445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23742628097534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24829435348511</t>
   </si>
   <si>
     <t xml:space="preserve">3.22791647911072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19395279884338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16542315483093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18444275856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18172597885132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20753860473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24014329910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26731443405151</t>
+    <t xml:space="preserve">3.19395232200623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16542339324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18444299697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18172574043274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20753836631775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24014353752136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26731491088867</t>
   </si>
   <si>
     <t xml:space="preserve">3.24286079406738</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22655773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23199152946472</t>
+    <t xml:space="preserve">3.226557970047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2319917678833</t>
   </si>
   <si>
     <t xml:space="preserve">3.20617938041687</t>
@@ -632,190 +632,190 @@
     <t xml:space="preserve">3.14640355110168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16814041137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157108306885</t>
+    <t xml:space="preserve">3.16813993453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157132148743</t>
   </si>
   <si>
     <t xml:space="preserve">3.16678166389465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21704816818237</t>
+    <t xml:space="preserve">3.21704792976379</t>
   </si>
   <si>
     <t xml:space="preserve">3.22927522659302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24421882629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21433091163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25372910499573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35154414176941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49147534370422</t>
+    <t xml:space="preserve">3.2442193031311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21433115005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25372862815857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35154438018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49147462844849</t>
   </si>
   <si>
     <t xml:space="preserve">3.39365935325623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46430373191833</t>
+    <t xml:space="preserve">3.46430468559265</t>
   </si>
   <si>
     <t xml:space="preserve">3.50506067276001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41675519943237</t>
+    <t xml:space="preserve">3.41675567626953</t>
   </si>
   <si>
     <t xml:space="preserve">3.40656566619873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44732189178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43373703956604</t>
+    <t xml:space="preserve">3.44732236862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43373656272888</t>
   </si>
   <si>
     <t xml:space="preserve">3.42694425582886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47109699249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46770095825195</t>
+    <t xml:space="preserve">3.4710967540741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46770048141479</t>
   </si>
   <si>
     <t xml:space="preserve">3.48128604888916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50166392326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54242062568665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51185345649719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54581665992737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55940246582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6341233253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60015964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53223180770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48468279838562</t>
+    <t xml:space="preserve">3.50166463851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5424211025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51185393333435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54581713676453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55940198898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412308692932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60015940666199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53223156929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48468255996704</t>
   </si>
   <si>
     <t xml:space="preserve">3.55260992050171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61374521255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52543878555298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58996939659119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60355567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59336686134338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62053775787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59676337242126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5661952495575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562784194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45411491394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45751118659973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39637660980225</t>
+    <t xml:space="preserve">3.61374473571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52543902397156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58996987342834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60355520248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5933666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6205370426178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59676289558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56619548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53562808036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45411562919617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45751190185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39637637138367</t>
   </si>
   <si>
     <t xml:space="preserve">3.3230152130127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38279128074646</t>
+    <t xml:space="preserve">3.38279104232788</t>
   </si>
   <si>
     <t xml:space="preserve">3.40996217727661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38958406448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32844924926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30807089805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31078767776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35018563270569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37599802017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35426211357117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37328147888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34339332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36648797988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37871527671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36105442047119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12126970291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16406464576721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06624889373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04587078094482</t>
+    <t xml:space="preserve">3.38958382606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.328449010849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30807113647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31078791618347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35018587112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3759982585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35426187515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37328195571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34339308738708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36648869514465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37871551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36105489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12127017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16406488418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06624865531921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0458710193634</t>
   </si>
   <si>
     <t xml:space="preserve">3.03228497505188</t>
@@ -833,19 +833,19 @@
     <t xml:space="preserve">3.04655027389526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99424576759338</t>
+    <t xml:space="preserve">2.99424600601196</t>
   </si>
   <si>
     <t xml:space="preserve">2.96164059638977</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97862243652344</t>
+    <t xml:space="preserve">2.97862267494202</t>
   </si>
   <si>
     <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11651492118835</t>
+    <t xml:space="preserve">3.11651515960693</t>
   </si>
   <si>
     <t xml:space="preserve">3.06828665733337</t>
@@ -860,49 +860,49 @@
     <t xml:space="preserve">2.92903518676758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92495965957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01326513290405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09409880638123</t>
+    <t xml:space="preserve">2.924959897995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01326537132263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0940990447998</t>
   </si>
   <si>
     <t xml:space="preserve">3.14300680160522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2353880405426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2272367477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21297287940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1932737827301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27342748641968</t>
+    <t xml:space="preserve">3.23538851737976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22723698616028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21297240257263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19327354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27342772483826</t>
   </si>
   <si>
     <t xml:space="preserve">3.29448509216309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20414209365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30739140510559</t>
+    <t xml:space="preserve">3.20414185523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30739116668701</t>
   </si>
   <si>
     <t xml:space="preserve">3.28565502166748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36377143859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39909386634827</t>
+    <t xml:space="preserve">3.36377191543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39909362792969</t>
   </si>
   <si>
     <t xml:space="preserve">3.47924828529358</t>
@@ -914,28 +914,28 @@
     <t xml:space="preserve">3.4819655418396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43713283538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44392585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49962639808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52815556526184</t>
+    <t xml:space="preserve">3.43713307380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4439263343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49962663650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52815580368042</t>
   </si>
   <si>
     <t xml:space="preserve">3.4778892993927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51457047462463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45886993408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5267972946167</t>
+    <t xml:space="preserve">3.51457071304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45887017250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52679777145386</t>
   </si>
   <si>
     <t xml:space="preserve">3.5200047492981</t>
@@ -944,19 +944,19 @@
     <t xml:space="preserve">3.57570552825928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62733101844788</t>
+    <t xml:space="preserve">3.62732982635498</t>
   </si>
   <si>
     <t xml:space="preserve">3.64499187469482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60423564910889</t>
+    <t xml:space="preserve">3.60423517227173</t>
   </si>
   <si>
     <t xml:space="preserve">3.60287642478943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62597155570984</t>
+    <t xml:space="preserve">3.62597179412842</t>
   </si>
   <si>
     <t xml:space="preserve">3.49419236183167</t>
@@ -965,31 +965,31 @@
     <t xml:space="preserve">3.45615267753601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41539597511292</t>
+    <t xml:space="preserve">3.41539621353149</t>
   </si>
   <si>
     <t xml:space="preserve">3.45479440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4425675868988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36309218406677</t>
+    <t xml:space="preserve">3.44256711006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36309242248535</t>
   </si>
   <si>
     <t xml:space="preserve">3.39298033714294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39461994171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4540011882782</t>
+    <t xml:space="preserve">3.39461946487427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45400071144104</t>
   </si>
   <si>
     <t xml:space="preserve">3.46107006072998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36280798912048</t>
+    <t xml:space="preserve">3.36280846595764</t>
   </si>
   <si>
     <t xml:space="preserve">3.28151273727417</t>
@@ -1001,76 +1001,76 @@
     <t xml:space="preserve">3.07367897033691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16699242591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15285348892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18961381912231</t>
+    <t xml:space="preserve">3.1669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1528537273407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18961358070374</t>
   </si>
   <si>
     <t xml:space="preserve">3.27868509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25747752189636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23556327819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23768353462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34089374542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43774151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39037799835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41087865829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37623977661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38967132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40946507453918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46319079399109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33735966682434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31544494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29989337921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34442853927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35432505607605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32958364486694</t>
+    <t xml:space="preserve">3.2574770450592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23556351661682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23768377304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20163130760193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34089326858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43774175643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39037775993347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4108784198761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37624001502991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38967108726501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40946531295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46319055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33735942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31544470787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29989290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34442830085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35432529449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32958316802979</t>
   </si>
   <si>
     <t xml:space="preserve">3.3380663394928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29211664199829</t>
+    <t xml:space="preserve">3.29211616516113</t>
   </si>
   <si>
     <t xml:space="preserve">3.35644602775574</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">3.40098190307617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41865539550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3776535987854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32534170150757</t>
+    <t xml:space="preserve">3.41865491867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37765383720398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32534193992615</t>
   </si>
   <si>
     <t xml:space="preserve">3.35573935508728</t>
@@ -1097,40 +1097,40 @@
     <t xml:space="preserve">3.34230804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40027475357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45258688926697</t>
+    <t xml:space="preserve">3.40027499198914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45258641242981</t>
   </si>
   <si>
     <t xml:space="preserve">3.44834518432617</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4426896572113</t>
+    <t xml:space="preserve">3.44268989562988</t>
   </si>
   <si>
     <t xml:space="preserve">3.4511730670929</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41229295730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4073441028595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46036314964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43137955665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47874283790588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42077565193176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42572450637817</t>
+    <t xml:space="preserve">3.41229319572449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40734457969666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46036291122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43137907981873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4787425994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42077589035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42572426795959</t>
   </si>
   <si>
     <t xml:space="preserve">3.51479578018188</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">3.49429488182068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39532685279846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41582679748535</t>
+    <t xml:space="preserve">3.3953263759613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41582751274109</t>
   </si>
   <si>
     <t xml:space="preserve">3.42925834655762</t>
@@ -1151,73 +1151,73 @@
     <t xml:space="preserve">3.4023962020874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36139440536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3882577419281</t>
+    <t xml:space="preserve">3.36139488220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38825750350952</t>
   </si>
   <si>
     <t xml:space="preserve">3.43279314041138</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33594536781311</t>
+    <t xml:space="preserve">3.33594512939453</t>
   </si>
   <si>
     <t xml:space="preserve">3.29706478118896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30413389205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30837512016296</t>
+    <t xml:space="preserve">3.30413413047791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30837535858154</t>
   </si>
   <si>
     <t xml:space="preserve">3.28787541389465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31615161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25182223320007</t>
+    <t xml:space="preserve">3.31615138053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25182199478149</t>
   </si>
   <si>
     <t xml:space="preserve">3.2899956703186</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33311820030212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33099722862244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.333824634552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32675552368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34654951095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47450160980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49924373626709</t>
+    <t xml:space="preserve">3.33311772346497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33099699020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33382487297058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32675528526306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34654927253723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47450113296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49924325942993</t>
   </si>
   <si>
     <t xml:space="preserve">3.49641633033752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46248364448547</t>
+    <t xml:space="preserve">3.46248340606689</t>
   </si>
   <si>
     <t xml:space="preserve">3.45682883262634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45470809936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38613653182983</t>
+    <t xml:space="preserve">3.45470762252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38613677024841</t>
   </si>
   <si>
     <t xml:space="preserve">3.45753526687622</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">3.45894932746887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37411856651306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39391231536865</t>
+    <t xml:space="preserve">3.37411880493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39391279220581</t>
   </si>
   <si>
     <t xml:space="preserve">3.42006850242615</t>
@@ -1238,13 +1238,13 @@
     <t xml:space="preserve">3.30978965759277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32816934585571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35715317726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27797818183899</t>
+    <t xml:space="preserve">3.32816982269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35715270042419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27797842025757</t>
   </si>
   <si>
     <t xml:space="preserve">3.24899482727051</t>
@@ -1253,25 +1253,25 @@
     <t xml:space="preserve">3.21011424064636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23485589027405</t>
+    <t xml:space="preserve">3.23485684394836</t>
   </si>
   <si>
     <t xml:space="preserve">3.20516562461853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15780234336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13093900680542</t>
+    <t xml:space="preserve">3.15780210494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.130939245224</t>
   </si>
   <si>
     <t xml:space="preserve">3.15356063842773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24546027183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16911244392395</t>
+    <t xml:space="preserve">3.24546003341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16911292076111</t>
   </si>
   <si>
     <t xml:space="preserve">3.19809651374817</t>
@@ -1283,55 +1283,55 @@
     <t xml:space="preserve">3.23909783363342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23344254493713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27727103233337</t>
+    <t xml:space="preserve">3.23344206809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27727150917053</t>
   </si>
   <si>
     <t xml:space="preserve">3.23202848434448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22920060157776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22495913505554</t>
+    <t xml:space="preserve">3.22920083999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22495937347412</t>
   </si>
   <si>
     <t xml:space="preserve">3.2723228931427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31473779678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3734118938446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42501664161682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43491411209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48863935470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4469313621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38755011558533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35927367210388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34160089492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3005998134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30484104156494</t>
+    <t xml:space="preserve">3.31473803520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37341213226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4250168800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43491387367249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48863959312439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44693160057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38755035400391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35927319526672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34160137176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30059957504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30484127998352</t>
   </si>
   <si>
     <t xml:space="preserve">3.2758572101593</t>
@@ -1340,82 +1340,82 @@
     <t xml:space="preserve">3.39603352546692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3493766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36068797111511</t>
+    <t xml:space="preserve">3.34937715530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36068773269653</t>
   </si>
   <si>
     <t xml:space="preserve">3.36704993247986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39179158210754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41653442382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45329427719116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52327919006348</t>
+    <t xml:space="preserve">3.3917920589447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4165346622467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45329356193542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5232789516449</t>
   </si>
   <si>
     <t xml:space="preserve">3.59114289283752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61235094070435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073039054871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61093640327454</t>
+    <t xml:space="preserve">3.61235046386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073015213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61093616485596</t>
   </si>
   <si>
     <t xml:space="preserve">3.62790274620056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60103988647461</t>
+    <t xml:space="preserve">3.60103940963745</t>
   </si>
   <si>
     <t xml:space="preserve">3.59962582588196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51055431365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53176140785217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57841825485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61941933631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64911031723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67880058288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62083339691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68586993217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70849084854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65335130691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68304204940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68728399276733</t>
+    <t xml:space="preserve">3.51055455207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53176164627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57841801643372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61941909790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64911007881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6788010597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62083315849304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68587017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70849061012268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65335154533386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68304228782654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68728423118591</t>
   </si>
   <si>
     <t xml:space="preserve">3.67738652229309</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">3.71131896972656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70990538597107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72545719146729</t>
+    <t xml:space="preserve">3.70990514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72545695304871</t>
   </si>
   <si>
     <t xml:space="preserve">3.73252630233765</t>
@@ -1442,43 +1442,43 @@
     <t xml:space="preserve">3.6717312335968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69293856620789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71980142593384</t>
+    <t xml:space="preserve">3.6929395198822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71980214118958</t>
   </si>
   <si>
     <t xml:space="preserve">3.63779950141907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61517786979675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68869733810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69576716423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69435286521912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69718098640442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68162822723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75232005119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7438371181488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72262978553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76504445075989</t>
+    <t xml:space="preserve">3.61517739295959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68869757652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69576692581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69435238838196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69718050956726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68162846565247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75231957435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74383687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72262954711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76504492759705</t>
   </si>
   <si>
     <t xml:space="preserve">3.7593891620636</t>
@@ -1487,25 +1487,25 @@
     <t xml:space="preserve">3.71697425842285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78342461585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83997750282288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86542725563049</t>
+    <t xml:space="preserve">3.78342413902283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83997797966003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86542654037476</t>
   </si>
   <si>
     <t xml:space="preserve">3.83573651313782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82442545890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79756307601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81735682487488</t>
+    <t xml:space="preserve">3.82442593574524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79756259918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81735634803772</t>
   </si>
   <si>
     <t xml:space="preserve">3.85977149009705</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">3.86966872215271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88380718231201</t>
+    <t xml:space="preserve">3.88380670547485</t>
   </si>
   <si>
     <t xml:space="preserve">3.87532353401184</t>
@@ -1523,7 +1523,7 @@
     <t xml:space="preserve">3.89370369911194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88804841041565</t>
+    <t xml:space="preserve">3.88804793357849</t>
   </si>
   <si>
     <t xml:space="preserve">3.85270237922668</t>
@@ -1532,13 +1532,13 @@
     <t xml:space="preserve">3.87108206748962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89087629318237</t>
+    <t xml:space="preserve">3.89087581634521</t>
   </si>
   <si>
     <t xml:space="preserve">3.84139180183411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8823926448822</t>
+    <t xml:space="preserve">3.88239312171936</t>
   </si>
   <si>
     <t xml:space="preserve">3.92339444160461</t>
@@ -1553,13 +1553,13 @@
     <t xml:space="preserve">3.92056655883789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91915273666382</t>
+    <t xml:space="preserve">3.91915321350098</t>
   </si>
   <si>
     <t xml:space="preserve">3.96439552307129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95732665061951</t>
+    <t xml:space="preserve">3.95732617378235</t>
   </si>
   <si>
     <t xml:space="preserve">3.91067004203796</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">3.93329119682312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90642786026001</t>
+    <t xml:space="preserve">3.90642833709717</t>
   </si>
   <si>
     <t xml:space="preserve">3.90501427650452</t>
@@ -1577,43 +1577,43 @@
     <t xml:space="preserve">3.92198014259338</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9120831489563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9304633140564</t>
+    <t xml:space="preserve">3.91208386421204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93046379089355</t>
   </si>
   <si>
     <t xml:space="preserve">3.87956523895264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.897944688797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88097929954529</t>
+    <t xml:space="preserve">3.89794516563416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88097834587097</t>
   </si>
   <si>
     <t xml:space="preserve">3.94742965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89228987693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87390995025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90925645828247</t>
+    <t xml:space="preserve">3.89229035377502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87390947341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90925621986389</t>
   </si>
   <si>
     <t xml:space="preserve">3.95025753974915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98136162757874</t>
+    <t xml:space="preserve">3.98136138916016</t>
   </si>
   <si>
     <t xml:space="preserve">4.00963830947876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08032941818237</t>
+    <t xml:space="preserve">4.08033037185669</t>
   </si>
   <si>
     <t xml:space="preserve">4.07891607284546</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">4.21100330352783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21394300460815</t>
+    <t xml:space="preserve">4.213942527771</t>
   </si>
   <si>
     <t xml:space="preserve">4.24921798706055</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">4.20512342453003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1948356628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12281465530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10811710357666</t>
+    <t xml:space="preserve">4.19483518600464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1228141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1081166267395</t>
   </si>
   <si>
     <t xml:space="preserve">4.16543912887573</t>
@@ -1655,61 +1655,61 @@
     <t xml:space="preserve">4.26979541778564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30507040023804</t>
+    <t xml:space="preserve">4.3050708770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.32123899459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36827278137207</t>
+    <t xml:space="preserve">4.36827230453491</t>
   </si>
   <si>
     <t xml:space="preserve">4.33152723312378</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32564830780029</t>
+    <t xml:space="preserve">4.32564783096313</t>
   </si>
   <si>
     <t xml:space="preserve">4.288902759552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35651445388794</t>
+    <t xml:space="preserve">4.35651397705078</t>
   </si>
   <si>
     <t xml:space="preserve">4.34328556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49908590316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44764184951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4461727142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48291730880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48732709884644</t>
+    <t xml:space="preserve">4.49908542633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44764137268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44617319107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48291778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48732662200928</t>
   </si>
   <si>
     <t xml:space="preserve">4.45352125167847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43735361099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35210466384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34181547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33446645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43147420883179</t>
+    <t xml:space="preserve">4.43735265731812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35210418701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34181594848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3344669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4314751625061</t>
   </si>
   <si>
     <t xml:space="preserve">4.47997808456421</t>
@@ -1718,37 +1718,37 @@
     <t xml:space="preserve">4.44911193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43882369995117</t>
+    <t xml:space="preserve">4.43882322311401</t>
   </si>
   <si>
     <t xml:space="preserve">4.49467611312866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51966285705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50349473953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54317951202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5622878074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57698488235474</t>
+    <t xml:space="preserve">4.51966238021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50349521636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54317998886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56228733062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57698535919189</t>
   </si>
   <si>
     <t xml:space="preserve">4.52701187133789</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5417103767395</t>
+    <t xml:space="preserve">4.54170989990234</t>
   </si>
   <si>
     <t xml:space="preserve">4.54905891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40207815170288</t>
+    <t xml:space="preserve">4.40207767486572</t>
   </si>
   <si>
     <t xml:space="preserve">4.43588352203369</t>
@@ -1757,28 +1757,28 @@
     <t xml:space="preserve">4.4255952835083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38885021209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38150119781494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2448091506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20218420028687</t>
+    <t xml:space="preserve">4.38884973526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38150072097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24480867385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20218372344971</t>
   </si>
   <si>
     <t xml:space="preserve">4.29037284851074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29331254959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27420473098755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26097583770752</t>
+    <t xml:space="preserve">4.29331207275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27420425415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26097631454468</t>
   </si>
   <si>
     <t xml:space="preserve">4.28449296951294</t>
@@ -1790,22 +1790,22 @@
     <t xml:space="preserve">4.11399555206299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16102933883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24186849594116</t>
+    <t xml:space="preserve">4.16102981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24186897277832</t>
   </si>
   <si>
     <t xml:space="preserve">4.15662002563477</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3036003112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21835136413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20071411132812</t>
+    <t xml:space="preserve">4.30360078811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2183518409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20071458816528</t>
   </si>
   <si>
     <t xml:space="preserve">4.19777393341064</t>
@@ -1814,19 +1814,19 @@
     <t xml:space="preserve">4.34034633636475</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33593702316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34916496276855</t>
+    <t xml:space="preserve">4.33593654632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34916543960571</t>
   </si>
   <si>
     <t xml:space="preserve">4.31388998031616</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30213165283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20806360244751</t>
+    <t xml:space="preserve">4.30213069915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20806264877319</t>
   </si>
   <si>
     <t xml:space="preserve">4.14192199707031</t>
@@ -1835,34 +1835,34 @@
     <t xml:space="preserve">4.10370683670044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18307685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14045143127441</t>
+    <t xml:space="preserve">4.18307638168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14045238494873</t>
   </si>
   <si>
     <t xml:space="preserve">4.12575387954712</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19336462020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18160629272461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18454599380493</t>
+    <t xml:space="preserve">4.1933650970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18160676956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18454647064209</t>
   </si>
   <si>
     <t xml:space="preserve">4.25215768814087</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29919099807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39031934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32711791992188</t>
+    <t xml:space="preserve">4.29919147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39031982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32711744308472</t>
   </si>
   <si>
     <t xml:space="preserve">4.30066156387329</t>
@@ -1877,16 +1877,16 @@
     <t xml:space="preserve">4.36974239349365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24774837493896</t>
+    <t xml:space="preserve">4.24774789810181</t>
   </si>
   <si>
     <t xml:space="preserve">4.18895530700684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011016845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18748617172241</t>
+    <t xml:space="preserve">4.23011064529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18748569488525</t>
   </si>
   <si>
     <t xml:space="preserve">4.17425727844238</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">4.18013715744019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.238929271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25362730026245</t>
+    <t xml:space="preserve">4.23892879486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25362682342529</t>
   </si>
   <si>
     <t xml:space="preserve">4.29478216171265</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">4.33740615844727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35063505172729</t>
+    <t xml:space="preserve">4.35063457489014</t>
   </si>
   <si>
     <t xml:space="preserve">4.28302335739136</t>
@@ -1931,28 +1931,28 @@
     <t xml:space="preserve">4.37268161773682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39178895950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27861404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22423124313354</t>
+    <t xml:space="preserve">4.39178943634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27861452102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22423076629639</t>
   </si>
   <si>
     <t xml:space="preserve">4.23745965957642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22570133209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19189548492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22129154205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23598957061768</t>
+    <t xml:space="preserve">4.22570085525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19189596176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22129201889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23599004745483</t>
   </si>
   <si>
     <t xml:space="preserve">4.22717094421387</t>
@@ -1970,31 +1970,31 @@
     <t xml:space="preserve">4.04932355880737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01992750167847</t>
+    <t xml:space="preserve">4.01992702484131</t>
   </si>
   <si>
     <t xml:space="preserve">3.95378637313843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99494051933289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0419750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99053168296814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03609561920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1066460609436</t>
+    <t xml:space="preserve">3.9949414730072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04197454452515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99053120613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03609609603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10664701461792</t>
   </si>
   <si>
     <t xml:space="preserve">4.16396903991699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12722396850586</t>
+    <t xml:space="preserve">4.1272234916687</t>
   </si>
   <si>
     <t xml:space="preserve">4.13751220703125</t>
@@ -2003,19 +2003,19 @@
     <t xml:space="preserve">4.00082015991211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09194803237915</t>
+    <t xml:space="preserve">4.09194850921631</t>
   </si>
   <si>
     <t xml:space="preserve">4.08459949493408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02727699279785</t>
+    <t xml:space="preserve">4.02727651596069</t>
   </si>
   <si>
     <t xml:space="preserve">4.02286767959595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10076713562012</t>
+    <t xml:space="preserve">4.10076761245728</t>
   </si>
   <si>
     <t xml:space="preserve">4.20365381240845</t>
@@ -2027,37 +2027,37 @@
     <t xml:space="preserve">4.25068759918213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20659351348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26391649246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30801057815552</t>
+    <t xml:space="preserve">4.20659399032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.263916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30801010131836</t>
   </si>
   <si>
     <t xml:space="preserve">4.48144769668579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51525354385376</t>
+    <t xml:space="preserve">4.5152530670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.49761533737183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40648698806763</t>
+    <t xml:space="preserve">4.40648794174194</t>
   </si>
   <si>
     <t xml:space="preserve">4.41677618026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46674966812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49173641204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46087026596069</t>
+    <t xml:space="preserve">4.46674919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4917368888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46087074279785</t>
   </si>
   <si>
     <t xml:space="preserve">4.46234035491943</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">4.4858570098877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62548923492432</t>
+    <t xml:space="preserve">4.62548971176147</t>
   </si>
   <si>
     <t xml:space="preserve">4.26538562774658</t>
@@ -2084,76 +2084,76 @@
     <t xml:space="preserve">4.06549215316772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08606863021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72890543937683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51798844337463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50181984901428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02192759513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24754333496094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15127086639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27032470703125</t>
+    <t xml:space="preserve">4.08606910705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72890520095825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51798820495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50182008743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02192735671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24754309654236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15127062797546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27032518386841</t>
   </si>
   <si>
     <t xml:space="preserve">3.29531216621399</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35189938545227</t>
+    <t xml:space="preserve">3.35189914703369</t>
   </si>
   <si>
     <t xml:space="preserve">3.21153283119202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12995839118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35557436943054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38937950134277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34381556510925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3592483997345</t>
+    <t xml:space="preserve">3.129958152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35557413101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38937997817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34381580352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35924816131592</t>
   </si>
   <si>
     <t xml:space="preserve">3.5709011554718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66643881797791</t>
+    <t xml:space="preserve">3.66643834114075</t>
   </si>
   <si>
     <t xml:space="preserve">3.44964194297791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55693769454956</t>
+    <t xml:space="preserve">3.55693817138672</t>
   </si>
   <si>
     <t xml:space="preserve">3.58780384063721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53636026382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54958915710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46580982208252</t>
+    <t xml:space="preserve">3.53636050224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54958844184875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4658100605011</t>
   </si>
   <si>
     <t xml:space="preserve">3.54811906814575</t>
@@ -2165,31 +2165,31 @@
     <t xml:space="preserve">3.59368348121643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62601900100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57163572311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57310557365417</t>
+    <t xml:space="preserve">3.62601852416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57163619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57310581207275</t>
   </si>
   <si>
     <t xml:space="preserve">3.44082307815552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61719989776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52754163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57457566261292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56722664833069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57898473739624</t>
+    <t xml:space="preserve">3.61719965934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52754211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57457518577576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56722640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57898497581482</t>
   </si>
   <si>
     <t xml:space="preserve">3.75168752670288</t>
@@ -2198,82 +2198,82 @@
     <t xml:space="preserve">3.68187165260315</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70391845703125</t>
+    <t xml:space="preserve">3.70391869544983</t>
   </si>
   <si>
     <t xml:space="preserve">3.60691165924072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61279034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66423392295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6318986415863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62454915046692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63777780532837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62307929992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71126818656921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73626232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60662746429443</t>
+    <t xml:space="preserve">3.61279082298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66423416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63189816474915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6245493888855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63777709007263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62307906150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71126794815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73626255989075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60662770271301</t>
   </si>
   <si>
     <t xml:space="preserve">3.66372871398926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63440680503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68533444404602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75015187263489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73008942604065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70231008529663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80725336074829</t>
+    <t xml:space="preserve">3.63440656661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6853346824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75015234947205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73008966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70231080055237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80725288391113</t>
   </si>
   <si>
     <t xml:space="preserve">3.77021479606628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81959939002991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90447974205017</t>
+    <t xml:space="preserve">3.81959891319275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90447878837585</t>
   </si>
   <si>
     <t xml:space="preserve">3.99707531929016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05108976364136</t>
+    <t xml:space="preserve">4.05109024047852</t>
   </si>
   <si>
     <t xml:space="preserve">4.02408266067505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9276282787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88133025169373</t>
+    <t xml:space="preserve">3.92762875556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88133072853088</t>
   </si>
   <si>
     <t xml:space="preserve">3.81651282310486</t>
@@ -2288,16 +2288,16 @@
     <t xml:space="preserve">4.05880641937256</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10896301269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14754486083984</t>
+    <t xml:space="preserve">4.10896253585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14754438400269</t>
   </si>
   <si>
     <t xml:space="preserve">4.02022457122803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96620965003967</t>
+    <t xml:space="preserve">3.96621012687683</t>
   </si>
   <si>
     <t xml:space="preserve">3.98935961723328</t>
@@ -2306,10 +2306,10 @@
     <t xml:space="preserve">4.03565740585327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08967208862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03179931640625</t>
+    <t xml:space="preserve">4.08967256546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03179836273193</t>
   </si>
   <si>
     <t xml:space="preserve">4.07038116455078</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">4.05494832992554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95463538169861</t>
+    <t xml:space="preserve">3.95463585853577</t>
   </si>
   <si>
     <t xml:space="preserve">3.96235251426697</t>
@@ -2330,22 +2330,22 @@
     <t xml:space="preserve">3.93534445762634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97006869316101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97392630577087</t>
+    <t xml:space="preserve">3.97006821632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97392678260803</t>
   </si>
   <si>
     <t xml:space="preserve">4.0742392539978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12439489364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10510444641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09352970123291</t>
+    <t xml:space="preserve">4.1243953704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10510492324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09353017807007</t>
   </si>
   <si>
     <t xml:space="preserve">4.04723167419434</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">4.12825345993042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25943183898926</t>
+    <t xml:space="preserve">4.25943231582642</t>
   </si>
   <si>
     <t xml:space="preserve">4.26714897155762</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">4.21313381195068</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1977014541626</t>
+    <t xml:space="preserve">4.19770097732544</t>
   </si>
   <si>
     <t xml:space="preserve">4.16297721862793</t>
@@ -2378,13 +2378,13 @@
     <t xml:space="preserve">4.28643941879272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36746072769165</t>
+    <t xml:space="preserve">4.36746120452881</t>
   </si>
   <si>
     <t xml:space="preserve">4.42147588729858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3906102180481</t>
+    <t xml:space="preserve">4.39061069488525</t>
   </si>
   <si>
     <t xml:space="preserve">4.37517786026001</t>
@@ -2393,16 +2393,16 @@
     <t xml:space="preserve">4.36360311508179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30573034286499</t>
+    <t xml:space="preserve">4.30572986602783</t>
   </si>
   <si>
     <t xml:space="preserve">4.26328992843628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24399948120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31344699859619</t>
+    <t xml:space="preserve">4.24399900436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31344652175903</t>
   </si>
   <si>
     <t xml:space="preserve">4.30187129974365</t>
@@ -2411,10 +2411,10 @@
     <t xml:space="preserve">4.13597011566162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22856664657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18612670898438</t>
+    <t xml:space="preserve">4.22856616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18612718582153</t>
   </si>
   <si>
     <t xml:space="preserve">4.17455196380615</t>
@@ -2429,28 +2429,28 @@
     <t xml:space="preserve">4.17841005325317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15526151657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15140247344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15911912918091</t>
+    <t xml:space="preserve">4.15526103973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15140295028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15911960601807</t>
   </si>
   <si>
     <t xml:space="preserve">4.19384288787842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07809734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89290499687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97778534889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06266450881958</t>
+    <t xml:space="preserve">4.07809782028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89290452003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97778487205505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06266498565674</t>
   </si>
   <si>
     <t xml:space="preserve">3.94691920280457</t>
@@ -2465,19 +2465,19 @@
     <t xml:space="preserve">3.88904643058777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71157026290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72700333595276</t>
+    <t xml:space="preserve">3.71157050132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72700262069702</t>
   </si>
   <si>
     <t xml:space="preserve">3.82885885238647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83194518089294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86589741706848</t>
+    <t xml:space="preserve">3.8319456577301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86589789390564</t>
   </si>
   <si>
     <t xml:space="preserve">4.00479125976562</t>
@@ -2492,22 +2492,22 @@
     <t xml:space="preserve">4.03951549530029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13982820510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17069339752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14368581771851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13211154937744</t>
+    <t xml:space="preserve">4.13982772827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17069387435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14368677139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1321120262146</t>
   </si>
   <si>
     <t xml:space="preserve">3.93920302391052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90062117576599</t>
+    <t xml:space="preserve">3.90062069892883</t>
   </si>
   <si>
     <t xml:space="preserve">3.80879616737366</t>
@@ -2519,16 +2519,16 @@
     <t xml:space="preserve">4.01250791549683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95849347114563</t>
+    <t xml:space="preserve">3.95849394798279</t>
   </si>
   <si>
     <t xml:space="preserve">3.8774721622467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93148684501648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92377066612244</t>
+    <t xml:space="preserve">3.93148636817932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92377018928528</t>
   </si>
   <si>
     <t xml:space="preserve">3.86203932762146</t>
@@ -2555,52 +2555,52 @@
     <t xml:space="preserve">3.83811902999878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9430615901947</t>
+    <t xml:space="preserve">3.94306111335754</t>
   </si>
   <si>
     <t xml:space="preserve">3.90833735466003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88518881797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83503174781799</t>
+    <t xml:space="preserve">3.88518834114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83503127098083</t>
   </si>
   <si>
     <t xml:space="preserve">3.76712822914124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76249766349792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82268619537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79799342155457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87361359596252</t>
+    <t xml:space="preserve">3.76249814033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82268571853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79799294471741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87361407279968</t>
   </si>
   <si>
     <t xml:space="preserve">4.02794075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04337310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20927572250366</t>
+    <t xml:space="preserve">4.04337358474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2092752456665</t>
   </si>
   <si>
     <t xml:space="preserve">4.25171566009521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25557327270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31730461120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27100610733032</t>
+    <t xml:space="preserve">4.25557374954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3173041343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27100658416748</t>
   </si>
   <si>
     <t xml:space="preserve">4.26251840591431</t>
@@ -2621,34 +2621,34 @@
     <t xml:space="preserve">4.12979698181152</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14060020446777</t>
+    <t xml:space="preserve">4.14059972763062</t>
   </si>
   <si>
     <t xml:space="preserve">4.12362337112427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16837882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17146587371826</t>
+    <t xml:space="preserve">4.16837930679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1714653968811</t>
   </si>
   <si>
     <t xml:space="preserve">4.19924402236938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23628282546997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18844175338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17763805389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17918157577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18381118774414</t>
+    <t xml:space="preserve">4.23628234863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18844127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1776385307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1791820526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1838116645813</t>
   </si>
   <si>
     <t xml:space="preserve">4.20387411117554</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">4.18535470962524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21621990203857</t>
+    <t xml:space="preserve">4.21622037887573</t>
   </si>
   <si>
     <t xml:space="preserve">4.29338407516479</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">4.25017213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23782587051392</t>
+    <t xml:space="preserve">4.23782634735107</t>
   </si>
   <si>
     <t xml:space="preserve">4.35048484802246</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">4.34122562408447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39369583129883</t>
+    <t xml:space="preserve">4.39369678497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.47086048126221</t>
@@ -2687,22 +2687,22 @@
     <t xml:space="preserve">4.46610307693481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44025039672852</t>
+    <t xml:space="preserve">4.44024991989136</t>
   </si>
   <si>
     <t xml:space="preserve">4.3885440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35622835159302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38531303405762</t>
+    <t xml:space="preserve">4.35622787475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38531255722046</t>
   </si>
   <si>
     <t xml:space="preserve">4.37400197982788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39016008377075</t>
+    <t xml:space="preserve">4.39015960693359</t>
   </si>
   <si>
     <t xml:space="preserve">4.37723398208618</t>
@@ -2714,10 +2714,10 @@
     <t xml:space="preserve">4.45156097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47418260574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49357223510742</t>
+    <t xml:space="preserve">4.47418212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49357175827026</t>
   </si>
   <si>
     <t xml:space="preserve">4.50165128707886</t>
@@ -2726,10 +2726,10 @@
     <t xml:space="preserve">4.52911996841431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5517406463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55012559890747</t>
+    <t xml:space="preserve">4.55174160003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55012512207031</t>
   </si>
   <si>
     <t xml:space="preserve">4.62122058868408</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">4.49680376052856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48226165771484</t>
+    <t xml:space="preserve">4.48226118087769</t>
   </si>
   <si>
     <t xml:space="preserve">4.48710918426514</t>
@@ -2762,10 +2762,10 @@
     <t xml:space="preserve">4.45317697525024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46771907806396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49841928482056</t>
+    <t xml:space="preserve">4.46771955490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49841976165771</t>
   </si>
   <si>
     <t xml:space="preserve">4.50649881362915</t>
@@ -2777,10 +2777,10 @@
     <t xml:space="preserve">4.4790301322937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52265691757202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54204702377319</t>
+    <t xml:space="preserve">4.52265644073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54204654693604</t>
   </si>
   <si>
     <t xml:space="preserve">4.54689359664917</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">4.37884902954102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35461235046387</t>
+    <t xml:space="preserve">4.35461282730103</t>
   </si>
   <si>
     <t xml:space="preserve">4.37238597869873</t>
@@ -2810,10 +2810,10 @@
     <t xml:space="preserve">4.6147575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61637401580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62768411636353</t>
+    <t xml:space="preserve">4.61637353897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62768459320068</t>
   </si>
   <si>
     <t xml:space="preserve">4.59375190734863</t>
@@ -2822,40 +2822,40 @@
     <t xml:space="preserve">4.60829496383667</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63091611862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65676879882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66484880447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69070100784302</t>
+    <t xml:space="preserve">4.63091564178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65676927566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66484832763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69070148468018</t>
   </si>
   <si>
     <t xml:space="preserve">4.73271179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76502799987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80219221115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79896020889282</t>
+    <t xml:space="preserve">4.76502847671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80219173431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79896068572998</t>
   </si>
   <si>
     <t xml:space="preserve">4.76987600326538</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82804441452026</t>
+    <t xml:space="preserve">4.82804489135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.82481384277344</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84420299530029</t>
+    <t xml:space="preserve">4.84420347213745</t>
   </si>
   <si>
     <t xml:space="preserve">4.80703926086426</t>
@@ -2864,28 +2864,28 @@
     <t xml:space="preserve">4.69554853439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57436275482178</t>
+    <t xml:space="preserve">4.57436323165894</t>
   </si>
   <si>
     <t xml:space="preserve">4.53558301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5921368598938</t>
+    <t xml:space="preserve">4.59213638305664</t>
   </si>
   <si>
     <t xml:space="preserve">4.54366207122803</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49034023284912</t>
+    <t xml:space="preserve">4.49034070968628</t>
   </si>
   <si>
     <t xml:space="preserve">4.49195623397827</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48549318313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45964002609253</t>
+    <t xml:space="preserve">4.48549270629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45964050292969</t>
   </si>
   <si>
     <t xml:space="preserve">4.51134586334229</t>
@@ -2894,19 +2894,19 @@
     <t xml:space="preserve">4.52427244186401</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46125602722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58567333221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63576316833496</t>
+    <t xml:space="preserve">4.46125555038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58567380905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63576364517212</t>
   </si>
   <si>
     <t xml:space="preserve">4.58890438079834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65353775024414</t>
+    <t xml:space="preserve">4.65353727340698</t>
   </si>
   <si>
     <t xml:space="preserve">4.57113122940063</t>
@@ -2921,10 +2921,10 @@
     <t xml:space="preserve">4.46933507919312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43217134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47095060348511</t>
+    <t xml:space="preserve">4.43217182159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47095108032227</t>
   </si>
   <si>
     <t xml:space="preserve">4.48387718200684</t>
@@ -2939,7 +2939,7 @@
     <t xml:space="preserve">4.39662313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41116523742676</t>
+    <t xml:space="preserve">4.41116571426392</t>
   </si>
   <si>
     <t xml:space="preserve">4.51457786560059</t>
@@ -2957,19 +2957,19 @@
     <t xml:space="preserve">4.53881454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6131420135498</t>
+    <t xml:space="preserve">4.61314249038696</t>
   </si>
   <si>
     <t xml:space="preserve">4.63253164291382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60021495819092</t>
+    <t xml:space="preserve">4.60021543502808</t>
   </si>
   <si>
     <t xml:space="preserve">4.55658864974976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57920980453491</t>
+    <t xml:space="preserve">4.57921028137207</t>
   </si>
   <si>
     <t xml:space="preserve">4.52588844299316</t>
@@ -2981,7 +2981,7 @@
     <t xml:space="preserve">4.53235149383545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44832944869995</t>
+    <t xml:space="preserve">4.44832992553711</t>
   </si>
   <si>
     <t xml:space="preserve">4.5048828125</t>
@@ -2990,19 +2990,19 @@
     <t xml:space="preserve">4.71978569030762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72301721572876</t>
+    <t xml:space="preserve">4.72301769256592</t>
   </si>
   <si>
     <t xml:space="preserve">4.65838479995728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68262195587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65515279769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64384269714355</t>
+    <t xml:space="preserve">4.68262147903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65515327453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6438422203064</t>
   </si>
   <si>
     <t xml:space="preserve">4.70201206207275</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">4.68585395812988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70362758636475</t>
+    <t xml:space="preserve">4.7036280632019</t>
   </si>
   <si>
     <t xml:space="preserve">4.66807985305786</t>
@@ -3023,19 +3023,19 @@
     <t xml:space="preserve">4.7262487411499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76179647445679</t>
+    <t xml:space="preserve">4.76179695129395</t>
   </si>
   <si>
     <t xml:space="preserve">4.75048637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84905004501343</t>
+    <t xml:space="preserve">4.84905052185059</t>
   </si>
   <si>
     <t xml:space="preserve">4.87490367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88944578170776</t>
+    <t xml:space="preserve">4.88944530487061</t>
   </si>
   <si>
     <t xml:space="preserve">4.91853046417236</t>
@@ -3053,10 +3053,10 @@
     <t xml:space="preserve">4.64061117172241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7294807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74402236938477</t>
+    <t xml:space="preserve">4.72948026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74402284622192</t>
   </si>
   <si>
     <t xml:space="preserve">4.76018095016479</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">4.74079132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79734468460083</t>
+    <t xml:space="preserve">4.79734516143799</t>
   </si>
   <si>
     <t xml:space="preserve">4.71655368804932</t>
@@ -3086,22 +3086,22 @@
     <t xml:space="preserve">4.46448755264282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57759428024292</t>
+    <t xml:space="preserve">4.57759380340576</t>
   </si>
   <si>
     <t xml:space="preserve">4.62930059432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55982065200806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54851007461548</t>
+    <t xml:space="preserve">4.5598201751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54850959777832</t>
   </si>
   <si>
     <t xml:space="preserve">4.50326681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41278171539307</t>
+    <t xml:space="preserve">4.41278123855591</t>
   </si>
   <si>
     <t xml:space="preserve">4.35299634933472</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">4.55820465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51780891418457</t>
+    <t xml:space="preserve">4.51780939102173</t>
   </si>
   <si>
     <t xml:space="preserve">4.49518775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4176287651062</t>
+    <t xml:space="preserve">4.41762828826904</t>
   </si>
   <si>
     <t xml:space="preserve">4.48872470855713</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">4.70524311065674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73028802871704</t>
+    <t xml:space="preserve">4.73028898239136</t>
   </si>
   <si>
     <t xml:space="preserve">4.68181419372559</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">4.77472305297852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89590930938721</t>
+    <t xml:space="preserve">4.89590883255005</t>
   </si>
   <si>
     <t xml:space="preserve">4.94034385681152</t>
@@ -3158,16 +3158,16 @@
     <t xml:space="preserve">5.04537153244019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15039968490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08980655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06556940078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98073959350586</t>
+    <t xml:space="preserve">5.15039920806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08980703353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0655689239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9807391166687</t>
   </si>
   <si>
     <t xml:space="preserve">4.96054124832153</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">5.01709508895874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00093650817871</t>
+    <t xml:space="preserve">5.00093698501587</t>
   </si>
   <si>
     <t xml:space="preserve">5.01305532455444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97266006469727</t>
+    <t xml:space="preserve">4.97266054153442</t>
   </si>
   <si>
     <t xml:space="preserve">4.8999490737915</t>
@@ -3194,10 +3194,10 @@
     <t xml:space="preserve">4.94842290878296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92014598846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10596466064453</t>
+    <t xml:space="preserve">4.92014646530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10596513748169</t>
   </si>
   <si>
     <t xml:space="preserve">5.05345058441162</t>
@@ -4130,9 +4130,6 @@
     <t xml:space="preserve">4.52464294433594</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54170989990234</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.53602123260498</t>
   </si>
   <si>
@@ -4944,6 +4941,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.40499973297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29500007629395</t>
   </si>
 </sst>
 </file>
@@ -56156,7 +56156,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>1372</v>
+        <v>576</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -56182,7 +56182,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1958" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -56234,7 +56234,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G1960" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -56286,7 +56286,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G1962" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -56312,7 +56312,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1963" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -56338,7 +56338,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G1964" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -56364,7 +56364,7 @@
         <v>4.92799997329712</v>
       </c>
       <c r="G1965" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -56390,7 +56390,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1966" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -56416,7 +56416,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1967" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -56442,7 +56442,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G1968" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -56468,7 +56468,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1969" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -56494,7 +56494,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G1970" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -56520,7 +56520,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G1971" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56546,7 +56546,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G1972" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -56572,7 +56572,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G1973" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -56598,7 +56598,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G1974" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -56624,7 +56624,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1975" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -56650,7 +56650,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G1976" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -56676,7 +56676,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1977" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -56702,7 +56702,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1978" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -56780,7 +56780,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G1981" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -56806,7 +56806,7 @@
         <v>4.98199987411499</v>
       </c>
       <c r="G1982" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -56832,7 +56832,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1983" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -56858,7 +56858,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1984" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56884,7 +56884,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G1985" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56910,7 +56910,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1986" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56936,7 +56936,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1987" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56988,7 +56988,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1989" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -57014,7 +57014,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G1990" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -57040,7 +57040,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1991" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -57066,7 +57066,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -57092,7 +57092,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1993" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -57118,7 +57118,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1994" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -57144,7 +57144,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1995" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -57170,7 +57170,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1996" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -57196,7 +57196,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G1997" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -57222,7 +57222,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G1998" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -57248,7 +57248,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G1999" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57274,7 +57274,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G2000" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57300,7 +57300,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -57326,7 +57326,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G2002" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -57352,7 +57352,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -57378,7 +57378,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2004" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -57404,7 +57404,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G2005" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -57430,7 +57430,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G2006" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -57456,7 +57456,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G2007" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -57482,7 +57482,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2008" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -57508,7 +57508,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G2009" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -57534,7 +57534,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2010" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -57560,7 +57560,7 @@
         <v>5.5</v>
       </c>
       <c r="G2011" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -57586,7 +57586,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2012" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -57612,7 +57612,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G2013" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -57638,7 +57638,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2014" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -57664,7 +57664,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2015" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -57690,7 +57690,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2016" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -57716,7 +57716,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G2017" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -57742,7 +57742,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G2018" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -57768,7 +57768,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2019" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57794,7 +57794,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G2020" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -57820,7 +57820,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2021" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -57846,7 +57846,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G2022" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -57872,7 +57872,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2023" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57898,7 +57898,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G2024" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57924,7 +57924,7 @@
         <v>5.875</v>
       </c>
       <c r="G2025" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57950,7 +57950,7 @@
         <v>5.79500007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57976,7 +57976,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G2027" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -58002,7 +58002,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2028" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -58028,7 +58028,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G2029" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -58054,7 +58054,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G2030" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -58080,7 +58080,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2031" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -58106,7 +58106,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2032" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -58132,7 +58132,7 @@
         <v>5.625</v>
       </c>
       <c r="G2033" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -58158,7 +58158,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G2034" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -58184,7 +58184,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2035" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58210,7 +58210,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2036" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58236,7 +58236,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2037" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58262,7 +58262,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G2038" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58288,7 +58288,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G2039" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58314,7 +58314,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G2040" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -58340,7 +58340,7 @@
         <v>5.5</v>
       </c>
       <c r="G2041" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -58366,7 +58366,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G2042" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -58392,7 +58392,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2043" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -58418,7 +58418,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G2044" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58444,7 +58444,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G2045" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -58470,7 +58470,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G2046" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -58496,7 +58496,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G2047" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58522,7 +58522,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2048" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -58548,7 +58548,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G2049" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -58574,7 +58574,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G2050" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -58600,7 +58600,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2051" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -58626,7 +58626,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -58652,7 +58652,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2053" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -58678,7 +58678,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2054" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -58704,7 +58704,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G2055" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -58730,7 +58730,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G2056" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -58756,7 +58756,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G2057" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -58782,7 +58782,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G2058" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -58808,7 +58808,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G2059" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -58834,7 +58834,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G2060" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -58860,7 +58860,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G2061" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58886,7 +58886,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G2062" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58912,7 +58912,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G2063" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58938,7 +58938,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2064" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58964,7 +58964,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2065" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58990,7 +58990,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2066" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -59016,7 +59016,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2067" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -59042,7 +59042,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G2068" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -59068,7 +59068,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2069" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -59094,7 +59094,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2070" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -59120,7 +59120,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2071" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -59146,7 +59146,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2072" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -59172,7 +59172,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G2073" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -59198,7 +59198,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2074" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -59224,7 +59224,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G2075" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -59250,7 +59250,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2076" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59276,7 +59276,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2077" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59302,7 +59302,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G2078" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -59328,7 +59328,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G2079" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -59354,7 +59354,7 @@
         <v>5.375</v>
       </c>
       <c r="G2080" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -59380,7 +59380,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2081" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -59406,7 +59406,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G2082" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59432,7 +59432,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G2083" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -59458,7 +59458,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2084" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -59484,7 +59484,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G2085" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59510,7 +59510,7 @@
         <v>5.625</v>
       </c>
       <c r="G2086" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -59536,7 +59536,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G2087" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -59562,7 +59562,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2088" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -59588,7 +59588,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G2089" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -59614,7 +59614,7 @@
         <v>5.63500022888184</v>
       </c>
       <c r="G2090" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -59640,7 +59640,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G2091" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -59666,7 +59666,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G2092" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -59692,7 +59692,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G2093" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -59718,7 +59718,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2094" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -59744,7 +59744,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G2095" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -59770,7 +59770,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G2096" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -59796,7 +59796,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G2097" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -59822,7 +59822,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2098" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -59848,7 +59848,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2099" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59874,7 +59874,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G2100" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59900,7 +59900,7 @@
         <v>5.875</v>
       </c>
       <c r="G2101" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59926,7 +59926,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G2102" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59952,7 +59952,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G2103" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59978,7 +59978,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G2104" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -60004,7 +60004,7 @@
         <v>5.90500020980835</v>
       </c>
       <c r="G2105" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -60030,7 +60030,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G2106" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -60056,7 +60056,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G2107" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -60082,7 +60082,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2108" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -60108,7 +60108,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G2109" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -60134,7 +60134,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G2110" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60160,7 +60160,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G2111" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -60186,7 +60186,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G2112" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -60212,7 +60212,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G2113" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -60238,7 +60238,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G2114" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60264,7 +60264,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G2115" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60290,7 +60290,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G2116" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -60316,7 +60316,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G2117" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -60342,7 +60342,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G2118" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -60368,7 +60368,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -60394,7 +60394,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G2120" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -60420,7 +60420,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G2121" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60446,7 +60446,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G2122" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60472,7 +60472,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G2123" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60498,7 +60498,7 @@
         <v>6.125</v>
       </c>
       <c r="G2124" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -60524,7 +60524,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G2125" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -60550,7 +60550,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G2126" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -60576,7 +60576,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G2127" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -60602,7 +60602,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G2128" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -60628,7 +60628,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G2129" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -60654,7 +60654,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G2130" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -60680,7 +60680,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G2131" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -60706,7 +60706,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G2132" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -60732,7 +60732,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G2133" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -60758,7 +60758,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G2134" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -60784,7 +60784,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G2135" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -60810,7 +60810,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G2136" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -60836,7 +60836,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G2137" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -60862,7 +60862,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G2138" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60888,7 +60888,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G2139" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60914,7 +60914,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2140" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60940,7 +60940,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G2141" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60966,7 +60966,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G2142" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60992,7 +60992,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2143" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -61018,7 +61018,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G2144" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -61044,7 +61044,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G2145" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -61070,7 +61070,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G2146" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -61096,7 +61096,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G2147" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -61122,7 +61122,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2148" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61148,7 +61148,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G2149" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -61174,7 +61174,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G2150" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -61200,7 +61200,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G2151" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -61226,7 +61226,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G2152" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -61252,7 +61252,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G2153" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61278,7 +61278,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G2154" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61304,7 +61304,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2155" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -61330,7 +61330,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2156" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -61356,7 +61356,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -61382,7 +61382,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G2158" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -61408,7 +61408,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G2159" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61434,7 +61434,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G2160" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61460,7 +61460,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2161" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61486,7 +61486,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G2162" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61512,7 +61512,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2163" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -61538,7 +61538,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2164" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -61564,7 +61564,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G2165" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -61590,7 +61590,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G2166" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -61616,7 +61616,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2167" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -61642,7 +61642,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G2168" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -61668,7 +61668,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G2169" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -61694,7 +61694,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G2170" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -61720,7 +61720,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G2171" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -61746,7 +61746,7 @@
         <v>6.72816181182861</v>
       </c>
       <c r="G2172" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -61772,7 +61772,7 @@
         <v>6.69060087203979</v>
       </c>
       <c r="G2173" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -61798,7 +61798,7 @@
         <v>6.66712522506714</v>
       </c>
       <c r="G2174" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61824,7 +61824,7 @@
         <v>6.61547899246216</v>
       </c>
       <c r="G2175" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -61850,7 +61850,7 @@
         <v>6.78919982910156</v>
       </c>
       <c r="G2176" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61876,7 +61876,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G2177" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61902,7 +61902,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G2178" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61928,7 +61928,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2179" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61954,7 +61954,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61980,7 +61980,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G2181" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62006,7 +62006,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G2182" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62032,7 +62032,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2183" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62058,7 +62058,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G2184" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62084,7 +62084,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2185" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62110,7 +62110,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G2186" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62136,7 +62136,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2187" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62162,7 +62162,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G2188" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62188,7 +62188,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2189" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62214,7 +62214,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G2190" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62240,7 +62240,7 @@
         <v>7</v>
       </c>
       <c r="G2191" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62266,7 +62266,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2192" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62292,7 +62292,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2193" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62318,7 +62318,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G2194" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62344,7 +62344,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G2195" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62370,7 +62370,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2196" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62396,7 +62396,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2197" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62422,7 +62422,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2198" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62448,7 +62448,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G2199" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62474,7 +62474,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2200" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62500,7 +62500,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2201" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62526,7 +62526,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G2202" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62552,7 +62552,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G2203" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -62578,7 +62578,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -62604,7 +62604,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2205" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -62630,7 +62630,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2206" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -62656,7 +62656,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2207" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -62682,7 +62682,7 @@
         <v>6.88500022888184</v>
       </c>
       <c r="G2208" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -62708,7 +62708,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G2209" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62734,7 +62734,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G2210" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62760,7 +62760,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2211" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -62786,7 +62786,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G2212" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62812,7 +62812,7 @@
         <v>7.25</v>
       </c>
       <c r="G2213" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -62838,7 +62838,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2214" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -62864,7 +62864,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G2215" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62890,7 +62890,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G2216" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62916,7 +62916,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2217" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62942,7 +62942,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G2218" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62968,7 +62968,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G2219" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62994,7 +62994,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G2220" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63020,7 +63020,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2221" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63046,7 +63046,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2222" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63072,7 +63072,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2223" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63098,7 +63098,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2224" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63124,7 +63124,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2225" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63150,7 +63150,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G2226" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63176,7 +63176,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G2227" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63202,7 +63202,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G2228" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63228,7 +63228,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G2229" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63254,7 +63254,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2230" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63280,7 +63280,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G2231" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63306,7 +63306,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2232" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63332,7 +63332,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2233" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63358,7 +63358,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G2234" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63384,7 +63384,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2235" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63410,7 +63410,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G2236" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63436,7 +63436,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2237" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63462,7 +63462,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63488,7 +63488,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G2239" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63514,7 +63514,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G2240" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63540,7 +63540,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G2241" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63566,7 +63566,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G2242" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -63592,7 +63592,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2243" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -63618,7 +63618,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G2244" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -63644,7 +63644,7 @@
         <v>7.625</v>
       </c>
       <c r="G2245" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -63670,7 +63670,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G2246" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -63696,7 +63696,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G2247" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -63722,7 +63722,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2248" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63748,7 +63748,7 @@
         <v>7.625</v>
       </c>
       <c r="G2249" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63774,7 +63774,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G2250" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63800,7 +63800,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2251" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63826,7 +63826,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2252" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63852,7 +63852,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2253" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63878,7 +63878,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G2254" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63904,7 +63904,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2255" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63930,7 +63930,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63956,7 +63956,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G2257" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63982,7 +63982,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G2258" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64008,7 +64008,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G2259" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64034,7 +64034,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G2260" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64060,7 +64060,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G2261" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64086,7 +64086,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G2262" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64112,7 +64112,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G2263" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64138,7 +64138,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G2264" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64164,7 +64164,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G2265" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64190,7 +64190,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2266" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64216,7 +64216,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2267" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64242,7 +64242,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G2268" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64268,7 +64268,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G2269" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64294,7 +64294,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G2270" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64320,7 +64320,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2271" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64346,7 +64346,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G2272" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64372,7 +64372,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2273" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64398,7 +64398,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G2274" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64424,7 +64424,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G2275" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64450,7 +64450,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G2276" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64476,7 +64476,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2277" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64502,7 +64502,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2278" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64528,7 +64528,7 @@
         <v>8.72500038146973</v>
       </c>
       <c r="G2279" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -64554,7 +64554,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2280" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64580,7 +64580,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G2281" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64606,7 +64606,7 @@
         <v>8.875</v>
       </c>
       <c r="G2282" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64632,7 +64632,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G2283" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64658,7 +64658,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G2284" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64684,7 +64684,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G2285" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -64710,7 +64710,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2286" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64736,7 +64736,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G2287" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -64762,7 +64762,7 @@
         <v>9.28499984741211</v>
       </c>
       <c r="G2288" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64788,7 +64788,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2289" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64814,7 +64814,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G2290" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64840,7 +64840,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G2291" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -64848,7 +64848,7 @@
     </row>
     <row r="2292">
       <c r="A2292" s="1" t="n">
-        <v>45972.6911689815</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2292" t="n">
         <v>2107354</v>
@@ -64866,9 +64866,35 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G2292" t="s">
+        <v>1642</v>
+      </c>
+      <c r="H2292" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" s="1" t="n">
+        <v>45973.6912847222</v>
+      </c>
+      <c r="B2293" t="n">
+        <v>3545908</v>
+      </c>
+      <c r="C2293" t="n">
+        <v>9.39500045776367</v>
+      </c>
+      <c r="D2293" t="n">
+        <v>9.23999977111816</v>
+      </c>
+      <c r="E2293" t="n">
+        <v>9.35000038146973</v>
+      </c>
+      <c r="F2293" t="n">
+        <v>9.29500007629395</v>
+      </c>
+      <c r="G2293" t="s">
         <v>1643</v>
       </c>
-      <c r="H2292" t="s">
+      <c r="H2293" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="1647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="1648">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58873581886292</t>
+    <t xml:space="preserve">2.58873558044434</t>
   </si>
   <si>
     <t xml:space="preserve">IG.MI</t>
@@ -47,64 +47,64 @@
     <t xml:space="preserve">2.5013575553894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32790565490723</t>
+    <t xml:space="preserve">2.32790589332581</t>
   </si>
   <si>
     <t xml:space="preserve">2.16488718986511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17271208763123</t>
+    <t xml:space="preserve">2.1727123260498</t>
   </si>
   <si>
     <t xml:space="preserve">2.09315896034241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06185960769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08663845062256</t>
+    <t xml:space="preserve">2.06185913085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08663821220398</t>
   </si>
   <si>
     <t xml:space="preserve">2.04490518569946</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06055521965027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04360127449036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10489654541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12967538833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14532494544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17923283576965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20009922981262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20140361785889</t>
+    <t xml:space="preserve">2.06055545806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04360151290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10489630699158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1296751499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14532518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17923331260681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20009899139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20140314102173</t>
   </si>
   <si>
     <t xml:space="preserve">2.17792868614197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13228344917297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09837579727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22357416152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29138994216919</t>
+    <t xml:space="preserve">2.13228321075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09837532043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22357392311096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29138970375061</t>
   </si>
   <si>
     <t xml:space="preserve">2.33181834220886</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">2.2379195690155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30051875114441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30443120002747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37094259262085</t>
+    <t xml:space="preserve">2.30051851272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30443096160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37094283103943</t>
   </si>
   <si>
     <t xml:space="preserve">2.3461639881134</t>
@@ -131,28 +131,28 @@
     <t xml:space="preserve">2.39572167396545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45571231842041</t>
+    <t xml:space="preserve">2.45571255683899</t>
   </si>
   <si>
     <t xml:space="preserve">2.39702558517456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38007164001465</t>
+    <t xml:space="preserve">2.38007187843323</t>
   </si>
   <si>
     <t xml:space="preserve">2.39441752433777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42180442810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41006731987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43093347549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43745398521423</t>
+    <t xml:space="preserve">2.42180466651917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41006708145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43093323707581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43745422363281</t>
   </si>
   <si>
     <t xml:space="preserve">2.48701214790344</t>
@@ -164,13 +164,13 @@
     <t xml:space="preserve">2.4909245967865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44527912139893</t>
+    <t xml:space="preserve">2.44527888298035</t>
   </si>
   <si>
     <t xml:space="preserve">2.46614575386047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43223786354065</t>
+    <t xml:space="preserve">2.43223762512207</t>
   </si>
   <si>
     <t xml:space="preserve">2.44006276130676</t>
@@ -179,61 +179,61 @@
     <t xml:space="preserve">2.47788310050964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43615031242371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43354201316833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4570164680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48831605911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41789174079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43484616279602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41267538070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35659742355347</t>
+    <t xml:space="preserve">2.43615055084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43354177474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45701670646667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48831629753113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41789197921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43484592437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41267561912537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35659718513489</t>
   </si>
   <si>
     <t xml:space="preserve">2.27573990821838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29530191421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.312255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38137602806091</t>
+    <t xml:space="preserve">2.29530239105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31225609779358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38137578964233</t>
   </si>
   <si>
     <t xml:space="preserve">2.40876293182373</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39311337471008</t>
+    <t xml:space="preserve">2.39311361312866</t>
   </si>
   <si>
     <t xml:space="preserve">2.44919180870056</t>
   </si>
   <si>
-    <t xml:space="preserve">2.467449426651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47397041320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48440384864807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4635374546051</t>
+    <t xml:space="preserve">2.46744966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47397065162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48440361022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46353721618652</t>
   </si>
   <si>
     <t xml:space="preserve">2.47266674041748</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">2.47136259078979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4478874206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49614095687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49744534492493</t>
+    <t xml:space="preserve">2.44788718223572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49614119529724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49744510650635</t>
   </si>
   <si>
     <t xml:space="preserve">2.51570320129395</t>
@@ -260,13 +260,13 @@
     <t xml:space="preserve">2.51439905166626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53657007217407</t>
+    <t xml:space="preserve">2.53656959533691</t>
   </si>
   <si>
     <t xml:space="preserve">2.52744054794312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54830694198608</t>
+    <t xml:space="preserve">2.54830718040466</t>
   </si>
   <si>
     <t xml:space="preserve">2.55091547966003</t>
@@ -275,28 +275,28 @@
     <t xml:space="preserve">2.5378737449646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58612728118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57699799537659</t>
+    <t xml:space="preserve">2.58612751960754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57699823379517</t>
   </si>
   <si>
     <t xml:space="preserve">2.59786462783813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57308602333069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66959309577942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68393898010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6982843875885</t>
+    <t xml:space="preserve">2.60438561439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57308578491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66959261894226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68393874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69828414916992</t>
   </si>
   <si>
     <t xml:space="preserve">2.64872622489929</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">2.64742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68132996559143</t>
+    <t xml:space="preserve">2.68133020401001</t>
   </si>
   <si>
     <t xml:space="preserve">2.67480969429016</t>
@@ -314,10 +314,10 @@
     <t xml:space="preserve">2.63438081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64350962638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69567561149597</t>
+    <t xml:space="preserve">2.64350986480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69567584991455</t>
   </si>
   <si>
     <t xml:space="preserve">2.69958829879761</t>
@@ -335,37 +335,37 @@
     <t xml:space="preserve">2.7543625831604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71262955665588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70089244842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70219659805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66176772117615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7830536365509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74523377418518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69306755065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71915054321289</t>
+    <t xml:space="preserve">2.71262979507446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70089268684387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70219683647156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66176748275757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78305411338806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7452335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6930673122406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71915078163147</t>
   </si>
   <si>
     <t xml:space="preserve">2.70610928535461</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74914622306824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77783727645874</t>
+    <t xml:space="preserve">2.74914598464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77783703804016</t>
   </si>
   <si>
     <t xml:space="preserve">2.8352198600769</t>
@@ -377,37 +377,37 @@
     <t xml:space="preserve">2.88738584518433</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89651489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85347747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91477274894714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00867128372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02040863037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96824288368225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0073676109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05822944641113</t>
+    <t xml:space="preserve">2.89651465415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8534779548645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91477251052856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00867176055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02040910720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96824264526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00736737251282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05822896957397</t>
   </si>
   <si>
     <t xml:space="preserve">3.09885382652283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15591287612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09613680839539</t>
+    <t xml:space="preserve">3.15591311454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09613728523254</t>
   </si>
   <si>
     <t xml:space="preserve">3.13825178146362</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">2.97658467292786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13417601585388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20074510574341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24965286254883</t>
+    <t xml:space="preserve">3.13417649269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20074486732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24965357780457</t>
   </si>
   <si>
     <t xml:space="preserve">3.28769302368164</t>
@@ -434,58 +434,58 @@
     <t xml:space="preserve">3.23063349723816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24557757377625</t>
+    <t xml:space="preserve">3.24557733535767</t>
   </si>
   <si>
     <t xml:space="preserve">3.22248220443726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25101161003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1871600151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09477877616882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11379814147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19938707351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10428833961487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12059044837952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15727162361145</t>
+    <t xml:space="preserve">3.25101184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18715977668762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09477806091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11379861831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19938683509827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10428810119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12059092521667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15727186203003</t>
   </si>
   <si>
     <t xml:space="preserve">3.16270589828491</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14504456520081</t>
+    <t xml:space="preserve">3.14504480361938</t>
   </si>
   <si>
     <t xml:space="preserve">3.03907775878906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02820920944214</t>
+    <t xml:space="preserve">3.02820944786072</t>
   </si>
   <si>
     <t xml:space="preserve">2.96707463264465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00375556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03636050224304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02005791664124</t>
+    <t xml:space="preserve">3.00375533103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03636026382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02005839347839</t>
   </si>
   <si>
     <t xml:space="preserve">2.97794318199158</t>
@@ -494,25 +494,25 @@
     <t xml:space="preserve">2.9860942363739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9956042766571</t>
+    <t xml:space="preserve">2.99560451507568</t>
   </si>
   <si>
     <t xml:space="preserve">3.07575869560242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0839102268219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12466669082642</t>
+    <t xml:space="preserve">3.08390974998474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12466621398926</t>
   </si>
   <si>
     <t xml:space="preserve">3.10836410522461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12874174118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17900848388672</t>
+    <t xml:space="preserve">3.12874245643616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17900824546814</t>
   </si>
   <si>
     <t xml:space="preserve">3.17221570014954</t>
@@ -524,28 +524,28 @@
     <t xml:space="preserve">3.15863037109375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2251992225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26052165031433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25237059593201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27682423591614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30671238899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30263662338257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2808997631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21025490760803</t>
+    <t xml:space="preserve">3.22519969940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26052188873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25237035751343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27682375907898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30671286582947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30263638496399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28090000152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21025514602661</t>
   </si>
   <si>
     <t xml:space="preserve">3.28361701965332</t>
@@ -560,52 +560,52 @@
     <t xml:space="preserve">3.26323866844177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25644588470459</t>
+    <t xml:space="preserve">3.25644564628601</t>
   </si>
   <si>
     <t xml:space="preserve">3.27003145217896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24693584442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23335075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21976518630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24150133132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26187992095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23470950126648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1980288028717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23742628097534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24829435348511</t>
+    <t xml:space="preserve">3.24693608283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23335099220276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21976494789124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24150156974792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26188039779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23470902442932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19802808761597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23742580413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24829483032227</t>
   </si>
   <si>
     <t xml:space="preserve">3.22791647911072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19395303726196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16542291641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18444299697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18172597885132</t>
+    <t xml:space="preserve">3.1939525604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16542267799377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18444275856018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18172574043274</t>
   </si>
   <si>
     <t xml:space="preserve">3.20753812789917</t>
@@ -614,22 +614,22 @@
     <t xml:space="preserve">3.24014329910278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26731419563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2428605556488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22655749320984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23199200630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20617961883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14640307426453</t>
+    <t xml:space="preserve">3.26731395721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24286079406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22655773162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23199248313904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20617914199829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14640355110168</t>
   </si>
   <si>
     <t xml:space="preserve">3.16813993453979</t>
@@ -638,16 +638,16 @@
     <t xml:space="preserve">3.10157108306885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16678142547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21704840660095</t>
+    <t xml:space="preserve">3.16678166389465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21704792976379</t>
   </si>
   <si>
     <t xml:space="preserve">3.22927498817444</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24421906471252</t>
+    <t xml:space="preserve">3.24421882629395</t>
   </si>
   <si>
     <t xml:space="preserve">3.21433067321777</t>
@@ -656,40 +656,40 @@
     <t xml:space="preserve">3.25372862815857</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35154438018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4914755821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39366006851196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46430420875549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50506091117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41675543785095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40656518936157</t>
+    <t xml:space="preserve">3.35154485702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49147534370422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3936595916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46430373191833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50506019592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41675496101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40656542778015</t>
   </si>
   <si>
     <t xml:space="preserve">3.44732189178467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43373656272888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42694425582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47109651565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46770048141479</t>
+    <t xml:space="preserve">3.43373680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42694401741028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47109723091125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46770071983337</t>
   </si>
   <si>
     <t xml:space="preserve">3.48128604888916</t>
@@ -698,100 +698,100 @@
     <t xml:space="preserve">3.50166440010071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54242062568665</t>
+    <t xml:space="preserve">3.54242086410522</t>
   </si>
   <si>
     <t xml:space="preserve">3.51185345649719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54581689834595</t>
+    <t xml:space="preserve">3.54581713676453</t>
   </si>
   <si>
     <t xml:space="preserve">3.55940270423889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63412308692932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60015964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53223156929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48468279838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55260968208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61374545097351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52543902397156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5899703502655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60355544090271</t>
+    <t xml:space="preserve">3.63412284851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60015916824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53223180770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48468232154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55261015892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61374497413635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52543878555298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58997011184692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60355591773987</t>
   </si>
   <si>
     <t xml:space="preserve">3.5933666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62053751945496</t>
+    <t xml:space="preserve">3.62053775787354</t>
   </si>
   <si>
     <t xml:space="preserve">3.59676289558411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56619548797607</t>
+    <t xml:space="preserve">3.56619572639465</t>
   </si>
   <si>
     <t xml:space="preserve">3.53562784194946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45411467552185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45751190185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39637684822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32301545143127</t>
+    <t xml:space="preserve">3.45411515235901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45751118659973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39637660980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32301473617554</t>
   </si>
   <si>
     <t xml:space="preserve">3.38279128074646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40996265411377</t>
+    <t xml:space="preserve">3.40996193885803</t>
   </si>
   <si>
     <t xml:space="preserve">3.38958358764648</t>
   </si>
   <si>
-    <t xml:space="preserve">3.328449010849</t>
+    <t xml:space="preserve">3.32844948768616</t>
   </si>
   <si>
     <t xml:space="preserve">3.30807089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31078839302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35018587112427</t>
+    <t xml:space="preserve">3.31078791618347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35018563270569</t>
   </si>
   <si>
     <t xml:space="preserve">3.3759982585907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35426163673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37328100204468</t>
+    <t xml:space="preserve">3.35426211357117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37328171730042</t>
   </si>
   <si>
     <t xml:space="preserve">3.34339308738708</t>
@@ -800,25 +800,25 @@
     <t xml:space="preserve">3.36648845672607</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37871551513672</t>
+    <t xml:space="preserve">3.37871527671814</t>
   </si>
   <si>
     <t xml:space="preserve">3.36105442047119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12127017974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16406440734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06624889373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04587054252625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03228545188904</t>
+    <t xml:space="preserve">3.12126994132996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16406416893005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06624841690063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04587078094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03228521347046</t>
   </si>
   <si>
     <t xml:space="preserve">3.00239706039429</t>
@@ -827,22 +827,22 @@
     <t xml:space="preserve">3.0220959186554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0254921913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04655003547668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9942455291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96164035797119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97862219810486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092646598816</t>
+    <t xml:space="preserve">3.02549242973328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04655027389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99424600601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96164059638977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97862243652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092622756958</t>
   </si>
   <si>
     <t xml:space="preserve">3.11651515960693</t>
@@ -863,28 +863,28 @@
     <t xml:space="preserve">2.92495965957642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01326560974121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09409928321838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14300656318665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23538827896118</t>
+    <t xml:space="preserve">3.01326489448547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0940990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14300680160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23538851737976</t>
   </si>
   <si>
     <t xml:space="preserve">3.22723722457886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21297264099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19327354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27342772483826</t>
+    <t xml:space="preserve">3.21297287940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19327330589294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27342796325684</t>
   </si>
   <si>
     <t xml:space="preserve">3.29448509216309</t>
@@ -896,22 +896,22 @@
     <t xml:space="preserve">3.30739164352417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28565502166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36377120018005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39909386634827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.479248046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47517275810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4819655418396</t>
+    <t xml:space="preserve">3.28565454483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36377191543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39909362792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47924900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47517228126526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48196530342102</t>
   </si>
   <si>
     <t xml:space="preserve">3.43713307380676</t>
@@ -920,76 +920,76 @@
     <t xml:space="preserve">3.44392609596252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49962687492371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.528156042099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4778892993927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51457047462463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45886969566345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52679753303528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5200047492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5757052898407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62733030319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64499139785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60423541069031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60287666320801</t>
+    <t xml:space="preserve">3.49962711334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52815580368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47788953781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51457071304321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45887041091919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52679777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52000427246094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57570552825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6273295879364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64499163627625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60423493385315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60287618637085</t>
   </si>
   <si>
     <t xml:space="preserve">3.62597131729126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49419188499451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45615291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41539597511292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45479369163513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44256687164307</t>
+    <t xml:space="preserve">3.49419236183167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45615267753601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41539621353149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45479440689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44256734848022</t>
   </si>
   <si>
     <t xml:space="preserve">3.36309242248535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39298057556152</t>
+    <t xml:space="preserve">3.39298033714294</t>
   </si>
   <si>
     <t xml:space="preserve">3.39461970329285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45400071144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46107006072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36280822753906</t>
+    <t xml:space="preserve">3.45400094985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4610698223114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36280846595764</t>
   </si>
   <si>
     <t xml:space="preserve">3.28151297569275</t>
@@ -998,31 +998,31 @@
     <t xml:space="preserve">3.23414897918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07367920875549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16699194908142</t>
+    <t xml:space="preserve">3.07367897033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1669921875</t>
   </si>
   <si>
     <t xml:space="preserve">3.1528537273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18961334228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2786853313446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25747728347778</t>
+    <t xml:space="preserve">3.18961358070374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27868509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25747752189636</t>
   </si>
   <si>
     <t xml:space="preserve">3.23556351661682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23768401145935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20163130760193</t>
+    <t xml:space="preserve">3.23768424987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20163106918335</t>
   </si>
   <si>
     <t xml:space="preserve">3.34089350700378</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">3.43774151802063</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39037799835205</t>
+    <t xml:space="preserve">3.39037823677063</t>
   </si>
   <si>
     <t xml:space="preserve">3.41087865829468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37623977661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38967108726501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40946555137634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46319079399109</t>
+    <t xml:space="preserve">3.37623953819275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38967132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40946483612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46319055557251</t>
   </si>
   <si>
     <t xml:space="preserve">3.33735942840576</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">3.29989242553711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34442853927612</t>
+    <t xml:space="preserve">3.34442830085754</t>
   </si>
   <si>
     <t xml:space="preserve">3.35432553291321</t>
@@ -1076,49 +1076,49 @@
     <t xml:space="preserve">3.35644602775574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35220456123352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40098190307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41865491867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37765336036682</t>
+    <t xml:space="preserve">3.3522047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40098142623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41865468025208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37765383720398</t>
   </si>
   <si>
     <t xml:space="preserve">3.32534193992615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35573935508728</t>
+    <t xml:space="preserve">3.35573959350586</t>
   </si>
   <si>
     <t xml:space="preserve">3.34230804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40027499198914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45258688926697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44834542274475</t>
+    <t xml:space="preserve">3.40027475357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45258665084839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44834518432617</t>
   </si>
   <si>
     <t xml:space="preserve">3.44269013404846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45117330551147</t>
+    <t xml:space="preserve">3.4511730670929</t>
   </si>
   <si>
     <t xml:space="preserve">3.41229271888733</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40734434127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46036291122437</t>
+    <t xml:space="preserve">3.40734386444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46036314964294</t>
   </si>
   <si>
     <t xml:space="preserve">3.4313793182373</t>
@@ -1127,28 +1127,28 @@
     <t xml:space="preserve">3.4787425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42077612876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42572450637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51479554176331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49429512023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3953263759613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41582727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4292585849762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40239572525024</t>
+    <t xml:space="preserve">3.42077589035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42572402954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51479601860046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49429488182068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39532661437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41582703590393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42925834655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40239596366882</t>
   </si>
   <si>
     <t xml:space="preserve">3.36139440536499</t>
@@ -1160,43 +1160,43 @@
     <t xml:space="preserve">3.43279361724854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33594560623169</t>
+    <t xml:space="preserve">3.33594536781311</t>
   </si>
   <si>
     <t xml:space="preserve">3.29706478118896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30413413047791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30837535858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2878749370575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31615161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25182247161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28999543190002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33311772346497</t>
+    <t xml:space="preserve">3.30413389205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30837559700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28787517547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3161518573761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25182199478149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2899956703186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33311796188354</t>
   </si>
   <si>
     <t xml:space="preserve">3.33099675178528</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33382511138916</t>
+    <t xml:space="preserve">3.33382487297058</t>
   </si>
   <si>
     <t xml:space="preserve">3.32675576210022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34654927253723</t>
+    <t xml:space="preserve">3.34654951095581</t>
   </si>
   <si>
     <t xml:space="preserve">3.47450160980225</t>
@@ -1205,28 +1205,28 @@
     <t xml:space="preserve">3.49924302101135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49641585350037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46248340606689</t>
+    <t xml:space="preserve">3.49641609191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46248388290405</t>
   </si>
   <si>
     <t xml:space="preserve">3.45682859420776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45470762252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38613629341125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4575355052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45894908905029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37411856651306</t>
+    <t xml:space="preserve">3.45470809936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38613677024841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45753526687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45894932746887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37411880493164</t>
   </si>
   <si>
     <t xml:space="preserve">3.39391279220581</t>
@@ -1235,34 +1235,34 @@
     <t xml:space="preserve">3.42006850242615</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30978989601135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32816958427429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35715293884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27797818183899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24899482727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21011424064636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23485660552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20516586303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15780186653137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.130939245224</t>
+    <t xml:space="preserve">3.30978941917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32816910743713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35715317726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27797842025757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24899458885193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2101137638092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23485636711121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20516562461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15780234336853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13093900680542</t>
   </si>
   <si>
     <t xml:space="preserve">3.15356087684631</t>
@@ -1274,73 +1274,73 @@
     <t xml:space="preserve">3.16911268234253</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19809651374817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18890643119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23909759521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23344230651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27727127075195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23202848434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22920060157776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22495937347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2723228931427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31473803520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3734118938446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42501711845398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43491411209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48863983154297</t>
+    <t xml:space="preserve">3.19809699058533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1889066696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23909735679626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23344206809998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27727150917053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23202872276306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22920083999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22495913505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27232336997986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31473827362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37341213226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4250168800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43491435050964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48864006996155</t>
   </si>
   <si>
     <t xml:space="preserve">3.4469313621521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38755011558533</t>
+    <t xml:space="preserve">3.38755035400391</t>
   </si>
   <si>
     <t xml:space="preserve">3.35927391052246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34160137176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30059957504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30484127998352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27585744857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39603352546692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34937644004822</t>
+    <t xml:space="preserve">3.34160089492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3005998134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30484056472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2758572101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39603328704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3493766784668</t>
   </si>
   <si>
     <t xml:space="preserve">3.36068749427795</t>
@@ -1349,40 +1349,40 @@
     <t xml:space="preserve">3.36704993247986</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39179158210754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41653418540955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.453293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52327942848206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59114265441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61235022544861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073039054871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61093616485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62790250778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60103940963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5996253490448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51055383682251</t>
+    <t xml:space="preserve">3.39179182052612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41653442382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45329403877258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5232789516449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5911431312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61235046386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073086738586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61093640327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6279022693634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60103988647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59962630271912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51055431365967</t>
   </si>
   <si>
     <t xml:space="preserve">3.53176164627075</t>
@@ -1391,46 +1391,46 @@
     <t xml:space="preserve">3.57841801643372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61941885948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64911031723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67880034446716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62083315849304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6858696937561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70849084854126</t>
+    <t xml:space="preserve">3.61941957473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6491105556488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6788010597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62083387374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68587040901184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70849132537842</t>
   </si>
   <si>
     <t xml:space="preserve">3.65335154533386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68304204940796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68728399276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67738699913025</t>
+    <t xml:space="preserve">3.68304228782654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68728351593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67738676071167</t>
   </si>
   <si>
     <t xml:space="preserve">3.71414661407471</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7113184928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70990467071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72545719146729</t>
+    <t xml:space="preserve">3.71131896972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70990538597107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72545695304871</t>
   </si>
   <si>
     <t xml:space="preserve">3.7325267791748</t>
@@ -1439,178 +1439,178 @@
     <t xml:space="preserve">3.731112241745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67173171043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69293904304504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71980214118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779950141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61517810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68869733810425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69576692581177</t>
+    <t xml:space="preserve">3.6717312335968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69293928146362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.719801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779902458191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61517858505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68869757652283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69576644897461</t>
   </si>
   <si>
     <t xml:space="preserve">3.69435262680054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69718050956726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68162846565247</t>
+    <t xml:space="preserve">3.69718074798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68162822723389</t>
   </si>
   <si>
     <t xml:space="preserve">3.75232005119324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74383687973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72262907028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76504445075989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75938892364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71697378158569</t>
+    <t xml:space="preserve">3.7438371181488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72262930870056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76504492759705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75938940048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71697425842285</t>
   </si>
   <si>
     <t xml:space="preserve">3.78342437744141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83997797966003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86542677879333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83573698997498</t>
+    <t xml:space="preserve">3.83997821807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86542701721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83573627471924</t>
   </si>
   <si>
     <t xml:space="preserve">3.82442545890808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79756307601929</t>
+    <t xml:space="preserve">3.79756283760071</t>
   </si>
   <si>
     <t xml:space="preserve">3.8173565864563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85977172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86966824531555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88380670547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87532377243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89370369911194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88804817199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85270261764526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8710823059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89087629318237</t>
+    <t xml:space="preserve">3.85977125167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86966800689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8838062286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87532448768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89370322227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88804864883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85270190238953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87108206748962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89087605476379</t>
   </si>
   <si>
     <t xml:space="preserve">3.84139204025269</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88239312171936</t>
+    <t xml:space="preserve">3.88239336013794</t>
   </si>
   <si>
     <t xml:space="preserve">3.92339444160461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88946175575256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90360069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92056632041931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91915249824524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96439552307129</t>
+    <t xml:space="preserve">3.88946223258972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90359997749329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92056655883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9191529750824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96439528465271</t>
   </si>
   <si>
     <t xml:space="preserve">3.95732641220093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91067028045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93329095840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90642833709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90501475334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9219799041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91208338737488</t>
+    <t xml:space="preserve">3.91066932678223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93329071998596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90642881393433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90501427650452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92198014259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91208362579346</t>
   </si>
   <si>
     <t xml:space="preserve">3.9304633140564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87956571578979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89794516563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88097882270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94742941856384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89228987693787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87391018867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90925621986389</t>
+    <t xml:space="preserve">3.87956500053406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89794540405273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88097929954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.947429895401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89229011535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87390995025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90925574302673</t>
   </si>
   <si>
     <t xml:space="preserve">3.95025706291199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98136162757874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0096378326416</t>
+    <t xml:space="preserve">3.98136138916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00963830947876</t>
   </si>
   <si>
     <t xml:space="preserve">4.08032989501953</t>
@@ -1625,19 +1625,19 @@
     <t xml:space="preserve">4.16984796524048</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21100282669067</t>
+    <t xml:space="preserve">4.21100330352783</t>
   </si>
   <si>
     <t xml:space="preserve">4.213942527771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24921846389771</t>
+    <t xml:space="preserve">4.24921798706055</t>
   </si>
   <si>
     <t xml:space="preserve">4.20512390136719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19483470916748</t>
+    <t xml:space="preserve">4.1948356628418</t>
   </si>
   <si>
     <t xml:space="preserve">4.12281465530396</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">4.21541213989258</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26979541778564</t>
+    <t xml:space="preserve">4.26979494094849</t>
   </si>
   <si>
     <t xml:space="preserve">4.30507040023804</t>
@@ -1673,13 +1673,13 @@
     <t xml:space="preserve">4.28890228271484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35651445388794</t>
+    <t xml:space="preserve">4.35651397705078</t>
   </si>
   <si>
     <t xml:space="preserve">4.34328556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49908494949341</t>
+    <t xml:space="preserve">4.49908590316772</t>
   </si>
   <si>
     <t xml:space="preserve">4.44764184951782</t>
@@ -1691,19 +1691,19 @@
     <t xml:space="preserve">4.48291778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48732709884644</t>
+    <t xml:space="preserve">4.48732662200928</t>
   </si>
   <si>
     <t xml:space="preserve">4.45352172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43735313415527</t>
+    <t xml:space="preserve">4.43735361099243</t>
   </si>
   <si>
     <t xml:space="preserve">4.35210466384888</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34181594848633</t>
+    <t xml:space="preserve">4.34181547164917</t>
   </si>
   <si>
     <t xml:space="preserve">4.3344669342041</t>
@@ -1712,34 +1712,34 @@
     <t xml:space="preserve">4.43147420883179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47997760772705</t>
+    <t xml:space="preserve">4.47997808456421</t>
   </si>
   <si>
     <t xml:space="preserve">4.44911193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43882274627686</t>
+    <t xml:space="preserve">4.43882322311401</t>
   </si>
   <si>
     <t xml:space="preserve">4.49467611312866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51966285705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50349473953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54317951202393</t>
+    <t xml:space="preserve">4.51966238021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50349521636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54317998886108</t>
   </si>
   <si>
     <t xml:space="preserve">4.56228733062744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57698583602905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52701187133789</t>
+    <t xml:space="preserve">4.57698535919189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52701139450073</t>
   </si>
   <si>
     <t xml:space="preserve">4.54170942306519</t>
@@ -1748,7 +1748,7 @@
     <t xml:space="preserve">4.54905891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40207815170288</t>
+    <t xml:space="preserve">4.40207767486572</t>
   </si>
   <si>
     <t xml:space="preserve">4.43588352203369</t>
@@ -1766,13 +1766,13 @@
     <t xml:space="preserve">4.24480867385864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20218372344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29037189483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29331207275391</t>
+    <t xml:space="preserve">4.20218420028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29037237167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29331254959106</t>
   </si>
   <si>
     <t xml:space="preserve">4.27420473098755</t>
@@ -1781,19 +1781,19 @@
     <t xml:space="preserve">4.26097631454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28449296951294</t>
+    <t xml:space="preserve">4.2844934463501</t>
   </si>
   <si>
     <t xml:space="preserve">4.28743314743042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11399555206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16102933883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24186897277832</t>
+    <t xml:space="preserve">4.11399602890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16102981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24186849594116</t>
   </si>
   <si>
     <t xml:space="preserve">4.15662002563477</t>
@@ -1802,49 +1802,49 @@
     <t xml:space="preserve">4.30360078811646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21835279464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20071411132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1977744102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34034633636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33593702316284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34916543960571</t>
+    <t xml:space="preserve">4.2183518409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20071363449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19777393341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34034585952759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33593654632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34916496276855</t>
   </si>
   <si>
     <t xml:space="preserve">4.31388902664185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30213069915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20806264877319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14192247390747</t>
+    <t xml:space="preserve">4.30213117599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20806312561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14192199707031</t>
   </si>
   <si>
     <t xml:space="preserve">4.10370683670044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18307685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14045190811157</t>
+    <t xml:space="preserve">4.18307638168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14045143127441</t>
   </si>
   <si>
     <t xml:space="preserve">4.12575387954712</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19336462020874</t>
+    <t xml:space="preserve">4.1933650970459</t>
   </si>
   <si>
     <t xml:space="preserve">4.18160676956177</t>
@@ -1853,46 +1853,46 @@
     <t xml:space="preserve">4.18454647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25215721130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29919147491455</t>
+    <t xml:space="preserve">4.25215768814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29919099807739</t>
   </si>
   <si>
     <t xml:space="preserve">4.39031934738159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32711696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30066156387329</t>
+    <t xml:space="preserve">4.32711791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30066108703613</t>
   </si>
   <si>
     <t xml:space="preserve">4.21247243881226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31241941452026</t>
+    <t xml:space="preserve">4.31241989135742</t>
   </si>
   <si>
     <t xml:space="preserve">4.36974287033081</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24774885177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18895530700684</t>
+    <t xml:space="preserve">4.24774837493896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18895578384399</t>
   </si>
   <si>
     <t xml:space="preserve">4.23011064529419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18748569488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17425727844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1727876663208</t>
+    <t xml:space="preserve">4.18748617172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17425775527954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17278814315796</t>
   </si>
   <si>
     <t xml:space="preserve">4.14486122131348</t>
@@ -1901,19 +1901,19 @@
     <t xml:space="preserve">4.1683783531189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18013763427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.238929271698</t>
+    <t xml:space="preserve">4.18013715744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23892879486084</t>
   </si>
   <si>
     <t xml:space="preserve">4.25362730026245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29478216171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33740711212158</t>
+    <t xml:space="preserve">4.29478168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33740663528442</t>
   </si>
   <si>
     <t xml:space="preserve">4.35063505172729</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">4.28302335739136</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33299779891968</t>
+    <t xml:space="preserve">4.33299684524536</t>
   </si>
   <si>
     <t xml:space="preserve">4.30654096603394</t>
@@ -1931,19 +1931,19 @@
     <t xml:space="preserve">4.37268209457397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39178895950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27861404418945</t>
+    <t xml:space="preserve">4.39178943634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27861452102661</t>
   </si>
   <si>
     <t xml:space="preserve">4.22423124313354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23745965957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22570037841797</t>
+    <t xml:space="preserve">4.23745918273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22570085525513</t>
   </si>
   <si>
     <t xml:space="preserve">4.19189548492432</t>
@@ -1955,34 +1955,34 @@
     <t xml:space="preserve">4.23599004745483</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22717046737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00963878631592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07431030273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08900833129883</t>
+    <t xml:space="preserve">4.22717094421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00963926315308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07431077957153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08900928497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.04932403564453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01992750167847</t>
+    <t xml:space="preserve">4.01992702484131</t>
   </si>
   <si>
     <t xml:space="preserve">3.95378637313843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99494123458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04197454452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9905309677124</t>
+    <t xml:space="preserve">3.99494051933289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0419750213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99053120613098</t>
   </si>
   <si>
     <t xml:space="preserve">4.03609561920166</t>
@@ -1991,16 +1991,16 @@
     <t xml:space="preserve">4.10664653778076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16396856307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1272234916687</t>
+    <t xml:space="preserve">4.16396903991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12722396850586</t>
   </si>
   <si>
     <t xml:space="preserve">4.13751220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00082015991211</t>
+    <t xml:space="preserve">4.00081968307495</t>
   </si>
   <si>
     <t xml:space="preserve">4.09194803237915</t>
@@ -2009,67 +2009,67 @@
     <t xml:space="preserve">4.08459949493408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02727699279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02286720275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10076665878296</t>
+    <t xml:space="preserve">4.02727651596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02286672592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10076713562012</t>
   </si>
   <si>
     <t xml:space="preserve">4.20365381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13898181915283</t>
+    <t xml:space="preserve">4.13898277282715</t>
   </si>
   <si>
     <t xml:space="preserve">4.25068759918213</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20659303665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.263916015625</t>
+    <t xml:space="preserve">4.20659351348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26391553878784</t>
   </si>
   <si>
     <t xml:space="preserve">4.30801010131836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48144721984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5152530670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49761533737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40648746490479</t>
+    <t xml:space="preserve">4.48144769668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51525354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49761581420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40648698806763</t>
   </si>
   <si>
     <t xml:space="preserve">4.41677618026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46674966812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4917368888855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46087074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46234035491943</t>
+    <t xml:space="preserve">4.46674919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49173641204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46087121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46233987808228</t>
   </si>
   <si>
     <t xml:space="preserve">4.51231336593628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45205211639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48585748672485</t>
+    <t xml:space="preserve">4.45205163955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4858570098877</t>
   </si>
   <si>
     <t xml:space="preserve">4.62548923492432</t>
@@ -2078,19 +2078,19 @@
     <t xml:space="preserve">4.26538562774658</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26244640350342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06549263000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08606863021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72890567779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51798844337463</t>
+    <t xml:space="preserve">4.26244592666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06549167633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08606910705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72890543937683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51798796653748</t>
   </si>
   <si>
     <t xml:space="preserve">3.50181984901428</t>
@@ -2102,88 +2102,88 @@
     <t xml:space="preserve">3.24754309654236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15127086639404</t>
+    <t xml:space="preserve">3.15127062797546</t>
   </si>
   <si>
     <t xml:space="preserve">3.27032494544983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29531192779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35189962387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21153283119202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12995839118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35557389259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38937973976135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34381556510925</t>
+    <t xml:space="preserve">3.29531216621399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35189938545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21153259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.129958152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35557413101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38937950134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34381604194641</t>
   </si>
   <si>
     <t xml:space="preserve">3.35924863815308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5709011554718</t>
+    <t xml:space="preserve">3.57090163230896</t>
   </si>
   <si>
     <t xml:space="preserve">3.66643857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44964194297791</t>
+    <t xml:space="preserve">3.44964146614075</t>
   </si>
   <si>
     <t xml:space="preserve">3.55693817138672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58780407905579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53636050224304</t>
+    <t xml:space="preserve">3.58780384063721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53636074066162</t>
   </si>
   <si>
     <t xml:space="preserve">3.54958891868591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4658100605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54811930656433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56428670883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368348121643</t>
+    <t xml:space="preserve">3.46580958366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54811906814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56428647041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368324279785</t>
   </si>
   <si>
     <t xml:space="preserve">3.6260187625885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57163596153259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57310581207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44082355499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61719989776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52754163742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57457542419434</t>
+    <t xml:space="preserve">3.57163619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57310557365417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44082283973694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61719965934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52754187583923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57457566261292</t>
   </si>
   <si>
     <t xml:space="preserve">3.56722664833069</t>
@@ -2192,64 +2192,64 @@
     <t xml:space="preserve">3.57898497581482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75168752670288</t>
+    <t xml:space="preserve">3.75168776512146</t>
   </si>
   <si>
     <t xml:space="preserve">3.68187212944031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70391821861267</t>
+    <t xml:space="preserve">3.70391917228699</t>
   </si>
   <si>
     <t xml:space="preserve">3.60691142082214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61279082298279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66423463821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63189816474915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62454915046692</t>
+    <t xml:space="preserve">3.61279034614563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66423368453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63189840316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62454891204834</t>
   </si>
   <si>
     <t xml:space="preserve">3.63777709007263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6230788230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71126770973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73626255989075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60662794113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66372871398926</t>
+    <t xml:space="preserve">3.62307929992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71126842498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73626303672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60662746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66372919082642</t>
   </si>
   <si>
     <t xml:space="preserve">3.63440680503845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6853346824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75015211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73008990287781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70231032371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80725288391113</t>
+    <t xml:space="preserve">3.68533444404602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75015234947205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73008966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70231056213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80725312232971</t>
   </si>
   <si>
     <t xml:space="preserve">3.77021455764771</t>
@@ -2258,10 +2258,10 @@
     <t xml:space="preserve">3.81959915161133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90447902679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99707531929016</t>
+    <t xml:space="preserve">3.90447926521301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99707555770874</t>
   </si>
   <si>
     <t xml:space="preserve">4.05109024047852</t>
@@ -2270,22 +2270,22 @@
     <t xml:space="preserve">4.02408266067505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92762851715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88133096694946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81651258468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91991186141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08581352233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05880641937256</t>
+    <t xml:space="preserve">3.9276282787323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88133025169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81651306152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91991257667542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08581399917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05880689620972</t>
   </si>
   <si>
     <t xml:space="preserve">4.10896301269531</t>
@@ -2297,43 +2297,43 @@
     <t xml:space="preserve">4.02022504806519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96621036529541</t>
+    <t xml:space="preserve">3.96620988845825</t>
   </si>
   <si>
     <t xml:space="preserve">3.9893593788147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03565692901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08967208862305</t>
+    <t xml:space="preserve">4.03565788269043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08967161178589</t>
   </si>
   <si>
     <t xml:space="preserve">4.03179883956909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07038116455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11282062530518</t>
+    <t xml:space="preserve">4.07038164138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11282110214233</t>
   </si>
   <si>
     <t xml:space="preserve">4.05494832992554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95463562011719</t>
+    <t xml:space="preserve">3.95463585853577</t>
   </si>
   <si>
     <t xml:space="preserve">3.96235251426697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9353449344635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97006845474243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97392678260803</t>
+    <t xml:space="preserve">3.93534445762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97006821632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97392654418945</t>
   </si>
   <si>
     <t xml:space="preserve">4.0742392539978</t>
@@ -2342,85 +2342,85 @@
     <t xml:space="preserve">4.1243953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10510540008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09353017807007</t>
+    <t xml:space="preserve">4.10510444641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09353065490723</t>
   </si>
   <si>
     <t xml:space="preserve">4.04723215103149</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12825393676758</t>
+    <t xml:space="preserve">4.12825345993042</t>
   </si>
   <si>
     <t xml:space="preserve">4.25943183898926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26714897155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21313428878784</t>
+    <t xml:space="preserve">4.26714849472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21313333511353</t>
   </si>
   <si>
     <t xml:space="preserve">4.19770097732544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16297721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16683530807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470808029175</t>
+    <t xml:space="preserve">4.16297674179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16683626174927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470855712891</t>
   </si>
   <si>
     <t xml:space="preserve">4.28643894195557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36746072769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42147541046143</t>
+    <t xml:space="preserve">4.36746025085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42147588729858</t>
   </si>
   <si>
     <t xml:space="preserve">4.39060974121094</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37517786026001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36360263824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30572986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26328992843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24399948120117</t>
+    <t xml:space="preserve">4.37517738342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36360359191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30573034286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26329040527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24399900436401</t>
   </si>
   <si>
     <t xml:space="preserve">4.31344652175903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30187177658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13597011566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22856664657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18612670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17455148696899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18998432159424</t>
+    <t xml:space="preserve">4.30187129974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13597059249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22856616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18612623214722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17455196380615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1899847984314</t>
   </si>
   <si>
     <t xml:space="preserve">4.11667919158936</t>
@@ -2429,43 +2429,43 @@
     <t xml:space="preserve">4.17841005325317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15526151657104</t>
+    <t xml:space="preserve">4.15526103973389</t>
   </si>
   <si>
     <t xml:space="preserve">4.15140295028687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15911912918091</t>
+    <t xml:space="preserve">4.15911960601807</t>
   </si>
   <si>
     <t xml:space="preserve">4.19384288787842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07809782028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89290475845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97778463363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06266403198242</t>
+    <t xml:space="preserve">4.07809734344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89290428161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97778534889221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06266450881958</t>
   </si>
   <si>
     <t xml:space="preserve">3.94691872596741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9855010509491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98164319992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88904595375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71157026290894</t>
+    <t xml:space="preserve">3.98550152778625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98164224624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88904690742493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71157002449036</t>
   </si>
   <si>
     <t xml:space="preserve">3.7270028591156</t>
@@ -2474,19 +2474,19 @@
     <t xml:space="preserve">3.8288586139679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83194541931152</t>
+    <t xml:space="preserve">3.8319456577301</t>
   </si>
   <si>
     <t xml:space="preserve">3.86589789390564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00479173660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95077681541443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.081955909729</t>
+    <t xml:space="preserve">4.00479221343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95077705383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08195543289185</t>
   </si>
   <si>
     <t xml:space="preserve">4.03951549530029</t>
@@ -2495,43 +2495,43 @@
     <t xml:space="preserve">4.13982772827148</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17069339752197</t>
+    <t xml:space="preserve">4.17069387435913</t>
   </si>
   <si>
     <t xml:space="preserve">4.14368629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13211250305176</t>
+    <t xml:space="preserve">4.13211154937744</t>
   </si>
   <si>
     <t xml:space="preserve">3.93920302391052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90062117576599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80879616737366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99321794509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01250791549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95849394798279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8774721622467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93148612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92376971244812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8620388507843</t>
+    <t xml:space="preserve">3.90062093734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80879592895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9932177066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01250839233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95849323272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87747240066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9314866065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9237699508667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86203932762146</t>
   </si>
   <si>
     <t xml:space="preserve">3.8180558681488</t>
@@ -2540,37 +2540,37 @@
     <t xml:space="preserve">3.80570983886719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85818147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89676284790039</t>
+    <t xml:space="preserve">3.85818099975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89676356315613</t>
   </si>
   <si>
     <t xml:space="preserve">3.85663795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82114267349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83811831474304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94306087493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90833806991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88518834114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83503198623657</t>
+    <t xml:space="preserve">3.82114291191101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83811807632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94306135177612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90833759307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88518810272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83503150939941</t>
   </si>
   <si>
     <t xml:space="preserve">3.76712822914124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7624979019165</t>
+    <t xml:space="preserve">3.76249814033508</t>
   </si>
   <si>
     <t xml:space="preserve">3.82268571853638</t>
@@ -2579,16 +2579,16 @@
     <t xml:space="preserve">3.79799318313599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87361407279968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02794075012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04337358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2092752456665</t>
+    <t xml:space="preserve">3.87361359596252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02794122695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04337406158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20927572250366</t>
   </si>
   <si>
     <t xml:space="preserve">4.25171566009521</t>
@@ -2600,10 +2600,10 @@
     <t xml:space="preserve">4.31730461120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27100610733032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26251888275146</t>
+    <t xml:space="preserve">4.27100658416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26251840591431</t>
   </si>
   <si>
     <t xml:space="preserve">4.2872109413147</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">4.25634527206421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24554204940796</t>
+    <t xml:space="preserve">4.24554300308228</t>
   </si>
   <si>
     <t xml:space="preserve">4.14985942840576</t>
@@ -2627,10 +2627,10 @@
     <t xml:space="preserve">4.12362384796143</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16837930679321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1714653968811</t>
+    <t xml:space="preserve">4.16837882995605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17146492004395</t>
   </si>
   <si>
     <t xml:space="preserve">4.19924449920654</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">4.23628234863281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18844127655029</t>
+    <t xml:space="preserve">4.18844175338745</t>
   </si>
   <si>
     <t xml:space="preserve">4.1776385307312</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">4.17918157577515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18381071090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2038745880127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18535423278809</t>
+    <t xml:space="preserve">4.18381118774414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20387411117554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18535470962524</t>
   </si>
   <si>
     <t xml:space="preserve">4.21622037887573</t>
@@ -2669,10 +2669,10 @@
     <t xml:space="preserve">4.25017213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23782587051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35048484802246</t>
+    <t xml:space="preserve">4.23782634735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35048532485962</t>
   </si>
   <si>
     <t xml:space="preserve">4.34122562408447</t>
@@ -2684,13 +2684,13 @@
     <t xml:space="preserve">4.47086000442505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46610307693481</t>
+    <t xml:space="preserve">4.46610355377197</t>
   </si>
   <si>
     <t xml:space="preserve">4.44025039672852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3885440826416</t>
+    <t xml:space="preserve">4.38854455947876</t>
   </si>
   <si>
     <t xml:space="preserve">4.35622835159302</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">4.38531255722046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37400197982788</t>
+    <t xml:space="preserve">4.37400245666504</t>
   </si>
   <si>
     <t xml:space="preserve">4.39016008377075</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">4.47418212890625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49357128143311</t>
+    <t xml:space="preserve">4.49357175827026</t>
   </si>
   <si>
     <t xml:space="preserve">4.5016508102417</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">4.52911996841431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55174160003662</t>
+    <t xml:space="preserve">4.55174112319946</t>
   </si>
   <si>
     <t xml:space="preserve">4.55012512207031</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">4.45640802383423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49680376052856</t>
+    <t xml:space="preserve">4.49680328369141</t>
   </si>
   <si>
     <t xml:space="preserve">4.48226118087769</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">4.48710870742798</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45317697525024</t>
+    <t xml:space="preserve">4.4531774520874</t>
   </si>
   <si>
     <t xml:space="preserve">4.46771955490112</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">4.4984188079834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50649833679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55335760116577</t>
+    <t xml:space="preserve">4.50649881362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55335712432861</t>
   </si>
   <si>
     <t xml:space="preserve">4.47902965545654</t>
@@ -2789,19 +2789,19 @@
     <t xml:space="preserve">4.50811433792114</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37884950637817</t>
+    <t xml:space="preserve">4.37884902954102</t>
   </si>
   <si>
     <t xml:space="preserve">4.35461235046387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37238597869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5371994972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56789922714233</t>
+    <t xml:space="preserve">4.37238645553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53719902038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56789875030518</t>
   </si>
   <si>
     <t xml:space="preserve">4.61152648925781</t>
@@ -2819,19 +2819,19 @@
     <t xml:space="preserve">4.59375238418579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60829496383667</t>
+    <t xml:space="preserve">4.60829448699951</t>
   </si>
   <si>
     <t xml:space="preserve">4.63091611862183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65676927566528</t>
+    <t xml:space="preserve">4.65676879882812</t>
   </si>
   <si>
     <t xml:space="preserve">4.66484880447388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69070100784302</t>
+    <t xml:space="preserve">4.69070148468018</t>
   </si>
   <si>
     <t xml:space="preserve">4.73271179199219</t>
@@ -2840,7 +2840,7 @@
     <t xml:space="preserve">4.76502799987793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80219173431396</t>
+    <t xml:space="preserve">4.80219221115112</t>
   </si>
   <si>
     <t xml:space="preserve">4.79896068572998</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">4.84420299530029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80703926086426</t>
+    <t xml:space="preserve">4.8070387840271</t>
   </si>
   <si>
     <t xml:space="preserve">4.69554805755615</t>
@@ -2873,13 +2873,13 @@
     <t xml:space="preserve">4.59213638305664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54366254806519</t>
+    <t xml:space="preserve">4.54366207122803</t>
   </si>
   <si>
     <t xml:space="preserve">4.49034070968628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49195575714111</t>
+    <t xml:space="preserve">4.49195623397827</t>
   </si>
   <si>
     <t xml:space="preserve">4.48549270629883</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">4.51134586334229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52427291870117</t>
+    <t xml:space="preserve">4.52427196502686</t>
   </si>
   <si>
     <t xml:space="preserve">4.46125555038452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58567333221436</t>
+    <t xml:space="preserve">4.58567380905151</t>
   </si>
   <si>
     <t xml:space="preserve">4.63576364517212</t>
@@ -2909,19 +2909,19 @@
     <t xml:space="preserve">4.65353727340698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57113122940063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4757981300354</t>
+    <t xml:space="preserve">4.57113075256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47579860687256</t>
   </si>
   <si>
     <t xml:space="preserve">4.42247629165649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46933507919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43217134475708</t>
+    <t xml:space="preserve">4.46933460235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43217086791992</t>
   </si>
   <si>
     <t xml:space="preserve">4.47095060348511</t>
@@ -2930,37 +2930,37 @@
     <t xml:space="preserve">4.48387718200684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39985513687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37076997756958</t>
+    <t xml:space="preserve">4.39985466003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37077045440674</t>
   </si>
   <si>
     <t xml:space="preserve">4.3966236114502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41116619110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51457786560059</t>
+    <t xml:space="preserve">4.41116571426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51457738876343</t>
   </si>
   <si>
     <t xml:space="preserve">4.46287202835083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43540239334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50003528594971</t>
+    <t xml:space="preserve">4.43540287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50003576278687</t>
   </si>
   <si>
     <t xml:space="preserve">4.53881502151489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6131420135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63253164291382</t>
+    <t xml:space="preserve">4.61314249038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63253211975098</t>
   </si>
   <si>
     <t xml:space="preserve">4.60021543502808</t>
@@ -2975,43 +2975,43 @@
     <t xml:space="preserve">4.52588844299316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48064565658569</t>
+    <t xml:space="preserve">4.48064613342285</t>
   </si>
   <si>
     <t xml:space="preserve">4.53235197067261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44832992553711</t>
+    <t xml:space="preserve">4.44832944869995</t>
   </si>
   <si>
     <t xml:space="preserve">4.5048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71978569030762</t>
+    <t xml:space="preserve">4.71978616714478</t>
   </si>
   <si>
     <t xml:space="preserve">4.72301721572876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65838527679443</t>
+    <t xml:space="preserve">4.65838479995728</t>
   </si>
   <si>
     <t xml:space="preserve">4.68262195587158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65515375137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64384269714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70201206207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68585395812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70362758636475</t>
+    <t xml:space="preserve">4.65515327453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6438422203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7020115852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68585348129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7036280632019</t>
   </si>
   <si>
     <t xml:space="preserve">4.66807985305786</t>
@@ -3026,10 +3026,10 @@
     <t xml:space="preserve">4.76179695129395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75048589706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84905004501343</t>
+    <t xml:space="preserve">4.75048637390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84905052185059</t>
   </si>
   <si>
     <t xml:space="preserve">4.87490367889404</t>
@@ -3047,43 +3047,43 @@
     <t xml:space="preserve">4.83127641677856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66161632537842</t>
+    <t xml:space="preserve">4.66161584854126</t>
   </si>
   <si>
     <t xml:space="preserve">4.64061117172241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72948026657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74402284622192</t>
+    <t xml:space="preserve">4.7294807434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74402332305908</t>
   </si>
   <si>
     <t xml:space="preserve">4.76018095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74079132080078</t>
+    <t xml:space="preserve">4.74079084396362</t>
   </si>
   <si>
     <t xml:space="preserve">4.79734516143799</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71655368804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79572916030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83450841903687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74563837051392</t>
+    <t xml:space="preserve">4.71655416488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79572868347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83450794219971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74563884735107</t>
   </si>
   <si>
     <t xml:space="preserve">4.50972986221313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46448707580566</t>
+    <t xml:space="preserve">4.46448755264282</t>
   </si>
   <si>
     <t xml:space="preserve">4.57759380340576</t>
@@ -3098,10 +3098,10 @@
     <t xml:space="preserve">4.54850959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50326633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41278171539307</t>
+    <t xml:space="preserve">4.50326681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41278123855591</t>
   </si>
   <si>
     <t xml:space="preserve">4.35299587249756</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">4.51780939102173</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49518775939941</t>
+    <t xml:space="preserve">4.49518823623657</t>
   </si>
   <si>
     <t xml:space="preserve">4.4176287651062</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">4.48872470855713</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43378734588623</t>
+    <t xml:space="preserve">4.43378686904907</t>
   </si>
   <si>
     <t xml:space="preserve">4.7052435874939</t>
@@ -3161,16 +3161,16 @@
     <t xml:space="preserve">5.15039920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08980703353882</t>
+    <t xml:space="preserve">5.08980655670166</t>
   </si>
   <si>
     <t xml:space="preserve">5.0655689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98073863983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96054124832153</t>
+    <t xml:space="preserve">4.9807391166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96054172515869</t>
   </si>
   <si>
     <t xml:space="preserve">4.99285745620728</t>
@@ -3179,25 +3179,25 @@
     <t xml:space="preserve">5.01709508895874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00093698501587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0130558013916</t>
+    <t xml:space="preserve">5.00093746185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01305532455444</t>
   </si>
   <si>
     <t xml:space="preserve">4.97266054153442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8999490737915</t>
+    <t xml:space="preserve">4.89994859695435</t>
   </si>
   <si>
     <t xml:space="preserve">4.94842290878296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92014646530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10596466064453</t>
+    <t xml:space="preserve">4.92014598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10596513748169</t>
   </si>
   <si>
     <t xml:space="preserve">5.05345106124878</t>
@@ -4953,6 +4953,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.35000038146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4350004196167</t>
   </si>
 </sst>
 </file>
@@ -64935,7 +64938,7 @@
     </row>
     <row r="2295">
       <c r="A2295" s="1" t="n">
-        <v>45975.6911342593</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2295" t="n">
         <v>2941597</v>
@@ -64956,6 +64959,32 @@
         <v>1646</v>
       </c>
       <c r="H2295" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" s="1" t="n">
+        <v>45978.6910763889</v>
+      </c>
+      <c r="B2296" t="n">
+        <v>2255148</v>
+      </c>
+      <c r="C2296" t="n">
+        <v>9.44499969482422</v>
+      </c>
+      <c r="D2296" t="n">
+        <v>9.35000038146973</v>
+      </c>
+      <c r="E2296" t="n">
+        <v>9.38000011444092</v>
+      </c>
+      <c r="F2296" t="n">
+        <v>9.4350004196167</v>
+      </c>
+      <c r="G2296" t="s">
+        <v>1647</v>
+      </c>
+      <c r="H2296" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="1648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="1647">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -53,7 +53,7 @@
     <t xml:space="preserve">2.16488718986511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1727123260498</t>
+    <t xml:space="preserve">2.17271208763123</t>
   </si>
   <si>
     <t xml:space="preserve">2.09315896034241</t>
@@ -62,31 +62,31 @@
     <t xml:space="preserve">2.06185913085938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08663821220398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04490518569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06055545806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04360151290894</t>
+    <t xml:space="preserve">2.08663845062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04490566253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06055521965027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04360127449036</t>
   </si>
   <si>
     <t xml:space="preserve">2.10489630699158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1296751499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14532518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17923331260681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20009899139404</t>
+    <t xml:space="preserve">2.12967538833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14532494544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17923283576965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20009922981262</t>
   </si>
   <si>
     <t xml:space="preserve">2.20140314102173</t>
@@ -95,67 +95,67 @@
     <t xml:space="preserve">2.17792868614197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13228321075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09837532043457</t>
+    <t xml:space="preserve">2.13228368759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09837579727173</t>
   </si>
   <si>
     <t xml:space="preserve">2.22357392311096</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29138970375061</t>
+    <t xml:space="preserve">2.29138994216919</t>
   </si>
   <si>
     <t xml:space="preserve">2.33181834220886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29791045188904</t>
+    <t xml:space="preserve">2.29791069030762</t>
   </si>
   <si>
     <t xml:space="preserve">2.2379195690155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30051851272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30443096160889</t>
+    <t xml:space="preserve">2.30051875114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30443120002747</t>
   </si>
   <si>
     <t xml:space="preserve">2.37094283103943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3461639881134</t>
+    <t xml:space="preserve">2.34616422653198</t>
   </si>
   <si>
     <t xml:space="preserve">2.39572167396545</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45571255683899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39702558517456</t>
+    <t xml:space="preserve">2.45571231842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39702582359314</t>
   </si>
   <si>
     <t xml:space="preserve">2.38007187843323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39441752433777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42180466651917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41006708145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43093323707581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43745422363281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701214790344</t>
+    <t xml:space="preserve">2.39441728591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42180418968201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41006731987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43093347549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43745446205139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701190948486</t>
   </si>
   <si>
     <t xml:space="preserve">2.45049571990967</t>
@@ -164,25 +164,25 @@
     <t xml:space="preserve">2.4909245967865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44527888298035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46614575386047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43223762512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44006276130676</t>
+    <t xml:space="preserve">2.4452793598175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46614551544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43223786354065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44006299972534</t>
   </si>
   <si>
     <t xml:space="preserve">2.47788310050964</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43615055084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43354177474976</t>
+    <t xml:space="preserve">2.43615007400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43354201316833</t>
   </si>
   <si>
     <t xml:space="preserve">2.45701670646667</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">2.48831629753113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41789197921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43484592437744</t>
+    <t xml:space="preserve">2.41789221763611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43484616279602</t>
   </si>
   <si>
     <t xml:space="preserve">2.41267561912537</t>
@@ -206,28 +206,28 @@
     <t xml:space="preserve">2.27573990821838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29530239105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31225609779358</t>
+    <t xml:space="preserve">2.29530191421509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.312255859375</t>
   </si>
   <si>
     <t xml:space="preserve">2.38137578964233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40876293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39311361312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44919180870056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46744966506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47397065162659</t>
+    <t xml:space="preserve">2.40876317024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39311337471008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44919157028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46744990348816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47397017478943</t>
   </si>
   <si>
     <t xml:space="preserve">2.48440361022949</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">2.46353721618652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47266674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47136259078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44788718223572</t>
+    <t xml:space="preserve">2.47266626358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47136211395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44788765907288</t>
   </si>
   <si>
     <t xml:space="preserve">2.49614119529724</t>
@@ -254,28 +254,28 @@
     <t xml:space="preserve">2.51570320129395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53135323524475</t>
+    <t xml:space="preserve">2.53135299682617</t>
   </si>
   <si>
     <t xml:space="preserve">2.51439905166626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53656959533691</t>
+    <t xml:space="preserve">2.53656935691833</t>
   </si>
   <si>
     <t xml:space="preserve">2.52744054794312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54830718040466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55091547966003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5378737449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58612751960754</t>
+    <t xml:space="preserve">2.54830694198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55091524124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53787398338318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58612728118896</t>
   </si>
   <si>
     <t xml:space="preserve">2.57699823379517</t>
@@ -284,43 +284,43 @@
     <t xml:space="preserve">2.59786462783813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60438561439514</t>
+    <t xml:space="preserve">2.60438537597656</t>
   </si>
   <si>
     <t xml:space="preserve">2.57308578491211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66959261894226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68393874168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69828414916992</t>
+    <t xml:space="preserve">2.66959285736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68393850326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6982843875885</t>
   </si>
   <si>
     <t xml:space="preserve">2.64872622489929</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64742231369019</t>
+    <t xml:space="preserve">2.64742207527161</t>
   </si>
   <si>
     <t xml:space="preserve">2.68133020401001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67480969429016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63438081741333</t>
+    <t xml:space="preserve">2.67480945587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63438057899475</t>
   </si>
   <si>
     <t xml:space="preserve">2.64350986480713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69567584991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69958829879761</t>
+    <t xml:space="preserve">2.69567561149597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69958853721619</t>
   </si>
   <si>
     <t xml:space="preserve">2.67872190475464</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">2.73480010032654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77262043952942</t>
+    <t xml:space="preserve">2.772620677948</t>
   </si>
   <si>
     <t xml:space="preserve">2.7543625831604</t>
@@ -338,25 +338,25 @@
     <t xml:space="preserve">2.71262979507446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70089268684387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70219683647156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66176748275757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78305411338806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7452335357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6930673122406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71915078163147</t>
+    <t xml:space="preserve">2.70089292526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7021963596344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66176772117615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7830536365509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74523329734802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69306778907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71915054321289</t>
   </si>
   <si>
     <t xml:space="preserve">2.70610928535461</t>
@@ -365,112 +365,112 @@
     <t xml:space="preserve">2.74914598464966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77783703804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8352198600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84043645858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88738584518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89651465415955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8534779548645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91477251052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00867176055908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02040910720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96824264526367</t>
+    <t xml:space="preserve">2.77783751487732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83521962165833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84043622016907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88738560676575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89651489257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85347747802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91477274894714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0086715221405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02040863037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96824288368225</t>
   </si>
   <si>
     <t xml:space="preserve">3.00736737251282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05822896957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09885382652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15591311454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09613728523254</t>
+    <t xml:space="preserve">3.05822944641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09885358810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15591335296631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09613680839539</t>
   </si>
   <si>
     <t xml:space="preserve">3.13825178146362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09070301055908</t>
+    <t xml:space="preserve">3.0907027721405</t>
   </si>
   <si>
     <t xml:space="preserve">2.97658467292786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13417649269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20074486732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24965357780457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28769302368164</t>
+    <t xml:space="preserve">3.13417625427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20074534416199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24965286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28769278526306</t>
   </si>
   <si>
     <t xml:space="preserve">3.23063349723816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24557733535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22248220443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25101184844971</t>
+    <t xml:space="preserve">3.24557757377625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2224817276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25101113319397</t>
   </si>
   <si>
     <t xml:space="preserve">3.18715977668762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09477806091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11379861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19938683509827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10428810119629</t>
+    <t xml:space="preserve">3.09477877616882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11379837989807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19938731193542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10428833961487</t>
   </si>
   <si>
     <t xml:space="preserve">3.12059092521667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15727186203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16270589828491</t>
+    <t xml:space="preserve">3.15727210044861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16270637512207</t>
   </si>
   <si>
     <t xml:space="preserve">3.14504480361938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03907775878906</t>
+    <t xml:space="preserve">3.03907799720764</t>
   </si>
   <si>
     <t xml:space="preserve">3.02820944786072</t>
@@ -479,25 +479,25 @@
     <t xml:space="preserve">2.96707463264465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00375533103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03636026382446</t>
+    <t xml:space="preserve">3.00375556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03636050224304</t>
   </si>
   <si>
     <t xml:space="preserve">3.02005839347839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97794318199158</t>
+    <t xml:space="preserve">2.977942943573</t>
   </si>
   <si>
     <t xml:space="preserve">2.9860942363739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99560451507568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07575869560242</t>
+    <t xml:space="preserve">2.9956042766571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.075758934021</t>
   </si>
   <si>
     <t xml:space="preserve">3.08390974998474</t>
@@ -509,22 +509,22 @@
     <t xml:space="preserve">3.10836410522461</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12874245643616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17900824546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17221570014954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12602519989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15863037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22519969940186</t>
+    <t xml:space="preserve">3.12874221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1790087223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17221546173096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12602543830872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15863013267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2251992225647</t>
   </si>
   <si>
     <t xml:space="preserve">3.26052188873291</t>
@@ -533,37 +533,37 @@
     <t xml:space="preserve">3.25237035751343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27682375907898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30671286582947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30263638496399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28090000152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21025514602661</t>
+    <t xml:space="preserve">3.27682399749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30671238899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30263710021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2808997631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21025490760803</t>
   </si>
   <si>
     <t xml:space="preserve">3.28361701965332</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29856133460999</t>
+    <t xml:space="preserve">3.29856061935425</t>
   </si>
   <si>
     <t xml:space="preserve">3.28225827217102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26323866844177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25644564628601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27003145217896</t>
+    <t xml:space="preserve">3.26323843002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25644588470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27003192901611</t>
   </si>
   <si>
     <t xml:space="preserve">3.24693608283997</t>
@@ -578,73 +578,73 @@
     <t xml:space="preserve">3.24150156974792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26188039779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23470902442932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19802808761597</t>
+    <t xml:space="preserve">3.26187968254089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2347092628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19802856445312</t>
   </si>
   <si>
     <t xml:space="preserve">3.23742580413818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24829483032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22791647911072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1939525604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16542267799377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18444275856018</t>
+    <t xml:space="preserve">3.24829459190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22791624069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19395303726196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16542315483093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18444299697876</t>
   </si>
   <si>
     <t xml:space="preserve">3.18172574043274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20753812789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24014329910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26731395721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24286079406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22655773162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23199248313904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20617914199829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14640355110168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16813993453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157108306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678166389465</t>
+    <t xml:space="preserve">3.20753860473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2401430606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26731443405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24286031723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.226557970047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2319917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20617961883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14640331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16814017295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157084465027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678142547607</t>
   </si>
   <si>
     <t xml:space="preserve">3.21704792976379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22927498817444</t>
+    <t xml:space="preserve">3.22927474975586</t>
   </si>
   <si>
     <t xml:space="preserve">3.24421882629395</t>
@@ -653,115 +653,115 @@
     <t xml:space="preserve">3.21433067321777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25372862815857</t>
+    <t xml:space="preserve">3.25372838973999</t>
   </si>
   <si>
     <t xml:space="preserve">3.35154485702515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49147534370422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3936595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46430373191833</t>
+    <t xml:space="preserve">3.49147510528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39365935325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46430444717407</t>
   </si>
   <si>
     <t xml:space="preserve">3.50506019592285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41675496101379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40656542778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44732189178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43373680114746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42694401741028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47109723091125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46770071983337</t>
+    <t xml:space="preserve">3.41675519943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40656590461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44732213020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43373656272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4269437789917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47109699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46770048141479</t>
   </si>
   <si>
     <t xml:space="preserve">3.48128604888916</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50166440010071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54242086410522</t>
+    <t xml:space="preserve">3.50166463851929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54242038726807</t>
   </si>
   <si>
     <t xml:space="preserve">3.51185345649719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54581713676453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55940270423889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412284851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60015916824341</t>
+    <t xml:space="preserve">3.54581737518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55940294265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412308692932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60015964508057</t>
   </si>
   <si>
     <t xml:space="preserve">3.53223180770874</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48468232154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55261015892029</t>
+    <t xml:space="preserve">3.48468255996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55260968208313</t>
   </si>
   <si>
     <t xml:space="preserve">3.61374497413635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52543878555298</t>
+    <t xml:space="preserve">3.52543902397156</t>
   </si>
   <si>
     <t xml:space="preserve">3.58997011184692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60355591773987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5933666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62053775787354</t>
+    <t xml:space="preserve">3.60355567932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59336638450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62053751945496</t>
   </si>
   <si>
     <t xml:space="preserve">3.59676289558411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56619572639465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562784194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45411515235901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45751118659973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39637660980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32301473617554</t>
+    <t xml:space="preserve">3.56619548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53562808036804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45411491394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45751142501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39637637138367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32301497459412</t>
   </si>
   <si>
     <t xml:space="preserve">3.38279128074646</t>
@@ -770,10 +770,10 @@
     <t xml:space="preserve">3.40996193885803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38958358764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32844948768616</t>
+    <t xml:space="preserve">3.38958382606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32844924926758</t>
   </si>
   <si>
     <t xml:space="preserve">3.30807089805603</t>
@@ -782,22 +782,22 @@
     <t xml:space="preserve">3.31078791618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35018563270569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3759982585907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35426211357117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37328171730042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34339308738708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36648845672607</t>
+    <t xml:space="preserve">3.35018610954285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37599802017212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35426187515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37328147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34339380264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36648797988892</t>
   </si>
   <si>
     <t xml:space="preserve">3.37871527671814</t>
@@ -809,19 +809,19 @@
     <t xml:space="preserve">3.12126994132996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16406416893005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06624841690063</t>
+    <t xml:space="preserve">3.16406488418579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06624913215637</t>
   </si>
   <si>
     <t xml:space="preserve">3.04587078094482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03228521347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00239706039429</t>
+    <t xml:space="preserve">3.03228545188904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00239658355713</t>
   </si>
   <si>
     <t xml:space="preserve">3.0220959186554</t>
@@ -830,10 +830,10 @@
     <t xml:space="preserve">3.02549242973328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04655027389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99424600601196</t>
+    <t xml:space="preserve">3.04654979705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99424529075623</t>
   </si>
   <si>
     <t xml:space="preserve">2.96164059638977</t>
@@ -845,52 +845,52 @@
     <t xml:space="preserve">3.03092622756958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11651515960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06828689575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00035905838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96639561653137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.929034948349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92495965957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01326489448547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0940990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14300680160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23538851737976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22723722457886</t>
+    <t xml:space="preserve">3.11651492118835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06828713417053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00035929679871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96639537811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92903518676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.924959897995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01326537132263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09409880638123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14300656318665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23538827896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2272367477417</t>
   </si>
   <si>
     <t xml:space="preserve">3.21297287940979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19327330589294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27342796325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29448509216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20414209365845</t>
+    <t xml:space="preserve">3.19327354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27342748641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29448533058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20414161682129</t>
   </si>
   <si>
     <t xml:space="preserve">3.30739164352417</t>
@@ -899,145 +899,145 @@
     <t xml:space="preserve">3.28565454483032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36377191543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39909362792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47924900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47517228126526</t>
+    <t xml:space="preserve">3.36377120018005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39909410476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47924828529358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47517275810242</t>
   </si>
   <si>
     <t xml:space="preserve">3.48196530342102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43713307380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44392609596252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49962711334229</t>
+    <t xml:space="preserve">3.43713283538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44392585754395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49962687492371</t>
   </si>
   <si>
     <t xml:space="preserve">3.52815580368042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47788953781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51457071304321</t>
+    <t xml:space="preserve">3.47789001464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51457023620605</t>
   </si>
   <si>
     <t xml:space="preserve">3.45887041091919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52679777145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52000427246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57570552825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6273295879364</t>
+    <t xml:space="preserve">3.52679753303528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52000498771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57570505142212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62733054161072</t>
   </si>
   <si>
     <t xml:space="preserve">3.64499163627625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60423493385315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60287618637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62597131729126</t>
+    <t xml:space="preserve">3.60423517227173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60287690162659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62597155570984</t>
   </si>
   <si>
     <t xml:space="preserve">3.49419236183167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45615267753601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41539621353149</t>
+    <t xml:space="preserve">3.45615291595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41539645195007</t>
   </si>
   <si>
     <t xml:space="preserve">3.45479440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44256734848022</t>
+    <t xml:space="preserve">3.44256711006165</t>
   </si>
   <si>
     <t xml:space="preserve">3.36309242248535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39298033714294</t>
+    <t xml:space="preserve">3.39297986030579</t>
   </si>
   <si>
     <t xml:space="preserve">3.39461970329285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45400094985962</t>
+    <t xml:space="preserve">3.45400071144104</t>
   </si>
   <si>
     <t xml:space="preserve">3.4610698223114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36280846595764</t>
+    <t xml:space="preserve">3.36280798912048</t>
   </si>
   <si>
     <t xml:space="preserve">3.28151297569275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23414897918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07367897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1669921875</t>
+    <t xml:space="preserve">3.23414921760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07367873191833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16699171066284</t>
   </si>
   <si>
     <t xml:space="preserve">3.1528537273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18961358070374</t>
+    <t xml:space="preserve">3.18961405754089</t>
   </si>
   <si>
     <t xml:space="preserve">3.27868509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25747752189636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23556351661682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23768424987793</t>
+    <t xml:space="preserve">3.25747728347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23556303977966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23768377304077</t>
   </si>
   <si>
     <t xml:space="preserve">3.20163106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34089350700378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43774151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39037823677063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41087865829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37623953819275</t>
+    <t xml:space="preserve">3.34089374542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43774175643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39037799835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4108784198761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37624001502991</t>
   </si>
   <si>
     <t xml:space="preserve">3.38967132568359</t>
@@ -1046,28 +1046,28 @@
     <t xml:space="preserve">3.40946483612061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46319055557251</t>
+    <t xml:space="preserve">3.46319079399109</t>
   </si>
   <si>
     <t xml:space="preserve">3.33735942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31544494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29989242553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34442830085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35432553291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32958316802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3380663394928</t>
+    <t xml:space="preserve">3.31544470787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29989290237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3444287776947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35432529449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32958340644836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33806610107422</t>
   </si>
   <si>
     <t xml:space="preserve">3.29211640357971</t>
@@ -1076,37 +1076,37 @@
     <t xml:space="preserve">3.35644602775574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3522047996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40098142623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41865468025208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37765383720398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32534193992615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35573959350586</t>
+    <t xml:space="preserve">3.35220456123352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40098190307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41865491867065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37765312194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32534146308899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3557391166687</t>
   </si>
   <si>
     <t xml:space="preserve">3.34230804443359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40027475357056</t>
+    <t xml:space="preserve">3.40027499198914</t>
   </si>
   <si>
     <t xml:space="preserve">3.45258665084839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44834518432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44269013404846</t>
+    <t xml:space="preserve">3.44834542274475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44269037246704</t>
   </si>
   <si>
     <t xml:space="preserve">3.4511730670929</t>
@@ -1115,46 +1115,46 @@
     <t xml:space="preserve">3.41229271888733</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40734386444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46036314964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4313793182373</t>
+    <t xml:space="preserve">3.40734434127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46036291122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43137907981873</t>
   </si>
   <si>
     <t xml:space="preserve">3.4787425994873</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42077589035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42572402954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51479601860046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49429488182068</t>
+    <t xml:space="preserve">3.42077565193176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42572426795959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51479554176331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49429512023926</t>
   </si>
   <si>
     <t xml:space="preserve">3.39532661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41582703590393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42925834655762</t>
+    <t xml:space="preserve">3.41582679748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4292585849762</t>
   </si>
   <si>
     <t xml:space="preserve">3.40239596366882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36139440536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38825750350952</t>
+    <t xml:space="preserve">3.36139488220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3882577419281</t>
   </si>
   <si>
     <t xml:space="preserve">3.43279361724854</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">3.29706478118896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30413389205933</t>
+    <t xml:space="preserve">3.30413413047791</t>
   </si>
   <si>
     <t xml:space="preserve">3.30837559700012</t>
@@ -1175,70 +1175,70 @@
     <t xml:space="preserve">3.28787517547607</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3161518573761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25182199478149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2899956703186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33311796188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33099675178528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33382487297058</t>
+    <t xml:space="preserve">3.31615161895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25182223320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28999590873718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33311748504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3309965133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33382511138916</t>
   </si>
   <si>
     <t xml:space="preserve">3.32675576210022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34654951095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47450160980225</t>
+    <t xml:space="preserve">3.34654927253723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47450184822083</t>
   </si>
   <si>
     <t xml:space="preserve">3.49924302101135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49641609191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46248388290405</t>
+    <t xml:space="preserve">3.49641585350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46248364448547</t>
   </si>
   <si>
     <t xml:space="preserve">3.45682859420776</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45470809936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38613677024841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45753526687622</t>
+    <t xml:space="preserve">3.45470786094666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38613653182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45753502845764</t>
   </si>
   <si>
     <t xml:space="preserve">3.45894932746887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37411880493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39391279220581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42006850242615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30978941917419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32816910743713</t>
+    <t xml:space="preserve">3.37411904335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39391255378723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42006874084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30978965759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32816958427429</t>
   </si>
   <si>
     <t xml:space="preserve">3.35715317726135</t>
@@ -1250,109 +1250,109 @@
     <t xml:space="preserve">3.24899458885193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2101137638092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23485636711121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20516562461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15780234336853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13093900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15356087684631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24546003341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16911268234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19809699058533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1889066696167</t>
+    <t xml:space="preserve">3.21011400222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23485612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20516586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15780258178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.130939245224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15356063842773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24546027183533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16911244392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19809627532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18890690803528</t>
   </si>
   <si>
     <t xml:space="preserve">3.23909735679626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23344206809998</t>
+    <t xml:space="preserve">3.23344254493713</t>
   </si>
   <si>
     <t xml:space="preserve">3.27727150917053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23202872276306</t>
+    <t xml:space="preserve">3.23202848434448</t>
   </si>
   <si>
     <t xml:space="preserve">3.22920083999634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22495913505554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27232336997986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31473827362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37341213226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4250168800354</t>
+    <t xml:space="preserve">3.22495937347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2723228931427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31473803520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37341237068176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42501711845398</t>
   </si>
   <si>
     <t xml:space="preserve">3.43491435050964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48864006996155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4469313621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38755035400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35927391052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34160089492798</t>
+    <t xml:space="preserve">3.48863983154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44693160057068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38755011558533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35927367210388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34160137176514</t>
   </si>
   <si>
     <t xml:space="preserve">3.3005998134613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30484056472778</t>
+    <t xml:space="preserve">3.3048415184021</t>
   </si>
   <si>
     <t xml:space="preserve">3.2758572101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39603328704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3493766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36068749427795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36704993247986</t>
+    <t xml:space="preserve">3.3960337638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34937739372253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36068773269653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36705017089844</t>
   </si>
   <si>
     <t xml:space="preserve">3.39179182052612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41653442382812</t>
+    <t xml:space="preserve">3.41653370857239</t>
   </si>
   <si>
     <t xml:space="preserve">3.45329403877258</t>
@@ -1361,25 +1361,25 @@
     <t xml:space="preserve">3.5232789516449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5911431312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61235046386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073086738586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61093640327454</t>
+    <t xml:space="preserve">3.59114265441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61235022544861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073039054871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61093616485596</t>
   </si>
   <si>
     <t xml:space="preserve">3.6279022693634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60103988647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59962630271912</t>
+    <t xml:space="preserve">3.60103964805603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59962606430054</t>
   </si>
   <si>
     <t xml:space="preserve">3.51055431365967</t>
@@ -1388,70 +1388,70 @@
     <t xml:space="preserve">3.53176164627075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57841801643372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61941957473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6491105556488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6788010597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62083387374878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68587040901184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70849132537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65335154533386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68304228782654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68728351593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67738676071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71414661407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71131896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70990538597107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72545695304871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7325267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.731112241745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6717312335968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69293928146362</t>
+    <t xml:space="preserve">3.57841825485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61941933631897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64911031723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67880058288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62083339691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68586945533752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70849108695984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65335178375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6830427646637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68728375434875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67738699913025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71414685249329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71131825447083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70990514755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72545719146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73252606391907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73111200332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67173171043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6929395198822</t>
   </si>
   <si>
     <t xml:space="preserve">3.719801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63779902458191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61517858505249</t>
+    <t xml:space="preserve">3.63779950141907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61517834663391</t>
   </si>
   <si>
     <t xml:space="preserve">3.68869757652283</t>
@@ -1463,10 +1463,10 @@
     <t xml:space="preserve">3.69435262680054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69718074798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68162822723389</t>
+    <t xml:space="preserve">3.69718027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68162846565247</t>
   </si>
   <si>
     <t xml:space="preserve">3.75232005119324</t>
@@ -1475,145 +1475,145 @@
     <t xml:space="preserve">3.7438371181488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72262930870056</t>
+    <t xml:space="preserve">3.72262978553772</t>
   </si>
   <si>
     <t xml:space="preserve">3.76504492759705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75938940048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71697425842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78342437744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83997821807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86542701721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83573627471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82442545890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79756283760071</t>
+    <t xml:space="preserve">3.75938963890076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71697402000427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78342509269714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83997774124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86542677879333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83573651313782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82442498207092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79756307601929</t>
   </si>
   <si>
     <t xml:space="preserve">3.8173565864563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85977125167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86966800689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8838062286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87532448768616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89370322227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88804864883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85270190238953</t>
+    <t xml:space="preserve">3.85977220535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86966824531555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88380718231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87532377243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89370369911194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88804817199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85270214080811</t>
   </si>
   <si>
     <t xml:space="preserve">3.87108206748962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89087605476379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84139204025269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88239336013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92339444160461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88946223258972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90359997749329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92056655883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9191529750824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96439528465271</t>
+    <t xml:space="preserve">3.89087629318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84139156341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88239312171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92339468002319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88946270942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90360069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92056679725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91915273666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96439480781555</t>
   </si>
   <si>
     <t xml:space="preserve">3.95732641220093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91066932678223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93329071998596</t>
+    <t xml:space="preserve">3.91066980361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93329119682312</t>
   </si>
   <si>
     <t xml:space="preserve">3.90642881393433</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90501427650452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92198014259338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91208362579346</t>
+    <t xml:space="preserve">3.90501523017883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92198038101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91208338737488</t>
   </si>
   <si>
     <t xml:space="preserve">3.9304633140564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87956500053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89794540405273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88097929954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.947429895401</t>
+    <t xml:space="preserve">3.87956523895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.897944688797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88097882270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94742894172668</t>
   </si>
   <si>
     <t xml:space="preserve">3.89229011535645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87390995025635</t>
+    <t xml:space="preserve">3.87391018867493</t>
   </si>
   <si>
     <t xml:space="preserve">3.90925574302673</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95025706291199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98136138916016</t>
+    <t xml:space="preserve">3.95025682449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.981360912323</t>
   </si>
   <si>
     <t xml:space="preserve">4.00963830947876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08032989501953</t>
+    <t xml:space="preserve">4.08033037185669</t>
   </si>
   <si>
     <t xml:space="preserve">4.07891607284546</t>
@@ -1622,22 +1622,22 @@
     <t xml:space="preserve">4.13016319274902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16984796524048</t>
+    <t xml:space="preserve">4.16984748840332</t>
   </si>
   <si>
     <t xml:space="preserve">4.21100330352783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.213942527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24921798706055</t>
+    <t xml:space="preserve">4.21394300460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24921846389771</t>
   </si>
   <si>
     <t xml:space="preserve">4.20512390136719</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1948356628418</t>
+    <t xml:space="preserve">4.19483518600464</t>
   </si>
   <si>
     <t xml:space="preserve">4.12281465530396</t>
@@ -1646,16 +1646,16 @@
     <t xml:space="preserve">4.10811614990234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16543865203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21541213989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26979494094849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30507040023804</t>
+    <t xml:space="preserve">4.16543817520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21541261672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26979541778564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3050708770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.32123851776123</t>
@@ -1664,31 +1664,31 @@
     <t xml:space="preserve">4.36827230453491</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33152770996094</t>
+    <t xml:space="preserve">4.33152723312378</t>
   </si>
   <si>
     <t xml:space="preserve">4.32564783096313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28890228271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35651397705078</t>
+    <t xml:space="preserve">4.288902759552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35651350021362</t>
   </si>
   <si>
     <t xml:space="preserve">4.34328556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49908590316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44764184951782</t>
+    <t xml:space="preserve">4.49908542633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44764232635498</t>
   </si>
   <si>
     <t xml:space="preserve">4.4461727142334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48291778564453</t>
+    <t xml:space="preserve">4.48291730880737</t>
   </si>
   <si>
     <t xml:space="preserve">4.48732662200928</t>
@@ -1700,34 +1700,34 @@
     <t xml:space="preserve">4.43735361099243</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35210466384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34181547164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3344669342041</t>
+    <t xml:space="preserve">4.35210418701172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34181594848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33446645736694</t>
   </si>
   <si>
     <t xml:space="preserve">4.43147420883179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47997808456421</t>
+    <t xml:space="preserve">4.47997856140137</t>
   </si>
   <si>
     <t xml:space="preserve">4.44911193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43882322311401</t>
+    <t xml:space="preserve">4.43882369995117</t>
   </si>
   <si>
     <t xml:space="preserve">4.49467611312866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51966238021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50349521636963</t>
+    <t xml:space="preserve">4.51966285705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50349473953247</t>
   </si>
   <si>
     <t xml:space="preserve">4.54317998886108</t>
@@ -1736,19 +1736,19 @@
     <t xml:space="preserve">4.56228733062744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57698535919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52701139450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54170942306519</t>
+    <t xml:space="preserve">4.57698583602905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52701187133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54170989990234</t>
   </si>
   <si>
     <t xml:space="preserve">4.54905891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40207767486572</t>
+    <t xml:space="preserve">4.40207815170288</t>
   </si>
   <si>
     <t xml:space="preserve">4.43588352203369</t>
@@ -1757,7 +1757,7 @@
     <t xml:space="preserve">4.42559480667114</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38885021209717</t>
+    <t xml:space="preserve">4.38884973526001</t>
   </si>
   <si>
     <t xml:space="preserve">4.38150072097778</t>
@@ -1766,19 +1766,19 @@
     <t xml:space="preserve">4.24480867385864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20218420028687</t>
+    <t xml:space="preserve">4.20218324661255</t>
   </si>
   <si>
     <t xml:space="preserve">4.29037237167358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29331254959106</t>
+    <t xml:space="preserve">4.29331207275391</t>
   </si>
   <si>
     <t xml:space="preserve">4.27420473098755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26097631454468</t>
+    <t xml:space="preserve">4.26097583770752</t>
   </si>
   <si>
     <t xml:space="preserve">4.2844934463501</t>
@@ -1790,7 +1790,7 @@
     <t xml:space="preserve">4.11399602890015</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16102981567383</t>
+    <t xml:space="preserve">4.16102886199951</t>
   </si>
   <si>
     <t xml:space="preserve">4.24186849594116</t>
@@ -1811,40 +1811,40 @@
     <t xml:space="preserve">4.19777393341064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34034585952759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33593654632568</t>
+    <t xml:space="preserve">4.34034633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33593702316284</t>
   </si>
   <si>
     <t xml:space="preserve">4.34916496276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31388902664185</t>
+    <t xml:space="preserve">4.313889503479</t>
   </si>
   <si>
     <t xml:space="preserve">4.30213117599487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20806312561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14192199707031</t>
+    <t xml:space="preserve">4.20806360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14192152023315</t>
   </si>
   <si>
     <t xml:space="preserve">4.10370683670044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18307638168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14045143127441</t>
+    <t xml:space="preserve">4.18307685852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14045190811157</t>
   </si>
   <si>
     <t xml:space="preserve">4.12575387954712</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1933650970459</t>
+    <t xml:space="preserve">4.19336462020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.18160676956177</t>
@@ -1862,13 +1862,13 @@
     <t xml:space="preserve">4.39031934738159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32711791992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30066108703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21247243881226</t>
+    <t xml:space="preserve">4.32711744308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30066204071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21247339248657</t>
   </si>
   <si>
     <t xml:space="preserve">4.31241989135742</t>
@@ -1883,7 +1883,7 @@
     <t xml:space="preserve">4.18895578384399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011064529419</t>
+    <t xml:space="preserve">4.23010969161987</t>
   </si>
   <si>
     <t xml:space="preserve">4.18748617172241</t>
@@ -1892,16 +1892,16 @@
     <t xml:space="preserve">4.17425775527954</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17278814315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14486122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1683783531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18013715744019</t>
+    <t xml:space="preserve">4.1727876663208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14486169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16837787628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18013763427734</t>
   </si>
   <si>
     <t xml:space="preserve">4.23892879486084</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">4.25362730026245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29478168487549</t>
+    <t xml:space="preserve">4.29478120803833</t>
   </si>
   <si>
     <t xml:space="preserve">4.33740663528442</t>
@@ -1919,22 +1919,22 @@
     <t xml:space="preserve">4.35063505172729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28302335739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33299684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30654096603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37268209457397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39178943634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27861452102661</t>
+    <t xml:space="preserve">4.28302383422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33299732208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30654048919678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37268161773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39178895950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27861404418945</t>
   </si>
   <si>
     <t xml:space="preserve">4.22423124313354</t>
@@ -1943,10 +1943,10 @@
     <t xml:space="preserve">4.23745918273926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22570085525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19189548492432</t>
+    <t xml:space="preserve">4.22570037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19189500808716</t>
   </si>
   <si>
     <t xml:space="preserve">4.22129154205322</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">4.23599004745483</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22717094421387</t>
+    <t xml:space="preserve">4.22717046737671</t>
   </si>
   <si>
     <t xml:space="preserve">4.00963926315308</t>
@@ -1964,43 +1964,43 @@
     <t xml:space="preserve">4.07431077957153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08900928497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04932403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01992702484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95378637313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99494051933289</t>
+    <t xml:space="preserve">4.08900880813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04932355880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01992750167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95378661155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99494099617004</t>
   </si>
   <si>
     <t xml:space="preserve">4.0419750213623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99053120613098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03609561920166</t>
+    <t xml:space="preserve">3.9905321598053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0360951423645</t>
   </si>
   <si>
     <t xml:space="preserve">4.10664653778076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16396903991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12722396850586</t>
+    <t xml:space="preserve">4.16396856307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1272234916687</t>
   </si>
   <si>
     <t xml:space="preserve">4.13751220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00081968307495</t>
+    <t xml:space="preserve">4.00082015991211</t>
   </si>
   <si>
     <t xml:space="preserve">4.09194803237915</t>
@@ -2012,28 +2012,28 @@
     <t xml:space="preserve">4.02727651596069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02286672592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10076713562012</t>
+    <t xml:space="preserve">4.02286767959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10076665878296</t>
   </si>
   <si>
     <t xml:space="preserve">4.20365381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13898277282715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25068759918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20659351348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26391553878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30801010131836</t>
+    <t xml:space="preserve">4.13898229598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25068807601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20659303665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.263916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30801057815552</t>
   </si>
   <si>
     <t xml:space="preserve">4.48144769668579</t>
@@ -2042,34 +2042,34 @@
     <t xml:space="preserve">4.51525354385376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49761581420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40648698806763</t>
+    <t xml:space="preserve">4.49761533737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40648746490479</t>
   </si>
   <si>
     <t xml:space="preserve">4.41677618026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46674919128418</t>
+    <t xml:space="preserve">4.46674966812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.49173641204834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46087121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46233987808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51231336593628</t>
+    <t xml:space="preserve">4.46087026596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46234035491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5123143196106</t>
   </si>
   <si>
     <t xml:space="preserve">4.45205163955688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4858570098877</t>
+    <t xml:space="preserve">4.48585748672485</t>
   </si>
   <si>
     <t xml:space="preserve">4.62548923492432</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">4.26244592666626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06549167633057</t>
+    <t xml:space="preserve">4.06549215316772</t>
   </si>
   <si>
     <t xml:space="preserve">4.08606910705566</t>
@@ -2093,31 +2093,31 @@
     <t xml:space="preserve">3.51798796653748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50181984901428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02192735671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24754309654236</t>
+    <t xml:space="preserve">3.5018196105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02192711830139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24754333496094</t>
   </si>
   <si>
     <t xml:space="preserve">3.15127062797546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27032494544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29531216621399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35189938545227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21153259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.129958152771</t>
+    <t xml:space="preserve">3.27032470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29531240463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35189962387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21153283119202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12995839118958</t>
   </si>
   <si>
     <t xml:space="preserve">3.35557413101196</t>
@@ -2126,28 +2126,28 @@
     <t xml:space="preserve">3.38937950134277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34381604194641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35924863815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57090163230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66643857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44964146614075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55693817138672</t>
+    <t xml:space="preserve">3.34381556510925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3592483997345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57090091705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66643881797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44964170455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55693769454956</t>
   </si>
   <si>
     <t xml:space="preserve">3.58780384063721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53636074066162</t>
+    <t xml:space="preserve">3.53636002540588</t>
   </si>
   <si>
     <t xml:space="preserve">3.54958891868591</t>
@@ -2159,88 +2159,88 @@
     <t xml:space="preserve">3.54811906814575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56428647041321</t>
+    <t xml:space="preserve">3.56428670883179</t>
   </si>
   <si>
     <t xml:space="preserve">3.59368324279785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6260187625885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57163619995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57310557365417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44082283973694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61719965934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52754187583923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57457566261292</t>
+    <t xml:space="preserve">3.62601900100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57163596153259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57310509681702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44082307815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61719989776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52754139900208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57457542419434</t>
   </si>
   <si>
     <t xml:space="preserve">3.56722664833069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57898497581482</t>
+    <t xml:space="preserve">3.5789852142334</t>
   </si>
   <si>
     <t xml:space="preserve">3.75168776512146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68187212944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70391917228699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60691142082214</t>
+    <t xml:space="preserve">3.68187165260315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70391893386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60691118240356</t>
   </si>
   <si>
     <t xml:space="preserve">3.61279034614563</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66423368453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63189840316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62454891204834</t>
+    <t xml:space="preserve">3.66423392295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63189816474915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62454915046692</t>
   </si>
   <si>
     <t xml:space="preserve">3.63777709007263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62307929992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71126842498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73626303672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60662746429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66372919082642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63440680503845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68533444404602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75015234947205</t>
+    <t xml:space="preserve">3.62307906150818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71126770973206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73626279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60662722587585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66372895240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63440656661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68533492088318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75015187263489</t>
   </si>
   <si>
     <t xml:space="preserve">3.73008966445923</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">3.80725312232971</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77021455764771</t>
+    <t xml:space="preserve">3.77021479606628</t>
   </si>
   <si>
     <t xml:space="preserve">3.81959915161133</t>
@@ -2261,43 +2261,43 @@
     <t xml:space="preserve">3.90447926521301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99707555770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05109024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02408266067505</t>
+    <t xml:space="preserve">3.99707579612732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05108976364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02408313751221</t>
   </si>
   <si>
     <t xml:space="preserve">3.9276282787323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88133025169373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81651306152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91991257667542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08581399917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05880689620972</t>
+    <t xml:space="preserve">3.88133072853088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81651258468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91991186141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08581352233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05880641937256</t>
   </si>
   <si>
     <t xml:space="preserve">4.10896301269531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14754438400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02022504806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96620988845825</t>
+    <t xml:space="preserve">4.14754486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02022457122803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96621036529541</t>
   </si>
   <si>
     <t xml:space="preserve">3.9893593788147</t>
@@ -2306,13 +2306,13 @@
     <t xml:space="preserve">4.03565788269043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08967161178589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03179883956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07038164138794</t>
+    <t xml:space="preserve">4.08967208862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03179979324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07038116455078</t>
   </si>
   <si>
     <t xml:space="preserve">4.11282110214233</t>
@@ -2321,22 +2321,22 @@
     <t xml:space="preserve">4.05494832992554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95463585853577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96235251426697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93534445762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97006821632385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97392654418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0742392539978</t>
+    <t xml:space="preserve">3.95463562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96235203742981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93534469604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97006797790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97392678260803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07423973083496</t>
   </si>
   <si>
     <t xml:space="preserve">4.1243953704834</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">4.10510444641113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09353065490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04723215103149</t>
+    <t xml:space="preserve">4.09352970123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04723167419434</t>
   </si>
   <si>
     <t xml:space="preserve">4.12825345993042</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">4.25943183898926</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26714849472046</t>
+    <t xml:space="preserve">4.26714897155762</t>
   </si>
   <si>
     <t xml:space="preserve">4.21313333511353</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">4.19770097732544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16297674179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16683626174927</t>
+    <t xml:space="preserve">4.16297721862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16683578491211</t>
   </si>
   <si>
     <t xml:space="preserve">4.22470855712891</t>
@@ -2378,58 +2378,58 @@
     <t xml:space="preserve">4.28643894195557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36746025085449</t>
+    <t xml:space="preserve">4.36746072769165</t>
   </si>
   <si>
     <t xml:space="preserve">4.42147588729858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39060974121094</t>
+    <t xml:space="preserve">4.3906102180481</t>
   </si>
   <si>
     <t xml:space="preserve">4.37517738342285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36360359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30573034286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26329040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24399900436401</t>
+    <t xml:space="preserve">4.36360263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30572986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26328992843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24399948120117</t>
   </si>
   <si>
     <t xml:space="preserve">4.31344652175903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30187129974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13597059249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22856616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18612623214722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17455196380615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1899847984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11667919158936</t>
+    <t xml:space="preserve">4.30187225341797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13597011566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22856664657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18612670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17455148696899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18998527526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11667966842651</t>
   </si>
   <si>
     <t xml:space="preserve">4.17841005325317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15526103973389</t>
+    <t xml:space="preserve">4.15526151657104</t>
   </si>
   <si>
     <t xml:space="preserve">4.15140295028687</t>
@@ -2441,28 +2441,28 @@
     <t xml:space="preserve">4.19384288787842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07809734344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89290428161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97778534889221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06266450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94691872596741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98550152778625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98164224624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88904690742493</t>
+    <t xml:space="preserve">4.07809782028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89290499687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97778463363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06266403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94691896438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9855010509491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9816427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88904666900635</t>
   </si>
   <si>
     <t xml:space="preserve">3.71157002449036</t>
@@ -2471,19 +2471,19 @@
     <t xml:space="preserve">3.7270028591156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8288586139679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8319456577301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86589789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00479221343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95077705383301</t>
+    <t xml:space="preserve">3.82885885238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83194518089294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86589765548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00479173660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95077729225159</t>
   </si>
   <si>
     <t xml:space="preserve">4.08195543289185</t>
@@ -2492,16 +2492,16 @@
     <t xml:space="preserve">4.03951549530029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13982772827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17069387435913</t>
+    <t xml:space="preserve">4.13982820510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17069339752197</t>
   </si>
   <si>
     <t xml:space="preserve">4.14368629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13211154937744</t>
+    <t xml:space="preserve">4.1321120262146</t>
   </si>
   <si>
     <t xml:space="preserve">3.93920302391052</t>
@@ -2510,25 +2510,25 @@
     <t xml:space="preserve">3.90062093734741</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80879592895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9932177066803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01250839233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95849323272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87747240066528</t>
+    <t xml:space="preserve">3.80879664421082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99321746826172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01250791549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95849370956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87747192382812</t>
   </si>
   <si>
     <t xml:space="preserve">3.9314866065979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9237699508667</t>
+    <t xml:space="preserve">3.92377042770386</t>
   </si>
   <si>
     <t xml:space="preserve">3.86203932762146</t>
@@ -2537,64 +2537,64 @@
     <t xml:space="preserve">3.8180558681488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80570983886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85818099975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89676356315613</t>
+    <t xml:space="preserve">3.80571007728577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85818123817444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89676260948181</t>
   </si>
   <si>
     <t xml:space="preserve">3.85663795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82114291191101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83811807632446</t>
+    <t xml:space="preserve">3.82114267349243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83811902999878</t>
   </si>
   <si>
     <t xml:space="preserve">3.94306135177612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90833759307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88518810272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83503150939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76712822914124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76249814033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82268571853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79799318313599</t>
+    <t xml:space="preserve">3.90833711624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88518834114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83503198623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76712799072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76249837875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8226854801178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79799342155457</t>
   </si>
   <si>
     <t xml:space="preserve">3.87361359596252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02794122695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04337406158447</t>
+    <t xml:space="preserve">4.02794075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04337358474731</t>
   </si>
   <si>
     <t xml:space="preserve">4.20927572250366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25171566009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25557374954224</t>
+    <t xml:space="preserve">4.25171518325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25557327270508</t>
   </si>
   <si>
     <t xml:space="preserve">4.31730461120605</t>
@@ -2603,25 +2603,25 @@
     <t xml:space="preserve">4.27100658416748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26251840591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2872109413147</t>
+    <t xml:space="preserve">4.26251888275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28721141815186</t>
   </si>
   <si>
     <t xml:space="preserve">4.25634527206421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24554300308228</t>
+    <t xml:space="preserve">4.24554204940796</t>
   </si>
   <si>
     <t xml:space="preserve">4.14985942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12979698181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14060020446777</t>
+    <t xml:space="preserve">4.12979793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14059972763062</t>
   </si>
   <si>
     <t xml:space="preserve">4.12362384796143</t>
@@ -2630,25 +2630,25 @@
     <t xml:space="preserve">4.16837882995605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17146492004395</t>
+    <t xml:space="preserve">4.17146587371826</t>
   </si>
   <si>
     <t xml:space="preserve">4.19924449920654</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23628234863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18844175338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1776385307312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17918157577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18381118774414</t>
+    <t xml:space="preserve">4.23628282546997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18844127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17763805389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17918109893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18381071090698</t>
   </si>
   <si>
     <t xml:space="preserve">4.20387411117554</t>
@@ -2657,19 +2657,19 @@
     <t xml:space="preserve">4.18535470962524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21622037887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29338407516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23165321350098</t>
+    <t xml:space="preserve">4.21621990203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29338359832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23165369033813</t>
   </si>
   <si>
     <t xml:space="preserve">4.25017213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23782634735107</t>
+    <t xml:space="preserve">4.23782587051392</t>
   </si>
   <si>
     <t xml:space="preserve">4.35048532485962</t>
@@ -2684,22 +2684,22 @@
     <t xml:space="preserve">4.47086000442505</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46610355377197</t>
+    <t xml:space="preserve">4.46610307693481</t>
   </si>
   <si>
     <t xml:space="preserve">4.44025039672852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38854455947876</t>
+    <t xml:space="preserve">4.3885440826416</t>
   </si>
   <si>
     <t xml:space="preserve">4.35622835159302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38531255722046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37400245666504</t>
+    <t xml:space="preserve">4.38531303405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37400197982788</t>
   </si>
   <si>
     <t xml:space="preserve">4.39016008377075</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">4.37723398208618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40147113800049</t>
+    <t xml:space="preserve">4.40147018432617</t>
   </si>
   <si>
     <t xml:space="preserve">4.45156097412109</t>
@@ -2720,16 +2720,16 @@
     <t xml:space="preserve">4.49357175827026</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5016508102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52911996841431</t>
+    <t xml:space="preserve">4.50165128707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52911949157715</t>
   </si>
   <si>
     <t xml:space="preserve">4.55174112319946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55012512207031</t>
+    <t xml:space="preserve">4.55012559890747</t>
   </si>
   <si>
     <t xml:space="preserve">4.62122106552124</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">4.58405733108521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56628370285034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54527807235718</t>
+    <t xml:space="preserve">4.56628322601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54527854919434</t>
   </si>
   <si>
     <t xml:space="preserve">4.52750444412231</t>
@@ -2750,40 +2750,40 @@
     <t xml:space="preserve">4.45640802383423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49680328369141</t>
+    <t xml:space="preserve">4.49680376052856</t>
   </si>
   <si>
     <t xml:space="preserve">4.48226118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48710870742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4531774520874</t>
+    <t xml:space="preserve">4.48710918426514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45317697525024</t>
   </si>
   <si>
     <t xml:space="preserve">4.46771955490112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4984188079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50649881362915</t>
+    <t xml:space="preserve">4.49841928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50649833679199</t>
   </si>
   <si>
     <t xml:space="preserve">4.55335712432861</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47902965545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52265691757202</t>
+    <t xml:space="preserve">4.4790301322937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52265739440918</t>
   </si>
   <si>
     <t xml:space="preserve">4.54204654693604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54689407348633</t>
+    <t xml:space="preserve">4.54689359664917</t>
   </si>
   <si>
     <t xml:space="preserve">4.50811433792114</t>
@@ -2798,10 +2798,10 @@
     <t xml:space="preserve">4.37238645553589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53719902038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56789875030518</t>
+    <t xml:space="preserve">4.5371994972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56789922714233</t>
   </si>
   <si>
     <t xml:space="preserve">4.61152648925781</t>
@@ -2810,19 +2810,19 @@
     <t xml:space="preserve">4.6147575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61637401580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62768459320068</t>
+    <t xml:space="preserve">4.61637353897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62768411636353</t>
   </si>
   <si>
     <t xml:space="preserve">4.59375238418579</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60829448699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63091611862183</t>
+    <t xml:space="preserve">4.60829496383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63091564178467</t>
   </si>
   <si>
     <t xml:space="preserve">4.65676879882812</t>
@@ -2840,40 +2840,40 @@
     <t xml:space="preserve">4.76502799987793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80219221115112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79896068572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76987600326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82804489135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82481384277344</t>
+    <t xml:space="preserve">4.80219173431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79896020889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76987552642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82804441452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82481336593628</t>
   </si>
   <si>
     <t xml:space="preserve">4.84420299530029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8070387840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69554805755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57436323165894</t>
+    <t xml:space="preserve">4.80703973770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69554853439331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57436275482178</t>
   </si>
   <si>
     <t xml:space="preserve">4.53558301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59213638305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54366207122803</t>
+    <t xml:space="preserve">4.5921368598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54366159439087</t>
   </si>
   <si>
     <t xml:space="preserve">4.49034070968628</t>
@@ -2885,13 +2885,13 @@
     <t xml:space="preserve">4.48549270629883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45964002609253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51134586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52427196502686</t>
+    <t xml:space="preserve">4.45963954925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51134634017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52427244186401</t>
   </si>
   <si>
     <t xml:space="preserve">4.46125555038452</t>
@@ -2903,43 +2903,43 @@
     <t xml:space="preserve">4.63576364517212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5889048576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65353727340698</t>
+    <t xml:space="preserve">4.58890438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65353775024414</t>
   </si>
   <si>
     <t xml:space="preserve">4.57113075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47579860687256</t>
+    <t xml:space="preserve">4.4757981300354</t>
   </si>
   <si>
     <t xml:space="preserve">4.42247629165649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46933460235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43217086791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47095060348511</t>
+    <t xml:space="preserve">4.46933507919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43217134475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47095012664795</t>
   </si>
   <si>
     <t xml:space="preserve">4.48387718200684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39985466003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37077045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3966236114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41116571426392</t>
+    <t xml:space="preserve">4.39985513687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37076997756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39662313461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41116523742676</t>
   </si>
   <si>
     <t xml:space="preserve">4.51457738876343</t>
@@ -2951,13 +2951,13 @@
     <t xml:space="preserve">4.43540287017822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50003576278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53881502151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61314249038696</t>
+    <t xml:space="preserve">4.50003528594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53881454467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6131420135498</t>
   </si>
   <si>
     <t xml:space="preserve">4.63253211975098</t>
@@ -2969,28 +2969,28 @@
     <t xml:space="preserve">4.55658864974976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57921028137207</t>
+    <t xml:space="preserve">4.57920980453491</t>
   </si>
   <si>
     <t xml:space="preserve">4.52588844299316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48064613342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53235197067261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44832944869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71978616714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72301721572876</t>
+    <t xml:space="preserve">4.48064565658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53235149383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44832897186279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50488328933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71978569030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72301816940308</t>
   </si>
   <si>
     <t xml:space="preserve">4.65838479995728</t>
@@ -3002,16 +3002,16 @@
     <t xml:space="preserve">4.65515327453613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6438422203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7020115852356</t>
+    <t xml:space="preserve">4.64384269714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70201206207275</t>
   </si>
   <si>
     <t xml:space="preserve">4.68585348129272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7036280632019</t>
+    <t xml:space="preserve">4.70362710952759</t>
   </si>
   <si>
     <t xml:space="preserve">4.66807985305786</t>
@@ -3023,16 +3023,16 @@
     <t xml:space="preserve">4.7262487411499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76179695129395</t>
+    <t xml:space="preserve">4.76179647445679</t>
   </si>
   <si>
     <t xml:space="preserve">4.75048637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84905052185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87490367889404</t>
+    <t xml:space="preserve">4.84905004501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87490320205688</t>
   </si>
   <si>
     <t xml:space="preserve">4.88944578170776</t>
@@ -3047,52 +3047,52 @@
     <t xml:space="preserve">4.83127641677856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66161584854126</t>
+    <t xml:space="preserve">4.66161632537842</t>
   </si>
   <si>
     <t xml:space="preserve">4.64061117172241</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7294807434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74402332305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76018095016479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74079084396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79734516143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71655416488647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79572868347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83450794219971</t>
+    <t xml:space="preserve">4.72948026657104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74402236938477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76018142700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74079132080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79734468460083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71655368804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79572916030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83450841903687</t>
   </si>
   <si>
     <t xml:space="preserve">4.74563884735107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50972986221313</t>
+    <t xml:space="preserve">4.50973033905029</t>
   </si>
   <si>
     <t xml:space="preserve">4.46448755264282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57759380340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62930011749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5598201751709</t>
+    <t xml:space="preserve">4.57759428024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62930059432983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55982065200806</t>
   </si>
   <si>
     <t xml:space="preserve">4.54850959777832</t>
@@ -3104,7 +3104,7 @@
     <t xml:space="preserve">4.41278123855591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35299587249756</t>
+    <t xml:space="preserve">4.35299634933472</t>
   </si>
   <si>
     <t xml:space="preserve">4.32068014144897</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">4.55820465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51780939102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49518823623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4176287651062</t>
+    <t xml:space="preserve">4.51780891418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49518775939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41762924194336</t>
   </si>
   <si>
     <t xml:space="preserve">4.48872470855713</t>
@@ -3143,19 +3143,19 @@
     <t xml:space="preserve">4.89590930938721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94034385681152</t>
+    <t xml:space="preserve">4.94034337997437</t>
   </si>
   <si>
     <t xml:space="preserve">4.91610670089722</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91206741333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00497627258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04537153244019</t>
+    <t xml:space="preserve">4.91206693649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00497674942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04537105560303</t>
   </si>
   <si>
     <t xml:space="preserve">5.15039920806885</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">5.08980655670166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0655689239502</t>
+    <t xml:space="preserve">5.06556987762451</t>
   </si>
   <si>
     <t xml:space="preserve">4.9807391166687</t>
@@ -3173,19 +3173,19 @@
     <t xml:space="preserve">4.96054172515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99285745620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01709508895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00093746185303</t>
+    <t xml:space="preserve">4.99285793304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01709461212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00093698501587</t>
   </si>
   <si>
     <t xml:space="preserve">5.01305532455444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97266054153442</t>
+    <t xml:space="preserve">4.97266006469727</t>
   </si>
   <si>
     <t xml:space="preserve">4.89994859695435</t>
@@ -3194,13 +3194,13 @@
     <t xml:space="preserve">4.94842290878296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92014598846436</t>
+    <t xml:space="preserve">4.92014646530151</t>
   </si>
   <si>
     <t xml:space="preserve">5.10596513748169</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05345106124878</t>
+    <t xml:space="preserve">5.05345058441162</t>
   </si>
   <si>
     <t xml:space="preserve">5.16251802444458</t>
@@ -3227,52 +3227,52 @@
     <t xml:space="preserve">5.07554531097412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0290961265564</t>
+    <t xml:space="preserve">5.02909660339355</t>
   </si>
   <si>
     <t xml:space="preserve">5.04598665237427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02487325668335</t>
+    <t xml:space="preserve">5.02487373352051</t>
   </si>
   <si>
     <t xml:space="preserve">4.87286043167114</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70395803451538</t>
+    <t xml:space="preserve">4.70395755767822</t>
   </si>
   <si>
     <t xml:space="preserve">4.58572483062744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54772186279297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60261487960815</t>
+    <t xml:space="preserve">4.54772233963013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60261583328247</t>
   </si>
   <si>
     <t xml:space="preserve">4.53505373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71662521362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64906358718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50971841812134</t>
+    <t xml:space="preserve">4.71662473678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64906406402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5097188949585</t>
   </si>
   <si>
     <t xml:space="preserve">4.34081506729126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45904731750488</t>
+    <t xml:space="preserve">4.45904779434204</t>
   </si>
   <si>
     <t xml:space="preserve">4.69551229476929</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63217401504517</t>
+    <t xml:space="preserve">4.63217353820801</t>
   </si>
   <si>
     <t xml:space="preserve">4.7419605255127</t>
@@ -3284,7 +3284,7 @@
     <t xml:space="preserve">4.69128942489624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72929239273071</t>
+    <t xml:space="preserve">4.72929286956787</t>
   </si>
   <si>
     <t xml:space="preserve">4.64061880111694</t>
@@ -3302,13 +3302,13 @@
     <t xml:space="preserve">4.64484119415283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45060205459595</t>
+    <t xml:space="preserve">4.45060253143311</t>
   </si>
   <si>
     <t xml:space="preserve">4.51816368103027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45482492446899</t>
+    <t xml:space="preserve">4.45482540130615</t>
   </si>
   <si>
     <t xml:space="preserve">4.38726377487183</t>
@@ -3317,16 +3317,16 @@
     <t xml:space="preserve">4.46327018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59417009353638</t>
+    <t xml:space="preserve">4.59417057037354</t>
   </si>
   <si>
     <t xml:space="preserve">4.67017698287964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71240282058716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61528348922729</t>
+    <t xml:space="preserve">4.71240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61528301239014</t>
   </si>
   <si>
     <t xml:space="preserve">4.62795114517212</t>
@@ -3359,22 +3359,22 @@
     <t xml:space="preserve">4.70817995071411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6617317199707</t>
+    <t xml:space="preserve">4.66173124313354</t>
   </si>
   <si>
     <t xml:space="preserve">4.53927659988403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47593832015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33659315109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31125736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42104434967041</t>
+    <t xml:space="preserve">4.47593784332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33659267425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31125688552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42104387283325</t>
   </si>
   <si>
     <t xml:space="preserve">4.29436683654785</t>
@@ -3383,22 +3383,22 @@
     <t xml:space="preserve">4.33237028121948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25636386871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39148616790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41259908676147</t>
+    <t xml:space="preserve">4.25636339187622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39148569107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41259956359863</t>
   </si>
   <si>
     <t xml:space="preserve">4.4041543006897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32392501831055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35770511627197</t>
+    <t xml:space="preserve">4.32392454147339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35770559310913</t>
   </si>
   <si>
     <t xml:space="preserve">4.3197021484375</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">4.03341102600098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12630796432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22680521011353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1009726524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03678941726685</t>
+    <t xml:space="preserve">4.12630844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22680616378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10097217559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.036789894104</t>
   </si>
   <si>
     <t xml:space="preserve">4.02834415435791</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">3.88984346389771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84761738777161</t>
+    <t xml:space="preserve">3.84761762619019</t>
   </si>
   <si>
     <t xml:space="preserve">3.97091674804688</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">4.09421634674072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01483249664307</t>
+    <t xml:space="preserve">4.01483201980591</t>
   </si>
   <si>
     <t xml:space="preserve">4.15333271026611</t>
@@ -3491,13 +3491,13 @@
     <t xml:space="preserve">4.68706703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80952167510986</t>
+    <t xml:space="preserve">4.80952215194702</t>
   </si>
   <si>
     <t xml:space="preserve">4.75462818145752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73351526260376</t>
+    <t xml:space="preserve">4.73351573944092</t>
   </si>
   <si>
     <t xml:space="preserve">4.75040578842163</t>
@@ -3506,22 +3506,22 @@
     <t xml:space="preserve">4.76307344436646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7672963142395</t>
+    <t xml:space="preserve">4.76729583740234</t>
   </si>
   <si>
     <t xml:space="preserve">4.75885105133057</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74618291854858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55194473266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53083086013794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4801607131958</t>
+    <t xml:space="preserve">4.74618339538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55194425582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5308313369751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48016023635864</t>
   </si>
   <si>
     <t xml:space="preserve">4.42948913574219</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">4.51394081115723</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56883478164673</t>
+    <t xml:space="preserve">4.56883430480957</t>
   </si>
   <si>
     <t xml:space="preserve">4.78418684005737</t>
@@ -3548,10 +3548,10 @@
     <t xml:space="preserve">4.58994770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52238607406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62372875213623</t>
+    <t xml:space="preserve">4.52238655090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62372827529907</t>
   </si>
   <si>
     <t xml:space="preserve">4.48438310623169</t>
@@ -3563,16 +3563,16 @@
     <t xml:space="preserve">4.35348320007324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4252667427063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47171545028687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56038999557495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90241861343384</t>
+    <t xml:space="preserve">4.42526626586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47171497344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56038951873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90241813659668</t>
   </si>
   <si>
     <t xml:space="preserve">4.97842502593994</t>
@@ -3590,10 +3590,10 @@
     <t xml:space="preserve">4.99109268188477</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09243535995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01220607757568</t>
+    <t xml:space="preserve">5.09243488311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01220560073853</t>
   </si>
   <si>
     <t xml:space="preserve">4.98687028884888</t>
@@ -3611,10 +3611,10 @@
     <t xml:space="preserve">4.86019325256348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94042205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93619918823242</t>
+    <t xml:space="preserve">4.94042158126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93619966506958</t>
   </si>
   <si>
     <t xml:space="preserve">4.96575784683228</t>
@@ -3623,28 +3623,28 @@
     <t xml:space="preserve">4.96153497695923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00376129150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96998023986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83907985687256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88975095748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82535886764526</t>
+    <t xml:space="preserve">5.00376081466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96998071670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83908033370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88975143432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82535934448242</t>
   </si>
   <si>
     <t xml:space="preserve">4.82981061935425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66955852508545</t>
+    <t xml:space="preserve">4.75858783721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66955900192261</t>
   </si>
   <si>
     <t xml:space="preserve">4.71852493286133</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">4.78529596328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90993595123291</t>
+    <t xml:space="preserve">4.90993642807007</t>
   </si>
   <si>
     <t xml:space="preserve">4.95890283584595</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">4.93219375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9678053855896</t>
+    <t xml:space="preserve">4.96780490875244</t>
   </si>
   <si>
     <t xml:space="preserve">4.9989652633667</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">4.99006223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.869873046875</t>
+    <t xml:space="preserve">4.86987352371216</t>
   </si>
   <si>
     <t xml:space="preserve">4.95445108413696</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">4.88322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87432527542114</t>
+    <t xml:space="preserve">4.87432479858398</t>
   </si>
   <si>
     <t xml:space="preserve">4.80755376815796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75413608551025</t>
+    <t xml:space="preserve">4.75413656234741</t>
   </si>
   <si>
     <t xml:space="preserve">4.85206747055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63839912414551</t>
+    <t xml:space="preserve">4.63839864730835</t>
   </si>
   <si>
     <t xml:space="preserve">4.60278749465942</t>
@@ -3716,19 +3716,19 @@
     <t xml:space="preserve">4.70517015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69626760482788</t>
+    <t xml:space="preserve">4.69626712799072</t>
   </si>
   <si>
     <t xml:space="preserve">4.68291330337524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74523305892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76303911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77194213867188</t>
+    <t xml:space="preserve">4.7452335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76303863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77194166183472</t>
   </si>
   <si>
     <t xml:space="preserve">4.71407318115234</t>
@@ -3746,25 +3746,25 @@
     <t xml:space="preserve">4.57607841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55382108688354</t>
+    <t xml:space="preserve">4.5538215637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.53156423568726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59388399124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64730167388916</t>
+    <t xml:space="preserve">4.59388446807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.647301197052</t>
   </si>
   <si>
     <t xml:space="preserve">4.66510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6161413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54936981201172</t>
+    <t xml:space="preserve">4.61614179611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54937028884888</t>
   </si>
   <si>
     <t xml:space="preserve">4.50485563278198</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">4.500403881073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49595308303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48705005645752</t>
+    <t xml:space="preserve">4.49595260620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48704957962036</t>
   </si>
   <si>
     <t xml:space="preserve">4.70071887969971</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">4.73187923431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72297620773315</t>
+    <t xml:space="preserve">4.722975730896</t>
   </si>
   <si>
     <t xml:space="preserve">4.44609642028809</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">4.24489164352417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28228378295898</t>
+    <t xml:space="preserve">4.28228330612183</t>
   </si>
   <si>
     <t xml:space="preserve">4.31789493560791</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">4.34282302856445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41226530075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4354133605957</t>
+    <t xml:space="preserve">4.41226577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43541288375854</t>
   </si>
   <si>
     <t xml:space="preserve">4.42829084396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3926796913147</t>
+    <t xml:space="preserve">4.39267921447754</t>
   </si>
   <si>
     <t xml:space="preserve">4.45588970184326</t>
@@ -3857,22 +3857,22 @@
     <t xml:space="preserve">4.30186986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25201368331909</t>
+    <t xml:space="preserve">4.25201416015625</t>
   </si>
   <si>
     <t xml:space="preserve">4.26625823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27694177627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20928001403809</t>
+    <t xml:space="preserve">4.27694225311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20928049087524</t>
   </si>
   <si>
     <t xml:space="preserve">4.19147443771362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21996355056763</t>
+    <t xml:space="preserve">4.21996307373047</t>
   </si>
   <si>
     <t xml:space="preserve">4.27160024642944</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">4.30899238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3054313659668</t>
+    <t xml:space="preserve">4.30543088912964</t>
   </si>
   <si>
     <t xml:space="preserve">4.39445972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40336275100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47369527816772</t>
+    <t xml:space="preserve">4.40336322784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47369575500488</t>
   </si>
   <si>
     <t xml:space="preserve">4.49150133132935</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">4.46034145355225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43185234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5226616859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47814702987671</t>
+    <t xml:space="preserve">4.43185186386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52266120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47814750671387</t>
   </si>
   <si>
     <t xml:space="preserve">4.56717586517334</t>
@@ -3944,22 +3944,22 @@
     <t xml:space="preserve">4.61169004440308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5983362197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55827283859253</t>
+    <t xml:space="preserve">4.59833574295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55827236175537</t>
   </si>
   <si>
     <t xml:space="preserve">4.58053016662598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56272459030151</t>
+    <t xml:space="preserve">4.56272411346436</t>
   </si>
   <si>
     <t xml:space="preserve">4.5849814414978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54046678543091</t>
+    <t xml:space="preserve">4.54046726226807</t>
   </si>
   <si>
     <t xml:space="preserve">4.51375865936279</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">4.6918158531189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74968433380127</t>
+    <t xml:space="preserve">4.74968481063843</t>
   </si>
   <si>
     <t xml:space="preserve">4.4692440032959</t>
@@ -3998,16 +3998,16 @@
     <t xml:space="preserve">4.44787693023682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57162761688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79419898986816</t>
+    <t xml:space="preserve">4.57162714004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79419946670532</t>
   </si>
   <si>
     <t xml:space="preserve">4.80310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82090759277344</t>
+    <t xml:space="preserve">4.8209080696106</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
@@ -4128,9 +4128,6 @@
   </si>
   <si>
     <t xml:space="preserve">4.52464294433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54170989990234</t>
   </si>
   <si>
     <t xml:space="preserve">4.53602123260498</t>
@@ -56168,7 +56165,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G1957" t="s">
-        <v>1372</v>
+        <v>576</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -56194,7 +56191,7 @@
         <v>4.78399991989136</v>
       </c>
       <c r="G1958" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -56246,7 +56243,7 @@
         <v>4.7960000038147</v>
       </c>
       <c r="G1960" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -56298,7 +56295,7 @@
         <v>4.84600019454956</v>
       </c>
       <c r="G1962" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -56324,7 +56321,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1963" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -56350,7 +56347,7 @@
         <v>4.97399997711182</v>
       </c>
       <c r="G1964" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -56376,7 +56373,7 @@
         <v>4.92799997329712</v>
       </c>
       <c r="G1965" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -56402,7 +56399,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G1966" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -56428,7 +56425,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G1967" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -56454,7 +56451,7 @@
         <v>4.93800020217896</v>
       </c>
       <c r="G1968" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -56480,7 +56477,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G1969" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -56506,7 +56503,7 @@
         <v>4.95800018310547</v>
       </c>
       <c r="G1970" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -56532,7 +56529,7 @@
         <v>4.82600021362305</v>
       </c>
       <c r="G1971" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56558,7 +56555,7 @@
         <v>4.80399990081787</v>
       </c>
       <c r="G1972" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -56584,7 +56581,7 @@
         <v>4.87799978256226</v>
       </c>
       <c r="G1973" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -56610,7 +56607,7 @@
         <v>4.89200019836426</v>
       </c>
       <c r="G1974" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -56636,7 +56633,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G1975" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -56662,7 +56659,7 @@
         <v>4.90399980545044</v>
       </c>
       <c r="G1976" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -56688,7 +56685,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G1977" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -56714,7 +56711,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1978" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -56792,7 +56789,7 @@
         <v>4.98400020599365</v>
       </c>
       <c r="G1981" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -56818,7 +56815,7 @@
         <v>4.98199987411499</v>
       </c>
       <c r="G1982" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -56844,7 +56841,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G1983" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -56870,7 +56867,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1984" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56896,7 +56893,7 @@
         <v>5.03499984741211</v>
       </c>
       <c r="G1985" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56922,7 +56919,7 @@
         <v>5.04500007629395</v>
       </c>
       <c r="G1986" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56948,7 +56945,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1987" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -57000,7 +56997,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G1989" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -57026,7 +57023,7 @@
         <v>5.07000017166138</v>
       </c>
       <c r="G1990" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -57052,7 +57049,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1991" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -57078,7 +57075,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G1992" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -57104,7 +57101,7 @@
         <v>5.16499996185303</v>
       </c>
       <c r="G1993" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -57130,7 +57127,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G1994" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -57156,7 +57153,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G1995" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -57182,7 +57179,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G1996" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -57208,7 +57205,7 @@
         <v>5.21500015258789</v>
       </c>
       <c r="G1997" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -57234,7 +57231,7 @@
         <v>5.20499992370605</v>
       </c>
       <c r="G1998" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -57260,7 +57257,7 @@
         <v>5.25500011444092</v>
       </c>
       <c r="G1999" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57286,7 +57283,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G2000" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57312,7 +57309,7 @@
         <v>5.35500001907349</v>
       </c>
       <c r="G2001" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -57338,7 +57335,7 @@
         <v>5.34999990463257</v>
       </c>
       <c r="G2002" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -57364,7 +57361,7 @@
         <v>5.33500003814697</v>
       </c>
       <c r="G2003" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -57390,7 +57387,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2004" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -57416,7 +57413,7 @@
         <v>5.44999980926514</v>
       </c>
       <c r="G2005" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -57442,7 +57439,7 @@
         <v>5.41499996185303</v>
       </c>
       <c r="G2006" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -57468,7 +57465,7 @@
         <v>5.39499998092651</v>
       </c>
       <c r="G2007" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -57494,7 +57491,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2008" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -57520,7 +57517,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G2009" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -57546,7 +57543,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2010" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -57572,7 +57569,7 @@
         <v>5.5</v>
       </c>
       <c r="G2011" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -57598,7 +57595,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2012" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -57624,7 +57621,7 @@
         <v>5.36499977111816</v>
       </c>
       <c r="G2013" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -57650,7 +57647,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2014" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -57676,7 +57673,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2015" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -57702,7 +57699,7 @@
         <v>5.6100001335144</v>
       </c>
       <c r="G2016" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -57728,7 +57725,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G2017" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -57754,7 +57751,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G2018" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -57780,7 +57777,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2019" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57806,7 +57803,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G2020" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -57832,7 +57829,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2021" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -57858,7 +57855,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G2022" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -57884,7 +57881,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2023" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57910,7 +57907,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G2024" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57936,7 +57933,7 @@
         <v>5.875</v>
       </c>
       <c r="G2025" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57962,7 +57959,7 @@
         <v>5.79500007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57988,7 +57985,7 @@
         <v>5.81500005722046</v>
       </c>
       <c r="G2027" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -58014,7 +58011,7 @@
         <v>5.73000001907349</v>
       </c>
       <c r="G2028" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -58040,7 +58037,7 @@
         <v>5.7350001335144</v>
       </c>
       <c r="G2029" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -58066,7 +58063,7 @@
         <v>5.78499984741211</v>
       </c>
       <c r="G2030" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -58092,7 +58089,7 @@
         <v>5.71000003814697</v>
       </c>
       <c r="G2031" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -58118,7 +58115,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2032" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -58144,7 +58141,7 @@
         <v>5.625</v>
       </c>
       <c r="G2033" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -58170,7 +58167,7 @@
         <v>5.65500020980835</v>
       </c>
       <c r="G2034" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -58196,7 +58193,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2035" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58222,7 +58219,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2036" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58248,7 +58245,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2037" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58274,7 +58271,7 @@
         <v>5.5149998664856</v>
       </c>
       <c r="G2038" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58300,7 +58297,7 @@
         <v>5.53000020980835</v>
       </c>
       <c r="G2039" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58326,7 +58323,7 @@
         <v>5.57499980926514</v>
       </c>
       <c r="G2040" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -58352,7 +58349,7 @@
         <v>5.5</v>
       </c>
       <c r="G2041" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -58378,7 +58375,7 @@
         <v>5.50500011444092</v>
       </c>
       <c r="G2042" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -58404,7 +58401,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2043" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -58430,7 +58427,7 @@
         <v>5.59499979019165</v>
       </c>
       <c r="G2044" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58456,7 +58453,7 @@
         <v>5.60500001907349</v>
       </c>
       <c r="G2045" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -58482,7 +58479,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G2046" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -58508,7 +58505,7 @@
         <v>5.53499984741211</v>
       </c>
       <c r="G2047" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58534,7 +58531,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2048" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -58560,7 +58557,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G2049" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -58586,7 +58583,7 @@
         <v>5.68499994277954</v>
       </c>
       <c r="G2050" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -58612,7 +58609,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2051" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -58638,7 +58635,7 @@
         <v>5.64499998092651</v>
       </c>
       <c r="G2052" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -58664,7 +58661,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2053" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -58690,7 +58687,7 @@
         <v>5.67500019073486</v>
       </c>
       <c r="G2054" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -58716,7 +58713,7 @@
         <v>5.55499982833862</v>
       </c>
       <c r="G2055" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -58742,7 +58739,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G2056" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -58768,7 +58765,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G2057" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -58794,7 +58791,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G2058" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -58820,7 +58817,7 @@
         <v>5.55000019073486</v>
       </c>
       <c r="G2059" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -58846,7 +58843,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G2060" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -58872,7 +58869,7 @@
         <v>5.4850001335144</v>
       </c>
       <c r="G2061" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58898,7 +58895,7 @@
         <v>5.46999979019165</v>
       </c>
       <c r="G2062" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58924,7 +58921,7 @@
         <v>5.44500017166138</v>
       </c>
       <c r="G2063" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58950,7 +58947,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2064" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58976,7 +58973,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2065" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -59002,7 +58999,7 @@
         <v>5.42500019073486</v>
       </c>
       <c r="G2066" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -59028,7 +59025,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2067" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -59054,7 +59051,7 @@
         <v>5.28999996185303</v>
       </c>
       <c r="G2068" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -59080,7 +59077,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2069" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -59106,7 +59103,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2070" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -59132,7 +59129,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2071" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -59158,7 +59155,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2072" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -59184,7 +59181,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G2073" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -59210,7 +59207,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G2074" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -59236,7 +59233,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G2075" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -59262,7 +59259,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2076" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59288,7 +59285,7 @@
         <v>5.40999984741211</v>
       </c>
       <c r="G2077" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59314,7 +59311,7 @@
         <v>5.46500015258789</v>
       </c>
       <c r="G2078" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -59340,7 +59337,7 @@
         <v>5.40500020980835</v>
       </c>
       <c r="G2079" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -59366,7 +59363,7 @@
         <v>5.375</v>
       </c>
       <c r="G2080" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -59392,7 +59389,7 @@
         <v>5.36999988555908</v>
       </c>
       <c r="G2081" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -59418,7 +59415,7 @@
         <v>5.47499990463257</v>
       </c>
       <c r="G2082" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59444,7 +59441,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G2083" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -59470,7 +59467,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2084" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -59496,7 +59493,7 @@
         <v>5.52500009536743</v>
       </c>
       <c r="G2085" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59522,7 +59519,7 @@
         <v>5.625</v>
       </c>
       <c r="G2086" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -59548,7 +59545,7 @@
         <v>5.58500003814697</v>
       </c>
       <c r="G2087" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -59574,7 +59571,7 @@
         <v>5.63000011444092</v>
       </c>
       <c r="G2088" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -59600,7 +59597,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G2089" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -59626,7 +59623,7 @@
         <v>5.63500022888184</v>
       </c>
       <c r="G2090" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -59652,7 +59649,7 @@
         <v>5.70499992370605</v>
       </c>
       <c r="G2091" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -59678,7 +59675,7 @@
         <v>5.69000005722046</v>
       </c>
       <c r="G2092" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -59704,7 +59701,7 @@
         <v>5.77500009536743</v>
       </c>
       <c r="G2093" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -59730,7 +59727,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2094" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -59756,7 +59753,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G2095" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -59782,7 +59779,7 @@
         <v>5.74499988555908</v>
       </c>
       <c r="G2096" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -59808,7 +59805,7 @@
         <v>5.80999994277954</v>
       </c>
       <c r="G2097" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -59834,7 +59831,7 @@
         <v>5.76999998092651</v>
       </c>
       <c r="G2098" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -59860,7 +59857,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2099" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59886,7 +59883,7 @@
         <v>5.85500001907349</v>
       </c>
       <c r="G2100" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59912,7 +59909,7 @@
         <v>5.875</v>
       </c>
       <c r="G2101" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59938,7 +59935,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G2102" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59964,7 +59961,7 @@
         <v>6.03499984741211</v>
       </c>
       <c r="G2103" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59990,7 +59987,7 @@
         <v>5.93499994277954</v>
       </c>
       <c r="G2104" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -60016,7 +60013,7 @@
         <v>5.90500020980835</v>
       </c>
       <c r="G2105" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -60042,7 +60039,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G2106" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -60068,7 +60065,7 @@
         <v>5.90999984741211</v>
       </c>
       <c r="G2107" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -60094,7 +60091,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G2108" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -60120,7 +60117,7 @@
         <v>5.92500019073486</v>
       </c>
       <c r="G2109" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -60146,7 +60143,7 @@
         <v>6.03000020980835</v>
       </c>
       <c r="G2110" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -60172,7 +60169,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G2111" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -60198,7 +60195,7 @@
         <v>6.17500019073486</v>
       </c>
       <c r="G2112" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -60224,7 +60221,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G2113" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -60250,7 +60247,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G2114" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60276,7 +60273,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G2115" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60302,7 +60299,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G2116" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -60328,7 +60325,7 @@
         <v>6.00500011444092</v>
       </c>
       <c r="G2117" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -60354,7 +60351,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G2118" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -60380,7 +60377,7 @@
         <v>6.08500003814697</v>
       </c>
       <c r="G2119" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -60406,7 +60403,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G2120" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -60432,7 +60429,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G2121" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60458,7 +60455,7 @@
         <v>6.09499979019165</v>
       </c>
       <c r="G2122" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60484,7 +60481,7 @@
         <v>6.15500020980835</v>
       </c>
       <c r="G2123" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60510,7 +60507,7 @@
         <v>6.125</v>
       </c>
       <c r="G2124" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -60536,7 +60533,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G2125" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -60562,7 +60559,7 @@
         <v>6.21500015258789</v>
       </c>
       <c r="G2126" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -60588,7 +60585,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G2127" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -60614,7 +60611,7 @@
         <v>6.35500001907349</v>
       </c>
       <c r="G2128" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -60640,7 +60637,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G2129" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -60666,7 +60663,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G2130" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -60692,7 +60689,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G2131" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -60718,7 +60715,7 @@
         <v>6.45499992370605</v>
       </c>
       <c r="G2132" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -60744,7 +60741,7 @@
         <v>6.46500015258789</v>
       </c>
       <c r="G2133" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -60770,7 +60767,7 @@
         <v>6.60500001907349</v>
       </c>
       <c r="G2134" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -60796,7 +60793,7 @@
         <v>6.63500022888184</v>
       </c>
       <c r="G2135" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -60822,7 +60819,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G2136" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -60848,7 +60845,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G2137" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -60874,7 +60871,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G2138" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60900,7 +60897,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G2139" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60926,7 +60923,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2140" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60952,7 +60949,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G2141" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60978,7 +60975,7 @@
         <v>6.43499994277954</v>
       </c>
       <c r="G2142" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -61004,7 +61001,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G2143" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -61030,7 +61027,7 @@
         <v>6.56500005722046</v>
       </c>
       <c r="G2144" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -61056,7 +61053,7 @@
         <v>6.68499994277954</v>
       </c>
       <c r="G2145" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -61082,7 +61079,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G2146" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -61108,7 +61105,7 @@
         <v>6.89499998092651</v>
       </c>
       <c r="G2147" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -61134,7 +61131,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2148" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -61160,7 +61157,7 @@
         <v>7.09499979019165</v>
       </c>
       <c r="G2149" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -61186,7 +61183,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G2150" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -61212,7 +61209,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G2151" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -61238,7 +61235,7 @@
         <v>7.06500005722046</v>
       </c>
       <c r="G2152" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -61264,7 +61261,7 @@
         <v>7.13500022888184</v>
       </c>
       <c r="G2153" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61290,7 +61287,7 @@
         <v>7.19000005722046</v>
       </c>
       <c r="G2154" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61316,7 +61313,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2155" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -61342,7 +61339,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2156" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -61368,7 +61365,7 @@
         <v>7.21000003814697</v>
       </c>
       <c r="G2157" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -61394,7 +61391,7 @@
         <v>7.17000007629395</v>
       </c>
       <c r="G2158" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -61420,7 +61417,7 @@
         <v>7.26999998092651</v>
       </c>
       <c r="G2159" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61446,7 +61443,7 @@
         <v>7.28499984741211</v>
       </c>
       <c r="G2160" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61472,7 +61469,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2161" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61498,7 +61495,7 @@
         <v>7.1100001335144</v>
       </c>
       <c r="G2162" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61524,7 +61521,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2163" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -61550,7 +61547,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2164" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -61576,7 +61573,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G2165" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -61602,7 +61599,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G2166" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -61628,7 +61625,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2167" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -61654,7 +61651,7 @@
         <v>7.05499982833862</v>
       </c>
       <c r="G2168" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -61680,7 +61677,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G2169" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -61706,7 +61703,7 @@
         <v>7.14499998092651</v>
       </c>
       <c r="G2170" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -61732,7 +61729,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G2171" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -61758,7 +61755,7 @@
         <v>6.72816181182861</v>
       </c>
       <c r="G2172" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -61784,7 +61781,7 @@
         <v>6.69060087203979</v>
       </c>
       <c r="G2173" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -61810,7 +61807,7 @@
         <v>6.66712522506714</v>
       </c>
       <c r="G2174" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61836,7 +61833,7 @@
         <v>6.61547899246216</v>
       </c>
       <c r="G2175" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -61862,7 +61859,7 @@
         <v>6.78919982910156</v>
       </c>
       <c r="G2176" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61888,7 +61885,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G2177" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61914,7 +61911,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G2178" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61940,7 +61937,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2179" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61966,7 +61963,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G2180" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61992,7 +61989,7 @@
         <v>6.82499980926514</v>
       </c>
       <c r="G2181" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -62018,7 +62015,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G2182" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -62044,7 +62041,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G2183" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -62070,7 +62067,7 @@
         <v>6.91499996185303</v>
       </c>
       <c r="G2184" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -62096,7 +62093,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G2185" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -62122,7 +62119,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G2186" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -62148,7 +62145,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2187" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -62174,7 +62171,7 @@
         <v>6.9850001335144</v>
       </c>
       <c r="G2188" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -62200,7 +62197,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2189" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62226,7 +62223,7 @@
         <v>6.96500015258789</v>
       </c>
       <c r="G2190" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62252,7 +62249,7 @@
         <v>7</v>
       </c>
       <c r="G2191" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62278,7 +62275,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2192" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62304,7 +62301,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2193" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62330,7 +62327,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G2194" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62356,7 +62353,7 @@
         <v>7.18499994277954</v>
       </c>
       <c r="G2195" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62382,7 +62379,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2196" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62408,7 +62405,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2197" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62434,7 +62431,7 @@
         <v>7.23000001907349</v>
       </c>
       <c r="G2198" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62460,7 +62457,7 @@
         <v>7.08500003814697</v>
       </c>
       <c r="G2199" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62486,7 +62483,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2200" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62512,7 +62509,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G2201" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62538,7 +62535,7 @@
         <v>6.95499992370605</v>
       </c>
       <c r="G2202" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62564,7 +62561,7 @@
         <v>6.92500019073486</v>
       </c>
       <c r="G2203" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -62590,7 +62587,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2204" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -62616,7 +62613,7 @@
         <v>6.86999988555908</v>
       </c>
       <c r="G2205" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -62642,7 +62639,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2206" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -62668,7 +62665,7 @@
         <v>6.97499990463257</v>
       </c>
       <c r="G2207" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -62694,7 +62691,7 @@
         <v>6.88500022888184</v>
       </c>
       <c r="G2208" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -62720,7 +62717,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G2209" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62746,7 +62743,7 @@
         <v>7.07499980926514</v>
       </c>
       <c r="G2210" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62772,7 +62769,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2211" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -62798,7 +62795,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G2212" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62824,7 +62821,7 @@
         <v>7.25</v>
       </c>
       <c r="G2213" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -62850,7 +62847,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G2214" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -62876,7 +62873,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G2215" t="s">
-        <v>1574</v>
+        <v>1573</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62902,7 +62899,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G2216" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62928,7 +62925,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2217" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62954,7 +62951,7 @@
         <v>7.27500009536743</v>
       </c>
       <c r="G2218" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -62980,7 +62977,7 @@
         <v>7.25500011444092</v>
       </c>
       <c r="G2219" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -63006,7 +63003,7 @@
         <v>7.24499988555908</v>
       </c>
       <c r="G2220" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -63032,7 +63029,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G2221" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -63058,7 +63055,7 @@
         <v>7.34999990463257</v>
       </c>
       <c r="G2222" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -63084,7 +63081,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2223" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -63110,7 +63107,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2224" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -63136,7 +63133,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2225" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -63162,7 +63159,7 @@
         <v>7.30499982833862</v>
       </c>
       <c r="G2226" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -63188,7 +63185,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G2227" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -63214,7 +63211,7 @@
         <v>7.38500022888184</v>
       </c>
       <c r="G2228" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63240,7 +63237,7 @@
         <v>7.46500015258789</v>
       </c>
       <c r="G2229" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63266,7 +63263,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2230" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63292,7 +63289,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G2231" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63318,7 +63315,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2232" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63344,7 +63341,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2233" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63370,7 +63367,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G2234" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63396,7 +63393,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G2235" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63422,7 +63419,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G2236" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63448,7 +63445,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G2237" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63474,7 +63471,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G2238" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63500,7 +63497,7 @@
         <v>7.7350001335144</v>
       </c>
       <c r="G2239" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63526,7 +63523,7 @@
         <v>7.68499994277954</v>
       </c>
       <c r="G2240" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63552,7 +63549,7 @@
         <v>7.64499998092651</v>
       </c>
       <c r="G2241" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63578,7 +63575,7 @@
         <v>7.55499982833862</v>
       </c>
       <c r="G2242" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -63604,7 +63601,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2243" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -63630,7 +63627,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G2244" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -63656,7 +63653,7 @@
         <v>7.625</v>
       </c>
       <c r="G2245" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -63682,7 +63679,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G2246" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -63708,7 +63705,7 @@
         <v>7.58500003814697</v>
       </c>
       <c r="G2247" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -63734,7 +63731,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2248" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63760,7 +63757,7 @@
         <v>7.625</v>
       </c>
       <c r="G2249" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63786,7 +63783,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G2250" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63812,7 +63809,7 @@
         <v>7.6100001335144</v>
       </c>
       <c r="G2251" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63838,7 +63835,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G2252" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63864,7 +63861,7 @@
         <v>7.42999982833862</v>
       </c>
       <c r="G2253" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63890,7 +63887,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G2254" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63916,7 +63913,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2255" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63942,7 +63939,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G2256" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63968,7 +63965,7 @@
         <v>7.69000005722046</v>
       </c>
       <c r="G2257" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63994,7 +63991,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G2258" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -64020,7 +64017,7 @@
         <v>7.63500022888184</v>
       </c>
       <c r="G2259" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -64046,7 +64043,7 @@
         <v>7.69500017166138</v>
       </c>
       <c r="G2260" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -64072,7 +64069,7 @@
         <v>7.71500015258789</v>
       </c>
       <c r="G2261" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -64098,7 +64095,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G2262" t="s">
-        <v>1613</v>
+        <v>1612</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -64124,7 +64121,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G2263" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -64150,7 +64147,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G2264" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -64176,7 +64173,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G2265" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -64202,7 +64199,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G2266" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64228,7 +64225,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G2267" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64254,7 +64251,7 @@
         <v>8.01500034332275</v>
       </c>
       <c r="G2268" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64280,7 +64277,7 @@
         <v>8.11499977111816</v>
       </c>
       <c r="G2269" t="s">
-        <v>1620</v>
+        <v>1619</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64306,7 +64303,7 @@
         <v>8.22500038146973</v>
       </c>
       <c r="G2270" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64332,7 +64329,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2271" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64358,7 +64355,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G2272" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64384,7 +64381,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G2273" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64410,7 +64407,7 @@
         <v>8.39500045776367</v>
       </c>
       <c r="G2274" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64436,7 +64433,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G2275" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64462,7 +64459,7 @@
         <v>8.45499992370605</v>
       </c>
       <c r="G2276" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64488,7 +64485,7 @@
         <v>8.59000015258789</v>
       </c>
       <c r="G2277" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64514,7 +64511,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G2278" t="s">
-        <v>1629</v>
+        <v>1628</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64540,7 +64537,7 @@
         <v>8.72500038146973</v>
       </c>
       <c r="G2279" t="s">
-        <v>1630</v>
+        <v>1629</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -64566,7 +64563,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2280" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64592,7 +64589,7 @@
         <v>8.76500034332275</v>
       </c>
       <c r="G2281" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64618,7 +64615,7 @@
         <v>8.875</v>
       </c>
       <c r="G2282" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -64644,7 +64641,7 @@
         <v>8.86999988555908</v>
       </c>
       <c r="G2283" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64670,7 +64667,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G2284" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64696,7 +64693,7 @@
         <v>9.09000015258789</v>
       </c>
       <c r="G2285" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -64722,7 +64719,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G2286" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64748,7 +64745,7 @@
         <v>9.33500003814697</v>
       </c>
       <c r="G2287" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -64774,7 +64771,7 @@
         <v>9.28499984741211</v>
       </c>
       <c r="G2288" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64800,7 +64797,7 @@
         <v>9.27999973297119</v>
       </c>
       <c r="G2289" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64826,7 +64823,7 @@
         <v>9.27499961853027</v>
       </c>
       <c r="G2290" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64852,7 +64849,7 @@
         <v>9.36999988555908</v>
       </c>
       <c r="G2291" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -64878,7 +64875,7 @@
         <v>9.40499973297119</v>
       </c>
       <c r="G2292" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64904,7 +64901,7 @@
         <v>9.29500007629395</v>
       </c>
       <c r="G2293" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64930,7 +64927,7 @@
         <v>9.3149995803833</v>
       </c>
       <c r="G2294" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64956,7 +64953,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G2295" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64964,7 +64961,7 @@
     </row>
     <row r="2296">
       <c r="A2296" s="1" t="n">
-        <v>45978.6910763889</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2296" t="n">
         <v>2255148</v>
@@ -64982,9 +64979,35 @@
         <v>9.4350004196167</v>
       </c>
       <c r="G2296" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
       <c r="H2296" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" s="1" t="n">
+        <v>45979.6910185185</v>
+      </c>
+      <c r="B2297" t="n">
+        <v>2465326</v>
+      </c>
+      <c r="C2297" t="n">
+        <v>9.4399995803833</v>
+      </c>
+      <c r="D2297" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="E2297" t="n">
+        <v>9.34000015258789</v>
+      </c>
+      <c r="F2297" t="n">
+        <v>9.4350004196167</v>
+      </c>
+      <c r="G2297" t="s">
+        <v>1646</v>
+      </c>
+      <c r="H2297" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1647" uniqueCount="1647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="1648">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,79 +38,79 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58873558044434</t>
+    <t xml:space="preserve">2.58873581886292</t>
   </si>
   <si>
     <t xml:space="preserve">IG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5013575553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32790589332581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16488718986511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17271208763123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09315896034241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06185913085938</t>
+    <t xml:space="preserve">2.50135779380798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32790613174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16488695144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1727123260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09315872192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06185936927795</t>
   </si>
   <si>
     <t xml:space="preserve">2.08663845062256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04490566253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06055521965027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04360127449036</t>
+    <t xml:space="preserve">2.04490542411804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06055545806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04360151290894</t>
   </si>
   <si>
     <t xml:space="preserve">2.10489630699158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12967538833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14532494544983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17923283576965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20009922981262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20140314102173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17792868614197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13228368759155</t>
+    <t xml:space="preserve">2.1296751499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14532518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1792323589325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2000994682312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20140337944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17792844772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13228321075439</t>
   </si>
   <si>
     <t xml:space="preserve">2.09837579727173</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22357392311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29138994216919</t>
+    <t xml:space="preserve">2.22357416152954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29138970375061</t>
   </si>
   <si>
     <t xml:space="preserve">2.33181834220886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29791069030762</t>
+    <t xml:space="preserve">2.29791045188904</t>
   </si>
   <si>
     <t xml:space="preserve">2.2379195690155</t>
@@ -119,124 +119,124 @@
     <t xml:space="preserve">2.30051875114441</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30443120002747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37094283103943</t>
+    <t xml:space="preserve">2.30443096160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37094259262085</t>
   </si>
   <si>
     <t xml:space="preserve">2.34616422653198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39572167396545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45571231842041</t>
+    <t xml:space="preserve">2.39572143554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45571255683899</t>
   </si>
   <si>
     <t xml:space="preserve">2.39702582359314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38007187843323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39441728591919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42180418968201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41006731987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43093347549438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43745446205139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48701190948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45049571990967</t>
+    <t xml:space="preserve">2.38007164001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39441752433777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42180442810059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41006708145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43093371391296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43745422363281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48701214790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45049595832825</t>
   </si>
   <si>
     <t xml:space="preserve">2.4909245967865</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4452793598175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46614551544189</t>
+    <t xml:space="preserve">2.44527912139893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46614575386047</t>
   </si>
   <si>
     <t xml:space="preserve">2.43223786354065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44006299972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47788310050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43615007400513</t>
+    <t xml:space="preserve">2.44006252288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47788286209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43615031242371</t>
   </si>
   <si>
     <t xml:space="preserve">2.43354201316833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45701670646667</t>
+    <t xml:space="preserve">2.4570164680481</t>
   </si>
   <si>
     <t xml:space="preserve">2.48831629753113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41789221763611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43484616279602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41267561912537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35659718513489</t>
+    <t xml:space="preserve">2.41789245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43484592437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41267538070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35659694671631</t>
   </si>
   <si>
     <t xml:space="preserve">2.27573990821838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29530191421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.312255859375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38137578964233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40876317024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39311337471008</t>
+    <t xml:space="preserve">2.29530239105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31225609779358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38137602806091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40876293182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3931131362915</t>
   </si>
   <si>
     <t xml:space="preserve">2.44919157028198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46744990348816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47397017478943</t>
+    <t xml:space="preserve">2.46744966506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47397065162659</t>
   </si>
   <si>
     <t xml:space="preserve">2.48440361022949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46353721618652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47266626358032</t>
+    <t xml:space="preserve">2.4635374546051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4726665019989</t>
   </si>
   <si>
     <t xml:space="preserve">2.47136211395264</t>
@@ -245,28 +245,28 @@
     <t xml:space="preserve">2.44788765907288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49614119529724</t>
+    <t xml:space="preserve">2.49614095687866</t>
   </si>
   <si>
     <t xml:space="preserve">2.49744510650635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51570320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53135299682617</t>
+    <t xml:space="preserve">2.5157036781311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53135323524475</t>
   </si>
   <si>
     <t xml:space="preserve">2.51439905166626</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53656935691833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52744054794312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54830694198608</t>
+    <t xml:space="preserve">2.53656959533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52744030952454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54830718040466</t>
   </si>
   <si>
     <t xml:space="preserve">2.55091524124146</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">2.53787398338318</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58612728118896</t>
+    <t xml:space="preserve">2.58612704277039</t>
   </si>
   <si>
     <t xml:space="preserve">2.57699823379517</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">2.60438537597656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57308578491211</t>
+    <t xml:space="preserve">2.57308602333069</t>
   </si>
   <si>
     <t xml:space="preserve">2.66959285736084</t>
@@ -299,58 +299,58 @@
     <t xml:space="preserve">2.6982843875885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64872622489929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64742207527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68133020401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67480945587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63438057899475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64350986480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69567561149597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69958853721619</t>
+    <t xml:space="preserve">2.64872646331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64742231369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68133044242859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67480969429016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63438081741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64351010322571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69567584991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69958829879761</t>
   </si>
   <si>
     <t xml:space="preserve">2.67872190475464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73480010032654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.772620677948</t>
+    <t xml:space="preserve">2.73480033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77262043952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.7543625831604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71262979507446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70089292526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7021963596344</t>
+    <t xml:space="preserve">2.71262955665588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70089268684387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70219659805298</t>
   </si>
   <si>
     <t xml:space="preserve">2.66176772117615</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7830536365509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74523329734802</t>
+    <t xml:space="preserve">2.78305411338806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7452335357666</t>
   </si>
   <si>
     <t xml:space="preserve">2.69306778907776</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">2.71915054321289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70610928535461</t>
+    <t xml:space="preserve">2.70610904693604</t>
   </si>
   <si>
     <t xml:space="preserve">2.74914598464966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77783751487732</t>
+    <t xml:space="preserve">2.77783727645874</t>
   </si>
   <si>
     <t xml:space="preserve">2.83521962165833</t>
@@ -377,25 +377,25 @@
     <t xml:space="preserve">2.88738560676575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89651489257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85347747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91477274894714</t>
+    <t xml:space="preserve">2.89651441574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85347771644592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91477251052856</t>
   </si>
   <si>
     <t xml:space="preserve">3.0086715221405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02040863037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96824288368225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00736737251282</t>
+    <t xml:space="preserve">3.02040910720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96824312210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0073676109314</t>
   </si>
   <si>
     <t xml:space="preserve">3.05822944641113</t>
@@ -404,67 +404,67 @@
     <t xml:space="preserve">3.09885358810425</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15591335296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09613680839539</t>
+    <t xml:space="preserve">3.15591311454773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09613704681396</t>
   </si>
   <si>
     <t xml:space="preserve">3.13825178146362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0907027721405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97658467292786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13417625427246</t>
+    <t xml:space="preserve">3.09070301055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97658443450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13417673110962</t>
   </si>
   <si>
     <t xml:space="preserve">3.20074534416199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24965286254883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28769278526306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23063349723816</t>
+    <t xml:space="preserve">3.24965310096741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28769254684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23063373565674</t>
   </si>
   <si>
     <t xml:space="preserve">3.24557757377625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2224817276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25101113319397</t>
+    <t xml:space="preserve">3.22248196601868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25101137161255</t>
   </si>
   <si>
     <t xml:space="preserve">3.18715977668762</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09477877616882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11379837989807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19938731193542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10428833961487</t>
+    <t xml:space="preserve">3.09477853775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11379790306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19938683509827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10428810119629</t>
   </si>
   <si>
     <t xml:space="preserve">3.12059092521667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15727210044861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16270637512207</t>
+    <t xml:space="preserve">3.15727162361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16270589828491</t>
   </si>
   <si>
     <t xml:space="preserve">3.14504480361938</t>
@@ -473,46 +473,46 @@
     <t xml:space="preserve">3.03907799720764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02820944786072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96707463264465</t>
+    <t xml:space="preserve">3.02820992469788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96707439422607</t>
   </si>
   <si>
     <t xml:space="preserve">3.00375556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03636050224304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02005839347839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.977942943573</t>
+    <t xml:space="preserve">3.03636074066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02005815505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97794270515442</t>
   </si>
   <si>
     <t xml:space="preserve">2.9860942363739</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9956042766571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.075758934021</t>
+    <t xml:space="preserve">2.99560403823853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07575845718384</t>
   </si>
   <si>
     <t xml:space="preserve">3.08390974998474</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12466621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10836410522461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12874221801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1790087223053</t>
+    <t xml:space="preserve">3.12466645240784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10836362838745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12874174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17900848388672</t>
   </si>
   <si>
     <t xml:space="preserve">3.17221546173096</t>
@@ -521,25 +521,25 @@
     <t xml:space="preserve">3.12602543830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15863013267517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2251992225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26052188873291</t>
+    <t xml:space="preserve">3.15863060951233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22519898414612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26052212715149</t>
   </si>
   <si>
     <t xml:space="preserve">3.25237035751343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27682399749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30671238899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30263710021973</t>
+    <t xml:space="preserve">3.27682447433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30671191215515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30263686180115</t>
   </si>
   <si>
     <t xml:space="preserve">3.2808997631073</t>
@@ -548,13 +548,13 @@
     <t xml:space="preserve">3.21025490760803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28361701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29856061935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28225827217102</t>
+    <t xml:space="preserve">3.2836172580719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29856109619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28225779533386</t>
   </si>
   <si>
     <t xml:space="preserve">3.26323843002319</t>
@@ -563,31 +563,31 @@
     <t xml:space="preserve">3.25644588470459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27003192901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24693608283997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23335099220276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21976494789124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24150156974792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26187968254089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2347092628479</t>
+    <t xml:space="preserve">3.27003169059753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24693632125854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23335075378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21976470947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24150133132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26188015937805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23470854759216</t>
   </si>
   <si>
     <t xml:space="preserve">3.19802856445312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23742580413818</t>
+    <t xml:space="preserve">3.23742628097534</t>
   </si>
   <si>
     <t xml:space="preserve">3.24829459190369</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">3.22791624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19395303726196</t>
+    <t xml:space="preserve">3.19395279884338</t>
   </si>
   <si>
     <t xml:space="preserve">3.16542315483093</t>
@@ -611,16 +611,16 @@
     <t xml:space="preserve">3.20753860473633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2401430606842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26731443405151</t>
+    <t xml:space="preserve">3.24014329910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26731419563293</t>
   </si>
   <si>
     <t xml:space="preserve">3.24286031723022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.226557970047</t>
+    <t xml:space="preserve">3.22655749320984</t>
   </si>
   <si>
     <t xml:space="preserve">3.2319917678833</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">3.14640331268311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16814017295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157084465027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678142547607</t>
+    <t xml:space="preserve">3.16814064979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157132148743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678166389465</t>
   </si>
   <si>
     <t xml:space="preserve">3.21704792976379</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">3.22927474975586</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24421882629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21433067321777</t>
+    <t xml:space="preserve">3.24421906471252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21433091163635</t>
   </si>
   <si>
     <t xml:space="preserve">3.25372838973999</t>
@@ -659,55 +659,55 @@
     <t xml:space="preserve">3.35154485702515</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49147510528564</t>
+    <t xml:space="preserve">3.49147534370422</t>
   </si>
   <si>
     <t xml:space="preserve">3.39365935325623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46430444717407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50506019592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41675519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40656590461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44732213020325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43373656272888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4269437789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47109699249268</t>
+    <t xml:space="preserve">3.46430420875549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50506114959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41675472259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40656542778015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44732189178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4337363243103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42694401741028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4710967540741</t>
   </si>
   <si>
     <t xml:space="preserve">3.46770048141479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48128604888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50166463851929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54242038726807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51185345649719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54581737518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55940294265747</t>
+    <t xml:space="preserve">3.48128652572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50166440010071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54242086410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51185297966003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54581713676453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55940246582031</t>
   </si>
   <si>
     <t xml:space="preserve">3.63412308692932</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">3.60015964508057</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53223180770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48468255996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55260968208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61374497413635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52543902397156</t>
+    <t xml:space="preserve">3.53223133087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48468279838562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55260992050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61374521255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52543926239014</t>
   </si>
   <si>
     <t xml:space="preserve">3.58997011184692</t>
@@ -737,37 +737,37 @@
     <t xml:space="preserve">3.60355567932129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59336638450623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62053751945496</t>
+    <t xml:space="preserve">3.59336686134338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62053775787354</t>
   </si>
   <si>
     <t xml:space="preserve">3.59676289558411</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56619548797607</t>
+    <t xml:space="preserve">3.5661952495575</t>
   </si>
   <si>
     <t xml:space="preserve">3.53562808036804</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45411491394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45751142501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39637637138367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32301497459412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38279128074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40996193885803</t>
+    <t xml:space="preserve">3.45411515235901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45751166343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39637684822083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3230152130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3827908039093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40996241569519</t>
   </si>
   <si>
     <t xml:space="preserve">3.38958382606506</t>
@@ -779,25 +779,25 @@
     <t xml:space="preserve">3.30807089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31078791618347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35018610954285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37599802017212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35426187515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37328147888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34339380264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36648797988892</t>
+    <t xml:space="preserve">3.31078815460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35018587112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3759982585907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35426163673401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37328124046326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34339332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3664882183075</t>
   </si>
   <si>
     <t xml:space="preserve">3.37871527671814</t>
@@ -806,22 +806,22 @@
     <t xml:space="preserve">3.36105442047119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12126994132996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16406488418579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06624913215637</t>
+    <t xml:space="preserve">3.12127017974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16406440734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06624865531921</t>
   </si>
   <si>
     <t xml:space="preserve">3.04587078094482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03228545188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00239658355713</t>
+    <t xml:space="preserve">3.03228497505188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00239706039429</t>
   </si>
   <si>
     <t xml:space="preserve">3.0220959186554</t>
@@ -830,28 +830,28 @@
     <t xml:space="preserve">3.02549242973328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04654979705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99424529075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96164059638977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97862243652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092622756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11651492118835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06828713417053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00035929679871</t>
+    <t xml:space="preserve">3.04655003547668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99424600601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96164083480835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97862267494202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092646598816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11651468276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06828689575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00035881996155</t>
   </si>
   <si>
     <t xml:space="preserve">2.96639537811279</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">3.01326537132263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09409880638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14300656318665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23538827896118</t>
+    <t xml:space="preserve">3.0940990447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14300680160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23538851737976</t>
   </si>
   <si>
     <t xml:space="preserve">3.2272367477417</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.21297287940979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19327354431152</t>
+    <t xml:space="preserve">3.1932737827301</t>
   </si>
   <si>
     <t xml:space="preserve">3.27342748641968</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">3.29448533058167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20414161682129</t>
+    <t xml:space="preserve">3.20414209365845</t>
   </si>
   <si>
     <t xml:space="preserve">3.30739164352417</t>
@@ -899,124 +899,124 @@
     <t xml:space="preserve">3.28565454483032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36377120018005</t>
+    <t xml:space="preserve">3.36377143859863</t>
   </si>
   <si>
     <t xml:space="preserve">3.39909410476685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47924828529358</t>
+    <t xml:space="preserve">3.47924852371216</t>
   </si>
   <si>
     <t xml:space="preserve">3.47517275810242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48196530342102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43713283538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44392585754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49962687492371</t>
+    <t xml:space="preserve">3.48196578025818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43713307380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4439263343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49962615966797</t>
   </si>
   <si>
     <t xml:space="preserve">3.52815580368042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47789001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51457023620605</t>
+    <t xml:space="preserve">3.47788953781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51457047462463</t>
   </si>
   <si>
     <t xml:space="preserve">3.45887041091919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52679753303528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52000498771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57570505142212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62733054161072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64499163627625</t>
+    <t xml:space="preserve">3.5267972946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52000451087952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57570552825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62733030319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64499139785767</t>
   </si>
   <si>
     <t xml:space="preserve">3.60423517227173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60287690162659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62597155570984</t>
+    <t xml:space="preserve">3.60287594795227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62597179412842</t>
   </si>
   <si>
     <t xml:space="preserve">3.49419236183167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45615291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41539645195007</t>
+    <t xml:space="preserve">3.45615220069885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41539621353149</t>
   </si>
   <si>
     <t xml:space="preserve">3.45479440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44256711006165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36309242248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39297986030579</t>
+    <t xml:space="preserve">3.44256782531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36309218406677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39298033714294</t>
   </si>
   <si>
     <t xml:space="preserve">3.39461970329285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45400071144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4610698223114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36280798912048</t>
+    <t xml:space="preserve">3.45400094985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46107006072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36280846595764</t>
   </si>
   <si>
     <t xml:space="preserve">3.28151297569275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23414921760559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07367873191833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16699171066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1528537273407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18961405754089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27868509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25747728347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23556303977966</t>
+    <t xml:space="preserve">3.23414897918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07367897033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16699194908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15285396575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18961381912231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27868556976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25747752189636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23556327819824</t>
   </si>
   <si>
     <t xml:space="preserve">3.23768377304077</t>
@@ -1028,28 +1028,28 @@
     <t xml:space="preserve">3.34089374542236</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43774175643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39037799835205</t>
+    <t xml:space="preserve">3.43774151802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39037752151489</t>
   </si>
   <si>
     <t xml:space="preserve">3.4108784198761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37624001502991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38967132568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40946483612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46319079399109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33735942840576</t>
+    <t xml:space="preserve">3.37623977661133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38967156410217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40946507453918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46319055557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33735966682434</t>
   </si>
   <si>
     <t xml:space="preserve">3.31544470787048</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">3.29989290237427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3444287776947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35432529449463</t>
+    <t xml:space="preserve">3.34442830085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35432553291321</t>
   </si>
   <si>
     <t xml:space="preserve">3.32958340644836</t>
@@ -1070,49 +1070,49 @@
     <t xml:space="preserve">3.33806610107422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29211640357971</t>
+    <t xml:space="preserve">3.29211616516113</t>
   </si>
   <si>
     <t xml:space="preserve">3.35644602775574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35220456123352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40098190307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41865491867065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37765312194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32534146308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3557391166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34230804443359</t>
+    <t xml:space="preserve">3.3522047996521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40098166465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41865515708923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37765336036682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32534193992615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35573935508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34230756759644</t>
   </si>
   <si>
     <t xml:space="preserve">3.40027499198914</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45258665084839</t>
+    <t xml:space="preserve">3.45258688926697</t>
   </si>
   <si>
     <t xml:space="preserve">3.44834542274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44269037246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4511730670929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41229271888733</t>
+    <t xml:space="preserve">3.44268989562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45117330551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41229295730591</t>
   </si>
   <si>
     <t xml:space="preserve">3.40734434127808</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">3.46036291122437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43137907981873</t>
+    <t xml:space="preserve">3.4313793182373</t>
   </si>
   <si>
     <t xml:space="preserve">3.4787425994873</t>
@@ -1130,19 +1130,19 @@
     <t xml:space="preserve">3.42077565193176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42572426795959</t>
+    <t xml:space="preserve">3.42572450637817</t>
   </si>
   <si>
     <t xml:space="preserve">3.51479554176331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49429512023926</t>
+    <t xml:space="preserve">3.49429488182068</t>
   </si>
   <si>
     <t xml:space="preserve">3.39532661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41582679748535</t>
+    <t xml:space="preserve">3.41582751274109</t>
   </si>
   <si>
     <t xml:space="preserve">3.4292585849762</t>
@@ -1151,19 +1151,19 @@
     <t xml:space="preserve">3.40239596366882</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36139488220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3882577419281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43279361724854</t>
+    <t xml:space="preserve">3.36139464378357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38825726509094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43279314041138</t>
   </si>
   <si>
     <t xml:space="preserve">3.33594536781311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29706478118896</t>
+    <t xml:space="preserve">3.29706501960754</t>
   </si>
   <si>
     <t xml:space="preserve">3.30413413047791</t>
@@ -1175,70 +1175,70 @@
     <t xml:space="preserve">3.28787517547607</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31615161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25182223320007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28999590873718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33311748504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3309965133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33382511138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32675576210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34654927253723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47450184822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49924302101135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49641585350037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46248364448547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45682859420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45470786094666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38613653182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45753502845764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45894932746887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37411904335022</t>
+    <t xml:space="preserve">3.31615138053894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25182247161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28999519348145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33311796188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33099699020386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33382487297058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32675552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34654951095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47450113296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49924325942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49641609191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46248292922974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45682835578918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45470762252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38613700866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45753526687622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45894908905029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37411856651306</t>
   </si>
   <si>
     <t xml:space="preserve">3.39391255378723</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42006874084473</t>
+    <t xml:space="preserve">3.42006802558899</t>
   </si>
   <si>
     <t xml:space="preserve">3.30978965759277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32816958427429</t>
+    <t xml:space="preserve">3.32816934585571</t>
   </si>
   <si>
     <t xml:space="preserve">3.35715317726135</t>
@@ -1256,22 +1256,22 @@
     <t xml:space="preserve">3.23485612869263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20516586303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15780258178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.130939245224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15356063842773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24546027183533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16911244392395</t>
+    <t xml:space="preserve">3.20516562461853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15780186653137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13093900680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15356087684631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24546003341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16911292076111</t>
   </si>
   <si>
     <t xml:space="preserve">3.19809627532959</t>
@@ -1280,10 +1280,10 @@
     <t xml:space="preserve">3.18890690803528</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23909735679626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23344254493713</t>
+    <t xml:space="preserve">3.23909759521484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23344206809998</t>
   </si>
   <si>
     <t xml:space="preserve">3.27727150917053</t>
@@ -1295,37 +1295,37 @@
     <t xml:space="preserve">3.22920083999634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22495937347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2723228931427</t>
+    <t xml:space="preserve">3.22495913505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27232313156128</t>
   </si>
   <si>
     <t xml:space="preserve">3.31473803520203</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37341237068176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42501711845398</t>
+    <t xml:space="preserve">3.37341213226318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4250168800354</t>
   </si>
   <si>
     <t xml:space="preserve">3.43491435050964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48863983154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44693160057068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38755011558533</t>
+    <t xml:space="preserve">3.48863935470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44693112373352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38755035400391</t>
   </si>
   <si>
     <t xml:space="preserve">3.35927367210388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34160137176514</t>
+    <t xml:space="preserve">3.34160113334656</t>
   </si>
   <si>
     <t xml:space="preserve">3.3005998134613</t>
@@ -1337,64 +1337,64 @@
     <t xml:space="preserve">3.2758572101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3960337638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34937739372253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36068773269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36705017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39179182052612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41653370857239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45329403877258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5232789516449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59114265441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61235022544861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073039054871</t>
+    <t xml:space="preserve">3.39603352546692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34937644004822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36068749427795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36704993247986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3917920589447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41653394699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.453293800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52327942848206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59114289283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61235070228577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073062896729</t>
   </si>
   <si>
     <t xml:space="preserve">3.61093616485596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6279022693634</t>
+    <t xml:space="preserve">3.62790250778198</t>
   </si>
   <si>
     <t xml:space="preserve">3.60103964805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59962606430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51055431365967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53176164627075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57841825485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61941933631897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64911031723022</t>
+    <t xml:space="preserve">3.59962582588196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51055455207825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53176188468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57841801643372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61941957473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64911007881165</t>
   </si>
   <si>
     <t xml:space="preserve">3.67880058288574</t>
@@ -1403,19 +1403,19 @@
     <t xml:space="preserve">3.62083339691162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68586945533752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70849108695984</t>
+    <t xml:space="preserve">3.6858696937561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70849084854126</t>
   </si>
   <si>
     <t xml:space="preserve">3.65335178375244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6830427646637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68728375434875</t>
+    <t xml:space="preserve">3.68304204940796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68728399276733</t>
   </si>
   <si>
     <t xml:space="preserve">3.67738699913025</t>
@@ -1424,91 +1424,91 @@
     <t xml:space="preserve">3.71414685249329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71131825447083</t>
+    <t xml:space="preserve">3.71131896972656</t>
   </si>
   <si>
     <t xml:space="preserve">3.70990514755249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72545719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73252606391907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73111200332642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67173171043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6929395198822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.719801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779950141907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61517834663391</t>
+    <t xml:space="preserve">3.72545695304871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7325267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73111248016357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67173147201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69293904304504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71980237960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779997825623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61517786979675</t>
   </si>
   <si>
     <t xml:space="preserve">3.68869757652283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69576644897461</t>
+    <t xml:space="preserve">3.69576716423035</t>
   </si>
   <si>
     <t xml:space="preserve">3.69435262680054</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69718027114868</t>
+    <t xml:space="preserve">3.69718074798584</t>
   </si>
   <si>
     <t xml:space="preserve">3.68162846565247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75232005119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7438371181488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72262978553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76504492759705</t>
+    <t xml:space="preserve">3.75232028961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74383687973022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72262907028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76504445075989</t>
   </si>
   <si>
     <t xml:space="preserve">3.75938963890076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71697402000427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78342509269714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83997774124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86542677879333</t>
+    <t xml:space="preserve">3.71697449684143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78342461585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83997845649719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86542654037476</t>
   </si>
   <si>
     <t xml:space="preserve">3.83573651313782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82442498207092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79756307601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8173565864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85977220535278</t>
+    <t xml:space="preserve">3.82442593574524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79756355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81735682487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85977149009705</t>
   </si>
   <si>
     <t xml:space="preserve">3.86966824531555</t>
@@ -1517,94 +1517,94 @@
     <t xml:space="preserve">3.88380718231201</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87532377243042</t>
+    <t xml:space="preserve">3.87532353401184</t>
   </si>
   <si>
     <t xml:space="preserve">3.89370369911194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88804817199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85270214080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87108206748962</t>
+    <t xml:space="preserve">3.88804793357849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85270237922668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87108254432678</t>
   </si>
   <si>
     <t xml:space="preserve">3.89087629318237</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84139156341553</t>
+    <t xml:space="preserve">3.84139180183411</t>
   </si>
   <si>
     <t xml:space="preserve">3.88239312171936</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92339468002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88946270942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90360069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92056679725647</t>
+    <t xml:space="preserve">3.92339420318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88946199417114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90360045433044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92056703567505</t>
   </si>
   <si>
     <t xml:space="preserve">3.91915273666382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96439480781555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95732641220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91066980361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93329119682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90642881393433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90501523017883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92198038101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91208338737488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9304633140564</t>
+    <t xml:space="preserve">3.96439552307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95732617378235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91067004203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93329167366028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90642833709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90501427650452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92198014259338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91208362579346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93046379089355</t>
   </si>
   <si>
     <t xml:space="preserve">3.87956523895264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.897944688797</t>
+    <t xml:space="preserve">3.89794516563416</t>
   </si>
   <si>
     <t xml:space="preserve">3.88097882270813</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94742894172668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89229011535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87391018867493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90925574302673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95025682449341</t>
+    <t xml:space="preserve">3.94742965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89228987693787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87390947341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90925621986389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95025658607483</t>
   </si>
   <si>
     <t xml:space="preserve">3.981360912323</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">4.00963830947876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08033037185669</t>
+    <t xml:space="preserve">4.08032989501953</t>
   </si>
   <si>
     <t xml:space="preserve">4.07891607284546</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">4.13016319274902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16984748840332</t>
+    <t xml:space="preserve">4.16984796524048</t>
   </si>
   <si>
     <t xml:space="preserve">4.21100330352783</t>
@@ -1646,10 +1646,10 @@
     <t xml:space="preserve">4.10811614990234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16543817520142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21541261672974</t>
+    <t xml:space="preserve">4.16543865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21541213989258</t>
   </si>
   <si>
     <t xml:space="preserve">4.26979541778564</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">4.3050708770752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32123851776123</t>
+    <t xml:space="preserve">4.32123899459839</t>
   </si>
   <si>
     <t xml:space="preserve">4.36827230453491</t>
@@ -1667,7 +1667,7 @@
     <t xml:space="preserve">4.33152723312378</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32564783096313</t>
+    <t xml:space="preserve">4.32564735412598</t>
   </si>
   <si>
     <t xml:space="preserve">4.288902759552</t>
@@ -1679,55 +1679,55 @@
     <t xml:space="preserve">4.34328556060791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49908542633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44764232635498</t>
+    <t xml:space="preserve">4.49908494949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44764184951782</t>
   </si>
   <si>
     <t xml:space="preserve">4.4461727142334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48291730880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48732662200928</t>
+    <t xml:space="preserve">4.48291778564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48732709884644</t>
   </si>
   <si>
     <t xml:space="preserve">4.45352172851562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43735361099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35210418701172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34181594848633</t>
+    <t xml:space="preserve">4.43735313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35210466384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34181547164917</t>
   </si>
   <si>
     <t xml:space="preserve">4.33446645736694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43147420883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47997856140137</t>
+    <t xml:space="preserve">4.4314751625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47997808456421</t>
   </si>
   <si>
     <t xml:space="preserve">4.44911193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43882369995117</t>
+    <t xml:space="preserve">4.43882274627686</t>
   </si>
   <si>
     <t xml:space="preserve">4.49467611312866</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51966285705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50349473953247</t>
+    <t xml:space="preserve">4.51966238021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50349521636963</t>
   </si>
   <si>
     <t xml:space="preserve">4.54317998886108</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">4.56228733062744</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57698583602905</t>
+    <t xml:space="preserve">4.57698535919189</t>
   </si>
   <si>
     <t xml:space="preserve">4.52701187133789</t>
@@ -1748,16 +1748,16 @@
     <t xml:space="preserve">4.54905891418457</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40207815170288</t>
+    <t xml:space="preserve">4.40207767486572</t>
   </si>
   <si>
     <t xml:space="preserve">4.43588352203369</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42559480667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38884973526001</t>
+    <t xml:space="preserve">4.4255952835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38885021209717</t>
   </si>
   <si>
     <t xml:space="preserve">4.38150072097778</t>
@@ -1766,31 +1766,31 @@
     <t xml:space="preserve">4.24480867385864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20218324661255</t>
+    <t xml:space="preserve">4.20218372344971</t>
   </si>
   <si>
     <t xml:space="preserve">4.29037237167358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29331207275391</t>
+    <t xml:space="preserve">4.29331254959106</t>
   </si>
   <si>
     <t xml:space="preserve">4.27420473098755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26097583770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2844934463501</t>
+    <t xml:space="preserve">4.26097631454468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28449249267578</t>
   </si>
   <si>
     <t xml:space="preserve">4.28743314743042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11399602890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16102886199951</t>
+    <t xml:space="preserve">4.11399507522583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16102981567383</t>
   </si>
   <si>
     <t xml:space="preserve">4.24186849594116</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">4.2183518409729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20071363449097</t>
+    <t xml:space="preserve">4.20071458816528</t>
   </si>
   <si>
     <t xml:space="preserve">4.19777393341064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34034633636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33593702316284</t>
+    <t xml:space="preserve">4.3403468132019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33593654632568</t>
   </si>
   <si>
     <t xml:space="preserve">4.34916496276855</t>
@@ -1826,13 +1826,13 @@
     <t xml:space="preserve">4.30213117599487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20806360244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14192152023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10370683670044</t>
+    <t xml:space="preserve">4.20806264877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14192199707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1037073135376</t>
   </si>
   <si>
     <t xml:space="preserve">4.18307685852051</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">4.12575387954712</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19336462020874</t>
+    <t xml:space="preserve">4.1933650970459</t>
   </si>
   <si>
     <t xml:space="preserve">4.18160676956177</t>
@@ -1853,43 +1853,43 @@
     <t xml:space="preserve">4.18454647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25215768814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29919099807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39031934738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32711744308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30066204071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21247339248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31241989135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36974287033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24774837493896</t>
+    <t xml:space="preserve">4.25215816497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29919147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39031982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32711791992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30066108703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21247243881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31241941452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36974239349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24774885177612</t>
   </si>
   <si>
     <t xml:space="preserve">4.18895578384399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23010969161987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18748617172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17425775527954</t>
+    <t xml:space="preserve">4.23011064529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18748569488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17425680160522</t>
   </si>
   <si>
     <t xml:space="preserve">4.1727876663208</t>
@@ -1898,25 +1898,25 @@
     <t xml:space="preserve">4.14486169815063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16837787628174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18013763427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23892879486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25362730026245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29478120803833</t>
+    <t xml:space="preserve">4.1683783531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18013715744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.238929271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25362682342529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29478216171265</t>
   </si>
   <si>
     <t xml:space="preserve">4.33740663528442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35063505172729</t>
+    <t xml:space="preserve">4.35063457489014</t>
   </si>
   <si>
     <t xml:space="preserve">4.28302383422852</t>
@@ -1928,25 +1928,25 @@
     <t xml:space="preserve">4.30654048919678</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37268161773682</t>
+    <t xml:space="preserve">4.37268114089966</t>
   </si>
   <si>
     <t xml:space="preserve">4.39178895950317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27861404418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22423124313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23745918273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22570037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19189500808716</t>
+    <t xml:space="preserve">4.27861452102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22423076629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23745965957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22570085525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19189596176147</t>
   </si>
   <si>
     <t xml:space="preserve">4.22129154205322</t>
@@ -1955,7 +1955,7 @@
     <t xml:space="preserve">4.23599004745483</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22717046737671</t>
+    <t xml:space="preserve">4.22717094421387</t>
   </si>
   <si>
     <t xml:space="preserve">4.00963926315308</t>
@@ -1970,10 +1970,10 @@
     <t xml:space="preserve">4.04932355880737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01992750167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95378661155701</t>
+    <t xml:space="preserve">4.01992702484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95378637313843</t>
   </si>
   <si>
     <t xml:space="preserve">3.99494099617004</t>
@@ -1982,25 +1982,25 @@
     <t xml:space="preserve">4.0419750213623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9905321598053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0360951423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10664653778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16396856307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1272234916687</t>
+    <t xml:space="preserve">3.99053120613098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03609561920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1066460609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16396903991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12722396850586</t>
   </si>
   <si>
     <t xml:space="preserve">4.13751220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00082015991211</t>
+    <t xml:space="preserve">4.00081968307495</t>
   </si>
   <si>
     <t xml:space="preserve">4.09194803237915</t>
@@ -2012,10 +2012,10 @@
     <t xml:space="preserve">4.02727651596069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02286767959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10076665878296</t>
+    <t xml:space="preserve">4.02286720275879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10076761245728</t>
   </si>
   <si>
     <t xml:space="preserve">4.20365381240845</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">4.13898229598999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25068807601929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20659303665161</t>
+    <t xml:space="preserve">4.25068759918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20659351348877</t>
   </si>
   <si>
     <t xml:space="preserve">4.263916015625</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">4.46674966812134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49173641204834</t>
+    <t xml:space="preserve">4.4917368888855</t>
   </si>
   <si>
     <t xml:space="preserve">4.46087026596069</t>
@@ -2063,184 +2063,184 @@
     <t xml:space="preserve">4.46234035491943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5123143196106</t>
+    <t xml:space="preserve">4.51231384277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.45205163955688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48585748672485</t>
+    <t xml:space="preserve">4.4858570098877</t>
   </si>
   <si>
     <t xml:space="preserve">4.62548923492432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26538562774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26244592666626</t>
+    <t xml:space="preserve">4.26538515090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26244640350342</t>
   </si>
   <si>
     <t xml:space="preserve">4.06549215316772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08606910705566</t>
+    <t xml:space="preserve">4.08606863021851</t>
   </si>
   <si>
     <t xml:space="preserve">3.72890543937683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51798796653748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5018196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02192711830139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24754333496094</t>
+    <t xml:space="preserve">3.51798820495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50182008743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02192759513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24754309654236</t>
   </si>
   <si>
     <t xml:space="preserve">3.15127062797546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27032470703125</t>
+    <t xml:space="preserve">3.27032518386841</t>
   </si>
   <si>
     <t xml:space="preserve">3.29531240463257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35189962387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21153283119202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12995839118958</t>
+    <t xml:space="preserve">3.35189938545227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21153259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.129958152771</t>
   </si>
   <si>
     <t xml:space="preserve">3.35557413101196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38937950134277</t>
+    <t xml:space="preserve">3.38937973976135</t>
   </si>
   <si>
     <t xml:space="preserve">3.34381556510925</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3592483997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57090091705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66643881797791</t>
+    <t xml:space="preserve">3.35924816131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5709011554718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66643857955933</t>
   </si>
   <si>
     <t xml:space="preserve">3.44964170455933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55693769454956</t>
+    <t xml:space="preserve">3.55693817138672</t>
   </si>
   <si>
     <t xml:space="preserve">3.58780384063721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53636002540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54958891868591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46580958366394</t>
+    <t xml:space="preserve">3.53636050224304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54958868026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46581029891968</t>
   </si>
   <si>
     <t xml:space="preserve">3.54811906814575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56428670883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59368324279785</t>
+    <t xml:space="preserve">3.56428647041321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59368348121643</t>
   </si>
   <si>
     <t xml:space="preserve">3.62601900100708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57163596153259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57310509681702</t>
+    <t xml:space="preserve">3.57163572311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57310581207275</t>
   </si>
   <si>
     <t xml:space="preserve">3.44082307815552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61719989776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52754139900208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57457542419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56722664833069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5789852142334</t>
+    <t xml:space="preserve">3.61720013618469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52754211425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57457494735718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56722688674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57898497581482</t>
   </si>
   <si>
     <t xml:space="preserve">3.75168776512146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68187165260315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70391893386841</t>
+    <t xml:space="preserve">3.68187189102173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70391845703125</t>
   </si>
   <si>
     <t xml:space="preserve">3.60691118240356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61279034614563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66423392295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63189816474915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62454915046692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63777709007263</t>
+    <t xml:space="preserve">3.61279082298279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66423416137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63189768791199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62454962730408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63777732849121</t>
   </si>
   <si>
     <t xml:space="preserve">3.62307906150818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71126770973206</t>
+    <t xml:space="preserve">3.71126818656921</t>
   </si>
   <si>
     <t xml:space="preserve">3.73626279830933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60662722587585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66372895240784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63440656661987</t>
+    <t xml:space="preserve">3.60662746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66372871398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63440632820129</t>
   </si>
   <si>
     <t xml:space="preserve">3.68533492088318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75015187263489</t>
+    <t xml:space="preserve">3.75015211105347</t>
   </si>
   <si>
     <t xml:space="preserve">3.73008966445923</t>
@@ -2249,58 +2249,58 @@
     <t xml:space="preserve">3.70231056213379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80725312232971</t>
+    <t xml:space="preserve">3.80725288391113</t>
   </si>
   <si>
     <t xml:space="preserve">3.77021479606628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81959915161133</t>
+    <t xml:space="preserve">3.81959939002991</t>
   </si>
   <si>
     <t xml:space="preserve">3.90447926521301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99707579612732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05108976364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02408313751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9276282787323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88133072853088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81651258468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91991186141968</t>
+    <t xml:space="preserve">3.99707531929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05109024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02408266067505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92762875556946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88133025169373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81651282310486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91991209983826</t>
   </si>
   <si>
     <t xml:space="preserve">4.08581352233887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05880641937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10896301269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14754486083984</t>
+    <t xml:space="preserve">4.0588059425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10896253585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14754438400269</t>
   </si>
   <si>
     <t xml:space="preserve">4.02022457122803</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96621036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9893593788147</t>
+    <t xml:space="preserve">3.96621012687683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98935961723328</t>
   </si>
   <si>
     <t xml:space="preserve">4.03565788269043</t>
@@ -2309,40 +2309,40 @@
     <t xml:space="preserve">4.08967208862305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03179979324341</t>
+    <t xml:space="preserve">4.03179883956909</t>
   </si>
   <si>
     <t xml:space="preserve">4.07038116455078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11282110214233</t>
+    <t xml:space="preserve">4.11282062530518</t>
   </si>
   <si>
     <t xml:space="preserve">4.05494832992554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95463562011719</t>
+    <t xml:space="preserve">3.95463585853577</t>
   </si>
   <si>
     <t xml:space="preserve">3.96235203742981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93534469604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97006797790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97392678260803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07423973083496</t>
+    <t xml:space="preserve">3.93534445762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97006821632385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97392630577087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0742392539978</t>
   </si>
   <si>
     <t xml:space="preserve">4.1243953704834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10510444641113</t>
+    <t xml:space="preserve">4.10510492324829</t>
   </si>
   <si>
     <t xml:space="preserve">4.09352970123291</t>
@@ -2360,25 +2360,25 @@
     <t xml:space="preserve">4.26714897155762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21313333511353</t>
+    <t xml:space="preserve">4.21313381195068</t>
   </si>
   <si>
     <t xml:space="preserve">4.19770097732544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16297721862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16683578491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470855712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28643894195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36746072769165</t>
+    <t xml:space="preserve">4.16297769546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16683530807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470808029175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28643941879272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36746120452881</t>
   </si>
   <si>
     <t xml:space="preserve">4.42147588729858</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">4.3906102180481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37517738342285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36360263824463</t>
+    <t xml:space="preserve">4.37517786026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36360311508179</t>
   </si>
   <si>
     <t xml:space="preserve">4.30572986602783</t>
@@ -2405,13 +2405,13 @@
     <t xml:space="preserve">4.31344652175903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30187225341797</t>
+    <t xml:space="preserve">4.30187129974365</t>
   </si>
   <si>
     <t xml:space="preserve">4.13597011566162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22856664657593</t>
+    <t xml:space="preserve">4.22856616973877</t>
   </si>
   <si>
     <t xml:space="preserve">4.18612670898438</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">4.17455148696899</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18998527526855</t>
+    <t xml:space="preserve">4.18998432159424</t>
   </si>
   <si>
     <t xml:space="preserve">4.11667966842651</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">4.17841005325317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15526151657104</t>
+    <t xml:space="preserve">4.15526103973389</t>
   </si>
   <si>
     <t xml:space="preserve">4.15140295028687</t>
@@ -2438,52 +2438,52 @@
     <t xml:space="preserve">4.15911960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19384288787842</t>
+    <t xml:space="preserve">4.19384241104126</t>
   </si>
   <si>
     <t xml:space="preserve">4.07809782028198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89290499687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97778463363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06266403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94691896438599</t>
+    <t xml:space="preserve">3.89290452003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9777843952179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06266450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94691920280457</t>
   </si>
   <si>
     <t xml:space="preserve">3.9855010509491</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9816427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88904666900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71157002449036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7270028591156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82885885238647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83194518089294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86589765548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00479173660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95077729225159</t>
+    <t xml:space="preserve">3.98164296150208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88904595375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71157050132751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72700262069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8288586139679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8319456577301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86589789390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00479125976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95077776908875</t>
   </si>
   <si>
     <t xml:space="preserve">4.08195543289185</t>
@@ -2492,10 +2492,10 @@
     <t xml:space="preserve">4.03951549530029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13982820510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17069339752197</t>
+    <t xml:space="preserve">4.13982772827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17069387435913</t>
   </si>
   <si>
     <t xml:space="preserve">4.14368629455566</t>
@@ -2507,43 +2507,43 @@
     <t xml:space="preserve">3.93920302391052</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90062093734741</t>
+    <t xml:space="preserve">3.90062117576599</t>
   </si>
   <si>
     <t xml:space="preserve">3.80879664421082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99321746826172</t>
+    <t xml:space="preserve">3.99321818351746</t>
   </si>
   <si>
     <t xml:space="preserve">4.01250791549683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95849370956421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87747192382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9314866065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92377042770386</t>
+    <t xml:space="preserve">3.95849394798279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8774721622467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93148589134216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92377018928528</t>
   </si>
   <si>
     <t xml:space="preserve">3.86203932762146</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8180558681488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80571007728577</t>
+    <t xml:space="preserve">3.81805610656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80571031570435</t>
   </si>
   <si>
     <t xml:space="preserve">3.85818123817444</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89676260948181</t>
+    <t xml:space="preserve">3.89676308631897</t>
   </si>
   <si>
     <t xml:space="preserve">3.85663795471191</t>
@@ -2555,31 +2555,31 @@
     <t xml:space="preserve">3.83811902999878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94306135177612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90833711624146</t>
+    <t xml:space="preserve">3.94306111335754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90833783149719</t>
   </si>
   <si>
     <t xml:space="preserve">3.88518834114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83503198623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76712799072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76249837875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8226854801178</t>
+    <t xml:space="preserve">3.83503174781799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76712822914124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76249814033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82268571853638</t>
   </si>
   <si>
     <t xml:space="preserve">3.79799342155457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87361359596252</t>
+    <t xml:space="preserve">3.87361407279968</t>
   </si>
   <si>
     <t xml:space="preserve">4.02794075012207</t>
@@ -2588,37 +2588,37 @@
     <t xml:space="preserve">4.04337358474731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20927572250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25171518325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25557327270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31730461120605</t>
+    <t xml:space="preserve">4.2092752456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25171566009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25557374954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3173041343689</t>
   </si>
   <si>
     <t xml:space="preserve">4.27100658416748</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26251888275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28721141815186</t>
+    <t xml:space="preserve">4.26251840591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2872109413147</t>
   </si>
   <si>
     <t xml:space="preserve">4.25634527206421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24554204940796</t>
+    <t xml:space="preserve">4.24554252624512</t>
   </si>
   <si>
     <t xml:space="preserve">4.14985942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12979793548584</t>
+    <t xml:space="preserve">4.12979698181152</t>
   </si>
   <si>
     <t xml:space="preserve">4.14059972763062</t>
@@ -2627,49 +2627,49 @@
     <t xml:space="preserve">4.12362384796143</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16837882995605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17146587371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19924449920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23628282546997</t>
+    <t xml:space="preserve">4.16837930679321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1714653968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19924402236938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23628234863281</t>
   </si>
   <si>
     <t xml:space="preserve">4.18844127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17763805389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17918109893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18381071090698</t>
+    <t xml:space="preserve">4.1776385307312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17918157577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1838116645813</t>
   </si>
   <si>
     <t xml:space="preserve">4.20387411117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18535470962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21621990203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29338359832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23165369033813</t>
+    <t xml:space="preserve">4.18535423278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21622037887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29338407516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23165321350098</t>
   </si>
   <si>
     <t xml:space="preserve">4.25017213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23782587051392</t>
+    <t xml:space="preserve">4.23782634735107</t>
   </si>
   <si>
     <t xml:space="preserve">4.35048532485962</t>
@@ -2681,34 +2681,34 @@
     <t xml:space="preserve">4.39369630813599</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47086000442505</t>
+    <t xml:space="preserve">4.47086048126221</t>
   </si>
   <si>
     <t xml:space="preserve">4.46610307693481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44025039672852</t>
+    <t xml:space="preserve">4.44024991989136</t>
   </si>
   <si>
     <t xml:space="preserve">4.3885440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35622835159302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38531303405762</t>
+    <t xml:space="preserve">4.35622787475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38531255722046</t>
   </si>
   <si>
     <t xml:space="preserve">4.37400197982788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39016008377075</t>
+    <t xml:space="preserve">4.39015960693359</t>
   </si>
   <si>
     <t xml:space="preserve">4.37723398208618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40147018432617</t>
+    <t xml:space="preserve">4.40147066116333</t>
   </si>
   <si>
     <t xml:space="preserve">4.45156097412109</t>
@@ -2723,16 +2723,16 @@
     <t xml:space="preserve">4.50165128707886</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52911949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55174112319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55012559890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62122106552124</t>
+    <t xml:space="preserve">4.52911996841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55174160003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55012512207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62122058868408</t>
   </si>
   <si>
     <t xml:space="preserve">4.58405733108521</t>
@@ -2741,10 +2741,10 @@
     <t xml:space="preserve">4.56628322601318</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54527854919434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52750444412231</t>
+    <t xml:space="preserve">4.54527807235718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52750396728516</t>
   </si>
   <si>
     <t xml:space="preserve">4.45640802383423</t>
@@ -2765,10 +2765,10 @@
     <t xml:space="preserve">4.46771955490112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49841928482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50649833679199</t>
+    <t xml:space="preserve">4.49841976165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50649881362915</t>
   </si>
   <si>
     <t xml:space="preserve">4.55335712432861</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">4.4790301322937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52265739440918</t>
+    <t xml:space="preserve">4.52265644073486</t>
   </si>
   <si>
     <t xml:space="preserve">4.54204654693604</t>
@@ -2792,13 +2792,13 @@
     <t xml:space="preserve">4.37884902954102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35461235046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37238645553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5371994972229</t>
+    <t xml:space="preserve">4.35461282730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37238597869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53719902038574</t>
   </si>
   <si>
     <t xml:space="preserve">4.56789922714233</t>
@@ -2813,10 +2813,10 @@
     <t xml:space="preserve">4.61637353897095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62768411636353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59375238418579</t>
+    <t xml:space="preserve">4.62768459320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59375190734863</t>
   </si>
   <si>
     <t xml:space="preserve">4.60829496383667</t>
@@ -2825,10 +2825,10 @@
     <t xml:space="preserve">4.63091564178467</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65676879882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66484880447388</t>
+    <t xml:space="preserve">4.65676927566528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66484832763672</t>
   </si>
   <si>
     <t xml:space="preserve">4.69070148468018</t>
@@ -2837,43 +2837,43 @@
     <t xml:space="preserve">4.73271179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76502799987793</t>
+    <t xml:space="preserve">4.76502847671509</t>
   </si>
   <si>
     <t xml:space="preserve">4.80219173431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79896020889282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76987552642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82804441452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82481336593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84420299530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80703973770142</t>
+    <t xml:space="preserve">4.79896068572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76987600326538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82804489135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82481384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84420347213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80703926086426</t>
   </si>
   <si>
     <t xml:space="preserve">4.69554853439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57436275482178</t>
+    <t xml:space="preserve">4.57436323165894</t>
   </si>
   <si>
     <t xml:space="preserve">4.53558301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5921368598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54366159439087</t>
+    <t xml:space="preserve">4.59213638305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54366207122803</t>
   </si>
   <si>
     <t xml:space="preserve">4.49034070968628</t>
@@ -2885,10 +2885,10 @@
     <t xml:space="preserve">4.48549270629883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45963954925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51134634017944</t>
+    <t xml:space="preserve">4.45964050292969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51134586334229</t>
   </si>
   <si>
     <t xml:space="preserve">4.52427244186401</t>
@@ -2906,10 +2906,10 @@
     <t xml:space="preserve">4.58890438079834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65353775024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57113075256348</t>
+    <t xml:space="preserve">4.65353727340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57113122940063</t>
   </si>
   <si>
     <t xml:space="preserve">4.4757981300354</t>
@@ -2921,34 +2921,34 @@
     <t xml:space="preserve">4.46933507919312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43217134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47095012664795</t>
+    <t xml:space="preserve">4.43217182159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47095108032227</t>
   </si>
   <si>
     <t xml:space="preserve">4.48387718200684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39985513687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37076997756958</t>
+    <t xml:space="preserve">4.39985466003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37077045440674</t>
   </si>
   <si>
     <t xml:space="preserve">4.39662313461304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41116523742676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51457738876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46287202835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43540287017822</t>
+    <t xml:space="preserve">4.41116571426392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51457786560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46287155151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43540239334106</t>
   </si>
   <si>
     <t xml:space="preserve">4.50003528594971</t>
@@ -2957,10 +2957,10 @@
     <t xml:space="preserve">4.53881454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6131420135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63253211975098</t>
+    <t xml:space="preserve">4.61314249038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63253164291382</t>
   </si>
   <si>
     <t xml:space="preserve">4.60021543502808</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">4.55658864974976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57920980453491</t>
+    <t xml:space="preserve">4.57921028137207</t>
   </si>
   <si>
     <t xml:space="preserve">4.52588844299316</t>
@@ -2981,37 +2981,37 @@
     <t xml:space="preserve">4.53235149383545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44832897186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50488328933716</t>
+    <t xml:space="preserve">4.44832992553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5048828125</t>
   </si>
   <si>
     <t xml:space="preserve">4.71978569030762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72301816940308</t>
+    <t xml:space="preserve">4.72301769256592</t>
   </si>
   <si>
     <t xml:space="preserve">4.65838479995728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68262195587158</t>
+    <t xml:space="preserve">4.68262147903442</t>
   </si>
   <si>
     <t xml:space="preserve">4.65515327453613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64384269714355</t>
+    <t xml:space="preserve">4.6438422203064</t>
   </si>
   <si>
     <t xml:space="preserve">4.70201206207275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68585348129272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70362710952759</t>
+    <t xml:space="preserve">4.68585395812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7036280632019</t>
   </si>
   <si>
     <t xml:space="preserve">4.66807985305786</t>
@@ -3023,28 +3023,28 @@
     <t xml:space="preserve">4.7262487411499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76179647445679</t>
+    <t xml:space="preserve">4.76179695129395</t>
   </si>
   <si>
     <t xml:space="preserve">4.75048637390137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84905004501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87490320205688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88944578170776</t>
+    <t xml:space="preserve">4.84905052185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87490367889404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88944530487061</t>
   </si>
   <si>
     <t xml:space="preserve">4.91853046417236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85874509811401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83127641677856</t>
+    <t xml:space="preserve">4.85874557495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83127689361572</t>
   </si>
   <si>
     <t xml:space="preserve">4.66161632537842</t>
@@ -3056,22 +3056,22 @@
     <t xml:space="preserve">4.72948026657104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74402236938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76018142700195</t>
+    <t xml:space="preserve">4.74402284622192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76018095016479</t>
   </si>
   <si>
     <t xml:space="preserve">4.74079132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79734468460083</t>
+    <t xml:space="preserve">4.79734516143799</t>
   </si>
   <si>
     <t xml:space="preserve">4.71655368804932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79572916030884</t>
+    <t xml:space="preserve">4.79572868347168</t>
   </si>
   <si>
     <t xml:space="preserve">4.83450841903687</t>
@@ -3080,19 +3080,19 @@
     <t xml:space="preserve">4.74563884735107</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50973033905029</t>
+    <t xml:space="preserve">4.50972986221313</t>
   </si>
   <si>
     <t xml:space="preserve">4.46448755264282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57759428024292</t>
+    <t xml:space="preserve">4.57759380340576</t>
   </si>
   <si>
     <t xml:space="preserve">4.62930059432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55982065200806</t>
+    <t xml:space="preserve">4.5598201751709</t>
   </si>
   <si>
     <t xml:space="preserve">4.54850959777832</t>
@@ -3107,19 +3107,19 @@
     <t xml:space="preserve">4.35299634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32068014144897</t>
+    <t xml:space="preserve">4.32068061828613</t>
   </si>
   <si>
     <t xml:space="preserve">4.55820465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51780891418457</t>
+    <t xml:space="preserve">4.51780939102173</t>
   </si>
   <si>
     <t xml:space="preserve">4.49518775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41762924194336</t>
+    <t xml:space="preserve">4.41762828826904</t>
   </si>
   <si>
     <t xml:space="preserve">4.48872470855713</t>
@@ -3128,10 +3128,10 @@
     <t xml:space="preserve">4.43378686904907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7052435874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7302885055542</t>
+    <t xml:space="preserve">4.70524311065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73028898239136</t>
   </si>
   <si>
     <t xml:space="preserve">4.68181419372559</t>
@@ -3140,10 +3140,10 @@
     <t xml:space="preserve">4.77472305297852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89590930938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94034337997437</t>
+    <t xml:space="preserve">4.89590883255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94034385681152</t>
   </si>
   <si>
     <t xml:space="preserve">4.91610670089722</t>
@@ -3155,28 +3155,28 @@
     <t xml:space="preserve">5.00497674942017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04537105560303</t>
+    <t xml:space="preserve">5.04537153244019</t>
   </si>
   <si>
     <t xml:space="preserve">5.15039920806885</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08980655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06556987762451</t>
+    <t xml:space="preserve">5.08980703353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0655689239502</t>
   </si>
   <si>
     <t xml:space="preserve">4.9807391166687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96054172515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99285793304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01709461212158</t>
+    <t xml:space="preserve">4.96054124832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99285745620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01709508895874</t>
   </si>
   <si>
     <t xml:space="preserve">5.00093698501587</t>
@@ -3185,10 +3185,10 @@
     <t xml:space="preserve">5.01305532455444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97266006469727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89994859695435</t>
+    <t xml:space="preserve">4.97266054153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8999490737915</t>
   </si>
   <si>
     <t xml:space="preserve">4.94842290878296</t>
@@ -3203,19 +3203,19 @@
     <t xml:space="preserve">5.05345058441162</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16251802444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20222187042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11777067184448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15577411651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18533182144165</t>
+    <t xml:space="preserve">5.16251850128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20222234725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11777019500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15577363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18533134460449</t>
   </si>
   <si>
     <t xml:space="preserve">5.10088014602661</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">5.06287670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07554531097412</t>
+    <t xml:space="preserve">5.07554483413696</t>
   </si>
   <si>
     <t xml:space="preserve">5.02909660339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04598665237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02487373352051</t>
+    <t xml:space="preserve">5.04598617553711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02487325668335</t>
   </si>
   <si>
     <t xml:space="preserve">4.87286043167114</t>
@@ -3248,13 +3248,13 @@
     <t xml:space="preserve">4.54772233963013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60261583328247</t>
+    <t xml:space="preserve">4.60261535644531</t>
   </si>
   <si>
     <t xml:space="preserve">4.53505373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71662473678589</t>
+    <t xml:space="preserve">4.71662521362305</t>
   </si>
   <si>
     <t xml:space="preserve">4.64906406402588</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">4.73773813247681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69128942489624</t>
+    <t xml:space="preserve">4.6912899017334</t>
   </si>
   <si>
     <t xml:space="preserve">4.72929286956787</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">4.61950540542603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61106014251709</t>
+    <t xml:space="preserve">4.61106061935425</t>
   </si>
   <si>
     <t xml:space="preserve">4.6068377494812</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">4.51816368103027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45482540130615</t>
+    <t xml:space="preserve">4.45482492446899</t>
   </si>
   <si>
     <t xml:space="preserve">4.38726377487183</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">4.46327018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59417057037354</t>
+    <t xml:space="preserve">4.59417009353638</t>
   </si>
   <si>
     <t xml:space="preserve">4.67017698287964</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">4.61528301239014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62795114517212</t>
+    <t xml:space="preserve">4.62795066833496</t>
   </si>
   <si>
     <t xml:space="preserve">4.6575083732605</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">4.6363959312439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77996397018433</t>
+    <t xml:space="preserve">4.77996349334717</t>
   </si>
   <si>
     <t xml:space="preserve">4.80107641220093</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">4.72506999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77151870727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70817995071411</t>
+    <t xml:space="preserve">4.77151918411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70817947387695</t>
   </si>
   <si>
     <t xml:space="preserve">4.66173124313354</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">4.53927659988403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47593784332275</t>
+    <t xml:space="preserve">4.47593832015991</t>
   </si>
   <si>
     <t xml:space="preserve">4.33659267425537</t>
@@ -3374,13 +3374,13 @@
     <t xml:space="preserve">4.31125688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42104387283325</t>
+    <t xml:space="preserve">4.42104434967041</t>
   </si>
   <si>
     <t xml:space="preserve">4.29436683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33237028121948</t>
+    <t xml:space="preserve">4.33236980438232</t>
   </si>
   <si>
     <t xml:space="preserve">4.25636339187622</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">4.39148569107056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41259956359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4041543006897</t>
+    <t xml:space="preserve">4.41259908676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40415382385254</t>
   </si>
   <si>
     <t xml:space="preserve">4.32392454147339</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">4.3197021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36192846298218</t>
+    <t xml:space="preserve">4.36192798614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.27747631072998</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">4.34503793716431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27325391769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14319801330566</t>
+    <t xml:space="preserve">4.27325439453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14319849014282</t>
   </si>
   <si>
     <t xml:space="preserve">4.07225894927979</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">4.02665519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03341102600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12630844116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22680616378784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10097217559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.036789894104</t>
+    <t xml:space="preserve">4.03341150283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12630796432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22680568695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1009726524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03678941726685</t>
   </si>
   <si>
     <t xml:space="preserve">4.02834415435791</t>
@@ -3452,10 +3452,10 @@
     <t xml:space="preserve">3.88984346389771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84761762619019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97091674804688</t>
+    <t xml:space="preserve">3.84761786460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97091698646545</t>
   </si>
   <si>
     <t xml:space="preserve">4.06719160079956</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">4.04016733169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09421634674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01483201980591</t>
+    <t xml:space="preserve">4.09421682357788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01483249664307</t>
   </si>
   <si>
     <t xml:space="preserve">4.15333271026611</t>
@@ -3485,13 +3485,13 @@
     <t xml:space="preserve">4.43371200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56461238861084</t>
+    <t xml:space="preserve">4.56461191177368</t>
   </si>
   <si>
     <t xml:space="preserve">4.68706703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80952215194702</t>
+    <t xml:space="preserve">4.80952167510986</t>
   </si>
   <si>
     <t xml:space="preserve">4.75462818145752</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">4.73351573944092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75040578842163</t>
+    <t xml:space="preserve">4.75040531158447</t>
   </si>
   <si>
     <t xml:space="preserve">4.76307344436646</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">4.51394081115723</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56883430480957</t>
+    <t xml:space="preserve">4.56883478164673</t>
   </si>
   <si>
     <t xml:space="preserve">4.78418684005737</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">4.58994770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52238655090332</t>
+    <t xml:space="preserve">4.52238607406616</t>
   </si>
   <si>
     <t xml:space="preserve">4.62372827529907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48438310623169</t>
+    <t xml:space="preserve">4.48438262939453</t>
   </si>
   <si>
     <t xml:space="preserve">4.44215726852417</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">4.35348320007324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42526626586914</t>
+    <t xml:space="preserve">4.4252667427063</t>
   </si>
   <si>
     <t xml:space="preserve">4.47171497344971</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">4.90241813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97842502593994</t>
+    <t xml:space="preserve">4.9784255027771</t>
   </si>
   <si>
     <t xml:space="preserve">5.04176378250122</t>
@@ -3593,10 +3593,10 @@
     <t xml:space="preserve">5.09243488311768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01220560073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98687028884888</t>
+    <t xml:space="preserve">5.01220607757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98687076568604</t>
   </si>
   <si>
     <t xml:space="preserve">4.91930913925171</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">5.00798320770264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86019325256348</t>
+    <t xml:space="preserve">4.86019277572632</t>
   </si>
   <si>
     <t xml:space="preserve">4.94042158126831</t>
@@ -3626,25 +3626,25 @@
     <t xml:space="preserve">5.00376081466675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96998071670532</t>
+    <t xml:space="preserve">4.96998023986816</t>
   </si>
   <si>
     <t xml:space="preserve">4.83908033370972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88975143432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82535934448242</t>
+    <t xml:space="preserve">4.88975095748901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82535886764526</t>
   </si>
   <si>
     <t xml:space="preserve">4.82981061935425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75858783721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66955900192261</t>
+    <t xml:space="preserve">4.75858736038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66955852508545</t>
   </si>
   <si>
     <t xml:space="preserve">4.71852493286133</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">4.78529596328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90993642807007</t>
+    <t xml:space="preserve">4.90993595123291</t>
   </si>
   <si>
     <t xml:space="preserve">4.95890283584595</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">4.93219375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96780490875244</t>
+    <t xml:space="preserve">4.9678053855896</t>
   </si>
   <si>
     <t xml:space="preserve">4.9989652633667</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">4.99006223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86987352371216</t>
+    <t xml:space="preserve">4.869873046875</t>
   </si>
   <si>
     <t xml:space="preserve">4.95445108413696</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">4.88322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87432479858398</t>
+    <t xml:space="preserve">4.87432527542114</t>
   </si>
   <si>
     <t xml:space="preserve">4.80755376815796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75413656234741</t>
+    <t xml:space="preserve">4.75413608551025</t>
   </si>
   <si>
     <t xml:space="preserve">4.85206747055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63839864730835</t>
+    <t xml:space="preserve">4.63839912414551</t>
   </si>
   <si>
     <t xml:space="preserve">4.60278749465942</t>
@@ -3716,19 +3716,19 @@
     <t xml:space="preserve">4.70517015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69626712799072</t>
+    <t xml:space="preserve">4.69626760482788</t>
   </si>
   <si>
     <t xml:space="preserve">4.68291330337524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7452335357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76303863525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77194166183472</t>
+    <t xml:space="preserve">4.74523305892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76303911209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77194213867188</t>
   </si>
   <si>
     <t xml:space="preserve">4.71407318115234</t>
@@ -3746,25 +3746,25 @@
     <t xml:space="preserve">4.57607841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5538215637207</t>
+    <t xml:space="preserve">4.55382108688354</t>
   </si>
   <si>
     <t xml:space="preserve">4.53156423568726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59388446807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.647301197052</t>
+    <t xml:space="preserve">4.59388399124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64730167388916</t>
   </si>
   <si>
     <t xml:space="preserve">4.66510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61614179611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54937028884888</t>
+    <t xml:space="preserve">4.6161413192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54936981201172</t>
   </si>
   <si>
     <t xml:space="preserve">4.50485563278198</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">4.500403881073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49595260620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48704957962036</t>
+    <t xml:space="preserve">4.49595308303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48705005645752</t>
   </si>
   <si>
     <t xml:space="preserve">4.70071887969971</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">4.73187923431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.722975730896</t>
+    <t xml:space="preserve">4.72297620773315</t>
   </si>
   <si>
     <t xml:space="preserve">4.44609642028809</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">4.24489164352417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28228330612183</t>
+    <t xml:space="preserve">4.28228378295898</t>
   </si>
   <si>
     <t xml:space="preserve">4.31789493560791</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">4.34282302856445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41226577758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43541288375854</t>
+    <t xml:space="preserve">4.41226530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4354133605957</t>
   </si>
   <si>
     <t xml:space="preserve">4.42829084396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39267921447754</t>
+    <t xml:space="preserve">4.3926796913147</t>
   </si>
   <si>
     <t xml:space="preserve">4.45588970184326</t>
@@ -3857,22 +3857,22 @@
     <t xml:space="preserve">4.30186986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25201416015625</t>
+    <t xml:space="preserve">4.25201368331909</t>
   </si>
   <si>
     <t xml:space="preserve">4.26625823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27694225311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20928049087524</t>
+    <t xml:space="preserve">4.27694177627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20928001403809</t>
   </si>
   <si>
     <t xml:space="preserve">4.19147443771362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21996307373047</t>
+    <t xml:space="preserve">4.21996355056763</t>
   </si>
   <si>
     <t xml:space="preserve">4.27160024642944</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">4.30899238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30543088912964</t>
+    <t xml:space="preserve">4.3054313659668</t>
   </si>
   <si>
     <t xml:space="preserve">4.39445972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40336322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47369575500488</t>
+    <t xml:space="preserve">4.40336275100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47369527816772</t>
   </si>
   <si>
     <t xml:space="preserve">4.49150133132935</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">4.46034145355225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43185186386108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52266120910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47814750671387</t>
+    <t xml:space="preserve">4.43185234069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5226616859436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47814702987671</t>
   </si>
   <si>
     <t xml:space="preserve">4.56717586517334</t>
@@ -3944,22 +3944,22 @@
     <t xml:space="preserve">4.61169004440308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59833574295044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55827236175537</t>
+    <t xml:space="preserve">4.5983362197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55827283859253</t>
   </si>
   <si>
     <t xml:space="preserve">4.58053016662598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56272411346436</t>
+    <t xml:space="preserve">4.56272459030151</t>
   </si>
   <si>
     <t xml:space="preserve">4.5849814414978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54046726226807</t>
+    <t xml:space="preserve">4.54046678543091</t>
   </si>
   <si>
     <t xml:space="preserve">4.51375865936279</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">4.6918158531189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74968481063843</t>
+    <t xml:space="preserve">4.74968433380127</t>
   </si>
   <si>
     <t xml:space="preserve">4.4692440032959</t>
@@ -3998,16 +3998,16 @@
     <t xml:space="preserve">4.44787693023682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57162714004517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79419946670532</t>
+    <t xml:space="preserve">4.57162761688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79419898986816</t>
   </si>
   <si>
     <t xml:space="preserve">4.80310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8209080696106</t>
+    <t xml:space="preserve">4.82090759277344</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
@@ -4953,6 +4953,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.4350004196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48499965667725</t>
   </si>
 </sst>
 </file>
@@ -64987,7 +64990,7 @@
     </row>
     <row r="2297">
       <c r="A2297" s="1" t="n">
-        <v>45979.6910185185</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2297" t="n">
         <v>2465326</v>
@@ -65008,6 +65011,32 @@
         <v>1646</v>
       </c>
       <c r="H2297" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" s="1" t="n">
+        <v>45980.6911689815</v>
+      </c>
+      <c r="B2298" t="n">
+        <v>2610623</v>
+      </c>
+      <c r="C2298" t="n">
+        <v>9.55500030517578</v>
+      </c>
+      <c r="D2298" t="n">
+        <v>9.34500026702881</v>
+      </c>
+      <c r="E2298" t="n">
+        <v>9.40499973297119</v>
+      </c>
+      <c r="F2298" t="n">
+        <v>9.48499965667725</v>
+      </c>
+      <c r="G2298" t="s">
+        <v>1647</v>
+      </c>
+      <c r="H2298" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="1648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="1649">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.50135779380798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32790613174438</t>
+    <t xml:space="preserve">2.32790589332581</t>
   </si>
   <si>
     <t xml:space="preserve">2.16488695144653</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">2.1727123260498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09315872192383</t>
+    <t xml:space="preserve">2.09315896034241</t>
   </si>
   <si>
     <t xml:space="preserve">2.06185936927795</t>
@@ -65,25 +65,25 @@
     <t xml:space="preserve">2.08663845062256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04490542411804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06055545806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04360151290894</t>
+    <t xml:space="preserve">2.0449059009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06055521965027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04360175132751</t>
   </si>
   <si>
     <t xml:space="preserve">2.10489630699158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1296751499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14532518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1792323589325</t>
+    <t xml:space="preserve">2.12967538833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14532494544983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17923283576965</t>
   </si>
   <si>
     <t xml:space="preserve">2.2000994682312</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">2.20140337944031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17792844772339</t>
+    <t xml:space="preserve">2.17792868614197</t>
   </si>
   <si>
     <t xml:space="preserve">2.13228321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09837579727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22357416152954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29138970375061</t>
+    <t xml:space="preserve">2.09837555885315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22357392311096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29138994216919</t>
   </si>
   <si>
     <t xml:space="preserve">2.33181834220886</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">2.29791045188904</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2379195690155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30051875114441</t>
+    <t xml:space="preserve">2.23791933059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30051851272583</t>
   </si>
   <si>
     <t xml:space="preserve">2.30443096160889</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">2.34616422653198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39572143554688</t>
+    <t xml:space="preserve">2.3957211971283</t>
   </si>
   <si>
     <t xml:space="preserve">2.45571255683899</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">2.42180442810059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41006708145142</t>
+    <t xml:space="preserve">2.41006731987</t>
   </si>
   <si>
     <t xml:space="preserve">2.43093371391296</t>
@@ -155,25 +155,25 @@
     <t xml:space="preserve">2.43745422363281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48701214790344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45049595832825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4909245967865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44527912139893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46614575386047</t>
+    <t xml:space="preserve">2.48701190948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45049571990967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49092435836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44527959823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46614599227905</t>
   </si>
   <si>
     <t xml:space="preserve">2.43223786354065</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44006252288818</t>
+    <t xml:space="preserve">2.44006299972534</t>
   </si>
   <si>
     <t xml:space="preserve">2.47788286209106</t>
@@ -194,22 +194,22 @@
     <t xml:space="preserve">2.41789245605469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43484592437744</t>
+    <t xml:space="preserve">2.43484616279602</t>
   </si>
   <si>
     <t xml:space="preserve">2.41267538070679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35659694671631</t>
+    <t xml:space="preserve">2.35659742355347</t>
   </si>
   <si>
     <t xml:space="preserve">2.27573990821838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29530239105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31225609779358</t>
+    <t xml:space="preserve">2.29530215263367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31225633621216</t>
   </si>
   <si>
     <t xml:space="preserve">2.38137602806091</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">2.46744966506958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47397065162659</t>
+    <t xml:space="preserve">2.47397041320801</t>
   </si>
   <si>
     <t xml:space="preserve">2.48440361022949</t>
@@ -236,58 +236,58 @@
     <t xml:space="preserve">2.4635374546051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4726665019989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47136211395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44788765907288</t>
+    <t xml:space="preserve">2.47266674041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47136235237122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4478874206543</t>
   </si>
   <si>
     <t xml:space="preserve">2.49614095687866</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49744510650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5157036781311</t>
+    <t xml:space="preserve">2.49744534492493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51570320129395</t>
   </si>
   <si>
     <t xml:space="preserve">2.53135323524475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51439905166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53656959533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52744030952454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54830718040466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55091524124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53787398338318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58612704277039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57699823379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59786462783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60438537597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57308602333069</t>
+    <t xml:space="preserve">2.51439929008484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53656983375549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52744078636169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54830694198608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55091500282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5378737449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58612751960754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57699799537659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59786486625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60438561439514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57308554649353</t>
   </si>
   <si>
     <t xml:space="preserve">2.66959285736084</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">2.68393850326538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6982843875885</t>
+    <t xml:space="preserve">2.69828414916992</t>
   </si>
   <si>
     <t xml:space="preserve">2.64872646331787</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">2.64742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68133044242859</t>
+    <t xml:space="preserve">2.68133020401001</t>
   </si>
   <si>
     <t xml:space="preserve">2.67480969429016</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">2.63438081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64351010322571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69567584991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69958829879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67872190475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73480033874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77262043952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7543625831604</t>
+    <t xml:space="preserve">2.64350962638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69567561149597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69958806037903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67872166633606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73480010032654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.772620677948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75436234474182</t>
   </si>
   <si>
     <t xml:space="preserve">2.71262955665588</t>
@@ -344,31 +344,31 @@
     <t xml:space="preserve">2.70219659805298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66176772117615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78305411338806</t>
+    <t xml:space="preserve">2.66176795959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7830536365509</t>
   </si>
   <si>
     <t xml:space="preserve">2.7452335357666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69306778907776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71915054321289</t>
+    <t xml:space="preserve">2.69306755065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71915078163147</t>
   </si>
   <si>
     <t xml:space="preserve">2.70610904693604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74914598464966</t>
+    <t xml:space="preserve">2.74914622306824</t>
   </si>
   <si>
     <t xml:space="preserve">2.77783727645874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83521962165833</t>
+    <t xml:space="preserve">2.8352198600769</t>
   </si>
   <si>
     <t xml:space="preserve">2.84043622016907</t>
@@ -377,37 +377,37 @@
     <t xml:space="preserve">2.88738560676575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89651441574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85347771644592</t>
+    <t xml:space="preserve">2.89651465415955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8534779548645</t>
   </si>
   <si>
     <t xml:space="preserve">2.91477251052856</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0086715221405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02040910720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96824312210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0073676109314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05822944641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09885358810425</t>
+    <t xml:space="preserve">3.00867128372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02040934562683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96824288368225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00736737251282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05822920799255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09885382652283</t>
   </si>
   <si>
     <t xml:space="preserve">3.15591311454773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09613704681396</t>
+    <t xml:space="preserve">3.09613680839539</t>
   </si>
   <si>
     <t xml:space="preserve">3.13825178146362</t>
@@ -416,40 +416,40 @@
     <t xml:space="preserve">3.09070301055908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97658443450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13417673110962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20074534416199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24965310096741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28769254684448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23063373565674</t>
+    <t xml:space="preserve">2.97658467292786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13417649269104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20074486732483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24965286254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28769278526306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23063349723816</t>
   </si>
   <si>
     <t xml:space="preserve">3.24557757377625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22248196601868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25101137161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18715977668762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09477853775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11379790306091</t>
+    <t xml:space="preserve">3.22248220443726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25101208686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1871600151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0947790145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11379814147949</t>
   </si>
   <si>
     <t xml:space="preserve">3.19938683509827</t>
@@ -461,37 +461,37 @@
     <t xml:space="preserve">3.12059092521667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15727162361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16270589828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14504480361938</t>
+    <t xml:space="preserve">3.15727186203003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16270637512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14504456520081</t>
   </si>
   <si>
     <t xml:space="preserve">3.03907799720764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02820992469788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96707439422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00375556945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03636074066162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02005815505981</t>
+    <t xml:space="preserve">3.02820944786072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96707463264465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00375533103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03636026382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02005839347839</t>
   </si>
   <si>
     <t xml:space="preserve">2.97794270515442</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9860942363739</t>
+    <t xml:space="preserve">2.98609471321106</t>
   </si>
   <si>
     <t xml:space="preserve">2.99560403823853</t>
@@ -500,34 +500,34 @@
     <t xml:space="preserve">3.07575845718384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08390974998474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12466645240784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10836362838745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12874174118042</t>
+    <t xml:space="preserve">3.0839102268219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12466669082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10836386680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12874221801758</t>
   </si>
   <si>
     <t xml:space="preserve">3.17900848388672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17221546173096</t>
+    <t xml:space="preserve">3.17221593856812</t>
   </si>
   <si>
     <t xml:space="preserve">3.12602543830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15863060951233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22519898414612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26052212715149</t>
+    <t xml:space="preserve">3.15863013267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22519946098328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26052165031433</t>
   </si>
   <si>
     <t xml:space="preserve">3.25237035751343</t>
@@ -536,124 +536,124 @@
     <t xml:space="preserve">3.27682447433472</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30671191215515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30263686180115</t>
+    <t xml:space="preserve">3.30671262741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30263662338257</t>
   </si>
   <si>
     <t xml:space="preserve">3.2808997631073</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21025490760803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2836172580719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29856109619141</t>
+    <t xml:space="preserve">3.21025514602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28361701965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29856133460999</t>
   </si>
   <si>
     <t xml:space="preserve">3.28225779533386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26323843002319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25644588470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27003169059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24693632125854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23335075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21976470947266</t>
+    <t xml:space="preserve">3.26323866844177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25644612312317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27003145217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24693655967712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23335099220276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21976518630981</t>
   </si>
   <si>
     <t xml:space="preserve">3.24150133132935</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26188015937805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23470854759216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19802856445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23742628097534</t>
+    <t xml:space="preserve">3.26188039779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2347092628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19802832603455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23742604255676</t>
   </si>
   <si>
     <t xml:space="preserve">3.24829459190369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22791624069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19395279884338</t>
+    <t xml:space="preserve">3.22791600227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1939525604248</t>
   </si>
   <si>
     <t xml:space="preserve">3.16542315483093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18444299697876</t>
+    <t xml:space="preserve">3.18444275856018</t>
   </si>
   <si>
     <t xml:space="preserve">3.18172574043274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20753860473633</t>
+    <t xml:space="preserve">3.20753836631775</t>
   </si>
   <si>
     <t xml:space="preserve">3.24014329910278</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26731419563293</t>
+    <t xml:space="preserve">3.26731443405151</t>
   </si>
   <si>
     <t xml:space="preserve">3.24286031723022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22655749320984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2319917678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20617961883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14640331268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16814064979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157132148743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678166389465</t>
+    <t xml:space="preserve">3.226557970047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23199200630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20617938041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14640355110168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16814017295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157108306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678142547607</t>
   </si>
   <si>
     <t xml:space="preserve">3.21704792976379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22927474975586</t>
+    <t xml:space="preserve">3.22927522659302</t>
   </si>
   <si>
     <t xml:space="preserve">3.24421906471252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21433091163635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25372838973999</t>
+    <t xml:space="preserve">3.21433067321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25372886657715</t>
   </si>
   <si>
     <t xml:space="preserve">3.35154485702515</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">3.49147534370422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39365935325623</t>
+    <t xml:space="preserve">3.3936595916748</t>
   </si>
   <si>
     <t xml:space="preserve">3.46430420875549</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">3.50506114959717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41675472259521</t>
+    <t xml:space="preserve">3.41675519943237</t>
   </si>
   <si>
     <t xml:space="preserve">3.40656542778015</t>
@@ -680,31 +680,31 @@
     <t xml:space="preserve">3.44732189178467</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4337363243103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42694401741028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4710967540741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46770048141479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48128652572632</t>
+    <t xml:space="preserve">3.43373608589172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42694449424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47109746932983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46770071983337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48128604888916</t>
   </si>
   <si>
     <t xml:space="preserve">3.50166440010071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54242086410522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51185297966003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54581713676453</t>
+    <t xml:space="preserve">3.5424211025238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51185393333435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54581737518311</t>
   </si>
   <si>
     <t xml:space="preserve">3.55940246582031</t>
@@ -713,16 +713,16 @@
     <t xml:space="preserve">3.63412308692932</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60015964508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53223133087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48468279838562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55260992050171</t>
+    <t xml:space="preserve">3.60015916824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53223180770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48468232154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55261039733887</t>
   </si>
   <si>
     <t xml:space="preserve">3.61374521255493</t>
@@ -734,16 +734,16 @@
     <t xml:space="preserve">3.58997011184692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60355567932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59336686134338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62053775787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59676289558411</t>
+    <t xml:space="preserve">3.60355496406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5933666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62053751945496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59676313400269</t>
   </si>
   <si>
     <t xml:space="preserve">3.5661952495575</t>
@@ -758,28 +758,28 @@
     <t xml:space="preserve">3.45751166343689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39637684822083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3230152130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3827908039093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40996241569519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38958382606506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32844924926758</t>
+    <t xml:space="preserve">3.39637660980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32301497459412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38279128074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40996193885803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38958430290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32844877243042</t>
   </si>
   <si>
     <t xml:space="preserve">3.30807089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31078815460205</t>
+    <t xml:space="preserve">3.31078791618347</t>
   </si>
   <si>
     <t xml:space="preserve">3.35018587112427</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">3.37328124046326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34339332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3664882183075</t>
+    <t xml:space="preserve">3.34339308738708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36648893356323</t>
   </si>
   <si>
     <t xml:space="preserve">3.37871527671814</t>
@@ -806,25 +806,25 @@
     <t xml:space="preserve">3.36105442047119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12127017974854</t>
+    <t xml:space="preserve">3.12126970291138</t>
   </si>
   <si>
     <t xml:space="preserve">3.16406440734863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06624865531921</t>
+    <t xml:space="preserve">3.06624889373779</t>
   </si>
   <si>
     <t xml:space="preserve">3.04587078094482</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03228497505188</t>
+    <t xml:space="preserve">3.03228521347046</t>
   </si>
   <si>
     <t xml:space="preserve">3.00239706039429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0220959186554</t>
+    <t xml:space="preserve">3.02209568023682</t>
   </si>
   <si>
     <t xml:space="preserve">3.02549242973328</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">3.04655003547668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99424600601196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96164083480835</t>
+    <t xml:space="preserve">2.9942455291748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96164059638977</t>
   </si>
   <si>
     <t xml:space="preserve">2.97862267494202</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11651468276978</t>
+    <t xml:space="preserve">3.11651515960693</t>
   </si>
   <si>
     <t xml:space="preserve">3.06828689575195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00035881996155</t>
+    <t xml:space="preserve">3.00035905838013</t>
   </si>
   <si>
     <t xml:space="preserve">2.96639537811279</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">2.92903518676758</t>
   </si>
   <si>
-    <t xml:space="preserve">2.924959897995</t>
+    <t xml:space="preserve">2.92495965957642</t>
   </si>
   <si>
     <t xml:space="preserve">3.01326537132263</t>
@@ -869,28 +869,28 @@
     <t xml:space="preserve">3.0940990447998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14300680160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23538851737976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2272367477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21297287940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1932737827301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27342748641968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29448533058167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20414209365845</t>
+    <t xml:space="preserve">3.1430070400238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23538827896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22723698616028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21297216415405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19327354431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27342796325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29448485374451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20414161682129</t>
   </si>
   <si>
     <t xml:space="preserve">3.30739164352417</t>
@@ -905,118 +905,118 @@
     <t xml:space="preserve">3.39909410476685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47924852371216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47517275810242</t>
+    <t xml:space="preserve">3.47924828529358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47517228126526</t>
   </si>
   <si>
     <t xml:space="preserve">3.48196578025818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43713307380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4439263343811</t>
+    <t xml:space="preserve">3.43713331222534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44392585754395</t>
   </si>
   <si>
     <t xml:space="preserve">3.49962615966797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52815580368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47788953781128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51457047462463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45887041091919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5267972946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52000451087952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57570552825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62733030319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64499139785767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60423517227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60287594795227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62597179412842</t>
+    <t xml:space="preserve">3.528156042099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47788906097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51456999778748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45887017250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52679777145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52000498771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5757052898407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6273307800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64499115943909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60423493385315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60287618637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62597131729126</t>
   </si>
   <si>
     <t xml:space="preserve">3.49419236183167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45615220069885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41539621353149</t>
+    <t xml:space="preserve">3.45615267753601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41539669036865</t>
   </si>
   <si>
     <t xml:space="preserve">3.45479440689087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44256782531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36309218406677</t>
+    <t xml:space="preserve">3.44256734848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36309266090393</t>
   </si>
   <si>
     <t xml:space="preserve">3.39298033714294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39461970329285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45400094985962</t>
+    <t xml:space="preserve">3.39462018013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4540011882782</t>
   </si>
   <si>
     <t xml:space="preserve">3.46107006072998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36280846595764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28151297569275</t>
+    <t xml:space="preserve">3.36280798912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28151249885559</t>
   </si>
   <si>
     <t xml:space="preserve">3.23414897918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07367897033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16699194908142</t>
+    <t xml:space="preserve">3.07367920875549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1669921875</t>
   </si>
   <si>
     <t xml:space="preserve">3.15285396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18961381912231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27868556976318</t>
+    <t xml:space="preserve">3.18961358070374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27868509292603</t>
   </si>
   <si>
     <t xml:space="preserve">3.25747752189636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23556327819824</t>
+    <t xml:space="preserve">3.23556351661682</t>
   </si>
   <si>
     <t xml:space="preserve">3.23768377304077</t>
@@ -1025,22 +1025,22 @@
     <t xml:space="preserve">3.20163106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34089374542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43774151802063</t>
+    <t xml:space="preserve">3.34089422225952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43774199485779</t>
   </si>
   <si>
     <t xml:space="preserve">3.39037752151489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4108784198761</t>
+    <t xml:space="preserve">3.41087889671326</t>
   </si>
   <si>
     <t xml:space="preserve">3.37623977661133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38967156410217</t>
+    <t xml:space="preserve">3.38967108726501</t>
   </si>
   <si>
     <t xml:space="preserve">3.40946507453918</t>
@@ -1049,22 +1049,22 @@
     <t xml:space="preserve">3.46319055557251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33735966682434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31544470787048</t>
+    <t xml:space="preserve">3.33735942840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31544518470764</t>
   </si>
   <si>
     <t xml:space="preserve">3.29989290237427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34442830085754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35432553291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32958340644836</t>
+    <t xml:space="preserve">3.34442853927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35432529449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32958316802979</t>
   </si>
   <si>
     <t xml:space="preserve">3.33806610107422</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">3.29211616516113</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35644602775574</t>
+    <t xml:space="preserve">3.3564465045929</t>
   </si>
   <si>
     <t xml:space="preserve">3.3522047996521</t>
@@ -1082,43 +1082,43 @@
     <t xml:space="preserve">3.40098166465759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41865515708923</t>
+    <t xml:space="preserve">3.41865491867065</t>
   </si>
   <si>
     <t xml:space="preserve">3.37765336036682</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32534193992615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35573935508728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34230756759644</t>
+    <t xml:space="preserve">3.32534170150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35573983192444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34230780601501</t>
   </si>
   <si>
     <t xml:space="preserve">3.40027499198914</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45258688926697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44834542274475</t>
+    <t xml:space="preserve">3.45258712768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44834518432617</t>
   </si>
   <si>
     <t xml:space="preserve">3.44268989562988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45117330551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41229295730591</t>
+    <t xml:space="preserve">3.45117282867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41229271888733</t>
   </si>
   <si>
     <t xml:space="preserve">3.40734434127808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46036291122437</t>
+    <t xml:space="preserve">3.46036338806152</t>
   </si>
   <si>
     <t xml:space="preserve">3.4313793182373</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">3.42077565193176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42572450637817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51479554176331</t>
+    <t xml:space="preserve">3.42572426795959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51479601860046</t>
   </si>
   <si>
     <t xml:space="preserve">3.49429488182068</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">3.39532661437988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41582751274109</t>
+    <t xml:space="preserve">3.41582703590393</t>
   </si>
   <si>
     <t xml:space="preserve">3.4292585849762</t>
@@ -1154,22 +1154,22 @@
     <t xml:space="preserve">3.36139464378357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38825726509094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43279314041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33594536781311</t>
+    <t xml:space="preserve">3.38825750350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43279337882996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33594560623169</t>
   </si>
   <si>
     <t xml:space="preserve">3.29706501960754</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30413413047791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30837559700012</t>
+    <t xml:space="preserve">3.30413365364075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30837535858154</t>
   </si>
   <si>
     <t xml:space="preserve">3.28787517547607</t>
@@ -1178,22 +1178,22 @@
     <t xml:space="preserve">3.31615138053894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25182247161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28999519348145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33311796188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33099699020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33382487297058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32675552368164</t>
+    <t xml:space="preserve">3.25182223320007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28999590873718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3331184387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33099675178528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.333824634552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32675576210022</t>
   </si>
   <si>
     <t xml:space="preserve">3.34654951095581</t>
@@ -1205,34 +1205,34 @@
     <t xml:space="preserve">3.49924325942993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49641609191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46248292922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45682835578918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45470762252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38613700866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45753526687622</t>
+    <t xml:space="preserve">3.49641585350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46248340606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45682883262634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4547073841095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38613653182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45753502845764</t>
   </si>
   <si>
     <t xml:space="preserve">3.45894908905029</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37411856651306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39391255378723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42006802558899</t>
+    <t xml:space="preserve">3.37411880493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39391279220581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42006850242615</t>
   </si>
   <si>
     <t xml:space="preserve">3.30978965759277</t>
@@ -1250,52 +1250,52 @@
     <t xml:space="preserve">3.24899458885193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21011400222778</t>
+    <t xml:space="preserve">3.21011352539062</t>
   </si>
   <si>
     <t xml:space="preserve">3.23485612869263</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20516562461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15780186653137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13093900680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15356087684631</t>
+    <t xml:space="preserve">3.20516586303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15780210494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13093948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15356040000916</t>
   </si>
   <si>
     <t xml:space="preserve">3.24546003341675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16911292076111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19809627532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18890690803528</t>
+    <t xml:space="preserve">3.16911244392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19809651374817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1889066696167</t>
   </si>
   <si>
     <t xml:space="preserve">3.23909759521484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23344206809998</t>
+    <t xml:space="preserve">3.2334418296814</t>
   </si>
   <si>
     <t xml:space="preserve">3.27727150917053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23202848434448</t>
+    <t xml:space="preserve">3.23202872276306</t>
   </si>
   <si>
     <t xml:space="preserve">3.22920083999634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22495913505554</t>
+    <t xml:space="preserve">3.22495937347412</t>
   </si>
   <si>
     <t xml:space="preserve">3.27232313156128</t>
@@ -1307,46 +1307,46 @@
     <t xml:space="preserve">3.37341213226318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4250168800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43491435050964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48863935470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44693112373352</t>
+    <t xml:space="preserve">3.42501664161682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43491458892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48864006996155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44693160057068</t>
   </si>
   <si>
     <t xml:space="preserve">3.38755035400391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35927367210388</t>
+    <t xml:space="preserve">3.35927319526672</t>
   </si>
   <si>
     <t xml:space="preserve">3.34160113334656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3005998134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3048415184021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2758572101593</t>
+    <t xml:space="preserve">3.30059957504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30484127998352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27585744857788</t>
   </si>
   <si>
     <t xml:space="preserve">3.39603352546692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34937644004822</t>
+    <t xml:space="preserve">3.34937691688538</t>
   </si>
   <si>
     <t xml:space="preserve">3.36068749427795</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36704993247986</t>
+    <t xml:space="preserve">3.3670494556427</t>
   </si>
   <si>
     <t xml:space="preserve">3.3917920589447</t>
@@ -1355,19 +1355,19 @@
     <t xml:space="preserve">3.41653394699097</t>
   </si>
   <si>
-    <t xml:space="preserve">3.453293800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52327942848206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59114289283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61235070228577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63073062896729</t>
+    <t xml:space="preserve">3.45329427719116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5232789516449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59114265441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61235094070435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63073039054871</t>
   </si>
   <si>
     <t xml:space="preserve">3.61093616485596</t>
@@ -1376,13 +1376,13 @@
     <t xml:space="preserve">3.62790250778198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60103964805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59962582588196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51055455207825</t>
+    <t xml:space="preserve">3.60104012489319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59962558746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51055383682251</t>
   </si>
   <si>
     <t xml:space="preserve">3.53176188468933</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">3.57841801643372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61941957473755</t>
+    <t xml:space="preserve">3.61941933631897</t>
   </si>
   <si>
     <t xml:space="preserve">3.64911007881165</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67880058288574</t>
+    <t xml:space="preserve">3.67880082130432</t>
   </si>
   <si>
     <t xml:space="preserve">3.62083339691162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6858696937561</t>
+    <t xml:space="preserve">3.68587040901184</t>
   </si>
   <si>
     <t xml:space="preserve">3.70849084854126</t>
@@ -1415,73 +1415,73 @@
     <t xml:space="preserve">3.68304204940796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68728399276733</t>
+    <t xml:space="preserve">3.68728375434875</t>
   </si>
   <si>
     <t xml:space="preserve">3.67738699913025</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71414685249329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71131896972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70990514755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72545695304871</t>
+    <t xml:space="preserve">3.71414637565613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7113184928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70990490913391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72545671463013</t>
   </si>
   <si>
     <t xml:space="preserve">3.7325267791748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73111248016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67173147201538</t>
+    <t xml:space="preserve">3.73111200332642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67173171043396</t>
   </si>
   <si>
     <t xml:space="preserve">3.69293904304504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71980237960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63779997825623</t>
+    <t xml:space="preserve">3.719801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63779950141907</t>
   </si>
   <si>
     <t xml:space="preserve">3.61517786979675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68869757652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69576716423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69435262680054</t>
+    <t xml:space="preserve">3.68869733810425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69576668739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6943531036377</t>
   </si>
   <si>
     <t xml:space="preserve">3.69718074798584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68162846565247</t>
+    <t xml:space="preserve">3.68162798881531</t>
   </si>
   <si>
     <t xml:space="preserve">3.75232028961182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74383687973022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72262907028198</t>
+    <t xml:space="preserve">3.74383759498596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72262930870056</t>
   </si>
   <si>
     <t xml:space="preserve">3.76504445075989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75938963890076</t>
+    <t xml:space="preserve">3.75938940048218</t>
   </si>
   <si>
     <t xml:space="preserve">3.71697449684143</t>
@@ -1490,85 +1490,85 @@
     <t xml:space="preserve">3.78342461585999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83997845649719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86542654037476</t>
+    <t xml:space="preserve">3.83997774124146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86542725563049</t>
   </si>
   <si>
     <t xml:space="preserve">3.83573651313782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82442593574524</t>
+    <t xml:space="preserve">3.82442569732666</t>
   </si>
   <si>
     <t xml:space="preserve">3.79756355285645</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81735682487488</t>
+    <t xml:space="preserve">3.81735634803772</t>
   </si>
   <si>
     <t xml:space="preserve">3.85977149009705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86966824531555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88380718231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87532353401184</t>
+    <t xml:space="preserve">3.86966800689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88380765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.875324010849</t>
   </si>
   <si>
     <t xml:space="preserve">3.89370369911194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88804793357849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85270237922668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87108254432678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89087629318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84139180183411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88239312171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92339420318604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88946199417114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90360045433044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92056703567505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91915273666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96439552307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95732617378235</t>
+    <t xml:space="preserve">3.88804817199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85270261764526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87108182907104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89087557792664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84139204025269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88239288330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92339444160461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88946223258972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90360069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92056632041931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91915249824524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96439528465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95732688903809</t>
   </si>
   <si>
     <t xml:space="preserve">3.91067004203796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93329167366028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90642833709717</t>
+    <t xml:space="preserve">3.9332914352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90642809867859</t>
   </si>
   <si>
     <t xml:space="preserve">3.90501427650452</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">3.93046379089355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87956523895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89794516563416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88097882270813</t>
+    <t xml:space="preserve">3.87956595420837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89794492721558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88097929954529</t>
   </si>
   <si>
     <t xml:space="preserve">3.94742965698242</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">3.89228987693787</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87390947341919</t>
+    <t xml:space="preserve">3.87390995025635</t>
   </si>
   <si>
     <t xml:space="preserve">3.90925621986389</t>
@@ -1607,34 +1607,34 @@
     <t xml:space="preserve">3.95025658607483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.981360912323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00963830947876</t>
+    <t xml:space="preserve">3.98136115074158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00963878631592</t>
   </si>
   <si>
     <t xml:space="preserve">4.08032989501953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07891607284546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13016319274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16984796524048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21100330352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21394300460815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24921846389771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20512390136719</t>
+    <t xml:space="preserve">4.0789155960083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13016366958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16984748840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21100282669067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.213942527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24921798706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20512342453003</t>
   </si>
   <si>
     <t xml:space="preserve">4.19483518600464</t>
@@ -1646,10 +1646,10 @@
     <t xml:space="preserve">4.10811614990234</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16543865203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21541213989258</t>
+    <t xml:space="preserve">4.16543817520142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21541309356689</t>
   </si>
   <si>
     <t xml:space="preserve">4.26979541778564</t>
@@ -1658,31 +1658,31 @@
     <t xml:space="preserve">4.3050708770752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32123899459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36827230453491</t>
+    <t xml:space="preserve">4.32123851776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36827278137207</t>
   </si>
   <si>
     <t xml:space="preserve">4.33152723312378</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32564735412598</t>
+    <t xml:space="preserve">4.32564830780029</t>
   </si>
   <si>
     <t xml:space="preserve">4.288902759552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35651350021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34328556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49908494949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44764184951782</t>
+    <t xml:space="preserve">4.35651397705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34328508377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49908542633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44764232635498</t>
   </si>
   <si>
     <t xml:space="preserve">4.4461727142334</t>
@@ -1694,10 +1694,10 @@
     <t xml:space="preserve">4.48732709884644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45352172851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43735313415527</t>
+    <t xml:space="preserve">4.45352125167847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43735361099243</t>
   </si>
   <si>
     <t xml:space="preserve">4.35210466384888</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">4.33446645736694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4314751625061</t>
+    <t xml:space="preserve">4.43147468566895</t>
   </si>
   <si>
     <t xml:space="preserve">4.47997808456421</t>
@@ -1718,7 +1718,7 @@
     <t xml:space="preserve">4.44911193847656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43882274627686</t>
+    <t xml:space="preserve">4.43882322311401</t>
   </si>
   <si>
     <t xml:space="preserve">4.49467611312866</t>
@@ -1727,7 +1727,7 @@
     <t xml:space="preserve">4.51966238021851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50349521636963</t>
+    <t xml:space="preserve">4.50349473953247</t>
   </si>
   <si>
     <t xml:space="preserve">4.54317998886108</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">4.57698535919189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52701187133789</t>
+    <t xml:space="preserve">4.52701139450073</t>
   </si>
   <si>
     <t xml:space="preserve">4.54170989990234</t>
@@ -1757,43 +1757,43 @@
     <t xml:space="preserve">4.4255952835083</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38885021209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38150072097778</t>
+    <t xml:space="preserve">4.38884973526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38150024414062</t>
   </si>
   <si>
     <t xml:space="preserve">4.24480867385864</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20218372344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29037237167358</t>
+    <t xml:space="preserve">4.20218420028687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29037189483643</t>
   </si>
   <si>
     <t xml:space="preserve">4.29331254959106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27420473098755</t>
+    <t xml:space="preserve">4.27420425415039</t>
   </si>
   <si>
     <t xml:space="preserve">4.26097631454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28449249267578</t>
+    <t xml:space="preserve">4.2844934463501</t>
   </si>
   <si>
     <t xml:space="preserve">4.28743314743042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11399507522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16102981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24186849594116</t>
+    <t xml:space="preserve">4.11399555206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16102933883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24186897277832</t>
   </si>
   <si>
     <t xml:space="preserve">4.15662002563477</t>
@@ -1805,28 +1805,28 @@
     <t xml:space="preserve">4.2183518409729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20071458816528</t>
+    <t xml:space="preserve">4.20071411132812</t>
   </si>
   <si>
     <t xml:space="preserve">4.19777393341064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3403468132019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33593654632568</t>
+    <t xml:space="preserve">4.34034633636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33593702316284</t>
   </si>
   <si>
     <t xml:space="preserve">4.34916496276855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.313889503479</t>
+    <t xml:space="preserve">4.31388902664185</t>
   </si>
   <si>
     <t xml:space="preserve">4.30213117599487</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20806264877319</t>
+    <t xml:space="preserve">4.20806312561035</t>
   </si>
   <si>
     <t xml:space="preserve">4.14192199707031</t>
@@ -1835,40 +1835,40 @@
     <t xml:space="preserve">4.1037073135376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18307685852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14045190811157</t>
+    <t xml:space="preserve">4.18307638168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14045143127441</t>
   </si>
   <si>
     <t xml:space="preserve">4.12575387954712</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1933650970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18160676956177</t>
+    <t xml:space="preserve">4.19336557388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18160724639893</t>
   </si>
   <si>
     <t xml:space="preserve">4.18454647064209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25215816497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29919147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39031982421875</t>
+    <t xml:space="preserve">4.25215768814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29919099807739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39031934738159</t>
   </si>
   <si>
     <t xml:space="preserve">4.32711791992188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30066108703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21247243881226</t>
+    <t xml:space="preserve">4.30066156387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21247291564941</t>
   </si>
   <si>
     <t xml:space="preserve">4.31241941452026</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">4.18895578384399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23011064529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18748569488525</t>
+    <t xml:space="preserve">4.23011016845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18748617172241</t>
   </si>
   <si>
     <t xml:space="preserve">4.17425680160522</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">4.1727876663208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14486169815063</t>
+    <t xml:space="preserve">4.14486122131348</t>
   </si>
   <si>
     <t xml:space="preserve">4.1683783531189</t>
@@ -1907,46 +1907,46 @@
     <t xml:space="preserve">4.238929271698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25362682342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29478216171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33740663528442</t>
+    <t xml:space="preserve">4.25362730026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29478168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33740615844727</t>
   </si>
   <si>
     <t xml:space="preserve">4.35063457489014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28302383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33299732208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30654048919678</t>
+    <t xml:space="preserve">4.2830228805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33299684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30654096603394</t>
   </si>
   <si>
     <t xml:space="preserve">4.37268114089966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39178895950317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27861452102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22423076629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23745965957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22570085525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19189596176147</t>
+    <t xml:space="preserve">4.39178943634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27861404418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2242317199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23745918273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22570037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19189548492432</t>
   </si>
   <si>
     <t xml:space="preserve">4.22129154205322</t>
@@ -1958,10 +1958,10 @@
     <t xml:space="preserve">4.22717094421387</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00963926315308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07431077957153</t>
+    <t xml:space="preserve">4.00963973999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07431125640869</t>
   </si>
   <si>
     <t xml:space="preserve">4.08900880813599</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">4.01992702484131</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95378637313843</t>
+    <t xml:space="preserve">3.95378684997559</t>
   </si>
   <si>
     <t xml:space="preserve">3.99494099617004</t>
@@ -1985,7 +1985,7 @@
     <t xml:space="preserve">3.99053120613098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03609561920166</t>
+    <t xml:space="preserve">4.0360951423645</t>
   </si>
   <si>
     <t xml:space="preserve">4.1066460609436</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">4.13751220703125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00081968307495</t>
+    <t xml:space="preserve">4.00082063674927</t>
   </si>
   <si>
     <t xml:space="preserve">4.09194803237915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08459949493408</t>
+    <t xml:space="preserve">4.08459901809692</t>
   </si>
   <si>
     <t xml:space="preserve">4.02727651596069</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">4.02286720275879</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10076761245728</t>
+    <t xml:space="preserve">4.10076713562012</t>
   </si>
   <si>
     <t xml:space="preserve">4.20365381240845</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">4.13898229598999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25068759918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20659351348877</t>
+    <t xml:space="preserve">4.25068807601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20659303665161</t>
   </si>
   <si>
     <t xml:space="preserve">4.263916015625</t>
@@ -2036,7 +2036,7 @@
     <t xml:space="preserve">4.30801057815552</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48144769668579</t>
+    <t xml:space="preserve">4.48144817352295</t>
   </si>
   <si>
     <t xml:space="preserve">4.51525354385376</t>
@@ -2045,22 +2045,22 @@
     <t xml:space="preserve">4.49761533737183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40648746490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41677618026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46674966812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4917368888855</t>
+    <t xml:space="preserve">4.40648651123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41677665710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46674919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49173641204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.46087026596069</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46234035491943</t>
+    <t xml:space="preserve">4.46233987808228</t>
   </si>
   <si>
     <t xml:space="preserve">4.51231384277344</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">4.45205163955688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4858570098877</t>
+    <t xml:space="preserve">4.48585748672485</t>
   </si>
   <si>
     <t xml:space="preserve">4.62548923492432</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26538515090942</t>
+    <t xml:space="preserve">4.26538562774658</t>
   </si>
   <si>
     <t xml:space="preserve">4.26244640350342</t>
@@ -2084,46 +2084,46 @@
     <t xml:space="preserve">4.06549215316772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08606863021851</t>
+    <t xml:space="preserve">4.08606958389282</t>
   </si>
   <si>
     <t xml:space="preserve">3.72890543937683</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51798820495605</t>
+    <t xml:space="preserve">3.51798844337463</t>
   </si>
   <si>
     <t xml:space="preserve">3.50182008743286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02192759513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24754309654236</t>
+    <t xml:space="preserve">3.02192735671997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24754357337952</t>
   </si>
   <si>
     <t xml:space="preserve">3.15127062797546</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27032518386841</t>
+    <t xml:space="preserve">3.27032470703125</t>
   </si>
   <si>
     <t xml:space="preserve">3.29531240463257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35189938545227</t>
+    <t xml:space="preserve">3.35189986228943</t>
   </si>
   <si>
     <t xml:space="preserve">3.21153259277344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.129958152771</t>
+    <t xml:space="preserve">3.12995839118958</t>
   </si>
   <si>
     <t xml:space="preserve">3.35557413101196</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38937973976135</t>
+    <t xml:space="preserve">3.38937926292419</t>
   </si>
   <si>
     <t xml:space="preserve">3.34381556510925</t>
@@ -2135,25 +2135,25 @@
     <t xml:space="preserve">3.5709011554718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66643857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44964170455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55693817138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58780384063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53636050224304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54958868026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46581029891968</t>
+    <t xml:space="preserve">3.66643905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44964146614075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55693793296814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58780336380005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53636002540588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54958891868591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46580982208252</t>
   </si>
   <si>
     <t xml:space="preserve">3.54811906814575</t>
@@ -2165,13 +2165,13 @@
     <t xml:space="preserve">3.59368348121643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62601900100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57163572311401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57310581207275</t>
+    <t xml:space="preserve">3.62601923942566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57163596153259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57310509681702</t>
   </si>
   <si>
     <t xml:space="preserve">3.44082307815552</t>
@@ -2180,16 +2180,16 @@
     <t xml:space="preserve">3.61720013618469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52754211425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57457494735718</t>
+    <t xml:space="preserve">3.52754163742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57457518577576</t>
   </si>
   <si>
     <t xml:space="preserve">3.56722688674927</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57898497581482</t>
+    <t xml:space="preserve">3.57898473739624</t>
   </si>
   <si>
     <t xml:space="preserve">3.75168776512146</t>
@@ -2198,13 +2198,13 @@
     <t xml:space="preserve">3.68187189102173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70391845703125</t>
+    <t xml:space="preserve">3.70391869544983</t>
   </si>
   <si>
     <t xml:space="preserve">3.60691118240356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61279082298279</t>
+    <t xml:space="preserve">3.61279058456421</t>
   </si>
   <si>
     <t xml:space="preserve">3.66423416137695</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">3.63189768791199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62454962730408</t>
+    <t xml:space="preserve">3.62454915046692</t>
   </si>
   <si>
     <t xml:space="preserve">3.63777732849121</t>
@@ -2228,28 +2228,28 @@
     <t xml:space="preserve">3.73626279830933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60662746429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66372871398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63440632820129</t>
+    <t xml:space="preserve">3.60662722587585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66372919082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63440656661987</t>
   </si>
   <si>
     <t xml:space="preserve">3.68533492088318</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75015211105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73008966445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70231056213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80725288391113</t>
+    <t xml:space="preserve">3.75015234947205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73008918762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70231080055237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80725336074829</t>
   </si>
   <si>
     <t xml:space="preserve">3.77021479606628</t>
@@ -2258,34 +2258,34 @@
     <t xml:space="preserve">3.81959939002991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90447926521301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99707531929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05109024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02408266067505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92762875556946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88133025169373</t>
+    <t xml:space="preserve">3.90447950363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99707508087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05108976364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02408361434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92762899398804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8813304901123</t>
   </si>
   <si>
     <t xml:space="preserve">3.81651282310486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91991209983826</t>
+    <t xml:space="preserve">3.9199116230011</t>
   </si>
   <si>
     <t xml:space="preserve">4.08581352233887</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0588059425354</t>
+    <t xml:space="preserve">4.05880689620972</t>
   </si>
   <si>
     <t xml:space="preserve">4.10896253585815</t>
@@ -2309,22 +2309,22 @@
     <t xml:space="preserve">4.08967208862305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03179883956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07038116455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11282062530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05494832992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95463585853577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96235203742981</t>
+    <t xml:space="preserve">4.03179931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07038164138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11282110214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0549488067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95463538169861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96235227584839</t>
   </si>
   <si>
     <t xml:space="preserve">3.93534445762634</t>
@@ -2333,19 +2333,19 @@
     <t xml:space="preserve">3.97006821632385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97392630577087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0742392539978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1243953704834</t>
+    <t xml:space="preserve">3.97392654418945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07423973083496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12439489364624</t>
   </si>
   <si>
     <t xml:space="preserve">4.10510492324829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09352970123291</t>
+    <t xml:space="preserve">4.09353017807007</t>
   </si>
   <si>
     <t xml:space="preserve">4.04723167419434</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">4.12825345993042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25943183898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26714897155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21313381195068</t>
+    <t xml:space="preserve">4.2594313621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26714849472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21313333511353</t>
   </si>
   <si>
     <t xml:space="preserve">4.19770097732544</t>
@@ -2381,13 +2381,13 @@
     <t xml:space="preserve">4.36746120452881</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42147588729858</t>
+    <t xml:space="preserve">4.42147541046143</t>
   </si>
   <si>
     <t xml:space="preserve">4.3906102180481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37517786026001</t>
+    <t xml:space="preserve">4.37517738342285</t>
   </si>
   <si>
     <t xml:space="preserve">4.36360311508179</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">4.30572986602783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26328992843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24399948120117</t>
+    <t xml:space="preserve">4.26329040527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24399900436401</t>
   </si>
   <si>
     <t xml:space="preserve">4.31344652175903</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">4.30187129974365</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13597011566162</t>
+    <t xml:space="preserve">4.13597059249878</t>
   </si>
   <si>
     <t xml:space="preserve">4.22856616973877</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">4.18612670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17455148696899</t>
+    <t xml:space="preserve">4.17455196380615</t>
   </si>
   <si>
     <t xml:space="preserve">4.18998432159424</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">4.17841005325317</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15526103973389</t>
+    <t xml:space="preserve">4.15526151657104</t>
   </si>
   <si>
     <t xml:space="preserve">4.15140295028687</t>
@@ -2438,52 +2438,52 @@
     <t xml:space="preserve">4.15911960601807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19384241104126</t>
+    <t xml:space="preserve">4.19384288787842</t>
   </si>
   <si>
     <t xml:space="preserve">4.07809782028198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89290452003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9777843952179</t>
+    <t xml:space="preserve">3.89290475845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97778487205505</t>
   </si>
   <si>
     <t xml:space="preserve">4.06266450881958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94691920280457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9855010509491</t>
+    <t xml:space="preserve">3.94691967964172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98550128936768</t>
   </si>
   <si>
     <t xml:space="preserve">3.98164296150208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88904595375061</t>
+    <t xml:space="preserve">3.88904643058777</t>
   </si>
   <si>
     <t xml:space="preserve">3.71157050132751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72700262069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8288586139679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8319456577301</t>
+    <t xml:space="preserve">3.72700309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82885885238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83194541931152</t>
   </si>
   <si>
     <t xml:space="preserve">3.86589789390564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00479125976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95077776908875</t>
+    <t xml:space="preserve">4.00479221343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95077705383301</t>
   </si>
   <si>
     <t xml:space="preserve">4.08195543289185</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">4.03951549530029</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13982772827148</t>
+    <t xml:space="preserve">4.1398286819458</t>
   </si>
   <si>
     <t xml:space="preserve">4.17069387435913</t>
@@ -2501,22 +2501,22 @@
     <t xml:space="preserve">4.14368629455566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1321120262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93920302391052</t>
+    <t xml:space="preserve">4.13211154937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93920278549194</t>
   </si>
   <si>
     <t xml:space="preserve">3.90062117576599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80879664421082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99321818351746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01250791549683</t>
+    <t xml:space="preserve">3.80879640579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9932177066803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01250839233398</t>
   </si>
   <si>
     <t xml:space="preserve">3.95849394798279</t>
@@ -2528,19 +2528,19 @@
     <t xml:space="preserve">3.93148589134216</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92377018928528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86203932762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81805610656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80571031570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85818123817444</t>
+    <t xml:space="preserve">3.92377066612244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86203980445862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81805634498596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80570983886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85818099975586</t>
   </si>
   <si>
     <t xml:space="preserve">3.89676308631897</t>
@@ -2549,13 +2549,13 @@
     <t xml:space="preserve">3.85663795471191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82114267349243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83811902999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94306111335754</t>
+    <t xml:space="preserve">3.82114291191101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83811807632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9430615901947</t>
   </si>
   <si>
     <t xml:space="preserve">3.90833783149719</t>
@@ -2564,22 +2564,22 @@
     <t xml:space="preserve">3.88518834114075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83503174781799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76712822914124</t>
+    <t xml:space="preserve">3.83503150939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7671275138855</t>
   </si>
   <si>
     <t xml:space="preserve">3.76249814033508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82268571853638</t>
+    <t xml:space="preserve">3.8226854801178</t>
   </si>
   <si>
     <t xml:space="preserve">3.79799342155457</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87361407279968</t>
+    <t xml:space="preserve">3.87361335754395</t>
   </si>
   <si>
     <t xml:space="preserve">4.02794075012207</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">4.25171566009521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25557374954224</t>
+    <t xml:space="preserve">4.25557327270508</t>
   </si>
   <si>
     <t xml:space="preserve">4.3173041343689</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">4.14985942840576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12979698181152</t>
+    <t xml:space="preserve">4.12979745864868</t>
   </si>
   <si>
     <t xml:space="preserve">4.14059972763062</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">4.16837930679321</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1714653968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19924402236938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23628234863281</t>
+    <t xml:space="preserve">4.17146587371826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19924449920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23628282546997</t>
   </si>
   <si>
     <t xml:space="preserve">4.18844127655029</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">4.1776385307312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17918157577515</t>
+    <t xml:space="preserve">4.17918109893799</t>
   </si>
   <si>
     <t xml:space="preserve">4.1838116645813</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">4.20387411117554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18535423278809</t>
+    <t xml:space="preserve">4.18535470962524</t>
   </si>
   <si>
     <t xml:space="preserve">4.21622037887573</t>
@@ -2663,13 +2663,13 @@
     <t xml:space="preserve">4.29338407516479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23165321350098</t>
+    <t xml:space="preserve">4.23165369033813</t>
   </si>
   <si>
     <t xml:space="preserve">4.25017213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23782634735107</t>
+    <t xml:space="preserve">4.23782587051392</t>
   </si>
   <si>
     <t xml:space="preserve">4.35048532485962</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">4.34122562408447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39369630813599</t>
+    <t xml:space="preserve">4.39369678497314</t>
   </si>
   <si>
     <t xml:space="preserve">4.47086048126221</t>
@@ -2687,13 +2687,13 @@
     <t xml:space="preserve">4.46610307693481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44024991989136</t>
+    <t xml:space="preserve">4.44025039672852</t>
   </si>
   <si>
     <t xml:space="preserve">4.3885440826416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35622787475586</t>
+    <t xml:space="preserve">4.35622835159302</t>
   </si>
   <si>
     <t xml:space="preserve">4.38531255722046</t>
@@ -2702,19 +2702,19 @@
     <t xml:space="preserve">4.37400197982788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39015960693359</t>
+    <t xml:space="preserve">4.39016008377075</t>
   </si>
   <si>
     <t xml:space="preserve">4.37723398208618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40147066116333</t>
+    <t xml:space="preserve">4.40147113800049</t>
   </si>
   <si>
     <t xml:space="preserve">4.45156097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47418212890625</t>
+    <t xml:space="preserve">4.47418260574341</t>
   </si>
   <si>
     <t xml:space="preserve">4.49357175827026</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">4.52911996841431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55174160003662</t>
+    <t xml:space="preserve">4.55174112319946</t>
   </si>
   <si>
     <t xml:space="preserve">4.55012512207031</t>
@@ -2735,16 +2735,16 @@
     <t xml:space="preserve">4.62122058868408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58405733108521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56628322601318</t>
+    <t xml:space="preserve">4.58405685424805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56628370285034</t>
   </si>
   <si>
     <t xml:space="preserve">4.54527807235718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52750396728516</t>
+    <t xml:space="preserve">4.52750444412231</t>
   </si>
   <si>
     <t xml:space="preserve">4.45640802383423</t>
@@ -2756,19 +2756,19 @@
     <t xml:space="preserve">4.48226118087769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48710918426514</t>
+    <t xml:space="preserve">4.48710870742798</t>
   </si>
   <si>
     <t xml:space="preserve">4.45317697525024</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46771955490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49841976165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50649881362915</t>
+    <t xml:space="preserve">4.46771907806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49841928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50649833679199</t>
   </si>
   <si>
     <t xml:space="preserve">4.55335712432861</t>
@@ -2777,10 +2777,10 @@
     <t xml:space="preserve">4.4790301322937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52265644073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54204654693604</t>
+    <t xml:space="preserve">4.52265739440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54204702377319</t>
   </si>
   <si>
     <t xml:space="preserve">4.54689359664917</t>
@@ -2792,10 +2792,10 @@
     <t xml:space="preserve">4.37884902954102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35461282730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37238597869873</t>
+    <t xml:space="preserve">4.35461235046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37238645553589</t>
   </si>
   <si>
     <t xml:space="preserve">4.53719902038574</t>
@@ -2810,19 +2810,19 @@
     <t xml:space="preserve">4.6147575378418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61637353897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62768459320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59375190734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60829496383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63091564178467</t>
+    <t xml:space="preserve">4.61637401580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62768411636353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59375286102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60829448699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63091611862183</t>
   </si>
   <si>
     <t xml:space="preserve">4.65676927566528</t>
@@ -2837,34 +2837,34 @@
     <t xml:space="preserve">4.73271179199219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76502847671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80219173431396</t>
+    <t xml:space="preserve">4.76502799987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80219221115112</t>
   </si>
   <si>
     <t xml:space="preserve">4.79896068572998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76987600326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82804489135742</t>
+    <t xml:space="preserve">4.76987504959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82804441452026</t>
   </si>
   <si>
     <t xml:space="preserve">4.82481384277344</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84420347213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80703926086426</t>
+    <t xml:space="preserve">4.84420299530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80703973770142</t>
   </si>
   <si>
     <t xml:space="preserve">4.69554853439331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57436323165894</t>
+    <t xml:space="preserve">4.57436275482178</t>
   </si>
   <si>
     <t xml:space="preserve">4.53558301925659</t>
@@ -2873,10 +2873,10 @@
     <t xml:space="preserve">4.59213638305664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54366207122803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49034070968628</t>
+    <t xml:space="preserve">4.54366159439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49034023284912</t>
   </si>
   <si>
     <t xml:space="preserve">4.49195623397827</t>
@@ -2885,13 +2885,13 @@
     <t xml:space="preserve">4.48549270629883</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45964050292969</t>
+    <t xml:space="preserve">4.45964002609253</t>
   </si>
   <si>
     <t xml:space="preserve">4.51134586334229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52427244186401</t>
+    <t xml:space="preserve">4.52427196502686</t>
   </si>
   <si>
     <t xml:space="preserve">4.46125555038452</t>
@@ -2900,7 +2900,7 @@
     <t xml:space="preserve">4.58567380905151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63576364517212</t>
+    <t xml:space="preserve">4.63576316833496</t>
   </si>
   <si>
     <t xml:space="preserve">4.58890438079834</t>
@@ -2909,31 +2909,31 @@
     <t xml:space="preserve">4.65353727340698</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57113122940063</t>
+    <t xml:space="preserve">4.57113075256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.4757981300354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42247629165649</t>
+    <t xml:space="preserve">4.42247581481934</t>
   </si>
   <si>
     <t xml:space="preserve">4.46933507919312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43217182159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47095108032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48387718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39985466003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37077045440674</t>
+    <t xml:space="preserve">4.43217134475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47095060348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48387765884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39985513687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37076997756958</t>
   </si>
   <si>
     <t xml:space="preserve">4.39662313461304</t>
@@ -2942,16 +2942,16 @@
     <t xml:space="preserve">4.41116571426392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51457786560059</t>
+    <t xml:space="preserve">4.51457738876343</t>
   </si>
   <si>
     <t xml:space="preserve">4.46287155151367</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43540239334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50003528594971</t>
+    <t xml:space="preserve">4.43540287017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50003480911255</t>
   </si>
   <si>
     <t xml:space="preserve">4.53881454467773</t>
@@ -2960,10 +2960,10 @@
     <t xml:space="preserve">4.61314249038696</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63253164291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60021543502808</t>
+    <t xml:space="preserve">4.63253211975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60021591186523</t>
   </si>
   <si>
     <t xml:space="preserve">4.55658864974976</t>
@@ -2975,13 +2975,13 @@
     <t xml:space="preserve">4.52588844299316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48064565658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53235149383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44832992553711</t>
+    <t xml:space="preserve">4.48064517974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53235197067261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44832944869995</t>
   </si>
   <si>
     <t xml:space="preserve">4.5048828125</t>
@@ -2996,37 +2996,37 @@
     <t xml:space="preserve">4.65838479995728</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68262147903442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65515327453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6438422203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70201206207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68585395812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7036280632019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66807985305786</t>
+    <t xml:space="preserve">4.68262195587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65515279769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64384269714355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7020115852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68585348129272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70362758636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6680793762207</t>
   </si>
   <si>
     <t xml:space="preserve">4.64545822143555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7262487411499</t>
+    <t xml:space="preserve">4.72624826431274</t>
   </si>
   <si>
     <t xml:space="preserve">4.76179695129395</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75048637390137</t>
+    <t xml:space="preserve">4.75048589706421</t>
   </si>
   <si>
     <t xml:space="preserve">4.84905052185059</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">4.87490367889404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88944530487061</t>
+    <t xml:space="preserve">4.88944625854492</t>
   </si>
   <si>
     <t xml:space="preserve">4.91853046417236</t>
@@ -3050,10 +3050,10 @@
     <t xml:space="preserve">4.66161632537842</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64061117172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72948026657104</t>
+    <t xml:space="preserve">4.64061069488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7294807434082</t>
   </si>
   <si>
     <t xml:space="preserve">4.74402284622192</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">4.74079132080078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79734516143799</t>
+    <t xml:space="preserve">4.79734468460083</t>
   </si>
   <si>
     <t xml:space="preserve">4.71655368804932</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">4.83450841903687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74563884735107</t>
+    <t xml:space="preserve">4.74563837051392</t>
   </si>
   <si>
     <t xml:space="preserve">4.50972986221313</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">4.62930059432983</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5598201751709</t>
+    <t xml:space="preserve">4.55982065200806</t>
   </si>
   <si>
     <t xml:space="preserve">4.54850959777832</t>
@@ -3107,31 +3107,31 @@
     <t xml:space="preserve">4.35299634933472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32068061828613</t>
+    <t xml:space="preserve">4.32068014144897</t>
   </si>
   <si>
     <t xml:space="preserve">4.55820465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51780939102173</t>
+    <t xml:space="preserve">4.51780891418457</t>
   </si>
   <si>
     <t xml:space="preserve">4.49518775939941</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41762828826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48872470855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43378686904907</t>
+    <t xml:space="preserve">4.4176287651062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48872518539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43378734588623</t>
   </si>
   <si>
     <t xml:space="preserve">4.70524311065674</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73028898239136</t>
+    <t xml:space="preserve">4.7302885055542</t>
   </si>
   <si>
     <t xml:space="preserve">4.68181419372559</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">4.77472305297852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89590883255005</t>
+    <t xml:space="preserve">4.89590930938721</t>
   </si>
   <si>
     <t xml:space="preserve">4.94034385681152</t>
@@ -3152,40 +3152,40 @@
     <t xml:space="preserve">4.91206693649292</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00497674942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04537153244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15039920806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08980703353882</t>
+    <t xml:space="preserve">5.00497627258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04537105560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15039968490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08980655670166</t>
   </si>
   <si>
     <t xml:space="preserve">5.0655689239502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9807391166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96054124832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99285745620728</t>
+    <t xml:space="preserve">4.98073959350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96054172515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99285793304443</t>
   </si>
   <si>
     <t xml:space="preserve">5.01709508895874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00093698501587</t>
+    <t xml:space="preserve">5.00093650817871</t>
   </si>
   <si>
     <t xml:space="preserve">5.01305532455444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97266054153442</t>
+    <t xml:space="preserve">4.97266006469727</t>
   </si>
   <si>
     <t xml:space="preserve">4.8999490737915</t>
@@ -3197,25 +3197,25 @@
     <t xml:space="preserve">4.92014646530151</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10596513748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05345058441162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16251850128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20222234725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11777019500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15577363967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18533134460449</t>
+    <t xml:space="preserve">5.10596466064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05345106124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16251802444458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20222187042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11777067184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15577411651611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18533182144165</t>
   </si>
   <si>
     <t xml:space="preserve">5.10088014602661</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">5.06287670135498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07554483413696</t>
+    <t xml:space="preserve">5.07554531097412</t>
   </si>
   <si>
     <t xml:space="preserve">5.02909660339355</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04598617553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02487325668335</t>
+    <t xml:space="preserve">5.04598665237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02487373352051</t>
   </si>
   <si>
     <t xml:space="preserve">4.87286043167114</t>
@@ -3248,13 +3248,13 @@
     <t xml:space="preserve">4.54772233963013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60261535644531</t>
+    <t xml:space="preserve">4.60261583328247</t>
   </si>
   <si>
     <t xml:space="preserve">4.53505373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71662521362305</t>
+    <t xml:space="preserve">4.71662473678589</t>
   </si>
   <si>
     <t xml:space="preserve">4.64906406402588</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">4.73773813247681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6912899017334</t>
+    <t xml:space="preserve">4.69128942489624</t>
   </si>
   <si>
     <t xml:space="preserve">4.72929286956787</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">4.61950540542603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61106061935425</t>
+    <t xml:space="preserve">4.61106014251709</t>
   </si>
   <si>
     <t xml:space="preserve">4.6068377494812</t>
@@ -3308,7 +3308,7 @@
     <t xml:space="preserve">4.51816368103027</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45482492446899</t>
+    <t xml:space="preserve">4.45482540130615</t>
   </si>
   <si>
     <t xml:space="preserve">4.38726377487183</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">4.46327018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59417009353638</t>
+    <t xml:space="preserve">4.59417057037354</t>
   </si>
   <si>
     <t xml:space="preserve">4.67017698287964</t>
@@ -3329,7 +3329,7 @@
     <t xml:space="preserve">4.61528301239014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62795066833496</t>
+    <t xml:space="preserve">4.62795114517212</t>
   </si>
   <si>
     <t xml:space="preserve">4.6575083732605</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">4.6363959312439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77996349334717</t>
+    <t xml:space="preserve">4.77996397018433</t>
   </si>
   <si>
     <t xml:space="preserve">4.80107641220093</t>
@@ -3353,10 +3353,10 @@
     <t xml:space="preserve">4.72506999969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77151918411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70817947387695</t>
+    <t xml:space="preserve">4.77151870727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70817995071411</t>
   </si>
   <si>
     <t xml:space="preserve">4.66173124313354</t>
@@ -3365,7 +3365,7 @@
     <t xml:space="preserve">4.53927659988403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47593832015991</t>
+    <t xml:space="preserve">4.47593784332275</t>
   </si>
   <si>
     <t xml:space="preserve">4.33659267425537</t>
@@ -3374,13 +3374,13 @@
     <t xml:space="preserve">4.31125688552856</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42104434967041</t>
+    <t xml:space="preserve">4.42104387283325</t>
   </si>
   <si>
     <t xml:space="preserve">4.29436683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33236980438232</t>
+    <t xml:space="preserve">4.33237028121948</t>
   </si>
   <si>
     <t xml:space="preserve">4.25636339187622</t>
@@ -3389,10 +3389,10 @@
     <t xml:space="preserve">4.39148569107056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41259908676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40415382385254</t>
+    <t xml:space="preserve">4.41259956359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4041543006897</t>
   </si>
   <si>
     <t xml:space="preserve">4.32392454147339</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">4.3197021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36192798614502</t>
+    <t xml:space="preserve">4.36192846298218</t>
   </si>
   <si>
     <t xml:space="preserve">4.27747631072998</t>
@@ -3416,10 +3416,10 @@
     <t xml:space="preserve">4.34503793716431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27325439453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14319849014282</t>
+    <t xml:space="preserve">4.27325391769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14319801330566</t>
   </si>
   <si>
     <t xml:space="preserve">4.07225894927979</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">4.02665519714355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03341150283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12630796432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22680568695068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1009726524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03678941726685</t>
+    <t xml:space="preserve">4.03341102600098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12630844116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22680616378784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10097217559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.036789894104</t>
   </si>
   <si>
     <t xml:space="preserve">4.02834415435791</t>
@@ -3452,10 +3452,10 @@
     <t xml:space="preserve">3.88984346389771</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84761786460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97091698646545</t>
+    <t xml:space="preserve">3.84761762619019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97091674804688</t>
   </si>
   <si>
     <t xml:space="preserve">4.06719160079956</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">4.04016733169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09421682357788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01483249664307</t>
+    <t xml:space="preserve">4.09421634674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01483201980591</t>
   </si>
   <si>
     <t xml:space="preserve">4.15333271026611</t>
@@ -3485,13 +3485,13 @@
     <t xml:space="preserve">4.43371200561523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56461191177368</t>
+    <t xml:space="preserve">4.56461238861084</t>
   </si>
   <si>
     <t xml:space="preserve">4.68706703186035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80952167510986</t>
+    <t xml:space="preserve">4.80952215194702</t>
   </si>
   <si>
     <t xml:space="preserve">4.75462818145752</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">4.73351573944092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75040531158447</t>
+    <t xml:space="preserve">4.75040578842163</t>
   </si>
   <si>
     <t xml:space="preserve">4.76307344436646</t>
@@ -3539,7 +3539,7 @@
     <t xml:space="preserve">4.51394081115723</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56883478164673</t>
+    <t xml:space="preserve">4.56883430480957</t>
   </si>
   <si>
     <t xml:space="preserve">4.78418684005737</t>
@@ -3548,13 +3548,13 @@
     <t xml:space="preserve">4.58994770050049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52238607406616</t>
+    <t xml:space="preserve">4.52238655090332</t>
   </si>
   <si>
     <t xml:space="preserve">4.62372827529907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48438262939453</t>
+    <t xml:space="preserve">4.48438310623169</t>
   </si>
   <si>
     <t xml:space="preserve">4.44215726852417</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">4.35348320007324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4252667427063</t>
+    <t xml:space="preserve">4.42526626586914</t>
   </si>
   <si>
     <t xml:space="preserve">4.47171497344971</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">4.90241813659668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9784255027771</t>
+    <t xml:space="preserve">4.97842502593994</t>
   </si>
   <si>
     <t xml:space="preserve">5.04176378250122</t>
@@ -3593,10 +3593,10 @@
     <t xml:space="preserve">5.09243488311768</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01220607757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98687076568604</t>
+    <t xml:space="preserve">5.01220560073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98687028884888</t>
   </si>
   <si>
     <t xml:space="preserve">4.91930913925171</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">5.00798320770264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86019277572632</t>
+    <t xml:space="preserve">4.86019325256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.94042158126831</t>
@@ -3626,25 +3626,25 @@
     <t xml:space="preserve">5.00376081466675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96998023986816</t>
+    <t xml:space="preserve">4.96998071670532</t>
   </si>
   <si>
     <t xml:space="preserve">4.83908033370972</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88975095748901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82535886764526</t>
+    <t xml:space="preserve">4.88975143432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82535934448242</t>
   </si>
   <si>
     <t xml:space="preserve">4.82981061935425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75858736038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66955852508545</t>
+    <t xml:space="preserve">4.75858783721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66955900192261</t>
   </si>
   <si>
     <t xml:space="preserve">4.71852493286133</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">4.78529596328735</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90993595123291</t>
+    <t xml:space="preserve">4.90993642807007</t>
   </si>
   <si>
     <t xml:space="preserve">4.95890283584595</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">4.93219375610352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9678053855896</t>
+    <t xml:space="preserve">4.96780490875244</t>
   </si>
   <si>
     <t xml:space="preserve">4.9989652633667</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">4.99006223678589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.869873046875</t>
+    <t xml:space="preserve">4.86987352371216</t>
   </si>
   <si>
     <t xml:space="preserve">4.95445108413696</t>
@@ -3689,19 +3689,19 @@
     <t xml:space="preserve">4.88322830200195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87432527542114</t>
+    <t xml:space="preserve">4.87432479858398</t>
   </si>
   <si>
     <t xml:space="preserve">4.80755376815796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75413608551025</t>
+    <t xml:space="preserve">4.75413656234741</t>
   </si>
   <si>
     <t xml:space="preserve">4.85206747055054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63839912414551</t>
+    <t xml:space="preserve">4.63839864730835</t>
   </si>
   <si>
     <t xml:space="preserve">4.60278749465942</t>
@@ -3716,19 +3716,19 @@
     <t xml:space="preserve">4.70517015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69626760482788</t>
+    <t xml:space="preserve">4.69626712799072</t>
   </si>
   <si>
     <t xml:space="preserve">4.68291330337524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74523305892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76303911209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77194213867188</t>
+    <t xml:space="preserve">4.7452335357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76303863525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77194166183472</t>
   </si>
   <si>
     <t xml:space="preserve">4.71407318115234</t>
@@ -3746,25 +3746,25 @@
     <t xml:space="preserve">4.57607841491699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55382108688354</t>
+    <t xml:space="preserve">4.5538215637207</t>
   </si>
   <si>
     <t xml:space="preserve">4.53156423568726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59388399124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64730167388916</t>
+    <t xml:space="preserve">4.59388446807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.647301197052</t>
   </si>
   <si>
     <t xml:space="preserve">4.66510725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6161413192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54936981201172</t>
+    <t xml:space="preserve">4.61614179611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54937028884888</t>
   </si>
   <si>
     <t xml:space="preserve">4.50485563278198</t>
@@ -3773,10 +3773,10 @@
     <t xml:space="preserve">4.500403881073</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49595308303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48705005645752</t>
+    <t xml:space="preserve">4.49595260620117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48704957962036</t>
   </si>
   <si>
     <t xml:space="preserve">4.70071887969971</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">4.73187923431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72297620773315</t>
+    <t xml:space="preserve">4.722975730896</t>
   </si>
   <si>
     <t xml:space="preserve">4.44609642028809</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">4.24489164352417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28228378295898</t>
+    <t xml:space="preserve">4.28228330612183</t>
   </si>
   <si>
     <t xml:space="preserve">4.31789493560791</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">4.34282302856445</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41226530075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4354133605957</t>
+    <t xml:space="preserve">4.41226577758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43541288375854</t>
   </si>
   <si>
     <t xml:space="preserve">4.42829084396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3926796913147</t>
+    <t xml:space="preserve">4.39267921447754</t>
   </si>
   <si>
     <t xml:space="preserve">4.45588970184326</t>
@@ -3857,22 +3857,22 @@
     <t xml:space="preserve">4.30186986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25201368331909</t>
+    <t xml:space="preserve">4.25201416015625</t>
   </si>
   <si>
     <t xml:space="preserve">4.26625823974609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27694177627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20928001403809</t>
+    <t xml:space="preserve">4.27694225311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20928049087524</t>
   </si>
   <si>
     <t xml:space="preserve">4.19147443771362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21996355056763</t>
+    <t xml:space="preserve">4.21996307373047</t>
   </si>
   <si>
     <t xml:space="preserve">4.27160024642944</t>
@@ -3902,16 +3902,16 @@
     <t xml:space="preserve">4.30899238586426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3054313659668</t>
+    <t xml:space="preserve">4.30543088912964</t>
   </si>
   <si>
     <t xml:space="preserve">4.39445972442627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40336275100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47369527816772</t>
+    <t xml:space="preserve">4.40336322784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47369575500488</t>
   </si>
   <si>
     <t xml:space="preserve">4.49150133132935</t>
@@ -3920,13 +3920,13 @@
     <t xml:space="preserve">4.46034145355225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43185234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5226616859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47814702987671</t>
+    <t xml:space="preserve">4.43185186386108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52266120910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47814750671387</t>
   </si>
   <si>
     <t xml:space="preserve">4.56717586517334</t>
@@ -3944,22 +3944,22 @@
     <t xml:space="preserve">4.61169004440308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5983362197876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55827283859253</t>
+    <t xml:space="preserve">4.59833574295044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55827236175537</t>
   </si>
   <si>
     <t xml:space="preserve">4.58053016662598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56272459030151</t>
+    <t xml:space="preserve">4.56272411346436</t>
   </si>
   <si>
     <t xml:space="preserve">4.5849814414978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54046678543091</t>
+    <t xml:space="preserve">4.54046726226807</t>
   </si>
   <si>
     <t xml:space="preserve">4.51375865936279</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">4.6918158531189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74968433380127</t>
+    <t xml:space="preserve">4.74968481063843</t>
   </si>
   <si>
     <t xml:space="preserve">4.4692440032959</t>
@@ -3998,16 +3998,16 @@
     <t xml:space="preserve">4.44787693023682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57162761688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79419898986816</t>
+    <t xml:space="preserve">4.57162714004517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79419946670532</t>
   </si>
   <si>
     <t xml:space="preserve">4.80310201644897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82090759277344</t>
+    <t xml:space="preserve">4.8209080696106</t>
   </si>
   <si>
     <t xml:space="preserve">4.77875137329102</t>
@@ -4956,6 +4956,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.48499965667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69499969482422</t>
   </si>
 </sst>
 </file>
@@ -65016,7 +65019,7 @@
     </row>
     <row r="2298">
       <c r="A2298" s="1" t="n">
-        <v>45980.6911689815</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2298" t="n">
         <v>2610623</v>
@@ -65037,6 +65040,32 @@
         <v>1647</v>
       </c>
       <c r="H2298" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" s="1" t="n">
+        <v>45981.6909837963</v>
+      </c>
+      <c r="B2299" t="n">
+        <v>2953903</v>
+      </c>
+      <c r="C2299" t="n">
+        <v>9.69499969482422</v>
+      </c>
+      <c r="D2299" t="n">
+        <v>9.47500038146973</v>
+      </c>
+      <c r="E2299" t="n">
+        <v>9.51000022888184</v>
+      </c>
+      <c r="F2299" t="n">
+        <v>9.69499969482422</v>
+      </c>
+      <c r="G2299" t="s">
+        <v>1648</v>
+      </c>
+      <c r="H2299" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IG.MI.xlsx
+++ b/data/IG.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="1649">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="1650">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,19 +44,19 @@
     <t xml:space="preserve">IG.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50135779380798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32790589332581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16488695144653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1727123260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09315896034241</t>
+    <t xml:space="preserve">2.5013575553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32790565490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16488742828369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17271208763123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09315919876099</t>
   </si>
   <si>
     <t xml:space="preserve">2.06185936927795</t>
@@ -65,19 +65,19 @@
     <t xml:space="preserve">2.08663845062256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0449059009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06055521965027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04360175132751</t>
+    <t xml:space="preserve">2.04490566253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06055545806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04360151290894</t>
   </si>
   <si>
     <t xml:space="preserve">2.10489630699158</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12967538833618</t>
+    <t xml:space="preserve">2.12967491149902</t>
   </si>
   <si>
     <t xml:space="preserve">2.14532494544983</t>
@@ -86,49 +86,49 @@
     <t xml:space="preserve">2.17923283576965</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2000994682312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20140337944031</t>
+    <t xml:space="preserve">2.20009899139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20140314102173</t>
   </si>
   <si>
     <t xml:space="preserve">2.17792868614197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13228321075439</t>
+    <t xml:space="preserve">2.13228368759155</t>
   </si>
   <si>
     <t xml:space="preserve">2.09837555885315</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22357392311096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29138994216919</t>
+    <t xml:space="preserve">2.22357368469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29138970375061</t>
   </si>
   <si>
     <t xml:space="preserve">2.33181834220886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29791045188904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23791933059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30051851272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30443096160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37094259262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34616422653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3957211971283</t>
+    <t xml:space="preserve">2.29791021347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2379195690155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30051875114441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30443120002747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37094306945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3461639881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39572167396545</t>
   </si>
   <si>
     <t xml:space="preserve">2.45571255683899</t>
@@ -137,22 +137,22 @@
     <t xml:space="preserve">2.39702582359314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38007164001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39441752433777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42180442810059</t>
+    <t xml:space="preserve">2.38007187843323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39441728591919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42180466651917</t>
   </si>
   <si>
     <t xml:space="preserve">2.41006731987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43093371391296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43745422363281</t>
+    <t xml:space="preserve">2.43093347549438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43745446205139</t>
   </si>
   <si>
     <t xml:space="preserve">2.48701190948486</t>
@@ -167,40 +167,40 @@
     <t xml:space="preserve">2.44527959823608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46614599227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43223786354065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44006299972534</t>
+    <t xml:space="preserve">2.46614575386047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43223762512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44006252288818</t>
   </si>
   <si>
     <t xml:space="preserve">2.47788286209106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43615031242371</t>
+    <t xml:space="preserve">2.43615007400513</t>
   </si>
   <si>
     <t xml:space="preserve">2.43354201316833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4570164680481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48831629753113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41789245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43484616279602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41267538070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35659742355347</t>
+    <t xml:space="preserve">2.45701622962952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48831605911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41789221763611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43484592437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41267561912537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35659718513489</t>
   </si>
   <si>
     <t xml:space="preserve">2.27573990821838</t>
@@ -215,19 +215,19 @@
     <t xml:space="preserve">2.38137602806091</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40876293182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3931131362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44919157028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46744966506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47397041320801</t>
+    <t xml:space="preserve">2.40876340866089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39311289787292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44919180870056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46744990348816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47397065162659</t>
   </si>
   <si>
     <t xml:space="preserve">2.48440361022949</t>
@@ -236,22 +236,22 @@
     <t xml:space="preserve">2.4635374546051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47266674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47136235237122</t>
+    <t xml:space="preserve">2.47266626358032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47136211395264</t>
   </si>
   <si>
     <t xml:space="preserve">2.4478874206543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49614095687866</t>
+    <t xml:space="preserve">2.49614119529724</t>
   </si>
   <si>
     <t xml:space="preserve">2.49744534492493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51570320129395</t>
+    <t xml:space="preserve">2.51570343971252</t>
   </si>
   <si>
     <t xml:space="preserve">2.53135323524475</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">2.51439929008484</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53656983375549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52744078636169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54830694198608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55091500282288</t>
+    <t xml:space="preserve">2.53656959533691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52744030952454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5483067035675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55091547966003</t>
   </si>
   <si>
     <t xml:space="preserve">2.5378737449646</t>
@@ -278,25 +278,25 @@
     <t xml:space="preserve">2.58612751960754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57699799537659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59786486625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60438561439514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57308554649353</t>
+    <t xml:space="preserve">2.57699823379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59786462783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60438513755798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57308602333069</t>
   </si>
   <si>
     <t xml:space="preserve">2.66959285736084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68393850326538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69828414916992</t>
+    <t xml:space="preserve">2.68393874168396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6982843875885</t>
   </si>
   <si>
     <t xml:space="preserve">2.64872646331787</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">2.64742231369019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68133020401001</t>
+    <t xml:space="preserve">2.68133044242859</t>
   </si>
   <si>
     <t xml:space="preserve">2.67480969429016</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">2.63438081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64350962638855</t>
+    <t xml:space="preserve">2.64350986480713</t>
   </si>
   <si>
     <t xml:space="preserve">2.69567561149597</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">2.67872166633606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73480010032654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.772620677948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75436234474182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71262955665588</t>
+    <t xml:space="preserve">2.73480033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77262020111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7543625831604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71262979507446</t>
   </si>
   <si>
     <t xml:space="preserve">2.70089268684387</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">2.70219659805298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66176795959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7830536365509</t>
+    <t xml:space="preserve">2.66176772117615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78305387496948</t>
   </si>
   <si>
     <t xml:space="preserve">2.7452335357666</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">2.69306755065918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71915078163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70610904693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74914622306824</t>
+    <t xml:space="preserve">2.71915054321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70610928535461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74914598464966</t>
   </si>
   <si>
     <t xml:space="preserve">2.77783727645874</t>
@@ -377,19 +377,19 @@
     <t xml:space="preserve">2.88738560676575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89651465415955</t>
+    <t xml:space="preserve">2.89651441574097</t>
   </si>
   <si>
     <t xml:space="preserve">2.8534779548645</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91477251052856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00867128372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02040934562683</t>
+    <t xml:space="preserve">2.91477274894714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0086715221405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02040886878967</t>
   </si>
   <si>
     <t xml:space="preserve">2.96824288368225</t>
@@ -398,76 +398,76 @@
     <t xml:space="preserve">3.00736737251282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05822920799255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09885382652283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15591311454773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09613680839539</t>
+    <t xml:space="preserve">3.05822944641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09885406494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15591287612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09613728523254</t>
   </si>
   <si>
     <t xml:space="preserve">3.13825178146362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09070301055908</t>
+    <t xml:space="preserve">3.0907027721405</t>
   </si>
   <si>
     <t xml:space="preserve">2.97658467292786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13417649269104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20074486732483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24965286254883</t>
+    <t xml:space="preserve">3.13417625427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20074534416199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24965310096741</t>
   </si>
   <si>
     <t xml:space="preserve">3.28769278526306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23063349723816</t>
+    <t xml:space="preserve">3.23063325881958</t>
   </si>
   <si>
     <t xml:space="preserve">3.24557757377625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22248220443726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25101208686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1871600151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0947790145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11379814147949</t>
+    <t xml:space="preserve">3.22248196601868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25101161003113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18715953826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09477853775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11379861831665</t>
   </si>
   <si>
     <t xml:space="preserve">3.19938683509827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10428810119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12059092521667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15727186203003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16270637512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14504456520081</t>
+    <t xml:space="preserve">3.10428857803345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12059116363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15727114677429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16270565986633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14504528045654</t>
   </si>
   <si>
     <t xml:space="preserve">3.03907799720764</t>
@@ -476,31 +476,31 @@
     <t xml:space="preserve">3.02820944786072</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96707463264465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00375533103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03636026382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02005839347839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97794270515442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98609471321106</t>
+    <t xml:space="preserve">2.96707439422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00375580787659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03636074066162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02005815505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.977942943573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9860942363739</t>
   </si>
   <si>
     <t xml:space="preserve">2.99560403823853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07575845718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0839102268219</t>
+    <t xml:space="preserve">3.07575869560242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08390998840332</t>
   </si>
   <si>
     <t xml:space="preserve">3.12466669082642</t>
@@ -512,139 +512,139 @@
     <t xml:space="preserve">3.12874221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17900848388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17221593856812</t>
+    <t xml:space="preserve">3.1790087223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17221570014954</t>
   </si>
   <si>
     <t xml:space="preserve">3.12602543830872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15863013267517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22519946098328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26052165031433</t>
+    <t xml:space="preserve">3.15863037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2251992225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26052141189575</t>
   </si>
   <si>
     <t xml:space="preserve">3.25237035751343</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27682447433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30671262741089</t>
+    <t xml:space="preserve">3.27682375907898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30671238899231</t>
   </si>
   <si>
     <t xml:space="preserve">3.30263662338257</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2808997631073</t>
+    <t xml:space="preserve">3.28090023994446</t>
   </si>
   <si>
     <t xml:space="preserve">3.21025514602661</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28361701965332</t>
+    <t xml:space="preserve">3.2836172580719</t>
   </si>
   <si>
     <t xml:space="preserve">3.29856133460999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28225779533386</t>
+    <t xml:space="preserve">3.28225827217102</t>
   </si>
   <si>
     <t xml:space="preserve">3.26323866844177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25644612312317</t>
+    <t xml:space="preserve">3.25644564628601</t>
   </si>
   <si>
     <t xml:space="preserve">3.27003145217896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24693655967712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23335099220276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21976518630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24150133132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26188039779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2347092628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19802832603455</t>
+    <t xml:space="preserve">3.24693608283997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2333505153656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21976494789124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24150204658508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26187968254089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23470973968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19802808761597</t>
   </si>
   <si>
     <t xml:space="preserve">3.23742604255676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24829459190369</t>
+    <t xml:space="preserve">3.24829506874084</t>
   </si>
   <si>
     <t xml:space="preserve">3.22791600227356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1939525604248</t>
+    <t xml:space="preserve">3.19395279884338</t>
   </si>
   <si>
     <t xml:space="preserve">3.16542315483093</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18444275856018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18172574043274</t>
+    <t xml:space="preserve">3.18444323539734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18172526359558</t>
   </si>
   <si>
     <t xml:space="preserve">3.20753836631775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24014329910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26731443405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24286031723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.226557970047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23199200630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20617938041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14640355110168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16814017295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10157108306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16678142547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21704792976379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22927522659302</t>
+    <t xml:space="preserve">3.24014377593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26731395721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2428605556488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22655749320984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23199224472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20617961883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14640331268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16813993453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10157132148743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16678166389465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21704816818237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22927498817444</t>
   </si>
   <si>
     <t xml:space="preserve">3.24421906471252</t>
@@ -656,52 +656,52 @@
     <t xml:space="preserve">3.25372886657715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35154485702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49147534370422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3936595916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46430420875549</t>
+    <t xml:space="preserve">3.35154461860657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49147486686707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39365935325623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46430444717407</t>
   </si>
   <si>
     <t xml:space="preserve">3.50506114959717</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41675519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40656542778015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44732189178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43373608589172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42694449424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47109746932983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46770071983337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48128604888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50166440010071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5424211025238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51185393333435</t>
+    <t xml:space="preserve">3.41675496101379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40656590461731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44732213020325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43373680114746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42694401741028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47109699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46770095825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48128581047058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50166392326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54242086410522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51185369491577</t>
   </si>
   <si>
     <t xml:space="preserve">3.54581737518311</t>
@@ -710,100 +710,100 @@
     <t xml:space="preserve">3.55940246582031</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63412308692932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60015916824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53223180770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48468232154846</t>
+    <t xml:space="preserve">3.6341233253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60015940666199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53223133087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48468279838562</t>
   </si>
   <si>
     <t xml:space="preserve">3.55261039733887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61374521255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52543926239014</t>
+    <t xml:space="preserve">3.61374497413635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52543878555298</t>
   </si>
   <si>
     <t xml:space="preserve">3.58997011184692</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60355496406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5933666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62053751945496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59676313400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5661952495575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53562808036804</t>
+    <t xml:space="preserve">3.60355544090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59336638450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62053728103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59676289558411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56619548797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53562784194946</t>
   </si>
   <si>
     <t xml:space="preserve">3.45411515235901</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45751166343689</t>
+    <t xml:space="preserve">3.45751142501831</t>
   </si>
   <si>
     <t xml:space="preserve">3.39637660980225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32301497459412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38279128074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40996193885803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38958430290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32844877243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30807089805603</t>
+    <t xml:space="preserve">3.3230152130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38279104232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40996170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38958382606506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32844948768616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30807065963745</t>
   </si>
   <si>
     <t xml:space="preserve">3.31078791618347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35018587112427</t>
+    <t xml:space="preserve">3.35018610954285</t>
   </si>
   <si>
     <t xml:space="preserve">3.3759982585907</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35426163673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37328124046326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34339308738708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36648893356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37871527671814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36105442047119</t>
+    <t xml:space="preserve">3.35426211357117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37328147888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34339332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36648845672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37871551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36105465888977</t>
   </si>
   <si>
     <t xml:space="preserve">3.12126970291138</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">3.16406440734863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06624889373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04587078094482</t>
+    <t xml:space="preserve">3.06624865531921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04587054252625</t>
   </si>
   <si>
     <t xml:space="preserve">3.03228521347046</t>
@@ -824,25 +824,25 @@
     <t xml:space="preserve">3.00239706039429</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02209568023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02549242973328</t>
+    <t xml:space="preserve">3.0220959186554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0254921913147</t>
   </si>
   <si>
     <t xml:space="preserve">3.04655003547668</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9942455291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96164059638977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97862267494202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092646598816</t>
+    <t xml:space="preserve">2.99424576759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96164035797119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97862243652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092622756958</t>
   </si>
   <si>
     <t xml:space="preserve">3.11651515960693</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">3.00035905838013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96639537811279</t>
+    <t xml:space="preserve">2.96639561653137</t>
   </si>
   <si>
     <t xml:space="preserve">2.92903518676758</t>
@@ -863,70 +863,70 @@
     <t xml:space="preserve">2.92495965957642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01326537132263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0940990447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1430070400238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23538827896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22723698616028</t>
+    <t xml:space="preserve">3.01326489448547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09409928321838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14300680160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23538851737976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2272367477417</t>
   </si>
   <si>
     <t xml:space="preserve">3.21297216415405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19327354431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27342796325684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29448485374451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20414161682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30739164352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28565454483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36377143859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39909410476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47924828529358</t>
+    <t xml:space="preserve">3.19327306747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27342748641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29448533058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20414185523987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30739140510559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28565502166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36377191543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39909386634827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47924852371216</t>
   </si>
   <si>
     <t xml:space="preserve">3.47517228126526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48196578025818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43713331222534</t>
+    <t xml:space="preserve">3.48196530342102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43713283538818</t>
   </si>
   <si>
     <t xml:space="preserve">3.44392585754395</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49962615966797</t>
+    <t xml:space="preserve">3.49962639808655</t>
   </si>
   <si>
     <t xml:space="preserve">3.528156042099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47788906097412</t>
+    <t xml:space="preserve">3.47788977622986</t>
   </si>
   <si>
     <t xml:space="preserve">3.51456999778748</t>
@@ -935,28 +935,28 @@
     <t xml:space="preserve">3.45887017250061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52679777145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52000498771667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5757052898407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6273307800293</t>
+    <t xml:space="preserve">3.52679681777954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5200047492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57570552825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62733101844788</t>
   </si>
   <si>
     <t xml:space="preserve">3.64499115943909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60423493385315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60287618637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62597131729126</t>
+    <t xml:space="preserve">3.60423469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60287642478943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.625972032547</t>
   </si>
   <si>
     <t xml:space="preserve">3.49419236183167</t>
@@ -965,175 +965,175 @@
     <t xml:space="preserve">3.45615267753601</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41539669036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45479440689087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44256734848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36309266090393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39298033714294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39462018013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4540011882782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46107006072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36280798912048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28151249885559</t>
+    <t xml:space="preserve">3.41539645195007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45479464530945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44256711006165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36309242248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39298009872437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39461994171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45400071144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46107029914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36280822753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28151273727417</t>
   </si>
   <si>
     <t xml:space="preserve">3.23414897918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07367920875549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15285396575928</t>
+    <t xml:space="preserve">3.07367897033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16699194908142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1528537273407</t>
   </si>
   <si>
     <t xml:space="preserve">3.18961358070374</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27868509292603</t>
+    <t xml:space="preserve">3.2786853313446</t>
   </si>
   <si>
     <t xml:space="preserve">3.25747752189636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23556351661682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23768377304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20163106918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34089422225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43774199485779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39037752151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41087889671326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37623977661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38967108726501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40946507453918</t>
+    <t xml:space="preserve">3.2355637550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23768401145935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20163083076477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34089398384094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43774151802063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39037823677063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4108784198761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37624025344849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38967132568359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40946531295776</t>
   </si>
   <si>
     <t xml:space="preserve">3.46319055557251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33735942840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31544518470764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29989290237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34442853927612</t>
+    <t xml:space="preserve">3.33735966682434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31544470787048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29989266395569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34442830085754</t>
   </si>
   <si>
     <t xml:space="preserve">3.35432529449463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32958316802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33806610107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29211616516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3564465045929</t>
+    <t xml:space="preserve">3.32958340644836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3380663394928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29211711883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35644578933716</t>
   </si>
   <si>
     <t xml:space="preserve">3.3522047996521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40098166465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41865491867065</t>
+    <t xml:space="preserve">3.40098214149475</t>
